--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -1088,12 +1088,12 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Max PS 7 Max PS+ 2 Details Submit by in 10 days Expiry in 17 days Coins Cost 35,000 Points Cost 250</t>
+          <t>Excluded Rarity World Tour Silver Stars Max PS 7 Max PS+ 2 Details Submit by in 9 days Expiry in 16 days Coins Cost 35,000 Points Cost 250</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Max PS 7 Max PS+ 2 Details Submit by in 10 days Expiry in 17 days Coins Cost 35,000 Points Cost 250</t>
+          <t>Excluded Rarity World Tour Silver Stars Max PS 7 Max PS+ 2 Details Submit by in 9 days Expiry in 16 days Coins Cost 35,000 Points Cost 250</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>Maestro Unbound NEW 35,000 250 2 Unlock the true playmaking abilities of a player by adding all passing PlayStyles. Pelé 96 CAM PAC 94 SHO 96 PAS 92 DRI 95 DEF 60 PHY 75 ST R 5 ★ 4 CAM 90.6 Pelé 96 CAM PAC 94 SHO 96 PAS 92 DRI 95 DEF 60 PHY 75 ST R 5 ★ 4 CAM 92.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max PS 7 Max PS+ 2 UPGRADES 8 in 10 days in 17 days 25% 75%</t>
+          <t>Maestro Unbound NEW 35,000 250 2 Unlock the true playmaking abilities of a player by adding all passing PlayStyles. Pelé 96 CAM PAC 94 SHO 96 PAS 92 DRI 95 DEF 60 PHY 75 ST R 5 ★ 4 CAM 90.6 Pelé 96 CAM PAC 94 SHO 96 PAS 92 DRI 95 DEF 60 PHY 75 ST R 5 ★ 4 CAM 92.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max PS 7 Max PS+ 2 UPGRADES 8 in 9 days in 16 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position GK Max PS 10 Max PS+ 2 Details Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position GK Max PS 10 Max PS+ 2 Details Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position GK Max PS 10 Max PS+ 2 Details Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position GK Max PS 10 Max PS+ 2 Details Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>Cat Like Reflexes Elevate your goalkeeper with elite-level reactions boosts designed to turn split-second moments into match-winning saves. Casillas 90 GK DIV 90 HAN 88 KIC 84 REF 93 SPD 59 POS 88 L 1 ★ 3 GK 83.1 Casillas 92 GK DIV 90 HAN 91 KIC 90 REF 94 SPD 69 POS 92 L 1 ★ 4 GK 87.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position GK Max PS 10 Max PS+ 2 UPGRADES +15 OVR 92 +15 POS 92 +1 WF +10 Acceleration 82 +10 Sprint Speed 82 +25 Reactions 93 +15 Diving 90 +15 Handling 91 +15 Kicking 90 +15 Reflexes 94 GK Goalkeeper ++ GK Ball Playing Keeper ++ GK Sweeper Keeper ++ 2 8 Show less in 9 days in 16 days 90% 10%</t>
+          <t>Cat Like Reflexes Elevate your goalkeeper with elite-level reactions boosts designed to turn split-second moments into match-winning saves. Casillas 90 GK DIV 90 HAN 88 KIC 84 REF 93 SPD 59 POS 88 L 1 ★ 3 GK 83.1 Casillas 92 GK DIV 90 HAN 91 KIC 90 REF 94 SPD 69 POS 92 L 1 ★ 4 GK 87.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position GK Max PS 10 Max PS+ 2 UPGRADES +15 OVR 92 +15 POS 92 +1 WF +10 Acceleration 82 +10 Sprint Speed 82 +25 Reactions 93 +15 Diving 90 +15 Handling 91 +15 Kicking 90 +15 Reflexes 94 GK Goalkeeper ++ GK Ball Playing Keeper ++ GK Sweeper Keeper ++ 2 8 Show less in 8 days in 15 days 90% 10%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position CB Max PS 10 Max PS+ 2 Heading Accuracy Max. 94 Details Submit by in 8 days Expiry in 15 days Coins Cost 125,000 Points Cost 750</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position CB Max PS 10 Max PS+ 2 Heading Accuracy Max. 94 Details Submit by in 7 days Expiry in 14 days Coins Cost 125,000 Points Cost 750</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position CB Max PS 10 Max PS+ 2 Heading Accuracy Max. 94 Details Submit by in 8 days Expiry in 15 days Coins Cost 125,000 Points Cost 750</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position CB Max PS 10 Max PS+ 2 Heading Accuracy Max. 94 Details Submit by in 7 days Expiry in 14 days Coins Cost 125,000 Points Cost 750</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>Le Président 125,000 750 Transform your CB with the defensive excellence that made Laurent Blanc one of the greatest. Cool, composed, and unbeatable. Laporte 90 CB PAC 85 SHO 60 PAS 87 DRI 84 DEF 91 PHY 90 L 5 ★ 5 CB 79.3 Laporte 92 CB PAC 88 SHO 61 PAS 87 DRI 89 DEF 93 PHY 92 L 5 ★ 5 CB 91.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position CB Max PS 10 Max PS+ 2 Heading Accuracy Max. 94 UPGRADES +20 OVR 92 +3 WF 4 +30 Composure 92 +25 Aggression 90 +30 Short Pass 90 +30 Reactions 92 +30 Defensive Awareness 93 +30 Interceptions 92 +25 Stamina 90 +30 Heading Acc. 90 +20 Dribbling 87 +20 Sprint Speed 90 +25 Strength 91 +20 Balance 87 +25 Penalties 94 +30 Standing Tackle 94 +20 Acceleration 86 +20 Agility 88 +30 Long Pass 90 +25 Jumping 88 +30 Sliding Tackle 92 +30 Ball Control 92 3 7 in 8 days in 15 days 59% 41%</t>
+          <t>Le Président 125,000 750 Transform your CB with the defensive excellence that made Laurent Blanc one of the greatest. Cool, composed, and unbeatable. Laporte 90 CB PAC 85 SHO 60 PAS 87 DRI 84 DEF 91 PHY 90 L 5 ★ 5 CB 79.3 Laporte 92 CB PAC 88 SHO 61 PAS 87 DRI 89 DEF 93 PHY 92 L 5 ★ 5 CB 91.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position CB Max PS 10 Max PS+ 2 Heading Accuracy Max. 94 UPGRADES +20 OVR 92 +3 WF 4 +30 Composure 92 +25 Aggression 90 +30 Short Pass 90 +30 Reactions 92 +30 Defensive Awareness 93 +30 Interceptions 92 +25 Stamina 90 +30 Heading Acc. 90 +20 Dribbling 87 +20 Sprint Speed 90 +25 Strength 91 +20 Balance 87 +25 Penalties 94 +30 Standing Tackle 94 +20 Acceleration 86 +20 Agility 88 +30 Long Pass 90 +25 Jumping 88 +30 Sliding Tackle 92 +30 Ball Control 92 3 7 in 7 days in 14 days 59% 41%</t>
         </is>
       </c>
     </row>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Details Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Details Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Details Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Details Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>Lucky Number Seven 3 Hit your stride with Lucky Number Seven and give your eligible player boosts across key stats. Riise 88 LB PAC 88 SHO 83 PAS 86 DRI 85 DEF 86 PHY 88 LM L 4 ★ 4 LB 88.2 Riise 89 LB PAC 88 SHO 83 PAS 88 DRI 89 DEF 86 PHY 91 LM L 4 ★ 4 LB 89.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 UPGRADES +1 OVR +7 Shot Power 95 +7 Vision 92 +7 Crossing 93 +7 Balance 90 +7 Dribbling 93 +7 Jumping 92 +7 Strength 92 in 7 days in 14 days 26% 74%</t>
+          <t>Lucky Number Seven 3 Hit your stride with Lucky Number Seven and give your eligible player boosts across key stats. Riise 88 LB PAC 88 SHO 83 PAS 86 DRI 85 DEF 86 PHY 88 LM L 4 ★ 4 LB 88.2 Riise 89 LB PAC 88 SHO 83 PAS 88 DRI 89 DEF 86 PHY 91 LM L 4 ★ 4 LB 89.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 UPGRADES +1 OVR +7 Shot Power 95 +7 Vision 92 +7 Crossing 93 +7 Balance 90 +7 Dribbling 93 +7 Jumping 92 +7 Strength 92 in 6 days in 13 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Max Pos. 3 Overall Max. 89 Position RB Excluded Position CB Max PS 10 Max PS+ 2 Details Submit by in 6 days Expiry in 13 days Coins Cost 35,000 Points Cost 200</t>
+          <t>Excluded Rarity World Tour Silver Stars Max Pos. 3 Overall Max. 89 Position RB Excluded Position CB Max PS 10 Max PS+ 2 Details Submit by in 5 days Expiry in 12 days Coins Cost 35,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Max Pos. 3 Overall Max. 89 Position RB Excluded Position CB Max PS 10 Max PS+ 2 Details Submit by in 6 days Expiry in 13 days Coins Cost 35,000 Points Cost 200</t>
+          <t>Excluded Rarity World Tour Silver Stars Max Pos. 3 Overall Max. 89 Position RB Excluded Position CB Max PS 10 Max PS+ 2 Details Submit by in 5 days Expiry in 12 days Coins Cost 35,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>Fullback Takeover 35,000 200 Speed at the back. Power in every duel. A certain alpine player once ruled the center with unexpected power. Shift the role, break the line, and rediscover that unstoppable edge. Kimmich 89 RB PAC 81 SHO 74 PAS 89 DRI 85 DEF 85 PHY 80 CDM CM R 3 ★ 4 RB 81.0 Kimmich 90 RB PAC 91 SHO 74 PAS 89 DRI 85 DEF 90 PHY 88 CB CDM CM R 3 ★ 4 RB 89.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max Pos. 3 Overall Max. 89 Position RB Excluded Position CB Max PS 10 Max PS+ 2 UPGRADES +15 OVR 90 +15 PAS 87 CB +2 WF 4 +20 Interceptions 91 +15 Strength 88 +20 Standing Tackle 90 +20 Defensive Awareness 91 +20 Stamina 92 +10 Composure 88 +10 Balance 86 +20 Acceleration 89 +15 Aggression 86 +20 Heading Acc. 83 +20 Sprint Speed 92 +10 Agility 88 +15 Jumping 88 +20 Sliding Tackle 93 +10 Reactions 88 3 7 Show less in 6 days in 13 days 22% 78%</t>
+          <t>Fullback Takeover 35,000 200 Speed at the back. Power in every duel. A certain alpine player once ruled the center with unexpected power. Shift the role, break the line, and rediscover that unstoppable edge. Kimmich 89 RB PAC 81 SHO 74 PAS 89 DRI 85 DEF 85 PHY 80 CDM CM R 3 ★ 4 RB 81.0 Kimmich 90 RB PAC 91 SHO 74 PAS 89 DRI 85 DEF 90 PHY 88 CB CDM CM R 3 ★ 4 RB 89.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max Pos. 3 Overall Max. 89 Position RB Excluded Position CB Max PS 10 Max PS+ 2 UPGRADES +15 OVR 90 +15 PAS 87 CB +2 WF 4 +20 Interceptions 91 +15 Strength 88 +20 Standing Tackle 90 +20 Defensive Awareness 91 +20 Stamina 92 +10 Composure 88 +10 Balance 86 +20 Acceleration 89 +15 Aggression 86 +20 Heading Acc. 83 +20 Sprint Speed 92 +10 Agility 88 +15 Jumping 88 +20 Sliding Tackle 93 +10 Reactions 88 3 7 Show less in 5 days in 12 days 22% 78%</t>
         </is>
       </c>
     </row>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 5 days Expiry in 12 days Coins Cost 75,000 Points Cost 400</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 11 days Coins Cost 75,000 Points Cost 400</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 5 days Expiry in 12 days Coins Cost 75,000 Points Cost 400</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 11 days Coins Cost 75,000 Points Cost 400</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>Gear 5 75,000 400 Hit the gear and let loose with +5 boosts across key stats. Bounce past rivals, stretch the game, and chase victory with a grin. Davies 89 LB PAC 95 SHO 80 PAS 84 DRI 87 DEF 82 PHY 84 LM L 4 ★ 3 LB 87.9 Davies 91 LB PAC 95 SHO 83 PAS 86 DRI 91 DEF 86 PHY 87 LM L 5 ★ 5 LB 91.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES +5 OVR 91 +4 SM +4 WF +5 Sliding Tackle 90 +5 Vision 91 +5 Sprint Speed 89 +5 Crossing 86 +5 Long Pass 90 +5 Interceptions 88 +5 Volleys 86 +5 Composure 87 +5 Heading Acc. 85 +5 Curve 90 +5 Agility 92 +5 Positioning 91 +5 Standing Tackle 86 +5 Finishing 89 +5 Reactions 90 +5 Balance 92 +5 Strength 86 +5 Short Pass 90 +5 Jumping 90 +5 Long Shots 87 +5 Stamina 90 +5 Defensive Awareness 86 +5 Ball Control 91 +5 Dribbling 92 +5 Aggression 86 +5 Shot Power 88 +5 Acceleration 89 in 5 days in 12 days 8% 92%</t>
+          <t>Gear 5 75,000 400 Hit the gear and let loose with +5 boosts across key stats. Bounce past rivals, stretch the game, and chase victory with a grin. Davies 89 LB PAC 95 SHO 80 PAS 84 DRI 87 DEF 82 PHY 84 LM L 4 ★ 3 LB 87.9 Davies 91 LB PAC 95 SHO 83 PAS 86 DRI 91 DEF 86 PHY 87 LM L 5 ★ 5 LB 91.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES +5 OVR 91 +4 SM +4 WF +5 Sliding Tackle 90 +5 Vision 91 +5 Sprint Speed 89 +5 Crossing 86 +5 Long Pass 90 +5 Interceptions 88 +5 Volleys 86 +5 Composure 87 +5 Heading Acc. 85 +5 Curve 90 +5 Agility 92 +5 Positioning 91 +5 Standing Tackle 86 +5 Finishing 89 +5 Reactions 90 +5 Balance 92 +5 Strength 86 +5 Short Pass 90 +5 Jumping 90 +5 Long Shots 87 +5 Stamina 90 +5 Defensive Awareness 86 +5 Ball Control 91 +5 Dribbling 92 +5 Aggression 86 +5 Shot Power 88 +5 Acceleration 89 in 4 days in 11 days 8% 92%</t>
         </is>
       </c>
     </row>
@@ -2458,12 +2458,12 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 74 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 74 Max PS 10 Max PS+ 2 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 74 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 74 Max PS 10 Max PS+ 2 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>Steel Guard 3 Cold as steel and impossible to break, dominates every duel, reads the game perfectly, and shuts down attacks before they even become a threat. Zima 74 CB PAC 76 SHO 38 PAS 54 DRI 62 DEF 75 PHY 75 R 2 ★ 4 CB 65.6 Zima 74 CB PAC 77 SHO 38 PAS 55 DRI 62 DEF 77 PHY 75 R 2 ★ 4 CB 75.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 74 Max PS 10 Max PS+ 2 UPGRADES +2 Sliding Tackle 78 +2 Short Pass 78 +2 Defensive Awareness 80 +2 Interceptions 80 +1 Jumping 75 +1 Sprint Speed 80 +2 Standing Tackle 80 +1 Acceleration 80 +1 Strength 78 +2 Vision 72 +1 Aggression 75 +1 Stamina 78 +2 Heading Acc. 76 2 8 in 4 days in 11 days 7% 93%</t>
+          <t>Steel Guard 3 Cold as steel and impossible to break, dominates every duel, reads the game perfectly, and shuts down attacks before they even become a threat. Zima 74 CB PAC 76 SHO 38 PAS 54 DRI 62 DEF 75 PHY 75 R 2 ★ 4 CB 65.6 Zima 74 CB PAC 77 SHO 38 PAS 55 DRI 62 DEF 77 PHY 75 R 2 ★ 4 CB 75.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 74 Max PS 10 Max PS+ 2 UPGRADES +2 Sliding Tackle 78 +2 Short Pass 78 +2 Defensive Awareness 80 +2 Interceptions 80 +1 Jumping 75 +1 Sprint Speed 80 +2 Standing Tackle 80 +1 Acceleration 80 +1 Strength 78 +2 Vision 72 +1 Aggression 75 +1 Stamina 78 +2 Heading Acc. 76 2 8 in 3 days in 10 days 7% 93%</t>
         </is>
       </c>
     </row>
@@ -2723,12 +2723,12 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Position LB Excluded Position CB Max PS 10 Max PS+ 2 Details Submit by in 3 days Expiry in 10 days Coins Cost 50,000 Points Cost 300</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Position LB Excluded Position CB Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 9 days Coins Cost 50,000 Points Cost 300</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Position LB Excluded Position CB Max PS 10 Max PS+ 2 Details Submit by in 3 days Expiry in 10 days Coins Cost 50,000 Points Cost 300</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Position LB Excluded Position CB Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 9 days Coins Cost 50,000 Points Cost 300</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>Lightning Wingback 50,000 300 Lightning-fast wingback to dominate the flank. Explosive pace, relentless overlaps, and pinpoint delivery. A constant threat in attack while tracking back with power and precision. Savona 83 RB PAC 84 SHO 57 PAS 75 DRI 76 DEF 83 PHY 83 LB RM R 2 ★ 3 RB 80.1 Savona 91 RB PAC 93 SHO 64 PAS 81 DRI 90 DEF 90 PHY 92 LB RM R 2 ★ 5 RB 94.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Position LB Excluded Position CB Max PS 10 Max PS+ 2 UPGRADES +30 OVR 91 +4 WF +35 Standing Tackle 87 +25 Aggression 92 +30 Sprint Speed 93 +50 Positioning 90 +30 Crossing 94 +30 Composure 89 +30 Acceleration 93 +30 Dribbling 89 +35 Interceptions 92 +30 Short Pass 92 +50 Long Pass 93 +35 Defensive Awareness 90 +30 Balance 90 +30 Agility 90 +20 Stamina 94 +50 Shot Power 94 +35 Sliding Tackle 95 +20 Jumping 90 +35 Heading Acc. 92 +30 Reactions 93 +30 Ball Control 90 +25 Strength 91 3 7 in 3 days in 10 days 91% 9%</t>
+          <t>Lightning Wingback 50,000 300 Lightning-fast wingback to dominate the flank. Explosive pace, relentless overlaps, and pinpoint delivery. A constant threat in attack while tracking back with power and precision. Savona 83 RB PAC 84 SHO 57 PAS 75 DRI 76 DEF 83 PHY 83 LB RM R 2 ★ 3 RB 80.1 Savona 91 RB PAC 93 SHO 64 PAS 81 DRI 90 DEF 90 PHY 92 LB RM R 2 ★ 5 RB 94.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Position LB Excluded Position CB Max PS 10 Max PS+ 2 UPGRADES +30 OVR 91 +4 WF +35 Standing Tackle 87 +25 Aggression 92 +30 Sprint Speed 93 +50 Positioning 90 +30 Crossing 94 +30 Composure 89 +30 Acceleration 93 +30 Dribbling 89 +35 Interceptions 92 +30 Short Pass 92 +50 Long Pass 93 +35 Defensive Awareness 90 +30 Balance 90 +30 Agility 90 +20 Stamina 94 +50 Shot Power 94 +35 Sliding Tackle 95 +20 Jumping 90 +35 Heading Acc. 92 +30 Reactions 93 +30 Ball Control 90 +25 Strength 91 3 7 in 2 days in 9 days 91% 9%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 Details Submit by in 2 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 Details Submit by in 1 day Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 Details Submit by in 2 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 Details Submit by in 1 day Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>Curve Your Enthusiasm 5 Bend the game to your will and create moments of magic by transforming a player into a ball-bending specialist. Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 90 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 UPGRADES +3 Positioning 90 +5 Finishing 92 +5 Long Shots 92 +3 Shot Power 90 +8 Curve 95 8 in 2 days in 9 days 31% 69%</t>
+          <t>Curve Your Enthusiasm 5 Bend the game to your will and create moments of magic by transforming a player into a ball-bending specialist. Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 90 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 UPGRADES +3 Positioning 90 +5 Finishing 92 +5 Long Shots 92 +3 Shot Power 90 +8 Curve 95 8 in 1 day in 8 days 31% 69%</t>
         </is>
       </c>
     </row>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 13 hours Expiry in 8 days Coins Cost 100,000 Points Cost 500</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 11 hours Expiry in 7 days Coins Cost 100,000 Points Cost 500</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 13 hours Expiry in 8 days Coins Cost 100,000 Points Cost 500</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 11 hours Expiry in 7 days Coins Cost 100,000 Points Cost 500</t>
         </is>
       </c>
       <c r="CZ11" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>Cut In, Say Less 100,000 500 Elevate your favourite qualified player with enhanced pace, dribbling, shooting, and passing, allowing them to cut inside, get past defenders, and deliver in decisive moments! Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 92 RW PAC 92 SHO 90 PAS 92 DRI 93 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 93.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 in 13 hours in 8 days 64% 36%</t>
+          <t>Cut In, Say Less 100,000 500 Elevate your favourite qualified player with enhanced pace, dribbling, shooting, and passing, allowing them to cut inside, get past defenders, and deliver in decisive moments! Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 92 RW PAC 92 SHO 90 PAS 92 DRI 93 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 93.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 in 11 hours in 7 days 64% 36%</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="DA17" t="inlineStr">
         <is>
-          <t>Rapid+ Unlocked by completing the Assist in 10 task in the Ligue 1 TOTS Exhibition objective Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 84.0 Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 85.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 9 days in 9 days 92% 8%</t>
+          <t>Rapid+ Unlocked by completing the Assist in 10 task in the Ligue 1 TOTS Exhibition objective Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 84.0 Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 85.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 9 days in 9 days 91% 9%</t>
         </is>
       </c>
     </row>
@@ -7082,12 +7082,12 @@
       </c>
       <c r="CX34" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 87 Max PS 10 Max PS+ 2 Details Submit by in 3 days Expiry in 3 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 87 Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY34" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 87 Max PS 10 Max PS+ 2 Details Submit by in 3 days Expiry in 3 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 87 Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ34" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="DA34" t="inlineStr">
         <is>
-          <t>Welsh Wonder Strike [Store] Unlocked by purchasing the Captains' Armband EVO pack. Lukaku 85 CAM PAC 84 SHO 86 PAS 80 DRI 81 DEF 42 PHY 85 ST L 4 ★ 4 ST 80.4 Lukaku 89 CAM PAC 92 SHO 90 PAS 86 DRI 89 DEF 42 PHY 85 ST L 4 ★ 4 ST 90.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 87 Max PS 10 Max PS+ 2 UPGRADES +15 OVR 89 +25 Acceleration 90 +20 Shot Power 90 +10 Vision 87 +25 Composure 88 +25 Sprint Speed 93 +20 Long Shots 90 +10 Long Pass 87 +25 Dribbling 90 +20 Positioning 89 +20 Volleys 93 +15 Short Pass 88 +25 Ball Control 89 +30 Jumping 92 +20 Finishing 90 +10 Crossing 86 +15 Curve 89 +25 Reactions 90 +20 Heading Acc. 87 +20 Penalties 87 +15 Fk Accuracy 88 +25 Agility 88 +25 Balance 87 2 8 TRAINING TIME 31 minutes in 3 days in 3 days 18% 82%</t>
+          <t>Welsh Wonder Strike [Store] Unlocked by purchasing the Captains' Armband EVO pack. Lukaku 85 CAM PAC 84 SHO 86 PAS 80 DRI 81 DEF 42 PHY 85 ST L 4 ★ 4 ST 80.4 Lukaku 89 CAM PAC 92 SHO 90 PAS 86 DRI 89 DEF 42 PHY 85 ST L 4 ★ 4 ST 90.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 87 Max PS 10 Max PS+ 2 UPGRADES +15 OVR 89 +25 Acceleration 90 +20 Shot Power 90 +10 Vision 87 +25 Composure 88 +25 Sprint Speed 93 +20 Long Shots 90 +10 Long Pass 87 +25 Dribbling 90 +20 Positioning 89 +20 Volleys 93 +15 Short Pass 88 +25 Ball Control 89 +30 Jumping 92 +20 Finishing 90 +10 Crossing 86 +15 Curve 89 +25 Reactions 90 +20 Heading Acc. 87 +20 Penalties 87 +15 Fk Accuracy 88 +25 Agility 88 +25 Balance 87 2 8 TRAINING TIME 31 minutes in 2 days in 2 days 18% 82%</t>
         </is>
       </c>
     </row>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="CX35" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Position CB Excluded Position CM Max PS 10 Max PS+ 2 Pace Max. 90 Details Submit by in 3 days Expiry in 3 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Position CB Excluded Position CM Max PS 10 Max PS+ 2 Pace Max. 90 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY35" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Position CB Excluded Position CM Max PS 10 Max PS+ 2 Pace Max. 90 Details Submit by in 3 days Expiry in 3 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Position CB Excluded Position CM Max PS 10 Max PS+ 2 Pace Max. 90 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ35" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="DA35" t="inlineStr">
         <is>
-          <t>Il Capitano [Store] Unlocked by purchasing the Captains' Armband EVO pack. Lawrence 70 CB PAC 60 SHO 26 PAS 49 DRI 46 DEF 70 PHY 73 R 2 ★ 2 CB 62.3 Lawrence 91 CB PAC 88 SHO 26 PAS 68 DRI 72 DEF 93 PHY 90 R 2 ★ 2 CB 92.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Position CB Excluded Position CM Max PS 10 Max PS+ 2 Pace Max. 90 UPGRADES +30 OVR 91 +30 Acceleration 87 +30 Short Pass 90 +30 Heading Acc. 92 +30 Defensive Awareness 95 +30 Sprint Speed 88 +30 Vision 70 +30 Agility 73 +30 Balance 80 +30 Long Pass 85 +30 Ball Control 75 +30 Dribbling 75 +30 Reactions 95 +30 Composure 91 +30 Interceptions 93 +30 Standing Tackle 92 +30 Sliding Tackle 92 +30 Stamina 90 +30 Strength 92 +30 Jumping 90 +30 Aggression 85 CB Defender ++ CB Stopper ++ CB Wideback ++ 2 8 in 3 days in 3 days 19% 81%</t>
+          <t>Il Capitano [Store] Unlocked by purchasing the Captains' Armband EVO pack. Lawrence 70 CB PAC 60 SHO 26 PAS 49 DRI 46 DEF 70 PHY 73 R 2 ★ 2 CB 62.3 Lawrence 91 CB PAC 88 SHO 26 PAS 68 DRI 72 DEF 93 PHY 90 R 2 ★ 2 CB 92.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Position CB Excluded Position CM Max PS 10 Max PS+ 2 Pace Max. 90 UPGRADES +30 OVR 91 +30 Acceleration 87 +30 Short Pass 90 +30 Heading Acc. 92 +30 Defensive Awareness 95 +30 Sprint Speed 88 +30 Vision 70 +30 Agility 73 +30 Balance 80 +30 Long Pass 85 +30 Ball Control 75 +30 Dribbling 75 +30 Reactions 95 +30 Composure 91 +30 Interceptions 93 +30 Standing Tackle 92 +30 Sliding Tackle 92 +30 Stamina 90 +30 Strength 92 +30 Jumping 90 +30 Aggression 85 CB Defender ++ CB Stopper ++ CB Wideback ++ 2 8 in 2 days in 2 days 19% 81%</t>
         </is>
       </c>
     </row>
@@ -65689,7 +65689,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Maestro Unbound NEW 35,000 250 2 Unlock the true playmaking abilities of a player by adding all passing PlayStyles. Pelé 96 CAM PAC 94 SHO 96 PAS 92 DRI 95 DEF 60 PHY 75 ST R 5 ★ 4 CAM 90.6 Pelé 96 CAM PAC 94 SHO 96 PAS 92 DRI 95 DEF 60 PHY 75 ST R 5 ★ 4 CAM 92.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max PS 7 Max PS+ 2 UPGRADES 8 in 10 days in 17 days 25% 75%</t>
+          <t>Maestro Unbound NEW 35,000 250 2 Unlock the true playmaking abilities of a player by adding all passing PlayStyles. Pelé 96 CAM PAC 94 SHO 96 PAS 92 DRI 95 DEF 60 PHY 75 ST R 5 ★ 4 CAM 90.6 Pelé 96 CAM PAC 94 SHO 96 PAS 92 DRI 95 DEF 60 PHY 75 ST R 5 ★ 4 CAM 92.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max PS 7 Max PS+ 2 UPGRADES 8 in 9 days in 16 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -65716,7 +65716,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cat Like Reflexes Elevate your goalkeeper with elite-level reactions boosts designed to turn split-second moments into match-winning saves. Casillas 90 GK DIV 90 HAN 88 KIC 84 REF 93 SPD 59 POS 88 L 1 ★ 3 GK 83.1 Casillas 92 GK DIV 90 HAN 91 KIC 90 REF 94 SPD 69 POS 92 L 1 ★ 4 GK 87.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position GK Max PS 10 Max PS+ 2 UPGRADES +15 OVR 92 +15 POS 92 +1 WF +10 Acceleration 82 +10 Sprint Speed 82 +25 Reactions 93 +15 Diving 90 +15 Handling 91 +15 Kicking 90 +15 Reflexes 94 GK Goalkeeper ++ GK Ball Playing Keeper ++ GK Sweeper Keeper ++ 2 8 Show less in 9 days in 16 days 90% 10%</t>
+          <t>Cat Like Reflexes Elevate your goalkeeper with elite-level reactions boosts designed to turn split-second moments into match-winning saves. Casillas 90 GK DIV 90 HAN 88 KIC 84 REF 93 SPD 59 POS 88 L 1 ★ 3 GK 83.1 Casillas 92 GK DIV 90 HAN 91 KIC 90 REF 94 SPD 69 POS 92 L 1 ★ 4 GK 87.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position GK Max PS 10 Max PS+ 2 UPGRADES +15 OVR 92 +15 POS 92 +1 WF +10 Acceleration 82 +10 Sprint Speed 82 +25 Reactions 93 +15 Diving 90 +15 Handling 91 +15 Kicking 90 +15 Reflexes 94 GK Goalkeeper ++ GK Ball Playing Keeper ++ GK Sweeper Keeper ++ 2 8 Show less in 8 days in 15 days 90% 10%</t>
         </is>
       </c>
     </row>
@@ -65743,7 +65743,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Le Président 125,000 750 Transform your CB with the defensive excellence that made Laurent Blanc one of the greatest. Cool, composed, and unbeatable. Laporte 90 CB PAC 85 SHO 60 PAS 87 DRI 84 DEF 91 PHY 90 L 5 ★ 5 CB 79.3 Laporte 92 CB PAC 88 SHO 61 PAS 87 DRI 89 DEF 93 PHY 92 L 5 ★ 5 CB 91.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position CB Max PS 10 Max PS+ 2 Heading Accuracy Max. 94 UPGRADES +20 OVR 92 +3 WF 4 +30 Composure 92 +25 Aggression 90 +30 Short Pass 90 +30 Reactions 92 +30 Defensive Awareness 93 +30 Interceptions 92 +25 Stamina 90 +30 Heading Acc. 90 +20 Dribbling 87 +20 Sprint Speed 90 +25 Strength 91 +20 Balance 87 +25 Penalties 94 +30 Standing Tackle 94 +20 Acceleration 86 +20 Agility 88 +30 Long Pass 90 +25 Jumping 88 +30 Sliding Tackle 92 +30 Ball Control 92 3 7 in 8 days in 15 days 59% 41%</t>
+          <t>Le Président 125,000 750 Transform your CB with the defensive excellence that made Laurent Blanc one of the greatest. Cool, composed, and unbeatable. Laporte 90 CB PAC 85 SHO 60 PAS 87 DRI 84 DEF 91 PHY 90 L 5 ★ 5 CB 79.3 Laporte 92 CB PAC 88 SHO 61 PAS 87 DRI 89 DEF 93 PHY 92 L 5 ★ 5 CB 91.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position CB Max PS 10 Max PS+ 2 Heading Accuracy Max. 94 UPGRADES +20 OVR 92 +3 WF 4 +30 Composure 92 +25 Aggression 90 +30 Short Pass 90 +30 Reactions 92 +30 Defensive Awareness 93 +30 Interceptions 92 +25 Stamina 90 +30 Heading Acc. 90 +20 Dribbling 87 +20 Sprint Speed 90 +25 Strength 91 +20 Balance 87 +25 Penalties 94 +30 Standing Tackle 94 +20 Acceleration 86 +20 Agility 88 +30 Long Pass 90 +25 Jumping 88 +30 Sliding Tackle 92 +30 Ball Control 92 3 7 in 7 days in 14 days 59% 41%</t>
         </is>
       </c>
     </row>
@@ -65770,7 +65770,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lucky Number Seven 3 Hit your stride with Lucky Number Seven and give your eligible player boosts across key stats. Riise 88 LB PAC 88 SHO 83 PAS 86 DRI 85 DEF 86 PHY 88 LM L 4 ★ 4 LB 88.2 Riise 89 LB PAC 88 SHO 83 PAS 88 DRI 89 DEF 86 PHY 91 LM L 4 ★ 4 LB 89.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 UPGRADES +1 OVR +7 Shot Power 95 +7 Vision 92 +7 Crossing 93 +7 Balance 90 +7 Dribbling 93 +7 Jumping 92 +7 Strength 92 in 7 days in 14 days 26% 74%</t>
+          <t>Lucky Number Seven 3 Hit your stride with Lucky Number Seven and give your eligible player boosts across key stats. Riise 88 LB PAC 88 SHO 83 PAS 86 DRI 85 DEF 86 PHY 88 LM L 4 ★ 4 LB 88.2 Riise 89 LB PAC 88 SHO 83 PAS 88 DRI 89 DEF 86 PHY 91 LM L 4 ★ 4 LB 89.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 UPGRADES +1 OVR +7 Shot Power 95 +7 Vision 92 +7 Crossing 93 +7 Balance 90 +7 Dribbling 93 +7 Jumping 92 +7 Strength 92 in 6 days in 13 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -65797,7 +65797,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fullback Takeover 35,000 200 Speed at the back. Power in every duel. A certain alpine player once ruled the center with unexpected power. Shift the role, break the line, and rediscover that unstoppable edge. Kimmich 89 RB PAC 81 SHO 74 PAS 89 DRI 85 DEF 85 PHY 80 CDM CM R 3 ★ 4 RB 81.0 Kimmich 90 RB PAC 91 SHO 74 PAS 89 DRI 85 DEF 90 PHY 88 CB CDM CM R 3 ★ 4 RB 89.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max Pos. 3 Overall Max. 89 Position RB Excluded Position CB Max PS 10 Max PS+ 2 UPGRADES +15 OVR 90 +15 PAS 87 CB +2 WF 4 +20 Interceptions 91 +15 Strength 88 +20 Standing Tackle 90 +20 Defensive Awareness 91 +20 Stamina 92 +10 Composure 88 +10 Balance 86 +20 Acceleration 89 +15 Aggression 86 +20 Heading Acc. 83 +20 Sprint Speed 92 +10 Agility 88 +15 Jumping 88 +20 Sliding Tackle 93 +10 Reactions 88 3 7 Show less in 6 days in 13 days 22% 78%</t>
+          <t>Fullback Takeover 35,000 200 Speed at the back. Power in every duel. A certain alpine player once ruled the center with unexpected power. Shift the role, break the line, and rediscover that unstoppable edge. Kimmich 89 RB PAC 81 SHO 74 PAS 89 DRI 85 DEF 85 PHY 80 CDM CM R 3 ★ 4 RB 81.0 Kimmich 90 RB PAC 91 SHO 74 PAS 89 DRI 85 DEF 90 PHY 88 CB CDM CM R 3 ★ 4 RB 89.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max Pos. 3 Overall Max. 89 Position RB Excluded Position CB Max PS 10 Max PS+ 2 UPGRADES +15 OVR 90 +15 PAS 87 CB +2 WF 4 +20 Interceptions 91 +15 Strength 88 +20 Standing Tackle 90 +20 Defensive Awareness 91 +20 Stamina 92 +10 Composure 88 +10 Balance 86 +20 Acceleration 89 +15 Aggression 86 +20 Heading Acc. 83 +20 Sprint Speed 92 +10 Agility 88 +15 Jumping 88 +20 Sliding Tackle 93 +10 Reactions 88 3 7 Show less in 5 days in 12 days 22% 78%</t>
         </is>
       </c>
     </row>
@@ -65824,7 +65824,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gear 5 75,000 400 Hit the gear and let loose with +5 boosts across key stats. Bounce past rivals, stretch the game, and chase victory with a grin. Davies 89 LB PAC 95 SHO 80 PAS 84 DRI 87 DEF 82 PHY 84 LM L 4 ★ 3 LB 87.9 Davies 91 LB PAC 95 SHO 83 PAS 86 DRI 91 DEF 86 PHY 87 LM L 5 ★ 5 LB 91.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES +5 OVR 91 +4 SM +4 WF +5 Sliding Tackle 90 +5 Vision 91 +5 Sprint Speed 89 +5 Crossing 86 +5 Long Pass 90 +5 Interceptions 88 +5 Volleys 86 +5 Composure 87 +5 Heading Acc. 85 +5 Curve 90 +5 Agility 92 +5 Positioning 91 +5 Standing Tackle 86 +5 Finishing 89 +5 Reactions 90 +5 Balance 92 +5 Strength 86 +5 Short Pass 90 +5 Jumping 90 +5 Long Shots 87 +5 Stamina 90 +5 Defensive Awareness 86 +5 Ball Control 91 +5 Dribbling 92 +5 Aggression 86 +5 Shot Power 88 +5 Acceleration 89 in 5 days in 12 days 8% 92%</t>
+          <t>Gear 5 75,000 400 Hit the gear and let loose with +5 boosts across key stats. Bounce past rivals, stretch the game, and chase victory with a grin. Davies 89 LB PAC 95 SHO 80 PAS 84 DRI 87 DEF 82 PHY 84 LM L 4 ★ 3 LB 87.9 Davies 91 LB PAC 95 SHO 83 PAS 86 DRI 91 DEF 86 PHY 87 LM L 5 ★ 5 LB 91.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES +5 OVR 91 +4 SM +4 WF +5 Sliding Tackle 90 +5 Vision 91 +5 Sprint Speed 89 +5 Crossing 86 +5 Long Pass 90 +5 Interceptions 88 +5 Volleys 86 +5 Composure 87 +5 Heading Acc. 85 +5 Curve 90 +5 Agility 92 +5 Positioning 91 +5 Standing Tackle 86 +5 Finishing 89 +5 Reactions 90 +5 Balance 92 +5 Strength 86 +5 Short Pass 90 +5 Jumping 90 +5 Long Shots 87 +5 Stamina 90 +5 Defensive Awareness 86 +5 Ball Control 91 +5 Dribbling 92 +5 Aggression 86 +5 Shot Power 88 +5 Acceleration 89 in 4 days in 11 days 8% 92%</t>
         </is>
       </c>
     </row>
@@ -65851,7 +65851,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Steel Guard 3 Cold as steel and impossible to break, dominates every duel, reads the game perfectly, and shuts down attacks before they even become a threat. Zima 74 CB PAC 76 SHO 38 PAS 54 DRI 62 DEF 75 PHY 75 R 2 ★ 4 CB 65.6 Zima 74 CB PAC 77 SHO 38 PAS 55 DRI 62 DEF 77 PHY 75 R 2 ★ 4 CB 75.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 74 Max PS 10 Max PS+ 2 UPGRADES +2 Sliding Tackle 78 +2 Short Pass 78 +2 Defensive Awareness 80 +2 Interceptions 80 +1 Jumping 75 +1 Sprint Speed 80 +2 Standing Tackle 80 +1 Acceleration 80 +1 Strength 78 +2 Vision 72 +1 Aggression 75 +1 Stamina 78 +2 Heading Acc. 76 2 8 in 4 days in 11 days 7% 93%</t>
+          <t>Steel Guard 3 Cold as steel and impossible to break, dominates every duel, reads the game perfectly, and shuts down attacks before they even become a threat. Zima 74 CB PAC 76 SHO 38 PAS 54 DRI 62 DEF 75 PHY 75 R 2 ★ 4 CB 65.6 Zima 74 CB PAC 77 SHO 38 PAS 55 DRI 62 DEF 77 PHY 75 R 2 ★ 4 CB 75.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 74 Max PS 10 Max PS+ 2 UPGRADES +2 Sliding Tackle 78 +2 Short Pass 78 +2 Defensive Awareness 80 +2 Interceptions 80 +1 Jumping 75 +1 Sprint Speed 80 +2 Standing Tackle 80 +1 Acceleration 80 +1 Strength 78 +2 Vision 72 +1 Aggression 75 +1 Stamina 78 +2 Heading Acc. 76 2 8 in 3 days in 10 days 7% 93%</t>
         </is>
       </c>
     </row>
@@ -65878,7 +65878,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lightning Wingback 50,000 300 Lightning-fast wingback to dominate the flank. Explosive pace, relentless overlaps, and pinpoint delivery. A constant threat in attack while tracking back with power and precision. Savona 83 RB PAC 84 SHO 57 PAS 75 DRI 76 DEF 83 PHY 83 LB RM R 2 ★ 3 RB 80.1 Savona 91 RB PAC 93 SHO 64 PAS 81 DRI 90 DEF 90 PHY 92 LB RM R 2 ★ 5 RB 94.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Position LB Excluded Position CB Max PS 10 Max PS+ 2 UPGRADES +30 OVR 91 +4 WF +35 Standing Tackle 87 +25 Aggression 92 +30 Sprint Speed 93 +50 Positioning 90 +30 Crossing 94 +30 Composure 89 +30 Acceleration 93 +30 Dribbling 89 +35 Interceptions 92 +30 Short Pass 92 +50 Long Pass 93 +35 Defensive Awareness 90 +30 Balance 90 +30 Agility 90 +20 Stamina 94 +50 Shot Power 94 +35 Sliding Tackle 95 +20 Jumping 90 +35 Heading Acc. 92 +30 Reactions 93 +30 Ball Control 90 +25 Strength 91 3 7 in 3 days in 10 days 91% 9%</t>
+          <t>Lightning Wingback 50,000 300 Lightning-fast wingback to dominate the flank. Explosive pace, relentless overlaps, and pinpoint delivery. A constant threat in attack while tracking back with power and precision. Savona 83 RB PAC 84 SHO 57 PAS 75 DRI 76 DEF 83 PHY 83 LB RM R 2 ★ 3 RB 80.1 Savona 91 RB PAC 93 SHO 64 PAS 81 DRI 90 DEF 90 PHY 92 LB RM R 2 ★ 5 RB 94.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Position LB Excluded Position CB Max PS 10 Max PS+ 2 UPGRADES +30 OVR 91 +4 WF +35 Standing Tackle 87 +25 Aggression 92 +30 Sprint Speed 93 +50 Positioning 90 +30 Crossing 94 +30 Composure 89 +30 Acceleration 93 +30 Dribbling 89 +35 Interceptions 92 +30 Short Pass 92 +50 Long Pass 93 +35 Defensive Awareness 90 +30 Balance 90 +30 Agility 90 +20 Stamina 94 +50 Shot Power 94 +35 Sliding Tackle 95 +20 Jumping 90 +35 Heading Acc. 92 +30 Reactions 93 +30 Ball Control 90 +25 Strength 91 3 7 in 2 days in 9 days 91% 9%</t>
         </is>
       </c>
     </row>
@@ -65905,7 +65905,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Curve Your Enthusiasm 5 Bend the game to your will and create moments of magic by transforming a player into a ball-bending specialist. Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 90 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 UPGRADES +3 Positioning 90 +5 Finishing 92 +5 Long Shots 92 +3 Shot Power 90 +8 Curve 95 8 in 2 days in 9 days 31% 69%</t>
+          <t>Curve Your Enthusiasm 5 Bend the game to your will and create moments of magic by transforming a player into a ball-bending specialist. Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 90 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 UPGRADES +3 Positioning 90 +5 Finishing 92 +5 Long Shots 92 +3 Shot Power 90 +8 Curve 95 8 in 1 day in 8 days 31% 69%</t>
         </is>
       </c>
     </row>
@@ -65932,7 +65932,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cut In, Say Less 100,000 500 Elevate your favourite qualified player with enhanced pace, dribbling, shooting, and passing, allowing them to cut inside, get past defenders, and deliver in decisive moments! Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 92 RW PAC 92 SHO 90 PAS 92 DRI 93 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 93.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 in 13 hours in 8 days 64% 36%</t>
+          <t>Cut In, Say Less 100,000 500 Elevate your favourite qualified player with enhanced pace, dribbling, shooting, and passing, allowing them to cut inside, get past defenders, and deliver in decisive moments! Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 92 RW PAC 92 SHO 90 PAS 92 DRI 93 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 93.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 in 11 hours in 7 days 64% 36%</t>
         </is>
       </c>
     </row>
@@ -66094,7 +66094,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rapid+ Unlocked by completing the Assist in 10 task in the Ligue 1 TOTS Exhibition objective Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 84.0 Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 85.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 9 days in 9 days 92% 8%</t>
+          <t>Rapid+ Unlocked by completing the Assist in 10 task in the Ligue 1 TOTS Exhibition objective Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 84.0 Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 85.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 9 days in 9 days 91% 9%</t>
         </is>
       </c>
     </row>
@@ -66553,7 +66553,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Welsh Wonder Strike [Store] Unlocked by purchasing the Captains' Armband EVO pack. Lukaku 85 CAM PAC 84 SHO 86 PAS 80 DRI 81 DEF 42 PHY 85 ST L 4 ★ 4 ST 80.4 Lukaku 89 CAM PAC 92 SHO 90 PAS 86 DRI 89 DEF 42 PHY 85 ST L 4 ★ 4 ST 90.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 87 Max PS 10 Max PS+ 2 UPGRADES +15 OVR 89 +25 Acceleration 90 +20 Shot Power 90 +10 Vision 87 +25 Composure 88 +25 Sprint Speed 93 +20 Long Shots 90 +10 Long Pass 87 +25 Dribbling 90 +20 Positioning 89 +20 Volleys 93 +15 Short Pass 88 +25 Ball Control 89 +30 Jumping 92 +20 Finishing 90 +10 Crossing 86 +15 Curve 89 +25 Reactions 90 +20 Heading Acc. 87 +20 Penalties 87 +15 Fk Accuracy 88 +25 Agility 88 +25 Balance 87 2 8 TRAINING TIME 31 minutes in 3 days in 3 days 18% 82%</t>
+          <t>Welsh Wonder Strike [Store] Unlocked by purchasing the Captains' Armband EVO pack. Lukaku 85 CAM PAC 84 SHO 86 PAS 80 DRI 81 DEF 42 PHY 85 ST L 4 ★ 4 ST 80.4 Lukaku 89 CAM PAC 92 SHO 90 PAS 86 DRI 89 DEF 42 PHY 85 ST L 4 ★ 4 ST 90.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 87 Max PS 10 Max PS+ 2 UPGRADES +15 OVR 89 +25 Acceleration 90 +20 Shot Power 90 +10 Vision 87 +25 Composure 88 +25 Sprint Speed 93 +20 Long Shots 90 +10 Long Pass 87 +25 Dribbling 90 +20 Positioning 89 +20 Volleys 93 +15 Short Pass 88 +25 Ball Control 89 +30 Jumping 92 +20 Finishing 90 +10 Crossing 86 +15 Curve 89 +25 Reactions 90 +20 Heading Acc. 87 +20 Penalties 87 +15 Fk Accuracy 88 +25 Agility 88 +25 Balance 87 2 8 TRAINING TIME 31 minutes in 2 days in 2 days 18% 82%</t>
         </is>
       </c>
     </row>
@@ -66580,7 +66580,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Il Capitano [Store] Unlocked by purchasing the Captains' Armband EVO pack. Lawrence 70 CB PAC 60 SHO 26 PAS 49 DRI 46 DEF 70 PHY 73 R 2 ★ 2 CB 62.3 Lawrence 91 CB PAC 88 SHO 26 PAS 68 DRI 72 DEF 93 PHY 90 R 2 ★ 2 CB 92.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Position CB Excluded Position CM Max PS 10 Max PS+ 2 Pace Max. 90 UPGRADES +30 OVR 91 +30 Acceleration 87 +30 Short Pass 90 +30 Heading Acc. 92 +30 Defensive Awareness 95 +30 Sprint Speed 88 +30 Vision 70 +30 Agility 73 +30 Balance 80 +30 Long Pass 85 +30 Ball Control 75 +30 Dribbling 75 +30 Reactions 95 +30 Composure 91 +30 Interceptions 93 +30 Standing Tackle 92 +30 Sliding Tackle 92 +30 Stamina 90 +30 Strength 92 +30 Jumping 90 +30 Aggression 85 CB Defender ++ CB Stopper ++ CB Wideback ++ 2 8 in 3 days in 3 days 19% 81%</t>
+          <t>Il Capitano [Store] Unlocked by purchasing the Captains' Armband EVO pack. Lawrence 70 CB PAC 60 SHO 26 PAS 49 DRI 46 DEF 70 PHY 73 R 2 ★ 2 CB 62.3 Lawrence 91 CB PAC 88 SHO 26 PAS 68 DRI 72 DEF 93 PHY 90 R 2 ★ 2 CB 92.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Position CB Excluded Position CM Max PS 10 Max PS+ 2 Pace Max. 90 UPGRADES +30 OVR 91 +30 Acceleration 87 +30 Short Pass 90 +30 Heading Acc. 92 +30 Defensive Awareness 95 +30 Sprint Speed 88 +30 Vision 70 +30 Agility 73 +30 Balance 80 +30 Long Pass 85 +30 Ball Control 75 +30 Dribbling 75 +30 Reactions 95 +30 Composure 91 +30 Interceptions 93 +30 Standing Tackle 92 +30 Sliding Tackle 92 +30 Stamina 90 +30 Strength 92 +30 Jumping 90 +30 Aggression 85 CB Defender ++ CB Stopper ++ CB Wideback ++ 2 8 in 2 days in 2 days 19% 81%</t>
         </is>
       </c>
     </row>
@@ -68136,7 +68136,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-11T04:11:09</t>
+          <t>2026-05-11T06:00:54</t>
         </is>
       </c>
     </row>

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -3145,12 +3145,12 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 11 hours Expiry in 7 days Coins Cost 100,000 Points Cost 500</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 10 hours Expiry in 7 days Coins Cost 100,000 Points Cost 500</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 11 hours Expiry in 7 days Coins Cost 100,000 Points Cost 500</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 10 hours Expiry in 7 days Coins Cost 100,000 Points Cost 500</t>
         </is>
       </c>
       <c r="CZ11" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>Cut In, Say Less 100,000 500 Elevate your favourite qualified player with enhanced pace, dribbling, shooting, and passing, allowing them to cut inside, get past defenders, and deliver in decisive moments! Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 92 RW PAC 92 SHO 90 PAS 92 DRI 93 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 93.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 in 11 hours in 7 days 64% 36%</t>
+          <t>Cut In, Say Less 100,000 500 Elevate your favourite qualified player with enhanced pace, dribbling, shooting, and passing, allowing them to cut inside, get past defenders, and deliver in decisive moments! Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 92 RW PAC 92 SHO 90 PAS 92 DRI 93 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 93.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 in 10 hours in 7 days 64% 36%</t>
         </is>
       </c>
     </row>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 6 days Expiry in 6 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY16" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 6 days Expiry in 6 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ16" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="DA16" t="inlineStr">
         <is>
-          <t>Tiki Taka Unlocked by completing the Score 5 task in the French TOTS Flash Rush objective Rijkaard 89 CDM PAC 84 SHO 80 PAS 85 DRI 86 DEF 89 PHY 88 CB CM R 4 ★ 4 CDM 87.2 Rijkaard 89 CDM PAC 84 SHO 80 PAS 85 DRI 86 DEF 89 PHY 88 CB CM R 4 ★ 4 CDM 88.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 6 days in 6 days 5% 95%</t>
+          <t>Tiki Taka Unlocked by completing the Score 5 task in the French TOTS Flash Rush objective Rijkaard 89 CDM PAC 84 SHO 80 PAS 85 DRI 86 DEF 89 PHY 88 CB CM R 4 ★ 4 CDM 87.2 Rijkaard 89 CDM PAC 84 SHO 80 PAS 85 DRI 86 DEF 89 PHY 88 CB CM R 4 ★ 4 CDM 88.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 5 days in 5 days 5% 95%</t>
         </is>
       </c>
     </row>
@@ -4171,12 +4171,12 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY17" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ17" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="DA17" t="inlineStr">
         <is>
-          <t>Rapid+ Unlocked by completing the Assist in 10 task in the Ligue 1 TOTS Exhibition objective Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 84.0 Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 85.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 9 days in 9 days 91% 9%</t>
+          <t>Rapid+ Unlocked by completing the Assist in 10 task in the Ligue 1 TOTS Exhibition objective Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 84.0 Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 85.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 8 days in 8 days 91% 9%</t>
         </is>
       </c>
     </row>
@@ -4330,12 +4330,12 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY18" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ18" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="DA18" t="inlineStr">
         <is>
-          <t>First Touch+ Unlocked by completing the Score in 10 task in the Ligue 1 TOTS Exhibition objective Nanasi 89 LM PAC 89 SHO 87 PAS 89 DRI 91 DEF 45 PHY 80 CM CAM R 5 ★ 4 CAM 89.6 Nanasi 89 LM PAC 89 SHO 87 PAS 89 DRI 91 DEF 45 PHY 80 CM CAM R 5 ★ 4 CAM 90.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 9 days in 9 days 62% 38%</t>
+          <t>First Touch+ Unlocked by completing the Score in 10 task in the Ligue 1 TOTS Exhibition objective Nanasi 89 LM PAC 89 SHO 87 PAS 89 DRI 91 DEF 45 PHY 80 CM CAM R 5 ★ 4 CAM 89.6 Nanasi 89 LM PAC 89 SHO 87 PAS 89 DRI 91 DEF 45 PHY 80 CM CAM R 5 ★ 4 CAM 90.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 8 days in 8 days 62% 38%</t>
         </is>
       </c>
     </row>
@@ -4489,12 +4489,12 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 6 days Expiry in 6 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY19" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 6 days Expiry in 6 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ19" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="DA19" t="inlineStr">
         <is>
-          <t>Tiki Taka and Low Driven Shot Unlocked by completing the Score in 5 task in the TOTS: Champions Objective objective Luna 89 LM PAC 89 SHO 87 PAS 90 DRI 90 DEF 60 PHY 85 CAM LW R 4 ★ 5 CAM 86.2 Luna 89 LM PAC 89 SHO 87 PAS 90 DRI 90 DEF 60 PHY 85 CAM LW R 4 ★ 5 CAM 88.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 6 days in 6 days 9% 91%</t>
+          <t>Tiki Taka and Low Driven Shot Unlocked by completing the Score in 5 task in the TOTS: Champions Objective objective Luna 89 LM PAC 89 SHO 87 PAS 90 DRI 90 DEF 60 PHY 85 CAM LW R 4 ★ 5 CAM 86.2 Luna 89 LM PAC 89 SHO 87 PAS 90 DRI 90 DEF 60 PHY 85 CAM LW R 4 ★ 5 CAM 88.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 5 days in 5 days 9% 91%</t>
         </is>
       </c>
     </row>
@@ -4648,12 +4648,12 @@
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 6 days Expiry in 6 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY20" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 6 days Expiry in 6 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ20" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="DA20" t="inlineStr">
         <is>
-          <t>Intercept and Pinged Pass Unlocked by completing the Win 4 task in the TOTS: Champions Objective objective ter Stegen 89 GK DIV 87 HAN 87 KIC 91 REF 89 SPD 53 POS 87 R 1 ★ 4 GK 85.9 ter Stegen 89 GK DIV 87 HAN 87 KIC 91 REF 89 SPD 53 POS 87 R 1 ★ 4 GK 87.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 6 days in 6 days 8% 92%</t>
+          <t>Intercept and Pinged Pass Unlocked by completing the Win 4 task in the TOTS: Champions Objective objective ter Stegen 89 GK DIV 87 HAN 87 KIC 91 REF 89 SPD 53 POS 87 R 1 ★ 4 GK 85.9 ter Stegen 89 GK DIV 87 HAN 87 KIC 91 REF 89 SPD 53 POS 87 R 1 ★ 4 GK 87.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 5 days in 5 days 8% 92%</t>
         </is>
       </c>
     </row>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY21" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ21" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="DA21" t="inlineStr">
         <is>
-          <t>Jockey+ &amp; Bruiser+ Unlocked by completing the 3 Completions task in the Season 7 Spirit of Africa Weekly Play Completionist objective Dumfries 89 RB PAC 89 SHO 75 PAS 84 DRI 86 DEF 86 PHY 89 RM R 4 ★ 3 RB 85.3 Dumfries 89 RB PAC 89 SHO 75 PAS 84 DRI 86 DEF 86 PHY 89 RM R 4 ★ 3 RB 87.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 29 days in 29 days 12% 88%</t>
+          <t>Jockey+ &amp; Bruiser+ Unlocked by completing the 3 Completions task in the Season 7 Spirit of Africa Weekly Play Completionist objective Dumfries 89 RB PAC 89 SHO 75 PAS 84 DRI 86 DEF 86 PHY 89 RM R 4 ★ 3 RB 85.3 Dumfries 89 RB PAC 89 SHO 75 PAS 84 DRI 86 DEF 86 PHY 89 RM R 4 ★ 3 RB 87.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 28 days in 28 days 12% 88%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Min Pos. 2 Overall Max. 89 Position CB, LB, RB Max PS 10 Max PS+ 2 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Min Pos. 2 Overall Max. 89 Position CB, LB, RB Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY22" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Min Pos. 2 Overall Max. 89 Position CB, LB, RB Max PS 10 Max PS+ 2 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Min Pos. 2 Overall Max. 89 Position CB, LB, RB Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ22" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="DA22" t="inlineStr">
         <is>
-          <t>Versatile Defender Unlocked by completing the Darwin Cup objective Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 84.9 Walker 90 RB PAC 91 SHO 81 PAS 88 DRI 87 DEF 91 PHY 91 RM R 4 ★ 5 RB 92.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Min Pos. 2 Overall Max. 89 Position CB, LB, RB Max PS 10 Max PS+ 2 UPGRADES +6 OVR 90 +4 WF +6 Acceleration 90 +6 Sprint Speed 90 +6 Agility 86 +8 Balance 90 +8 Interceptions 92 +8 Defensive Awareness 91 +6 Sliding Tackle 90 +8 Strength 90 +8 Aggression 90 +5 Stamina 89 +8 Vision 88 +6 Crossing 88 +8 Short Pass 90 +6 Long Shots 86 +5 Heading Acc. 88 +5 Jumping 89 +6 Reactions 88 +8 Composure 90 3 7 in 5 days in 5 days 81% 19%</t>
+          <t>Versatile Defender Unlocked by completing the Darwin Cup objective Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 84.9 Walker 90 RB PAC 91 SHO 81 PAS 88 DRI 87 DEF 91 PHY 91 RM R 4 ★ 5 RB 92.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Min Pos. 2 Overall Max. 89 Position CB, LB, RB Max PS 10 Max PS+ 2 UPGRADES +6 OVR 90 +4 WF +6 Acceleration 90 +6 Sprint Speed 90 +6 Agility 86 +8 Balance 90 +8 Interceptions 92 +8 Defensive Awareness 91 +6 Sliding Tackle 90 +8 Strength 90 +8 Aggression 90 +5 Stamina 89 +8 Vision 88 +6 Crossing 88 +8 Short Pass 90 +6 Long Shots 86 +5 Heading Acc. 88 +5 Jumping 89 +6 Reactions 88 +8 Composure 90 3 7 in 4 days in 4 days 81% 19%</t>
         </is>
       </c>
     </row>
@@ -5215,12 +5215,12 @@
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY23" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ23" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="DA23" t="inlineStr">
         <is>
-          <t>Technical+ and Finesse Shot Unlocked by completing the Win Tournament task in the Darwin Cup objective Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 88.9 Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 89.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 3 7 in 5 days in 5 days 66% 34%</t>
+          <t>Technical+ and Finesse Shot Unlocked by completing the Win Tournament task in the Darwin Cup objective Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 88.9 Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 89.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 3 7 in 4 days in 4 days 66% 34%</t>
         </is>
       </c>
     </row>
@@ -5378,12 +5378,12 @@
       </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY24" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ24" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="DA24" t="inlineStr">
         <is>
-          <t>Anticipate+ and Intercept Unlocked by completing the Win Quarter-Finals task in the Darwin Cup objective Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 84.9 Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 88.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 2 8 in 5 days in 5 days 33% 67%</t>
+          <t>Anticipate+ and Intercept Unlocked by completing the Win Quarter-Finals task in the Darwin Cup objective Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 84.9 Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 88.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 2 8 in 4 days in 4 days 33% 67%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY25" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ25" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="DA25" t="inlineStr">
         <is>
-          <t>Tiki Taka+ Unlocked by completing the May The 3rd Be With You EVO SBC Adopo 88 CM PAC 86 SHO 86 PAS 88 DRI 88 DEF 87 PHY 90 CDM R 4 ★ 4 CM 89.1 Adopo 88 CM PAC 86 SHO 86 PAS 88 DRI 88 DEF 87 PHY 90 CDM R 4 ★ 4 CM 90.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 10 days in 10 days 84% 16%</t>
+          <t>Tiki Taka+ Unlocked by completing the May The 3rd Be With You EVO SBC Adopo 88 CM PAC 86 SHO 86 PAS 88 DRI 88 DEF 87 PHY 90 CDM R 4 ★ 4 CM 89.1 Adopo 88 CM PAC 86 SHO 86 PAS 88 DRI 88 DEF 87 PHY 90 CDM R 4 ★ 4 CM 90.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 9 days in 9 days 84% 16%</t>
         </is>
       </c>
     </row>
@@ -5702,12 +5702,12 @@
       </c>
       <c r="CX26" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY26" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ26" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="DA26" t="inlineStr">
         <is>
-          <t>Turbo Strength Unlocked by completing the Turbo Strength task in the Evolution Revolution objective Schlotterbeck 89 CB PAC 86 SHO 41 PAS 79 DRI 74 DEF 91 PHY 88 L 3 ★ 5 CB 89.3 Schlotterbeck 90 CB PAC 90 SHO 41 PAS 79 DRI 74 DEF 91 PHY 91 L 3 ★ 5 CB 91.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 UPGRADES +1 OVR +4 PAC 91 +3 PHY 92 in 2 days in 2 days 87% 13%</t>
+          <t>Turbo Strength Unlocked by completing the Turbo Strength task in the Evolution Revolution objective Schlotterbeck 89 CB PAC 86 SHO 41 PAS 79 DRI 74 DEF 91 PHY 88 L 3 ★ 5 CB 89.3 Schlotterbeck 90 CB PAC 90 SHO 41 PAS 79 DRI 74 DEF 91 PHY 91 L 3 ★ 5 CB 91.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 UPGRADES +1 OVR +4 PAC 91 +3 PHY 92 in 1 day in 1 day 87% 13%</t>
         </is>
       </c>
     </row>
@@ -5865,12 +5865,12 @@
       </c>
       <c r="CX27" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY27" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ27" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="DA27" t="inlineStr">
         <is>
-          <t>Pass IQ 5 Unlocked by completing the Pass IQ task in the Evolution Revolution objective Hjulmand 88 CDM PAC 84 SHO 84 PAS 86 DRI 84 DEF 88 PHY 88 CM R 4 ★ 4 CM 89.8 Hjulmand 88 CDM PAC 84 SHO 84 PAS 88 DRI 84 DEF 88 PHY 88 CM R 4 ★ 4 CM 90.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 UPGRADES +3 Vision 93 +3 Short Pass 93 in 2 days in 2 days 88% 13%</t>
+          <t>Pass IQ 5 Unlocked by completing the Pass IQ task in the Evolution Revolution objective Hjulmand 88 CDM PAC 84 SHO 84 PAS 86 DRI 84 DEF 88 PHY 88 CM R 4 ★ 4 CM 89.8 Hjulmand 88 CDM PAC 84 SHO 84 PAS 88 DRI 84 DEF 88 PHY 88 CM R 4 ★ 4 CM 90.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 UPGRADES +3 Vision 93 +3 Short Pass 93 in 1 day in 1 day 88% 13%</t>
         </is>
       </c>
     </row>
@@ -6032,12 +6032,12 @@
       </c>
       <c r="CX28" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY28" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ28" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="DA28" t="inlineStr">
         <is>
-          <t>From Distance Unlocked by completing the From Distance task in the Evolution Revolution objective Carlos Espí 88 ST PAC 91 SHO 86 PAS 80 DRI 88 DEF 58 PHY 94 R 4 ★ 4 ST 89.3 Carlos Espí 88 ST PAC 91 SHO 89 PAS 80 DRI 88 DEF 58 PHY 94 R 4 ★ 4 ST 89.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +8 Shot Power 93 +8 Long Shots 93 8 in 2 days in 2 days 85% 15%</t>
+          <t>From Distance Unlocked by completing the From Distance task in the Evolution Revolution objective Carlos Espí 88 ST PAC 91 SHO 86 PAS 80 DRI 88 DEF 58 PHY 94 R 4 ★ 4 ST 89.3 Carlos Espí 88 ST PAC 91 SHO 89 PAS 80 DRI 88 DEF 58 PHY 94 R 4 ★ 4 ST 89.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +8 Shot Power 93 +8 Long Shots 93 8 in 1 day in 1 day 85% 15%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="CX29" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY29" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ29" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="DA29" t="inlineStr">
         <is>
-          <t>Intercept &amp; Aerial Fortress Unlocked by completing the Defensive Instinct task in the Evolution Revolution objective António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 86.6 António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 2 days in 2 days 33% 67%</t>
+          <t>Intercept &amp; Aerial Fortress Unlocked by completing the Defensive Instinct task in the Evolution Revolution objective António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 86.6 António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 1 day in 1 day 33% 67%</t>
         </is>
       </c>
     </row>
@@ -6350,12 +6350,12 @@
       </c>
       <c r="CX30" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 7 days Expiry in 7 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY30" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 7 days Expiry in 7 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ30" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="DA30" t="inlineStr">
         <is>
-          <t>Speed to Finish Unlocked by completing the Score in 5 task in the TOTS: Champions Objective objective Mayulu 89 CM PAC 88 SHO 88 PAS 90 DRI 92 DEF 80 PHY 82 L 3 ★ 5 CM 88.3 Mayulu 89 CM PAC 88 SHO 88 PAS 90 DRI 92 DEF 80 PHY 82 L 3 ★ 5 CM 89.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 8 days in 8 days 62% 38%</t>
+          <t>Speed to Finish Unlocked by completing the Score in 5 task in the TOTS: Champions Objective objective Mayulu 89 CM PAC 88 SHO 88 PAS 90 DRI 92 DEF 80 PHY 82 L 3 ★ 5 CM 88.3 Mayulu 89 CM PAC 88 SHO 88 PAS 90 DRI 92 DEF 80 PHY 82 L 3 ★ 5 CM 89.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 7 days in 7 days 62% 38%</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="CX31" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 7 days Expiry in 7 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY31" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 7 days Expiry in 7 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ31" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="DA31" t="inlineStr">
         <is>
-          <t>Creative Playmaker Unlocked by completing the Win 5 task in the TOTS: Champions Objective objective Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 88.9 Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 90.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 8 days in 8 days 33% 67%</t>
+          <t>Creative Playmaker Unlocked by completing the Win 5 task in the TOTS: Champions Objective objective Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 88.9 Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 90.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 7 days in 7 days 33% 67%</t>
         </is>
       </c>
     </row>
@@ -6672,12 +6672,12 @@
       </c>
       <c r="CX32" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY32" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ32" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="DA32" t="inlineStr">
         <is>
-          <t>Long Ball Pass+ &amp; Pinged Pass Unlocked by completing the Assist in 10 task in the Bundesliga TOTS Exhibition objective Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 2 8 in 2 days in 2 days 10% 90%</t>
+          <t>Long Ball Pass+ &amp; Pinged Pass Unlocked by completing the Assist in 10 task in the Bundesliga TOTS Exhibition objective Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 2 8 in 1 day in 1 day 10% 90%</t>
         </is>
       </c>
     </row>
@@ -6831,12 +6831,12 @@
       </c>
       <c r="CX33" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY33" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ33" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="DA33" t="inlineStr">
         <is>
-          <t>Finesse Shot+ Unlocked by completing the Score in 10 task in the Bundesliga TOTS Exhibition objective Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 88.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 2 days in 2 days 69% 31%</t>
+          <t>Finesse Shot+ Unlocked by completing the Score in 10 task in the Bundesliga TOTS Exhibition objective Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 88.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 1 day in 1 day 69% 31%</t>
         </is>
       </c>
     </row>
@@ -7504,12 +7504,12 @@
       </c>
       <c r="CX36" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY36" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ36" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="DA36" t="inlineStr">
         <is>
-          <t>Intercept+ &amp; Quick Step+ Unlocked by completing the Score in 30 task in the S7 Spirit of Africa League objective António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 86.6 António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 90.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 29 days in 29 days 75% 25%</t>
+          <t>Intercept+ &amp; Quick Step+ Unlocked by completing the Score in 30 task in the S7 Spirit of Africa League objective António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 86.6 António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 90.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 28 days in 28 days 75% 25%</t>
         </is>
       </c>
     </row>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="CX37" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY37" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ37" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="DA37" t="inlineStr">
         <is>
-          <t>WTSS Defender Boost Unlocked by completing the S7 Spirit of Africa Tournament objective Moore 74 CB PAC 74 SHO 42 PAS 70 DRI 57 DEF 83 PHY 72 R 2 ★ 3 CB 68.4 Moore 74 CB PAC 74 SHO 42 PAS 70 DRI 57 DEF 85 PHY 74 R 2 ★ 3 CB 76.2 REQUIREMENTS Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 UPGRADES +5 OVR 74 +3 Composure +2 Interceptions +2 Sliding Tackle +2 Jumping +2 Balance +2 Heading Acc. +2 Standing Tackle +3 Stamina +2 Reactions +3 Defensive Awareness +2 Strength +2 Aggression 3 in 29 days in 29 days 74% 26%</t>
+          <t>WTSS Defender Boost Unlocked by completing the S7 Spirit of Africa Tournament objective Moore 74 CB PAC 74 SHO 42 PAS 70 DRI 57 DEF 83 PHY 72 R 2 ★ 3 CB 68.4 Moore 74 CB PAC 74 SHO 42 PAS 70 DRI 57 DEF 85 PHY 74 R 2 ★ 3 CB 76.2 REQUIREMENTS Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 UPGRADES +5 OVR 74 +3 Composure +2 Interceptions +2 Sliding Tackle +2 Jumping +2 Balance +2 Heading Acc. +2 Standing Tackle +3 Stamina +2 Reactions +3 Defensive Awareness +2 Strength +2 Aggression 3 in 28 days in 28 days 74% 26%</t>
         </is>
       </c>
     </row>
@@ -7872,12 +7872,12 @@
       </c>
       <c r="CX38" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY38" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ38" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="DA38" t="inlineStr">
         <is>
-          <t>WTSS Attacker Boost Unlocked by completing the S7 Spirit of Africa League objective Šuker 73 ST PAC 71 SHO 83 PAS 70 DRI 83 DEF 30 PHY 65 L 4 ★ 4 ST 72.7 Šuker 74 ST PAC 73 SHO 86 PAS 70 DRI 83 DEF 30 PHY 65 L 4 ★ 4 ST 79.2 REQUIREMENTS Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 UPGRADES +5 OVR 74 +2 Positioning +2 Volleys +2 Penalties +2 Balance +2 Acceleration +3 Finishing +2 Long Shots +3 Composure +2 Sprint Speed +2 Shot Power +3 Stamina 3 in 29 days in 29 days 78% 22%</t>
+          <t>WTSS Attacker Boost Unlocked by completing the S7 Spirit of Africa League objective Šuker 73 ST PAC 71 SHO 83 PAS 70 DRI 83 DEF 30 PHY 65 L 4 ★ 4 ST 72.7 Šuker 74 ST PAC 73 SHO 86 PAS 70 DRI 83 DEF 30 PHY 65 L 4 ★ 4 ST 79.2 REQUIREMENTS Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 UPGRADES +5 OVR 74 +2 Positioning +2 Volleys +2 Penalties +2 Balance +2 Acceleration +3 Finishing +2 Long Shots +3 Composure +2 Sprint Speed +2 Shot Power +3 Stamina 3 in 28 days in 28 days 78% 22%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="CX60" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 7 Details Submit by in 6 days Expiry in 6 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 7 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY60" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 7 Details Submit by in 6 days Expiry in 6 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 7 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ60" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="DA60" t="inlineStr">
         <is>
-          <t>Finesse Shot Unlocked by completing the 10 Finesse Shots task in the Lowe's Scoring Marathon objective Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 7 UPGRADES 8 in 6 days in 6 days 28% 72%</t>
+          <t>Finesse Shot Unlocked by completing the 10 Finesse Shots task in the Lowe's Scoring Marathon objective Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 7 UPGRADES 8 in 5 days in 5 days 28% 72%</t>
         </is>
       </c>
     </row>
@@ -65932,7 +65932,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cut In, Say Less 100,000 500 Elevate your favourite qualified player with enhanced pace, dribbling, shooting, and passing, allowing them to cut inside, get past defenders, and deliver in decisive moments! Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 92 RW PAC 92 SHO 90 PAS 92 DRI 93 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 93.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 in 11 hours in 7 days 64% 36%</t>
+          <t>Cut In, Say Less 100,000 500 Elevate your favourite qualified player with enhanced pace, dribbling, shooting, and passing, allowing them to cut inside, get past defenders, and deliver in decisive moments! Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 92 RW PAC 92 SHO 90 PAS 92 DRI 93 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 93.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 in 10 hours in 7 days 64% 36%</t>
         </is>
       </c>
     </row>
@@ -66067,7 +66067,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tiki Taka Unlocked by completing the Score 5 task in the French TOTS Flash Rush objective Rijkaard 89 CDM PAC 84 SHO 80 PAS 85 DRI 86 DEF 89 PHY 88 CB CM R 4 ★ 4 CDM 87.2 Rijkaard 89 CDM PAC 84 SHO 80 PAS 85 DRI 86 DEF 89 PHY 88 CB CM R 4 ★ 4 CDM 88.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 6 days in 6 days 5% 95%</t>
+          <t>Tiki Taka Unlocked by completing the Score 5 task in the French TOTS Flash Rush objective Rijkaard 89 CDM PAC 84 SHO 80 PAS 85 DRI 86 DEF 89 PHY 88 CB CM R 4 ★ 4 CDM 87.2 Rijkaard 89 CDM PAC 84 SHO 80 PAS 85 DRI 86 DEF 89 PHY 88 CB CM R 4 ★ 4 CDM 88.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 5 days in 5 days 5% 95%</t>
         </is>
       </c>
     </row>
@@ -66094,7 +66094,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rapid+ Unlocked by completing the Assist in 10 task in the Ligue 1 TOTS Exhibition objective Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 84.0 Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 85.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 9 days in 9 days 91% 9%</t>
+          <t>Rapid+ Unlocked by completing the Assist in 10 task in the Ligue 1 TOTS Exhibition objective Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 84.0 Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 85.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 8 days in 8 days 91% 9%</t>
         </is>
       </c>
     </row>
@@ -66121,7 +66121,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>First Touch+ Unlocked by completing the Score in 10 task in the Ligue 1 TOTS Exhibition objective Nanasi 89 LM PAC 89 SHO 87 PAS 89 DRI 91 DEF 45 PHY 80 CM CAM R 5 ★ 4 CAM 89.6 Nanasi 89 LM PAC 89 SHO 87 PAS 89 DRI 91 DEF 45 PHY 80 CM CAM R 5 ★ 4 CAM 90.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 9 days in 9 days 62% 38%</t>
+          <t>First Touch+ Unlocked by completing the Score in 10 task in the Ligue 1 TOTS Exhibition objective Nanasi 89 LM PAC 89 SHO 87 PAS 89 DRI 91 DEF 45 PHY 80 CM CAM R 5 ★ 4 CAM 89.6 Nanasi 89 LM PAC 89 SHO 87 PAS 89 DRI 91 DEF 45 PHY 80 CM CAM R 5 ★ 4 CAM 90.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 8 days in 8 days 62% 38%</t>
         </is>
       </c>
     </row>
@@ -66148,7 +66148,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tiki Taka and Low Driven Shot Unlocked by completing the Score in 5 task in the TOTS: Champions Objective objective Luna 89 LM PAC 89 SHO 87 PAS 90 DRI 90 DEF 60 PHY 85 CAM LW R 4 ★ 5 CAM 86.2 Luna 89 LM PAC 89 SHO 87 PAS 90 DRI 90 DEF 60 PHY 85 CAM LW R 4 ★ 5 CAM 88.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 6 days in 6 days 9% 91%</t>
+          <t>Tiki Taka and Low Driven Shot Unlocked by completing the Score in 5 task in the TOTS: Champions Objective objective Luna 89 LM PAC 89 SHO 87 PAS 90 DRI 90 DEF 60 PHY 85 CAM LW R 4 ★ 5 CAM 86.2 Luna 89 LM PAC 89 SHO 87 PAS 90 DRI 90 DEF 60 PHY 85 CAM LW R 4 ★ 5 CAM 88.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 5 days in 5 days 9% 91%</t>
         </is>
       </c>
     </row>
@@ -66175,7 +66175,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Intercept and Pinged Pass Unlocked by completing the Win 4 task in the TOTS: Champions Objective objective ter Stegen 89 GK DIV 87 HAN 87 KIC 91 REF 89 SPD 53 POS 87 R 1 ★ 4 GK 85.9 ter Stegen 89 GK DIV 87 HAN 87 KIC 91 REF 89 SPD 53 POS 87 R 1 ★ 4 GK 87.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 6 days in 6 days 8% 92%</t>
+          <t>Intercept and Pinged Pass Unlocked by completing the Win 4 task in the TOTS: Champions Objective objective ter Stegen 89 GK DIV 87 HAN 87 KIC 91 REF 89 SPD 53 POS 87 R 1 ★ 4 GK 85.9 ter Stegen 89 GK DIV 87 HAN 87 KIC 91 REF 89 SPD 53 POS 87 R 1 ★ 4 GK 87.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 5 days in 5 days 8% 92%</t>
         </is>
       </c>
     </row>
@@ -66202,7 +66202,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jockey+ &amp; Bruiser+ Unlocked by completing the 3 Completions task in the Season 7 Spirit of Africa Weekly Play Completionist objective Dumfries 89 RB PAC 89 SHO 75 PAS 84 DRI 86 DEF 86 PHY 89 RM R 4 ★ 3 RB 85.3 Dumfries 89 RB PAC 89 SHO 75 PAS 84 DRI 86 DEF 86 PHY 89 RM R 4 ★ 3 RB 87.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 29 days in 29 days 12% 88%</t>
+          <t>Jockey+ &amp; Bruiser+ Unlocked by completing the 3 Completions task in the Season 7 Spirit of Africa Weekly Play Completionist objective Dumfries 89 RB PAC 89 SHO 75 PAS 84 DRI 86 DEF 86 PHY 89 RM R 4 ★ 3 RB 85.3 Dumfries 89 RB PAC 89 SHO 75 PAS 84 DRI 86 DEF 86 PHY 89 RM R 4 ★ 3 RB 87.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 28 days in 28 days 12% 88%</t>
         </is>
       </c>
     </row>
@@ -66229,7 +66229,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Versatile Defender Unlocked by completing the Darwin Cup objective Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 84.9 Walker 90 RB PAC 91 SHO 81 PAS 88 DRI 87 DEF 91 PHY 91 RM R 4 ★ 5 RB 92.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Min Pos. 2 Overall Max. 89 Position CB, LB, RB Max PS 10 Max PS+ 2 UPGRADES +6 OVR 90 +4 WF +6 Acceleration 90 +6 Sprint Speed 90 +6 Agility 86 +8 Balance 90 +8 Interceptions 92 +8 Defensive Awareness 91 +6 Sliding Tackle 90 +8 Strength 90 +8 Aggression 90 +5 Stamina 89 +8 Vision 88 +6 Crossing 88 +8 Short Pass 90 +6 Long Shots 86 +5 Heading Acc. 88 +5 Jumping 89 +6 Reactions 88 +8 Composure 90 3 7 in 5 days in 5 days 81% 19%</t>
+          <t>Versatile Defender Unlocked by completing the Darwin Cup objective Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 84.9 Walker 90 RB PAC 91 SHO 81 PAS 88 DRI 87 DEF 91 PHY 91 RM R 4 ★ 5 RB 92.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Min Pos. 2 Overall Max. 89 Position CB, LB, RB Max PS 10 Max PS+ 2 UPGRADES +6 OVR 90 +4 WF +6 Acceleration 90 +6 Sprint Speed 90 +6 Agility 86 +8 Balance 90 +8 Interceptions 92 +8 Defensive Awareness 91 +6 Sliding Tackle 90 +8 Strength 90 +8 Aggression 90 +5 Stamina 89 +8 Vision 88 +6 Crossing 88 +8 Short Pass 90 +6 Long Shots 86 +5 Heading Acc. 88 +5 Jumping 89 +6 Reactions 88 +8 Composure 90 3 7 in 4 days in 4 days 81% 19%</t>
         </is>
       </c>
     </row>
@@ -66256,7 +66256,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Technical+ and Finesse Shot Unlocked by completing the Win Tournament task in the Darwin Cup objective Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 88.9 Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 89.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 3 7 in 5 days in 5 days 66% 34%</t>
+          <t>Technical+ and Finesse Shot Unlocked by completing the Win Tournament task in the Darwin Cup objective Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 88.9 Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 89.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 3 7 in 4 days in 4 days 66% 34%</t>
         </is>
       </c>
     </row>
@@ -66283,7 +66283,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Anticipate+ and Intercept Unlocked by completing the Win Quarter-Finals task in the Darwin Cup objective Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 84.9 Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 88.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 2 8 in 5 days in 5 days 33% 67%</t>
+          <t>Anticipate+ and Intercept Unlocked by completing the Win Quarter-Finals task in the Darwin Cup objective Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 84.9 Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 88.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 2 8 in 4 days in 4 days 33% 67%</t>
         </is>
       </c>
     </row>
@@ -66310,7 +66310,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tiki Taka+ Unlocked by completing the May The 3rd Be With You EVO SBC Adopo 88 CM PAC 86 SHO 86 PAS 88 DRI 88 DEF 87 PHY 90 CDM R 4 ★ 4 CM 89.1 Adopo 88 CM PAC 86 SHO 86 PAS 88 DRI 88 DEF 87 PHY 90 CDM R 4 ★ 4 CM 90.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 10 days in 10 days 84% 16%</t>
+          <t>Tiki Taka+ Unlocked by completing the May The 3rd Be With You EVO SBC Adopo 88 CM PAC 86 SHO 86 PAS 88 DRI 88 DEF 87 PHY 90 CDM R 4 ★ 4 CM 89.1 Adopo 88 CM PAC 86 SHO 86 PAS 88 DRI 88 DEF 87 PHY 90 CDM R 4 ★ 4 CM 90.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 9 days in 9 days 84% 16%</t>
         </is>
       </c>
     </row>
@@ -66337,7 +66337,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Turbo Strength Unlocked by completing the Turbo Strength task in the Evolution Revolution objective Schlotterbeck 89 CB PAC 86 SHO 41 PAS 79 DRI 74 DEF 91 PHY 88 L 3 ★ 5 CB 89.3 Schlotterbeck 90 CB PAC 90 SHO 41 PAS 79 DRI 74 DEF 91 PHY 91 L 3 ★ 5 CB 91.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 UPGRADES +1 OVR +4 PAC 91 +3 PHY 92 in 2 days in 2 days 87% 13%</t>
+          <t>Turbo Strength Unlocked by completing the Turbo Strength task in the Evolution Revolution objective Schlotterbeck 89 CB PAC 86 SHO 41 PAS 79 DRI 74 DEF 91 PHY 88 L 3 ★ 5 CB 89.3 Schlotterbeck 90 CB PAC 90 SHO 41 PAS 79 DRI 74 DEF 91 PHY 91 L 3 ★ 5 CB 91.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 UPGRADES +1 OVR +4 PAC 91 +3 PHY 92 in 1 day in 1 day 87% 13%</t>
         </is>
       </c>
     </row>
@@ -66364,7 +66364,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pass IQ 5 Unlocked by completing the Pass IQ task in the Evolution Revolution objective Hjulmand 88 CDM PAC 84 SHO 84 PAS 86 DRI 84 DEF 88 PHY 88 CM R 4 ★ 4 CM 89.8 Hjulmand 88 CDM PAC 84 SHO 84 PAS 88 DRI 84 DEF 88 PHY 88 CM R 4 ★ 4 CM 90.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 UPGRADES +3 Vision 93 +3 Short Pass 93 in 2 days in 2 days 88% 13%</t>
+          <t>Pass IQ 5 Unlocked by completing the Pass IQ task in the Evolution Revolution objective Hjulmand 88 CDM PAC 84 SHO 84 PAS 86 DRI 84 DEF 88 PHY 88 CM R 4 ★ 4 CM 89.8 Hjulmand 88 CDM PAC 84 SHO 84 PAS 88 DRI 84 DEF 88 PHY 88 CM R 4 ★ 4 CM 90.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 UPGRADES +3 Vision 93 +3 Short Pass 93 in 1 day in 1 day 88% 13%</t>
         </is>
       </c>
     </row>
@@ -66391,7 +66391,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>From Distance Unlocked by completing the From Distance task in the Evolution Revolution objective Carlos Espí 88 ST PAC 91 SHO 86 PAS 80 DRI 88 DEF 58 PHY 94 R 4 ★ 4 ST 89.3 Carlos Espí 88 ST PAC 91 SHO 89 PAS 80 DRI 88 DEF 58 PHY 94 R 4 ★ 4 ST 89.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +8 Shot Power 93 +8 Long Shots 93 8 in 2 days in 2 days 85% 15%</t>
+          <t>From Distance Unlocked by completing the From Distance task in the Evolution Revolution objective Carlos Espí 88 ST PAC 91 SHO 86 PAS 80 DRI 88 DEF 58 PHY 94 R 4 ★ 4 ST 89.3 Carlos Espí 88 ST PAC 91 SHO 89 PAS 80 DRI 88 DEF 58 PHY 94 R 4 ★ 4 ST 89.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +8 Shot Power 93 +8 Long Shots 93 8 in 1 day in 1 day 85% 15%</t>
         </is>
       </c>
     </row>
@@ -66418,7 +66418,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Intercept &amp; Aerial Fortress Unlocked by completing the Defensive Instinct task in the Evolution Revolution objective António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 86.6 António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 2 days in 2 days 33% 67%</t>
+          <t>Intercept &amp; Aerial Fortress Unlocked by completing the Defensive Instinct task in the Evolution Revolution objective António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 86.6 António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 1 day in 1 day 33% 67%</t>
         </is>
       </c>
     </row>
@@ -66445,7 +66445,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Speed to Finish Unlocked by completing the Score in 5 task in the TOTS: Champions Objective objective Mayulu 89 CM PAC 88 SHO 88 PAS 90 DRI 92 DEF 80 PHY 82 L 3 ★ 5 CM 88.3 Mayulu 89 CM PAC 88 SHO 88 PAS 90 DRI 92 DEF 80 PHY 82 L 3 ★ 5 CM 89.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 8 days in 8 days 62% 38%</t>
+          <t>Speed to Finish Unlocked by completing the Score in 5 task in the TOTS: Champions Objective objective Mayulu 89 CM PAC 88 SHO 88 PAS 90 DRI 92 DEF 80 PHY 82 L 3 ★ 5 CM 88.3 Mayulu 89 CM PAC 88 SHO 88 PAS 90 DRI 92 DEF 80 PHY 82 L 3 ★ 5 CM 89.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 7 days in 7 days 62% 38%</t>
         </is>
       </c>
     </row>
@@ -66472,7 +66472,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Creative Playmaker Unlocked by completing the Win 5 task in the TOTS: Champions Objective objective Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 88.9 Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 90.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 8 days in 8 days 33% 67%</t>
+          <t>Creative Playmaker Unlocked by completing the Win 5 task in the TOTS: Champions Objective objective Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 88.9 Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 90.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 7 days in 7 days 33% 67%</t>
         </is>
       </c>
     </row>
@@ -66499,7 +66499,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Long Ball Pass+ &amp; Pinged Pass Unlocked by completing the Assist in 10 task in the Bundesliga TOTS Exhibition objective Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 2 8 in 2 days in 2 days 10% 90%</t>
+          <t>Long Ball Pass+ &amp; Pinged Pass Unlocked by completing the Assist in 10 task in the Bundesliga TOTS Exhibition objective Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 2 8 in 1 day in 1 day 10% 90%</t>
         </is>
       </c>
     </row>
@@ -66526,7 +66526,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Finesse Shot+ Unlocked by completing the Score in 10 task in the Bundesliga TOTS Exhibition objective Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 88.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 2 days in 2 days 69% 31%</t>
+          <t>Finesse Shot+ Unlocked by completing the Score in 10 task in the Bundesliga TOTS Exhibition objective Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 88.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 1 day in 1 day 69% 31%</t>
         </is>
       </c>
     </row>
@@ -66607,7 +66607,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Intercept+ &amp; Quick Step+ Unlocked by completing the Score in 30 task in the S7 Spirit of Africa League objective António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 86.6 António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 90.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 29 days in 29 days 75% 25%</t>
+          <t>Intercept+ &amp; Quick Step+ Unlocked by completing the Score in 30 task in the S7 Spirit of Africa League objective António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 86.6 António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 90.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 28 days in 28 days 75% 25%</t>
         </is>
       </c>
     </row>
@@ -66634,7 +66634,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>WTSS Defender Boost Unlocked by completing the S7 Spirit of Africa Tournament objective Moore 74 CB PAC 74 SHO 42 PAS 70 DRI 57 DEF 83 PHY 72 R 2 ★ 3 CB 68.4 Moore 74 CB PAC 74 SHO 42 PAS 70 DRI 57 DEF 85 PHY 74 R 2 ★ 3 CB 76.2 REQUIREMENTS Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 UPGRADES +5 OVR 74 +3 Composure +2 Interceptions +2 Sliding Tackle +2 Jumping +2 Balance +2 Heading Acc. +2 Standing Tackle +3 Stamina +2 Reactions +3 Defensive Awareness +2 Strength +2 Aggression 3 in 29 days in 29 days 74% 26%</t>
+          <t>WTSS Defender Boost Unlocked by completing the S7 Spirit of Africa Tournament objective Moore 74 CB PAC 74 SHO 42 PAS 70 DRI 57 DEF 83 PHY 72 R 2 ★ 3 CB 68.4 Moore 74 CB PAC 74 SHO 42 PAS 70 DRI 57 DEF 85 PHY 74 R 2 ★ 3 CB 76.2 REQUIREMENTS Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 UPGRADES +5 OVR 74 +3 Composure +2 Interceptions +2 Sliding Tackle +2 Jumping +2 Balance +2 Heading Acc. +2 Standing Tackle +3 Stamina +2 Reactions +3 Defensive Awareness +2 Strength +2 Aggression 3 in 28 days in 28 days 74% 26%</t>
         </is>
       </c>
     </row>
@@ -66661,7 +66661,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WTSS Attacker Boost Unlocked by completing the S7 Spirit of Africa League objective Šuker 73 ST PAC 71 SHO 83 PAS 70 DRI 83 DEF 30 PHY 65 L 4 ★ 4 ST 72.7 Šuker 74 ST PAC 73 SHO 86 PAS 70 DRI 83 DEF 30 PHY 65 L 4 ★ 4 ST 79.2 REQUIREMENTS Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 UPGRADES +5 OVR 74 +2 Positioning +2 Volleys +2 Penalties +2 Balance +2 Acceleration +3 Finishing +2 Long Shots +3 Composure +2 Sprint Speed +2 Shot Power +3 Stamina 3 in 29 days in 29 days 78% 22%</t>
+          <t>WTSS Attacker Boost Unlocked by completing the S7 Spirit of Africa League objective Šuker 73 ST PAC 71 SHO 83 PAS 70 DRI 83 DEF 30 PHY 65 L 4 ★ 4 ST 72.7 Šuker 74 ST PAC 73 SHO 86 PAS 70 DRI 83 DEF 30 PHY 65 L 4 ★ 4 ST 79.2 REQUIREMENTS Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 UPGRADES +5 OVR 74 +2 Positioning +2 Volleys +2 Penalties +2 Balance +2 Acceleration +3 Finishing +2 Long Shots +3 Composure +2 Sprint Speed +2 Shot Power +3 Stamina 3 in 28 days in 28 days 78% 22%</t>
         </is>
       </c>
     </row>
@@ -67255,7 +67255,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Finesse Shot Unlocked by completing the 10 Finesse Shots task in the Lowe's Scoring Marathon objective Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 7 UPGRADES 8 in 6 days in 6 days 28% 72%</t>
+          <t>Finesse Shot Unlocked by completing the 10 Finesse Shots task in the Lowe's Scoring Marathon objective Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 7 UPGRADES 8 in 5 days in 5 days 28% 72%</t>
         </is>
       </c>
     </row>
@@ -68136,7 +68136,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-11T06:00:54</t>
+          <t>2026-05-11T06:40:01</t>
         </is>
       </c>
     </row>

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DA90"/>
+  <dimension ref="A1:DB90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,405 +544,410 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>+ Stat Point</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>Max OVR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>+ PAC</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Max PAC</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>+ SHO</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Max SHO</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>+ PAS</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Max PAS</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>+ DRI</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Max DRI</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>+ DEF</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Max DEF</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>+ PHY</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Max PHY</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>+ Acceleration</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Max Acceleration</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>+ Sprint Speed</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Max Sprint Speed</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>+ Positioning</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Max Positioning</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>+ Finishing</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Max Finishing</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>+ Shot Power</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Max Shot Power</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>+ Long Shots</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Max Long Shots</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>+ Volleys</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Max Volleys</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>+ Penalties</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>Max Penalties</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>+ Vision</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>Max Vision</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>+ Crossing</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>Max Crossing</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>+ FK Accuracy</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>Max FK Accuracy</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>+ Short Passing</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>Max Short Passing</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>+ Long Passing</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>Max Long Passing</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>+ Curve</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>Max Curve</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>+ Agility</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>Max Agility</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>+ Balance</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>Max Balance</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>+ Reactions</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>Max Reactions</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>+ Ball Control</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>Max Ball Control</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>+ Dribbling</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>Max Dribbling</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>+ Composure</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>Max Composure</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>+ Interceptions</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>Max Interceptions</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>+ Heading Accuracy</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>Max Heading Accuracy</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>+ Defensive Awareness</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>Max Defensive Awareness</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>+ Standing Tackle</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>Max Standing Tackle</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>+ Sliding Tackle</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>Max Sliding Tackle</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>+ Jumping</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>Max Jumping</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>+ Stamina</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>Max Stamina</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>+ Strength</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>Max Strength</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>+ Aggression</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>Max Aggression</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>+ SM</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>Max SM</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>+ WF</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>Max WF</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>Role_Added</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>Other_Upgrade_Text</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>Raw_Requirements_Text</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>Req_Other</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>Link_Text</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>Parent_Text</t>
         </is>
@@ -1081,27 +1086,28 @@
       <c r="CT2" t="inlineStr"/>
       <c r="CU2" t="inlineStr"/>
       <c r="CV2" t="inlineStr"/>
-      <c r="CW2" t="inlineStr">
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr">
         <is>
           <t>8 Level 1 Maradona 95 CAM PAC 90 SHO 91 PAS 91 DRI 96 DEF 40 PHY 77 ST L 5 ★ 3 Maradona 95 CAM PAC 90 SHO 91 PAS 91 DRI 96 DEF 40 PHY 77 ST L 5 ★ 3 UPGRADES 8</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Max PS 7 Max PS+ 2 Details Submit by in 9 days Expiry in 16 days Coins Cost 35,000 Points Cost 250</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Max PS 7 Max PS+ 2 Details Submit by in 9 days Expiry in 16 days Coins Cost 35,000 Points Cost 250</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DA2" t="inlineStr">
         <is>
           <t>Maestro Unbound NEW 35,000 250 2</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>Maestro Unbound NEW 35,000 250 2 Unlock the true playmaking abilities of a player by adding all passing PlayStyles. Pelé 96 CAM PAC 94 SHO 96 PAS 92 DRI 95 DEF 60 PHY 75 ST R 5 ★ 4 CAM 90.6 Pelé 96 CAM PAC 94 SHO 96 PAS 92 DRI 95 DEF 60 PHY 75 ST R 5 ★ 4 CAM 92.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max PS 7 Max PS+ 2 UPGRADES 8 in 9 days in 16 days 26% 74%</t>
         </is>
@@ -1174,10 +1180,10 @@
       <c r="X3" t="n">
         <v>30</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
         <v>92</v>
       </c>
-      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -1189,19 +1195,19 @@
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="n">
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="n">
         <v>20</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AN3" t="n">
         <v>82</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AO3" t="n">
         <v>20</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AP3" t="n">
         <v>82</v>
       </c>
-      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
@@ -1229,13 +1235,13 @@
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr"/>
       <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="n">
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="n">
         <v>25</v>
       </c>
-      <c r="BS3" t="n">
+      <c r="BT3" t="n">
         <v>93</v>
       </c>
-      <c r="BT3" t="inlineStr"/>
       <c r="BU3" t="inlineStr"/>
       <c r="BV3" t="inlineStr"/>
       <c r="BW3" t="inlineStr"/>
@@ -1261,36 +1267,37 @@
       <c r="CQ3" t="inlineStr"/>
       <c r="CR3" t="inlineStr"/>
       <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="n">
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="n">
         <v>2</v>
       </c>
-      <c r="CU3" t="inlineStr"/>
-      <c r="CV3" t="inlineStr">
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr">
         <is>
           <t>GK Goalkeeper ++; GK Ball Playing Keeper ++; GK Sweeper Keeper ++</t>
         </is>
       </c>
-      <c r="CW3" t="inlineStr">
+      <c r="CX3" t="inlineStr">
         <is>
           <t>+15 OVR 92 +15 POS 92 +1 WF +10 Acceleration 82 +10 Sprint Speed 82 +25 Reactions 93 +15 Diving 90 +15 Handling 91 +15 Kicking 90 +15 Reflexes 94 GK Goalkeeper ++ GK Ball Playing Keeper ++ GK Sweeper Keeper ++ 2 8 Level 1 Nnadozie 90 GK DIV 92 HAN 87 KIC 86 REF 93 SPD 71 POS 91 R 2 ★ 5 Nnadozie 92 GK DIV 92 HAN 87 KIC 86 REF 93 SPD 71 POS 91 R 2 ★ 5 UPGRADES +15 OVR 92 +1 WF +10 Acceleration 82 +10 Sprint Speed 82 8</t>
         </is>
       </c>
-      <c r="CX3" t="inlineStr">
+      <c r="CY3" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position GK Max PS 10 Max PS+ 2 Details Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY3" t="inlineStr">
+      <c r="CZ3" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position GK Max PS 10 Max PS+ 2 Details Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ3" t="inlineStr">
+      <c r="DA3" t="inlineStr">
         <is>
           <t>Cat Like Reflexes</t>
         </is>
       </c>
-      <c r="DA3" t="inlineStr">
+      <c r="DB3" t="inlineStr">
         <is>
           <t>Cat Like Reflexes Elevate your goalkeeper with elite-level reactions boosts designed to turn split-second moments into match-winning saves. Casillas 90 GK DIV 90 HAN 88 KIC 84 REF 93 SPD 59 POS 88 L 1 ★ 3 GK 83.1 Casillas 92 GK DIV 90 HAN 91 KIC 90 REF 94 SPD 69 POS 92 L 1 ★ 4 GK 87.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position GK Max PS 10 Max PS+ 2 UPGRADES +15 OVR 92 +15 POS 92 +1 WF +10 Acceleration 82 +10 Sprint Speed 82 +25 Reactions 93 +15 Diving 90 +15 Handling 91 +15 Kicking 90 +15 Reflexes 94 GK Goalkeeper ++ GK Ball Playing Keeper ++ GK Sweeper Keeper ++ 2 8 Show less in 8 days in 15 days 90% 10%</t>
         </is>
@@ -1363,10 +1370,10 @@
       <c r="X4" t="n">
         <v>40</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
         <v>92</v>
       </c>
-      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -1378,19 +1385,19 @@
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="n">
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="n">
         <v>20</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AN4" t="n">
         <v>86</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AO4" t="n">
         <v>20</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AP4" t="n">
         <v>90</v>
       </c>
-      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
@@ -1400,152 +1407,153 @@
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="n">
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="n">
         <v>25</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BB4" t="n">
         <v>94</v>
       </c>
-      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="n">
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="n">
         <v>60</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BJ4" t="n">
         <v>90</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BK4" t="n">
         <v>30</v>
       </c>
-      <c r="BK4" t="n">
+      <c r="BL4" t="n">
         <v>90</v>
       </c>
-      <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="n">
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="n">
         <v>20</v>
       </c>
-      <c r="BO4" t="n">
+      <c r="BP4" t="n">
         <v>88</v>
       </c>
-      <c r="BP4" t="n">
+      <c r="BQ4" t="n">
         <v>20</v>
       </c>
-      <c r="BQ4" t="n">
+      <c r="BR4" t="n">
         <v>87</v>
       </c>
-      <c r="BR4" t="n">
+      <c r="BS4" t="n">
         <v>60</v>
       </c>
-      <c r="BS4" t="n">
+      <c r="BT4" t="n">
         <v>92</v>
       </c>
-      <c r="BT4" t="n">
+      <c r="BU4" t="n">
         <v>30</v>
       </c>
-      <c r="BU4" t="n">
+      <c r="BV4" t="n">
         <v>92</v>
       </c>
-      <c r="BV4" t="n">
+      <c r="BW4" t="n">
         <v>20</v>
       </c>
-      <c r="BW4" t="n">
+      <c r="BX4" t="n">
         <v>87</v>
       </c>
-      <c r="BX4" t="n">
+      <c r="BY4" t="n">
         <v>60</v>
       </c>
-      <c r="BY4" t="n">
+      <c r="BZ4" t="n">
         <v>92</v>
       </c>
-      <c r="BZ4" t="n">
+      <c r="CA4" t="n">
         <v>30</v>
       </c>
-      <c r="CA4" t="n">
+      <c r="CB4" t="n">
         <v>92</v>
       </c>
-      <c r="CB4" t="n">
+      <c r="CC4" t="n">
         <v>30</v>
       </c>
-      <c r="CC4" t="n">
+      <c r="CD4" t="n">
         <v>90</v>
       </c>
-      <c r="CD4" t="n">
+      <c r="CE4" t="n">
         <v>30</v>
       </c>
-      <c r="CE4" t="n">
+      <c r="CF4" t="n">
         <v>93</v>
       </c>
-      <c r="CF4" t="n">
+      <c r="CG4" t="n">
         <v>30</v>
       </c>
-      <c r="CG4" t="n">
+      <c r="CH4" t="n">
         <v>94</v>
       </c>
-      <c r="CH4" t="n">
+      <c r="CI4" t="n">
         <v>30</v>
       </c>
-      <c r="CI4" t="n">
+      <c r="CJ4" t="n">
         <v>92</v>
       </c>
-      <c r="CJ4" t="n">
+      <c r="CK4" t="n">
         <v>25</v>
       </c>
-      <c r="CK4" t="n">
+      <c r="CL4" t="n">
         <v>88</v>
       </c>
-      <c r="CL4" t="n">
+      <c r="CM4" t="n">
         <v>25</v>
       </c>
-      <c r="CM4" t="n">
+      <c r="CN4" t="n">
         <v>90</v>
       </c>
-      <c r="CN4" t="n">
+      <c r="CO4" t="n">
         <v>25</v>
       </c>
-      <c r="CO4" t="n">
+      <c r="CP4" t="n">
         <v>91</v>
       </c>
-      <c r="CP4" t="n">
+      <c r="CQ4" t="n">
         <v>50</v>
       </c>
-      <c r="CQ4" t="n">
+      <c r="CR4" t="n">
         <v>90</v>
       </c>
-      <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="inlineStr"/>
-      <c r="CT4" t="n">
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="n">
         <v>6</v>
       </c>
-      <c r="CU4" t="n">
+      <c r="CV4" t="n">
         <v>4</v>
       </c>
-      <c r="CV4" t="inlineStr"/>
-      <c r="CW4" t="inlineStr">
+      <c r="CW4" t="inlineStr"/>
+      <c r="CX4" t="inlineStr">
         <is>
           <t>+20 OVR 92 +3 WF 4 +30 Composure 92 +25 Aggression 90 +30 Short Pass 90 +30 Reactions 92 +30 Defensive Awareness 93 +30 Interceptions 92 +25 Stamina 90 +30 Heading Acc. 90 +20 Dribbling 87 +20 Sprint Speed 90 +25 Strength 91 +20 Balance 87 +25 Penalties 94 +30 Standing Tackle 94 +20 Acceleration 86 +20 Agility 88 +30 Long Pass 90 +25 Jumping 88 +30 Sliding Tackle 92 +30 Ball Control 92 3 7 Level 1 Pacho 90 CB PAC 86 SHO 40 PAS 73 DRI 73 DEF 90 PHY 91 L 5 ★ 5 Pacho 92 CB PAC 86 SHO 40 PAS 73 DRI 74 DEF 90 PHY 91 L 5 ★ 5 UPGRADES +20 OVR 92 +3 WF 4 +30 Composure 92 +25 Aggression 90 +30 Short Pass 90 +30 Reactions 92</t>
         </is>
       </c>
-      <c r="CX4" t="inlineStr">
+      <c r="CY4" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position CB Max PS 10 Max PS+ 2 Heading Accuracy Max. 94 Details Submit by in 7 days Expiry in 14 days Coins Cost 125,000 Points Cost 750</t>
         </is>
       </c>
-      <c r="CY4" t="inlineStr">
+      <c r="CZ4" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position CB Max PS 10 Max PS+ 2 Heading Accuracy Max. 94 Details Submit by in 7 days Expiry in 14 days Coins Cost 125,000 Points Cost 750</t>
         </is>
       </c>
-      <c r="CZ4" t="inlineStr">
+      <c r="DA4" t="inlineStr">
         <is>
           <t>Le Président 125,000 750</t>
         </is>
       </c>
-      <c r="DA4" t="inlineStr">
+      <c r="DB4" t="inlineStr">
         <is>
           <t>Le Président 125,000 750 Transform your CB with the defensive excellence that made Laurent Blanc one of the greatest. Cool, composed, and unbeatable. Laporte 90 CB PAC 85 SHO 60 PAS 87 DRI 84 DEF 91 PHY 90 L 5 ★ 5 CB 79.3 Laporte 92 CB PAC 88 SHO 61 PAS 87 DRI 89 DEF 93 PHY 92 L 5 ★ 5 CB 91.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position CB Max PS 10 Max PS+ 2 Heading Accuracy Max. 94 UPGRADES +20 OVR 92 +3 WF 4 +30 Composure 92 +25 Aggression 90 +30 Short Pass 90 +30 Reactions 92 +30 Defensive Awareness 93 +30 Interceptions 92 +25 Stamina 90 +30 Heading Acc. 90 +20 Dribbling 87 +20 Sprint Speed 90 +25 Strength 91 +20 Balance 87 +25 Penalties 94 +30 Standing Tackle 94 +20 Acceleration 86 +20 Agility 88 +30 Long Pass 90 +25 Jumping 88 +30 Sliding Tackle 92 +30 Ball Control 92 3 7 in 7 days in 14 days 59% 41%</t>
         </is>
@@ -1627,31 +1635,31 @@
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="n">
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
         <v>14</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
         <v>95</v>
       </c>
-      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="n">
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="n">
         <v>14</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BD5" t="n">
         <v>92</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BE5" t="n">
         <v>14</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BF5" t="n">
         <v>93</v>
       </c>
-      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr"/>
@@ -1661,23 +1669,23 @@
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="n">
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="n">
         <v>14</v>
       </c>
-      <c r="BQ5" t="n">
+      <c r="BR5" t="n">
         <v>90</v>
       </c>
-      <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="inlineStr"/>
       <c r="BT5" t="inlineStr"/>
       <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="n">
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="n">
         <v>7</v>
       </c>
-      <c r="BW5" t="n">
+      <c r="BX5" t="n">
         <v>93</v>
       </c>
-      <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="inlineStr"/>
       <c r="CA5" t="inlineStr"/>
@@ -1689,48 +1697,49 @@
       <c r="CG5" t="inlineStr"/>
       <c r="CH5" t="inlineStr"/>
       <c r="CI5" t="inlineStr"/>
-      <c r="CJ5" t="n">
+      <c r="CJ5" t="inlineStr"/>
+      <c r="CK5" t="n">
         <v>7</v>
       </c>
-      <c r="CK5" t="n">
+      <c r="CL5" t="n">
         <v>92</v>
       </c>
-      <c r="CL5" t="inlineStr"/>
       <c r="CM5" t="inlineStr"/>
-      <c r="CN5" t="n">
+      <c r="CN5" t="inlineStr"/>
+      <c r="CO5" t="n">
         <v>7</v>
       </c>
-      <c r="CO5" t="n">
+      <c r="CP5" t="n">
         <v>92</v>
       </c>
-      <c r="CP5" t="inlineStr"/>
       <c r="CQ5" t="inlineStr"/>
       <c r="CR5" t="inlineStr"/>
       <c r="CS5" t="inlineStr"/>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="inlineStr"/>
       <c r="CV5" t="inlineStr"/>
-      <c r="CW5" t="inlineStr">
+      <c r="CW5" t="inlineStr"/>
+      <c r="CX5" t="inlineStr">
         <is>
           <t>+1 OVR +7 Shot Power 95 +7 Vision 92 +7 Crossing 93 +7 Balance 90 +7 Dribbling 93 +7 Jumping 92 +7 Strength 92 Level 1 Moleiro 88 LM PAC 91 SHO 87 PAS 88 DRI 91 DEF 62 PHY 77 CAM LW R 4 ★ 4 Moleiro 89 LM PAC 91 SHO 88 PAS 89 DRI 91 DEF 62 PHY 77 CAM LW R 4 ★ 4 UPGRADES +1 OVR +7 Shot Power 95 +7 Vision 92 +7 Crossing 93 +7 Balance 90</t>
         </is>
       </c>
-      <c r="CX5" t="inlineStr">
+      <c r="CY5" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Details Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY5" t="inlineStr">
+      <c r="CZ5" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Details Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ5" t="inlineStr">
+      <c r="DA5" t="inlineStr">
         <is>
           <t>Lucky Number Seven 3</t>
         </is>
       </c>
-      <c r="DA5" t="inlineStr">
+      <c r="DB5" t="inlineStr">
         <is>
           <t>Lucky Number Seven 3 Hit your stride with Lucky Number Seven and give your eligible player boosts across key stats. Riise 88 LB PAC 88 SHO 83 PAS 86 DRI 85 DEF 86 PHY 88 LM L 4 ★ 4 LB 88.2 Riise 89 LB PAC 88 SHO 83 PAS 88 DRI 89 DEF 86 PHY 91 LM L 4 ★ 4 LB 89.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 UPGRADES +1 OVR +7 Shot Power 95 +7 Vision 92 +7 Crossing 93 +7 Balance 90 +7 Dribbling 93 +7 Jumping 92 +7 Strength 92 in 6 days in 13 days 26% 74%</t>
         </is>
@@ -1811,38 +1820,38 @@
       <c r="X6" t="n">
         <v>30</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
         <v>90</v>
       </c>
-      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="n">
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
         <v>15</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AF6" t="n">
         <v>87</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="n">
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
         <v>20</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AN6" t="n">
         <v>89</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AO6" t="n">
         <v>20</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AP6" t="n">
         <v>92</v>
       </c>
-      <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
@@ -1866,118 +1875,119 @@
       <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="n">
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="n">
         <v>10</v>
       </c>
-      <c r="BO6" t="n">
+      <c r="BP6" t="n">
         <v>88</v>
       </c>
-      <c r="BP6" t="n">
+      <c r="BQ6" t="n">
         <v>10</v>
       </c>
-      <c r="BQ6" t="n">
+      <c r="BR6" t="n">
         <v>86</v>
       </c>
-      <c r="BR6" t="n">
+      <c r="BS6" t="n">
         <v>10</v>
       </c>
-      <c r="BS6" t="n">
+      <c r="BT6" t="n">
         <v>88</v>
       </c>
-      <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="inlineStr"/>
       <c r="BW6" t="inlineStr"/>
-      <c r="BX6" t="n">
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="n">
         <v>10</v>
       </c>
-      <c r="BY6" t="n">
+      <c r="BZ6" t="n">
         <v>88</v>
       </c>
-      <c r="BZ6" t="n">
+      <c r="CA6" t="n">
         <v>40</v>
       </c>
-      <c r="CA6" t="n">
+      <c r="CB6" t="n">
         <v>91</v>
       </c>
-      <c r="CB6" t="n">
+      <c r="CC6" t="n">
         <v>20</v>
       </c>
-      <c r="CC6" t="n">
+      <c r="CD6" t="n">
         <v>83</v>
       </c>
-      <c r="CD6" t="n">
+      <c r="CE6" t="n">
         <v>20</v>
       </c>
-      <c r="CE6" t="n">
+      <c r="CF6" t="n">
         <v>91</v>
       </c>
-      <c r="CF6" t="n">
+      <c r="CG6" t="n">
         <v>20</v>
       </c>
-      <c r="CG6" t="n">
+      <c r="CH6" t="n">
         <v>90</v>
       </c>
-      <c r="CH6" t="n">
+      <c r="CI6" t="n">
         <v>20</v>
       </c>
-      <c r="CI6" t="n">
+      <c r="CJ6" t="n">
         <v>93</v>
       </c>
-      <c r="CJ6" t="n">
+      <c r="CK6" t="n">
         <v>15</v>
       </c>
-      <c r="CK6" t="n">
+      <c r="CL6" t="n">
         <v>88</v>
       </c>
-      <c r="CL6" t="n">
+      <c r="CM6" t="n">
         <v>20</v>
       </c>
-      <c r="CM6" t="n">
+      <c r="CN6" t="n">
         <v>92</v>
       </c>
-      <c r="CN6" t="n">
+      <c r="CO6" t="n">
         <v>30</v>
       </c>
-      <c r="CO6" t="n">
+      <c r="CP6" t="n">
         <v>88</v>
       </c>
-      <c r="CP6" t="n">
+      <c r="CQ6" t="n">
         <v>15</v>
       </c>
-      <c r="CQ6" t="n">
+      <c r="CR6" t="n">
         <v>86</v>
       </c>
-      <c r="CR6" t="inlineStr"/>
       <c r="CS6" t="inlineStr"/>
-      <c r="CT6" t="n">
-        <v>4</v>
-      </c>
+      <c r="CT6" t="inlineStr"/>
       <c r="CU6" t="n">
         <v>4</v>
       </c>
-      <c r="CV6" t="inlineStr"/>
-      <c r="CW6" t="inlineStr">
+      <c r="CV6" t="n">
+        <v>4</v>
+      </c>
+      <c r="CW6" t="inlineStr"/>
+      <c r="CX6" t="inlineStr">
         <is>
           <t>+15 OVR 90 +15 PAS 87 CB +2 WF 4 +20 Interceptions 91 +15 Strength 88 +20 Standing Tackle 90 +20 Defensive Awareness 91 +20 Stamina 92 +10 Composure 88 +10 Balance 86 +20 Acceleration 89 +15 Aggression 86 +20 Heading Acc. 83 +20 Sprint Speed 92 +10 Agility 88 +15 Jumping 88 +20 Sliding Tackle 93 +10 Reactions 88 3 7 Level 1 Wan-Bissaka 89 RB PAC 90 SHO 60 PAS 86 DRI 87 DEF 88 PHY 85 RM R 5 ★ 5 Wan-Bissaka 90 RB PAC 90 SHO 60 PAS 86 DRI 87 DEF 88 PHY 87 RM CB R 5 ★ 5 UPGRADES +15 OVR 90 CB +2 WF 4 +20 Interceptions 91 +15 Strength 88 3</t>
         </is>
       </c>
-      <c r="CX6" t="inlineStr">
+      <c r="CY6" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Max Pos. 3 Overall Max. 89 Position RB Excluded Position CB Max PS 10 Max PS+ 2 Details Submit by in 5 days Expiry in 12 days Coins Cost 35,000 Points Cost 200</t>
         </is>
       </c>
-      <c r="CY6" t="inlineStr">
+      <c r="CZ6" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Max Pos. 3 Overall Max. 89 Position RB Excluded Position CB Max PS 10 Max PS+ 2 Details Submit by in 5 days Expiry in 12 days Coins Cost 35,000 Points Cost 200</t>
         </is>
       </c>
-      <c r="CZ6" t="inlineStr">
+      <c r="DA6" t="inlineStr">
         <is>
           <t>Fullback Takeover 35,000 200</t>
         </is>
       </c>
-      <c r="DA6" t="inlineStr">
+      <c r="DB6" t="inlineStr">
         <is>
           <t>Fullback Takeover 35,000 200 Speed at the back. Power in every duel. A certain alpine player once ruled the center with unexpected power. Shift the role, break the line, and rediscover that unstoppable edge. Kimmich 89 RB PAC 81 SHO 74 PAS 89 DRI 85 DEF 85 PHY 80 CDM CM R 3 ★ 4 RB 81.0 Kimmich 90 RB PAC 91 SHO 74 PAS 89 DRI 85 DEF 90 PHY 88 CB CDM CM R 3 ★ 4 RB 89.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max Pos. 3 Overall Max. 89 Position RB Excluded Position CB Max PS 10 Max PS+ 2 UPGRADES +15 OVR 90 +15 PAS 87 CB +2 WF 4 +20 Interceptions 91 +15 Strength 88 +20 Standing Tackle 90 +20 Defensive Awareness 91 +20 Stamina 92 +10 Composure 88 +10 Balance 86 +20 Acceleration 89 +15 Aggression 86 +20 Heading Acc. 83 +20 Sprint Speed 92 +10 Agility 88 +15 Jumping 88 +20 Sliding Tackle 93 +10 Reactions 88 3 7 Show less in 5 days in 12 days 22% 78%</t>
         </is>
@@ -2046,10 +2056,10 @@
       <c r="X7" t="n">
         <v>10</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
         <v>91</v>
       </c>
-      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -2061,202 +2071,203 @@
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="n">
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="n">
         <v>5</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AN7" t="n">
         <v>89</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AO7" t="n">
         <v>10</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AP7" t="n">
         <v>89</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AQ7" t="n">
         <v>5</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AR7" t="n">
         <v>91</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AS7" t="n">
         <v>5</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AT7" t="n">
         <v>89</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
         <v>5</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AV7" t="n">
         <v>88</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AW7" t="n">
         <v>5</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AX7" t="n">
         <v>87</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AY7" t="n">
         <v>5</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="AZ7" t="n">
         <v>86</v>
       </c>
-      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="n">
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="n">
         <v>10</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BD7" t="n">
         <v>91</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BE7" t="n">
         <v>10</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BF7" t="n">
         <v>86</v>
       </c>
-      <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="n">
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="n">
         <v>5</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BJ7" t="n">
         <v>90</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BK7" t="n">
         <v>5</v>
       </c>
-      <c r="BK7" t="n">
+      <c r="BL7" t="n">
         <v>90</v>
       </c>
-      <c r="BL7" t="n">
+      <c r="BM7" t="n">
         <v>5</v>
       </c>
-      <c r="BM7" t="n">
+      <c r="BN7" t="n">
         <v>90</v>
       </c>
-      <c r="BN7" t="n">
+      <c r="BO7" t="n">
         <v>5</v>
       </c>
-      <c r="BO7" t="n">
+      <c r="BP7" t="n">
         <v>92</v>
       </c>
-      <c r="BP7" t="n">
+      <c r="BQ7" t="n">
         <v>5</v>
       </c>
-      <c r="BQ7" t="n">
+      <c r="BR7" t="n">
         <v>92</v>
       </c>
-      <c r="BR7" t="n">
+      <c r="BS7" t="n">
         <v>5</v>
       </c>
-      <c r="BS7" t="n">
+      <c r="BT7" t="n">
         <v>90</v>
       </c>
-      <c r="BT7" t="n">
+      <c r="BU7" t="n">
         <v>5</v>
       </c>
-      <c r="BU7" t="n">
+      <c r="BV7" t="n">
         <v>91</v>
       </c>
-      <c r="BV7" t="n">
+      <c r="BW7" t="n">
         <v>5</v>
       </c>
-      <c r="BW7" t="n">
+      <c r="BX7" t="n">
         <v>92</v>
       </c>
-      <c r="BX7" t="n">
+      <c r="BY7" t="n">
         <v>5</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="BZ7" t="n">
         <v>87</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="CA7" t="n">
         <v>5</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CB7" t="n">
         <v>88</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CC7" t="n">
         <v>5</v>
       </c>
-      <c r="CC7" t="n">
+      <c r="CD7" t="n">
         <v>85</v>
       </c>
-      <c r="CD7" t="n">
+      <c r="CE7" t="n">
         <v>5</v>
       </c>
-      <c r="CE7" t="n">
+      <c r="CF7" t="n">
         <v>86</v>
       </c>
-      <c r="CF7" t="n">
+      <c r="CG7" t="n">
         <v>5</v>
       </c>
-      <c r="CG7" t="n">
+      <c r="CH7" t="n">
         <v>86</v>
       </c>
-      <c r="CH7" t="n">
+      <c r="CI7" t="n">
         <v>10</v>
       </c>
-      <c r="CI7" t="n">
+      <c r="CJ7" t="n">
         <v>90</v>
       </c>
-      <c r="CJ7" t="n">
+      <c r="CK7" t="n">
         <v>5</v>
       </c>
-      <c r="CK7" t="n">
+      <c r="CL7" t="n">
         <v>90</v>
       </c>
-      <c r="CL7" t="n">
+      <c r="CM7" t="n">
         <v>5</v>
       </c>
-      <c r="CM7" t="n">
+      <c r="CN7" t="n">
         <v>90</v>
       </c>
-      <c r="CN7" t="n">
+      <c r="CO7" t="n">
         <v>5</v>
       </c>
-      <c r="CO7" t="n">
+      <c r="CP7" t="n">
         <v>86</v>
       </c>
-      <c r="CP7" t="n">
+      <c r="CQ7" t="n">
         <v>5</v>
       </c>
-      <c r="CQ7" t="n">
+      <c r="CR7" t="n">
         <v>86</v>
       </c>
-      <c r="CR7" t="n">
+      <c r="CS7" t="n">
         <v>4</v>
       </c>
-      <c r="CS7" t="inlineStr"/>
-      <c r="CT7" t="n">
+      <c r="CT7" t="inlineStr"/>
+      <c r="CU7" t="n">
         <v>8</v>
       </c>
-      <c r="CU7" t="inlineStr"/>
       <c r="CV7" t="inlineStr"/>
-      <c r="CW7" t="inlineStr">
+      <c r="CW7" t="inlineStr"/>
+      <c r="CX7" t="inlineStr">
         <is>
           <t>+5 OVR 91 +4 SM +4 WF +5 Sliding Tackle 90 +5 Vision 91 +5 Sprint Speed 89 +5 Crossing 86 +5 Long Pass 90 +5 Interceptions 88 +5 Volleys 86 +5 Composure 87 +5 Heading Acc. 85 +5 Curve 90 +5 Agility 92 +5 Positioning 91 +5 Standing Tackle 86 +5 Finishing 89 +5 Reactions 90 +5 Balance 92 +5 Strength 86 +5 Short Pass 90 +5 Jumping 90 +5 Long Shots 87 +5 Stamina 90 +5 Defensive Awareness 86 +5 Ball Control 91 +5 Dribbling 92 +5 Aggression 86 +5 Shot Power 88 +5 Acceleration 89 Level 1 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 Kerolin Nicoli 91 RM PAC 91 SHO 86 PAS 86 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 UPGRADES +5 OVR 91 +4 WF +5 Sliding Tackle 90 +5 Vision 91 +5 Sprint Speed 89 +5 Crossing 86</t>
         </is>
       </c>
-      <c r="CX7" t="inlineStr">
+      <c r="CY7" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 11 days Coins Cost 75,000 Points Cost 400</t>
         </is>
       </c>
-      <c r="CY7" t="inlineStr">
+      <c r="CZ7" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 11 days Coins Cost 75,000 Points Cost 400</t>
         </is>
       </c>
-      <c r="CZ7" t="inlineStr">
+      <c r="DA7" t="inlineStr">
         <is>
           <t>Gear 5 75,000 400</t>
         </is>
       </c>
-      <c r="DA7" t="inlineStr">
+      <c r="DB7" t="inlineStr">
         <is>
           <t>Gear 5 75,000 400 Hit the gear and let loose with +5 boosts across key stats. Bounce past rivals, stretch the game, and chase victory with a grin. Davies 89 LB PAC 95 SHO 80 PAS 84 DRI 87 DEF 82 PHY 84 LM L 4 ★ 3 LB 87.9 Davies 91 LB PAC 95 SHO 83 PAS 86 DRI 91 DEF 86 PHY 87 LM L 5 ★ 5 LB 91.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES +5 OVR 91 +4 SM +4 WF +5 Sliding Tackle 90 +5 Vision 91 +5 Sprint Speed 89 +5 Crossing 86 +5 Long Pass 90 +5 Interceptions 88 +5 Volleys 86 +5 Composure 87 +5 Heading Acc. 85 +5 Curve 90 +5 Agility 92 +5 Positioning 91 +5 Standing Tackle 86 +5 Finishing 89 +5 Reactions 90 +5 Balance 92 +5 Strength 86 +5 Short Pass 90 +5 Jumping 90 +5 Long Shots 87 +5 Stamina 90 +5 Defensive Awareness 86 +5 Ball Control 91 +5 Dribbling 92 +5 Aggression 86 +5 Shot Power 88 +5 Acceleration 89 in 4 days in 11 days 8% 92%</t>
         </is>
@@ -2336,19 +2347,19 @@
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="n">
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="n">
         <v>1</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AN8" t="n">
         <v>80</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AO8" t="n">
         <v>1</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AP8" t="n">
         <v>80</v>
       </c>
-      <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
@@ -2360,23 +2371,23 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="n">
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="n">
         <v>2</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BD8" t="n">
         <v>72</v>
       </c>
-      <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="n">
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="n">
         <v>4</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BJ8" t="n">
         <v>78</v>
       </c>
-      <c r="BJ8" t="inlineStr"/>
       <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="inlineStr"/>
       <c r="BM8" t="inlineStr"/>
@@ -2392,86 +2403,87 @@
       <c r="BW8" t="inlineStr"/>
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
-      <c r="BZ8" t="n">
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="n">
         <v>4</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CB8" t="n">
         <v>80</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CC8" t="n">
         <v>2</v>
       </c>
-      <c r="CC8" t="n">
+      <c r="CD8" t="n">
         <v>76</v>
       </c>
-      <c r="CD8" t="n">
+      <c r="CE8" t="n">
         <v>4</v>
       </c>
-      <c r="CE8" t="n">
+      <c r="CF8" t="n">
         <v>80</v>
       </c>
-      <c r="CF8" t="n">
+      <c r="CG8" t="n">
         <v>2</v>
       </c>
-      <c r="CG8" t="n">
+      <c r="CH8" t="n">
         <v>80</v>
       </c>
-      <c r="CH8" t="n">
+      <c r="CI8" t="n">
         <v>4</v>
       </c>
-      <c r="CI8" t="n">
+      <c r="CJ8" t="n">
         <v>78</v>
       </c>
-      <c r="CJ8" t="n">
+      <c r="CK8" t="n">
         <v>2</v>
       </c>
-      <c r="CK8" t="n">
+      <c r="CL8" t="n">
         <v>75</v>
       </c>
-      <c r="CL8" t="n">
+      <c r="CM8" t="n">
         <v>1</v>
       </c>
-      <c r="CM8" t="n">
+      <c r="CN8" t="n">
         <v>78</v>
       </c>
-      <c r="CN8" t="n">
+      <c r="CO8" t="n">
         <v>1</v>
       </c>
-      <c r="CO8" t="n">
+      <c r="CP8" t="n">
         <v>78</v>
       </c>
-      <c r="CP8" t="n">
+      <c r="CQ8" t="n">
         <v>1</v>
       </c>
-      <c r="CQ8" t="n">
+      <c r="CR8" t="n">
         <v>75</v>
       </c>
-      <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="inlineStr"/>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="inlineStr"/>
       <c r="CV8" t="inlineStr"/>
-      <c r="CW8" t="inlineStr">
+      <c r="CW8" t="inlineStr"/>
+      <c r="CX8" t="inlineStr">
         <is>
           <t>+2 Sliding Tackle 78 +2 Short Pass 78 +2 Defensive Awareness 80 +2 Interceptions 80 +1 Jumping 75 +1 Sprint Speed 80 +2 Standing Tackle 80 +1 Acceleration 80 +1 Strength 78 +2 Vision 72 +1 Aggression 75 +1 Stamina 78 +2 Heading Acc. 76 2 8 Level 1 Jair Cunha 74 CB PAC 67 SHO 38 PAS 59 DRI 58 DEF 73 PHY 80 R 2 ★ 4 Jair Cunha 74 CB PAC 67 SHO 38 PAS 60 DRI 58 DEF 75 PHY 80 R 2 ★ 4 UPGRADES +2 Sliding Tackle 78 +2 Short Pass 78 +2 Defensive Awareness 80 +2 Interceptions 80 +1 Jumping 75 8</t>
         </is>
       </c>
-      <c r="CX8" t="inlineStr">
+      <c r="CY8" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 74 Max PS 10 Max PS+ 2 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY8" t="inlineStr">
+      <c r="CZ8" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 74 Max PS 10 Max PS+ 2 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ8" t="inlineStr">
+      <c r="DA8" t="inlineStr">
         <is>
           <t>Steel Guard 3</t>
         </is>
       </c>
-      <c r="DA8" t="inlineStr">
+      <c r="DB8" t="inlineStr">
         <is>
           <t>Steel Guard 3 Cold as steel and impossible to break, dominates every duel, reads the game perfectly, and shuts down attacks before they even become a threat. Zima 74 CB PAC 76 SHO 38 PAS 54 DRI 62 DEF 75 PHY 75 R 2 ★ 4 CB 65.6 Zima 74 CB PAC 77 SHO 38 PAS 55 DRI 62 DEF 77 PHY 75 R 2 ★ 4 CB 75.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 74 Max PS 10 Max PS+ 2 UPGRADES +2 Sliding Tackle 78 +2 Short Pass 78 +2 Defensive Awareness 80 +2 Interceptions 80 +1 Jumping 75 +1 Sprint Speed 80 +2 Standing Tackle 80 +1 Acceleration 80 +1 Strength 78 +2 Vision 72 +1 Aggression 75 +1 Stamina 78 +2 Heading Acc. 76 2 8 in 3 days in 10 days 7% 93%</t>
         </is>
@@ -2548,10 +2560,10 @@
       <c r="X9" t="n">
         <v>60</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
         <v>91</v>
       </c>
-      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -2563,33 +2575,33 @@
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="n">
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="n">
         <v>30</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AN9" t="n">
         <v>93</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AO9" t="n">
         <v>60</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AP9" t="n">
         <v>93</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AQ9" t="n">
         <v>100</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AR9" t="n">
         <v>90</v>
       </c>
-      <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="n">
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
         <v>50</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
         <v>94</v>
       </c>
-      <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr"/>
@@ -2597,146 +2609,147 @@
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="n">
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="n">
         <v>30</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BF9" t="n">
         <v>94</v>
       </c>
-      <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="n">
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="n">
         <v>30</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BJ9" t="n">
         <v>92</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BK9" t="n">
         <v>50</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BL9" t="n">
         <v>93</v>
       </c>
-      <c r="BL9" t="inlineStr"/>
       <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="n">
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="n">
         <v>30</v>
       </c>
-      <c r="BO9" t="n">
+      <c r="BP9" t="n">
         <v>90</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BQ9" t="n">
         <v>30</v>
       </c>
-      <c r="BQ9" t="n">
+      <c r="BR9" t="n">
         <v>90</v>
       </c>
-      <c r="BR9" t="n">
+      <c r="BS9" t="n">
         <v>30</v>
       </c>
-      <c r="BS9" t="n">
+      <c r="BT9" t="n">
         <v>93</v>
       </c>
-      <c r="BT9" t="n">
+      <c r="BU9" t="n">
         <v>30</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="BV9" t="n">
         <v>90</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="BW9" t="n">
         <v>30</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="BX9" t="n">
         <v>89</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="BY9" t="n">
         <v>30</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="BZ9" t="n">
         <v>89</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CA9" t="n">
         <v>35</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CB9" t="n">
         <v>92</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CC9" t="n">
         <v>35</v>
       </c>
-      <c r="CC9" t="n">
+      <c r="CD9" t="n">
         <v>92</v>
       </c>
-      <c r="CD9" t="n">
+      <c r="CE9" t="n">
         <v>35</v>
       </c>
-      <c r="CE9" t="n">
+      <c r="CF9" t="n">
         <v>90</v>
       </c>
-      <c r="CF9" t="n">
+      <c r="CG9" t="n">
         <v>70</v>
       </c>
-      <c r="CG9" t="n">
+      <c r="CH9" t="n">
         <v>87</v>
       </c>
-      <c r="CH9" t="n">
+      <c r="CI9" t="n">
         <v>35</v>
       </c>
-      <c r="CI9" t="n">
+      <c r="CJ9" t="n">
         <v>95</v>
       </c>
-      <c r="CJ9" t="n">
+      <c r="CK9" t="n">
         <v>20</v>
       </c>
-      <c r="CK9" t="n">
+      <c r="CL9" t="n">
         <v>90</v>
       </c>
-      <c r="CL9" t="n">
+      <c r="CM9" t="n">
         <v>20</v>
       </c>
-      <c r="CM9" t="n">
+      <c r="CN9" t="n">
         <v>94</v>
       </c>
-      <c r="CN9" t="n">
+      <c r="CO9" t="n">
         <v>25</v>
       </c>
-      <c r="CO9" t="n">
+      <c r="CP9" t="n">
         <v>91</v>
       </c>
-      <c r="CP9" t="n">
+      <c r="CQ9" t="n">
         <v>50</v>
       </c>
-      <c r="CQ9" t="n">
+      <c r="CR9" t="n">
         <v>92</v>
       </c>
-      <c r="CR9" t="inlineStr"/>
       <c r="CS9" t="inlineStr"/>
-      <c r="CT9" t="n">
+      <c r="CT9" t="inlineStr"/>
+      <c r="CU9" t="n">
         <v>4</v>
       </c>
-      <c r="CU9" t="inlineStr"/>
       <c r="CV9" t="inlineStr"/>
-      <c r="CW9" t="inlineStr">
+      <c r="CW9" t="inlineStr"/>
+      <c r="CX9" t="inlineStr">
         <is>
           <t>+30 OVR 91 +4 WF +35 Standing Tackle 87 +25 Aggression 92 +30 Sprint Speed 93 +50 Positioning 90 +30 Crossing 94 +30 Composure 89 +30 Acceleration 93 +30 Dribbling 89 +35 Interceptions 92 +30 Short Pass 92 +50 Long Pass 93 +35 Defensive Awareness 90 +30 Balance 90 +30 Agility 90 +20 Stamina 94 +50 Shot Power 94 +35 Sliding Tackle 95 +20 Jumping 90 +35 Heading Acc. 92 +30 Reactions 93 +30 Ball Control 90 +25 Strength 91 3 7 Level 1 Dorgu 89 LM PAC 94 SHO 82 PAS 86 DRI 89 DEF 86 PHY 88 LB LW L 3 ★ 4 Dorgu 91 LM PAC 94 SHO 82 PAS 86 DRI 89 DEF 86 PHY 90 LB LW L 3 ★ 4 UPGRADES +30 OVR 91 +35 Standing Tackle 87 +25 Aggression 92 +30 Sprint Speed 93 +50 Positioning 90 7</t>
         </is>
       </c>
-      <c r="CX9" t="inlineStr">
+      <c r="CY9" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Position LB Excluded Position CB Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 9 days Coins Cost 50,000 Points Cost 300</t>
         </is>
       </c>
-      <c r="CY9" t="inlineStr">
+      <c r="CZ9" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Position LB Excluded Position CB Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 9 days Coins Cost 50,000 Points Cost 300</t>
         </is>
       </c>
-      <c r="CZ9" t="inlineStr">
+      <c r="DA9" t="inlineStr">
         <is>
           <t>Lightning Wingback 50,000 300</t>
         </is>
       </c>
-      <c r="DA9" t="inlineStr">
+      <c r="DB9" t="inlineStr">
         <is>
           <t>Lightning Wingback 50,000 300 Lightning-fast wingback to dominate the flank. Explosive pace, relentless overlaps, and pinpoint delivery. A constant threat in attack while tracking back with power and precision. Savona 83 RB PAC 84 SHO 57 PAS 75 DRI 76 DEF 83 PHY 83 LB RM R 2 ★ 3 RB 80.1 Savona 91 RB PAC 93 SHO 64 PAS 81 DRI 90 DEF 90 PHY 92 LB RM R 2 ★ 5 RB 94.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Position LB Excluded Position CB Max PS 10 Max PS+ 2 UPGRADES +30 OVR 91 +4 WF +35 Standing Tackle 87 +25 Aggression 92 +30 Sprint Speed 93 +50 Positioning 90 +30 Crossing 94 +30 Composure 89 +30 Acceleration 93 +30 Dribbling 89 +35 Interceptions 92 +30 Short Pass 92 +50 Long Pass 93 +35 Defensive Awareness 90 +30 Balance 90 +30 Agility 90 +20 Stamina 94 +50 Shot Power 94 +35 Sliding Tackle 95 +20 Jumping 90 +35 Heading Acc. 92 +30 Reactions 93 +30 Ball Control 90 +25 Strength 91 3 7 in 2 days in 9 days 91% 9%</t>
         </is>
@@ -2816,31 +2829,31 @@
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="n">
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
         <v>6</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AR10" t="n">
         <v>90</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AS10" t="n">
         <v>10</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AT10" t="n">
         <v>92</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>3</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
         <v>90</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AW10" t="n">
         <v>5</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AX10" t="n">
         <v>92</v>
       </c>
-      <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="inlineStr"/>
@@ -2854,13 +2867,13 @@
       <c r="BI10" t="inlineStr"/>
       <c r="BJ10" t="inlineStr"/>
       <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="n">
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="n">
         <v>8</v>
       </c>
-      <c r="BM10" t="n">
+      <c r="BN10" t="n">
         <v>95</v>
       </c>
-      <c r="BN10" t="inlineStr"/>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr"/>
       <c r="BQ10" t="inlineStr"/>
@@ -2895,27 +2908,28 @@
       <c r="CT10" t="inlineStr"/>
       <c r="CU10" t="inlineStr"/>
       <c r="CV10" t="inlineStr"/>
-      <c r="CW10" t="inlineStr">
+      <c r="CW10" t="inlineStr"/>
+      <c r="CX10" t="inlineStr">
         <is>
           <t>+3 Positioning 90 +5 Finishing 92 +5 Long Shots 92 +3 Shot Power 90 +8 Curve 95 8 Level 1 Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 Bobb 88 RW PAC 93 SHO 89 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 UPGRADES +3 Positioning 90 +5 Finishing 92 8</t>
         </is>
       </c>
-      <c r="CX10" t="inlineStr">
+      <c r="CY10" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 Details Submit by in 1 day Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY10" t="inlineStr">
+      <c r="CZ10" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 Details Submit by in 1 day Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ10" t="inlineStr">
+      <c r="DA10" t="inlineStr">
         <is>
           <t>Curve Your Enthusiasm 5</t>
         </is>
       </c>
-      <c r="DA10" t="inlineStr">
+      <c r="DB10" t="inlineStr">
         <is>
           <t>Curve Your Enthusiasm 5 Bend the game to your will and create moments of magic by transforming a player into a ball-bending specialist. Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 90 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 UPGRADES +3 Positioning 90 +5 Finishing 92 +5 Long Shots 92 +3 Shot Power 90 +8 Curve 95 8 in 1 day in 8 days 31% 69%</t>
         </is>
@@ -2988,10 +3002,10 @@
       <c r="X11" t="n">
         <v>34</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
         <v>92</v>
       </c>
-      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -3003,115 +3017,115 @@
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="n">
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="n">
         <v>34</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AN11" t="n">
         <v>93</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AO11" t="n">
         <v>34</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AP11" t="n">
         <v>91</v>
       </c>
-      <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="n">
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
         <v>17</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AT11" t="n">
         <v>92</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>17</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
         <v>91</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AW11" t="n">
         <v>17</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AX11" t="n">
         <v>90</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="AY11" t="n">
         <v>17</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="AZ11" t="n">
         <v>86</v>
       </c>
-      <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="n">
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="n">
         <v>34</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BD11" t="n">
         <v>93</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BE11" t="n">
         <v>34</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BF11" t="n">
         <v>90</v>
       </c>
-      <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="n">
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="n">
         <v>17</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BJ11" t="n">
         <v>92</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BK11" t="n">
         <v>17</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BL11" t="n">
         <v>91</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BM11" t="n">
         <v>17</v>
       </c>
-      <c r="BM11" t="n">
+      <c r="BN11" t="n">
         <v>94</v>
       </c>
-      <c r="BN11" t="n">
+      <c r="BO11" t="n">
         <v>17</v>
       </c>
-      <c r="BO11" t="n">
+      <c r="BP11" t="n">
         <v>94</v>
       </c>
-      <c r="BP11" t="n">
+      <c r="BQ11" t="n">
         <v>17</v>
       </c>
-      <c r="BQ11" t="n">
+      <c r="BR11" t="n">
         <v>92</v>
       </c>
-      <c r="BR11" t="n">
+      <c r="BS11" t="n">
         <v>17</v>
       </c>
-      <c r="BS11" t="n">
+      <c r="BT11" t="n">
         <v>91</v>
       </c>
-      <c r="BT11" t="n">
+      <c r="BU11" t="n">
         <v>17</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="BV11" t="n">
         <v>91</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="BW11" t="n">
         <v>17</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="BX11" t="n">
         <v>92</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="BY11" t="n">
         <v>17</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="BZ11" t="n">
         <v>91</v>
       </c>
-      <c r="BZ11" t="inlineStr"/>
       <c r="CA11" t="inlineStr"/>
       <c r="CB11" t="inlineStr"/>
       <c r="CC11" t="inlineStr"/>
@@ -3129,36 +3143,37 @@
       <c r="CO11" t="inlineStr"/>
       <c r="CP11" t="inlineStr"/>
       <c r="CQ11" t="inlineStr"/>
-      <c r="CR11" t="n">
+      <c r="CR11" t="inlineStr"/>
+      <c r="CS11" t="n">
         <v>4</v>
       </c>
-      <c r="CS11" t="n">
+      <c r="CT11" t="n">
         <v>5</v>
       </c>
-      <c r="CT11" t="inlineStr"/>
       <c r="CU11" t="inlineStr"/>
       <c r="CV11" t="inlineStr"/>
-      <c r="CW11" t="inlineStr">
+      <c r="CW11" t="inlineStr"/>
+      <c r="CX11" t="inlineStr">
         <is>
           <t>+17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 Level 1 Gnabry 90 CAM PAC 92 SHO 90 PAS 90 DRI 90 DEF 51 PHY 73 RM LM ST LW R 4 ★ 5 Gnabry 92 CAM PAC 92 SHO 90 PAS 91 DRI 90 DEF 51 PHY 73 RM LM ST LW R 4 ★ 5 UPGRADES +17 OVR 92 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 3</t>
         </is>
       </c>
-      <c r="CX11" t="inlineStr">
+      <c r="CY11" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 10 hours Expiry in 7 days Coins Cost 100,000 Points Cost 500</t>
         </is>
       </c>
-      <c r="CY11" t="inlineStr">
+      <c r="CZ11" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 10 hours Expiry in 7 days Coins Cost 100,000 Points Cost 500</t>
         </is>
       </c>
-      <c r="CZ11" t="inlineStr">
+      <c r="DA11" t="inlineStr">
         <is>
           <t>Cut In, Say Less 100,000 500</t>
         </is>
       </c>
-      <c r="DA11" t="inlineStr">
+      <c r="DB11" t="inlineStr">
         <is>
           <t>Cut In, Say Less 100,000 500 Elevate your favourite qualified player with enhanced pace, dribbling, shooting, and passing, allowing them to cut inside, get past defenders, and deliver in decisive moments! Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 92 RW PAC 92 SHO 90 PAS 92 DRI 93 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 93.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 in 10 hours in 7 days 64% 36%</t>
         </is>
@@ -3235,40 +3250,40 @@
       <c r="X12" t="n">
         <v>20</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
         <v>86</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>35</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AB12" t="n">
         <v>80</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>15</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>82</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>10</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AF12" t="n">
         <v>82</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AG12" t="n">
         <v>15</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AH12" t="n">
         <v>88</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AI12" t="n">
         <v>5</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AJ12" t="n">
         <v>60</v>
       </c>
-      <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
@@ -3320,64 +3335,65 @@
       <c r="CG12" t="inlineStr"/>
       <c r="CH12" t="inlineStr"/>
       <c r="CI12" t="inlineStr"/>
-      <c r="CJ12" t="n">
+      <c r="CJ12" t="inlineStr"/>
+      <c r="CK12" t="n">
         <v>15</v>
       </c>
-      <c r="CK12" t="n">
+      <c r="CL12" t="n">
         <v>80</v>
       </c>
-      <c r="CL12" t="n">
+      <c r="CM12" t="n">
         <v>20</v>
       </c>
-      <c r="CM12" t="n">
+      <c r="CN12" t="n">
         <v>80</v>
       </c>
-      <c r="CN12" t="n">
+      <c r="CO12" t="n">
         <v>15</v>
       </c>
-      <c r="CO12" t="n">
+      <c r="CP12" t="n">
         <v>70</v>
       </c>
-      <c r="CP12" t="n">
+      <c r="CQ12" t="n">
         <v>15</v>
       </c>
-      <c r="CQ12" t="n">
+      <c r="CR12" t="n">
         <v>65</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>6</v>
       </c>
       <c r="CS12" t="n">
         <v>6</v>
       </c>
-      <c r="CT12" t="inlineStr"/>
+      <c r="CT12" t="n">
+        <v>6</v>
+      </c>
       <c r="CU12" t="inlineStr"/>
-      <c r="CV12" t="inlineStr">
+      <c r="CV12" t="inlineStr"/>
+      <c r="CW12" t="inlineStr">
         <is>
           <t>CAM Shadow Striker ++; CAM Half Winger +</t>
         </is>
       </c>
-      <c r="CW12" t="inlineStr">
+      <c r="CX12" t="inlineStr">
         <is>
           <t>+10 OVR 86 +25 PAC 80 +10 SHO 82 +10 DRI 88 +5 DEF 60 +10 PAS 82 +4 SM +15 Jumping 80 +20 Stamina 80 +15 Aggression 65 +15 Strength 70 CAM Shadow Striker ++ CAM Half Winger + 1 6 Level 1 Cahill 85 ST PAC 80 SHO 85 PAS 76 DRI 81 DEF 62 PHY 86 CM CAM R 3 ★ 4 Cahill 86 ST PAC 80 SHO 85 PAS 76 DRI 86 DEF 62 PHY 86 CM CAM R 5 ★ 4 UPGRADES +10 OVR 86 +10 PAC 80 +5 SHO 82 +5 DRI 88 +2 SM 6</t>
         </is>
       </c>
-      <c r="CX12" t="inlineStr">
+      <c r="CY12" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 85 Position CAM Max PS 10 Max PS+ 1 Pace Max. 85 Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY12" t="inlineStr">
+      <c r="CZ12" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 85 Position CAM Max PS 10 Max PS+ 1 Pace Max. 85 Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ12" t="inlineStr">
+      <c r="DA12" t="inlineStr">
         <is>
           <t>Star in Motion</t>
         </is>
       </c>
-      <c r="DA12" t="inlineStr">
+      <c r="DB12" t="inlineStr">
         <is>
           <t>Star in Motion Celebrate Jamal Musiala’s rise to football’s elite. Step into the spotlight with enhanced creativity, flair, and precision that define the face of the game’s new generation. Dunn 82 CM PAC 85 SHO 76 PAS 80 DRI 82 DEF 75 PHY 79 LB RM CAM R 4 ★ 4 RM 77.1 Dunn 86 CM PAC 85 SHO 82 PAS 82 DRI 88 DEF 75 PHY 79 LB RM CAM R 5 ★ 4 CAM 83.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 85 Position CAM Max PS 10 Max PS+ 1 Pace Max. 85 UPGRADES +10 OVR 86 +25 PAC 80 +10 SHO 82 +10 DRI 88 +5 DEF 60 +10 PAS 82 +4 SM +15 Jumping 80 +20 Stamina 80 +15 Aggression 65 +15 Strength 70 CAM Shadow Striker ++ CAM Half Winger + 1 6 Show less in 5 months in 5 months 90% 10%</t>
         </is>
@@ -3515,32 +3531,33 @@
       <c r="CS13" t="inlineStr"/>
       <c r="CT13" t="inlineStr"/>
       <c r="CU13" t="inlineStr"/>
-      <c r="CV13" t="inlineStr">
+      <c r="CV13" t="inlineStr"/>
+      <c r="CW13" t="inlineStr">
         <is>
           <t>GK Sweeper Keeper +</t>
         </is>
       </c>
-      <c r="CW13" t="inlineStr">
+      <c r="CX13" t="inlineStr">
         <is>
           <t>. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Solid Evo 70% of GG users upvoted this Evolution. Vote Now! 70% 30% Completion Difficulty Easy Number of Games 0 Recommended Position - Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Casteels 82 GK DIV 82 HAN 79 KIC 74 REF 85 SPD 45 POS 83 L 1 ★ 2 GK 79.3 Strakosha 80 GK DIV 82 HAN 78 KIC 75 REF 83 SPD 50 POS 80 R 1 ★ 1 GK 78.5 Bounou 82 GK DIV 81 HAN 82 KIC 76 REF 85 SPD 38 POS 82 L 1 ★ 2 GK 78.4 Provedel 82 GK DIV 83 HAN 79 KIC 80 REF 84 SPD 42 POS 83 R 1 ★ 2 GK 78.2 Grabara 82 GK DIV 84 HAN 80 KIC 78 REF 87 SPD 46 POS 82 R 1 ★ 3 GK 77.8 Svilar 82 GK DIV 80 HAN 80 KIC 77 REF 85 SPD 58 POS 82 R 1 ★ 3 GK 77.6 Evolution Upgrades GK Sweeper Keeper + Level 1 Misa 82 GK DIV 84 HAN 77 KIC 77 REF 80 SPD 61 POS 84 L 1 ★ 3 Misa 82 GK DIV 84 HAN 77 KIC 77 REF 80 SPD 61 POS 84 L 1 ★ 3 UPGRADES GK Sweeper Keeper +</t>
         </is>
       </c>
-      <c r="CX13" t="inlineStr">
+      <c r="CY13" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Position GK Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY13" t="inlineStr">
+      <c r="CZ13" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Position GK Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ13" t="inlineStr">
+      <c r="DA13" t="inlineStr">
         <is>
           <t>Intro to Training Camp EVOs I</t>
         </is>
       </c>
-      <c r="DA13" t="inlineStr">
+      <c r="DB13" t="inlineStr">
         <is>
           <t>Intro to Training Camp EVOs I Assign a GK to Training Camp Evolutions through the Companion App. When the training session concludes, collect their earned upgrades. Svilar 82 GK DIV 80 HAN 80 KIC 77 REF 85 SPD 58 POS 82 R 1 ★ 3 GK 76.7 Svilar 82 GK DIV 80 HAN 80 KIC 77 REF 85 SPD 58 POS 82 R 1 ★ 3 GK 77.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Position GK UPGRADES GK Sweeper Keeper + TRAINING TIME 1 day in 5 months in 5 months 70% 30%</t>
         </is>
@@ -3679,27 +3696,28 @@
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="inlineStr"/>
       <c r="CV14" t="inlineStr"/>
-      <c r="CW14" t="inlineStr">
+      <c r="CW14" t="inlineStr"/>
+      <c r="CX14" t="inlineStr">
         <is>
           <t>. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Solid Evo 76% of GG users upvoted this Evolution. Vote Now! 76% 24% Completion Difficulty Easy Number of Games 0 Recommended Position ST Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Paintsil 81 LM PAC 92 SHO 77 PAS 75 DRI 85 DEF 40 PHY 75 RM LW R 4 ★ 3 LM 79.8 Chiesa 81 RM PAC 87 SHO 80 PAS 75 DRI 83 DEF 44 PHY 68 LM RW ST R 4 ★ 4 RM 79.5 Kouassi 80 LM PAC 94 SHO 79 PAS 71 DRI 80 DEF 37 PHY 75 RM LW R 4 ★ 4 RM 79.4 Adeyemi 81 RM PAC 96 SHO 76 PAS 72 DRI 82 DEF 36 PHY 69 CAM RW LW L 4 ★ 4 LW 79.1 Nusa 81 LM PAC 90 SHO 81 PAS 77 DRI 86 DEF 46 PHY 70 CAM LW R 4 ★ 4 LW 79.0 Saint-Maximin 79 LW PAC 90 SHO 71 PAS 70 DRI 87 DEF 29 PHY 68 LM R 5 ★ 4 LM 78.8 Evolution Upgrades 4 Level 1 Lukébakio 82 RM PAC 87 SHO 81 PAS 76 DRI 83 DEF 31 PHY 64 RW ST L 4 ★ 3 Lukébakio 82 RM PAC 87 SHO 81 PAS 76 DRI 83 DEF 31 PHY 64 RW ST L 4 ★ 3 UPGRADES 4</t>
         </is>
       </c>
-      <c r="CX14" t="inlineStr">
+      <c r="CY14" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Max PS 3 Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY14" t="inlineStr">
+      <c r="CZ14" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Max PS 3 Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ14" t="inlineStr">
+      <c r="DA14" t="inlineStr">
         <is>
           <t>Intro to Training Camp EVOs II</t>
         </is>
       </c>
-      <c r="DA14" t="inlineStr">
+      <c r="DB14" t="inlineStr">
         <is>
           <t>Intro to Training Camp EVOs II Assign a Player to Training Camp Evolutions through the Companion App. When the training session concludes, collect their earned upgrades. Sarr 82 CAM PAC 93 SHO 82 PAS 80 DRI 82 DEF 32 PHY 74 CM RW R 3 ★ 2 RW 76.3 Sarr 82 CAM PAC 93 SHO 82 PAS 80 DRI 82 DEF 32 PHY 74 CM RW R 3 ★ 2 RW 77.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Max PS 3 UPGRADES 4 TRAINING TIME 1 day in 5 months in 5 months 76% 24%</t>
         </is>
@@ -3760,22 +3778,22 @@
       <c r="X15" t="n">
         <v>2</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
         <v>82</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>2</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
         <v>83</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>2</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>83</v>
       </c>
-      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
@@ -3846,27 +3864,28 @@
       <c r="CT15" t="inlineStr"/>
       <c r="CU15" t="inlineStr"/>
       <c r="CV15" t="inlineStr"/>
-      <c r="CW15" t="inlineStr">
+      <c r="CW15" t="inlineStr"/>
+      <c r="CX15" t="inlineStr">
         <is>
           <t>+1 OVR 82 +1 PAC 83 +1 SHO 83 Level 1 Bergvall 81 CM PAC 79 SHO 70 PAS 81 DRI 82 DEF 78 PHY 79 CDM CAM R 3 ★ 3 Bergvall 82 CM PAC 80 SHO 71 PAS 81 DRI 82 DEF 78 PHY 79 CDM CAM R 3 ★ 3 UPGRADES +1 OVR 82 +1 PAC 83 +1 SHO 83</t>
         </is>
       </c>
-      <c r="CX15" t="inlineStr">
+      <c r="CY15" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 81 Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY15" t="inlineStr">
+      <c r="CZ15" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 81 Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ15" t="inlineStr">
+      <c r="DA15" t="inlineStr">
         <is>
           <t>Intro to Evolutions 2</t>
         </is>
       </c>
-      <c r="DA15" t="inlineStr">
+      <c r="DB15" t="inlineStr">
         <is>
           <t>Intro to Evolutions 2 Welcome to FC 26! Kick things off by exploring Evolutions, where you can upgrade Players over time until they reach their stated maximum. Chiesa 81 RM PAC 87 SHO 80 PAS 75 DRI 83 DEF 44 PHY 68 LM RW ST R 4 ★ 4 LM 78.5 Chiesa 82 RM PAC 87 SHO 81 PAS 75 DRI 83 DEF 44 PHY 68 LM RW ST R 4 ★ 4 LM 78.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 81 UPGRADES +1 OVR 82 +1 PAC 83 +1 SHO 83 in 5 months in 5 months 80% 20%</t>
         </is>
@@ -4005,27 +4024,28 @@
       <c r="CT16" t="inlineStr"/>
       <c r="CU16" t="inlineStr"/>
       <c r="CV16" t="inlineStr"/>
-      <c r="CW16" t="inlineStr">
+      <c r="CW16" t="inlineStr"/>
+      <c r="CX16" t="inlineStr">
         <is>
           <t>7 Level 1 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 UPGRADES 7</t>
         </is>
       </c>
-      <c r="CX16" t="inlineStr">
+      <c r="CY16" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY16" t="inlineStr">
+      <c r="CZ16" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ16" t="inlineStr">
+      <c r="DA16" t="inlineStr">
         <is>
           <t>Tiki Taka</t>
         </is>
       </c>
-      <c r="DA16" t="inlineStr">
+      <c r="DB16" t="inlineStr">
         <is>
           <t>Tiki Taka Unlocked by completing the Score 5 task in the French TOTS Flash Rush objective Rijkaard 89 CDM PAC 84 SHO 80 PAS 85 DRI 86 DEF 89 PHY 88 CB CM R 4 ★ 4 CDM 87.2 Rijkaard 89 CDM PAC 84 SHO 80 PAS 85 DRI 86 DEF 89 PHY 88 CB CM R 4 ★ 4 CDM 88.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 5 days in 5 days 5% 95%</t>
         </is>
@@ -4164,27 +4184,28 @@
       <c r="CT17" t="inlineStr"/>
       <c r="CU17" t="inlineStr"/>
       <c r="CV17" t="inlineStr"/>
-      <c r="CW17" t="inlineStr">
+      <c r="CW17" t="inlineStr"/>
+      <c r="CX17" t="inlineStr">
         <is>
           <t>3 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES 3</t>
         </is>
       </c>
-      <c r="CX17" t="inlineStr">
+      <c r="CY17" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY17" t="inlineStr">
+      <c r="CZ17" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ17" t="inlineStr">
+      <c r="DA17" t="inlineStr">
         <is>
           <t>Rapid+</t>
         </is>
       </c>
-      <c r="DA17" t="inlineStr">
+      <c r="DB17" t="inlineStr">
         <is>
           <t>Rapid+ Unlocked by completing the Assist in 10 task in the Ligue 1 TOTS Exhibition objective Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 84.0 Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 85.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 8 days in 8 days 91% 9%</t>
         </is>
@@ -4323,27 +4344,28 @@
       <c r="CT18" t="inlineStr"/>
       <c r="CU18" t="inlineStr"/>
       <c r="CV18" t="inlineStr"/>
-      <c r="CW18" t="inlineStr">
+      <c r="CW18" t="inlineStr"/>
+      <c r="CX18" t="inlineStr">
         <is>
           <t>3 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES 3</t>
         </is>
       </c>
-      <c r="CX18" t="inlineStr">
+      <c r="CY18" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY18" t="inlineStr">
+      <c r="CZ18" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ18" t="inlineStr">
+      <c r="DA18" t="inlineStr">
         <is>
           <t>First Touch+</t>
         </is>
       </c>
-      <c r="DA18" t="inlineStr">
+      <c r="DB18" t="inlineStr">
         <is>
           <t>First Touch+ Unlocked by completing the Score in 10 task in the Ligue 1 TOTS Exhibition objective Nanasi 89 LM PAC 89 SHO 87 PAS 89 DRI 91 DEF 45 PHY 80 CM CAM R 5 ★ 4 CAM 89.6 Nanasi 89 LM PAC 89 SHO 87 PAS 89 DRI 91 DEF 45 PHY 80 CM CAM R 5 ★ 4 CAM 90.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 8 days in 8 days 62% 38%</t>
         </is>
@@ -4482,27 +4504,28 @@
       <c r="CT19" t="inlineStr"/>
       <c r="CU19" t="inlineStr"/>
       <c r="CV19" t="inlineStr"/>
-      <c r="CW19" t="inlineStr">
+      <c r="CW19" t="inlineStr"/>
+      <c r="CX19" t="inlineStr">
         <is>
           <t>7 Level 1 Ndoye 89 LM PAC 96 SHO 87 PAS 87 DRI 90 DEF 72 PHY 81 RM LW R 4 ★ 4 Ndoye 89 LM PAC 96 SHO 87 PAS 87 DRI 90 DEF 72 PHY 81 RM LW R 4 ★ 4 UPGRADES 7</t>
         </is>
       </c>
-      <c r="CX19" t="inlineStr">
+      <c r="CY19" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY19" t="inlineStr">
+      <c r="CZ19" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ19" t="inlineStr">
+      <c r="DA19" t="inlineStr">
         <is>
           <t>Tiki Taka and Low Driven Shot</t>
         </is>
       </c>
-      <c r="DA19" t="inlineStr">
+      <c r="DB19" t="inlineStr">
         <is>
           <t>Tiki Taka and Low Driven Shot Unlocked by completing the Score in 5 task in the TOTS: Champions Objective objective Luna 89 LM PAC 89 SHO 87 PAS 90 DRI 90 DEF 60 PHY 85 CAM LW R 4 ★ 5 CAM 86.2 Luna 89 LM PAC 89 SHO 87 PAS 90 DRI 90 DEF 60 PHY 85 CAM LW R 4 ★ 5 CAM 88.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 5 days in 5 days 9% 91%</t>
         </is>
@@ -4641,27 +4664,28 @@
       <c r="CT20" t="inlineStr"/>
       <c r="CU20" t="inlineStr"/>
       <c r="CV20" t="inlineStr"/>
-      <c r="CW20" t="inlineStr">
+      <c r="CW20" t="inlineStr"/>
+      <c r="CX20" t="inlineStr">
         <is>
           <t>7 Level 1 Prinz 89 ST PAC 91 SHO 90 PAS 80 DRI 88 DEF 53 PHY 91 R 4 ★ 4 Prinz 89 ST PAC 91 SHO 90 PAS 80 DRI 88 DEF 53 PHY 91 R 4 ★ 4 UPGRADES 7</t>
         </is>
       </c>
-      <c r="CX20" t="inlineStr">
+      <c r="CY20" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY20" t="inlineStr">
+      <c r="CZ20" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ20" t="inlineStr">
+      <c r="DA20" t="inlineStr">
         <is>
           <t>Intercept and Pinged Pass</t>
         </is>
       </c>
-      <c r="DA20" t="inlineStr">
+      <c r="DB20" t="inlineStr">
         <is>
           <t>Intercept and Pinged Pass Unlocked by completing the Win 4 task in the TOTS: Champions Objective objective ter Stegen 89 GK DIV 87 HAN 87 KIC 91 REF 89 SPD 53 POS 87 R 1 ★ 4 GK 85.9 ter Stegen 89 GK DIV 87 HAN 87 KIC 91 REF 89 SPD 53 POS 87 R 1 ★ 4 GK 87.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 5 days in 5 days 8% 92%</t>
         </is>
@@ -4800,27 +4824,28 @@
       <c r="CT21" t="inlineStr"/>
       <c r="CU21" t="inlineStr"/>
       <c r="CV21" t="inlineStr"/>
-      <c r="CW21" t="inlineStr">
+      <c r="CW21" t="inlineStr"/>
+      <c r="CX21" t="inlineStr">
         <is>
           <t>2 Level 1 Eto'o 89 ST PAC 92 SHO 90 PAS 79 DRI 87 DEF 45 PHY 80 R 4 ★ 4 Eto'o 89 ST PAC 92 SHO 90 PAS 79 DRI 87 DEF 45 PHY 80 R 4 ★ 4 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX21" t="inlineStr">
+      <c r="CY21" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY21" t="inlineStr">
+      <c r="CZ21" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ21" t="inlineStr">
+      <c r="DA21" t="inlineStr">
         <is>
           <t>Jockey+ &amp; Bruiser+</t>
         </is>
       </c>
-      <c r="DA21" t="inlineStr">
+      <c r="DB21" t="inlineStr">
         <is>
           <t>Jockey+ &amp; Bruiser+ Unlocked by completing the 3 Completions task in the Season 7 Spirit of Africa Weekly Play Completionist objective Dumfries 89 RB PAC 89 SHO 75 PAS 84 DRI 86 DEF 86 PHY 89 RM R 4 ★ 3 RB 85.3 Dumfries 89 RB PAC 89 SHO 75 PAS 84 DRI 86 DEF 86 PHY 89 RM R 4 ★ 3 RB 87.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 28 days in 28 days 12% 88%</t>
         </is>
@@ -4893,10 +4918,10 @@
       <c r="X22" t="n">
         <v>8</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
         <v>90</v>
       </c>
-      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
@@ -4908,164 +4933,165 @@
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="n">
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="n">
         <v>12</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="AN22" t="n">
         <v>90</v>
       </c>
-      <c r="AN22" t="n">
+      <c r="AO22" t="n">
         <v>12</v>
       </c>
-      <c r="AO22" t="n">
+      <c r="AP22" t="n">
         <v>90</v>
       </c>
-      <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr"/>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr"/>
       <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="n">
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="n">
         <v>6</v>
       </c>
-      <c r="AW22" t="n">
+      <c r="AX22" t="n">
         <v>86</v>
       </c>
-      <c r="AX22" t="inlineStr"/>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="inlineStr"/>
-      <c r="BB22" t="n">
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="n">
         <v>8</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BD22" t="n">
         <v>88</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BE22" t="n">
         <v>6</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BF22" t="n">
         <v>88</v>
       </c>
-      <c r="BF22" t="inlineStr"/>
       <c r="BG22" t="inlineStr"/>
-      <c r="BH22" t="n">
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="n">
         <v>8</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BJ22" t="n">
         <v>90</v>
       </c>
-      <c r="BJ22" t="inlineStr"/>
       <c r="BK22" t="inlineStr"/>
       <c r="BL22" t="inlineStr"/>
       <c r="BM22" t="inlineStr"/>
-      <c r="BN22" t="n">
+      <c r="BN22" t="inlineStr"/>
+      <c r="BO22" t="n">
         <v>12</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BP22" t="n">
         <v>86</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BQ22" t="n">
         <v>16</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BR22" t="n">
         <v>90</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="BS22" t="n">
         <v>6</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="BT22" t="n">
         <v>88</v>
       </c>
-      <c r="BT22" t="inlineStr"/>
       <c r="BU22" t="inlineStr"/>
       <c r="BV22" t="inlineStr"/>
       <c r="BW22" t="inlineStr"/>
-      <c r="BX22" t="n">
+      <c r="BX22" t="inlineStr"/>
+      <c r="BY22" t="n">
         <v>8</v>
       </c>
-      <c r="BY22" t="n">
+      <c r="BZ22" t="n">
         <v>90</v>
       </c>
-      <c r="BZ22" t="n">
+      <c r="CA22" t="n">
         <v>8</v>
       </c>
-      <c r="CA22" t="n">
+      <c r="CB22" t="n">
         <v>92</v>
       </c>
-      <c r="CB22" t="n">
+      <c r="CC22" t="n">
         <v>5</v>
       </c>
-      <c r="CC22" t="n">
+      <c r="CD22" t="n">
         <v>88</v>
       </c>
-      <c r="CD22" t="n">
+      <c r="CE22" t="n">
         <v>8</v>
       </c>
-      <c r="CE22" t="n">
+      <c r="CF22" t="n">
         <v>91</v>
       </c>
-      <c r="CF22" t="inlineStr"/>
       <c r="CG22" t="inlineStr"/>
-      <c r="CH22" t="n">
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="n">
         <v>6</v>
       </c>
-      <c r="CI22" t="n">
+      <c r="CJ22" t="n">
         <v>90</v>
       </c>
-      <c r="CJ22" t="n">
+      <c r="CK22" t="n">
         <v>5</v>
       </c>
-      <c r="CK22" t="n">
+      <c r="CL22" t="n">
         <v>89</v>
       </c>
-      <c r="CL22" t="n">
+      <c r="CM22" t="n">
         <v>5</v>
       </c>
-      <c r="CM22" t="n">
+      <c r="CN22" t="n">
         <v>89</v>
       </c>
-      <c r="CN22" t="n">
+      <c r="CO22" t="n">
         <v>8</v>
       </c>
-      <c r="CO22" t="n">
+      <c r="CP22" t="n">
         <v>90</v>
       </c>
-      <c r="CP22" t="n">
+      <c r="CQ22" t="n">
         <v>8</v>
       </c>
-      <c r="CQ22" t="n">
+      <c r="CR22" t="n">
         <v>90</v>
       </c>
-      <c r="CR22" t="inlineStr"/>
       <c r="CS22" t="inlineStr"/>
-      <c r="CT22" t="n">
+      <c r="CT22" t="inlineStr"/>
+      <c r="CU22" t="n">
         <v>4</v>
       </c>
-      <c r="CU22" t="inlineStr"/>
       <c r="CV22" t="inlineStr"/>
-      <c r="CW22" t="inlineStr">
+      <c r="CW22" t="inlineStr"/>
+      <c r="CX22" t="inlineStr">
         <is>
           <t>+6 OVR 90 +4 WF +6 Acceleration 90 +6 Sprint Speed 90 +6 Agility 86 +8 Balance 90 +8 Interceptions 92 +8 Defensive Awareness 91 +6 Sliding Tackle 90 +8 Strength 90 +8 Aggression 90 +5 Stamina 89 +8 Vision 88 +6 Crossing 88 +8 Short Pass 90 +6 Long Shots 86 +5 Heading Acc. 88 +5 Jumping 89 +6 Reactions 88 +8 Composure 90 3 7 Level 1 Araujo 89 RB PAC 92 SHO 50 PAS 86 DRI 87 DEF 87 PHY 89 RM R 4 ★ 4 Araujo 90 RB PAC 92 SHO 50 PAS 86 DRI 87 DEF 87 PHY 89 RM R 4 ★ 4 UPGRADES +2 OVR 90 +6 Acceleration 90 +6 Sprint Speed 90 +6 Agility 86 +8 Balance 90 3</t>
         </is>
       </c>
-      <c r="CX22" t="inlineStr">
+      <c r="CY22" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Min Pos. 2 Overall Max. 89 Position CB, LB, RB Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY22" t="inlineStr">
+      <c r="CZ22" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Min Pos. 2 Overall Max. 89 Position CB, LB, RB Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ22" t="inlineStr">
+      <c r="DA22" t="inlineStr">
         <is>
           <t>Versatile Defender</t>
         </is>
       </c>
-      <c r="DA22" t="inlineStr">
+      <c r="DB22" t="inlineStr">
         <is>
           <t>Versatile Defender Unlocked by completing the Darwin Cup objective Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 84.9 Walker 90 RB PAC 91 SHO 81 PAS 88 DRI 87 DEF 91 PHY 91 RM R 4 ★ 5 RB 92.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Min Pos. 2 Overall Max. 89 Position CB, LB, RB Max PS 10 Max PS+ 2 UPGRADES +6 OVR 90 +4 WF +6 Acceleration 90 +6 Sprint Speed 90 +6 Agility 86 +8 Balance 90 +8 Interceptions 92 +8 Defensive Awareness 91 +6 Sliding Tackle 90 +8 Strength 90 +8 Aggression 90 +5 Stamina 89 +8 Vision 88 +6 Crossing 88 +8 Short Pass 90 +6 Long Shots 86 +5 Heading Acc. 88 +5 Jumping 89 +6 Reactions 88 +8 Composure 90 3 7 in 4 days in 4 days 81% 19%</t>
         </is>
@@ -5208,27 +5234,28 @@
       <c r="CT23" t="inlineStr"/>
       <c r="CU23" t="inlineStr"/>
       <c r="CV23" t="inlineStr"/>
-      <c r="CW23" t="inlineStr">
+      <c r="CW23" t="inlineStr"/>
+      <c r="CX23" t="inlineStr">
         <is>
           <t>3 7 Level 1 James 89 ST PAC 91 SHO 86 PAS 82 DRI 91 DEF 44 PHY 86 CAM R 4 ★ 5 James 89 ST PAC 91 SHO 86 PAS 82 DRI 91 DEF 44 PHY 86 CAM R 4 ★ 5 UPGRADES 3 7</t>
         </is>
       </c>
-      <c r="CX23" t="inlineStr">
+      <c r="CY23" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY23" t="inlineStr">
+      <c r="CZ23" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ23" t="inlineStr">
+      <c r="DA23" t="inlineStr">
         <is>
           <t>Technical+ and Finesse Shot</t>
         </is>
       </c>
-      <c r="DA23" t="inlineStr">
+      <c r="DB23" t="inlineStr">
         <is>
           <t>Technical+ and Finesse Shot Unlocked by completing the Win Tournament task in the Darwin Cup objective Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 88.9 Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 89.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 3 7 in 4 days in 4 days 66% 34%</t>
         </is>
@@ -5371,27 +5398,28 @@
       <c r="CT24" t="inlineStr"/>
       <c r="CU24" t="inlineStr"/>
       <c r="CV24" t="inlineStr"/>
-      <c r="CW24" t="inlineStr">
+      <c r="CW24" t="inlineStr"/>
+      <c r="CX24" t="inlineStr">
         <is>
           <t>2 8 Level 1 Matsukubo 89 CAM PAC 88 SHO 90 PAS 89 DRI 91 DEF 70 PHY 78 CM ST R 3 ★ 4 Matsukubo 89 CAM PAC 88 SHO 90 PAS 89 DRI 91 DEF 70 PHY 78 CM ST R 3 ★ 4 UPGRADES 2 8</t>
         </is>
       </c>
-      <c r="CX24" t="inlineStr">
+      <c r="CY24" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY24" t="inlineStr">
+      <c r="CZ24" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ24" t="inlineStr">
+      <c r="DA24" t="inlineStr">
         <is>
           <t>Anticipate+ and Intercept</t>
         </is>
       </c>
-      <c r="DA24" t="inlineStr">
+      <c r="DB24" t="inlineStr">
         <is>
           <t>Anticipate+ and Intercept Unlocked by completing the Win Quarter-Finals task in the Darwin Cup objective Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 84.9 Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 88.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 2 8 in 4 days in 4 days 33% 67%</t>
         </is>
@@ -5530,27 +5558,28 @@
       <c r="CT25" t="inlineStr"/>
       <c r="CU25" t="inlineStr"/>
       <c r="CV25" t="inlineStr"/>
-      <c r="CW25" t="inlineStr">
+      <c r="CW25" t="inlineStr"/>
+      <c r="CX25" t="inlineStr">
         <is>
           <t>3 Level 1 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 UPGRADES 3</t>
         </is>
       </c>
-      <c r="CX25" t="inlineStr">
+      <c r="CY25" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY25" t="inlineStr">
+      <c r="CZ25" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ25" t="inlineStr">
+      <c r="DA25" t="inlineStr">
         <is>
           <t>Tiki Taka+</t>
         </is>
       </c>
-      <c r="DA25" t="inlineStr">
+      <c r="DB25" t="inlineStr">
         <is>
           <t>Tiki Taka+ Unlocked by completing the May The 3rd Be With You EVO SBC Adopo 88 CM PAC 86 SHO 86 PAS 88 DRI 88 DEF 87 PHY 90 CDM R 4 ★ 4 CM 89.1 Adopo 88 CM PAC 86 SHO 86 PAS 88 DRI 88 DEF 87 PHY 90 CDM R 4 ★ 4 CM 90.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 9 days in 9 days 84% 16%</t>
         </is>
@@ -5612,13 +5641,13 @@
         <v>2</v>
       </c>
       <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="n">
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="n">
         <v>8</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AB26" t="n">
         <v>91</v>
       </c>
-      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
@@ -5626,13 +5655,13 @@
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="n">
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="n">
         <v>6</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AL26" t="n">
         <v>92</v>
       </c>
-      <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
@@ -5695,27 +5724,28 @@
       <c r="CT26" t="inlineStr"/>
       <c r="CU26" t="inlineStr"/>
       <c r="CV26" t="inlineStr"/>
-      <c r="CW26" t="inlineStr">
+      <c r="CW26" t="inlineStr"/>
+      <c r="CX26" t="inlineStr">
         <is>
           <t>+1 OVR +4 PAC 91 +3 PHY 92 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 90 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 78 CAM ST LW R 5 ★ 5 UPGRADES +1 OVR +4 PAC 91 +3 PHY 92</t>
         </is>
       </c>
-      <c r="CX26" t="inlineStr">
+      <c r="CY26" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY26" t="inlineStr">
+      <c r="CZ26" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ26" t="inlineStr">
+      <c r="DA26" t="inlineStr">
         <is>
           <t>Turbo Strength</t>
         </is>
       </c>
-      <c r="DA26" t="inlineStr">
+      <c r="DB26" t="inlineStr">
         <is>
           <t>Turbo Strength Unlocked by completing the Turbo Strength task in the Evolution Revolution objective Schlotterbeck 89 CB PAC 86 SHO 41 PAS 79 DRI 74 DEF 91 PHY 88 L 3 ★ 5 CB 89.3 Schlotterbeck 90 CB PAC 90 SHO 41 PAS 79 DRI 74 DEF 91 PHY 91 L 3 ★ 5 CB 91.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 UPGRADES +1 OVR +4 PAC 91 +3 PHY 92 in 1 day in 1 day 87% 13%</t>
         </is>
@@ -5803,23 +5833,23 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="inlineStr"/>
-      <c r="BB27" t="n">
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="n">
         <v>6</v>
       </c>
-      <c r="BC27" t="n">
+      <c r="BD27" t="n">
         <v>93</v>
       </c>
-      <c r="BD27" t="inlineStr"/>
       <c r="BE27" t="inlineStr"/>
       <c r="BF27" t="inlineStr"/>
       <c r="BG27" t="inlineStr"/>
-      <c r="BH27" t="n">
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="n">
         <v>6</v>
       </c>
-      <c r="BI27" t="n">
+      <c r="BJ27" t="n">
         <v>93</v>
       </c>
-      <c r="BJ27" t="inlineStr"/>
       <c r="BK27" t="inlineStr"/>
       <c r="BL27" t="inlineStr"/>
       <c r="BM27" t="inlineStr"/>
@@ -5858,27 +5888,28 @@
       <c r="CT27" t="inlineStr"/>
       <c r="CU27" t="inlineStr"/>
       <c r="CV27" t="inlineStr"/>
-      <c r="CW27" t="inlineStr">
+      <c r="CW27" t="inlineStr"/>
+      <c r="CX27" t="inlineStr">
         <is>
           <t>+3 Vision 93 +3 Short Pass 93 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 89 LM PAC 98 SHO 84 PAS 87 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES +3 Vision 93 +3 Short Pass 93</t>
         </is>
       </c>
-      <c r="CX27" t="inlineStr">
+      <c r="CY27" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY27" t="inlineStr">
+      <c r="CZ27" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ27" t="inlineStr">
+      <c r="DA27" t="inlineStr">
         <is>
           <t>Pass IQ 5</t>
         </is>
       </c>
-      <c r="DA27" t="inlineStr">
+      <c r="DB27" t="inlineStr">
         <is>
           <t>Pass IQ 5 Unlocked by completing the Pass IQ task in the Evolution Revolution objective Hjulmand 88 CDM PAC 84 SHO 84 PAS 86 DRI 84 DEF 88 PHY 88 CM R 4 ★ 4 CM 89.8 Hjulmand 88 CDM PAC 84 SHO 84 PAS 88 DRI 84 DEF 88 PHY 88 CM R 4 ★ 4 CM 90.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 UPGRADES +3 Vision 93 +3 Short Pass 93 in 1 day in 1 day 88% 13%</t>
         </is>
@@ -5962,19 +5993,19 @@
       <c r="AQ28" t="inlineStr"/>
       <c r="AR28" t="inlineStr"/>
       <c r="AS28" t="inlineStr"/>
-      <c r="AT28" t="n">
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="n">
         <v>16</v>
       </c>
-      <c r="AU28" t="n">
+      <c r="AV28" t="n">
         <v>93</v>
       </c>
-      <c r="AV28" t="n">
+      <c r="AW28" t="n">
         <v>16</v>
       </c>
-      <c r="AW28" t="n">
+      <c r="AX28" t="n">
         <v>93</v>
       </c>
-      <c r="AX28" t="inlineStr"/>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="inlineStr"/>
@@ -6025,27 +6056,28 @@
       <c r="CT28" t="inlineStr"/>
       <c r="CU28" t="inlineStr"/>
       <c r="CV28" t="inlineStr"/>
-      <c r="CW28" t="inlineStr">
+      <c r="CW28" t="inlineStr"/>
+      <c r="CX28" t="inlineStr">
         <is>
           <t>+8 Shot Power 93 +8 Long Shots 93 8 Level 1 Francisco Conceição 89 RM PAC 93 SHO 86 PAS 87 DRI 91 DEF 45 PHY 70 CAM RW L 4 ★ 3 Francisco Conceição 89 RM PAC 93 SHO 88 PAS 87 DRI 91 DEF 45 PHY 70 CAM RW L 4 ★ 3 UPGRADES +8 Shot Power 93 +8 Long Shots 93 8</t>
         </is>
       </c>
-      <c r="CX28" t="inlineStr">
+      <c r="CY28" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY28" t="inlineStr">
+      <c r="CZ28" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ28" t="inlineStr">
+      <c r="DA28" t="inlineStr">
         <is>
           <t>From Distance</t>
         </is>
       </c>
-      <c r="DA28" t="inlineStr">
+      <c r="DB28" t="inlineStr">
         <is>
           <t>From Distance Unlocked by completing the From Distance task in the Evolution Revolution objective Carlos Espí 88 ST PAC 91 SHO 86 PAS 80 DRI 88 DEF 58 PHY 94 R 4 ★ 4 ST 89.3 Carlos Espí 88 ST PAC 91 SHO 89 PAS 80 DRI 88 DEF 58 PHY 94 R 4 ★ 4 ST 89.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +8 Shot Power 93 +8 Long Shots 93 8 in 1 day in 1 day 85% 15%</t>
         </is>
@@ -6184,27 +6216,28 @@
       <c r="CT29" t="inlineStr"/>
       <c r="CU29" t="inlineStr"/>
       <c r="CV29" t="inlineStr"/>
-      <c r="CW29" t="inlineStr">
+      <c r="CW29" t="inlineStr"/>
+      <c r="CX29" t="inlineStr">
         <is>
           <t>8 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES 8</t>
         </is>
       </c>
-      <c r="CX29" t="inlineStr">
+      <c r="CY29" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY29" t="inlineStr">
+      <c r="CZ29" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ29" t="inlineStr">
+      <c r="DA29" t="inlineStr">
         <is>
           <t>Intercept &amp; Aerial Fortress</t>
         </is>
       </c>
-      <c r="DA29" t="inlineStr">
+      <c r="DB29" t="inlineStr">
         <is>
           <t>Intercept &amp; Aerial Fortress Unlocked by completing the Defensive Instinct task in the Evolution Revolution objective António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 86.6 António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 1 day in 1 day 33% 67%</t>
         </is>
@@ -6343,27 +6376,28 @@
       <c r="CT30" t="inlineStr"/>
       <c r="CU30" t="inlineStr"/>
       <c r="CV30" t="inlineStr"/>
-      <c r="CW30" t="inlineStr">
+      <c r="CW30" t="inlineStr"/>
+      <c r="CX30" t="inlineStr">
         <is>
           <t>8 Level 1 Eto'o 89 ST PAC 92 SHO 90 PAS 79 DRI 87 DEF 45 PHY 80 R 4 ★ 4 Eto'o 89 ST PAC 92 SHO 90 PAS 79 DRI 87 DEF 45 PHY 80 R 4 ★ 4 UPGRADES 8</t>
         </is>
       </c>
-      <c r="CX30" t="inlineStr">
+      <c r="CY30" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 7 days Expiry in 7 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY30" t="inlineStr">
+      <c r="CZ30" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 7 days Expiry in 7 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ30" t="inlineStr">
+      <c r="DA30" t="inlineStr">
         <is>
           <t>Speed to Finish</t>
         </is>
       </c>
-      <c r="DA30" t="inlineStr">
+      <c r="DB30" t="inlineStr">
         <is>
           <t>Speed to Finish Unlocked by completing the Score in 5 task in the TOTS: Champions Objective objective Mayulu 89 CM PAC 88 SHO 88 PAS 90 DRI 92 DEF 80 PHY 82 L 3 ★ 5 CM 88.3 Mayulu 89 CM PAC 88 SHO 88 PAS 90 DRI 92 DEF 80 PHY 82 L 3 ★ 5 CM 89.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 7 days in 7 days 62% 38%</t>
         </is>
@@ -6502,27 +6536,28 @@
       <c r="CT31" t="inlineStr"/>
       <c r="CU31" t="inlineStr"/>
       <c r="CV31" t="inlineStr"/>
-      <c r="CW31" t="inlineStr">
+      <c r="CW31" t="inlineStr"/>
+      <c r="CX31" t="inlineStr">
         <is>
           <t>8 Level 1 Uzun 89 CAM PAC 88 SHO 90 PAS 88 DRI 92 DEF 40 PHY 83 CM ST R 4 ★ 4 Uzun 89 CAM PAC 88 SHO 90 PAS 88 DRI 92 DEF 40 PHY 83 CM ST R 4 ★ 4 UPGRADES 8</t>
         </is>
       </c>
-      <c r="CX31" t="inlineStr">
+      <c r="CY31" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 7 days Expiry in 7 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY31" t="inlineStr">
+      <c r="CZ31" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 7 days Expiry in 7 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ31" t="inlineStr">
+      <c r="DA31" t="inlineStr">
         <is>
           <t>Creative Playmaker</t>
         </is>
       </c>
-      <c r="DA31" t="inlineStr">
+      <c r="DB31" t="inlineStr">
         <is>
           <t>Creative Playmaker Unlocked by completing the Win 5 task in the TOTS: Champions Objective objective Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 88.9 Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 90.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 7 days in 7 days 33% 67%</t>
         </is>
@@ -6665,27 +6700,28 @@
       <c r="CT32" t="inlineStr"/>
       <c r="CU32" t="inlineStr"/>
       <c r="CV32" t="inlineStr"/>
-      <c r="CW32" t="inlineStr">
+      <c r="CW32" t="inlineStr"/>
+      <c r="CX32" t="inlineStr">
         <is>
           <t>2 8 Level 1 Matsukubo 89 CAM PAC 88 SHO 90 PAS 89 DRI 91 DEF 70 PHY 78 CM ST R 3 ★ 4 Matsukubo 89 CAM PAC 88 SHO 90 PAS 89 DRI 91 DEF 70 PHY 78 CM ST R 3 ★ 4 UPGRADES 2 8</t>
         </is>
       </c>
-      <c r="CX32" t="inlineStr">
+      <c r="CY32" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY32" t="inlineStr">
+      <c r="CZ32" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ32" t="inlineStr">
+      <c r="DA32" t="inlineStr">
         <is>
           <t>Long Ball Pass+ &amp; Pinged Pass</t>
         </is>
       </c>
-      <c r="DA32" t="inlineStr">
+      <c r="DB32" t="inlineStr">
         <is>
           <t>Long Ball Pass+ &amp; Pinged Pass Unlocked by completing the Assist in 10 task in the Bundesliga TOTS Exhibition objective Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 2 8 in 1 day in 1 day 10% 90%</t>
         </is>
@@ -6824,27 +6860,28 @@
       <c r="CT33" t="inlineStr"/>
       <c r="CU33" t="inlineStr"/>
       <c r="CV33" t="inlineStr"/>
-      <c r="CW33" t="inlineStr">
+      <c r="CW33" t="inlineStr"/>
+      <c r="CX33" t="inlineStr">
         <is>
           <t>2 Level 1 De Ketelaere 89 CAM PAC 88 SHO 89 PAS 89 DRI 90 DEF 64 PHY 78 CM ST L 5 ★ 5 De Ketelaere 89 CAM PAC 88 SHO 89 PAS 89 DRI 90 DEF 64 PHY 78 CM ST L 5 ★ 5 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX33" t="inlineStr">
+      <c r="CY33" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY33" t="inlineStr">
+      <c r="CZ33" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ33" t="inlineStr">
+      <c r="DA33" t="inlineStr">
         <is>
           <t>Finesse Shot+</t>
         </is>
       </c>
-      <c r="DA33" t="inlineStr">
+      <c r="DB33" t="inlineStr">
         <is>
           <t>Finesse Shot+ Unlocked by completing the Score in 10 task in the Bundesliga TOTS Exhibition objective Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 88.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 1 day in 1 day 69% 31%</t>
         </is>
@@ -6913,10 +6950,10 @@
       <c r="X34" t="n">
         <v>30</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="n">
         <v>89</v>
       </c>
-      <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
@@ -6928,143 +6965,143 @@
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="n">
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="n">
         <v>50</v>
       </c>
-      <c r="AM34" t="n">
+      <c r="AN34" t="n">
         <v>90</v>
       </c>
-      <c r="AN34" t="n">
+      <c r="AO34" t="n">
         <v>25</v>
       </c>
-      <c r="AO34" t="n">
+      <c r="AP34" t="n">
         <v>93</v>
       </c>
-      <c r="AP34" t="n">
+      <c r="AQ34" t="n">
         <v>20</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AR34" t="n">
         <v>89</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="AS34" t="n">
         <v>20</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="AT34" t="n">
         <v>90</v>
       </c>
-      <c r="AT34" t="n">
+      <c r="AU34" t="n">
         <v>40</v>
       </c>
-      <c r="AU34" t="n">
+      <c r="AV34" t="n">
         <v>90</v>
       </c>
-      <c r="AV34" t="n">
+      <c r="AW34" t="n">
         <v>20</v>
       </c>
-      <c r="AW34" t="n">
+      <c r="AX34" t="n">
         <v>90</v>
       </c>
-      <c r="AX34" t="n">
+      <c r="AY34" t="n">
         <v>20</v>
       </c>
-      <c r="AY34" t="n">
+      <c r="AZ34" t="n">
         <v>93</v>
       </c>
-      <c r="AZ34" t="n">
+      <c r="BA34" t="n">
         <v>20</v>
       </c>
-      <c r="BA34" t="n">
+      <c r="BB34" t="n">
         <v>87</v>
       </c>
-      <c r="BB34" t="n">
+      <c r="BC34" t="n">
         <v>20</v>
       </c>
-      <c r="BC34" t="n">
+      <c r="BD34" t="n">
         <v>87</v>
       </c>
-      <c r="BD34" t="n">
+      <c r="BE34" t="n">
         <v>10</v>
       </c>
-      <c r="BE34" t="n">
+      <c r="BF34" t="n">
         <v>86</v>
       </c>
-      <c r="BF34" t="inlineStr"/>
       <c r="BG34" t="inlineStr"/>
-      <c r="BH34" t="n">
+      <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="n">
         <v>15</v>
       </c>
-      <c r="BI34" t="n">
+      <c r="BJ34" t="n">
         <v>88</v>
       </c>
-      <c r="BJ34" t="n">
+      <c r="BK34" t="n">
         <v>10</v>
       </c>
-      <c r="BK34" t="n">
+      <c r="BL34" t="n">
         <v>87</v>
       </c>
-      <c r="BL34" t="n">
+      <c r="BM34" t="n">
         <v>15</v>
       </c>
-      <c r="BM34" t="n">
+      <c r="BN34" t="n">
         <v>89</v>
       </c>
-      <c r="BN34" t="n">
+      <c r="BO34" t="n">
         <v>25</v>
       </c>
-      <c r="BO34" t="n">
+      <c r="BP34" t="n">
         <v>88</v>
       </c>
-      <c r="BP34" t="n">
+      <c r="BQ34" t="n">
         <v>25</v>
       </c>
-      <c r="BQ34" t="n">
+      <c r="BR34" t="n">
         <v>87</v>
       </c>
-      <c r="BR34" t="n">
+      <c r="BS34" t="n">
         <v>25</v>
       </c>
-      <c r="BS34" t="n">
+      <c r="BT34" t="n">
         <v>90</v>
       </c>
-      <c r="BT34" t="n">
+      <c r="BU34" t="n">
         <v>25</v>
       </c>
-      <c r="BU34" t="n">
+      <c r="BV34" t="n">
         <v>89</v>
       </c>
-      <c r="BV34" t="n">
+      <c r="BW34" t="n">
         <v>25</v>
       </c>
-      <c r="BW34" t="n">
+      <c r="BX34" t="n">
         <v>90</v>
       </c>
-      <c r="BX34" t="n">
+      <c r="BY34" t="n">
         <v>50</v>
       </c>
-      <c r="BY34" t="n">
+      <c r="BZ34" t="n">
         <v>88</v>
       </c>
-      <c r="BZ34" t="inlineStr"/>
       <c r="CA34" t="inlineStr"/>
-      <c r="CB34" t="n">
+      <c r="CB34" t="inlineStr"/>
+      <c r="CC34" t="n">
         <v>20</v>
       </c>
-      <c r="CC34" t="n">
+      <c r="CD34" t="n">
         <v>87</v>
       </c>
-      <c r="CD34" t="inlineStr"/>
       <c r="CE34" t="inlineStr"/>
       <c r="CF34" t="inlineStr"/>
       <c r="CG34" t="inlineStr"/>
       <c r="CH34" t="inlineStr"/>
       <c r="CI34" t="inlineStr"/>
-      <c r="CJ34" t="n">
+      <c r="CJ34" t="inlineStr"/>
+      <c r="CK34" t="n">
         <v>30</v>
       </c>
-      <c r="CK34" t="n">
+      <c r="CL34" t="n">
         <v>92</v>
       </c>
-      <c r="CL34" t="inlineStr"/>
       <c r="CM34" t="inlineStr"/>
       <c r="CN34" t="inlineStr"/>
       <c r="CO34" t="inlineStr"/>
@@ -7075,27 +7112,28 @@
       <c r="CT34" t="inlineStr"/>
       <c r="CU34" t="inlineStr"/>
       <c r="CV34" t="inlineStr"/>
-      <c r="CW34" t="inlineStr">
+      <c r="CW34" t="inlineStr"/>
+      <c r="CX34" t="inlineStr">
         <is>
           <t>+15 OVR 89 +25 Acceleration 90 +20 Shot Power 90 +10 Vision 87 +25 Composure 88 +25 Sprint Speed 93 +20 Long Shots 90 +10 Long Pass 87 +25 Dribbling 90 +20 Positioning 89 +20 Volleys 93 +15 Short Pass 88 +25 Ball Control 89 +30 Jumping 92 +20 Finishing 90 +10 Crossing 86 +15 Curve 89 +25 Reactions 90 +20 Heading Acc. 87 +20 Penalties 87 +15 Fk Accuracy 88 +25 Agility 88 +25 Balance 87 2 8 Level 1 Undav 87 ST PAC 86 SHO 89 PAS 81 DRI 87 DEF 40 PHY 84 CAM R 3 ★ 5 Undav 89 ST PAC 88 SHO 89 PAS 81 DRI 87 DEF 40 PHY 84 CAM R 3 ★ 5 UPGRADES +15 OVR 89 +25 Acceleration 90 +20 Shot Power 90 +10 Vision 87 +25 Composure 88 8</t>
         </is>
       </c>
-      <c r="CX34" t="inlineStr">
+      <c r="CY34" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 87 Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY34" t="inlineStr">
+      <c r="CZ34" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 87 Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ34" t="inlineStr">
+      <c r="DA34" t="inlineStr">
         <is>
           <t>Welsh Wonder Strike [Store]</t>
         </is>
       </c>
-      <c r="DA34" t="inlineStr">
+      <c r="DB34" t="inlineStr">
         <is>
           <t>Welsh Wonder Strike [Store] Unlocked by purchasing the Captains' Armband EVO pack. Lukaku 85 CAM PAC 84 SHO 86 PAS 80 DRI 81 DEF 42 PHY 85 ST L 4 ★ 4 ST 80.4 Lukaku 89 CAM PAC 92 SHO 90 PAS 86 DRI 89 DEF 42 PHY 85 ST L 4 ★ 4 ST 90.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 87 Max PS 10 Max PS+ 2 UPGRADES +15 OVR 89 +25 Acceleration 90 +20 Shot Power 90 +10 Vision 87 +25 Composure 88 +25 Sprint Speed 93 +20 Long Shots 90 +10 Long Pass 87 +25 Dribbling 90 +20 Positioning 89 +20 Volleys 93 +15 Short Pass 88 +25 Ball Control 89 +30 Jumping 92 +20 Finishing 90 +10 Crossing 86 +15 Curve 89 +25 Reactions 90 +20 Heading Acc. 87 +20 Penalties 87 +15 Fk Accuracy 88 +25 Agility 88 +25 Balance 87 2 8 TRAINING TIME 31 minutes in 2 days in 2 days 18% 82%</t>
         </is>
@@ -7176,10 +7214,10 @@
       <c r="X35" t="n">
         <v>60</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="n">
         <v>91</v>
       </c>
-      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -7191,19 +7229,19 @@
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="n">
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="n">
         <v>60</v>
       </c>
-      <c r="AM35" t="n">
+      <c r="AN35" t="n">
         <v>87</v>
       </c>
-      <c r="AN35" t="n">
+      <c r="AO35" t="n">
         <v>30</v>
       </c>
-      <c r="AO35" t="n">
+      <c r="AP35" t="n">
         <v>88</v>
       </c>
-      <c r="AP35" t="inlineStr"/>
       <c r="AQ35" t="inlineStr"/>
       <c r="AR35" t="inlineStr"/>
       <c r="AS35" t="inlineStr"/>
@@ -7215,150 +7253,151 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="inlineStr"/>
-      <c r="BB35" t="n">
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="n">
         <v>30</v>
       </c>
-      <c r="BC35" t="n">
+      <c r="BD35" t="n">
         <v>70</v>
       </c>
-      <c r="BD35" t="inlineStr"/>
       <c r="BE35" t="inlineStr"/>
       <c r="BF35" t="inlineStr"/>
       <c r="BG35" t="inlineStr"/>
-      <c r="BH35" t="n">
+      <c r="BH35" t="inlineStr"/>
+      <c r="BI35" t="n">
         <v>60</v>
       </c>
-      <c r="BI35" t="n">
+      <c r="BJ35" t="n">
         <v>90</v>
       </c>
-      <c r="BJ35" t="n">
+      <c r="BK35" t="n">
         <v>30</v>
       </c>
-      <c r="BK35" t="n">
+      <c r="BL35" t="n">
         <v>85</v>
       </c>
-      <c r="BL35" t="inlineStr"/>
       <c r="BM35" t="inlineStr"/>
-      <c r="BN35" t="n">
+      <c r="BN35" t="inlineStr"/>
+      <c r="BO35" t="n">
         <v>30</v>
       </c>
-      <c r="BO35" t="n">
+      <c r="BP35" t="n">
         <v>73</v>
       </c>
-      <c r="BP35" t="n">
+      <c r="BQ35" t="n">
         <v>30</v>
       </c>
-      <c r="BQ35" t="n">
+      <c r="BR35" t="n">
         <v>80</v>
       </c>
-      <c r="BR35" t="n">
+      <c r="BS35" t="n">
         <v>30</v>
       </c>
-      <c r="BS35" t="n">
+      <c r="BT35" t="n">
         <v>95</v>
       </c>
-      <c r="BT35" t="n">
+      <c r="BU35" t="n">
         <v>30</v>
       </c>
-      <c r="BU35" t="n">
+      <c r="BV35" t="n">
         <v>75</v>
       </c>
-      <c r="BV35" t="n">
+      <c r="BW35" t="n">
         <v>30</v>
       </c>
-      <c r="BW35" t="n">
+      <c r="BX35" t="n">
         <v>75</v>
       </c>
-      <c r="BX35" t="n">
+      <c r="BY35" t="n">
         <v>30</v>
       </c>
-      <c r="BY35" t="n">
+      <c r="BZ35" t="n">
         <v>91</v>
       </c>
-      <c r="BZ35" t="n">
+      <c r="CA35" t="n">
         <v>30</v>
       </c>
-      <c r="CA35" t="n">
+      <c r="CB35" t="n">
         <v>93</v>
       </c>
-      <c r="CB35" t="n">
+      <c r="CC35" t="n">
         <v>60</v>
       </c>
-      <c r="CC35" t="n">
+      <c r="CD35" t="n">
         <v>92</v>
       </c>
-      <c r="CD35" t="n">
+      <c r="CE35" t="n">
         <v>60</v>
       </c>
-      <c r="CE35" t="n">
+      <c r="CF35" t="n">
         <v>95</v>
       </c>
-      <c r="CF35" t="n">
+      <c r="CG35" t="n">
         <v>30</v>
       </c>
-      <c r="CG35" t="n">
+      <c r="CH35" t="n">
         <v>92</v>
       </c>
-      <c r="CH35" t="n">
+      <c r="CI35" t="n">
         <v>30</v>
       </c>
-      <c r="CI35" t="n">
+      <c r="CJ35" t="n">
         <v>92</v>
       </c>
-      <c r="CJ35" t="n">
+      <c r="CK35" t="n">
         <v>30</v>
       </c>
-      <c r="CK35" t="n">
+      <c r="CL35" t="n">
         <v>90</v>
       </c>
-      <c r="CL35" t="n">
+      <c r="CM35" t="n">
         <v>30</v>
       </c>
-      <c r="CM35" t="n">
+      <c r="CN35" t="n">
         <v>90</v>
       </c>
-      <c r="CN35" t="n">
+      <c r="CO35" t="n">
         <v>30</v>
       </c>
-      <c r="CO35" t="n">
+      <c r="CP35" t="n">
         <v>92</v>
       </c>
-      <c r="CP35" t="n">
+      <c r="CQ35" t="n">
         <v>30</v>
       </c>
-      <c r="CQ35" t="n">
+      <c r="CR35" t="n">
         <v>85</v>
       </c>
-      <c r="CR35" t="inlineStr"/>
       <c r="CS35" t="inlineStr"/>
       <c r="CT35" t="inlineStr"/>
       <c r="CU35" t="inlineStr"/>
-      <c r="CV35" t="inlineStr">
+      <c r="CV35" t="inlineStr"/>
+      <c r="CW35" t="inlineStr">
         <is>
           <t>CB Defender ++; CB Stopper ++; CB Wideback ++</t>
         </is>
       </c>
-      <c r="CW35" t="inlineStr">
+      <c r="CX35" t="inlineStr">
         <is>
           <t>+30 OVR 91 +30 Acceleration 87 +30 Short Pass 90 +30 Heading Acc. 92 +30 Defensive Awareness 95 +30 Sprint Speed 88 +30 Vision 70 +30 Agility 73 +30 Balance 80 +30 Long Pass 85 +30 Ball Control 75 +30 Dribbling 75 +30 Reactions 95 +30 Composure 91 +30 Interceptions 93 +30 Standing Tackle 92 +30 Sliding Tackle 92 +30 Stamina 90 +30 Strength 92 +30 Jumping 90 +30 Aggression 85 CB Defender ++ CB Stopper ++ CB Wideback ++ 2 8 Level 1 Gonçalo Inácio 89 CB PAC 83 SHO 43 PAS 80 DRI 81 DEF 89 PHY 89 L 3 ★ 4 Gonçalo Inácio 91 CB PAC 84 SHO 43 PAS 80 DRI 81 DEF 91 PHY 89 L 3 ★ 4 UPGRADES +30 OVR 91 +30 Acceleration 87 +30 Short Pass 90 +30 Heading Acc. 92 +30 Defensive Awareness 95 2</t>
         </is>
       </c>
-      <c r="CX35" t="inlineStr">
+      <c r="CY35" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Position CB Excluded Position CM Max PS 10 Max PS+ 2 Pace Max. 90 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY35" t="inlineStr">
+      <c r="CZ35" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Position CB Excluded Position CM Max PS 10 Max PS+ 2 Pace Max. 90 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ35" t="inlineStr">
+      <c r="DA35" t="inlineStr">
         <is>
           <t>Il Capitano [Store]</t>
         </is>
       </c>
-      <c r="DA35" t="inlineStr">
+      <c r="DB35" t="inlineStr">
         <is>
           <t>Il Capitano [Store] Unlocked by purchasing the Captains' Armband EVO pack. Lawrence 70 CB PAC 60 SHO 26 PAS 49 DRI 46 DEF 70 PHY 73 R 2 ★ 2 CB 62.3 Lawrence 91 CB PAC 88 SHO 26 PAS 68 DRI 72 DEF 93 PHY 90 R 2 ★ 2 CB 92.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Position CB Excluded Position CM Max PS 10 Max PS+ 2 Pace Max. 90 UPGRADES +30 OVR 91 +30 Acceleration 87 +30 Short Pass 90 +30 Heading Acc. 92 +30 Defensive Awareness 95 +30 Sprint Speed 88 +30 Vision 70 +30 Agility 73 +30 Balance 80 +30 Long Pass 85 +30 Ball Control 75 +30 Dribbling 75 +30 Reactions 95 +30 Composure 91 +30 Interceptions 93 +30 Standing Tackle 92 +30 Sliding Tackle 92 +30 Stamina 90 +30 Strength 92 +30 Jumping 90 +30 Aggression 85 CB Defender ++ CB Stopper ++ CB Wideback ++ 2 8 in 2 days in 2 days 19% 81%</t>
         </is>
@@ -7497,27 +7536,28 @@
       <c r="CT36" t="inlineStr"/>
       <c r="CU36" t="inlineStr"/>
       <c r="CV36" t="inlineStr"/>
-      <c r="CW36" t="inlineStr">
+      <c r="CW36" t="inlineStr"/>
+      <c r="CX36" t="inlineStr">
         <is>
           <t>2 Level 1 Hancko 89 CB PAC 87 SHO 72 PAS 81 DRI 85 DEF 90 PHY 89 LB LM L 5 ★ 5 Hancko 89 CB PAC 87 SHO 72 PAS 81 DRI 85 DEF 90 PHY 89 LB LM L 5 ★ 5 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX36" t="inlineStr">
+      <c r="CY36" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY36" t="inlineStr">
+      <c r="CZ36" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ36" t="inlineStr">
+      <c r="DA36" t="inlineStr">
         <is>
           <t>Intercept+ &amp; Quick Step+</t>
         </is>
       </c>
-      <c r="DA36" t="inlineStr">
+      <c r="DB36" t="inlineStr">
         <is>
           <t>Intercept+ &amp; Quick Step+ Unlocked by completing the Score in 30 task in the S7 Spirit of Africa League objective António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 86.6 António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 90.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 28 days in 28 days 75% 25%</t>
         </is>
@@ -7578,10 +7618,10 @@
       <c r="X37" t="n">
         <v>10</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="n">
         <v>74</v>
       </c>
-      <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
@@ -7623,86 +7663,87 @@
       <c r="BM37" t="inlineStr"/>
       <c r="BN37" t="inlineStr"/>
       <c r="BO37" t="inlineStr"/>
-      <c r="BP37" t="n">
+      <c r="BP37" t="inlineStr"/>
+      <c r="BQ37" t="n">
         <v>2</v>
       </c>
-      <c r="BQ37" t="inlineStr"/>
-      <c r="BR37" t="n">
+      <c r="BR37" t="inlineStr"/>
+      <c r="BS37" t="n">
         <v>2</v>
       </c>
-      <c r="BS37" t="inlineStr"/>
       <c r="BT37" t="inlineStr"/>
       <c r="BU37" t="inlineStr"/>
       <c r="BV37" t="inlineStr"/>
       <c r="BW37" t="inlineStr"/>
-      <c r="BX37" t="n">
+      <c r="BX37" t="inlineStr"/>
+      <c r="BY37" t="n">
         <v>6</v>
       </c>
-      <c r="BY37" t="inlineStr"/>
-      <c r="BZ37" t="n">
+      <c r="BZ37" t="inlineStr"/>
+      <c r="CA37" t="n">
         <v>4</v>
       </c>
-      <c r="CA37" t="inlineStr"/>
-      <c r="CB37" t="n">
+      <c r="CB37" t="inlineStr"/>
+      <c r="CC37" t="n">
         <v>2</v>
       </c>
-      <c r="CC37" t="inlineStr"/>
-      <c r="CD37" t="n">
+      <c r="CD37" t="inlineStr"/>
+      <c r="CE37" t="n">
         <v>3</v>
       </c>
-      <c r="CE37" t="inlineStr"/>
-      <c r="CF37" t="n">
+      <c r="CF37" t="inlineStr"/>
+      <c r="CG37" t="n">
         <v>2</v>
       </c>
-      <c r="CG37" t="inlineStr"/>
-      <c r="CH37" t="n">
+      <c r="CH37" t="inlineStr"/>
+      <c r="CI37" t="n">
         <v>4</v>
       </c>
-      <c r="CI37" t="inlineStr"/>
-      <c r="CJ37" t="n">
+      <c r="CJ37" t="inlineStr"/>
+      <c r="CK37" t="n">
         <v>4</v>
       </c>
-      <c r="CK37" t="inlineStr"/>
-      <c r="CL37" t="n">
+      <c r="CL37" t="inlineStr"/>
+      <c r="CM37" t="n">
         <v>3</v>
       </c>
-      <c r="CM37" t="inlineStr"/>
-      <c r="CN37" t="n">
+      <c r="CN37" t="inlineStr"/>
+      <c r="CO37" t="n">
         <v>2</v>
       </c>
-      <c r="CO37" t="inlineStr"/>
-      <c r="CP37" t="n">
+      <c r="CP37" t="inlineStr"/>
+      <c r="CQ37" t="n">
         <v>2</v>
       </c>
-      <c r="CQ37" t="n">
+      <c r="CR37" t="n">
         <v>3</v>
       </c>
-      <c r="CR37" t="inlineStr"/>
       <c r="CS37" t="inlineStr"/>
       <c r="CT37" t="inlineStr"/>
       <c r="CU37" t="inlineStr"/>
       <c r="CV37" t="inlineStr"/>
-      <c r="CW37" t="inlineStr">
+      <c r="CW37" t="inlineStr"/>
+      <c r="CX37" t="inlineStr">
         <is>
           <t>+5 OVR 74 +3 Composure +2 Interceptions +2 Sliding Tackle +2 Jumping +2 Balance +2 Heading Acc. +2 Standing Tackle +3 Stamina +2 Reactions +3 Defensive Awareness +2 Strength +2 Aggression 3 Level 1 Fernando Torres 74 ST PAC 83 SHO 75 PAS 72 DRI 78 DEF 42 PHY 62 R 4 ★ 4 Fernando Torres 74 ST PAC 83 SHO 75 PAS 72 DRI 78 DEF 42 PHY 62 R 4 ★ 4 UPGRADES +5 OVR 74 +3 Composure +2 Interceptions +2 Sliding Tackle +2 Jumping</t>
         </is>
       </c>
-      <c r="CX37" t="inlineStr">
+      <c r="CY37" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY37" t="inlineStr">
+      <c r="CZ37" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ37" t="inlineStr">
+      <c r="DA37" t="inlineStr">
         <is>
           <t>WTSS Defender Boost</t>
         </is>
       </c>
-      <c r="DA37" t="inlineStr">
+      <c r="DB37" t="inlineStr">
         <is>
           <t>WTSS Defender Boost Unlocked by completing the S7 Spirit of Africa Tournament objective Moore 74 CB PAC 74 SHO 42 PAS 70 DRI 57 DEF 83 PHY 72 R 2 ★ 3 CB 68.4 Moore 74 CB PAC 74 SHO 42 PAS 70 DRI 57 DEF 85 PHY 74 R 2 ★ 3 CB 76.2 REQUIREMENTS Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 UPGRADES +5 OVR 74 +3 Composure +2 Interceptions +2 Sliding Tackle +2 Jumping +2 Balance +2 Heading Acc. +2 Standing Tackle +3 Stamina +2 Reactions +3 Defensive Awareness +2 Strength +2 Aggression 3 in 28 days in 28 days 74% 26%</t>
         </is>
@@ -7763,10 +7804,10 @@
       <c r="X38" t="n">
         <v>10</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="n">
         <v>74</v>
       </c>
-      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
@@ -7778,38 +7819,38 @@
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="n">
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="n">
         <v>2</v>
       </c>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="n">
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="n">
         <v>2</v>
       </c>
-      <c r="AO38" t="inlineStr"/>
-      <c r="AP38" t="n">
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="n">
         <v>4</v>
       </c>
-      <c r="AQ38" t="inlineStr"/>
-      <c r="AR38" t="n">
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="n">
         <v>3</v>
       </c>
-      <c r="AS38" t="inlineStr"/>
-      <c r="AT38" t="n">
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="n">
         <v>2</v>
       </c>
-      <c r="AU38" t="inlineStr"/>
-      <c r="AV38" t="n">
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="n">
         <v>2</v>
       </c>
-      <c r="AW38" t="inlineStr"/>
-      <c r="AX38" t="n">
+      <c r="AX38" t="inlineStr"/>
+      <c r="AY38" t="n">
         <v>4</v>
       </c>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="n">
+      <c r="AZ38" t="inlineStr"/>
+      <c r="BA38" t="n">
         <v>4</v>
       </c>
-      <c r="BA38" t="inlineStr"/>
       <c r="BB38" t="inlineStr"/>
       <c r="BC38" t="inlineStr"/>
       <c r="BD38" t="inlineStr"/>
@@ -7824,20 +7865,20 @@
       <c r="BM38" t="inlineStr"/>
       <c r="BN38" t="inlineStr"/>
       <c r="BO38" t="inlineStr"/>
-      <c r="BP38" t="n">
+      <c r="BP38" t="inlineStr"/>
+      <c r="BQ38" t="n">
         <v>4</v>
       </c>
-      <c r="BQ38" t="inlineStr"/>
       <c r="BR38" t="inlineStr"/>
       <c r="BS38" t="inlineStr"/>
       <c r="BT38" t="inlineStr"/>
       <c r="BU38" t="inlineStr"/>
       <c r="BV38" t="inlineStr"/>
       <c r="BW38" t="inlineStr"/>
-      <c r="BX38" t="n">
+      <c r="BX38" t="inlineStr"/>
+      <c r="BY38" t="n">
         <v>3</v>
       </c>
-      <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="inlineStr"/>
       <c r="CA38" t="inlineStr"/>
       <c r="CB38" t="inlineStr"/>
@@ -7850,13 +7891,13 @@
       <c r="CI38" t="inlineStr"/>
       <c r="CJ38" t="inlineStr"/>
       <c r="CK38" t="inlineStr"/>
-      <c r="CL38" t="n">
-        <v>3</v>
-      </c>
+      <c r="CL38" t="inlineStr"/>
       <c r="CM38" t="n">
         <v>3</v>
       </c>
-      <c r="CN38" t="inlineStr"/>
+      <c r="CN38" t="n">
+        <v>3</v>
+      </c>
       <c r="CO38" t="inlineStr"/>
       <c r="CP38" t="inlineStr"/>
       <c r="CQ38" t="inlineStr"/>
@@ -7865,27 +7906,28 @@
       <c r="CT38" t="inlineStr"/>
       <c r="CU38" t="inlineStr"/>
       <c r="CV38" t="inlineStr"/>
-      <c r="CW38" t="inlineStr">
+      <c r="CW38" t="inlineStr"/>
+      <c r="CX38" t="inlineStr">
         <is>
           <t>+5 OVR 74 +2 Positioning +2 Volleys +2 Penalties +2 Balance +2 Acceleration +3 Finishing +2 Long Shots +3 Composure +2 Sprint Speed +2 Shot Power +3 Stamina 3 Level 1 Matthäus 74 CM PAC 72 SHO 76 PAS 85 DRI 71 DEF 77 PHY 72 CB CDM R 3 ★ 4 Matthäus 74 CM PAC 72 SHO 76 PAS 85 DRI 71 DEF 77 PHY 72 CB CDM R 3 ★ 4 UPGRADES +5 OVR 74 +2 Positioning +2 Volleys +2 Penalties +2 Balance</t>
         </is>
       </c>
-      <c r="CX38" t="inlineStr">
+      <c r="CY38" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY38" t="inlineStr">
+      <c r="CZ38" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ38" t="inlineStr">
+      <c r="DA38" t="inlineStr">
         <is>
           <t>WTSS Attacker Boost</t>
         </is>
       </c>
-      <c r="DA38" t="inlineStr">
+      <c r="DB38" t="inlineStr">
         <is>
           <t>WTSS Attacker Boost Unlocked by completing the S7 Spirit of Africa League objective Šuker 73 ST PAC 71 SHO 83 PAS 70 DRI 83 DEF 30 PHY 65 L 4 ★ 4 ST 72.7 Šuker 74 ST PAC 73 SHO 86 PAS 70 DRI 83 DEF 30 PHY 65 L 4 ★ 4 ST 79.2 REQUIREMENTS Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 UPGRADES +5 OVR 74 +2 Positioning +2 Volleys +2 Penalties +2 Balance +2 Acceleration +3 Finishing +2 Long Shots +3 Composure +2 Sprint Speed +2 Shot Power +3 Stamina 3 in 28 days in 28 days 78% 22%</t>
         </is>
@@ -7958,74 +8000,74 @@
       <c r="X39" t="n">
         <v>4</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="n">
         <v>92</v>
       </c>
-      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="n">
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="n">
         <v>4</v>
       </c>
-      <c r="AE39" t="n">
+      <c r="AF39" t="n">
         <v>93</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="n">
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="n">
         <v>5</v>
       </c>
-      <c r="AM39" t="n">
+      <c r="AN39" t="n">
         <v>90</v>
       </c>
-      <c r="AN39" t="n">
+      <c r="AO39" t="n">
         <v>5</v>
       </c>
-      <c r="AO39" t="n">
+      <c r="AP39" t="n">
         <v>90</v>
       </c>
-      <c r="AP39" t="n">
+      <c r="AQ39" t="n">
         <v>5</v>
       </c>
-      <c r="AQ39" t="n">
+      <c r="AR39" t="n">
         <v>90</v>
       </c>
-      <c r="AR39" t="n">
+      <c r="AS39" t="n">
         <v>10</v>
       </c>
-      <c r="AS39" t="n">
+      <c r="AT39" t="n">
         <v>90</v>
       </c>
-      <c r="AT39" t="n">
+      <c r="AU39" t="n">
         <v>5</v>
       </c>
-      <c r="AU39" t="n">
+      <c r="AV39" t="n">
         <v>91</v>
       </c>
-      <c r="AV39" t="n">
+      <c r="AW39" t="n">
         <v>5</v>
       </c>
-      <c r="AW39" t="n">
+      <c r="AX39" t="n">
         <v>91</v>
       </c>
-      <c r="AX39" t="n">
+      <c r="AY39" t="n">
         <v>5</v>
       </c>
-      <c r="AY39" t="n">
+      <c r="AZ39" t="n">
         <v>88</v>
       </c>
-      <c r="AZ39" t="n">
+      <c r="BA39" t="n">
         <v>5</v>
       </c>
-      <c r="BA39" t="n">
+      <c r="BB39" t="n">
         <v>88</v>
       </c>
-      <c r="BB39" t="inlineStr"/>
       <c r="BC39" t="inlineStr"/>
       <c r="BD39" t="inlineStr"/>
       <c r="BE39" t="inlineStr"/>
@@ -8037,43 +8079,43 @@
       <c r="BK39" t="inlineStr"/>
       <c r="BL39" t="inlineStr"/>
       <c r="BM39" t="inlineStr"/>
-      <c r="BN39" t="n">
+      <c r="BN39" t="inlineStr"/>
+      <c r="BO39" t="n">
         <v>10</v>
       </c>
-      <c r="BO39" t="n">
+      <c r="BP39" t="n">
         <v>92</v>
       </c>
-      <c r="BP39" t="n">
+      <c r="BQ39" t="n">
         <v>10</v>
       </c>
-      <c r="BQ39" t="n">
+      <c r="BR39" t="n">
         <v>92</v>
       </c>
-      <c r="BR39" t="n">
+      <c r="BS39" t="n">
         <v>20</v>
       </c>
-      <c r="BS39" t="n">
+      <c r="BT39" t="n">
         <v>91</v>
       </c>
-      <c r="BT39" t="n">
+      <c r="BU39" t="n">
         <v>10</v>
       </c>
-      <c r="BU39" t="n">
+      <c r="BV39" t="n">
         <v>92</v>
       </c>
-      <c r="BV39" t="n">
+      <c r="BW39" t="n">
         <v>10</v>
       </c>
-      <c r="BW39" t="n">
+      <c r="BX39" t="n">
         <v>93</v>
       </c>
-      <c r="BX39" t="n">
+      <c r="BY39" t="n">
         <v>10</v>
       </c>
-      <c r="BY39" t="n">
+      <c r="BZ39" t="n">
         <v>90</v>
       </c>
-      <c r="BZ39" t="inlineStr"/>
       <c r="CA39" t="inlineStr"/>
       <c r="CB39" t="inlineStr"/>
       <c r="CC39" t="inlineStr"/>
@@ -8093,34 +8135,35 @@
       <c r="CQ39" t="inlineStr"/>
       <c r="CR39" t="inlineStr"/>
       <c r="CS39" t="inlineStr"/>
-      <c r="CT39" t="n">
+      <c r="CT39" t="inlineStr"/>
+      <c r="CU39" t="n">
         <v>4</v>
       </c>
-      <c r="CU39" t="n">
+      <c r="CV39" t="n">
         <v>5</v>
       </c>
-      <c r="CV39" t="inlineStr"/>
-      <c r="CW39" t="inlineStr">
+      <c r="CW39" t="inlineStr"/>
+      <c r="CX39" t="inlineStr">
         <is>
           <t>+2 OVR 92 +2 PAS 93 +4 WF 5 +5 Finishing 90 +10 Reactions 91 +5 Acceleration 90 +5 Shot Power 91 +10 Balance 92 +10 Ball Control 92 +5 Sprint Speed 90 +5 Long Shots 91 +5 Penalties 88 +10 Dribbling 93 +5 Positioning 90 +5 Volleys 88 +10 Agility 92 +10 Composure 90 3 8 Level 1 Vieira 90 CM PAC 88 SHO 88 PAS 91 DRI 87 DEF 89 PHY 89 CDM R 4 ★ 4 CM 87.7 Vieira 92 CM PAC 88 SHO 89 PAS 93 DRI 87 DEF 89 PHY 89 CDM R 4 ★ 4 CM 87.7 UPGRADES +2 OVR 92 +2 PAS 93 +5 Finishing 90 +10 Reactions 91 3</t>
         </is>
       </c>
-      <c r="CX39" t="inlineStr">
+      <c r="CY39" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CAM, CM, CDM Max PS 10 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY39" t="inlineStr">
+      <c r="CZ39" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CAM, CM, CDM Max PS 10 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ39" t="inlineStr">
+      <c r="DA39" t="inlineStr">
         <is>
           <t>WTSS Journey 3 - Midfielder [SP 21]</t>
         </is>
       </c>
-      <c r="DA39" t="inlineStr">
+      <c r="DB39" t="inlineStr">
         <is>
           <t>WTSS Journey 3 - Midfielder [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CAM, CM, CDM Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +2 PAS 93 +4 WF 5 +5 Finishing 90 +10 Reactions 91 +5 Acceleration 90 +5 Shot Power 91 +10 Balance 92 +10 Ball Control 92 +5 Sprint Speed 90 +5 Long Shots 91 +5 Penalties 88 +10 Dribbling 93 +5 Positioning 90 +5 Volleys 88 +10 Agility 92 +10 Composure 90 3 8 Show less in 1 month in 1 month 84% 16%</t>
         </is>
@@ -8259,27 +8302,28 @@
       <c r="CT40" t="inlineStr"/>
       <c r="CU40" t="inlineStr"/>
       <c r="CV40" t="inlineStr"/>
-      <c r="CW40" t="inlineStr">
+      <c r="CW40" t="inlineStr"/>
+      <c r="CX40" t="inlineStr">
         <is>
           <t>3 Level 1 Lamine Yamal 91 RW PAC 87 SHO 83 PAS 88 DRI 92 DEF 25 PHY 55 RM L 5 ★ 3 Lamine Yamal 91 RW PAC 87 SHO 83 PAS 88 DRI 92 DEF 25 PHY 55 RM L 5 ★ 3 UPGRADES 3</t>
         </is>
       </c>
-      <c r="CX40" t="inlineStr">
+      <c r="CY40" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY40" t="inlineStr">
+      <c r="CZ40" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ40" t="inlineStr">
+      <c r="DA40" t="inlineStr">
         <is>
           <t>Bruiser+ [SP+ 28]</t>
         </is>
       </c>
-      <c r="DA40" t="inlineStr">
+      <c r="DB40" t="inlineStr">
         <is>
           <t>Bruiser+ [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 CB 90.5 van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 CB 93.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 2 UPGRADES 3 in 1 month in 1 month 91% 9%</t>
         </is>
@@ -8418,27 +8462,28 @@
       <c r="CT41" t="inlineStr"/>
       <c r="CU41" t="inlineStr"/>
       <c r="CV41" t="inlineStr"/>
-      <c r="CW41" t="inlineStr">
+      <c r="CW41" t="inlineStr"/>
+      <c r="CX41" t="inlineStr">
         <is>
           <t>3 Level 1 van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 UPGRADES 3</t>
         </is>
       </c>
-      <c r="CX41" t="inlineStr">
+      <c r="CY41" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY41" t="inlineStr">
+      <c r="CZ41" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ41" t="inlineStr">
+      <c r="DA41" t="inlineStr">
         <is>
           <t>Incisive Pass+ [SP 27]</t>
         </is>
       </c>
-      <c r="DA41" t="inlineStr">
+      <c r="DB41" t="inlineStr">
         <is>
           <t>Incisive Pass+ [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Calafiori 90 LB PAC 87 SHO 80 PAS 85 DRI 89 DEF 90 PHY 91 CB L 3 ★ 4 LB 89.9 Calafiori 90 LB PAC 87 SHO 80 PAS 85 DRI 89 DEF 90 PHY 91 CB L 3 ★ 4 LB 91.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 UPGRADES 3 in 1 month in 1 month 85% 15%</t>
         </is>
@@ -8516,19 +8561,19 @@
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="n">
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="n">
         <v>10</v>
       </c>
-      <c r="AM42" t="n">
+      <c r="AN42" t="n">
         <v>91</v>
       </c>
-      <c r="AN42" t="n">
+      <c r="AO42" t="n">
         <v>10</v>
       </c>
-      <c r="AO42" t="n">
+      <c r="AP42" t="n">
         <v>92</v>
       </c>
-      <c r="AP42" t="inlineStr"/>
       <c r="AQ42" t="inlineStr"/>
       <c r="AR42" t="inlineStr"/>
       <c r="AS42" t="inlineStr"/>
@@ -8556,102 +8601,103 @@
       <c r="BO42" t="inlineStr"/>
       <c r="BP42" t="inlineStr"/>
       <c r="BQ42" t="inlineStr"/>
-      <c r="BR42" t="n">
+      <c r="BR42" t="inlineStr"/>
+      <c r="BS42" t="n">
         <v>5</v>
       </c>
-      <c r="BS42" t="n">
+      <c r="BT42" t="n">
         <v>93</v>
       </c>
-      <c r="BT42" t="inlineStr"/>
       <c r="BU42" t="inlineStr"/>
       <c r="BV42" t="inlineStr"/>
       <c r="BW42" t="inlineStr"/>
-      <c r="BX42" t="n">
+      <c r="BX42" t="inlineStr"/>
+      <c r="BY42" t="n">
         <v>5</v>
       </c>
-      <c r="BY42" t="n">
+      <c r="BZ42" t="n">
         <v>93</v>
       </c>
-      <c r="BZ42" t="n">
+      <c r="CA42" t="n">
         <v>2</v>
       </c>
-      <c r="CA42" t="n">
+      <c r="CB42" t="n">
         <v>93</v>
       </c>
-      <c r="CB42" t="n">
+      <c r="CC42" t="n">
         <v>2</v>
       </c>
-      <c r="CC42" t="n">
+      <c r="CD42" t="n">
         <v>94</v>
       </c>
-      <c r="CD42" t="n">
+      <c r="CE42" t="n">
         <v>2</v>
       </c>
-      <c r="CE42" t="n">
+      <c r="CF42" t="n">
         <v>93</v>
       </c>
-      <c r="CF42" t="n">
+      <c r="CG42" t="n">
         <v>5</v>
       </c>
-      <c r="CG42" t="n">
+      <c r="CH42" t="n">
         <v>91</v>
       </c>
-      <c r="CH42" t="n">
+      <c r="CI42" t="n">
         <v>5</v>
       </c>
-      <c r="CI42" t="n">
+      <c r="CJ42" t="n">
         <v>92</v>
       </c>
-      <c r="CJ42" t="n">
+      <c r="CK42" t="n">
         <v>2</v>
       </c>
-      <c r="CK42" t="n">
+      <c r="CL42" t="n">
         <v>93</v>
       </c>
-      <c r="CL42" t="n">
+      <c r="CM42" t="n">
         <v>2</v>
       </c>
-      <c r="CM42" t="n">
+      <c r="CN42" t="n">
         <v>92</v>
       </c>
-      <c r="CN42" t="n">
+      <c r="CO42" t="n">
         <v>2</v>
       </c>
-      <c r="CO42" t="n">
+      <c r="CP42" t="n">
         <v>93</v>
       </c>
-      <c r="CP42" t="n">
+      <c r="CQ42" t="n">
         <v>5</v>
       </c>
-      <c r="CQ42" t="n">
+      <c r="CR42" t="n">
         <v>92</v>
       </c>
-      <c r="CR42" t="inlineStr"/>
       <c r="CS42" t="inlineStr"/>
       <c r="CT42" t="inlineStr"/>
       <c r="CU42" t="inlineStr"/>
       <c r="CV42" t="inlineStr"/>
-      <c r="CW42" t="inlineStr">
+      <c r="CW42" t="inlineStr"/>
+      <c r="CX42" t="inlineStr">
         <is>
           <t>+1 OVR +5 Acceleration 91 +5 Sprint Speed 92 +1 Interceptions 93 +1 Heading Acc. 94 +1 Defensive Awareness 93 +5 Reactions 93 +5 Composure 93 +5 Standing Tackle 91 +5 Sliding Tackle 92 +2 Jumping 93 +2 Stamina 92 +2 Strength 93 +5 Aggression 92 8 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 90 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 64 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES +1 OVR +5 Acceleration 91 +5 Sprint Speed 92 +1 Interceptions 93 +1 Heading Acc. 94 +1 Defensive Awareness 93</t>
         </is>
       </c>
-      <c r="CX42" t="inlineStr">
+      <c r="CY42" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY42" t="inlineStr">
+      <c r="CZ42" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ42" t="inlineStr">
+      <c r="DA42" t="inlineStr">
         <is>
           <t>Defender Round Out [SP 1] 10</t>
         </is>
       </c>
-      <c r="DA42" t="inlineStr">
+      <c r="DB42" t="inlineStr">
         <is>
           <t>Defender Round Out [SP 1] 10 Unlocked by reaching level 1 in the Standard Season Pass. Timber 88 RB PAC 87 SHO 54 PAS 83 DRI 86 DEF 88 PHY 88 CB LB RM R 4 ★ 5 LB 88.6 Timber 89 RB PAC 92 SHO 54 PAS 83 DRI 87 DEF 89 PHY 91 CB LB RM R 4 ★ 5 LB 92.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +1 OVR +5 Acceleration 91 +5 Sprint Speed 92 +1 Interceptions 93 +1 Heading Acc. 94 +1 Defensive Awareness 93 +5 Reactions 93 +5 Composure 93 +5 Standing Tackle 91 +5 Sliding Tackle 92 +2 Jumping 93 +2 Stamina 92 +2 Strength 93 +5 Aggression 92 8 in 1 month in 1 month 90% 10%</t>
         </is>
@@ -8724,10 +8770,10 @@
       <c r="X43" t="n">
         <v>4</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="n">
         <v>91</v>
       </c>
-      <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr"/>
@@ -8739,123 +8785,123 @@
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="n">
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="n">
         <v>6</v>
       </c>
-      <c r="AM43" t="n">
+      <c r="AN43" t="n">
         <v>93</v>
       </c>
-      <c r="AN43" t="n">
+      <c r="AO43" t="n">
         <v>3</v>
       </c>
-      <c r="AO43" t="n">
+      <c r="AP43" t="n">
         <v>94</v>
       </c>
-      <c r="AP43" t="n">
+      <c r="AQ43" t="n">
         <v>5</v>
       </c>
-      <c r="AQ43" t="n">
+      <c r="AR43" t="n">
         <v>93</v>
       </c>
-      <c r="AR43" t="n">
+      <c r="AS43" t="n">
         <v>5</v>
       </c>
-      <c r="AS43" t="n">
+      <c r="AT43" t="n">
         <v>94</v>
       </c>
-      <c r="AT43" t="n">
+      <c r="AU43" t="n">
         <v>3</v>
       </c>
-      <c r="AU43" t="n">
+      <c r="AV43" t="n">
         <v>93</v>
       </c>
-      <c r="AV43" t="n">
+      <c r="AW43" t="n">
         <v>3</v>
       </c>
-      <c r="AW43" t="n">
+      <c r="AX43" t="n">
         <v>92</v>
       </c>
-      <c r="AX43" t="n">
+      <c r="AY43" t="n">
         <v>3</v>
       </c>
-      <c r="AY43" t="n">
+      <c r="AZ43" t="n">
         <v>94</v>
       </c>
-      <c r="AZ43" t="n">
+      <c r="BA43" t="n">
         <v>3</v>
       </c>
-      <c r="BA43" t="n">
+      <c r="BB43" t="n">
         <v>94</v>
       </c>
-      <c r="BB43" t="n">
+      <c r="BC43" t="n">
         <v>5</v>
       </c>
-      <c r="BC43" t="n">
+      <c r="BD43" t="n">
         <v>93</v>
       </c>
-      <c r="BD43" t="n">
+      <c r="BE43" t="n">
         <v>2</v>
       </c>
-      <c r="BE43" t="n">
+      <c r="BF43" t="n">
         <v>94</v>
       </c>
-      <c r="BF43" t="inlineStr"/>
       <c r="BG43" t="inlineStr"/>
-      <c r="BH43" t="n">
+      <c r="BH43" t="inlineStr"/>
+      <c r="BI43" t="n">
         <v>5</v>
       </c>
-      <c r="BI43" t="n">
+      <c r="BJ43" t="n">
         <v>95</v>
       </c>
-      <c r="BJ43" t="n">
+      <c r="BK43" t="n">
         <v>5</v>
       </c>
-      <c r="BK43" t="n">
+      <c r="BL43" t="n">
         <v>94</v>
       </c>
-      <c r="BL43" t="n">
+      <c r="BM43" t="n">
         <v>2</v>
       </c>
-      <c r="BM43" t="n">
+      <c r="BN43" t="n">
         <v>92</v>
       </c>
-      <c r="BN43" t="n">
+      <c r="BO43" t="n">
         <v>10</v>
       </c>
-      <c r="BO43" t="n">
+      <c r="BP43" t="n">
         <v>94</v>
       </c>
-      <c r="BP43" t="n">
+      <c r="BQ43" t="n">
         <v>10</v>
       </c>
-      <c r="BQ43" t="n">
+      <c r="BR43" t="n">
         <v>93</v>
       </c>
-      <c r="BR43" t="n">
+      <c r="BS43" t="n">
         <v>2</v>
       </c>
-      <c r="BS43" t="n">
+      <c r="BT43" t="n">
         <v>92</v>
       </c>
-      <c r="BT43" t="n">
+      <c r="BU43" t="n">
         <v>5</v>
       </c>
-      <c r="BU43" t="n">
+      <c r="BV43" t="n">
         <v>94</v>
       </c>
-      <c r="BV43" t="n">
+      <c r="BW43" t="n">
         <v>5</v>
       </c>
-      <c r="BW43" t="n">
+      <c r="BX43" t="n">
         <v>95</v>
       </c>
-      <c r="BX43" t="n">
+      <c r="BY43" t="n">
         <v>2</v>
       </c>
-      <c r="BY43" t="n">
+      <c r="BZ43" t="n">
         <v>95</v>
       </c>
-      <c r="BZ43" t="inlineStr"/>
       <c r="CA43" t="inlineStr"/>
       <c r="CB43" t="inlineStr"/>
       <c r="CC43" t="inlineStr"/>
@@ -8878,27 +8924,28 @@
       <c r="CT43" t="inlineStr"/>
       <c r="CU43" t="inlineStr"/>
       <c r="CV43" t="inlineStr"/>
-      <c r="CW43" t="inlineStr">
+      <c r="CW43" t="inlineStr"/>
+      <c r="CX43" t="inlineStr">
         <is>
           <t>+2 OVR 91 +3 Acceleration 93 +5 Agility 94 +5 Balance 93 +3 Sprint Speed 94 +5 Long Pass 94 +2 Curve 92 +2 Composure 95 +5 Positioning 93 +5 Finishing 94 +3 Shot Power 93 +2 Reactions 92 +5 Ball Control 94 +3 Long Shots 92 +3 Volleys 94 +3 Penalties 94 +5 Short Pass 95 +5 Dribbling 95 +5 Vision 93 +2 Crossing 94 +2 Fk Accuracy 92 8 Level 1 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 Kerolin Nicoli 91 RM PAC 92 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 UPGRADES +2 OVR 91 +3 Acceleration 93 +5 Agility 94 +5 Balance 93 8</t>
         </is>
       </c>
-      <c r="CX43" t="inlineStr">
+      <c r="CY43" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Excluded Position CB Max PS 10 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY43" t="inlineStr">
+      <c r="CZ43" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Excluded Position CB Max PS 10 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ43" t="inlineStr">
+      <c r="DA43" t="inlineStr">
         <is>
           <t>Attacker Round Out [SP+ 1] 20</t>
         </is>
       </c>
-      <c r="DA43" t="inlineStr">
+      <c r="DB43" t="inlineStr">
         <is>
           <t>Attacker Round Out [SP+ 1] 20 Unlocked by reaching level 1 in the Premium Season Pass. Mead 89 LW PAC 89 SHO 88 PAS 87 DRI 90 DEF 70 PHY 77 RM RW ST R 5 ★ 4 RW 86.9 Mead 91 LW PAC 92 SHO 91 PAS 91 DRI 93 DEF 70 PHY 77 RM RW ST R 5 ★ 4 RW 91.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Excluded Position CB Max PS 10 UPGRADES +2 OVR 91 +3 Acceleration 93 +5 Agility 94 +5 Balance 93 +3 Sprint Speed 94 +5 Long Pass 94 +2 Curve 92 +2 Composure 95 +5 Positioning 93 +5 Finishing 94 +3 Shot Power 93 +2 Reactions 92 +5 Ball Control 94 +3 Long Shots 92 +3 Volleys 94 +3 Penalties 94 +5 Short Pass 95 +5 Dribbling 95 +5 Vision 93 +2 Crossing 94 +2 Fk Accuracy 92 8 in 1 month in 1 month 93% 7%</t>
         </is>
@@ -8971,10 +9018,10 @@
       <c r="X44" t="n">
         <v>4</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="n">
         <v>90</v>
       </c>
-      <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr"/>
@@ -8986,55 +9033,55 @@
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="n">
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="n">
         <v>20</v>
       </c>
-      <c r="AM44" t="n">
+      <c r="AN44" t="n">
         <v>90</v>
       </c>
-      <c r="AN44" t="n">
+      <c r="AO44" t="n">
         <v>20</v>
       </c>
-      <c r="AO44" t="n">
+      <c r="AP44" t="n">
         <v>90</v>
       </c>
-      <c r="AP44" t="n">
+      <c r="AQ44" t="n">
         <v>20</v>
       </c>
-      <c r="AQ44" t="n">
+      <c r="AR44" t="n">
         <v>90</v>
       </c>
-      <c r="AR44" t="n">
+      <c r="AS44" t="n">
         <v>20</v>
       </c>
-      <c r="AS44" t="n">
+      <c r="AT44" t="n">
         <v>90</v>
       </c>
-      <c r="AT44" t="n">
+      <c r="AU44" t="n">
         <v>10</v>
       </c>
-      <c r="AU44" t="n">
+      <c r="AV44" t="n">
         <v>91</v>
       </c>
-      <c r="AV44" t="n">
+      <c r="AW44" t="n">
         <v>10</v>
       </c>
-      <c r="AW44" t="n">
+      <c r="AX44" t="n">
         <v>90</v>
       </c>
-      <c r="AX44" t="n">
+      <c r="AY44" t="n">
         <v>10</v>
       </c>
-      <c r="AY44" t="n">
+      <c r="AZ44" t="n">
         <v>89</v>
       </c>
-      <c r="AZ44" t="n">
+      <c r="BA44" t="n">
         <v>10</v>
       </c>
-      <c r="BA44" t="n">
+      <c r="BB44" t="n">
         <v>90</v>
       </c>
-      <c r="BB44" t="inlineStr"/>
       <c r="BC44" t="inlineStr"/>
       <c r="BD44" t="inlineStr"/>
       <c r="BE44" t="inlineStr"/>
@@ -9044,49 +9091,49 @@
       <c r="BI44" t="inlineStr"/>
       <c r="BJ44" t="inlineStr"/>
       <c r="BK44" t="inlineStr"/>
-      <c r="BL44" t="n">
+      <c r="BL44" t="inlineStr"/>
+      <c r="BM44" t="n">
         <v>10</v>
       </c>
-      <c r="BM44" t="n">
+      <c r="BN44" t="n">
         <v>90</v>
       </c>
-      <c r="BN44" t="n">
+      <c r="BO44" t="n">
         <v>15</v>
       </c>
-      <c r="BO44" t="n">
+      <c r="BP44" t="n">
         <v>92</v>
       </c>
-      <c r="BP44" t="n">
+      <c r="BQ44" t="n">
         <v>15</v>
       </c>
-      <c r="BQ44" t="n">
+      <c r="BR44" t="n">
         <v>89</v>
       </c>
-      <c r="BR44" t="n">
+      <c r="BS44" t="n">
         <v>15</v>
       </c>
-      <c r="BS44" t="n">
+      <c r="BT44" t="n">
         <v>89</v>
       </c>
-      <c r="BT44" t="n">
+      <c r="BU44" t="n">
         <v>15</v>
       </c>
-      <c r="BU44" t="n">
+      <c r="BV44" t="n">
         <v>88</v>
       </c>
-      <c r="BV44" t="n">
+      <c r="BW44" t="n">
         <v>15</v>
       </c>
-      <c r="BW44" t="n">
+      <c r="BX44" t="n">
         <v>89</v>
       </c>
-      <c r="BX44" t="n">
+      <c r="BY44" t="n">
         <v>15</v>
       </c>
-      <c r="BY44" t="n">
+      <c r="BZ44" t="n">
         <v>88</v>
       </c>
-      <c r="BZ44" t="inlineStr"/>
       <c r="CA44" t="inlineStr"/>
       <c r="CB44" t="inlineStr"/>
       <c r="CC44" t="inlineStr"/>
@@ -9106,34 +9153,35 @@
       <c r="CQ44" t="inlineStr"/>
       <c r="CR44" t="inlineStr"/>
       <c r="CS44" t="inlineStr"/>
-      <c r="CT44" t="n">
+      <c r="CT44" t="inlineStr"/>
+      <c r="CU44" t="n">
         <v>3</v>
       </c>
-      <c r="CU44" t="n">
+      <c r="CV44" t="n">
         <v>4</v>
       </c>
-      <c r="CV44" t="inlineStr"/>
-      <c r="CW44" t="inlineStr">
+      <c r="CW44" t="inlineStr"/>
+      <c r="CX44" t="inlineStr">
         <is>
           <t>+2 OVR 90 +3 WF 4 +10 Acceleration 90 +10 Sprint Speed 90 +10 Finishing 90 +10 Positioning 90 +10 Volleys 89 +10 Penalties 90 +10 Curve 90 +15 Agility 92 +15 Balance 89 +15 Reactions 89 +10 Shot Power 91 +10 Long Shots 90 +15 Ball Control 88 +15 Dribbling 89 +15 Composure 88 2 8 Level 1 Park Ji Sung 88 RW PAC 88 SHO 87 PAS 89 DRI 88 DEF 85 PHY 84 RM CM CAM R 4 ★ 4 CM 85.3 Park Ji Sung 90 RW PAC 90 SHO 89 PAS 89 DRI 88 DEF 85 PHY 84 RM CM CAM R 4 ★ 4 CM 85.3 UPGRADES +2 OVR 90 +10 Acceleration 90 +10 Sprint Speed 90 +10 Finishing 90 +10 Positioning 90 8</t>
         </is>
       </c>
-      <c r="CX44" t="inlineStr">
+      <c r="CY44" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position ST, RW, LW Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY44" t="inlineStr">
+      <c r="CZ44" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position ST, RW, LW Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ44" t="inlineStr">
+      <c r="DA44" t="inlineStr">
         <is>
           <t>WTSS Journey 2 - Attacker [SP 8]</t>
         </is>
       </c>
-      <c r="DA44" t="inlineStr">
+      <c r="DB44" t="inlineStr">
         <is>
           <t>WTSS Journey 2 - Attacker [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Garrincha 70 RW PAC 82 SHO 64 PAS 67 DRI 78 DEF 34 PHY 48 RM R 5 ★ 4 RM 70.4 Garrincha 90 RW PAC 90 SHO 90 PAS 87 DRI 89 DEF 34 PHY 67 RM R 5 ★ 4 RM 88.6 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position ST, RW, LW Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +3 WF 4 +10 Acceleration 90 +10 Sprint Speed 90 +10 Finishing 90 +10 Positioning 90 +10 Volleys 89 +10 Penalties 90 +10 Curve 90 +15 Agility 92 +15 Balance 89 +15 Reactions 89 +10 Shot Power 91 +10 Long Shots 90 +15 Ball Control 88 +15 Dribbling 89 +15 Composure 88 2 8 in 1 month in 1 month 68% 32%</t>
         </is>
@@ -9206,16 +9254,16 @@
       <c r="X45" t="n">
         <v>4</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="n">
         <v>90</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AA45" t="n">
         <v>4</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AB45" t="n">
         <v>87</v>
       </c>
-      <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="inlineStr"/>
@@ -9253,65 +9301,65 @@
       <c r="BK45" t="inlineStr"/>
       <c r="BL45" t="inlineStr"/>
       <c r="BM45" t="inlineStr"/>
-      <c r="BN45" t="n">
+      <c r="BN45" t="inlineStr"/>
+      <c r="BO45" t="n">
         <v>10</v>
       </c>
-      <c r="BO45" t="n">
+      <c r="BP45" t="n">
         <v>88</v>
       </c>
-      <c r="BP45" t="n">
+      <c r="BQ45" t="n">
         <v>5</v>
       </c>
-      <c r="BQ45" t="n">
+      <c r="BR45" t="n">
         <v>88</v>
       </c>
-      <c r="BR45" t="n">
+      <c r="BS45" t="n">
         <v>5</v>
       </c>
-      <c r="BS45" t="n">
+      <c r="BT45" t="n">
         <v>90</v>
       </c>
-      <c r="BT45" t="inlineStr"/>
       <c r="BU45" t="inlineStr"/>
       <c r="BV45" t="inlineStr"/>
       <c r="BW45" t="inlineStr"/>
-      <c r="BX45" t="n">
+      <c r="BX45" t="inlineStr"/>
+      <c r="BY45" t="n">
         <v>5</v>
       </c>
-      <c r="BY45" t="n">
+      <c r="BZ45" t="n">
         <v>90</v>
       </c>
-      <c r="BZ45" t="n">
+      <c r="CA45" t="n">
         <v>10</v>
       </c>
-      <c r="CA45" t="n">
+      <c r="CB45" t="n">
         <v>93</v>
       </c>
-      <c r="CB45" t="n">
+      <c r="CC45" t="n">
         <v>10</v>
       </c>
-      <c r="CC45" t="n">
+      <c r="CD45" t="n">
         <v>94</v>
       </c>
-      <c r="CD45" t="n">
+      <c r="CE45" t="n">
         <v>10</v>
       </c>
-      <c r="CE45" t="n">
+      <c r="CF45" t="n">
         <v>90</v>
       </c>
-      <c r="CF45" t="n">
+      <c r="CG45" t="n">
         <v>10</v>
       </c>
-      <c r="CG45" t="n">
+      <c r="CH45" t="n">
         <v>92</v>
       </c>
-      <c r="CH45" t="n">
+      <c r="CI45" t="n">
         <v>10</v>
       </c>
-      <c r="CI45" t="n">
+      <c r="CJ45" t="n">
         <v>92</v>
       </c>
-      <c r="CJ45" t="inlineStr"/>
       <c r="CK45" t="inlineStr"/>
       <c r="CL45" t="inlineStr"/>
       <c r="CM45" t="inlineStr"/>
@@ -9324,27 +9372,28 @@
       <c r="CT45" t="inlineStr"/>
       <c r="CU45" t="inlineStr"/>
       <c r="CV45" t="inlineStr"/>
-      <c r="CW45" t="inlineStr">
+      <c r="CW45" t="inlineStr"/>
+      <c r="CX45" t="inlineStr">
         <is>
           <t>+2 OVR 90 +2 PAC 87 +5 Agility 88 +5 Balance 88 +5 Reactions 90 +5 Composure 90 +10 Standing Tackle 92 +10 Sliding Tackle 92 +10 Interceptions 93 +10 Heading Acc. 94 +10 Defensive Awareness 90 2 8 Level 1 Kohler 88 CB PAC 85 SHO 56 PAS 79 DRI 75 DEF 87 PHY 87 R 3 ★ 4 CB 85.4 Kohler 90 CB PAC 87 SHO 56 PAS 79 DRI 76 DEF 87 PHY 87 R 3 ★ 4 CB 85.4 UPGRADES +2 OVR 90 +2 PAC 87 +5 Agility 88 2 8</t>
         </is>
       </c>
-      <c r="CX45" t="inlineStr">
+      <c r="CY45" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CB, LB, RB Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY45" t="inlineStr">
+      <c r="CZ45" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CB, LB, RB Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ45" t="inlineStr">
+      <c r="DA45" t="inlineStr">
         <is>
           <t>WTSS Journey 2 - Defender [SP 8]</t>
         </is>
       </c>
-      <c r="DA45" t="inlineStr">
+      <c r="DB45" t="inlineStr">
         <is>
           <t>WTSS Journey 2 - Defender [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Koeman 71 CB PAC 70 SHO 72 PAS 71 DRI 68 DEF 82 PHY 73 CDM R 3 ★ 3 CB 64.0 Koeman 90 CB PAC 87 SHO 72 PAS 80 DRI 83 DEF 92 PHY 87 CDM R 4 ★ 4 CB 86.0 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CB, LB, RB Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +2 PAC 87 +5 Agility 88 +5 Balance 88 +5 Reactions 90 +5 Composure 90 +10 Standing Tackle 92 +10 Sliding Tackle 92 +10 Interceptions 93 +10 Heading Acc. 94 +10 Defensive Awareness 90 2 8 in 1 month in 1 month 73% 27%</t>
         </is>
@@ -9417,10 +9466,10 @@
       <c r="X46" t="n">
         <v>4</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="n">
         <v>92</v>
       </c>
-      <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
@@ -9432,31 +9481,31 @@
       <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
-      <c r="AL46" t="n">
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="n">
         <v>10</v>
       </c>
-      <c r="AM46" t="n">
+      <c r="AN46" t="n">
         <v>92</v>
       </c>
-      <c r="AN46" t="n">
+      <c r="AO46" t="n">
         <v>10</v>
       </c>
-      <c r="AO46" t="n">
+      <c r="AP46" t="n">
         <v>92</v>
       </c>
-      <c r="AP46" t="n">
+      <c r="AQ46" t="n">
         <v>5</v>
       </c>
-      <c r="AQ46" t="n">
+      <c r="AR46" t="n">
         <v>93</v>
       </c>
-      <c r="AR46" t="n">
+      <c r="AS46" t="n">
         <v>5</v>
       </c>
-      <c r="AS46" t="n">
+      <c r="AT46" t="n">
         <v>94</v>
       </c>
-      <c r="AT46" t="inlineStr"/>
       <c r="AU46" t="inlineStr"/>
       <c r="AV46" t="inlineStr"/>
       <c r="AW46" t="inlineStr"/>
@@ -9474,45 +9523,45 @@
       <c r="BI46" t="inlineStr"/>
       <c r="BJ46" t="inlineStr"/>
       <c r="BK46" t="inlineStr"/>
-      <c r="BL46" t="n">
+      <c r="BL46" t="inlineStr"/>
+      <c r="BM46" t="n">
         <v>5</v>
       </c>
-      <c r="BM46" t="n">
+      <c r="BN46" t="n">
         <v>93</v>
       </c>
-      <c r="BN46" t="inlineStr"/>
       <c r="BO46" t="inlineStr"/>
-      <c r="BP46" t="n">
+      <c r="BP46" t="inlineStr"/>
+      <c r="BQ46" t="n">
         <v>5</v>
       </c>
-      <c r="BQ46" t="n">
+      <c r="BR46" t="n">
         <v>94</v>
       </c>
-      <c r="BR46" t="n">
+      <c r="BS46" t="n">
         <v>5</v>
       </c>
-      <c r="BS46" t="n">
+      <c r="BT46" t="n">
         <v>93</v>
       </c>
-      <c r="BT46" t="n">
+      <c r="BU46" t="n">
         <v>5</v>
       </c>
-      <c r="BU46" t="n">
+      <c r="BV46" t="n">
         <v>94</v>
       </c>
-      <c r="BV46" t="n">
+      <c r="BW46" t="n">
         <v>5</v>
       </c>
-      <c r="BW46" t="n">
+      <c r="BX46" t="n">
         <v>94</v>
       </c>
-      <c r="BX46" t="n">
+      <c r="BY46" t="n">
         <v>5</v>
       </c>
-      <c r="BY46" t="n">
+      <c r="BZ46" t="n">
         <v>93</v>
       </c>
-      <c r="BZ46" t="inlineStr"/>
       <c r="CA46" t="inlineStr"/>
       <c r="CB46" t="inlineStr"/>
       <c r="CC46" t="inlineStr"/>
@@ -9530,34 +9579,35 @@
       <c r="CO46" t="inlineStr"/>
       <c r="CP46" t="inlineStr"/>
       <c r="CQ46" t="inlineStr"/>
-      <c r="CR46" t="n">
+      <c r="CR46" t="inlineStr"/>
+      <c r="CS46" t="n">
         <v>4</v>
       </c>
-      <c r="CS46" t="inlineStr"/>
       <c r="CT46" t="inlineStr"/>
       <c r="CU46" t="inlineStr"/>
       <c r="CV46" t="inlineStr"/>
-      <c r="CW46" t="inlineStr">
+      <c r="CW46" t="inlineStr"/>
+      <c r="CX46" t="inlineStr">
         <is>
           <t>+2 OVR 92 +4 SM +5 Acceleration 92 +5 Sprint Speed 92 +5 Positioning 93 +5 Finishing 94 +5 Curve 93 +5 Balance 94 +5 Reactions 93 +5 Ball Control 94 +5 Dribbling 94 +5 Composure 93 3 8 Level 1 Park Ji Sung 90 RW PAC 90 SHO 90 PAS 89 DRI 89 DEF 64 PHY 77 RM CM CAM R 4 ★ 4 RM 85.7 Park Ji Sung 92 RW PAC 92 SHO 90 PAS 89 DRI 89 DEF 64 PHY 77 RM CM CAM R 4 ★ 4 RM 85.7 UPGRADES +2 OVR 92 +5 Acceleration 92 +5 Sprint Speed 92 3 8</t>
         </is>
       </c>
-      <c r="CX46" t="inlineStr">
+      <c r="CY46" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position ST, RW, LW Max PS 10 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY46" t="inlineStr">
+      <c r="CZ46" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position ST, RW, LW Max PS 10 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ46" t="inlineStr">
+      <c r="DA46" t="inlineStr">
         <is>
           <t>WTSS Journey 3 - Attacker [SP 21]</t>
         </is>
       </c>
-      <c r="DA46" t="inlineStr">
+      <c r="DB46" t="inlineStr">
         <is>
           <t>WTSS Journey 3 - Attacker [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. Smolarek 73 ST PAC 80 SHO 84 PAS 67 DRI 77 DEF 28 PHY 68 LW L 3 ★ 3 LW 70.8 Smolarek 92 ST PAC 92 SHO 92 PAS 86 DRI 93 DEF 28 PHY 76 LW L 5 ★ 4 LW 92.4 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position ST, RW, LW Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +4 SM +5 Acceleration 92 +5 Sprint Speed 92 +5 Positioning 93 +5 Finishing 94 +5 Curve 93 +5 Balance 94 +5 Reactions 93 +5 Ball Control 94 +5 Dribbling 94 +5 Composure 93 3 8 in 1 month in 1 month 71% 29%</t>
         </is>
@@ -9630,16 +9680,16 @@
       <c r="X47" t="n">
         <v>4</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="n">
         <v>92</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AA47" t="n">
         <v>3</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AB47" t="n">
         <v>90</v>
       </c>
-      <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr"/>
@@ -9665,59 +9715,59 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr"/>
       <c r="BA47" t="inlineStr"/>
-      <c r="BB47" t="n">
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="n">
         <v>5</v>
       </c>
-      <c r="BC47" t="n">
+      <c r="BD47" t="n">
         <v>88</v>
       </c>
-      <c r="BD47" t="inlineStr"/>
       <c r="BE47" t="inlineStr"/>
       <c r="BF47" t="inlineStr"/>
       <c r="BG47" t="inlineStr"/>
-      <c r="BH47" t="n">
+      <c r="BH47" t="inlineStr"/>
+      <c r="BI47" t="n">
         <v>5</v>
       </c>
-      <c r="BI47" t="n">
+      <c r="BJ47" t="n">
         <v>88</v>
       </c>
-      <c r="BJ47" t="n">
+      <c r="BK47" t="n">
         <v>5</v>
       </c>
-      <c r="BK47" t="n">
+      <c r="BL47" t="n">
         <v>88</v>
       </c>
-      <c r="BL47" t="inlineStr"/>
       <c r="BM47" t="inlineStr"/>
       <c r="BN47" t="inlineStr"/>
       <c r="BO47" t="inlineStr"/>
       <c r="BP47" t="inlineStr"/>
       <c r="BQ47" t="inlineStr"/>
-      <c r="BR47" t="n">
+      <c r="BR47" t="inlineStr"/>
+      <c r="BS47" t="n">
         <v>10</v>
       </c>
-      <c r="BS47" t="n">
+      <c r="BT47" t="n">
         <v>93</v>
       </c>
-      <c r="BT47" t="n">
+      <c r="BU47" t="n">
         <v>10</v>
       </c>
-      <c r="BU47" t="n">
+      <c r="BV47" t="n">
         <v>88</v>
       </c>
-      <c r="BV47" t="n">
+      <c r="BW47" t="n">
         <v>5</v>
       </c>
-      <c r="BW47" t="n">
+      <c r="BX47" t="n">
         <v>88</v>
       </c>
-      <c r="BX47" t="n">
+      <c r="BY47" t="n">
         <v>5</v>
       </c>
-      <c r="BY47" t="n">
+      <c r="BZ47" t="n">
         <v>93</v>
       </c>
-      <c r="BZ47" t="inlineStr"/>
       <c r="CA47" t="inlineStr"/>
       <c r="CB47" t="inlineStr"/>
       <c r="CC47" t="inlineStr"/>
@@ -9727,62 +9777,63 @@
       <c r="CG47" t="inlineStr"/>
       <c r="CH47" t="inlineStr"/>
       <c r="CI47" t="inlineStr"/>
-      <c r="CJ47" t="n">
+      <c r="CJ47" t="inlineStr"/>
+      <c r="CK47" t="n">
         <v>10</v>
       </c>
-      <c r="CK47" t="n">
+      <c r="CL47" t="n">
         <v>90</v>
       </c>
-      <c r="CL47" t="n">
+      <c r="CM47" t="n">
         <v>10</v>
       </c>
-      <c r="CM47" t="n">
+      <c r="CN47" t="n">
         <v>95</v>
       </c>
-      <c r="CN47" t="n">
+      <c r="CO47" t="n">
         <v>10</v>
       </c>
-      <c r="CO47" t="n">
+      <c r="CP47" t="n">
         <v>93</v>
       </c>
-      <c r="CP47" t="n">
+      <c r="CQ47" t="n">
         <v>10</v>
       </c>
-      <c r="CQ47" t="n">
+      <c r="CR47" t="n">
         <v>88</v>
       </c>
-      <c r="CR47" t="n">
+      <c r="CS47" t="n">
         <v>3</v>
-      </c>
-      <c r="CS47" t="n">
-        <v>4</v>
       </c>
       <c r="CT47" t="n">
         <v>4</v>
       </c>
-      <c r="CU47" t="inlineStr"/>
+      <c r="CU47" t="n">
+        <v>4</v>
+      </c>
       <c r="CV47" t="inlineStr"/>
-      <c r="CW47" t="inlineStr">
+      <c r="CW47" t="inlineStr"/>
+      <c r="CX47" t="inlineStr">
         <is>
           <t>+2 OVR 92 +3 PAC 90 +3 SM 4 +4 WF +5 Reactions 93 +5 Ball Control 88 +5 Dribbling 88 +5 Composure 93 +5 Vision 88 +5 Short Pass 88 +5 Long Pass 88 +10 Aggression 88 +10 Jumping 90 +10 Stamina 95 +10 Strength 93 3 8 Level 1 Kohler 90 CB PAC 87 SHO 56 PAS 79 DRI 76 DEF 92 PHY 87 R 3 ★ 4 CB 88.3 Kohler 92 CB PAC 87 SHO 56 PAS 79 DRI 78 DEF 92 PHY 87 R 3 ★ 4 CB 88.3 UPGRADES +2 OVR 92 +5 Reactions 93 +5 Ball Control 88 3 8</t>
         </is>
       </c>
-      <c r="CX47" t="inlineStr">
+      <c r="CY47" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CB, LB, RB Max PS 10 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY47" t="inlineStr">
+      <c r="CZ47" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CB, LB, RB Max PS 10 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ47" t="inlineStr">
+      <c r="DA47" t="inlineStr">
         <is>
           <t>WTSS Journey 3 - Defender [SP 21]</t>
         </is>
       </c>
-      <c r="DA47" t="inlineStr">
+      <c r="DB47" t="inlineStr">
         <is>
           <t>WTSS Journey 3 - Defender [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. Thuram 74 RB PAC 75 SHO 52 PAS 67 DRI 65 DEF 84 PHY 74 CB R 3 ★ 3 RB 69.3 Thuram 92 RB PAC 90 SHO 70 PAS 82 DRI 85 DEF 92 PHY 93 CB R 4 ★ 5 RB 92.5 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CB, LB, RB Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +3 PAC 90 +3 SM 4 +4 WF +5 Reactions 93 +5 Ball Control 88 +5 Dribbling 88 +5 Composure 93 +5 Vision 88 +5 Short Pass 88 +5 Long Pass 88 +10 Aggression 88 +10 Jumping 90 +10 Stamina 95 +10 Strength 93 3 8 Show less in 1 month in 1 month 76% 24%</t>
         </is>
@@ -9855,18 +9906,18 @@
       <c r="X48" t="n">
         <v>4</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="n">
         <v>90</v>
       </c>
-      <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="n">
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="n">
         <v>4</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AD48" t="n">
         <v>88</v>
       </c>
-      <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
@@ -9874,19 +9925,19 @@
       <c r="AI48" t="inlineStr"/>
       <c r="AJ48" t="inlineStr"/>
       <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="n">
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="n">
         <v>5</v>
       </c>
-      <c r="AM48" t="n">
+      <c r="AN48" t="n">
         <v>88</v>
       </c>
-      <c r="AN48" t="n">
+      <c r="AO48" t="n">
         <v>10</v>
       </c>
-      <c r="AO48" t="n">
+      <c r="AP48" t="n">
         <v>88</v>
       </c>
-      <c r="AP48" t="inlineStr"/>
       <c r="AQ48" t="inlineStr"/>
       <c r="AR48" t="inlineStr"/>
       <c r="AS48" t="inlineStr"/>
@@ -9898,39 +9949,39 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr"/>
       <c r="BA48" t="inlineStr"/>
-      <c r="BB48" t="n">
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="n">
         <v>15</v>
       </c>
-      <c r="BC48" t="n">
+      <c r="BD48" t="n">
         <v>91</v>
       </c>
-      <c r="BD48" t="n">
+      <c r="BE48" t="n">
         <v>15</v>
       </c>
-      <c r="BE48" t="n">
+      <c r="BF48" t="n">
         <v>89</v>
       </c>
-      <c r="BF48" t="inlineStr"/>
       <c r="BG48" t="inlineStr"/>
-      <c r="BH48" t="n">
+      <c r="BH48" t="inlineStr"/>
+      <c r="BI48" t="n">
         <v>30</v>
       </c>
-      <c r="BI48" t="n">
+      <c r="BJ48" t="n">
         <v>93</v>
       </c>
-      <c r="BJ48" t="n">
+      <c r="BK48" t="n">
         <v>15</v>
       </c>
-      <c r="BK48" t="n">
+      <c r="BL48" t="n">
         <v>92</v>
       </c>
-      <c r="BL48" t="n">
+      <c r="BM48" t="n">
         <v>15</v>
       </c>
-      <c r="BM48" t="n">
+      <c r="BN48" t="n">
         <v>90</v>
       </c>
-      <c r="BN48" t="inlineStr"/>
       <c r="BO48" t="inlineStr"/>
       <c r="BP48" t="inlineStr"/>
       <c r="BQ48" t="inlineStr"/>
@@ -9942,90 +9993,91 @@
       <c r="BW48" t="inlineStr"/>
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
-      <c r="BZ48" t="n">
+      <c r="BZ48" t="inlineStr"/>
+      <c r="CA48" t="n">
         <v>30</v>
       </c>
-      <c r="CA48" t="n">
+      <c r="CB48" t="n">
         <v>90</v>
       </c>
-      <c r="CB48" t="n">
+      <c r="CC48" t="n">
         <v>15</v>
       </c>
-      <c r="CC48" t="n">
+      <c r="CD48" t="n">
         <v>89</v>
       </c>
-      <c r="CD48" t="n">
+      <c r="CE48" t="n">
         <v>15</v>
       </c>
-      <c r="CE48" t="n">
+      <c r="CF48" t="n">
         <v>89</v>
       </c>
-      <c r="CF48" t="n">
+      <c r="CG48" t="n">
         <v>15</v>
       </c>
-      <c r="CG48" t="n">
+      <c r="CH48" t="n">
         <v>90</v>
       </c>
-      <c r="CH48" t="n">
+      <c r="CI48" t="n">
         <v>15</v>
       </c>
-      <c r="CI48" t="n">
+      <c r="CJ48" t="n">
         <v>88</v>
       </c>
-      <c r="CJ48" t="n">
+      <c r="CK48" t="n">
         <v>15</v>
       </c>
-      <c r="CK48" t="n">
+      <c r="CL48" t="n">
         <v>89</v>
       </c>
-      <c r="CL48" t="n">
+      <c r="CM48" t="n">
         <v>30</v>
       </c>
-      <c r="CM48" t="n">
+      <c r="CN48" t="n">
         <v>90</v>
       </c>
-      <c r="CN48" t="n">
+      <c r="CO48" t="n">
         <v>15</v>
       </c>
-      <c r="CO48" t="n">
+      <c r="CP48" t="n">
         <v>89</v>
       </c>
-      <c r="CP48" t="n">
+      <c r="CQ48" t="n">
         <v>15</v>
       </c>
-      <c r="CQ48" t="n">
+      <c r="CR48" t="n">
         <v>89</v>
       </c>
-      <c r="CR48" t="n">
+      <c r="CS48" t="n">
         <v>1</v>
       </c>
-      <c r="CS48" t="n">
+      <c r="CT48" t="n">
         <v>4</v>
       </c>
-      <c r="CT48" t="inlineStr"/>
       <c r="CU48" t="inlineStr"/>
       <c r="CV48" t="inlineStr"/>
-      <c r="CW48" t="inlineStr">
+      <c r="CW48" t="inlineStr"/>
+      <c r="CX48" t="inlineStr">
         <is>
           <t>+2 OVR 90 +4 SHO 88 +1 SM 4 +5 Sprint Speed 88 +15 Short Pass 93 +15 Interceptions 90 +15 Stamina 90 +5 Acceleration 88 +15 Fk Accuracy 89 +15 Defensive Awareness 89 +15 Strength 89 +15 Vision 91 +15 Long Pass 92 +15 Heading Acc. 89 +15 Sliding Tackle 88 +15 Aggression 89 +15 Crossing 89 +15 Curve 90 +15 Standing Tackle 90 +15 Jumping 89 2 8 Level 1 Ronaldinho 88 CAM PAC 88 SHO 86 PAS 89 DRI 87 DEF 30 PHY 78 LW R 5 ★ 4 LW 83.8 Ronaldinho 90 CAM PAC 88 SHO 86 PAS 90 DRI 87 DEF 33 PHY 78 LW R 5 ★ 4 LW 83.8 UPGRADES +2 OVR 90 +5 Sprint Speed 88 +15 Short Pass 93 +15 Interceptions 90 +15 Stamina 90 2</t>
         </is>
       </c>
-      <c r="CX48" t="inlineStr">
+      <c r="CY48" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CAM, CDM, CM Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY48" t="inlineStr">
+      <c r="CZ48" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CAM, CDM, CM Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ48" t="inlineStr">
+      <c r="DA48" t="inlineStr">
         <is>
           <t>WTSS Journey 2 - Midfielder [SP 8]</t>
         </is>
       </c>
-      <c r="DA48" t="inlineStr">
+      <c r="DB48" t="inlineStr">
         <is>
           <t>WTSS Journey 2 - Midfielder [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Beckenbauer 71 CDM PAC 70 SHO 52 PAS 76 DRI 64 DEF 80 PHY 70 CB CM R 3 ★ 4 CDM 69.4 Beckenbauer 90 CDM PAC 88 SHO 76 PAS 91 DRI 87 DEF 89 PHY 90 CB CM R 4 ★ 4 CM 89.6 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CAM, CDM, CM Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +4 SHO 88 +1 SM 4 +5 Sprint Speed 88 +15 Short Pass 93 +15 Interceptions 90 +15 Stamina 90 +5 Acceleration 88 +15 Fk Accuracy 89 +15 Defensive Awareness 89 +15 Strength 89 +15 Vision 91 +15 Long Pass 92 +15 Heading Acc. 89 +15 Sliding Tackle 88 +15 Aggression 89 +15 Crossing 89 +15 Curve 90 +15 Standing Tackle 90 +15 Jumping 89 2 8 Show less in 1 month in 1 month 77% 23%</t>
         </is>
@@ -10090,10 +10142,10 @@
       <c r="X49" t="n">
         <v>60</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="n">
         <v>88</v>
       </c>
-      <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr"/>
@@ -10105,123 +10157,123 @@
       <c r="AI49" t="inlineStr"/>
       <c r="AJ49" t="inlineStr"/>
       <c r="AK49" t="inlineStr"/>
-      <c r="AL49" t="n">
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="n">
         <v>60</v>
       </c>
-      <c r="AM49" t="n">
+      <c r="AN49" t="n">
         <v>88</v>
       </c>
-      <c r="AN49" t="n">
+      <c r="AO49" t="n">
         <v>60</v>
       </c>
-      <c r="AO49" t="n">
+      <c r="AP49" t="n">
         <v>88</v>
       </c>
-      <c r="AP49" t="n">
+      <c r="AQ49" t="n">
         <v>30</v>
       </c>
-      <c r="AQ49" t="n">
+      <c r="AR49" t="n">
         <v>84</v>
       </c>
-      <c r="AR49" t="n">
+      <c r="AS49" t="n">
         <v>60</v>
       </c>
-      <c r="AS49" t="n">
+      <c r="AT49" t="n">
         <v>87</v>
       </c>
-      <c r="AT49" t="n">
+      <c r="AU49" t="n">
         <v>60</v>
       </c>
-      <c r="AU49" t="n">
+      <c r="AV49" t="n">
         <v>83</v>
       </c>
-      <c r="AV49" t="n">
+      <c r="AW49" t="n">
         <v>60</v>
       </c>
-      <c r="AW49" t="n">
+      <c r="AX49" t="n">
         <v>88</v>
       </c>
-      <c r="AX49" t="n">
+      <c r="AY49" t="n">
         <v>30</v>
       </c>
-      <c r="AY49" t="n">
+      <c r="AZ49" t="n">
         <v>87</v>
       </c>
-      <c r="AZ49" t="n">
+      <c r="BA49" t="n">
         <v>30</v>
       </c>
-      <c r="BA49" t="n">
+      <c r="BB49" t="n">
         <v>80</v>
       </c>
-      <c r="BB49" t="n">
+      <c r="BC49" t="n">
         <v>20</v>
       </c>
-      <c r="BC49" t="n">
+      <c r="BD49" t="n">
         <v>88</v>
       </c>
-      <c r="BD49" t="n">
+      <c r="BE49" t="n">
         <v>20</v>
       </c>
-      <c r="BE49" t="n">
+      <c r="BF49" t="n">
         <v>87</v>
       </c>
-      <c r="BF49" t="inlineStr"/>
       <c r="BG49" t="inlineStr"/>
-      <c r="BH49" t="n">
+      <c r="BH49" t="inlineStr"/>
+      <c r="BI49" t="n">
         <v>20</v>
       </c>
-      <c r="BI49" t="n">
+      <c r="BJ49" t="n">
         <v>90</v>
       </c>
-      <c r="BJ49" t="n">
+      <c r="BK49" t="n">
         <v>20</v>
       </c>
-      <c r="BK49" t="n">
+      <c r="BL49" t="n">
         <v>88</v>
       </c>
-      <c r="BL49" t="n">
+      <c r="BM49" t="n">
         <v>20</v>
       </c>
-      <c r="BM49" t="n">
+      <c r="BN49" t="n">
         <v>88</v>
       </c>
-      <c r="BN49" t="n">
+      <c r="BO49" t="n">
         <v>25</v>
       </c>
-      <c r="BO49" t="n">
+      <c r="BP49" t="n">
         <v>87</v>
       </c>
-      <c r="BP49" t="n">
+      <c r="BQ49" t="n">
         <v>25</v>
       </c>
-      <c r="BQ49" t="n">
+      <c r="BR49" t="n">
         <v>88</v>
       </c>
-      <c r="BR49" t="n">
+      <c r="BS49" t="n">
         <v>25</v>
       </c>
-      <c r="BS49" t="n">
+      <c r="BT49" t="n">
         <v>86</v>
       </c>
-      <c r="BT49" t="n">
+      <c r="BU49" t="n">
         <v>25</v>
       </c>
-      <c r="BU49" t="n">
+      <c r="BV49" t="n">
         <v>88</v>
       </c>
-      <c r="BV49" t="n">
+      <c r="BW49" t="n">
         <v>25</v>
       </c>
-      <c r="BW49" t="n">
+      <c r="BX49" t="n">
         <v>87</v>
       </c>
-      <c r="BX49" t="n">
+      <c r="BY49" t="n">
         <v>25</v>
       </c>
-      <c r="BY49" t="n">
+      <c r="BZ49" t="n">
         <v>88</v>
       </c>
-      <c r="BZ49" t="inlineStr"/>
       <c r="CA49" t="inlineStr"/>
       <c r="CB49" t="inlineStr"/>
       <c r="CC49" t="inlineStr"/>
@@ -10233,58 +10285,59 @@
       <c r="CI49" t="inlineStr"/>
       <c r="CJ49" t="inlineStr"/>
       <c r="CK49" t="inlineStr"/>
-      <c r="CL49" t="n">
+      <c r="CL49" t="inlineStr"/>
+      <c r="CM49" t="n">
         <v>20</v>
       </c>
-      <c r="CM49" t="n">
+      <c r="CN49" t="n">
         <v>90</v>
       </c>
-      <c r="CN49" t="n">
+      <c r="CO49" t="n">
         <v>20</v>
       </c>
-      <c r="CO49" t="n">
+      <c r="CP49" t="n">
         <v>75</v>
       </c>
-      <c r="CP49" t="n">
+      <c r="CQ49" t="n">
         <v>20</v>
       </c>
-      <c r="CQ49" t="n">
+      <c r="CR49" t="n">
         <v>70</v>
       </c>
-      <c r="CR49" t="n">
+      <c r="CS49" t="n">
         <v>1</v>
       </c>
-      <c r="CS49" t="n">
+      <c r="CT49" t="n">
         <v>4</v>
       </c>
-      <c r="CT49" t="n">
+      <c r="CU49" t="n">
         <v>1</v>
       </c>
-      <c r="CU49" t="n">
+      <c r="CV49" t="n">
         <v>4</v>
       </c>
-      <c r="CV49" t="inlineStr"/>
-      <c r="CW49" t="inlineStr">
+      <c r="CW49" t="inlineStr"/>
+      <c r="CX49" t="inlineStr">
         <is>
           <t>+30 OVR 88 +1 SM 4 +1 WF 4 +30 Acceleration 88 +30 Sprint Speed 88 +30 Finishing 87 +30 Shot Power 83 +30 Long Shots 88 +30 Positioning 84 +20 Vision 88 +20 Crossing 87 +20 Fk Accuracy 88 +20 Short Pass 90 +20 Long Pass 88 +30 Volleys 87 +30 Penalties 80 +25 Agility 87 +25 Balance 88 +20 Curve 88 +25 Reactions 86 +25 Ball Control 88 +20 Aggression 70 +25 Dribbling 87 +25 Composure 88 +20 Stamina 90 +20 Strength 75 8 Level 1 Maradona 74 CAM PAC 77 SHO 76 PAS 77 DRI 85 DEF 30 PHY 62 ST L 5 ★ 3 Maradona 88 CAM PAC 88 SHO 85 PAS 77 DRI 85 DEF 30 PHY 62 ST L 5 ★ 3 UPGRADES +30 OVR 88 +30 Acceleration 88 +30 Sprint Speed 88 +30 Finishing 87 +30 Shot Power 83 +30 Long Shots 88</t>
         </is>
       </c>
-      <c r="CX49" t="inlineStr">
+      <c r="CY49" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Position ST, RW, LW Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY49" t="inlineStr">
+      <c r="CZ49" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Position ST, RW, LW Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ49" t="inlineStr">
+      <c r="DA49" t="inlineStr">
         <is>
           <t>WTSS Journey 1 - Attacker [SP 3]</t>
         </is>
       </c>
-      <c r="DA49" t="inlineStr">
+      <c r="DB49" t="inlineStr">
         <is>
           <t>WTSS Journey 1 - Attacker [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Garrincha 70 RW PAC 82 SHO 64 PAS 67 DRI 78 DEF 34 PHY 48 RM R 5 ★ 4 RM 70.4 Garrincha 88 RW PAC 88 SHO 86 PAS 87 DRI 87 DEF 34 PHY 67 RM R 5 ★ 4 RM 83.9 REQUIREMENTS Rarity World Tour Silver Stars Position ST, RW, LW Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +1 SM 4 +1 WF 4 +30 Acceleration 88 +30 Sprint Speed 88 +30 Finishing 87 +30 Shot Power 83 +30 Long Shots 88 +30 Positioning 84 +20 Vision 88 +20 Crossing 87 +20 Fk Accuracy 88 +20 Short Pass 90 +20 Long Pass 88 +30 Volleys 87 +30 Penalties 80 +25 Agility 87 +25 Balance 88 +20 Curve 88 +25 Reactions 86 +25 Ball Control 88 +20 Aggression 70 +25 Dribbling 87 +25 Composure 88 +20 Stamina 90 +20 Strength 75 8 in 1 month in 1 month 78% 22%</t>
         </is>
@@ -10349,10 +10402,10 @@
       <c r="X50" t="n">
         <v>60</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="n">
         <v>88</v>
       </c>
-      <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr"/>
@@ -10362,159 +10415,159 @@
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="inlineStr"/>
-      <c r="AJ50" t="n">
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="n">
         <v>20</v>
       </c>
-      <c r="AK50" t="n">
+      <c r="AL50" t="n">
         <v>84</v>
       </c>
-      <c r="AL50" t="n">
+      <c r="AM50" t="n">
         <v>60</v>
       </c>
-      <c r="AM50" t="n">
+      <c r="AN50" t="n">
         <v>85</v>
       </c>
-      <c r="AN50" t="n">
+      <c r="AO50" t="n">
         <v>60</v>
       </c>
-      <c r="AO50" t="n">
+      <c r="AP50" t="n">
         <v>85</v>
       </c>
-      <c r="AP50" t="n">
+      <c r="AQ50" t="n">
         <v>20</v>
       </c>
-      <c r="AQ50" t="n">
+      <c r="AR50" t="n">
         <v>85</v>
       </c>
-      <c r="AR50" t="n">
+      <c r="AS50" t="n">
         <v>20</v>
       </c>
-      <c r="AS50" t="n">
+      <c r="AT50" t="n">
         <v>87</v>
       </c>
-      <c r="AT50" t="n">
+      <c r="AU50" t="n">
         <v>20</v>
       </c>
-      <c r="AU50" t="n">
+      <c r="AV50" t="n">
         <v>87</v>
       </c>
-      <c r="AV50" t="n">
+      <c r="AW50" t="n">
         <v>20</v>
       </c>
-      <c r="AW50" t="n">
+      <c r="AX50" t="n">
         <v>90</v>
       </c>
-      <c r="AX50" t="n">
+      <c r="AY50" t="n">
         <v>20</v>
       </c>
-      <c r="AY50" t="n">
+      <c r="AZ50" t="n">
         <v>88</v>
       </c>
-      <c r="AZ50" t="n">
+      <c r="BA50" t="n">
         <v>20</v>
       </c>
-      <c r="BA50" t="n">
+      <c r="BB50" t="n">
         <v>85</v>
       </c>
-      <c r="BB50" t="n">
+      <c r="BC50" t="n">
         <v>30</v>
       </c>
-      <c r="BC50" t="n">
+      <c r="BD50" t="n">
         <v>86</v>
       </c>
-      <c r="BD50" t="n">
+      <c r="BE50" t="n">
         <v>30</v>
       </c>
-      <c r="BE50" t="n">
+      <c r="BF50" t="n">
         <v>85</v>
       </c>
-      <c r="BF50" t="inlineStr"/>
       <c r="BG50" t="inlineStr"/>
-      <c r="BH50" t="n">
+      <c r="BH50" t="inlineStr"/>
+      <c r="BI50" t="n">
         <v>30</v>
       </c>
-      <c r="BI50" t="n">
+      <c r="BJ50" t="n">
         <v>87</v>
       </c>
-      <c r="BJ50" t="n">
+      <c r="BK50" t="n">
         <v>30</v>
       </c>
-      <c r="BK50" t="n">
+      <c r="BL50" t="n">
         <v>88</v>
       </c>
-      <c r="BL50" t="n">
+      <c r="BM50" t="n">
         <v>60</v>
       </c>
-      <c r="BM50" t="n">
+      <c r="BN50" t="n">
         <v>86</v>
       </c>
-      <c r="BN50" t="n">
+      <c r="BO50" t="n">
         <v>60</v>
       </c>
-      <c r="BO50" t="n">
+      <c r="BP50" t="n">
         <v>86</v>
       </c>
-      <c r="BP50" t="n">
+      <c r="BQ50" t="n">
         <v>60</v>
       </c>
-      <c r="BQ50" t="n">
+      <c r="BR50" t="n">
         <v>84</v>
       </c>
-      <c r="BR50" t="n">
+      <c r="BS50" t="n">
         <v>30</v>
       </c>
-      <c r="BS50" t="n">
+      <c r="BT50" t="n">
         <v>87</v>
       </c>
-      <c r="BT50" t="n">
+      <c r="BU50" t="n">
         <v>30</v>
       </c>
-      <c r="BU50" t="n">
+      <c r="BV50" t="n">
         <v>85</v>
       </c>
-      <c r="BV50" t="n">
+      <c r="BW50" t="n">
         <v>30</v>
       </c>
-      <c r="BW50" t="n">
+      <c r="BX50" t="n">
         <v>88</v>
       </c>
-      <c r="BX50" t="n">
+      <c r="BY50" t="n">
         <v>30</v>
       </c>
-      <c r="BY50" t="n">
+      <c r="BZ50" t="n">
         <v>88</v>
       </c>
-      <c r="BZ50" t="n">
+      <c r="CA50" t="n">
         <v>30</v>
       </c>
-      <c r="CA50" t="n">
+      <c r="CB50" t="n">
         <v>85</v>
       </c>
-      <c r="CB50" t="n">
+      <c r="CC50" t="n">
         <v>30</v>
       </c>
-      <c r="CC50" t="n">
+      <c r="CD50" t="n">
         <v>88</v>
       </c>
-      <c r="CD50" t="n">
+      <c r="CE50" t="n">
         <v>30</v>
       </c>
-      <c r="CE50" t="n">
+      <c r="CF50" t="n">
         <v>85</v>
       </c>
-      <c r="CF50" t="n">
+      <c r="CG50" t="n">
         <v>30</v>
       </c>
-      <c r="CG50" t="n">
+      <c r="CH50" t="n">
         <v>86</v>
       </c>
-      <c r="CH50" t="n">
+      <c r="CI50" t="n">
         <v>30</v>
       </c>
-      <c r="CI50" t="n">
+      <c r="CJ50" t="n">
         <v>88</v>
       </c>
-      <c r="CJ50" t="inlineStr"/>
       <c r="CK50" t="inlineStr"/>
       <c r="CL50" t="inlineStr"/>
       <c r="CM50" t="inlineStr"/>
@@ -10522,40 +10575,41 @@
       <c r="CO50" t="inlineStr"/>
       <c r="CP50" t="inlineStr"/>
       <c r="CQ50" t="inlineStr"/>
-      <c r="CR50" t="n">
+      <c r="CR50" t="inlineStr"/>
+      <c r="CS50" t="n">
         <v>1</v>
       </c>
-      <c r="CS50" t="n">
+      <c r="CT50" t="n">
         <v>4</v>
       </c>
-      <c r="CT50" t="n">
+      <c r="CU50" t="n">
         <v>1</v>
       </c>
-      <c r="CU50" t="n">
+      <c r="CV50" t="n">
         <v>4</v>
       </c>
-      <c r="CV50" t="inlineStr"/>
-      <c r="CW50" t="inlineStr">
+      <c r="CW50" t="inlineStr"/>
+      <c r="CX50" t="inlineStr">
         <is>
           <t>+30 OVR 88 +20 PHY 84 +1 SM 4 +1 WF 4 +30 Acceleration 85 +30 Sprint Speed 85 +30 Curve 86 +30 Agility 86 +30 Balance 84 +20 Positioning 85 +20 Finishing 87 +20 Shot Power 87 +20 Long Shots 90 +20 Volleys 88 +20 Penalties 85 +30 Reactions 87 +30 Ball Control 85 +30 Vision 86 +30 Crossing 85 +30 Fk Accuracy 88 +30 Short Pass 87 +30 Long Pass 88 +30 Heading Acc. 88 +30 Dribbling 88 +30 Composure 88 +30 Interceptions 85 +30 Defensive Awareness 85 +30 Standing Tackle 86 +30 Sliding Tackle 88 8 Level 1 Cesc Fàbregas 74 CAM PAC 72 SHO 74 PAS 84 DRI 82 DEF 54 PHY 60 ST R 3 ★ 3 Cesc Fàbregas 88 CAM PAC 85 SHO 74 PAS 84 DRI 83 DEF 54 PHY 60 ST R 3 ★ 3 UPGRADES +30 OVR 88 +30 Acceleration 85 +30 Sprint Speed 85 +30 Curve 86 +30 Agility 86 +30 Balance 84 8</t>
         </is>
       </c>
-      <c r="CX50" t="inlineStr">
+      <c r="CY50" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Position CAM, CM, CDM Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY50" t="inlineStr">
+      <c r="CZ50" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Position CAM, CM, CDM Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ50" t="inlineStr">
+      <c r="DA50" t="inlineStr">
         <is>
           <t>WTSS Journey 1 - Midfielder [SP 3]</t>
         </is>
       </c>
-      <c r="DA50" t="inlineStr">
+      <c r="DB50" t="inlineStr">
         <is>
           <t>WTSS Journey 1 - Midfielder [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Beckenbauer 71 CDM PAC 70 SHO 52 PAS 76 DRI 64 DEF 80 PHY 70 CB CM R 3 ★ 4 CDM 69.4 Beckenbauer 88 CDM PAC 85 SHO 72 PAS 87 DRI 87 DEF 86 PHY 84 CB CM R 4 ★ 4 CM 84.3 REQUIREMENTS Rarity World Tour Silver Stars Position CAM, CM, CDM Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +20 PHY 84 +1 SM 4 +1 WF 4 +30 Acceleration 85 +30 Sprint Speed 85 +30 Curve 86 +30 Agility 86 +30 Balance 84 +20 Positioning 85 +20 Finishing 87 +20 Shot Power 87 +20 Long Shots 90 +20 Volleys 88 +20 Penalties 85 +30 Reactions 87 +30 Ball Control 85 +30 Vision 86 +30 Crossing 85 +30 Fk Accuracy 88 +30 Short Pass 87 +30 Long Pass 88 +30 Heading Acc. 88 +30 Dribbling 88 +30 Composure 88 +30 Interceptions 85 +30 Defensive Awareness 85 +30 Standing Tackle 86 +30 Sliding Tackle 88 8 Show less in 1 month in 1 month 80% 20%</t>
         </is>
@@ -10620,18 +10674,18 @@
       <c r="X51" t="n">
         <v>60</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="n">
         <v>88</v>
       </c>
-      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="n">
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="n">
         <v>20</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AD51" t="n">
         <v>70</v>
       </c>
-      <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
@@ -10639,19 +10693,19 @@
       <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="n">
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="n">
         <v>30</v>
       </c>
-      <c r="AM51" t="n">
+      <c r="AN51" t="n">
         <v>85</v>
       </c>
-      <c r="AN51" t="n">
+      <c r="AO51" t="n">
         <v>30</v>
       </c>
-      <c r="AO51" t="n">
+      <c r="AP51" t="n">
         <v>85</v>
       </c>
-      <c r="AP51" t="inlineStr"/>
       <c r="AQ51" t="inlineStr"/>
       <c r="AR51" t="inlineStr"/>
       <c r="AS51" t="inlineStr"/>
@@ -10663,162 +10717,163 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="inlineStr"/>
-      <c r="BB51" t="n">
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="n">
         <v>30</v>
       </c>
-      <c r="BC51" t="n">
+      <c r="BD51" t="n">
         <v>75</v>
       </c>
-      <c r="BD51" t="n">
+      <c r="BE51" t="n">
         <v>30</v>
       </c>
-      <c r="BE51" t="n">
+      <c r="BF51" t="n">
         <v>75</v>
       </c>
-      <c r="BF51" t="inlineStr"/>
       <c r="BG51" t="inlineStr"/>
-      <c r="BH51" t="n">
+      <c r="BH51" t="inlineStr"/>
+      <c r="BI51" t="n">
         <v>30</v>
       </c>
-      <c r="BI51" t="n">
+      <c r="BJ51" t="n">
         <v>85</v>
       </c>
-      <c r="BJ51" t="n">
+      <c r="BK51" t="n">
         <v>30</v>
       </c>
-      <c r="BK51" t="n">
+      <c r="BL51" t="n">
         <v>80</v>
       </c>
-      <c r="BL51" t="n">
+      <c r="BM51" t="n">
         <v>60</v>
       </c>
-      <c r="BM51" t="n">
+      <c r="BN51" t="n">
         <v>80</v>
       </c>
-      <c r="BN51" t="n">
+      <c r="BO51" t="n">
         <v>30</v>
       </c>
-      <c r="BO51" t="n">
+      <c r="BP51" t="n">
         <v>80</v>
       </c>
-      <c r="BP51" t="n">
+      <c r="BQ51" t="n">
         <v>15</v>
       </c>
-      <c r="BQ51" t="n">
+      <c r="BR51" t="n">
         <v>80</v>
       </c>
-      <c r="BR51" t="n">
+      <c r="BS51" t="n">
         <v>30</v>
       </c>
-      <c r="BS51" t="n">
+      <c r="BT51" t="n">
         <v>88</v>
       </c>
-      <c r="BT51" t="n">
+      <c r="BU51" t="n">
         <v>15</v>
       </c>
-      <c r="BU51" t="n">
+      <c r="BV51" t="n">
         <v>85</v>
       </c>
-      <c r="BV51" t="n">
+      <c r="BW51" t="n">
         <v>15</v>
       </c>
-      <c r="BW51" t="n">
+      <c r="BX51" t="n">
         <v>85</v>
       </c>
-      <c r="BX51" t="n">
+      <c r="BY51" t="n">
         <v>30</v>
       </c>
-      <c r="BY51" t="n">
+      <c r="BZ51" t="n">
         <v>88</v>
       </c>
-      <c r="BZ51" t="n">
+      <c r="CA51" t="n">
         <v>30</v>
       </c>
-      <c r="CA51" t="n">
+      <c r="CB51" t="n">
         <v>88</v>
       </c>
-      <c r="CB51" t="n">
+      <c r="CC51" t="n">
         <v>30</v>
       </c>
-      <c r="CC51" t="n">
+      <c r="CD51" t="n">
         <v>87</v>
       </c>
-      <c r="CD51" t="n">
+      <c r="CE51" t="n">
         <v>60</v>
       </c>
-      <c r="CE51" t="n">
+      <c r="CF51" t="n">
         <v>87</v>
       </c>
-      <c r="CF51" t="n">
+      <c r="CG51" t="n">
         <v>60</v>
       </c>
-      <c r="CG51" t="n">
+      <c r="CH51" t="n">
         <v>88</v>
       </c>
-      <c r="CH51" t="n">
+      <c r="CI51" t="n">
         <v>60</v>
       </c>
-      <c r="CI51" t="n">
+      <c r="CJ51" t="n">
         <v>86</v>
       </c>
-      <c r="CJ51" t="n">
+      <c r="CK51" t="n">
         <v>30</v>
       </c>
-      <c r="CK51" t="n">
+      <c r="CL51" t="n">
         <v>80</v>
       </c>
-      <c r="CL51" t="n">
+      <c r="CM51" t="n">
         <v>30</v>
       </c>
-      <c r="CM51" t="n">
+      <c r="CN51" t="n">
         <v>85</v>
       </c>
-      <c r="CN51" t="n">
+      <c r="CO51" t="n">
         <v>30</v>
       </c>
-      <c r="CO51" t="n">
+      <c r="CP51" t="n">
         <v>87</v>
       </c>
-      <c r="CP51" t="n">
+      <c r="CQ51" t="n">
         <v>30</v>
       </c>
-      <c r="CQ51" t="n">
+      <c r="CR51" t="n">
         <v>90</v>
       </c>
-      <c r="CR51" t="n">
+      <c r="CS51" t="n">
         <v>1</v>
       </c>
-      <c r="CS51" t="n">
+      <c r="CT51" t="n">
         <v>4</v>
       </c>
-      <c r="CT51" t="n">
+      <c r="CU51" t="n">
         <v>1</v>
       </c>
-      <c r="CU51" t="n">
+      <c r="CV51" t="n">
         <v>4</v>
       </c>
-      <c r="CV51" t="inlineStr"/>
-      <c r="CW51" t="inlineStr">
+      <c r="CW51" t="inlineStr"/>
+      <c r="CX51" t="inlineStr">
         <is>
           <t>+30 OVR 88 +20 SHO 70 +1 SM 4 +1 WF 4 +30 Curve 80 +15 Agility 80 +30 Defensive Awareness 87 +30 Standing Tackle 88 +30 Sliding Tackle 86 +30 Acceleration 85 +30 Sprint Speed 85 +30 Vision 75 +30 Crossing 75 +30 Fk Accuracy 65 +30 Short Pass 85 +30 Long Pass 80 +15 Balance 80 +30 Reactions 88 +15 Ball Control 85 +30 Jumping 80 +30 Stamina 85 +30 Strength 87 +15 Dribbling 85 +30 Composure 88 +30 Interceptions 88 +30 Heading Acc. 87 +30 Aggression 90 8 Level 1 Petit 74 CDM PAC 70 SHO 70 PAS 85 DRI 72 DEF 74 PHY 76 LB CM L 3 ★ 3 Petit 88 CDM PAC 70 SHO 70 PAS 86 DRI 73 DEF 83 PHY 76 LB CM L 3 ★ 3 UPGRADES +30 OVR 88 +30 Curve 80 +15 Agility 80 +30 Defensive Awareness 87 +30 Standing Tackle 88 +30 Sliding Tackle 86</t>
         </is>
       </c>
-      <c r="CX51" t="inlineStr">
+      <c r="CY51" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Position CB, LB, RB Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY51" t="inlineStr">
+      <c r="CZ51" t="inlineStr">
         <is>
           <t>Rarity World Tour Silver Stars Position CB, LB, RB Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ51" t="inlineStr">
+      <c r="DA51" t="inlineStr">
         <is>
           <t>WTSS Journey 1 - Defender [SP 3]</t>
         </is>
       </c>
-      <c r="DA51" t="inlineStr">
+      <c r="DB51" t="inlineStr">
         <is>
           <t>WTSS Journey 1 - Defender [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Koeman 71 CB PAC 70 SHO 72 PAS 71 DRI 68 DEF 82 PHY 73 CDM R 3 ★ 3 CB 64.0 Koeman 88 CB PAC 85 SHO 72 PAS 80 DRI 82 DEF 87 PHY 87 CDM R 4 ★ 4 CB 80.4 REQUIREMENTS Rarity World Tour Silver Stars Position CB, LB, RB Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +20 SHO 70 +1 SM 4 +1 WF 4 +30 Curve 80 +15 Agility 80 +30 Defensive Awareness 87 +30 Standing Tackle 88 +30 Sliding Tackle 86 +30 Acceleration 85 +30 Sprint Speed 85 +30 Vision 75 +30 Crossing 75 +30 Fk Accuracy 65 +30 Short Pass 85 +30 Long Pass 80 +15 Balance 80 +30 Reactions 88 +15 Ball Control 85 +30 Jumping 80 +30 Stamina 85 +30 Strength 87 +15 Dribbling 85 +30 Composure 88 +30 Interceptions 88 +30 Heading Acc. 87 +30 Aggression 90 8 Show less in 1 month in 1 month 82% 18%</t>
         </is>
@@ -10949,27 +11004,28 @@
       <c r="CT52" t="inlineStr"/>
       <c r="CU52" t="inlineStr"/>
       <c r="CV52" t="inlineStr"/>
-      <c r="CW52" t="inlineStr">
+      <c r="CW52" t="inlineStr"/>
+      <c r="CX52" t="inlineStr">
         <is>
           <t>No upgrades Level 1 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 UPGRADES No upgrades</t>
         </is>
       </c>
-      <c r="CX52" t="inlineStr">
+      <c r="CY52" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY52" t="inlineStr">
+      <c r="CZ52" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ52" t="inlineStr">
+      <c r="DA52" t="inlineStr">
         <is>
           <t>Season Ladder Excellence [SP 27]</t>
         </is>
       </c>
-      <c r="DA52" t="inlineStr">
+      <c r="DB52" t="inlineStr">
         <is>
           <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Jacobo Ramón 94 CB PAC 88 SHO 46 PAS 84 DRI 81 DEF 94 PHY 91 R 3 ★ 4 CB 93.8 Jacobo Ramón 94 CB PAC 88 SHO 46 PAS 84 DRI 81 DEF 94 PHY 91 R 3 ★ 4 CB 93.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 1 month in 1 month 30% 70%</t>
         </is>
@@ -11045,13 +11101,13 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="n">
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="n">
         <v>2</v>
       </c>
-      <c r="AI53" t="n">
+      <c r="AJ53" t="n">
         <v>92</v>
       </c>
-      <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="inlineStr"/>
       <c r="AM53" t="inlineStr"/>
@@ -11116,27 +11172,28 @@
       <c r="CT53" t="inlineStr"/>
       <c r="CU53" t="inlineStr"/>
       <c r="CV53" t="inlineStr"/>
-      <c r="CW53" t="inlineStr">
+      <c r="CW53" t="inlineStr"/>
+      <c r="CX53" t="inlineStr">
         <is>
           <t>+2 DEF 92 2 8 Level 1 Lamine Yamal 91 RW PAC 87 SHO 83 PAS 88 DRI 92 DEF 25 PHY 55 RM L 5 ★ 3 Lamine Yamal 91 RW PAC 87 SHO 83 PAS 88 DRI 92 DEF 25 PHY 55 RM L 5 ★ 3 UPGRADES 8</t>
         </is>
       </c>
-      <c r="CX53" t="inlineStr">
+      <c r="CY53" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY53" t="inlineStr">
+      <c r="CZ53" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ53" t="inlineStr">
+      <c r="DA53" t="inlineStr">
         <is>
           <t>Crunch Time</t>
         </is>
       </c>
-      <c r="DA53" t="inlineStr">
+      <c r="DB53" t="inlineStr">
         <is>
           <t>Crunch Time Unlocked by completing the Unbreakable objective van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 CB 90.5 van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 90 PHY 88 L 3 ★ 3 CB 93.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 UPGRADES +2 DEF 92 2 8 in 7 months in 7 months 92% 8%</t>
         </is>
@@ -11279,27 +11336,28 @@
       <c r="CT54" t="inlineStr"/>
       <c r="CU54" t="inlineStr"/>
       <c r="CV54" t="inlineStr"/>
-      <c r="CW54" t="inlineStr">
+      <c r="CW54" t="inlineStr"/>
+      <c r="CX54" t="inlineStr">
         <is>
           <t>2 8 Level 1 Doué 91 RW PAC 91 SHO 87 PAS 86 DRI 95 DEF 61 PHY 83 RM CM LW R 5 ★ 4 Doué 91 RW PAC 91 SHO 87 PAS 86 DRI 95 DEF 61 PHY 83 RM CM LW R 5 ★ 4 UPGRADES 8</t>
         </is>
       </c>
-      <c r="CX54" t="inlineStr">
+      <c r="CY54" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY54" t="inlineStr">
+      <c r="CZ54" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ54" t="inlineStr">
+      <c r="DA54" t="inlineStr">
         <is>
           <t>Passing Technician</t>
         </is>
       </c>
-      <c r="DA54" t="inlineStr">
+      <c r="DB54" t="inlineStr">
         <is>
           <t>Passing Technician Unlocked by completing the Passing Mastermind objective Martínez 88 GK DIV 87 HAN 86 KIC 86 REF 88 SPD 60 POS 90 R 1 ★ 4 GK 89.1 Martínez 88 GK DIV 87 HAN 86 KIC 86 REF 88 SPD 60 POS 90 R 1 ★ 4 GK 91.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 UPGRADES 2 8 in 7 months in 7 months 86% 14%</t>
         </is>
@@ -11361,43 +11419,43 @@
         <v>2</v>
       </c>
       <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="n">
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="n">
         <v>4</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AB55" t="n">
         <v>92</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AC55" t="n">
         <v>4</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AD55" t="n">
         <v>91</v>
       </c>
-      <c r="AD55" t="n">
+      <c r="AE55" t="n">
         <v>4</v>
       </c>
-      <c r="AE55" t="n">
+      <c r="AF55" t="n">
         <v>92</v>
       </c>
-      <c r="AF55" t="n">
+      <c r="AG55" t="n">
         <v>6</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AH55" t="n">
         <v>93</v>
       </c>
-      <c r="AH55" t="n">
+      <c r="AI55" t="n">
         <v>4</v>
       </c>
-      <c r="AI55" t="n">
+      <c r="AJ55" t="n">
         <v>90</v>
       </c>
-      <c r="AJ55" t="n">
+      <c r="AK55" t="n">
         <v>2</v>
       </c>
-      <c r="AK55" t="n">
+      <c r="AL55" t="n">
         <v>89</v>
       </c>
-      <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="inlineStr"/>
       <c r="AN55" t="inlineStr"/>
       <c r="AO55" t="inlineStr"/>
@@ -11460,27 +11518,28 @@
       <c r="CT55" t="inlineStr"/>
       <c r="CU55" t="inlineStr"/>
       <c r="CV55" t="inlineStr"/>
-      <c r="CW55" t="inlineStr">
+      <c r="CW55" t="inlineStr"/>
+      <c r="CX55" t="inlineStr">
         <is>
           <t>+1 OVR +2 PAC 92 +2 SHO 91 +2 PAS 92 +3 DRI 93 +2 DEF 90 +1 PHY 89 Level 1 Doué 91 RW PAC 91 SHO 87 PAS 86 DRI 95 DEF 61 PHY 83 RM CM LW R 5 ★ 4 Doué 92 RW PAC 92 SHO 89 PAS 88 DRI 95 DEF 63 PHY 84 RM CM LW R 5 ★ 4 UPGRADES +1 OVR +2 PAC 92 +2 SHO 91 +2 PAS 92 +3 DRI 93 +2 DEF 90 +1 PHY 89</t>
         </is>
       </c>
-      <c r="CX55" t="inlineStr">
+      <c r="CY55" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY55" t="inlineStr">
+      <c r="CZ55" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ55" t="inlineStr">
+      <c r="DA55" t="inlineStr">
         <is>
           <t>All-Around Impact</t>
         </is>
       </c>
-      <c r="DA55" t="inlineStr">
+      <c r="DB55" t="inlineStr">
         <is>
           <t>All-Around Impact Unlocked by completing the Formation Excellence objective Nesta 88 CB PAC 87 SHO 43 PAS 65 DRI 80 DEF 88 PHY 86 R 3 ★ 4 CB 90.9 Nesta 89 CB PAC 89 SHO 45 PAS 67 DRI 83 DEF 90 PHY 87 R 3 ★ 4 CB 92.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 UPGRADES +1 OVR +2 PAC 92 +2 SHO 91 +2 PAS 92 +3 DRI 93 +2 DEF 90 +1 PHY 89 in 7 months in 7 months 98% 2%</t>
         </is>
@@ -11619,27 +11678,28 @@
       <c r="CT56" t="inlineStr"/>
       <c r="CU56" t="inlineStr"/>
       <c r="CV56" t="inlineStr"/>
-      <c r="CW56" t="inlineStr">
+      <c r="CW56" t="inlineStr"/>
+      <c r="CX56" t="inlineStr">
         <is>
           <t>2 Level 1 Dembélé 91 CAM PAC 92 SHO 89 PAS 90 DRI 94 DEF 53 PHY 70 RW ST L 5 ★ 5 Dembélé 91 CAM PAC 92 SHO 89 PAS 90 DRI 94 DEF 53 PHY 70 RW ST L 5 ★ 5 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX56" t="inlineStr">
+      <c r="CY56" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY56" t="inlineStr">
+      <c r="CZ56" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ56" t="inlineStr">
+      <c r="DA56" t="inlineStr">
         <is>
           <t>Quick Step+</t>
         </is>
       </c>
-      <c r="DA56" t="inlineStr">
+      <c r="DB56" t="inlineStr">
         <is>
           <t>Quick Step+ Unlocked by completing the Ancient Triangle task in the Formation Excellence objective Henrichs 88 RB PAC 90 SHO 75 PAS 85 DRI 86 DEF 88 PHY 84 LB RM R 3 ★ 5 LB 87.0 Henrichs 88 RB PAC 90 SHO 75 PAS 85 DRI 86 DEF 88 PHY 84 LB RM R 3 ★ 5 LB 89.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 UPGRADES 2 in 7 months in 7 months 94% 6%</t>
         </is>
@@ -11778,27 +11838,28 @@
       <c r="CT57" t="inlineStr"/>
       <c r="CU57" t="inlineStr"/>
       <c r="CV57" t="inlineStr"/>
-      <c r="CW57" t="inlineStr">
+      <c r="CW57" t="inlineStr"/>
+      <c r="CX57" t="inlineStr">
         <is>
           <t>2 Level 1 Doku 91 LW PAC 97 SHO 86 PAS 84 DRI 93 DEF 45 PHY 82 LM RW R 5 ★ 5 Doku 91 LW PAC 97 SHO 86 PAS 84 DRI 93 DEF 45 PHY 82 LM RW R 5 ★ 5 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX57" t="inlineStr">
+      <c r="CY57" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY57" t="inlineStr">
+      <c r="CZ57" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ57" t="inlineStr">
+      <c r="DA57" t="inlineStr">
         <is>
           <t>Finesse Shot+</t>
         </is>
       </c>
-      <c r="DA57" t="inlineStr">
+      <c r="DB57" t="inlineStr">
         <is>
           <t>Finesse Shot+ Unlocked by completing the Magic Rectangle task in the Formation Excellence objective Kögel 89 LM PAC 93 SHO 88 PAS 86 DRI 89 DEF 61 PHY 76 LW L 5 ★ 4 LM 87.3 Kögel 89 LM PAC 93 SHO 88 PAS 86 DRI 89 DEF 61 PHY 76 LW L 5 ★ 4 LM 89.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 UPGRADES 2 in 7 months in 7 months 95% 5%</t>
         </is>
@@ -11937,27 +11998,28 @@
       <c r="CT58" t="inlineStr"/>
       <c r="CU58" t="inlineStr"/>
       <c r="CV58" t="inlineStr"/>
-      <c r="CW58" t="inlineStr">
+      <c r="CW58" t="inlineStr"/>
+      <c r="CX58" t="inlineStr">
         <is>
           <t>2 Level 1 Dybala 91 CAM PAC 90 SHO 90 PAS 90 DRI 92 DEF 50 PHY 75 RW ST L 5 ★ 5 Dybala 91 CAM PAC 90 SHO 90 PAS 90 DRI 92 DEF 50 PHY 75 RW ST L 5 ★ 5 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX58" t="inlineStr">
+      <c r="CY58" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY58" t="inlineStr">
+      <c r="CZ58" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ58" t="inlineStr">
+      <c r="DA58" t="inlineStr">
         <is>
           <t>Technical+</t>
         </is>
       </c>
-      <c r="DA58" t="inlineStr">
+      <c r="DB58" t="inlineStr">
         <is>
           <t>Technical+ Unlocked by completing the The Trident task in the Formation Excellence objective Vini Jr. 90 ST PAC 95 SHO 88 PAS 81 DRI 92 DEF 30 PHY 75 LM LW R 5 ★ 4 LM 87.4 Vini Jr. 90 ST PAC 95 SHO 88 PAS 81 DRI 92 DEF 30 PHY 75 LM LW R 5 ★ 4 LM 88.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 UPGRADES 2 in 7 months in 7 months 82% 18%</t>
         </is>
@@ -12096,27 +12158,28 @@
       <c r="CT59" t="inlineStr"/>
       <c r="CU59" t="inlineStr"/>
       <c r="CV59" t="inlineStr"/>
-      <c r="CW59" t="inlineStr">
+      <c r="CW59" t="inlineStr"/>
+      <c r="CX59" t="inlineStr">
         <is>
           <t>2 Level 1 Vitinha 91 CM PAC 85 SHO 82 PAS 88 DRI 92 DEF 80 PHY 73 CDM CAM R 5 ★ 4 Vitinha 91 CM PAC 85 SHO 82 PAS 88 DRI 92 DEF 80 PHY 73 CDM CAM R 5 ★ 4 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX59" t="inlineStr">
+      <c r="CY59" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY59" t="inlineStr">
+      <c r="CZ59" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ59" t="inlineStr">
+      <c r="DA59" t="inlineStr">
         <is>
           <t>Anticipate+</t>
         </is>
       </c>
-      <c r="DA59" t="inlineStr">
+      <c r="DB59" t="inlineStr">
         <is>
           <t>Anticipate+ Unlocked by completing the Three at the Back task in the Formation Excellence objective Mendy 87 LB PAC 91 SHO 70 PAS 80 DRI 81 DEF 84 PHY 90 LM L 4 ★ 5 LB 87.0 Mendy 87 LB PAC 91 SHO 70 PAS 80 DRI 81 DEF 84 PHY 90 LM L 4 ★ 5 LB 88.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 UPGRADES 2 in 7 months in 7 months 90% 10%</t>
         </is>
@@ -12255,27 +12318,28 @@
       <c r="CT60" t="inlineStr"/>
       <c r="CU60" t="inlineStr"/>
       <c r="CV60" t="inlineStr"/>
-      <c r="CW60" t="inlineStr">
+      <c r="CW60" t="inlineStr"/>
+      <c r="CX60" t="inlineStr">
         <is>
           <t>8 Level 1 Rodman 88 ST PAC 91 SHO 88 PAS 81 DRI 86 DEF 70 PHY 86 RM RW R 4 ★ 5 Rodman 88 ST PAC 91 SHO 88 PAS 81 DRI 86 DEF 70 PHY 86 RM RW R 4 ★ 5 UPGRADES 8</t>
         </is>
       </c>
-      <c r="CX60" t="inlineStr">
+      <c r="CY60" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 7 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY60" t="inlineStr">
+      <c r="CZ60" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 7 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ60" t="inlineStr">
+      <c r="DA60" t="inlineStr">
         <is>
           <t>Finesse Shot</t>
         </is>
       </c>
-      <c r="DA60" t="inlineStr">
+      <c r="DB60" t="inlineStr">
         <is>
           <t>Finesse Shot Unlocked by completing the 10 Finesse Shots task in the Lowe's Scoring Marathon objective Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 7 UPGRADES 8 in 5 days in 5 days 28% 72%</t>
         </is>
@@ -12414,27 +12478,28 @@
       <c r="CT61" t="inlineStr"/>
       <c r="CU61" t="inlineStr"/>
       <c r="CV61" t="inlineStr"/>
-      <c r="CW61" t="inlineStr">
+      <c r="CW61" t="inlineStr"/>
+      <c r="CX61" t="inlineStr">
         <is>
           <t>2 Level 1 Szoboszlai 90 CAM PAC 87 SHO 90 PAS 90 DRI 92 DEF 80 PHY 85 RB CM R 5 ★ 5 Szoboszlai 90 CAM PAC 87 SHO 90 PAS 90 DRI 92 DEF 80 PHY 85 RB CM R 5 ★ 5 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX61" t="inlineStr">
+      <c r="CY61" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY61" t="inlineStr">
+      <c r="CZ61" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ61" t="inlineStr">
+      <c r="DA61" t="inlineStr">
         <is>
           <t>Low Driven Shot+</t>
         </is>
       </c>
-      <c r="DA61" t="inlineStr">
+      <c r="DB61" t="inlineStr">
         <is>
           <t>Low Driven Shot+ Unlocked by completing the Low Driven Shot+ Milestone objective Ginola 90 LM PAC 91 SHO 90 PAS 88 DRI 92 DEF 56 PHY 86 CAM ST R 5 ★ 5 ST 87.6 Ginola 90 LM PAC 91 SHO 90 PAS 88 DRI 92 DEF 56 PHY 86 CAM ST R 5 ★ 5 ST 89.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 UPGRADES 2 in 7 months in 7 months 88% 12%</t>
         </is>
@@ -12573,27 +12638,28 @@
       <c r="CT62" t="inlineStr"/>
       <c r="CU62" t="inlineStr"/>
       <c r="CV62" t="inlineStr"/>
-      <c r="CW62" t="inlineStr">
+      <c r="CW62" t="inlineStr"/>
+      <c r="CX62" t="inlineStr">
         <is>
           <t>2 Level 1 Dumornay 90 ST PAC 96 SHO 90 PAS 85 DRI 90 DEF 66 PHY 80 CAM R 5 ★ 5 Dumornay 90 ST PAC 96 SHO 90 PAS 85 DRI 90 DEF 66 PHY 80 CAM R 5 ★ 5 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX62" t="inlineStr">
+      <c r="CY62" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY62" t="inlineStr">
+      <c r="CZ62" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ62" t="inlineStr">
+      <c r="DA62" t="inlineStr">
         <is>
           <t>Intercept+</t>
         </is>
       </c>
-      <c r="DA62" t="inlineStr">
+      <c r="DB62" t="inlineStr">
         <is>
           <t>Intercept+ Unlocked by completing the Intercept+ Milestone objective António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 86.6 António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 90.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 UPGRADES 2 in 7 months in 7 months 96% 4%</t>
         </is>
@@ -12732,27 +12798,28 @@
       <c r="CT63" t="inlineStr"/>
       <c r="CU63" t="inlineStr"/>
       <c r="CV63" t="inlineStr"/>
-      <c r="CW63" t="inlineStr">
+      <c r="CW63" t="inlineStr"/>
+      <c r="CX63" t="inlineStr">
         <is>
           <t>9 Level 1 Prinz 89 ST PAC 91 SHO 90 PAS 80 DRI 88 DEF 53 PHY 91 R 4 ★ 4 Prinz 89 ST PAC 91 SHO 90 PAS 80 DRI 88 DEF 53 PHY 91 R 4 ★ 4 UPGRADES 9</t>
         </is>
       </c>
-      <c r="CX63" t="inlineStr">
+      <c r="CY63" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 8 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY63" t="inlineStr">
+      <c r="CZ63" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 8 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ63" t="inlineStr">
+      <c r="DA63" t="inlineStr">
         <is>
           <t>Architect of Play [SP+ 4] 2</t>
         </is>
       </c>
-      <c r="DA63" t="inlineStr">
+      <c r="DB63" t="inlineStr">
         <is>
           <t>Architect of Play [SP+ 4] 2 Unlocked by reaching level 4 in the Premium Season Pass. Sergi Cardona 88 LB PAC 90 SHO 75 PAS 84 DRI 86 DEF 88 PHY 88 LM L 4 ★ 4 LB 89.2 Sergi Cardona 88 LB PAC 90 SHO 75 PAS 84 DRI 86 DEF 88 PHY 88 LM L 4 ★ 4 LB 91.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 8 UPGRADES 9 in 5 months 4 days ago 91% 9%</t>
         </is>
@@ -12891,27 +12958,28 @@
       <c r="CT64" t="inlineStr"/>
       <c r="CU64" t="inlineStr"/>
       <c r="CV64" t="inlineStr"/>
-      <c r="CW64" t="inlineStr">
+      <c r="CW64" t="inlineStr"/>
+      <c r="CX64" t="inlineStr">
         <is>
           <t>1 Level 1 UPGRADES 1</t>
         </is>
       </c>
-      <c r="CX64" t="inlineStr">
+      <c r="CY64" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY64" t="inlineStr">
+      <c r="CZ64" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ64" t="inlineStr">
+      <c r="DA64" t="inlineStr">
         <is>
           <t>Make Your Idol - Tiki Taka+ [SP 3]</t>
         </is>
       </c>
-      <c r="DA64" t="inlineStr">
+      <c r="DB64" t="inlineStr">
         <is>
           <t>Make Your Idol - Tiki Taka+ [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 UPGRADES 1 in 5 months 4 days ago 69% 31%</t>
         </is>
@@ -13050,27 +13118,28 @@
       <c r="CT65" t="inlineStr"/>
       <c r="CU65" t="inlineStr"/>
       <c r="CV65" t="inlineStr"/>
-      <c r="CW65" t="inlineStr">
+      <c r="CW65" t="inlineStr"/>
+      <c r="CX65" t="inlineStr">
         <is>
           <t>1 Level 1 UPGRADES 1</t>
         </is>
       </c>
-      <c r="CX65" t="inlineStr">
+      <c r="CY65" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY65" t="inlineStr">
+      <c r="CZ65" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ65" t="inlineStr">
+      <c r="DA65" t="inlineStr">
         <is>
           <t>Make Your Idol - Incisive Pass+ [SP 3]</t>
         </is>
       </c>
-      <c r="DA65" t="inlineStr">
+      <c r="DB65" t="inlineStr">
         <is>
           <t>Make Your Idol - Incisive Pass+ [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 UPGRADES 1 in 5 months 4 days ago 68% 32%</t>
         </is>
@@ -13209,27 +13278,28 @@
       <c r="CT66" t="inlineStr"/>
       <c r="CU66" t="inlineStr"/>
       <c r="CV66" t="inlineStr"/>
-      <c r="CW66" t="inlineStr">
+      <c r="CW66" t="inlineStr"/>
+      <c r="CX66" t="inlineStr">
         <is>
           <t>1 Level 1 UPGRADES 1</t>
         </is>
       </c>
-      <c r="CX66" t="inlineStr">
+      <c r="CY66" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY66" t="inlineStr">
+      <c r="CZ66" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ66" t="inlineStr">
+      <c r="DA66" t="inlineStr">
         <is>
           <t>Make Your Idol - Low Driven+ [SP 3]</t>
         </is>
       </c>
-      <c r="DA66" t="inlineStr">
+      <c r="DB66" t="inlineStr">
         <is>
           <t>Make Your Idol - Low Driven+ [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 UPGRADES 1 in 5 months 4 days ago 26% 74%</t>
         </is>
@@ -13368,27 +13438,28 @@
       <c r="CT67" t="inlineStr"/>
       <c r="CU67" t="inlineStr"/>
       <c r="CV67" t="inlineStr"/>
-      <c r="CW67" t="inlineStr">
+      <c r="CW67" t="inlineStr"/>
+      <c r="CX67" t="inlineStr">
         <is>
           <t>1 Level 1 UPGRADES 1</t>
         </is>
       </c>
-      <c r="CX67" t="inlineStr">
+      <c r="CY67" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY67" t="inlineStr">
+      <c r="CZ67" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ67" t="inlineStr">
+      <c r="DA67" t="inlineStr">
         <is>
           <t>Make Your Idol - Technical+ [SP 3]</t>
         </is>
       </c>
-      <c r="DA67" t="inlineStr">
+      <c r="DB67" t="inlineStr">
         <is>
           <t>Make Your Idol - Technical+ [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 UPGRADES 1 in 5 months 4 days ago 29% 71%</t>
         </is>
@@ -13527,27 +13598,28 @@
       <c r="CT68" t="inlineStr"/>
       <c r="CU68" t="inlineStr"/>
       <c r="CV68" t="inlineStr"/>
-      <c r="CW68" t="inlineStr">
+      <c r="CW68" t="inlineStr"/>
+      <c r="CX68" t="inlineStr">
         <is>
           <t>1 Level 1 UPGRADES 1</t>
         </is>
       </c>
-      <c r="CX68" t="inlineStr">
+      <c r="CY68" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY68" t="inlineStr">
+      <c r="CZ68" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ68" t="inlineStr">
+      <c r="DA68" t="inlineStr">
         <is>
           <t>Make Your Idol - Jockey+ [SP 3]</t>
         </is>
       </c>
-      <c r="DA68" t="inlineStr">
+      <c r="DB68" t="inlineStr">
         <is>
           <t>Make Your Idol - Jockey+ [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 UPGRADES 1 in 5 months 4 days ago 25% 75%</t>
         </is>
@@ -13686,27 +13758,28 @@
       <c r="CT69" t="inlineStr"/>
       <c r="CU69" t="inlineStr"/>
       <c r="CV69" t="inlineStr"/>
-      <c r="CW69" t="inlineStr">
+      <c r="CW69" t="inlineStr"/>
+      <c r="CX69" t="inlineStr">
         <is>
           <t>1 Level 1 UPGRADES 1</t>
         </is>
       </c>
-      <c r="CX69" t="inlineStr">
+      <c r="CY69" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY69" t="inlineStr">
+      <c r="CZ69" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ69" t="inlineStr">
+      <c r="DA69" t="inlineStr">
         <is>
           <t>Make Your Idol - Intercept+ [SP 3]</t>
         </is>
       </c>
-      <c r="DA69" t="inlineStr">
+      <c r="DB69" t="inlineStr">
         <is>
           <t>Make Your Idol - Intercept+ [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 UPGRADES 1 in 5 months 4 days ago 38% 62%</t>
         </is>
@@ -13845,27 +13918,28 @@
       <c r="CT70" t="inlineStr"/>
       <c r="CU70" t="inlineStr"/>
       <c r="CV70" t="inlineStr"/>
-      <c r="CW70" t="inlineStr">
+      <c r="CW70" t="inlineStr"/>
+      <c r="CX70" t="inlineStr">
         <is>
           <t>2 Level 1 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX70" t="inlineStr">
+      <c r="CY70" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY70" t="inlineStr">
+      <c r="CZ70" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ70" t="inlineStr">
+      <c r="DA70" t="inlineStr">
         <is>
           <t>Make Your Idol - Finesse Shot+ [SP 7]</t>
         </is>
       </c>
-      <c r="DA70" t="inlineStr">
+      <c r="DB70" t="inlineStr">
         <is>
           <t>Make Your Idol - Finesse Shot+ [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 UPGRADES 2 in 5 months 4 days ago 44% 56%</t>
         </is>
@@ -14004,27 +14078,28 @@
       <c r="CT71" t="inlineStr"/>
       <c r="CU71" t="inlineStr"/>
       <c r="CV71" t="inlineStr"/>
-      <c r="CW71" t="inlineStr">
+      <c r="CW71" t="inlineStr"/>
+      <c r="CX71" t="inlineStr">
         <is>
           <t>2 Level 1 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX71" t="inlineStr">
+      <c r="CY71" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY71" t="inlineStr">
+      <c r="CZ71" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ71" t="inlineStr">
+      <c r="DA71" t="inlineStr">
         <is>
           <t>Make Your Idol - First Touch+ [SP 7]</t>
         </is>
       </c>
-      <c r="DA71" t="inlineStr">
+      <c r="DB71" t="inlineStr">
         <is>
           <t>Make Your Idol - First Touch+ [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 UPGRADES 2 in 5 months 4 days ago 28% 72%</t>
         </is>
@@ -14163,27 +14238,28 @@
       <c r="CT72" t="inlineStr"/>
       <c r="CU72" t="inlineStr"/>
       <c r="CV72" t="inlineStr"/>
-      <c r="CW72" t="inlineStr">
+      <c r="CW72" t="inlineStr"/>
+      <c r="CX72" t="inlineStr">
         <is>
           <t>2 Level 1 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX72" t="inlineStr">
+      <c r="CY72" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY72" t="inlineStr">
+      <c r="CZ72" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ72" t="inlineStr">
+      <c r="DA72" t="inlineStr">
         <is>
           <t>Make Your Idol - Pinged Pass+ [SP 7]</t>
         </is>
       </c>
-      <c r="DA72" t="inlineStr">
+      <c r="DB72" t="inlineStr">
         <is>
           <t>Make Your Idol - Pinged Pass+ [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 UPGRADES 2 in 5 months 4 days ago 33% 67%</t>
         </is>
@@ -14322,27 +14398,28 @@
       <c r="CT73" t="inlineStr"/>
       <c r="CU73" t="inlineStr"/>
       <c r="CV73" t="inlineStr"/>
-      <c r="CW73" t="inlineStr">
+      <c r="CW73" t="inlineStr"/>
+      <c r="CX73" t="inlineStr">
         <is>
           <t>2 Level 1 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX73" t="inlineStr">
+      <c r="CY73" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY73" t="inlineStr">
+      <c r="CZ73" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ73" t="inlineStr">
+      <c r="DA73" t="inlineStr">
         <is>
           <t>Make Your Idol - Rapid+ [SP 7]</t>
         </is>
       </c>
-      <c r="DA73" t="inlineStr">
+      <c r="DB73" t="inlineStr">
         <is>
           <t>Make Your Idol - Rapid+ [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 UPGRADES 2 in 5 months 4 days ago 37% 63%</t>
         </is>
@@ -14481,27 +14558,28 @@
       <c r="CT74" t="inlineStr"/>
       <c r="CU74" t="inlineStr"/>
       <c r="CV74" t="inlineStr"/>
-      <c r="CW74" t="inlineStr">
+      <c r="CW74" t="inlineStr"/>
+      <c r="CX74" t="inlineStr">
         <is>
           <t>2 Level 1 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX74" t="inlineStr">
+      <c r="CY74" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY74" t="inlineStr">
+      <c r="CZ74" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ74" t="inlineStr">
+      <c r="DA74" t="inlineStr">
         <is>
           <t>Make Your Idol - Quick Step+ [SP 7]</t>
         </is>
       </c>
-      <c r="DA74" t="inlineStr">
+      <c r="DB74" t="inlineStr">
         <is>
           <t>Make Your Idol - Quick Step+ [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 UPGRADES 2 in 5 months 4 days ago 37% 63%</t>
         </is>
@@ -14640,27 +14718,28 @@
       <c r="CT75" t="inlineStr"/>
       <c r="CU75" t="inlineStr"/>
       <c r="CV75" t="inlineStr"/>
-      <c r="CW75" t="inlineStr">
+      <c r="CW75" t="inlineStr"/>
+      <c r="CX75" t="inlineStr">
         <is>
           <t>2 Level 1 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX75" t="inlineStr">
+      <c r="CY75" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY75" t="inlineStr">
+      <c r="CZ75" t="inlineStr">
         <is>
           <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ75" t="inlineStr">
+      <c r="DA75" t="inlineStr">
         <is>
           <t>Make Your Idol - Anticipate+ [SP 7]</t>
         </is>
       </c>
-      <c r="DA75" t="inlineStr">
+      <c r="DB75" t="inlineStr">
         <is>
           <t>Make Your Idol - Anticipate+ [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 UPGRADES 2 in 5 months 4 days ago 35% 65%</t>
         </is>
@@ -14799,27 +14878,28 @@
       <c r="CT76" t="inlineStr"/>
       <c r="CU76" t="inlineStr"/>
       <c r="CV76" t="inlineStr"/>
-      <c r="CW76" t="inlineStr">
+      <c r="CW76" t="inlineStr"/>
+      <c r="CX76" t="inlineStr">
         <is>
           <t>9 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES 9</t>
         </is>
       </c>
-      <c r="CX76" t="inlineStr">
+      <c r="CY76" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 8 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY76" t="inlineStr">
+      <c r="CZ76" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 8 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ76" t="inlineStr">
+      <c r="DA76" t="inlineStr">
         <is>
           <t>Guardian of the Line [SP+ 10] 2</t>
         </is>
       </c>
-      <c r="DA76" t="inlineStr">
+      <c r="DB76" t="inlineStr">
         <is>
           <t>Guardian of the Line [SP+ 10] 2 Unlocked by reaching level 10 in the Premium Season Pass. Dorgu 89 LM PAC 94 SHO 82 PAS 86 DRI 89 DEF 86 PHY 88 LB LW L 3 ★ 4 LB 88.8 Dorgu 89 LM PAC 94 SHO 82 PAS 86 DRI 89 DEF 86 PHY 88 LB LW L 3 ★ 4 LB 90.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 8 UPGRADES 9 in 5 months 4 days ago 89% 11%</t>
         </is>
@@ -14889,23 +14969,23 @@
         <v>4</v>
       </c>
       <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="n">
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="n">
         <v>4</v>
       </c>
-      <c r="AA77" t="n">
+      <c r="AB77" t="n">
         <v>91</v>
       </c>
-      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr"/>
-      <c r="AF77" t="n">
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="n">
         <v>4</v>
       </c>
-      <c r="AG77" t="n">
+      <c r="AH77" t="n">
         <v>91</v>
       </c>
-      <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="inlineStr"/>
       <c r="AJ77" t="inlineStr"/>
       <c r="AK77" t="inlineStr"/>
@@ -14913,59 +14993,59 @@
       <c r="AM77" t="inlineStr"/>
       <c r="AN77" t="inlineStr"/>
       <c r="AO77" t="inlineStr"/>
-      <c r="AP77" t="n">
+      <c r="AP77" t="inlineStr"/>
+      <c r="AQ77" t="n">
         <v>16</v>
       </c>
-      <c r="AQ77" t="n">
+      <c r="AR77" t="n">
         <v>92</v>
       </c>
-      <c r="AR77" t="n">
+      <c r="AS77" t="n">
         <v>8</v>
       </c>
-      <c r="AS77" t="n">
+      <c r="AT77" t="n">
         <v>92</v>
       </c>
-      <c r="AT77" t="n">
+      <c r="AU77" t="n">
         <v>8</v>
       </c>
-      <c r="AU77" t="n">
+      <c r="AV77" t="n">
         <v>92</v>
       </c>
-      <c r="AV77" t="inlineStr"/>
       <c r="AW77" t="inlineStr"/>
-      <c r="AX77" t="n">
+      <c r="AX77" t="inlineStr"/>
+      <c r="AY77" t="n">
         <v>16</v>
       </c>
-      <c r="AY77" t="n">
+      <c r="AZ77" t="n">
         <v>91</v>
       </c>
-      <c r="AZ77" t="inlineStr"/>
       <c r="BA77" t="inlineStr"/>
-      <c r="BB77" t="n">
+      <c r="BB77" t="inlineStr"/>
+      <c r="BC77" t="n">
         <v>4</v>
       </c>
-      <c r="BC77" t="n">
+      <c r="BD77" t="n">
         <v>91</v>
       </c>
-      <c r="BD77" t="inlineStr"/>
       <c r="BE77" t="inlineStr"/>
       <c r="BF77" t="inlineStr"/>
       <c r="BG77" t="inlineStr"/>
-      <c r="BH77" t="n">
+      <c r="BH77" t="inlineStr"/>
+      <c r="BI77" t="n">
         <v>4</v>
       </c>
-      <c r="BI77" t="n">
+      <c r="BJ77" t="n">
         <v>92</v>
       </c>
-      <c r="BJ77" t="inlineStr"/>
       <c r="BK77" t="inlineStr"/>
-      <c r="BL77" t="n">
+      <c r="BL77" t="inlineStr"/>
+      <c r="BM77" t="n">
         <v>8</v>
       </c>
-      <c r="BM77" t="n">
+      <c r="BN77" t="n">
         <v>92</v>
       </c>
-      <c r="BN77" t="inlineStr"/>
       <c r="BO77" t="inlineStr"/>
       <c r="BP77" t="inlineStr"/>
       <c r="BQ77" t="inlineStr"/>
@@ -15000,27 +15080,28 @@
       <c r="CT77" t="inlineStr"/>
       <c r="CU77" t="inlineStr"/>
       <c r="CV77" t="inlineStr"/>
-      <c r="CW77" t="inlineStr">
+      <c r="CW77" t="inlineStr"/>
+      <c r="CX77" t="inlineStr">
         <is>
           <t>+2 OVR +4 PAC 91 +4 DRI 91 +8 Positioning 92 +8 Volleys 91 +4 Curve 92 +8 Shot Power 92 +4 Vision 91 +8 Finishing 92 +4 Short Pass 92 2 9 Level 1 Amaiur Sarriegi 89 ST PAC 94 SHO 88 PAS 86 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 Amaiur Sarriegi 91 ST PAC 94 SHO 89 PAS 86 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 UPGRADES +2 OVR +8 Positioning 92 +8 Volleys 91 +4 Curve 92 9</t>
         </is>
       </c>
-      <c r="CX77" t="inlineStr">
+      <c r="CY77" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY77" t="inlineStr">
+      <c r="CZ77" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ77" t="inlineStr">
+      <c r="DA77" t="inlineStr">
         <is>
           <t>Up to Speed [SP+ 26]</t>
         </is>
       </c>
-      <c r="DA77" t="inlineStr">
+      <c r="DB77" t="inlineStr">
         <is>
           <t>Up to Speed [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Hall 89 LB PAC 88 SHO 82 PAS 88 DRI 89 DEF 89 PHY 86 L 4 ★ 4 LB 88.5 Hall 91 LB PAC 91 SHO 87 PAS 91 DRI 91 DEF 89 PHY 86 L 4 ★ 4 LB 91.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES +2 OVR +4 PAC 91 +4 DRI 91 +8 Positioning 92 +8 Volleys 91 +4 Curve 92 +8 Shot Power 92 +4 Vision 91 +8 Finishing 92 +4 Short Pass 92 2 9 in 5 months 4 days ago 85% 15%</t>
         </is>
@@ -15151,27 +15232,28 @@
       <c r="CT78" t="inlineStr"/>
       <c r="CU78" t="inlineStr"/>
       <c r="CV78" t="inlineStr"/>
-      <c r="CW78" t="inlineStr">
+      <c r="CW78" t="inlineStr"/>
+      <c r="CX78" t="inlineStr">
         <is>
           <t>No upgrades Level 1 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 UPGRADES No upgrades</t>
         </is>
       </c>
-      <c r="CX78" t="inlineStr">
+      <c r="CY78" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY78" t="inlineStr">
+      <c r="CZ78" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ78" t="inlineStr">
+      <c r="DA78" t="inlineStr">
         <is>
           <t>Fantasy Captain ICON [SP 27]</t>
         </is>
       </c>
-      <c r="DA78" t="inlineStr">
+      <c r="DB78" t="inlineStr">
         <is>
           <t>Fantasy Captain ICON [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Jacobo Ramón 94 CB PAC 88 SHO 46 PAS 84 DRI 81 DEF 94 PHY 91 R 3 ★ 4 CB 93.8 Jacobo Ramón 94 CB PAC 88 SHO 46 PAS 84 DRI 81 DEF 94 PHY 91 R 3 ★ 4 CB 93.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 5 months 4 days ago 96% 4%</t>
         </is>
@@ -15302,27 +15384,28 @@
       <c r="CT79" t="inlineStr"/>
       <c r="CU79" t="inlineStr"/>
       <c r="CV79" t="inlineStr"/>
-      <c r="CW79" t="inlineStr">
+      <c r="CW79" t="inlineStr"/>
+      <c r="CX79" t="inlineStr">
         <is>
           <t>No upgrades Level 1 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 UPGRADES No upgrades</t>
         </is>
       </c>
-      <c r="CX79" t="inlineStr">
+      <c r="CY79" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY79" t="inlineStr">
+      <c r="CZ79" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ79" t="inlineStr">
+      <c r="DA79" t="inlineStr">
         <is>
           <t>Season Ladder Excellence [SP 15]</t>
         </is>
       </c>
-      <c r="DA79" t="inlineStr">
+      <c r="DB79" t="inlineStr">
         <is>
           <t>Season Ladder Excellence [SP 15] Unlocked by reaching level 15 in the Standard Season Pass. Jacobo Ramón 94 CB PAC 88 SHO 46 PAS 84 DRI 81 DEF 94 PHY 91 R 3 ★ 4 CB 93.8 Jacobo Ramón 94 CB PAC 88 SHO 46 PAS 84 DRI 81 DEF 94 PHY 91 R 3 ★ 4 CB 93.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 5 months 4 days ago 39% 61%</t>
         </is>
@@ -15461,27 +15544,28 @@
       <c r="CT80" t="inlineStr"/>
       <c r="CU80" t="inlineStr"/>
       <c r="CV80" t="inlineStr"/>
-      <c r="CW80" t="inlineStr">
+      <c r="CW80" t="inlineStr"/>
+      <c r="CX80" t="inlineStr">
         <is>
           <t>3 Level 1 Dumornay 90 ST PAC 96 SHO 90 PAS 85 DRI 90 DEF 66 PHY 80 CAM R 5 ★ 5 Dumornay 90 ST PAC 96 SHO 90 PAS 85 DRI 90 DEF 66 PHY 80 CAM R 5 ★ 5 UPGRADES 3</t>
         </is>
       </c>
-      <c r="CX80" t="inlineStr">
+      <c r="CY80" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY80" t="inlineStr">
+      <c r="CZ80" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ80" t="inlineStr">
+      <c r="DA80" t="inlineStr">
         <is>
           <t>Pinged Pass+ [SP+ 28]</t>
         </is>
       </c>
-      <c r="DA80" t="inlineStr">
+      <c r="DB80" t="inlineStr">
         <is>
           <t>Pinged Pass+ [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Messi 90 ST PAC 90 SHO 90 PAS 90 DRI 94 DEF 37 PHY 71 RM CAM RW L 4 ★ 5 CAM 90.3 Messi 90 ST PAC 90 SHO 90 PAS 90 DRI 94 DEF 37 PHY 71 RM CAM RW L 4 ★ 5 CAM 91.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 UPGRADES 3 in 5 months 4 days ago 95% 5%</t>
         </is>
@@ -15620,27 +15704,28 @@
       <c r="CT81" t="inlineStr"/>
       <c r="CU81" t="inlineStr"/>
       <c r="CV81" t="inlineStr"/>
-      <c r="CW81" t="inlineStr">
+      <c r="CW81" t="inlineStr"/>
+      <c r="CX81" t="inlineStr">
         <is>
           <t>3 Level 1 Francisco Conceição 89 RM PAC 93 SHO 86 PAS 87 DRI 91 DEF 45 PHY 70 CAM RW L 4 ★ 3 Francisco Conceição 89 RM PAC 93 SHO 86 PAS 87 DRI 91 DEF 45 PHY 70 CAM RW L 4 ★ 3 UPGRADES 3</t>
         </is>
       </c>
-      <c r="CX81" t="inlineStr">
+      <c r="CY81" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY81" t="inlineStr">
+      <c r="CZ81" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ81" t="inlineStr">
+      <c r="DA81" t="inlineStr">
         <is>
           <t>Relentless+ [SP+ 27]</t>
         </is>
       </c>
-      <c r="DA81" t="inlineStr">
+      <c r="DB81" t="inlineStr">
         <is>
           <t>Relentless+ [SP+ 27] Unlocked by reaching level 27 in the Premium Season Pass. Spinazzola 89 LB PAC 93 SHO 76 PAS 87 DRI 89 DEF 88 PHY 84 LM R 4 ★ 4 LB 89.7 Spinazzola 89 LB PAC 93 SHO 76 PAS 87 DRI 89 DEF 88 PHY 84 LM R 4 ★ 4 LB 90.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 5 months 4 days ago 14% 86%</t>
         </is>
@@ -15734,31 +15819,31 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="inlineStr"/>
-      <c r="BB82" t="n">
+      <c r="BB82" t="inlineStr"/>
+      <c r="BC82" t="n">
         <v>20</v>
       </c>
-      <c r="BC82" t="n">
+      <c r="BD82" t="n">
         <v>92</v>
       </c>
-      <c r="BD82" t="inlineStr"/>
       <c r="BE82" t="inlineStr"/>
       <c r="BF82" t="inlineStr"/>
       <c r="BG82" t="inlineStr"/>
       <c r="BH82" t="inlineStr"/>
       <c r="BI82" t="inlineStr"/>
-      <c r="BJ82" t="n">
+      <c r="BJ82" t="inlineStr"/>
+      <c r="BK82" t="n">
         <v>20</v>
       </c>
-      <c r="BK82" t="n">
+      <c r="BL82" t="n">
         <v>92</v>
       </c>
-      <c r="BL82" t="n">
+      <c r="BM82" t="n">
         <v>20</v>
       </c>
-      <c r="BM82" t="n">
+      <c r="BN82" t="n">
         <v>92</v>
       </c>
-      <c r="BN82" t="inlineStr"/>
       <c r="BO82" t="inlineStr"/>
       <c r="BP82" t="inlineStr"/>
       <c r="BQ82" t="inlineStr"/>
@@ -15768,23 +15853,23 @@
       <c r="BU82" t="inlineStr"/>
       <c r="BV82" t="inlineStr"/>
       <c r="BW82" t="inlineStr"/>
-      <c r="BX82" t="n">
+      <c r="BX82" t="inlineStr"/>
+      <c r="BY82" t="n">
         <v>20</v>
       </c>
-      <c r="BY82" t="n">
+      <c r="BZ82" t="n">
         <v>91</v>
       </c>
-      <c r="BZ82" t="inlineStr"/>
       <c r="CA82" t="inlineStr"/>
       <c r="CB82" t="inlineStr"/>
       <c r="CC82" t="inlineStr"/>
-      <c r="CD82" t="n">
+      <c r="CD82" t="inlineStr"/>
+      <c r="CE82" t="n">
         <v>20</v>
       </c>
-      <c r="CE82" t="n">
+      <c r="CF82" t="n">
         <v>91</v>
       </c>
-      <c r="CF82" t="inlineStr"/>
       <c r="CG82" t="inlineStr"/>
       <c r="CH82" t="inlineStr"/>
       <c r="CI82" t="inlineStr"/>
@@ -15801,27 +15886,28 @@
       <c r="CT82" t="inlineStr"/>
       <c r="CU82" t="inlineStr"/>
       <c r="CV82" t="inlineStr"/>
-      <c r="CW82" t="inlineStr">
+      <c r="CW82" t="inlineStr"/>
+      <c r="CX82" t="inlineStr">
         <is>
           <t>+1 OVR +10 Vision 92 +10 Long Pass 92 +10 Curve 92 +10 Composure 91 +10 Defensive Awareness 91 9 Level 1 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 Kerolin Nicoli 90 RM PAC 91 SHO 86 PAS 88 DRI 90 DEF 55 PHY 86 RW ST R 5 ★ 5 UPGRADES +1 OVR +10 Vision 92 +10 Long Pass 92 +10 Curve 92 +10 Composure 91 +10 Defensive Awareness 91 9</t>
         </is>
       </c>
-      <c r="CX82" t="inlineStr">
+      <c r="CY82" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY82" t="inlineStr">
+      <c r="CZ82" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ82" t="inlineStr">
+      <c r="DA82" t="inlineStr">
         <is>
           <t>Dish 'em Out [SP+ 1]</t>
         </is>
       </c>
-      <c r="DA82" t="inlineStr">
+      <c r="DB82" t="inlineStr">
         <is>
           <t>Dish 'em Out [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Hernández 88 LB PAC 92 SHO 81 PAS 82 DRI 87 DEF 83 PHY 86 LM L 4 ★ 3 LB 89.3 Hernández 89 LB PAC 92 SHO 81 PAS 86 DRI 87 DEF 86 PHY 86 LM L 4 ★ 3 LB 91.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +1 OVR +10 Vision 92 +10 Long Pass 92 +10 Curve 92 +10 Composure 91 +10 Defensive Awareness 91 9 in 5 months 4 days ago 92% 8%</t>
         </is>
@@ -15895,19 +15981,19 @@
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
-      <c r="AH83" t="n">
+      <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="n">
         <v>4</v>
       </c>
-      <c r="AI83" t="n">
+      <c r="AJ83" t="n">
         <v>90</v>
       </c>
-      <c r="AJ83" t="n">
+      <c r="AK83" t="n">
         <v>4</v>
       </c>
-      <c r="AK83" t="n">
+      <c r="AL83" t="n">
         <v>91</v>
       </c>
-      <c r="AL83" t="inlineStr"/>
       <c r="AM83" t="inlineStr"/>
       <c r="AN83" t="inlineStr"/>
       <c r="AO83" t="inlineStr"/>
@@ -15923,55 +16009,55 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr"/>
       <c r="BA83" t="inlineStr"/>
-      <c r="BB83" t="n">
+      <c r="BB83" t="inlineStr"/>
+      <c r="BC83" t="n">
         <v>12</v>
       </c>
-      <c r="BC83" t="n">
+      <c r="BD83" t="n">
         <v>92</v>
       </c>
-      <c r="BD83" t="inlineStr"/>
       <c r="BE83" t="inlineStr"/>
       <c r="BF83" t="inlineStr"/>
       <c r="BG83" t="inlineStr"/>
-      <c r="BH83" t="n">
+      <c r="BH83" t="inlineStr"/>
+      <c r="BI83" t="n">
         <v>12</v>
       </c>
-      <c r="BI83" t="n">
+      <c r="BJ83" t="n">
         <v>92</v>
       </c>
-      <c r="BJ83" t="inlineStr"/>
       <c r="BK83" t="inlineStr"/>
-      <c r="BL83" t="n">
+      <c r="BL83" t="inlineStr"/>
+      <c r="BM83" t="n">
         <v>12</v>
       </c>
-      <c r="BM83" t="n">
+      <c r="BN83" t="n">
         <v>89</v>
       </c>
-      <c r="BN83" t="inlineStr"/>
       <c r="BO83" t="inlineStr"/>
       <c r="BP83" t="inlineStr"/>
       <c r="BQ83" t="inlineStr"/>
-      <c r="BR83" t="n">
+      <c r="BR83" t="inlineStr"/>
+      <c r="BS83" t="n">
         <v>12</v>
       </c>
-      <c r="BS83" t="n">
+      <c r="BT83" t="n">
         <v>90</v>
       </c>
-      <c r="BT83" t="n">
+      <c r="BU83" t="n">
         <v>12</v>
       </c>
-      <c r="BU83" t="n">
+      <c r="BV83" t="n">
         <v>90</v>
       </c>
-      <c r="BV83" t="inlineStr"/>
       <c r="BW83" t="inlineStr"/>
-      <c r="BX83" t="n">
+      <c r="BX83" t="inlineStr"/>
+      <c r="BY83" t="n">
         <v>6</v>
       </c>
-      <c r="BY83" t="n">
+      <c r="BZ83" t="n">
         <v>90</v>
       </c>
-      <c r="BZ83" t="inlineStr"/>
       <c r="CA83" t="inlineStr"/>
       <c r="CB83" t="inlineStr"/>
       <c r="CC83" t="inlineStr"/>
@@ -15994,27 +16080,28 @@
       <c r="CT83" t="inlineStr"/>
       <c r="CU83" t="inlineStr"/>
       <c r="CV83" t="inlineStr"/>
-      <c r="CW83" t="inlineStr">
+      <c r="CW83" t="inlineStr"/>
+      <c r="CX83" t="inlineStr">
         <is>
           <t>+2 OVR +4 DEF 90 +4 PHY 91 +6 Vision 92 +6 Short Pass 92 +6 Curve 89 +6 Reactions 90 +6 Ball Control 90 +6 Composure 90 9 Level 1 Claudia Pina 88 LW PAC 85 SHO 89 PAS 87 DRI 90 DEF 48 PHY 74 LM ST R 5 ★ 5 Claudia Pina 90 LW PAC 85 SHO 89 PAS 89 DRI 90 DEF 48 PHY 74 LM ST R 5 ★ 5 UPGRADES +2 OVR +6 Vision 92 +6 Short Pass 92 +6 Curve 89 +6 Reactions 90 +6 Ball Control 90</t>
         </is>
       </c>
-      <c r="CX83" t="inlineStr">
+      <c r="CY83" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY83" t="inlineStr">
+      <c r="CZ83" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ83" t="inlineStr">
+      <c r="DA83" t="inlineStr">
         <is>
           <t>Locked &amp; Loaded [SP 25]</t>
         </is>
       </c>
-      <c r="DA83" t="inlineStr">
+      <c r="DB83" t="inlineStr">
         <is>
           <t>Locked &amp; Loaded [SP 25] Unlocked by reaching level 25 in the Standard Season Pass. O'Reilly 87 LB PAC 89 SHO 82 PAS 86 DRI 87 DEF 85 PHY 85 CM CAM L 3 ★ 3 LB 87.2 O'Reilly 89 LB PAC 89 SHO 82 PAS 88 DRI 88 DEF 89 PHY 89 CM CAM L 3 ★ 3 LB 90.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 UPGRADES +2 OVR +4 DEF 90 +4 PHY 91 +6 Vision 92 +6 Short Pass 92 +6 Curve 89 +6 Reactions 90 +6 Ball Control 90 +6 Composure 90 9 in 5 months 4 days ago 91% 9%</t>
         </is>
@@ -16090,27 +16177,27 @@
       <c r="AM84" t="inlineStr"/>
       <c r="AN84" t="inlineStr"/>
       <c r="AO84" t="inlineStr"/>
-      <c r="AP84" t="n">
+      <c r="AP84" t="inlineStr"/>
+      <c r="AQ84" t="n">
         <v>4</v>
       </c>
-      <c r="AQ84" t="n">
+      <c r="AR84" t="n">
         <v>90</v>
       </c>
-      <c r="AR84" t="n">
+      <c r="AS84" t="n">
         <v>4</v>
       </c>
-      <c r="AS84" t="n">
+      <c r="AT84" t="n">
         <v>90</v>
       </c>
-      <c r="AT84" t="inlineStr"/>
       <c r="AU84" t="inlineStr"/>
-      <c r="AV84" t="n">
+      <c r="AV84" t="inlineStr"/>
+      <c r="AW84" t="n">
         <v>4</v>
       </c>
-      <c r="AW84" t="n">
+      <c r="AX84" t="n">
         <v>90</v>
       </c>
-      <c r="AX84" t="inlineStr"/>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr"/>
       <c r="BA84" t="inlineStr"/>
@@ -16161,27 +16248,28 @@
       <c r="CT84" t="inlineStr"/>
       <c r="CU84" t="inlineStr"/>
       <c r="CV84" t="inlineStr"/>
-      <c r="CW84" t="inlineStr">
+      <c r="CW84" t="inlineStr"/>
+      <c r="CX84" t="inlineStr">
         <is>
           <t>+2 Positioning 90 +2 Finishing 90 +2 Long Shots 90 Level 1 Ona Batlle 88 RB PAC 88 SHO 60 PAS 84 DRI 83 DEF 83 PHY 78 LB RM R 3 ★ 4 Ona Batlle 88 RB PAC 88 SHO 62 PAS 84 DRI 83 DEF 83 PHY 78 LB RM R 3 ★ 4 UPGRADES +2 Positioning 90 +2 Finishing 90 +2 Long Shots 90</t>
         </is>
       </c>
-      <c r="CX84" t="inlineStr">
+      <c r="CY84" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY84" t="inlineStr">
+      <c r="CZ84" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ84" t="inlineStr">
+      <c r="DA84" t="inlineStr">
         <is>
           <t>Goal Machine [SP 8] 5</t>
         </is>
       </c>
-      <c r="DA84" t="inlineStr">
+      <c r="DB84" t="inlineStr">
         <is>
           <t>Goal Machine [SP 8] 5 Unlocked by reaching level 8 in the Standard Season Pass. Pedrinho 88 RM PAC 93 SHO 85 PAS 87 DRI 91 DEF 60 PHY 75 LM CAM RW L 5 ★ 4 LM 90.9 Pedrinho 88 RM PAC 93 SHO 87 PAS 87 DRI 91 DEF 60 PHY 75 LM CAM RW L 5 ★ 4 LM 91.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 UPGRADES +2 Positioning 90 +2 Finishing 90 +2 Long Shots 90 in 5 months 4 days ago 92% 8%</t>
         </is>
@@ -16247,23 +16335,23 @@
         <v>4</v>
       </c>
       <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="n">
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="n">
         <v>14</v>
       </c>
-      <c r="AA85" t="n">
+      <c r="AB85" t="n">
         <v>90</v>
       </c>
-      <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="inlineStr"/>
       <c r="AD85" t="inlineStr"/>
       <c r="AE85" t="inlineStr"/>
-      <c r="AF85" t="n">
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="n">
         <v>14</v>
       </c>
-      <c r="AG85" t="n">
+      <c r="AH85" t="n">
         <v>91</v>
       </c>
-      <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="inlineStr"/>
       <c r="AJ85" t="inlineStr"/>
       <c r="AK85" t="inlineStr"/>
@@ -16330,27 +16418,28 @@
       <c r="CT85" t="inlineStr"/>
       <c r="CU85" t="inlineStr"/>
       <c r="CV85" t="inlineStr"/>
-      <c r="CW85" t="inlineStr">
+      <c r="CW85" t="inlineStr"/>
+      <c r="CX85" t="inlineStr">
         <is>
           <t>+2 OVR +7 PAC 90 +7 DRI 91 9 Level 1 Amaiur Sarriegi 89 ST PAC 94 SHO 88 PAS 86 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 Amaiur Sarriegi 91 ST PAC 94 SHO 88 PAS 86 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 UPGRADES +2 OVR +7 PAC 90 +7 DRI 91 9</t>
         </is>
       </c>
-      <c r="CX85" t="inlineStr">
+      <c r="CY85" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY85" t="inlineStr">
+      <c r="CZ85" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ85" t="inlineStr">
+      <c r="DA85" t="inlineStr">
         <is>
           <t>Roadrunner [SP+ 24]</t>
         </is>
       </c>
-      <c r="DA85" t="inlineStr">
+      <c r="DB85" t="inlineStr">
         <is>
           <t>Roadrunner [SP+ 24] Unlocked by reaching level 24 in the Premium Season Pass. Bardakcı 88 CB PAC 85 SHO 53 PAS 85 DRI 76 DEF 88 PHY 92 LB LM L 4 ★ 5 LB 88.3 Bardakcı 90 CB PAC 90 SHO 53 PAS 85 DRI 84 DEF 88 PHY 92 LB LM L 4 ★ 5 LB 91.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +2 OVR +7 PAC 90 +7 DRI 91 9 in 5 months 4 days ago 84% 16%</t>
         </is>
@@ -16420,21 +16509,21 @@
       <c r="AA86" t="inlineStr"/>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr"/>
-      <c r="AD86" t="n">
+      <c r="AD86" t="inlineStr"/>
+      <c r="AE86" t="n">
         <v>14</v>
       </c>
-      <c r="AE86" t="n">
+      <c r="AF86" t="n">
         <v>91</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="inlineStr"/>
-      <c r="AH86" t="n">
+      <c r="AH86" t="inlineStr"/>
+      <c r="AI86" t="n">
         <v>14</v>
       </c>
-      <c r="AI86" t="n">
+      <c r="AJ86" t="n">
         <v>91</v>
       </c>
-      <c r="AJ86" t="inlineStr"/>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
       <c r="AM86" t="inlineStr"/>
@@ -16499,27 +16588,28 @@
       <c r="CT86" t="inlineStr"/>
       <c r="CU86" t="inlineStr"/>
       <c r="CV86" t="inlineStr"/>
-      <c r="CW86" t="inlineStr">
+      <c r="CW86" t="inlineStr"/>
+      <c r="CX86" t="inlineStr">
         <is>
           <t>+2 OVR +7 PAS 91 +7 DEF 91 9 Level 1 James 89 ST PAC 91 SHO 86 PAS 82 DRI 91 DEF 44 PHY 86 CAM R 4 ★ 5 James 91 ST PAC 91 SHO 86 PAS 90 DRI 91 DEF 51 PHY 86 CAM R 4 ★ 5 UPGRADES +2 OVR +7 PAS 91 +7 DEF 91 9</t>
         </is>
       </c>
-      <c r="CX86" t="inlineStr">
+      <c r="CY86" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY86" t="inlineStr">
+      <c r="CZ86" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ86" t="inlineStr">
+      <c r="DA86" t="inlineStr">
         <is>
           <t>Sweep &amp; Supply [SP+ 18]</t>
         </is>
       </c>
-      <c r="DA86" t="inlineStr">
+      <c r="DB86" t="inlineStr">
         <is>
           <t>Sweep &amp; Supply [SP+ 18] Unlocked by reaching level 18 in the Premium Season Pass. Timber 88 RB PAC 87 SHO 54 PAS 83 DRI 86 DEF 88 PHY 88 CB LB RM R 4 ★ 5 LB 88.6 Timber 90 RB PAC 87 SHO 54 PAS 90 DRI 86 DEF 91 PHY 88 CB LB RM R 4 ★ 5 LB 91.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +2 OVR +7 PAS 91 +7 DEF 91 9 in 5 months 4 days ago 86% 14%</t>
         </is>
@@ -16658,27 +16748,28 @@
       <c r="CT87" t="inlineStr"/>
       <c r="CU87" t="inlineStr"/>
       <c r="CV87" t="inlineStr"/>
-      <c r="CW87" t="inlineStr">
+      <c r="CW87" t="inlineStr"/>
+      <c r="CX87" t="inlineStr">
         <is>
           <t>2 Level 1 Karchaoui 90 CM PAC 92 SHO 82 PAS 90 DRI 91 DEF 85 PHY 74 LB CAM LW L 5 ★ 4 Karchaoui 90 CM PAC 92 SHO 82 PAS 90 DRI 91 DEF 85 PHY 74 LB CAM LW L 5 ★ 4 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX87" t="inlineStr">
+      <c r="CY87" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 Details Submit by in 8 months Expiry in 8 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY87" t="inlineStr">
+      <c r="CZ87" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 Details Submit by in 8 months Expiry in 8 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ87" t="inlineStr">
+      <c r="DA87" t="inlineStr">
         <is>
           <t>Quick Step+</t>
         </is>
       </c>
-      <c r="DA87" t="inlineStr">
+      <c r="DB87" t="inlineStr">
         <is>
           <t>Quick Step+ Unlocked by completing the Quick Step+ Milestone objective Henrichs 88 RB PAC 90 SHO 75 PAS 85 DRI 86 DEF 88 PHY 84 LB RM R 3 ★ 5 LB 87.0 Henrichs 88 RB PAC 90 SHO 75 PAS 85 DRI 86 DEF 88 PHY 84 LB RM R 3 ★ 5 LB 89.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 UPGRADES 2 in 8 months in 8 months 94% 6%</t>
         </is>
@@ -16817,27 +16908,28 @@
       <c r="CT88" t="inlineStr"/>
       <c r="CU88" t="inlineStr"/>
       <c r="CV88" t="inlineStr"/>
-      <c r="CW88" t="inlineStr">
+      <c r="CW88" t="inlineStr"/>
+      <c r="CX88" t="inlineStr">
         <is>
           <t>2 Level 1 Gravenberch 90 CDM PAC 84 SHO 83 PAS 87 DRI 90 DEF 88 PHY 88 CM R 4 ★ 4 Gravenberch 90 CDM PAC 84 SHO 83 PAS 87 DRI 90 DEF 88 PHY 88 CM R 4 ★ 4 UPGRADES 2</t>
         </is>
       </c>
-      <c r="CX88" t="inlineStr">
+      <c r="CY88" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 Details Submit by in 3 years Expiry in 3 years Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY88" t="inlineStr">
+      <c r="CZ88" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 Details Submit by in 3 years Expiry in 3 years Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ88" t="inlineStr">
+      <c r="DA88" t="inlineStr">
         <is>
           <t>Finesse Shot+</t>
         </is>
       </c>
-      <c r="DA88" t="inlineStr">
+      <c r="DB88" t="inlineStr">
         <is>
           <t>Finesse Shot+ Unlocked by completing the Finesse Shot+ Milestone objective Pulisic 90 CAM PAC 92 SHO 88 PAS 87 DRI 93 DEF 52 PHY 75 RM RW R 4 ★ 5 RM 86.8 Pulisic 90 CAM PAC 92 SHO 88 PAS 87 DRI 93 DEF 52 PHY 75 RM RW R 4 ★ 5 RM 88.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 UPGRADES 2 in 3 years in 3 years 94% 6%</t>
         </is>
@@ -16923,69 +17015,69 @@
       <c r="AQ89" t="inlineStr"/>
       <c r="AR89" t="inlineStr"/>
       <c r="AS89" t="inlineStr"/>
-      <c r="AT89" t="n">
+      <c r="AT89" t="inlineStr"/>
+      <c r="AU89" t="n">
         <v>6</v>
       </c>
-      <c r="AU89" t="n">
+      <c r="AV89" t="n">
         <v>80</v>
       </c>
-      <c r="AV89" t="n">
+      <c r="AW89" t="n">
         <v>8</v>
       </c>
-      <c r="AW89" t="n">
+      <c r="AX89" t="n">
         <v>80</v>
       </c>
-      <c r="AX89" t="n">
+      <c r="AY89" t="n">
         <v>6</v>
       </c>
-      <c r="AY89" t="n">
+      <c r="AZ89" t="n">
         <v>79</v>
       </c>
-      <c r="AZ89" t="inlineStr"/>
       <c r="BA89" t="inlineStr"/>
-      <c r="BB89" t="n">
+      <c r="BB89" t="inlineStr"/>
+      <c r="BC89" t="n">
         <v>6</v>
       </c>
-      <c r="BC89" t="n">
+      <c r="BD89" t="n">
         <v>80</v>
       </c>
-      <c r="BD89" t="inlineStr"/>
       <c r="BE89" t="inlineStr"/>
       <c r="BF89" t="inlineStr"/>
       <c r="BG89" t="inlineStr"/>
-      <c r="BH89" t="n">
+      <c r="BH89" t="inlineStr"/>
+      <c r="BI89" t="n">
         <v>3</v>
       </c>
-      <c r="BI89" t="n">
+      <c r="BJ89" t="n">
         <v>80</v>
       </c>
-      <c r="BJ89" t="n">
+      <c r="BK89" t="n">
         <v>4</v>
       </c>
-      <c r="BK89" t="n">
+      <c r="BL89" t="n">
         <v>79</v>
       </c>
-      <c r="BL89" t="inlineStr"/>
       <c r="BM89" t="inlineStr"/>
       <c r="BN89" t="inlineStr"/>
       <c r="BO89" t="inlineStr"/>
       <c r="BP89" t="inlineStr"/>
       <c r="BQ89" t="inlineStr"/>
-      <c r="BR89" t="n">
+      <c r="BR89" t="inlineStr"/>
+      <c r="BS89" t="n">
         <v>4</v>
       </c>
-      <c r="BS89" t="n">
+      <c r="BT89" t="n">
         <v>81</v>
       </c>
-      <c r="BT89" t="inlineStr"/>
       <c r="BU89" t="inlineStr"/>
-      <c r="BV89" t="n">
+      <c r="BV89" t="inlineStr"/>
+      <c r="BW89" t="n">
         <v>4</v>
       </c>
-      <c r="BW89" t="n">
+      <c r="BX89" t="n">
         <v>81</v>
       </c>
-      <c r="BX89" t="inlineStr"/>
       <c r="BY89" t="inlineStr"/>
       <c r="BZ89" t="inlineStr"/>
       <c r="CA89" t="inlineStr"/>
@@ -17010,27 +17102,28 @@
       <c r="CT89" t="inlineStr"/>
       <c r="CU89" t="inlineStr"/>
       <c r="CV89" t="inlineStr"/>
-      <c r="CW89" t="inlineStr">
+      <c r="CW89" t="inlineStr"/>
+      <c r="CX89" t="inlineStr">
         <is>
           <t>+1 OVR +3 Shot Power 80 +3 Vision 80 +4 Long Shots 80 +3 Volleys 79 +3 Short Pass 80 +4 Fk Accuracy 80 +4 Dribbling 81 +4 Reactions 81 +4 Long Pass 79 Level 1 Posch 82 RB PAC 82 SHO 60 PAS 74 DRI 73 DEF 83 PHY 80 RM R 2 ★ 3 Posch 83 RB PAC 82 SHO 62 PAS 75 DRI 73 DEF 83 PHY 80 RM R 2 ★ 3 UPGRADES +1 OVR +3 Shot Power 80 +3 Vision 80 +4 Long Shots 80 +3 Volleys 79</t>
         </is>
       </c>
-      <c r="CX89" t="inlineStr">
+      <c r="CY89" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Pace Max. 84 Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY89" t="inlineStr">
+      <c r="CZ89" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Pace Max. 84 Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ89" t="inlineStr">
+      <c r="DA89" t="inlineStr">
         <is>
           <t>Intro to Rewards EVOs</t>
         </is>
       </c>
-      <c r="DA89" t="inlineStr">
+      <c r="DB89" t="inlineStr">
         <is>
           <t>Intro to Rewards EVOs Upgrade your qualified Player's attributes and Overall Rating with this Evolution. Tzolis 80 LM PAC 78 SHO 77 PAS 75 DRI 83 DEF 38 PHY 71 LW R 4 ★ 4 LM 75.9 Tzolis 81 LM PAC 78 SHO 78 PAS 77 DRI 83 DEF 38 PHY 71 LW R 4 ★ 4 LM 76.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Pace Max. 84 UPGRADES +1 OVR +3 Shot Power 80 +3 Vision 80 +4 Long Shots 80 +3 Volleys 79 +3 Short Pass 80 +4 Fk Accuracy 80 +4 Dribbling 81 +4 Reactions 81 +4 Long Pass 79 in 5 months in 5 months 84% 16%</t>
         </is>
@@ -17168,32 +17261,33 @@
       <c r="CS90" t="inlineStr"/>
       <c r="CT90" t="inlineStr"/>
       <c r="CU90" t="inlineStr"/>
-      <c r="CV90" t="inlineStr">
+      <c r="CV90" t="inlineStr"/>
+      <c r="CW90" t="inlineStr">
         <is>
           <t>ST Advanced Forward +; ST Poacher +; ST Target Forward +</t>
         </is>
       </c>
-      <c r="CW90" t="inlineStr">
+      <c r="CX90" t="inlineStr">
         <is>
           <t>ST Advanced Forward + ST Poacher + ST False 9 + ST Target Forward + Level 1 Tabaković 83 ST PAC 81 SHO 83 PAS 75 DRI 80 DEF 39 PHY 88 R 2 ★ 3 Tabaković 83 ST PAC 81 SHO 83 PAS 75 DRI 80 DEF 39 PHY 88 R 2 ★ 3 UPGRADES ST Advanced Forward + ST Poacher + ST False 9 + ST Target Forward +</t>
         </is>
       </c>
-      <c r="CX90" t="inlineStr">
+      <c r="CY90" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 83 Position ST Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY90" t="inlineStr">
+      <c r="CZ90" t="inlineStr">
         <is>
           <t>Excluded Rarity World Tour Silver Stars Overall Max. 83 Position ST Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ90" t="inlineStr">
+      <c r="DA90" t="inlineStr">
         <is>
           <t>Club Member Reward</t>
         </is>
       </c>
-      <c r="DA90" t="inlineStr">
+      <c r="DB90" t="inlineStr">
         <is>
           <t>Club Member Reward Unlocked by being a Club Member on FC 26. Iñaki Williams 83 RM PAC 94 SHO 81 PAS 74 DRI 80 DEF 45 PHY 84 RW ST R 4 ★ 3 RM 79.3 Iñaki Williams 83 RM PAC 94 SHO 81 PAS 74 DRI 80 DEF 45 PHY 84 RW ST R 4 ★ 3 ST 79.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 83 Position ST UPGRADES ST Advanced Forward + ST Poacher + ST False 9 + ST Target Forward + in 5 months in 5 months 91% 9%</t>
         </is>
@@ -68136,7 +68230,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-11T06:40:01</t>
+          <t>2026-05-11T06:51:56</t>
         </is>
       </c>
     </row>

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB90"/>
+  <dimension ref="A1:DA90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,410 +544,405 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>+ Stat Point</t>
+          <t>Max OVR</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Max OVR</t>
+          <t>+ PAC</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>+ PAC</t>
+          <t>Max PAC</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Max PAC</t>
+          <t>+ SHO</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>+ SHO</t>
+          <t>Max SHO</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Max SHO</t>
+          <t>+ PAS</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>+ PAS</t>
+          <t>Max PAS</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>Max PAS</t>
+          <t>+ DRI</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>+ DRI</t>
+          <t>Max DRI</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Max DRI</t>
+          <t>+ DEF</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>+ DEF</t>
+          <t>Max DEF</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Max DEF</t>
+          <t>+ PHY</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>+ PHY</t>
+          <t>Max PHY</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>Max PHY</t>
+          <t>+ Acceleration</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>+ Acceleration</t>
+          <t>Max Acceleration</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>Max Acceleration</t>
+          <t>+ Sprint Speed</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>+ Sprint Speed</t>
+          <t>Max Sprint Speed</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>Max Sprint Speed</t>
+          <t>+ Positioning</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>+ Positioning</t>
+          <t>Max Positioning</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>Max Positioning</t>
+          <t>+ Finishing</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>+ Finishing</t>
+          <t>Max Finishing</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>Max Finishing</t>
+          <t>+ Shot Power</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>+ Shot Power</t>
+          <t>Max Shot Power</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>Max Shot Power</t>
+          <t>+ Long Shots</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>+ Long Shots</t>
+          <t>Max Long Shots</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>Max Long Shots</t>
+          <t>+ Volleys</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>+ Volleys</t>
+          <t>Max Volleys</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>Max Volleys</t>
+          <t>+ Penalties</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>+ Penalties</t>
+          <t>Max Penalties</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>Max Penalties</t>
+          <t>+ Vision</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>+ Vision</t>
+          <t>Max Vision</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>Max Vision</t>
+          <t>+ Crossing</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>+ Crossing</t>
+          <t>Max Crossing</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>Max Crossing</t>
+          <t>+ FK Accuracy</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>+ FK Accuracy</t>
+          <t>Max FK Accuracy</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>Max FK Accuracy</t>
+          <t>+ Short Passing</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>+ Short Passing</t>
+          <t>Max Short Passing</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>Max Short Passing</t>
+          <t>+ Long Passing</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>+ Long Passing</t>
+          <t>Max Long Passing</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>Max Long Passing</t>
+          <t>+ Curve</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>+ Curve</t>
+          <t>Max Curve</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>Max Curve</t>
+          <t>+ Agility</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>+ Agility</t>
+          <t>Max Agility</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>Max Agility</t>
+          <t>+ Balance</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>+ Balance</t>
+          <t>Max Balance</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>Max Balance</t>
+          <t>+ Reactions</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>+ Reactions</t>
+          <t>Max Reactions</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>Max Reactions</t>
+          <t>+ Ball Control</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>+ Ball Control</t>
+          <t>Max Ball Control</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>Max Ball Control</t>
+          <t>+ Dribbling</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>+ Dribbling</t>
+          <t>Max Dribbling</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>Max Dribbling</t>
+          <t>+ Composure</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>+ Composure</t>
+          <t>Max Composure</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>Max Composure</t>
+          <t>+ Interceptions</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>+ Interceptions</t>
+          <t>Max Interceptions</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>Max Interceptions</t>
+          <t>+ Heading Accuracy</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>+ Heading Accuracy</t>
+          <t>Max Heading Accuracy</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>Max Heading Accuracy</t>
+          <t>+ Defensive Awareness</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>+ Defensive Awareness</t>
+          <t>Max Defensive Awareness</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>Max Defensive Awareness</t>
+          <t>+ Standing Tackle</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>+ Standing Tackle</t>
+          <t>Max Standing Tackle</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>Max Standing Tackle</t>
+          <t>+ Sliding Tackle</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>+ Sliding Tackle</t>
+          <t>Max Sliding Tackle</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>Max Sliding Tackle</t>
+          <t>+ Jumping</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>+ Jumping</t>
+          <t>Max Jumping</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>Max Jumping</t>
+          <t>+ Stamina</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>+ Stamina</t>
+          <t>Max Stamina</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>Max Stamina</t>
+          <t>+ Strength</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>+ Strength</t>
+          <t>Max Strength</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>Max Strength</t>
+          <t>+ Aggression</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>+ Aggression</t>
+          <t>Max Aggression</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>Max Aggression</t>
+          <t>+ SM</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>+ SM</t>
+          <t>Max SM</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>Max SM</t>
+          <t>+ WF</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>+ WF</t>
+          <t>Max WF</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>Max WF</t>
+          <t>Role_Added</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>Role_Added</t>
+          <t>Other_Upgrade_Text</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>Other_Upgrade_Text</t>
+          <t>Raw_Requirements_Text</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>Raw_Requirements_Text</t>
+          <t>Req_Other</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>Req_Other</t>
+          <t>Link_Text</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
-        <is>
-          <t>Link_Text</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
         <is>
           <t>Parent_Text</t>
         </is>
@@ -1086,10 +1081,14 @@
       <c r="CT2" t="inlineStr"/>
       <c r="CU2" t="inlineStr"/>
       <c r="CV2" t="inlineStr"/>
-      <c r="CW2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>8 Level 1 Maradona 95 CAM PAC 90 SHO 91 PAS 91 DRI 96 DEF 40 PHY 77 ST L 5 ★ 3 Maradona 95 CAM PAC 90 SHO 91 PAS 91 DRI 96 DEF 40 PHY 77 ST L 5 ★ 3 UPGRADES 8</t>
+        </is>
+      </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>8 Level 1 Maradona 95 CAM PAC 90 SHO 91 PAS 91 DRI 96 DEF 40 PHY 77 ST L 5 ★ 3 Maradona 95 CAM PAC 90 SHO 91 PAS 91 DRI 96 DEF 40 PHY 77 ST L 5 ★ 3 UPGRADES 8</t>
+          <t>Excluded Rarity World Tour Silver Stars Max PS 7 Max PS+ 2 Details Submit by in 9 days Expiry in 16 days Coins Cost 35,000 Points Cost 250</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
@@ -1099,15 +1098,10 @@
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Max PS 7 Max PS+ 2 Details Submit by in 9 days Expiry in 16 days Coins Cost 35,000 Points Cost 250</t>
+          <t>Maestro Unbound NEW 35,000 250 2</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
-        <is>
-          <t>Maestro Unbound NEW 35,000 250 2</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
         <is>
           <t>Maestro Unbound NEW 35,000 250 2 Unlock the true playmaking abilities of a player by adding all passing PlayStyles. Pelé 96 CAM PAC 94 SHO 96 PAS 92 DRI 95 DEF 60 PHY 75 ST R 5 ★ 4 CAM 90.6 Pelé 96 CAM PAC 94 SHO 96 PAS 92 DRI 95 DEF 60 PHY 75 ST R 5 ★ 4 CAM 92.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max PS 7 Max PS+ 2 UPGRADES 8 in 9 days in 16 days 26% 74%</t>
         </is>
@@ -1180,10 +1174,10 @@
       <c r="X3" t="n">
         <v>30</v>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="n">
+      <c r="Y3" t="n">
         <v>92</v>
       </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -1195,19 +1189,19 @@
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AL3" t="n">
+        <v>20</v>
+      </c>
       <c r="AM3" t="n">
+        <v>82</v>
+      </c>
+      <c r="AN3" t="n">
         <v>20</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AO3" t="n">
         <v>82</v>
       </c>
-      <c r="AO3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>82</v>
-      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
@@ -1235,13 +1229,13 @@
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr"/>
       <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
+      <c r="BR3" t="n">
+        <v>25</v>
+      </c>
       <c r="BS3" t="n">
-        <v>25</v>
-      </c>
-      <c r="BT3" t="n">
         <v>93</v>
       </c>
+      <c r="BT3" t="inlineStr"/>
       <c r="BU3" t="inlineStr"/>
       <c r="BV3" t="inlineStr"/>
       <c r="BW3" t="inlineStr"/>
@@ -1267,19 +1261,23 @@
       <c r="CQ3" t="inlineStr"/>
       <c r="CR3" t="inlineStr"/>
       <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="inlineStr"/>
-      <c r="CU3" t="n">
+      <c r="CT3" t="n">
         <v>2</v>
       </c>
-      <c r="CV3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>GK Goalkeeper ++; GK Ball Playing Keeper ++; GK Sweeper Keeper ++</t>
+        </is>
+      </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>GK Goalkeeper ++; GK Ball Playing Keeper ++; GK Sweeper Keeper ++</t>
+          <t>+15 OVR 92 +15 POS 92 +1 WF +10 Acceleration 82 +10 Sprint Speed 82 +25 Reactions 93 +15 Diving 90 +15 Handling 91 +15 Kicking 90 +15 Reflexes 94 GK Goalkeeper ++ GK Ball Playing Keeper ++ GK Sweeper Keeper ++ 2 8 Level 1 Nnadozie 90 GK DIV 92 HAN 87 KIC 86 REF 93 SPD 71 POS 91 R 2 ★ 5 Nnadozie 92 GK DIV 92 HAN 87 KIC 86 REF 93 SPD 71 POS 91 R 2 ★ 5 UPGRADES +15 OVR 92 +1 WF +10 Acceleration 82 +10 Sprint Speed 82 8</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>+15 OVR 92 +15 POS 92 +1 WF +10 Acceleration 82 +10 Sprint Speed 82 +25 Reactions 93 +15 Diving 90 +15 Handling 91 +15 Kicking 90 +15 Reflexes 94 GK Goalkeeper ++ GK Ball Playing Keeper ++ GK Sweeper Keeper ++ 2 8 Level 1 Nnadozie 90 GK DIV 92 HAN 87 KIC 86 REF 93 SPD 71 POS 91 R 2 ★ 5 Nnadozie 92 GK DIV 92 HAN 87 KIC 86 REF 93 SPD 71 POS 91 R 2 ★ 5 UPGRADES +15 OVR 92 +1 WF +10 Acceleration 82 +10 Sprint Speed 82 8</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position GK Max PS 10 Max PS+ 2 Details Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
@@ -1289,15 +1287,10 @@
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position GK Max PS 10 Max PS+ 2 Details Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
+          <t>Cat Like Reflexes</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
-        <is>
-          <t>Cat Like Reflexes</t>
-        </is>
-      </c>
-      <c r="DB3" t="inlineStr">
         <is>
           <t>Cat Like Reflexes Elevate your goalkeeper with elite-level reactions boosts designed to turn split-second moments into match-winning saves. Casillas 90 GK DIV 90 HAN 88 KIC 84 REF 93 SPD 59 POS 88 L 1 ★ 3 GK 83.1 Casillas 92 GK DIV 90 HAN 91 KIC 90 REF 94 SPD 69 POS 92 L 1 ★ 4 GK 87.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position GK Max PS 10 Max PS+ 2 UPGRADES +15 OVR 92 +15 POS 92 +1 WF +10 Acceleration 82 +10 Sprint Speed 82 +25 Reactions 93 +15 Diving 90 +15 Handling 91 +15 Kicking 90 +15 Reflexes 94 GK Goalkeeper ++ GK Ball Playing Keeper ++ GK Sweeper Keeper ++ 2 8 Show less in 8 days in 15 days 90% 10%</t>
         </is>
@@ -1370,10 +1363,10 @@
       <c r="X4" t="n">
         <v>40</v>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="n">
+      <c r="Y4" t="n">
         <v>92</v>
       </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -1385,19 +1378,19 @@
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AL4" t="n">
+        <v>20</v>
+      </c>
       <c r="AM4" t="n">
+        <v>86</v>
+      </c>
+      <c r="AN4" t="n">
         <v>20</v>
       </c>
-      <c r="AN4" t="n">
-        <v>86</v>
-      </c>
       <c r="AO4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AP4" t="n">
         <v>90</v>
       </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
@@ -1407,135 +1400,139 @@
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
+      <c r="AZ4" t="n">
+        <v>25</v>
+      </c>
       <c r="BA4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB4" t="n">
         <v>94</v>
       </c>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BH4" t="n">
+        <v>60</v>
+      </c>
       <c r="BI4" t="n">
+        <v>90</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>90</v>
+      </c>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>88</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>87</v>
+      </c>
+      <c r="BR4" t="n">
         <v>60</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BS4" t="n">
+        <v>92</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>92</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>87</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>30</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>92</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>30</v>
+      </c>
+      <c r="CC4" t="n">
         <v>90</v>
       </c>
-      <c r="BK4" t="n">
+      <c r="CD4" t="n">
         <v>30</v>
       </c>
-      <c r="BL4" t="n">
+      <c r="CE4" t="n">
+        <v>93</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>30</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>94</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>30</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>92</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>25</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>88</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>25</v>
+      </c>
+      <c r="CM4" t="n">
         <v>90</v>
       </c>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>88</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>87</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>92</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>92</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>87</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>92</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>30</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>92</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>30</v>
-      </c>
-      <c r="CD4" t="n">
+      <c r="CN4" t="n">
+        <v>25</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>91</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>50</v>
+      </c>
+      <c r="CQ4" t="n">
         <v>90</v>
       </c>
-      <c r="CE4" t="n">
-        <v>30</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>93</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>30</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>94</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>30</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>92</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>25</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>88</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>25</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>90</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>25</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>91</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>50</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>90</v>
-      </c>
+      <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="inlineStr"/>
-      <c r="CT4" t="inlineStr"/>
+      <c r="CT4" t="n">
+        <v>6</v>
+      </c>
       <c r="CU4" t="n">
-        <v>6</v>
-      </c>
-      <c r="CV4" t="n">
         <v>4</v>
       </c>
-      <c r="CW4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>+20 OVR 92 +3 WF 4 +30 Composure 92 +25 Aggression 90 +30 Short Pass 90 +30 Reactions 92 +30 Defensive Awareness 93 +30 Interceptions 92 +25 Stamina 90 +30 Heading Acc. 90 +20 Dribbling 87 +20 Sprint Speed 90 +25 Strength 91 +20 Balance 87 +25 Penalties 94 +30 Standing Tackle 94 +20 Acceleration 86 +20 Agility 88 +30 Long Pass 90 +25 Jumping 88 +30 Sliding Tackle 92 +30 Ball Control 92 3 7 Level 1 Pacho 90 CB PAC 86 SHO 40 PAS 73 DRI 73 DEF 90 PHY 91 L 5 ★ 5 Pacho 92 CB PAC 86 SHO 40 PAS 73 DRI 74 DEF 90 PHY 91 L 5 ★ 5 UPGRADES +20 OVR 92 +3 WF 4 +30 Composure 92 +25 Aggression 90 +30 Short Pass 90 +30 Reactions 92</t>
+        </is>
+      </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>+20 OVR 92 +3 WF 4 +30 Composure 92 +25 Aggression 90 +30 Short Pass 90 +30 Reactions 92 +30 Defensive Awareness 93 +30 Interceptions 92 +25 Stamina 90 +30 Heading Acc. 90 +20 Dribbling 87 +20 Sprint Speed 90 +25 Strength 91 +20 Balance 87 +25 Penalties 94 +30 Standing Tackle 94 +20 Acceleration 86 +20 Agility 88 +30 Long Pass 90 +25 Jumping 88 +30 Sliding Tackle 92 +30 Ball Control 92 3 7 Level 1 Pacho 90 CB PAC 86 SHO 40 PAS 73 DRI 73 DEF 90 PHY 91 L 5 ★ 5 Pacho 92 CB PAC 86 SHO 40 PAS 73 DRI 74 DEF 90 PHY 91 L 5 ★ 5 UPGRADES +20 OVR 92 +3 WF 4 +30 Composure 92 +25 Aggression 90 +30 Short Pass 90 +30 Reactions 92</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position CB Max PS 10 Max PS+ 2 Heading Accuracy Max. 94 Details Submit by in 7 days Expiry in 14 days Coins Cost 125,000 Points Cost 750</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
@@ -1545,15 +1542,10 @@
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position CB Max PS 10 Max PS+ 2 Heading Accuracy Max. 94 Details Submit by in 7 days Expiry in 14 days Coins Cost 125,000 Points Cost 750</t>
+          <t>Le Président 125,000 750</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
-        <is>
-          <t>Le Président 125,000 750</t>
-        </is>
-      </c>
-      <c r="DB4" t="inlineStr">
         <is>
           <t>Le Président 125,000 750 Transform your CB with the defensive excellence that made Laurent Blanc one of the greatest. Cool, composed, and unbeatable. Laporte 90 CB PAC 85 SHO 60 PAS 87 DRI 84 DEF 91 PHY 90 L 5 ★ 5 CB 79.3 Laporte 92 CB PAC 88 SHO 61 PAS 87 DRI 89 DEF 93 PHY 92 L 5 ★ 5 CB 91.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position CB Max PS 10 Max PS+ 2 Heading Accuracy Max. 94 UPGRADES +20 OVR 92 +3 WF 4 +30 Composure 92 +25 Aggression 90 +30 Short Pass 90 +30 Reactions 92 +30 Defensive Awareness 93 +30 Interceptions 92 +25 Stamina 90 +30 Heading Acc. 90 +20 Dribbling 87 +20 Sprint Speed 90 +25 Strength 91 +20 Balance 87 +25 Penalties 94 +30 Standing Tackle 94 +20 Acceleration 86 +20 Agility 88 +30 Long Pass 90 +25 Jumping 88 +30 Sliding Tackle 92 +30 Ball Control 92 3 7 in 7 days in 14 days 59% 41%</t>
         </is>
@@ -1635,31 +1627,31 @@
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>14</v>
+      </c>
       <c r="AU5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV5" t="n">
         <v>95</v>
       </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
+      <c r="BB5" t="n">
+        <v>14</v>
+      </c>
       <c r="BC5" t="n">
+        <v>92</v>
+      </c>
+      <c r="BD5" t="n">
         <v>14</v>
       </c>
-      <c r="BD5" t="n">
-        <v>92</v>
-      </c>
       <c r="BE5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BF5" t="n">
         <v>93</v>
       </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr"/>
@@ -1669,23 +1661,23 @@
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
+      <c r="BP5" t="n">
+        <v>14</v>
+      </c>
       <c r="BQ5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BR5" t="n">
         <v>90</v>
       </c>
+      <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="inlineStr"/>
       <c r="BT5" t="inlineStr"/>
       <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
+      <c r="BV5" t="n">
+        <v>7</v>
+      </c>
       <c r="BW5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BX5" t="n">
         <v>93</v>
       </c>
+      <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="inlineStr"/>
       <c r="CA5" t="inlineStr"/>
@@ -1697,31 +1689,35 @@
       <c r="CG5" t="inlineStr"/>
       <c r="CH5" t="inlineStr"/>
       <c r="CI5" t="inlineStr"/>
-      <c r="CJ5" t="inlineStr"/>
+      <c r="CJ5" t="n">
+        <v>7</v>
+      </c>
       <c r="CK5" t="n">
+        <v>92</v>
+      </c>
+      <c r="CL5" t="inlineStr"/>
+      <c r="CM5" t="inlineStr"/>
+      <c r="CN5" t="n">
         <v>7</v>
       </c>
-      <c r="CL5" t="n">
+      <c r="CO5" t="n">
         <v>92</v>
       </c>
-      <c r="CM5" t="inlineStr"/>
-      <c r="CN5" t="inlineStr"/>
-      <c r="CO5" t="n">
-        <v>7</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>92</v>
-      </c>
+      <c r="CP5" t="inlineStr"/>
       <c r="CQ5" t="inlineStr"/>
       <c r="CR5" t="inlineStr"/>
       <c r="CS5" t="inlineStr"/>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="inlineStr"/>
       <c r="CV5" t="inlineStr"/>
-      <c r="CW5" t="inlineStr"/>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>+1 OVR +7 Shot Power 95 +7 Vision 92 +7 Crossing 93 +7 Balance 90 +7 Dribbling 93 +7 Jumping 92 +7 Strength 92 Level 1 Moleiro 88 LM PAC 91 SHO 87 PAS 88 DRI 91 DEF 62 PHY 77 CAM LW R 4 ★ 4 Moleiro 89 LM PAC 91 SHO 88 PAS 89 DRI 91 DEF 62 PHY 77 CAM LW R 4 ★ 4 UPGRADES +1 OVR +7 Shot Power 95 +7 Vision 92 +7 Crossing 93 +7 Balance 90</t>
+        </is>
+      </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>+1 OVR +7 Shot Power 95 +7 Vision 92 +7 Crossing 93 +7 Balance 90 +7 Dribbling 93 +7 Jumping 92 +7 Strength 92 Level 1 Moleiro 88 LM PAC 91 SHO 87 PAS 88 DRI 91 DEF 62 PHY 77 CAM LW R 4 ★ 4 Moleiro 89 LM PAC 91 SHO 88 PAS 89 DRI 91 DEF 62 PHY 77 CAM LW R 4 ★ 4 UPGRADES +1 OVR +7 Shot Power 95 +7 Vision 92 +7 Crossing 93 +7 Balance 90</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Details Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
@@ -1731,15 +1727,10 @@
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Details Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
+          <t>Lucky Number Seven 3</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
-        <is>
-          <t>Lucky Number Seven 3</t>
-        </is>
-      </c>
-      <c r="DB5" t="inlineStr">
         <is>
           <t>Lucky Number Seven 3 Hit your stride with Lucky Number Seven and give your eligible player boosts across key stats. Riise 88 LB PAC 88 SHO 83 PAS 86 DRI 85 DEF 86 PHY 88 LM L 4 ★ 4 LB 88.2 Riise 89 LB PAC 88 SHO 83 PAS 88 DRI 89 DEF 86 PHY 91 LM L 4 ★ 4 LB 89.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 UPGRADES +1 OVR +7 Shot Power 95 +7 Vision 92 +7 Crossing 93 +7 Balance 90 +7 Dribbling 93 +7 Jumping 92 +7 Strength 92 in 6 days in 13 days 26% 74%</t>
         </is>
@@ -1820,38 +1811,38 @@
       <c r="X6" t="n">
         <v>30</v>
       </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="n">
+      <c r="Y6" t="n">
         <v>90</v>
       </c>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>15</v>
+      </c>
       <c r="AE6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF6" t="n">
         <v>87</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>20</v>
+      </c>
       <c r="AM6" t="n">
+        <v>89</v>
+      </c>
+      <c r="AN6" t="n">
         <v>20</v>
       </c>
-      <c r="AN6" t="n">
-        <v>89</v>
-      </c>
       <c r="AO6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AP6" t="n">
         <v>92</v>
       </c>
+      <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
@@ -1875,101 +1866,105 @@
       <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
+      <c r="BN6" t="n">
+        <v>10</v>
+      </c>
       <c r="BO6" t="n">
+        <v>88</v>
+      </c>
+      <c r="BP6" t="n">
         <v>10</v>
       </c>
-      <c r="BP6" t="n">
+      <c r="BQ6" t="n">
+        <v>86</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BS6" t="n">
         <v>88</v>
       </c>
-      <c r="BQ6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>86</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>88</v>
-      </c>
+      <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="inlineStr"/>
       <c r="BW6" t="inlineStr"/>
-      <c r="BX6" t="inlineStr"/>
+      <c r="BX6" t="n">
+        <v>10</v>
+      </c>
       <c r="BY6" t="n">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="BZ6" t="n">
+        <v>40</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>91</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>20</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>83</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>20</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>91</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>20</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>90</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>20</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>93</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>15</v>
+      </c>
+      <c r="CK6" t="n">
         <v>88</v>
       </c>
-      <c r="CA6" t="n">
-        <v>40</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>91</v>
-      </c>
-      <c r="CC6" t="n">
+      <c r="CL6" t="n">
         <v>20</v>
       </c>
-      <c r="CD6" t="n">
-        <v>83</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>20</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>91</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>20</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>90</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>20</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>93</v>
-      </c>
-      <c r="CK6" t="n">
+      <c r="CM6" t="n">
+        <v>92</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>30</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>88</v>
+      </c>
+      <c r="CP6" t="n">
         <v>15</v>
       </c>
-      <c r="CL6" t="n">
-        <v>88</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>20</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>92</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>30</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>88</v>
-      </c>
       <c r="CQ6" t="n">
-        <v>15</v>
-      </c>
-      <c r="CR6" t="n">
         <v>86</v>
       </c>
+      <c r="CR6" t="inlineStr"/>
       <c r="CS6" t="inlineStr"/>
-      <c r="CT6" t="inlineStr"/>
+      <c r="CT6" t="n">
+        <v>4</v>
+      </c>
       <c r="CU6" t="n">
         <v>4</v>
       </c>
-      <c r="CV6" t="n">
-        <v>4</v>
-      </c>
-      <c r="CW6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr"/>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>+15 OVR 90 +15 PAS 87 CB +2 WF 4 +20 Interceptions 91 +15 Strength 88 +20 Standing Tackle 90 +20 Defensive Awareness 91 +20 Stamina 92 +10 Composure 88 +10 Balance 86 +20 Acceleration 89 +15 Aggression 86 +20 Heading Acc. 83 +20 Sprint Speed 92 +10 Agility 88 +15 Jumping 88 +20 Sliding Tackle 93 +10 Reactions 88 3 7 Level 1 Wan-Bissaka 89 RB PAC 90 SHO 60 PAS 86 DRI 87 DEF 88 PHY 85 RM R 5 ★ 5 Wan-Bissaka 90 RB PAC 90 SHO 60 PAS 86 DRI 87 DEF 88 PHY 87 RM CB R 5 ★ 5 UPGRADES +15 OVR 90 CB +2 WF 4 +20 Interceptions 91 +15 Strength 88 3</t>
+        </is>
+      </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>+15 OVR 90 +15 PAS 87 CB +2 WF 4 +20 Interceptions 91 +15 Strength 88 +20 Standing Tackle 90 +20 Defensive Awareness 91 +20 Stamina 92 +10 Composure 88 +10 Balance 86 +20 Acceleration 89 +15 Aggression 86 +20 Heading Acc. 83 +20 Sprint Speed 92 +10 Agility 88 +15 Jumping 88 +20 Sliding Tackle 93 +10 Reactions 88 3 7 Level 1 Wan-Bissaka 89 RB PAC 90 SHO 60 PAS 86 DRI 87 DEF 88 PHY 85 RM R 5 ★ 5 Wan-Bissaka 90 RB PAC 90 SHO 60 PAS 86 DRI 87 DEF 88 PHY 87 RM CB R 5 ★ 5 UPGRADES +15 OVR 90 CB +2 WF 4 +20 Interceptions 91 +15 Strength 88 3</t>
+          <t>Excluded Rarity World Tour Silver Stars Max Pos. 3 Overall Max. 89 Position RB Excluded Position CB Max PS 10 Max PS+ 2 Details Submit by in 5 days Expiry in 12 days Coins Cost 35,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
@@ -1979,15 +1974,10 @@
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Max Pos. 3 Overall Max. 89 Position RB Excluded Position CB Max PS 10 Max PS+ 2 Details Submit by in 5 days Expiry in 12 days Coins Cost 35,000 Points Cost 200</t>
+          <t>Fullback Takeover 35,000 200</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
-        <is>
-          <t>Fullback Takeover 35,000 200</t>
-        </is>
-      </c>
-      <c r="DB6" t="inlineStr">
         <is>
           <t>Fullback Takeover 35,000 200 Speed at the back. Power in every duel. A certain alpine player once ruled the center with unexpected power. Shift the role, break the line, and rediscover that unstoppable edge. Kimmich 89 RB PAC 81 SHO 74 PAS 89 DRI 85 DEF 85 PHY 80 CDM CM R 3 ★ 4 RB 81.0 Kimmich 90 RB PAC 91 SHO 74 PAS 89 DRI 85 DEF 90 PHY 88 CB CDM CM R 3 ★ 4 RB 89.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max Pos. 3 Overall Max. 89 Position RB Excluded Position CB Max PS 10 Max PS+ 2 UPGRADES +15 OVR 90 +15 PAS 87 CB +2 WF 4 +20 Interceptions 91 +15 Strength 88 +20 Standing Tackle 90 +20 Defensive Awareness 91 +20 Stamina 92 +10 Composure 88 +10 Balance 86 +20 Acceleration 89 +15 Aggression 86 +20 Heading Acc. 83 +20 Sprint Speed 92 +10 Agility 88 +15 Jumping 88 +20 Sliding Tackle 93 +10 Reactions 88 3 7 Show less in 5 days in 12 days 22% 78%</t>
         </is>
@@ -2056,10 +2046,10 @@
       <c r="X7" t="n">
         <v>10</v>
       </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="n">
+      <c r="Y7" t="n">
         <v>91</v>
       </c>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -2071,185 +2061,189 @@
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
+      <c r="AL7" t="n">
+        <v>5</v>
+      </c>
       <c r="AM7" t="n">
+        <v>89</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>89</v>
+      </c>
+      <c r="AP7" t="n">
         <v>5</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AQ7" t="n">
+        <v>91</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS7" t="n">
         <v>89</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AT7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>88</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>87</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>86</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="n">
         <v>10</v>
       </c>
-      <c r="AP7" t="n">
-        <v>89</v>
-      </c>
-      <c r="AQ7" t="n">
+      <c r="BC7" t="n">
+        <v>91</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>86</v>
+      </c>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="n">
         <v>5</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BI7" t="n">
+        <v>90</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>90</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>90</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>92</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>92</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>90</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU7" t="n">
         <v>91</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BV7" t="n">
         <v>5</v>
       </c>
-      <c r="AT7" t="n">
-        <v>89</v>
-      </c>
-      <c r="AU7" t="n">
+      <c r="BW7" t="n">
+        <v>92</v>
+      </c>
+      <c r="BX7" t="n">
         <v>5</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="BY7" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="CA7" t="n">
         <v>88</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="CB7" t="n">
         <v>5</v>
       </c>
-      <c r="AX7" t="n">
-        <v>87</v>
-      </c>
-      <c r="AY7" t="n">
+      <c r="CC7" t="n">
+        <v>85</v>
+      </c>
+      <c r="CD7" t="n">
         <v>5</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="CE7" t="n">
         <v>86</v>
       </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="n">
+      <c r="CF7" t="n">
+        <v>5</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>86</v>
+      </c>
+      <c r="CH7" t="n">
         <v>10</v>
       </c>
-      <c r="BD7" t="n">
-        <v>91</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF7" t="n">
+      <c r="CI7" t="n">
+        <v>90</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>90</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>5</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>90</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>5</v>
+      </c>
+      <c r="CO7" t="n">
         <v>86</v>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="n">
+      <c r="CP7" t="n">
         <v>5</v>
       </c>
-      <c r="BJ7" t="n">
-        <v>90</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>90</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>90</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>92</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>92</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>90</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>91</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>92</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>87</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>5</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>88</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>5</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>85</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>5</v>
-      </c>
-      <c r="CF7" t="n">
+      <c r="CQ7" t="n">
         <v>86</v>
       </c>
-      <c r="CG7" t="n">
-        <v>5</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>86</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>10</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>90</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>5</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>90</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>5</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>90</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>5</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>86</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>5</v>
-      </c>
       <c r="CR7" t="n">
-        <v>86</v>
-      </c>
-      <c r="CS7" t="n">
         <v>4</v>
       </c>
-      <c r="CT7" t="inlineStr"/>
-      <c r="CU7" t="n">
+      <c r="CS7" t="inlineStr"/>
+      <c r="CT7" t="n">
         <v>8</v>
       </c>
+      <c r="CU7" t="inlineStr"/>
       <c r="CV7" t="inlineStr"/>
-      <c r="CW7" t="inlineStr"/>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>+5 OVR 91 +4 SM +4 WF +5 Sliding Tackle 90 +5 Vision 91 +5 Sprint Speed 89 +5 Crossing 86 +5 Long Pass 90 +5 Interceptions 88 +5 Volleys 86 +5 Composure 87 +5 Heading Acc. 85 +5 Curve 90 +5 Agility 92 +5 Positioning 91 +5 Standing Tackle 86 +5 Finishing 89 +5 Reactions 90 +5 Balance 92 +5 Strength 86 +5 Short Pass 90 +5 Jumping 90 +5 Long Shots 87 +5 Stamina 90 +5 Defensive Awareness 86 +5 Ball Control 91 +5 Dribbling 92 +5 Aggression 86 +5 Shot Power 88 +5 Acceleration 89 Level 1 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 Kerolin Nicoli 91 RM PAC 91 SHO 86 PAS 86 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 UPGRADES +5 OVR 91 +4 WF +5 Sliding Tackle 90 +5 Vision 91 +5 Sprint Speed 89 +5 Crossing 86</t>
+        </is>
+      </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>+5 OVR 91 +4 SM +4 WF +5 Sliding Tackle 90 +5 Vision 91 +5 Sprint Speed 89 +5 Crossing 86 +5 Long Pass 90 +5 Interceptions 88 +5 Volleys 86 +5 Composure 87 +5 Heading Acc. 85 +5 Curve 90 +5 Agility 92 +5 Positioning 91 +5 Standing Tackle 86 +5 Finishing 89 +5 Reactions 90 +5 Balance 92 +5 Strength 86 +5 Short Pass 90 +5 Jumping 90 +5 Long Shots 87 +5 Stamina 90 +5 Defensive Awareness 86 +5 Ball Control 91 +5 Dribbling 92 +5 Aggression 86 +5 Shot Power 88 +5 Acceleration 89 Level 1 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 Kerolin Nicoli 91 RM PAC 91 SHO 86 PAS 86 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 UPGRADES +5 OVR 91 +4 WF +5 Sliding Tackle 90 +5 Vision 91 +5 Sprint Speed 89 +5 Crossing 86</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 11 days Coins Cost 75,000 Points Cost 400</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
@@ -2259,15 +2253,10 @@
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 11 days Coins Cost 75,000 Points Cost 400</t>
+          <t>Gear 5 75,000 400</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
-        <is>
-          <t>Gear 5 75,000 400</t>
-        </is>
-      </c>
-      <c r="DB7" t="inlineStr">
         <is>
           <t>Gear 5 75,000 400 Hit the gear and let loose with +5 boosts across key stats. Bounce past rivals, stretch the game, and chase victory with a grin. Davies 89 LB PAC 95 SHO 80 PAS 84 DRI 87 DEF 82 PHY 84 LM L 4 ★ 3 LB 87.9 Davies 91 LB PAC 95 SHO 83 PAS 86 DRI 91 DEF 86 PHY 87 LM L 5 ★ 5 LB 91.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES +5 OVR 91 +4 SM +4 WF +5 Sliding Tackle 90 +5 Vision 91 +5 Sprint Speed 89 +5 Crossing 86 +5 Long Pass 90 +5 Interceptions 88 +5 Volleys 86 +5 Composure 87 +5 Heading Acc. 85 +5 Curve 90 +5 Agility 92 +5 Positioning 91 +5 Standing Tackle 86 +5 Finishing 89 +5 Reactions 90 +5 Balance 92 +5 Strength 86 +5 Short Pass 90 +5 Jumping 90 +5 Long Shots 87 +5 Stamina 90 +5 Defensive Awareness 86 +5 Ball Control 91 +5 Dribbling 92 +5 Aggression 86 +5 Shot Power 88 +5 Acceleration 89 in 4 days in 11 days 8% 92%</t>
         </is>
@@ -2347,19 +2336,19 @@
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
       <c r="AM8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN8" t="n">
         <v>1</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AO8" t="n">
         <v>80</v>
       </c>
-      <c r="AO8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>80</v>
-      </c>
+      <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
@@ -2371,23 +2360,23 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
+      <c r="BB8" t="n">
+        <v>2</v>
+      </c>
       <c r="BC8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD8" t="n">
         <v>72</v>
       </c>
+      <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BH8" t="n">
+        <v>4</v>
+      </c>
       <c r="BI8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ8" t="n">
         <v>78</v>
       </c>
+      <c r="BJ8" t="inlineStr"/>
       <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="inlineStr"/>
       <c r="BM8" t="inlineStr"/>
@@ -2403,69 +2392,73 @@
       <c r="BW8" t="inlineStr"/>
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
-      <c r="BZ8" t="inlineStr"/>
+      <c r="BZ8" t="n">
+        <v>4</v>
+      </c>
       <c r="CA8" t="n">
+        <v>80</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>76</v>
+      </c>
+      <c r="CD8" t="n">
         <v>4</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CE8" t="n">
         <v>80</v>
       </c>
-      <c r="CC8" t="n">
+      <c r="CF8" t="n">
         <v>2</v>
       </c>
-      <c r="CD8" t="n">
-        <v>76</v>
-      </c>
-      <c r="CE8" t="n">
+      <c r="CG8" t="n">
+        <v>80</v>
+      </c>
+      <c r="CH8" t="n">
         <v>4</v>
       </c>
-      <c r="CF8" t="n">
-        <v>80</v>
-      </c>
-      <c r="CG8" t="n">
+      <c r="CI8" t="n">
+        <v>78</v>
+      </c>
+      <c r="CJ8" t="n">
         <v>2</v>
       </c>
-      <c r="CH8" t="n">
-        <v>80</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>4</v>
-      </c>
-      <c r="CJ8" t="n">
+      <c r="CK8" t="n">
+        <v>75</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM8" t="n">
         <v>78</v>
       </c>
-      <c r="CK8" t="n">
-        <v>2</v>
-      </c>
-      <c r="CL8" t="n">
+      <c r="CN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>78</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ8" t="n">
         <v>75</v>
       </c>
-      <c r="CM8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>78</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>78</v>
-      </c>
-      <c r="CQ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>75</v>
-      </c>
+      <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="inlineStr"/>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="inlineStr"/>
       <c r="CV8" t="inlineStr"/>
-      <c r="CW8" t="inlineStr"/>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>+2 Sliding Tackle 78 +2 Short Pass 78 +2 Defensive Awareness 80 +2 Interceptions 80 +1 Jumping 75 +1 Sprint Speed 80 +2 Standing Tackle 80 +1 Acceleration 80 +1 Strength 78 +2 Vision 72 +1 Aggression 75 +1 Stamina 78 +2 Heading Acc. 76 2 8 Level 1 Jair Cunha 74 CB PAC 67 SHO 38 PAS 59 DRI 58 DEF 73 PHY 80 R 2 ★ 4 Jair Cunha 74 CB PAC 67 SHO 38 PAS 60 DRI 58 DEF 75 PHY 80 R 2 ★ 4 UPGRADES +2 Sliding Tackle 78 +2 Short Pass 78 +2 Defensive Awareness 80 +2 Interceptions 80 +1 Jumping 75 8</t>
+        </is>
+      </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>+2 Sliding Tackle 78 +2 Short Pass 78 +2 Defensive Awareness 80 +2 Interceptions 80 +1 Jumping 75 +1 Sprint Speed 80 +2 Standing Tackle 80 +1 Acceleration 80 +1 Strength 78 +2 Vision 72 +1 Aggression 75 +1 Stamina 78 +2 Heading Acc. 76 2 8 Level 1 Jair Cunha 74 CB PAC 67 SHO 38 PAS 59 DRI 58 DEF 73 PHY 80 R 2 ★ 4 Jair Cunha 74 CB PAC 67 SHO 38 PAS 60 DRI 58 DEF 75 PHY 80 R 2 ★ 4 UPGRADES +2 Sliding Tackle 78 +2 Short Pass 78 +2 Defensive Awareness 80 +2 Interceptions 80 +1 Jumping 75 8</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 74 Max PS 10 Max PS+ 2 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
@@ -2475,15 +2468,10 @@
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 74 Max PS 10 Max PS+ 2 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Steel Guard 3</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
-        <is>
-          <t>Steel Guard 3</t>
-        </is>
-      </c>
-      <c r="DB8" t="inlineStr">
         <is>
           <t>Steel Guard 3 Cold as steel and impossible to break, dominates every duel, reads the game perfectly, and shuts down attacks before they even become a threat. Zima 74 CB PAC 76 SHO 38 PAS 54 DRI 62 DEF 75 PHY 75 R 2 ★ 4 CB 65.6 Zima 74 CB PAC 77 SHO 38 PAS 55 DRI 62 DEF 77 PHY 75 R 2 ★ 4 CB 75.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 74 Max PS 10 Max PS+ 2 UPGRADES +2 Sliding Tackle 78 +2 Short Pass 78 +2 Defensive Awareness 80 +2 Interceptions 80 +1 Jumping 75 +1 Sprint Speed 80 +2 Standing Tackle 80 +1 Acceleration 80 +1 Strength 78 +2 Vision 72 +1 Aggression 75 +1 Stamina 78 +2 Heading Acc. 76 2 8 in 3 days in 10 days 7% 93%</t>
         </is>
@@ -2560,10 +2548,10 @@
       <c r="X9" t="n">
         <v>60</v>
       </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="n">
+      <c r="Y9" t="n">
         <v>91</v>
       </c>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -2575,33 +2563,33 @@
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
+      <c r="AL9" t="n">
+        <v>30</v>
+      </c>
       <c r="AM9" t="n">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="AN9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO9" t="n">
         <v>93</v>
       </c>
-      <c r="AO9" t="n">
-        <v>60</v>
-      </c>
       <c r="AP9" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="AQ9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AR9" t="n">
         <v>90</v>
       </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>50</v>
+      </c>
       <c r="AU9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AV9" t="n">
         <v>94</v>
       </c>
+      <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr"/>
@@ -2609,129 +2597,133 @@
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
+      <c r="BD9" t="n">
+        <v>30</v>
+      </c>
       <c r="BE9" t="n">
+        <v>94</v>
+      </c>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="n">
         <v>30</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BI9" t="n">
+        <v>92</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>50</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>93</v>
+      </c>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>90</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>90</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>93</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>90</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>89</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>89</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>35</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>92</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>35</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>92</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>35</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>90</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>70</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>87</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>35</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>95</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>20</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>90</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>20</v>
+      </c>
+      <c r="CM9" t="n">
         <v>94</v>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BJ9" t="n">
+      <c r="CN9" t="n">
+        <v>25</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>91</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>50</v>
+      </c>
+      <c r="CQ9" t="n">
         <v>92</v>
       </c>
-      <c r="BK9" t="n">
-        <v>50</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>93</v>
-      </c>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
-      <c r="BO9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>90</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>90</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>93</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>90</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>89</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>89</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>35</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>92</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>35</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>92</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>35</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>90</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>70</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>87</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>35</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>95</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>20</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>90</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>20</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>94</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>25</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>91</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>50</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>92</v>
-      </c>
+      <c r="CR9" t="inlineStr"/>
       <c r="CS9" t="inlineStr"/>
-      <c r="CT9" t="inlineStr"/>
-      <c r="CU9" t="n">
+      <c r="CT9" t="n">
         <v>4</v>
       </c>
+      <c r="CU9" t="inlineStr"/>
       <c r="CV9" t="inlineStr"/>
-      <c r="CW9" t="inlineStr"/>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>+30 OVR 91 +4 WF +35 Standing Tackle 87 +25 Aggression 92 +30 Sprint Speed 93 +50 Positioning 90 +30 Crossing 94 +30 Composure 89 +30 Acceleration 93 +30 Dribbling 89 +35 Interceptions 92 +30 Short Pass 92 +50 Long Pass 93 +35 Defensive Awareness 90 +30 Balance 90 +30 Agility 90 +20 Stamina 94 +50 Shot Power 94 +35 Sliding Tackle 95 +20 Jumping 90 +35 Heading Acc. 92 +30 Reactions 93 +30 Ball Control 90 +25 Strength 91 3 7 Level 1 Dorgu 89 LM PAC 94 SHO 82 PAS 86 DRI 89 DEF 86 PHY 88 LB LW L 3 ★ 4 Dorgu 91 LM PAC 94 SHO 82 PAS 86 DRI 89 DEF 86 PHY 90 LB LW L 3 ★ 4 UPGRADES +30 OVR 91 +35 Standing Tackle 87 +25 Aggression 92 +30 Sprint Speed 93 +50 Positioning 90 7</t>
+        </is>
+      </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>+30 OVR 91 +4 WF +35 Standing Tackle 87 +25 Aggression 92 +30 Sprint Speed 93 +50 Positioning 90 +30 Crossing 94 +30 Composure 89 +30 Acceleration 93 +30 Dribbling 89 +35 Interceptions 92 +30 Short Pass 92 +50 Long Pass 93 +35 Defensive Awareness 90 +30 Balance 90 +30 Agility 90 +20 Stamina 94 +50 Shot Power 94 +35 Sliding Tackle 95 +20 Jumping 90 +35 Heading Acc. 92 +30 Reactions 93 +30 Ball Control 90 +25 Strength 91 3 7 Level 1 Dorgu 89 LM PAC 94 SHO 82 PAS 86 DRI 89 DEF 86 PHY 88 LB LW L 3 ★ 4 Dorgu 91 LM PAC 94 SHO 82 PAS 86 DRI 89 DEF 86 PHY 90 LB LW L 3 ★ 4 UPGRADES +30 OVR 91 +35 Standing Tackle 87 +25 Aggression 92 +30 Sprint Speed 93 +50 Positioning 90 7</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Position LB Excluded Position CB Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 9 days Coins Cost 50,000 Points Cost 300</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
@@ -2741,15 +2733,10 @@
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Position LB Excluded Position CB Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 9 days Coins Cost 50,000 Points Cost 300</t>
+          <t>Lightning Wingback 50,000 300</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
-        <is>
-          <t>Lightning Wingback 50,000 300</t>
-        </is>
-      </c>
-      <c r="DB9" t="inlineStr">
         <is>
           <t>Lightning Wingback 50,000 300 Lightning-fast wingback to dominate the flank. Explosive pace, relentless overlaps, and pinpoint delivery. A constant threat in attack while tracking back with power and precision. Savona 83 RB PAC 84 SHO 57 PAS 75 DRI 76 DEF 83 PHY 83 LB RM R 2 ★ 3 RB 80.1 Savona 91 RB PAC 93 SHO 64 PAS 81 DRI 90 DEF 90 PHY 92 LB RM R 2 ★ 5 RB 94.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Position LB Excluded Position CB Max PS 10 Max PS+ 2 UPGRADES +30 OVR 91 +4 WF +35 Standing Tackle 87 +25 Aggression 92 +30 Sprint Speed 93 +50 Positioning 90 +30 Crossing 94 +30 Composure 89 +30 Acceleration 93 +30 Dribbling 89 +35 Interceptions 92 +30 Short Pass 92 +50 Long Pass 93 +35 Defensive Awareness 90 +30 Balance 90 +30 Agility 90 +20 Stamina 94 +50 Shot Power 94 +35 Sliding Tackle 95 +20 Jumping 90 +35 Heading Acc. 92 +30 Reactions 93 +30 Ball Control 90 +25 Strength 91 3 7 in 2 days in 9 days 91% 9%</t>
         </is>
@@ -2829,31 +2816,31 @@
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
+      <c r="AP10" t="n">
+        <v>6</v>
+      </c>
       <c r="AQ10" t="n">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="AR10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>92</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU10" t="n">
         <v>90</v>
       </c>
-      <c r="AS10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT10" t="n">
+      <c r="AV10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW10" t="n">
         <v>92</v>
       </c>
-      <c r="AU10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>92</v>
-      </c>
+      <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="inlineStr"/>
@@ -2867,13 +2854,13 @@
       <c r="BI10" t="inlineStr"/>
       <c r="BJ10" t="inlineStr"/>
       <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
+      <c r="BL10" t="n">
+        <v>8</v>
+      </c>
       <c r="BM10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN10" t="n">
         <v>95</v>
       </c>
+      <c r="BN10" t="inlineStr"/>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr"/>
       <c r="BQ10" t="inlineStr"/>
@@ -2908,10 +2895,14 @@
       <c r="CT10" t="inlineStr"/>
       <c r="CU10" t="inlineStr"/>
       <c r="CV10" t="inlineStr"/>
-      <c r="CW10" t="inlineStr"/>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>+3 Positioning 90 +5 Finishing 92 +5 Long Shots 92 +3 Shot Power 90 +8 Curve 95 8 Level 1 Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 Bobb 88 RW PAC 93 SHO 89 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 UPGRADES +3 Positioning 90 +5 Finishing 92 8</t>
+        </is>
+      </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>+3 Positioning 90 +5 Finishing 92 +5 Long Shots 92 +3 Shot Power 90 +8 Curve 95 8 Level 1 Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 Bobb 88 RW PAC 93 SHO 89 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 UPGRADES +3 Positioning 90 +5 Finishing 92 8</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 Details Submit by in 1 day Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
@@ -2921,15 +2912,10 @@
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 Details Submit by in 1 day Expiry in 8 days Coins Cost Free Points Cost Free</t>
+          <t>Curve Your Enthusiasm 5</t>
         </is>
       </c>
       <c r="DA10" t="inlineStr">
-        <is>
-          <t>Curve Your Enthusiasm 5</t>
-        </is>
-      </c>
-      <c r="DB10" t="inlineStr">
         <is>
           <t>Curve Your Enthusiasm 5 Bend the game to your will and create moments of magic by transforming a player into a ball-bending specialist. Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 90 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 UPGRADES +3 Positioning 90 +5 Finishing 92 +5 Long Shots 92 +3 Shot Power 90 +8 Curve 95 8 in 1 day in 8 days 31% 69%</t>
         </is>
@@ -3002,10 +2988,10 @@
       <c r="X11" t="n">
         <v>34</v>
       </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="n">
+      <c r="Y11" t="n">
         <v>92</v>
       </c>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -3017,115 +3003,115 @@
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
+      <c r="AL11" t="n">
+        <v>34</v>
+      </c>
       <c r="AM11" t="n">
+        <v>93</v>
+      </c>
+      <c r="AN11" t="n">
         <v>34</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AO11" t="n">
+        <v>91</v>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>92</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>91</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>86</v>
+      </c>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC11" t="n">
         <v>93</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="BD11" t="n">
         <v>34</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="BE11" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>92</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BK11" t="n">
         <v>91</v>
       </c>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="n">
+      <c r="BL11" t="n">
         <v>17</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BM11" t="n">
+        <v>94</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>94</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>92</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BR11" t="n">
         <v>17</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="BS11" t="n">
         <v>91</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="BT11" t="n">
         <v>17</v>
       </c>
-      <c r="AX11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AY11" t="n">
+      <c r="BU11" t="n">
+        <v>91</v>
+      </c>
+      <c r="BV11" t="n">
         <v>17</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>86</v>
-      </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>93</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>90</v>
-      </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="n">
+      <c r="BW11" t="n">
+        <v>92</v>
+      </c>
+      <c r="BX11" t="n">
         <v>17</v>
       </c>
-      <c r="BJ11" t="n">
-        <v>92</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BL11" t="n">
+      <c r="BY11" t="n">
         <v>91</v>
       </c>
-      <c r="BM11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>94</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>94</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>92</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>91</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>91</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>92</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>91</v>
-      </c>
+      <c r="BZ11" t="inlineStr"/>
       <c r="CA11" t="inlineStr"/>
       <c r="CB11" t="inlineStr"/>
       <c r="CC11" t="inlineStr"/>
@@ -3143,19 +3129,23 @@
       <c r="CO11" t="inlineStr"/>
       <c r="CP11" t="inlineStr"/>
       <c r="CQ11" t="inlineStr"/>
-      <c r="CR11" t="inlineStr"/>
+      <c r="CR11" t="n">
+        <v>4</v>
+      </c>
       <c r="CS11" t="n">
-        <v>4</v>
-      </c>
-      <c r="CT11" t="n">
         <v>5</v>
       </c>
+      <c r="CT11" t="inlineStr"/>
       <c r="CU11" t="inlineStr"/>
       <c r="CV11" t="inlineStr"/>
-      <c r="CW11" t="inlineStr"/>
+      <c r="CW11" t="inlineStr">
+        <is>
+          <t>+17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 Level 1 Gnabry 90 CAM PAC 92 SHO 90 PAS 90 DRI 90 DEF 51 PHY 73 RM LM ST LW R 4 ★ 5 Gnabry 92 CAM PAC 92 SHO 90 PAS 91 DRI 90 DEF 51 PHY 73 RM LM ST LW R 4 ★ 5 UPGRADES +17 OVR 92 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 3</t>
+        </is>
+      </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>+17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 Level 1 Gnabry 90 CAM PAC 92 SHO 90 PAS 90 DRI 90 DEF 51 PHY 73 RM LM ST LW R 4 ★ 5 Gnabry 92 CAM PAC 92 SHO 90 PAS 91 DRI 90 DEF 51 PHY 73 RM LM ST LW R 4 ★ 5 UPGRADES +17 OVR 92 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 3</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 10 hours Expiry in 7 days Coins Cost 100,000 Points Cost 500</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
@@ -3165,15 +3155,10 @@
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 10 hours Expiry in 7 days Coins Cost 100,000 Points Cost 500</t>
+          <t>Cut In, Say Less 100,000 500</t>
         </is>
       </c>
       <c r="DA11" t="inlineStr">
-        <is>
-          <t>Cut In, Say Less 100,000 500</t>
-        </is>
-      </c>
-      <c r="DB11" t="inlineStr">
         <is>
           <t>Cut In, Say Less 100,000 500 Elevate your favourite qualified player with enhanced pace, dribbling, shooting, and passing, allowing them to cut inside, get past defenders, and deliver in decisive moments! Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 92 RW PAC 92 SHO 90 PAS 92 DRI 93 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 93.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 in 10 hours in 7 days 64% 36%</t>
         </is>
@@ -3250,40 +3235,40 @@
       <c r="X12" t="n">
         <v>20</v>
       </c>
-      <c r="Y12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>86</v>
+      </c>
       <c r="Z12" t="n">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="AA12" t="n">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="AB12" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="AC12" t="n">
+        <v>82</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>82</v>
+      </c>
+      <c r="AF12" t="n">
         <v>15</v>
       </c>
-      <c r="AD12" t="n">
-        <v>82</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>82</v>
-      </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="AH12" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="AI12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ12" t="n">
         <v>60</v>
       </c>
+      <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
@@ -3335,47 +3320,51 @@
       <c r="CG12" t="inlineStr"/>
       <c r="CH12" t="inlineStr"/>
       <c r="CI12" t="inlineStr"/>
-      <c r="CJ12" t="inlineStr"/>
+      <c r="CJ12" t="n">
+        <v>15</v>
+      </c>
       <c r="CK12" t="n">
+        <v>80</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>20</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>80</v>
+      </c>
+      <c r="CN12" t="n">
         <v>15</v>
       </c>
-      <c r="CL12" t="n">
-        <v>80</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>20</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>80</v>
-      </c>
       <c r="CO12" t="n">
+        <v>70</v>
+      </c>
+      <c r="CP12" t="n">
         <v>15</v>
       </c>
-      <c r="CP12" t="n">
-        <v>70</v>
-      </c>
       <c r="CQ12" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="CR12" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="CS12" t="n">
         <v>6</v>
       </c>
-      <c r="CT12" t="n">
-        <v>6</v>
-      </c>
+      <c r="CT12" t="inlineStr"/>
       <c r="CU12" t="inlineStr"/>
-      <c r="CV12" t="inlineStr"/>
+      <c r="CV12" t="inlineStr">
+        <is>
+          <t>CAM Shadow Striker ++; CAM Half Winger +</t>
+        </is>
+      </c>
       <c r="CW12" t="inlineStr">
         <is>
-          <t>CAM Shadow Striker ++; CAM Half Winger +</t>
+          <t>+10 OVR 86 +25 PAC 80 +10 SHO 82 +10 DRI 88 +5 DEF 60 +10 PAS 82 +4 SM +15 Jumping 80 +20 Stamina 80 +15 Aggression 65 +15 Strength 70 CAM Shadow Striker ++ CAM Half Winger + 1 6 Level 1 Cahill 85 ST PAC 80 SHO 85 PAS 76 DRI 81 DEF 62 PHY 86 CM CAM R 3 ★ 4 Cahill 86 ST PAC 80 SHO 85 PAS 76 DRI 86 DEF 62 PHY 86 CM CAM R 5 ★ 4 UPGRADES +10 OVR 86 +10 PAC 80 +5 SHO 82 +5 DRI 88 +2 SM 6</t>
         </is>
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>+10 OVR 86 +25 PAC 80 +10 SHO 82 +10 DRI 88 +5 DEF 60 +10 PAS 82 +4 SM +15 Jumping 80 +20 Stamina 80 +15 Aggression 65 +15 Strength 70 CAM Shadow Striker ++ CAM Half Winger + 1 6 Level 1 Cahill 85 ST PAC 80 SHO 85 PAS 76 DRI 81 DEF 62 PHY 86 CM CAM R 3 ★ 4 Cahill 86 ST PAC 80 SHO 85 PAS 76 DRI 86 DEF 62 PHY 86 CM CAM R 5 ★ 4 UPGRADES +10 OVR 86 +10 PAC 80 +5 SHO 82 +5 DRI 88 +2 SM 6</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 85 Position CAM Max PS 10 Max PS+ 1 Pace Max. 85 Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY12" t="inlineStr">
@@ -3385,15 +3374,10 @@
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 85 Position CAM Max PS 10 Max PS+ 1 Pace Max. 85 Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
+          <t>Star in Motion</t>
         </is>
       </c>
       <c r="DA12" t="inlineStr">
-        <is>
-          <t>Star in Motion</t>
-        </is>
-      </c>
-      <c r="DB12" t="inlineStr">
         <is>
           <t>Star in Motion Celebrate Jamal Musiala’s rise to football’s elite. Step into the spotlight with enhanced creativity, flair, and precision that define the face of the game’s new generation. Dunn 82 CM PAC 85 SHO 76 PAS 80 DRI 82 DEF 75 PHY 79 LB RM CAM R 4 ★ 4 RM 77.1 Dunn 86 CM PAC 85 SHO 82 PAS 82 DRI 88 DEF 75 PHY 79 LB RM CAM R 5 ★ 4 CAM 83.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 85 Position CAM Max PS 10 Max PS+ 1 Pace Max. 85 UPGRADES +10 OVR 86 +25 PAC 80 +10 SHO 82 +10 DRI 88 +5 DEF 60 +10 PAS 82 +4 SM +15 Jumping 80 +20 Stamina 80 +15 Aggression 65 +15 Strength 70 CAM Shadow Striker ++ CAM Half Winger + 1 6 Show less in 5 months in 5 months 90% 10%</t>
         </is>
@@ -3531,15 +3515,19 @@
       <c r="CS13" t="inlineStr"/>
       <c r="CT13" t="inlineStr"/>
       <c r="CU13" t="inlineStr"/>
-      <c r="CV13" t="inlineStr"/>
+      <c r="CV13" t="inlineStr">
+        <is>
+          <t>GK Sweeper Keeper +</t>
+        </is>
+      </c>
       <c r="CW13" t="inlineStr">
         <is>
-          <t>GK Sweeper Keeper +</t>
+          <t>. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Solid Evo 70% of GG users upvoted this Evolution. Vote Now! 70% 30% Completion Difficulty Easy Number of Games 0 Recommended Position - Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Casteels 82 GK DIV 82 HAN 79 KIC 74 REF 85 SPD 45 POS 83 L 1 ★ 2 GK 79.3 Strakosha 80 GK DIV 82 HAN 78 KIC 75 REF 83 SPD 50 POS 80 R 1 ★ 1 GK 78.5 Bounou 82 GK DIV 81 HAN 82 KIC 76 REF 85 SPD 38 POS 82 L 1 ★ 2 GK 78.4 Provedel 82 GK DIV 83 HAN 79 KIC 80 REF 84 SPD 42 POS 83 R 1 ★ 2 GK 78.2 Grabara 82 GK DIV 84 HAN 80 KIC 78 REF 87 SPD 46 POS 82 R 1 ★ 3 GK 77.8 Svilar 82 GK DIV 80 HAN 80 KIC 77 REF 85 SPD 58 POS 82 R 1 ★ 3 GK 77.6 Evolution Upgrades GK Sweeper Keeper + Level 1 Misa 82 GK DIV 84 HAN 77 KIC 77 REF 80 SPD 61 POS 84 L 1 ★ 3 Misa 82 GK DIV 84 HAN 77 KIC 77 REF 80 SPD 61 POS 84 L 1 ★ 3 UPGRADES GK Sweeper Keeper +</t>
         </is>
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Solid Evo 70% of GG users upvoted this Evolution. Vote Now! 70% 30% Completion Difficulty Easy Number of Games 0 Recommended Position - Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Casteels 82 GK DIV 82 HAN 79 KIC 74 REF 85 SPD 45 POS 83 L 1 ★ 2 GK 79.3 Strakosha 80 GK DIV 82 HAN 78 KIC 75 REF 83 SPD 50 POS 80 R 1 ★ 1 GK 78.5 Bounou 82 GK DIV 81 HAN 82 KIC 76 REF 85 SPD 38 POS 82 L 1 ★ 2 GK 78.4 Provedel 82 GK DIV 83 HAN 79 KIC 80 REF 84 SPD 42 POS 83 R 1 ★ 2 GK 78.2 Grabara 82 GK DIV 84 HAN 80 KIC 78 REF 87 SPD 46 POS 82 R 1 ★ 3 GK 77.8 Svilar 82 GK DIV 80 HAN 80 KIC 77 REF 85 SPD 58 POS 82 R 1 ★ 3 GK 77.6 Evolution Upgrades GK Sweeper Keeper + Level 1 Misa 82 GK DIV 84 HAN 77 KIC 77 REF 80 SPD 61 POS 84 L 1 ★ 3 Misa 82 GK DIV 84 HAN 77 KIC 77 REF 80 SPD 61 POS 84 L 1 ★ 3 UPGRADES GK Sweeper Keeper +</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Position GK Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
@@ -3549,15 +3537,10 @@
       </c>
       <c r="CZ13" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Position GK Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
+          <t>Intro to Training Camp EVOs I</t>
         </is>
       </c>
       <c r="DA13" t="inlineStr">
-        <is>
-          <t>Intro to Training Camp EVOs I</t>
-        </is>
-      </c>
-      <c r="DB13" t="inlineStr">
         <is>
           <t>Intro to Training Camp EVOs I Assign a GK to Training Camp Evolutions through the Companion App. When the training session concludes, collect their earned upgrades. Svilar 82 GK DIV 80 HAN 80 KIC 77 REF 85 SPD 58 POS 82 R 1 ★ 3 GK 76.7 Svilar 82 GK DIV 80 HAN 80 KIC 77 REF 85 SPD 58 POS 82 R 1 ★ 3 GK 77.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Position GK UPGRADES GK Sweeper Keeper + TRAINING TIME 1 day in 5 months in 5 months 70% 30%</t>
         </is>
@@ -3696,10 +3679,14 @@
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="inlineStr"/>
       <c r="CV14" t="inlineStr"/>
-      <c r="CW14" t="inlineStr"/>
+      <c r="CW14" t="inlineStr">
+        <is>
+          <t>. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Solid Evo 76% of GG users upvoted this Evolution. Vote Now! 76% 24% Completion Difficulty Easy Number of Games 0 Recommended Position ST Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Paintsil 81 LM PAC 92 SHO 77 PAS 75 DRI 85 DEF 40 PHY 75 RM LW R 4 ★ 3 LM 79.8 Chiesa 81 RM PAC 87 SHO 80 PAS 75 DRI 83 DEF 44 PHY 68 LM RW ST R 4 ★ 4 RM 79.5 Kouassi 80 LM PAC 94 SHO 79 PAS 71 DRI 80 DEF 37 PHY 75 RM LW R 4 ★ 4 RM 79.4 Adeyemi 81 RM PAC 96 SHO 76 PAS 72 DRI 82 DEF 36 PHY 69 CAM RW LW L 4 ★ 4 LW 79.1 Nusa 81 LM PAC 90 SHO 81 PAS 77 DRI 86 DEF 46 PHY 70 CAM LW R 4 ★ 4 LW 79.0 Saint-Maximin 79 LW PAC 90 SHO 71 PAS 70 DRI 87 DEF 29 PHY 68 LM R 5 ★ 4 LM 78.8 Evolution Upgrades 4 Level 1 Lukébakio 82 RM PAC 87 SHO 81 PAS 76 DRI 83 DEF 31 PHY 64 RW ST L 4 ★ 3 Lukébakio 82 RM PAC 87 SHO 81 PAS 76 DRI 83 DEF 31 PHY 64 RW ST L 4 ★ 3 UPGRADES 4</t>
+        </is>
+      </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Solid Evo 76% of GG users upvoted this Evolution. Vote Now! 76% 24% Completion Difficulty Easy Number of Games 0 Recommended Position ST Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Paintsil 81 LM PAC 92 SHO 77 PAS 75 DRI 85 DEF 40 PHY 75 RM LW R 4 ★ 3 LM 79.8 Chiesa 81 RM PAC 87 SHO 80 PAS 75 DRI 83 DEF 44 PHY 68 LM RW ST R 4 ★ 4 RM 79.5 Kouassi 80 LM PAC 94 SHO 79 PAS 71 DRI 80 DEF 37 PHY 75 RM LW R 4 ★ 4 RM 79.4 Adeyemi 81 RM PAC 96 SHO 76 PAS 72 DRI 82 DEF 36 PHY 69 CAM RW LW L 4 ★ 4 LW 79.1 Nusa 81 LM PAC 90 SHO 81 PAS 77 DRI 86 DEF 46 PHY 70 CAM LW R 4 ★ 4 LW 79.0 Saint-Maximin 79 LW PAC 90 SHO 71 PAS 70 DRI 87 DEF 29 PHY 68 LM R 5 ★ 4 LM 78.8 Evolution Upgrades 4 Level 1 Lukébakio 82 RM PAC 87 SHO 81 PAS 76 DRI 83 DEF 31 PHY 64 RW ST L 4 ★ 3 Lukébakio 82 RM PAC 87 SHO 81 PAS 76 DRI 83 DEF 31 PHY 64 RW ST L 4 ★ 3 UPGRADES 4</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Max PS 3 Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY14" t="inlineStr">
@@ -3709,15 +3696,10 @@
       </c>
       <c r="CZ14" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Max PS 3 Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
+          <t>Intro to Training Camp EVOs II</t>
         </is>
       </c>
       <c r="DA14" t="inlineStr">
-        <is>
-          <t>Intro to Training Camp EVOs II</t>
-        </is>
-      </c>
-      <c r="DB14" t="inlineStr">
         <is>
           <t>Intro to Training Camp EVOs II Assign a Player to Training Camp Evolutions through the Companion App. When the training session concludes, collect their earned upgrades. Sarr 82 CAM PAC 93 SHO 82 PAS 80 DRI 82 DEF 32 PHY 74 CM RW R 3 ★ 2 RW 76.3 Sarr 82 CAM PAC 93 SHO 82 PAS 80 DRI 82 DEF 32 PHY 74 CM RW R 3 ★ 2 RW 77.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Max PS 3 UPGRADES 4 TRAINING TIME 1 day in 5 months in 5 months 76% 24%</t>
         </is>
@@ -3778,22 +3760,22 @@
       <c r="X15" t="n">
         <v>2</v>
       </c>
-      <c r="Y15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>82</v>
+      </c>
       <c r="Z15" t="n">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
+        <v>83</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>83</v>
       </c>
-      <c r="AC15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>83</v>
-      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
@@ -3864,10 +3846,14 @@
       <c r="CT15" t="inlineStr"/>
       <c r="CU15" t="inlineStr"/>
       <c r="CV15" t="inlineStr"/>
-      <c r="CW15" t="inlineStr"/>
+      <c r="CW15" t="inlineStr">
+        <is>
+          <t>+1 OVR 82 +1 PAC 83 +1 SHO 83 Level 1 Bergvall 81 CM PAC 79 SHO 70 PAS 81 DRI 82 DEF 78 PHY 79 CDM CAM R 3 ★ 3 Bergvall 82 CM PAC 80 SHO 71 PAS 81 DRI 82 DEF 78 PHY 79 CDM CAM R 3 ★ 3 UPGRADES +1 OVR 82 +1 PAC 83 +1 SHO 83</t>
+        </is>
+      </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>+1 OVR 82 +1 PAC 83 +1 SHO 83 Level 1 Bergvall 81 CM PAC 79 SHO 70 PAS 81 DRI 82 DEF 78 PHY 79 CDM CAM R 3 ★ 3 Bergvall 82 CM PAC 80 SHO 71 PAS 81 DRI 82 DEF 78 PHY 79 CDM CAM R 3 ★ 3 UPGRADES +1 OVR 82 +1 PAC 83 +1 SHO 83</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 81 Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY15" t="inlineStr">
@@ -3877,15 +3863,10 @@
       </c>
       <c r="CZ15" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 81 Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
+          <t>Intro to Evolutions 2</t>
         </is>
       </c>
       <c r="DA15" t="inlineStr">
-        <is>
-          <t>Intro to Evolutions 2</t>
-        </is>
-      </c>
-      <c r="DB15" t="inlineStr">
         <is>
           <t>Intro to Evolutions 2 Welcome to FC 26! Kick things off by exploring Evolutions, where you can upgrade Players over time until they reach their stated maximum. Chiesa 81 RM PAC 87 SHO 80 PAS 75 DRI 83 DEF 44 PHY 68 LM RW ST R 4 ★ 4 LM 78.5 Chiesa 82 RM PAC 87 SHO 81 PAS 75 DRI 83 DEF 44 PHY 68 LM RW ST R 4 ★ 4 LM 78.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 81 UPGRADES +1 OVR 82 +1 PAC 83 +1 SHO 83 in 5 months in 5 months 80% 20%</t>
         </is>
@@ -4024,10 +4005,14 @@
       <c r="CT16" t="inlineStr"/>
       <c r="CU16" t="inlineStr"/>
       <c r="CV16" t="inlineStr"/>
-      <c r="CW16" t="inlineStr"/>
+      <c r="CW16" t="inlineStr">
+        <is>
+          <t>7 Level 1 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 UPGRADES 7</t>
+        </is>
+      </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>7 Level 1 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 UPGRADES 7</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY16" t="inlineStr">
@@ -4037,15 +4022,10 @@
       </c>
       <c r="CZ16" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
+          <t>Tiki Taka</t>
         </is>
       </c>
       <c r="DA16" t="inlineStr">
-        <is>
-          <t>Tiki Taka</t>
-        </is>
-      </c>
-      <c r="DB16" t="inlineStr">
         <is>
           <t>Tiki Taka Unlocked by completing the Score 5 task in the French TOTS Flash Rush objective Rijkaard 89 CDM PAC 84 SHO 80 PAS 85 DRI 86 DEF 89 PHY 88 CB CM R 4 ★ 4 CDM 87.2 Rijkaard 89 CDM PAC 84 SHO 80 PAS 85 DRI 86 DEF 89 PHY 88 CB CM R 4 ★ 4 CDM 88.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 5 days in 5 days 5% 95%</t>
         </is>
@@ -4184,10 +4164,14 @@
       <c r="CT17" t="inlineStr"/>
       <c r="CU17" t="inlineStr"/>
       <c r="CV17" t="inlineStr"/>
-      <c r="CW17" t="inlineStr"/>
+      <c r="CW17" t="inlineStr">
+        <is>
+          <t>3 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES 3</t>
+        </is>
+      </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>3 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES 3</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY17" t="inlineStr">
@@ -4197,15 +4181,10 @@
       </c>
       <c r="CZ17" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
+          <t>Rapid+</t>
         </is>
       </c>
       <c r="DA17" t="inlineStr">
-        <is>
-          <t>Rapid+</t>
-        </is>
-      </c>
-      <c r="DB17" t="inlineStr">
         <is>
           <t>Rapid+ Unlocked by completing the Assist in 10 task in the Ligue 1 TOTS Exhibition objective Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 84.0 Yılmaz 89 LM PAC 97 SHO 86 PAS 85 DRI 89 DEF 81 PHY 95 RM LW R 5 ★ 5 LM 85.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 8 days in 8 days 91% 9%</t>
         </is>
@@ -4344,10 +4323,14 @@
       <c r="CT18" t="inlineStr"/>
       <c r="CU18" t="inlineStr"/>
       <c r="CV18" t="inlineStr"/>
-      <c r="CW18" t="inlineStr"/>
+      <c r="CW18" t="inlineStr">
+        <is>
+          <t>3 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES 3</t>
+        </is>
+      </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>3 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES 3</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY18" t="inlineStr">
@@ -4357,15 +4340,10 @@
       </c>
       <c r="CZ18" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
+          <t>First Touch+</t>
         </is>
       </c>
       <c r="DA18" t="inlineStr">
-        <is>
-          <t>First Touch+</t>
-        </is>
-      </c>
-      <c r="DB18" t="inlineStr">
         <is>
           <t>First Touch+ Unlocked by completing the Score in 10 task in the Ligue 1 TOTS Exhibition objective Nanasi 89 LM PAC 89 SHO 87 PAS 89 DRI 91 DEF 45 PHY 80 CM CAM R 5 ★ 4 CAM 89.6 Nanasi 89 LM PAC 89 SHO 87 PAS 89 DRI 91 DEF 45 PHY 80 CM CAM R 5 ★ 4 CAM 90.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 8 days in 8 days 62% 38%</t>
         </is>
@@ -4504,10 +4482,14 @@
       <c r="CT19" t="inlineStr"/>
       <c r="CU19" t="inlineStr"/>
       <c r="CV19" t="inlineStr"/>
-      <c r="CW19" t="inlineStr"/>
+      <c r="CW19" t="inlineStr">
+        <is>
+          <t>7 Level 1 Ndoye 89 LM PAC 96 SHO 87 PAS 87 DRI 90 DEF 72 PHY 81 RM LW R 4 ★ 4 Ndoye 89 LM PAC 96 SHO 87 PAS 87 DRI 90 DEF 72 PHY 81 RM LW R 4 ★ 4 UPGRADES 7</t>
+        </is>
+      </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>7 Level 1 Ndoye 89 LM PAC 96 SHO 87 PAS 87 DRI 90 DEF 72 PHY 81 RM LW R 4 ★ 4 Ndoye 89 LM PAC 96 SHO 87 PAS 87 DRI 90 DEF 72 PHY 81 RM LW R 4 ★ 4 UPGRADES 7</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY19" t="inlineStr">
@@ -4517,15 +4499,10 @@
       </c>
       <c r="CZ19" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
+          <t>Tiki Taka and Low Driven Shot</t>
         </is>
       </c>
       <c r="DA19" t="inlineStr">
-        <is>
-          <t>Tiki Taka and Low Driven Shot</t>
-        </is>
-      </c>
-      <c r="DB19" t="inlineStr">
         <is>
           <t>Tiki Taka and Low Driven Shot Unlocked by completing the Score in 5 task in the TOTS: Champions Objective objective Luna 89 LM PAC 89 SHO 87 PAS 90 DRI 90 DEF 60 PHY 85 CAM LW R 4 ★ 5 CAM 86.2 Luna 89 LM PAC 89 SHO 87 PAS 90 DRI 90 DEF 60 PHY 85 CAM LW R 4 ★ 5 CAM 88.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 5 days in 5 days 9% 91%</t>
         </is>
@@ -4664,10 +4641,14 @@
       <c r="CT20" t="inlineStr"/>
       <c r="CU20" t="inlineStr"/>
       <c r="CV20" t="inlineStr"/>
-      <c r="CW20" t="inlineStr"/>
+      <c r="CW20" t="inlineStr">
+        <is>
+          <t>7 Level 1 Prinz 89 ST PAC 91 SHO 90 PAS 80 DRI 88 DEF 53 PHY 91 R 4 ★ 4 Prinz 89 ST PAC 91 SHO 90 PAS 80 DRI 88 DEF 53 PHY 91 R 4 ★ 4 UPGRADES 7</t>
+        </is>
+      </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>7 Level 1 Prinz 89 ST PAC 91 SHO 90 PAS 80 DRI 88 DEF 53 PHY 91 R 4 ★ 4 Prinz 89 ST PAC 91 SHO 90 PAS 80 DRI 88 DEF 53 PHY 91 R 4 ★ 4 UPGRADES 7</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY20" t="inlineStr">
@@ -4677,15 +4658,10 @@
       </c>
       <c r="CZ20" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
+          <t>Intercept and Pinged Pass</t>
         </is>
       </c>
       <c r="DA20" t="inlineStr">
-        <is>
-          <t>Intercept and Pinged Pass</t>
-        </is>
-      </c>
-      <c r="DB20" t="inlineStr">
         <is>
           <t>Intercept and Pinged Pass Unlocked by completing the Win 4 task in the TOTS: Champions Objective objective ter Stegen 89 GK DIV 87 HAN 87 KIC 91 REF 89 SPD 53 POS 87 R 1 ★ 4 GK 85.9 ter Stegen 89 GK DIV 87 HAN 87 KIC 91 REF 89 SPD 53 POS 87 R 1 ★ 4 GK 87.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 6 UPGRADES 7 in 5 days in 5 days 8% 92%</t>
         </is>
@@ -4824,10 +4800,14 @@
       <c r="CT21" t="inlineStr"/>
       <c r="CU21" t="inlineStr"/>
       <c r="CV21" t="inlineStr"/>
-      <c r="CW21" t="inlineStr"/>
+      <c r="CW21" t="inlineStr">
+        <is>
+          <t>2 Level 1 Eto'o 89 ST PAC 92 SHO 90 PAS 79 DRI 87 DEF 45 PHY 80 R 4 ★ 4 Eto'o 89 ST PAC 92 SHO 90 PAS 79 DRI 87 DEF 45 PHY 80 R 4 ★ 4 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>2 Level 1 Eto'o 89 ST PAC 92 SHO 90 PAS 79 DRI 87 DEF 45 PHY 80 R 4 ★ 4 Eto'o 89 ST PAC 92 SHO 90 PAS 79 DRI 87 DEF 45 PHY 80 R 4 ★ 4 UPGRADES 2</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY21" t="inlineStr">
@@ -4837,15 +4817,10 @@
       </c>
       <c r="CZ21" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Jockey+ &amp; Bruiser+</t>
         </is>
       </c>
       <c r="DA21" t="inlineStr">
-        <is>
-          <t>Jockey+ &amp; Bruiser+</t>
-        </is>
-      </c>
-      <c r="DB21" t="inlineStr">
         <is>
           <t>Jockey+ &amp; Bruiser+ Unlocked by completing the 3 Completions task in the Season 7 Spirit of Africa Weekly Play Completionist objective Dumfries 89 RB PAC 89 SHO 75 PAS 84 DRI 86 DEF 86 PHY 89 RM R 4 ★ 3 RB 85.3 Dumfries 89 RB PAC 89 SHO 75 PAS 84 DRI 86 DEF 86 PHY 89 RM R 4 ★ 3 RB 87.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 28 days in 28 days 12% 88%</t>
         </is>
@@ -4918,10 +4893,10 @@
       <c r="X22" t="n">
         <v>8</v>
       </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="n">
+      <c r="Y22" t="n">
         <v>90</v>
       </c>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
@@ -4933,147 +4908,151 @@
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
+      <c r="AL22" t="n">
+        <v>12</v>
+      </c>
       <c r="AM22" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN22" t="n">
         <v>12</v>
       </c>
-      <c r="AN22" t="n">
+      <c r="AO22" t="n">
         <v>90</v>
       </c>
-      <c r="AO22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>90</v>
-      </c>
+      <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr"/>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr"/>
       <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="inlineStr"/>
+      <c r="AV22" t="n">
+        <v>6</v>
+      </c>
       <c r="AW22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX22" t="n">
         <v>86</v>
       </c>
+      <c r="AX22" t="inlineStr"/>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="inlineStr"/>
-      <c r="BB22" t="inlineStr"/>
+      <c r="BB22" t="n">
+        <v>8</v>
+      </c>
       <c r="BC22" t="n">
+        <v>88</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>88</v>
+      </c>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="n">
         <v>8</v>
       </c>
-      <c r="BD22" t="n">
-        <v>88</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>88</v>
-      </c>
-      <c r="BG22" t="inlineStr"/>
-      <c r="BH22" t="inlineStr"/>
       <c r="BI22" t="n">
-        <v>8</v>
-      </c>
-      <c r="BJ22" t="n">
         <v>90</v>
       </c>
+      <c r="BJ22" t="inlineStr"/>
       <c r="BK22" t="inlineStr"/>
       <c r="BL22" t="inlineStr"/>
       <c r="BM22" t="inlineStr"/>
-      <c r="BN22" t="inlineStr"/>
+      <c r="BN22" t="n">
+        <v>12</v>
+      </c>
       <c r="BO22" t="n">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="BP22" t="n">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="BQ22" t="n">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="BR22" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="BS22" t="n">
-        <v>6</v>
-      </c>
-      <c r="BT22" t="n">
         <v>88</v>
       </c>
+      <c r="BT22" t="inlineStr"/>
       <c r="BU22" t="inlineStr"/>
       <c r="BV22" t="inlineStr"/>
       <c r="BW22" t="inlineStr"/>
-      <c r="BX22" t="inlineStr"/>
+      <c r="BX22" t="n">
+        <v>8</v>
+      </c>
       <c r="BY22" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ22" t="n">
         <v>8</v>
       </c>
-      <c r="BZ22" t="n">
+      <c r="CA22" t="n">
+        <v>92</v>
+      </c>
+      <c r="CB22" t="n">
+        <v>5</v>
+      </c>
+      <c r="CC22" t="n">
+        <v>88</v>
+      </c>
+      <c r="CD22" t="n">
+        <v>8</v>
+      </c>
+      <c r="CE22" t="n">
+        <v>91</v>
+      </c>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="n">
+        <v>6</v>
+      </c>
+      <c r="CI22" t="n">
         <v>90</v>
       </c>
-      <c r="CA22" t="n">
+      <c r="CJ22" t="n">
+        <v>5</v>
+      </c>
+      <c r="CK22" t="n">
+        <v>89</v>
+      </c>
+      <c r="CL22" t="n">
+        <v>5</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>89</v>
+      </c>
+      <c r="CN22" t="n">
         <v>8</v>
       </c>
-      <c r="CB22" t="n">
-        <v>92</v>
-      </c>
-      <c r="CC22" t="n">
-        <v>5</v>
-      </c>
-      <c r="CD22" t="n">
-        <v>88</v>
-      </c>
-      <c r="CE22" t="n">
+      <c r="CO22" t="n">
+        <v>90</v>
+      </c>
+      <c r="CP22" t="n">
         <v>8</v>
       </c>
-      <c r="CF22" t="n">
-        <v>91</v>
-      </c>
-      <c r="CG22" t="inlineStr"/>
-      <c r="CH22" t="inlineStr"/>
-      <c r="CI22" t="n">
-        <v>6</v>
-      </c>
-      <c r="CJ22" t="n">
+      <c r="CQ22" t="n">
         <v>90</v>
       </c>
-      <c r="CK22" t="n">
-        <v>5</v>
-      </c>
-      <c r="CL22" t="n">
-        <v>89</v>
-      </c>
-      <c r="CM22" t="n">
-        <v>5</v>
-      </c>
-      <c r="CN22" t="n">
-        <v>89</v>
-      </c>
-      <c r="CO22" t="n">
-        <v>8</v>
-      </c>
-      <c r="CP22" t="n">
-        <v>90</v>
-      </c>
-      <c r="CQ22" t="n">
-        <v>8</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>90</v>
-      </c>
+      <c r="CR22" t="inlineStr"/>
       <c r="CS22" t="inlineStr"/>
-      <c r="CT22" t="inlineStr"/>
-      <c r="CU22" t="n">
+      <c r="CT22" t="n">
         <v>4</v>
       </c>
+      <c r="CU22" t="inlineStr"/>
       <c r="CV22" t="inlineStr"/>
-      <c r="CW22" t="inlineStr"/>
+      <c r="CW22" t="inlineStr">
+        <is>
+          <t>+6 OVR 90 +4 WF +6 Acceleration 90 +6 Sprint Speed 90 +6 Agility 86 +8 Balance 90 +8 Interceptions 92 +8 Defensive Awareness 91 +6 Sliding Tackle 90 +8 Strength 90 +8 Aggression 90 +5 Stamina 89 +8 Vision 88 +6 Crossing 88 +8 Short Pass 90 +6 Long Shots 86 +5 Heading Acc. 88 +5 Jumping 89 +6 Reactions 88 +8 Composure 90 3 7 Level 1 Araujo 89 RB PAC 92 SHO 50 PAS 86 DRI 87 DEF 87 PHY 89 RM R 4 ★ 4 Araujo 90 RB PAC 92 SHO 50 PAS 86 DRI 87 DEF 87 PHY 89 RM R 4 ★ 4 UPGRADES +2 OVR 90 +6 Acceleration 90 +6 Sprint Speed 90 +6 Agility 86 +8 Balance 90 3</t>
+        </is>
+      </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>+6 OVR 90 +4 WF +6 Acceleration 90 +6 Sprint Speed 90 +6 Agility 86 +8 Balance 90 +8 Interceptions 92 +8 Defensive Awareness 91 +6 Sliding Tackle 90 +8 Strength 90 +8 Aggression 90 +5 Stamina 89 +8 Vision 88 +6 Crossing 88 +8 Short Pass 90 +6 Long Shots 86 +5 Heading Acc. 88 +5 Jumping 89 +6 Reactions 88 +8 Composure 90 3 7 Level 1 Araujo 89 RB PAC 92 SHO 50 PAS 86 DRI 87 DEF 87 PHY 89 RM R 4 ★ 4 Araujo 90 RB PAC 92 SHO 50 PAS 86 DRI 87 DEF 87 PHY 89 RM R 4 ★ 4 UPGRADES +2 OVR 90 +6 Acceleration 90 +6 Sprint Speed 90 +6 Agility 86 +8 Balance 90 3</t>
+          <t>Excluded Rarity World Tour Silver Stars Min Pos. 2 Overall Max. 89 Position CB, LB, RB Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY22" t="inlineStr">
@@ -5083,15 +5062,10 @@
       </c>
       <c r="CZ22" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Min Pos. 2 Overall Max. 89 Position CB, LB, RB Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
+          <t>Versatile Defender</t>
         </is>
       </c>
       <c r="DA22" t="inlineStr">
-        <is>
-          <t>Versatile Defender</t>
-        </is>
-      </c>
-      <c r="DB22" t="inlineStr">
         <is>
           <t>Versatile Defender Unlocked by completing the Darwin Cup objective Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 84.9 Walker 90 RB PAC 91 SHO 81 PAS 88 DRI 87 DEF 91 PHY 91 RM R 4 ★ 5 RB 92.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Min Pos. 2 Overall Max. 89 Position CB, LB, RB Max PS 10 Max PS+ 2 UPGRADES +6 OVR 90 +4 WF +6 Acceleration 90 +6 Sprint Speed 90 +6 Agility 86 +8 Balance 90 +8 Interceptions 92 +8 Defensive Awareness 91 +6 Sliding Tackle 90 +8 Strength 90 +8 Aggression 90 +5 Stamina 89 +8 Vision 88 +6 Crossing 88 +8 Short Pass 90 +6 Long Shots 86 +5 Heading Acc. 88 +5 Jumping 89 +6 Reactions 88 +8 Composure 90 3 7 in 4 days in 4 days 81% 19%</t>
         </is>
@@ -5234,10 +5208,14 @@
       <c r="CT23" t="inlineStr"/>
       <c r="CU23" t="inlineStr"/>
       <c r="CV23" t="inlineStr"/>
-      <c r="CW23" t="inlineStr"/>
+      <c r="CW23" t="inlineStr">
+        <is>
+          <t>3 7 Level 1 James 89 ST PAC 91 SHO 86 PAS 82 DRI 91 DEF 44 PHY 86 CAM R 4 ★ 5 James 89 ST PAC 91 SHO 86 PAS 82 DRI 91 DEF 44 PHY 86 CAM R 4 ★ 5 UPGRADES 3 7</t>
+        </is>
+      </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>3 7 Level 1 James 89 ST PAC 91 SHO 86 PAS 82 DRI 91 DEF 44 PHY 86 CAM R 4 ★ 5 James 89 ST PAC 91 SHO 86 PAS 82 DRI 91 DEF 44 PHY 86 CAM R 4 ★ 5 UPGRADES 3 7</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY23" t="inlineStr">
@@ -5247,15 +5225,10 @@
       </c>
       <c r="CZ23" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
+          <t>Technical+ and Finesse Shot</t>
         </is>
       </c>
       <c r="DA23" t="inlineStr">
-        <is>
-          <t>Technical+ and Finesse Shot</t>
-        </is>
-      </c>
-      <c r="DB23" t="inlineStr">
         <is>
           <t>Technical+ and Finesse Shot Unlocked by completing the Win Tournament task in the Darwin Cup objective Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 88.9 Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 89.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 3 7 in 4 days in 4 days 66% 34%</t>
         </is>
@@ -5398,10 +5371,14 @@
       <c r="CT24" t="inlineStr"/>
       <c r="CU24" t="inlineStr"/>
       <c r="CV24" t="inlineStr"/>
-      <c r="CW24" t="inlineStr"/>
+      <c r="CW24" t="inlineStr">
+        <is>
+          <t>2 8 Level 1 Matsukubo 89 CAM PAC 88 SHO 90 PAS 89 DRI 91 DEF 70 PHY 78 CM ST R 3 ★ 4 Matsukubo 89 CAM PAC 88 SHO 90 PAS 89 DRI 91 DEF 70 PHY 78 CM ST R 3 ★ 4 UPGRADES 2 8</t>
+        </is>
+      </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>2 8 Level 1 Matsukubo 89 CAM PAC 88 SHO 90 PAS 89 DRI 91 DEF 70 PHY 78 CM ST R 3 ★ 4 Matsukubo 89 CAM PAC 88 SHO 90 PAS 89 DRI 91 DEF 70 PHY 78 CM ST R 3 ★ 4 UPGRADES 2 8</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY24" t="inlineStr">
@@ -5411,15 +5388,10 @@
       </c>
       <c r="CZ24" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 4 days Coins Cost Free Points Cost Free</t>
+          <t>Anticipate+ and Intercept</t>
         </is>
       </c>
       <c r="DA24" t="inlineStr">
-        <is>
-          <t>Anticipate+ and Intercept</t>
-        </is>
-      </c>
-      <c r="DB24" t="inlineStr">
         <is>
           <t>Anticipate+ and Intercept Unlocked by completing the Win Quarter-Finals task in the Darwin Cup objective Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 84.9 Walker 89 RB PAC 90 SHO 81 PAS 85 DRI 85 DEF 88 PHY 88 RM R 4 ★ 4 RB 88.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 2 8 in 4 days in 4 days 33% 67%</t>
         </is>
@@ -5558,10 +5530,14 @@
       <c r="CT25" t="inlineStr"/>
       <c r="CU25" t="inlineStr"/>
       <c r="CV25" t="inlineStr"/>
-      <c r="CW25" t="inlineStr"/>
+      <c r="CW25" t="inlineStr">
+        <is>
+          <t>3 Level 1 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 UPGRADES 3</t>
+        </is>
+      </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>3 Level 1 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 UPGRADES 3</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY25" t="inlineStr">
@@ -5571,15 +5547,10 @@
       </c>
       <c r="CZ25" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
+          <t>Tiki Taka+</t>
         </is>
       </c>
       <c r="DA25" t="inlineStr">
-        <is>
-          <t>Tiki Taka+</t>
-        </is>
-      </c>
-      <c r="DB25" t="inlineStr">
         <is>
           <t>Tiki Taka+ Unlocked by completing the May The 3rd Be With You EVO SBC Adopo 88 CM PAC 86 SHO 86 PAS 88 DRI 88 DEF 87 PHY 90 CDM R 4 ★ 4 CM 89.1 Adopo 88 CM PAC 86 SHO 86 PAS 88 DRI 88 DEF 87 PHY 90 CDM R 4 ★ 4 CM 90.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 9 days in 9 days 84% 16%</t>
         </is>
@@ -5641,13 +5612,13 @@
         <v>2</v>
       </c>
       <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>8</v>
+      </c>
       <c r="AA26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB26" t="n">
         <v>91</v>
       </c>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
@@ -5655,13 +5626,13 @@
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
+      <c r="AJ26" t="n">
+        <v>6</v>
+      </c>
       <c r="AK26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AL26" t="n">
         <v>92</v>
       </c>
+      <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
@@ -5724,10 +5695,14 @@
       <c r="CT26" t="inlineStr"/>
       <c r="CU26" t="inlineStr"/>
       <c r="CV26" t="inlineStr"/>
-      <c r="CW26" t="inlineStr"/>
+      <c r="CW26" t="inlineStr">
+        <is>
+          <t>+1 OVR +4 PAC 91 +3 PHY 92 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 90 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 78 CAM ST LW R 5 ★ 5 UPGRADES +1 OVR +4 PAC 91 +3 PHY 92</t>
+        </is>
+      </c>
       <c r="CX26" t="inlineStr">
         <is>
-          <t>+1 OVR +4 PAC 91 +3 PHY 92 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 90 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 78 CAM ST LW R 5 ★ 5 UPGRADES +1 OVR +4 PAC 91 +3 PHY 92</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY26" t="inlineStr">
@@ -5737,15 +5712,10 @@
       </c>
       <c r="CZ26" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
+          <t>Turbo Strength</t>
         </is>
       </c>
       <c r="DA26" t="inlineStr">
-        <is>
-          <t>Turbo Strength</t>
-        </is>
-      </c>
-      <c r="DB26" t="inlineStr">
         <is>
           <t>Turbo Strength Unlocked by completing the Turbo Strength task in the Evolution Revolution objective Schlotterbeck 89 CB PAC 86 SHO 41 PAS 79 DRI 74 DEF 91 PHY 88 L 3 ★ 5 CB 89.3 Schlotterbeck 90 CB PAC 90 SHO 41 PAS 79 DRI 74 DEF 91 PHY 91 L 3 ★ 5 CB 91.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 UPGRADES +1 OVR +4 PAC 91 +3 PHY 92 in 1 day in 1 day 87% 13%</t>
         </is>
@@ -5833,23 +5803,23 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="inlineStr"/>
-      <c r="BB27" t="inlineStr"/>
+      <c r="BB27" t="n">
+        <v>6</v>
+      </c>
       <c r="BC27" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD27" t="n">
         <v>93</v>
       </c>
+      <c r="BD27" t="inlineStr"/>
       <c r="BE27" t="inlineStr"/>
       <c r="BF27" t="inlineStr"/>
       <c r="BG27" t="inlineStr"/>
-      <c r="BH27" t="inlineStr"/>
+      <c r="BH27" t="n">
+        <v>6</v>
+      </c>
       <c r="BI27" t="n">
-        <v>6</v>
-      </c>
-      <c r="BJ27" t="n">
         <v>93</v>
       </c>
+      <c r="BJ27" t="inlineStr"/>
       <c r="BK27" t="inlineStr"/>
       <c r="BL27" t="inlineStr"/>
       <c r="BM27" t="inlineStr"/>
@@ -5888,10 +5858,14 @@
       <c r="CT27" t="inlineStr"/>
       <c r="CU27" t="inlineStr"/>
       <c r="CV27" t="inlineStr"/>
-      <c r="CW27" t="inlineStr"/>
+      <c r="CW27" t="inlineStr">
+        <is>
+          <t>+3 Vision 93 +3 Short Pass 93 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 89 LM PAC 98 SHO 84 PAS 87 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES +3 Vision 93 +3 Short Pass 93</t>
+        </is>
+      </c>
       <c r="CX27" t="inlineStr">
         <is>
-          <t>+3 Vision 93 +3 Short Pass 93 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 89 LM PAC 98 SHO 84 PAS 87 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES +3 Vision 93 +3 Short Pass 93</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY27" t="inlineStr">
@@ -5901,15 +5875,10 @@
       </c>
       <c r="CZ27" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
+          <t>Pass IQ 5</t>
         </is>
       </c>
       <c r="DA27" t="inlineStr">
-        <is>
-          <t>Pass IQ 5</t>
-        </is>
-      </c>
-      <c r="DB27" t="inlineStr">
         <is>
           <t>Pass IQ 5 Unlocked by completing the Pass IQ task in the Evolution Revolution objective Hjulmand 88 CDM PAC 84 SHO 84 PAS 86 DRI 84 DEF 88 PHY 88 CM R 4 ★ 4 CM 89.8 Hjulmand 88 CDM PAC 84 SHO 84 PAS 88 DRI 84 DEF 88 PHY 88 CM R 4 ★ 4 CM 90.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 UPGRADES +3 Vision 93 +3 Short Pass 93 in 1 day in 1 day 88% 13%</t>
         </is>
@@ -5993,19 +5962,19 @@
       <c r="AQ28" t="inlineStr"/>
       <c r="AR28" t="inlineStr"/>
       <c r="AS28" t="inlineStr"/>
-      <c r="AT28" t="inlineStr"/>
+      <c r="AT28" t="n">
+        <v>16</v>
+      </c>
       <c r="AU28" t="n">
+        <v>93</v>
+      </c>
+      <c r="AV28" t="n">
         <v>16</v>
       </c>
-      <c r="AV28" t="n">
+      <c r="AW28" t="n">
         <v>93</v>
       </c>
-      <c r="AW28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>93</v>
-      </c>
+      <c r="AX28" t="inlineStr"/>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="inlineStr"/>
@@ -6056,10 +6025,14 @@
       <c r="CT28" t="inlineStr"/>
       <c r="CU28" t="inlineStr"/>
       <c r="CV28" t="inlineStr"/>
-      <c r="CW28" t="inlineStr"/>
+      <c r="CW28" t="inlineStr">
+        <is>
+          <t>+8 Shot Power 93 +8 Long Shots 93 8 Level 1 Francisco Conceição 89 RM PAC 93 SHO 86 PAS 87 DRI 91 DEF 45 PHY 70 CAM RW L 4 ★ 3 Francisco Conceição 89 RM PAC 93 SHO 88 PAS 87 DRI 91 DEF 45 PHY 70 CAM RW L 4 ★ 3 UPGRADES +8 Shot Power 93 +8 Long Shots 93 8</t>
+        </is>
+      </c>
       <c r="CX28" t="inlineStr">
         <is>
-          <t>+8 Shot Power 93 +8 Long Shots 93 8 Level 1 Francisco Conceição 89 RM PAC 93 SHO 86 PAS 87 DRI 91 DEF 45 PHY 70 CAM RW L 4 ★ 3 Francisco Conceição 89 RM PAC 93 SHO 88 PAS 87 DRI 91 DEF 45 PHY 70 CAM RW L 4 ★ 3 UPGRADES +8 Shot Power 93 +8 Long Shots 93 8</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY28" t="inlineStr">
@@ -6069,15 +6042,10 @@
       </c>
       <c r="CZ28" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
+          <t>From Distance</t>
         </is>
       </c>
       <c r="DA28" t="inlineStr">
-        <is>
-          <t>From Distance</t>
-        </is>
-      </c>
-      <c r="DB28" t="inlineStr">
         <is>
           <t>From Distance Unlocked by completing the From Distance task in the Evolution Revolution objective Carlos Espí 88 ST PAC 91 SHO 86 PAS 80 DRI 88 DEF 58 PHY 94 R 4 ★ 4 ST 89.3 Carlos Espí 88 ST PAC 91 SHO 89 PAS 80 DRI 88 DEF 58 PHY 94 R 4 ★ 4 ST 89.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +8 Shot Power 93 +8 Long Shots 93 8 in 1 day in 1 day 85% 15%</t>
         </is>
@@ -6216,10 +6184,14 @@
       <c r="CT29" t="inlineStr"/>
       <c r="CU29" t="inlineStr"/>
       <c r="CV29" t="inlineStr"/>
-      <c r="CW29" t="inlineStr"/>
+      <c r="CW29" t="inlineStr">
+        <is>
+          <t>8 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES 8</t>
+        </is>
+      </c>
       <c r="CX29" t="inlineStr">
         <is>
-          <t>8 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES 8</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY29" t="inlineStr">
@@ -6229,15 +6201,10 @@
       </c>
       <c r="CZ29" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
+          <t>Intercept &amp; Aerial Fortress</t>
         </is>
       </c>
       <c r="DA29" t="inlineStr">
-        <is>
-          <t>Intercept &amp; Aerial Fortress</t>
-        </is>
-      </c>
-      <c r="DB29" t="inlineStr">
         <is>
           <t>Intercept &amp; Aerial Fortress Unlocked by completing the Defensive Instinct task in the Evolution Revolution objective António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 86.6 António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 1 day in 1 day 33% 67%</t>
         </is>
@@ -6376,10 +6343,14 @@
       <c r="CT30" t="inlineStr"/>
       <c r="CU30" t="inlineStr"/>
       <c r="CV30" t="inlineStr"/>
-      <c r="CW30" t="inlineStr"/>
+      <c r="CW30" t="inlineStr">
+        <is>
+          <t>8 Level 1 Eto'o 89 ST PAC 92 SHO 90 PAS 79 DRI 87 DEF 45 PHY 80 R 4 ★ 4 Eto'o 89 ST PAC 92 SHO 90 PAS 79 DRI 87 DEF 45 PHY 80 R 4 ★ 4 UPGRADES 8</t>
+        </is>
+      </c>
       <c r="CX30" t="inlineStr">
         <is>
-          <t>8 Level 1 Eto'o 89 ST PAC 92 SHO 90 PAS 79 DRI 87 DEF 45 PHY 80 R 4 ★ 4 Eto'o 89 ST PAC 92 SHO 90 PAS 79 DRI 87 DEF 45 PHY 80 R 4 ★ 4 UPGRADES 8</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 7 days Expiry in 7 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY30" t="inlineStr">
@@ -6389,15 +6360,10 @@
       </c>
       <c r="CZ30" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 7 days Expiry in 7 days Coins Cost Free Points Cost Free</t>
+          <t>Speed to Finish</t>
         </is>
       </c>
       <c r="DA30" t="inlineStr">
-        <is>
-          <t>Speed to Finish</t>
-        </is>
-      </c>
-      <c r="DB30" t="inlineStr">
         <is>
           <t>Speed to Finish Unlocked by completing the Score in 5 task in the TOTS: Champions Objective objective Mayulu 89 CM PAC 88 SHO 88 PAS 90 DRI 92 DEF 80 PHY 82 L 3 ★ 5 CM 88.3 Mayulu 89 CM PAC 88 SHO 88 PAS 90 DRI 92 DEF 80 PHY 82 L 3 ★ 5 CM 89.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 7 days in 7 days 62% 38%</t>
         </is>
@@ -6536,10 +6502,14 @@
       <c r="CT31" t="inlineStr"/>
       <c r="CU31" t="inlineStr"/>
       <c r="CV31" t="inlineStr"/>
-      <c r="CW31" t="inlineStr"/>
+      <c r="CW31" t="inlineStr">
+        <is>
+          <t>8 Level 1 Uzun 89 CAM PAC 88 SHO 90 PAS 88 DRI 92 DEF 40 PHY 83 CM ST R 4 ★ 4 Uzun 89 CAM PAC 88 SHO 90 PAS 88 DRI 92 DEF 40 PHY 83 CM ST R 4 ★ 4 UPGRADES 8</t>
+        </is>
+      </c>
       <c r="CX31" t="inlineStr">
         <is>
-          <t>8 Level 1 Uzun 89 CAM PAC 88 SHO 90 PAS 88 DRI 92 DEF 40 PHY 83 CM ST R 4 ★ 4 Uzun 89 CAM PAC 88 SHO 90 PAS 88 DRI 92 DEF 40 PHY 83 CM ST R 4 ★ 4 UPGRADES 8</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 7 days Expiry in 7 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY31" t="inlineStr">
@@ -6549,15 +6519,10 @@
       </c>
       <c r="CZ31" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 Details Submit by in 7 days Expiry in 7 days Coins Cost Free Points Cost Free</t>
+          <t>Creative Playmaker</t>
         </is>
       </c>
       <c r="DA31" t="inlineStr">
-        <is>
-          <t>Creative Playmaker</t>
-        </is>
-      </c>
-      <c r="DB31" t="inlineStr">
         <is>
           <t>Creative Playmaker Unlocked by completing the Win 5 task in the TOTS: Champions Objective objective Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 88.9 Becker 89 ST PAC 96 SHO 88 PAS 84 DRI 89 DEF 51 PHY 85 RM LM CAM R 4 ★ 5 ST 90.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 7 UPGRADES 8 in 7 days in 7 days 33% 67%</t>
         </is>
@@ -6700,10 +6665,14 @@
       <c r="CT32" t="inlineStr"/>
       <c r="CU32" t="inlineStr"/>
       <c r="CV32" t="inlineStr"/>
-      <c r="CW32" t="inlineStr"/>
+      <c r="CW32" t="inlineStr">
+        <is>
+          <t>2 8 Level 1 Matsukubo 89 CAM PAC 88 SHO 90 PAS 89 DRI 91 DEF 70 PHY 78 CM ST R 3 ★ 4 Matsukubo 89 CAM PAC 88 SHO 90 PAS 89 DRI 91 DEF 70 PHY 78 CM ST R 3 ★ 4 UPGRADES 2 8</t>
+        </is>
+      </c>
       <c r="CX32" t="inlineStr">
         <is>
-          <t>2 8 Level 1 Matsukubo 89 CAM PAC 88 SHO 90 PAS 89 DRI 91 DEF 70 PHY 78 CM ST R 3 ★ 4 Matsukubo 89 CAM PAC 88 SHO 90 PAS 89 DRI 91 DEF 70 PHY 78 CM ST R 3 ★ 4 UPGRADES 2 8</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY32" t="inlineStr">
@@ -6713,15 +6682,10 @@
       </c>
       <c r="CZ32" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
+          <t>Long Ball Pass+ &amp; Pinged Pass</t>
         </is>
       </c>
       <c r="DA32" t="inlineStr">
-        <is>
-          <t>Long Ball Pass+ &amp; Pinged Pass</t>
-        </is>
-      </c>
-      <c r="DB32" t="inlineStr">
         <is>
           <t>Long Ball Pass+ &amp; Pinged Pass Unlocked by completing the Assist in 10 task in the Bundesliga TOTS Exhibition objective Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES 2 8 in 1 day in 1 day 10% 90%</t>
         </is>
@@ -6860,10 +6824,14 @@
       <c r="CT33" t="inlineStr"/>
       <c r="CU33" t="inlineStr"/>
       <c r="CV33" t="inlineStr"/>
-      <c r="CW33" t="inlineStr"/>
+      <c r="CW33" t="inlineStr">
+        <is>
+          <t>2 Level 1 De Ketelaere 89 CAM PAC 88 SHO 89 PAS 89 DRI 90 DEF 64 PHY 78 CM ST L 5 ★ 5 De Ketelaere 89 CAM PAC 88 SHO 89 PAS 89 DRI 90 DEF 64 PHY 78 CM ST L 5 ★ 5 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX33" t="inlineStr">
         <is>
-          <t>2 Level 1 De Ketelaere 89 CAM PAC 88 SHO 89 PAS 89 DRI 90 DEF 64 PHY 78 CM ST L 5 ★ 5 De Ketelaere 89 CAM PAC 88 SHO 89 PAS 89 DRI 90 DEF 64 PHY 78 CM ST L 5 ★ 5 UPGRADES 2</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY33" t="inlineStr">
@@ -6873,15 +6841,10 @@
       </c>
       <c r="CZ33" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
+          <t>Finesse Shot+</t>
         </is>
       </c>
       <c r="DA33" t="inlineStr">
-        <is>
-          <t>Finesse Shot+</t>
-        </is>
-      </c>
-      <c r="DB33" t="inlineStr">
         <is>
           <t>Finesse Shot+ Unlocked by completing the Score in 10 task in the Bundesliga TOTS Exhibition objective Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 88.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 1 day in 1 day 69% 31%</t>
         </is>
@@ -6950,10 +6913,10 @@
       <c r="X34" t="n">
         <v>30</v>
       </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="n">
+      <c r="Y34" t="n">
         <v>89</v>
       </c>
+      <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
@@ -6965,143 +6928,143 @@
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
+      <c r="AL34" t="n">
+        <v>50</v>
+      </c>
       <c r="AM34" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>93</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>89</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>40</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>90</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>90</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>93</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>87</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>87</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>86</v>
+      </c>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>88</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>87</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>15</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>89</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>25</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>88</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>87</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>90</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>25</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>89</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>90</v>
+      </c>
+      <c r="BX34" t="n">
         <v>50</v>
       </c>
-      <c r="AN34" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>93</v>
-      </c>
-      <c r="AQ34" t="n">
+      <c r="BY34" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ34" t="inlineStr"/>
+      <c r="CA34" t="inlineStr"/>
+      <c r="CB34" t="n">
         <v>20</v>
       </c>
-      <c r="AR34" t="n">
-        <v>89</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>90</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>40</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>90</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>90</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>93</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB34" t="n">
+      <c r="CC34" t="n">
         <v>87</v>
       </c>
-      <c r="BC34" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>87</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>86</v>
-      </c>
-      <c r="BG34" t="inlineStr"/>
-      <c r="BH34" t="inlineStr"/>
-      <c r="BI34" t="n">
-        <v>15</v>
-      </c>
-      <c r="BJ34" t="n">
-        <v>88</v>
-      </c>
-      <c r="BK34" t="n">
-        <v>10</v>
-      </c>
-      <c r="BL34" t="n">
-        <v>87</v>
-      </c>
-      <c r="BM34" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN34" t="n">
-        <v>89</v>
-      </c>
-      <c r="BO34" t="n">
-        <v>25</v>
-      </c>
-      <c r="BP34" t="n">
-        <v>88</v>
-      </c>
-      <c r="BQ34" t="n">
-        <v>25</v>
-      </c>
-      <c r="BR34" t="n">
-        <v>87</v>
-      </c>
-      <c r="BS34" t="n">
-        <v>25</v>
-      </c>
-      <c r="BT34" t="n">
-        <v>90</v>
-      </c>
-      <c r="BU34" t="n">
-        <v>25</v>
-      </c>
-      <c r="BV34" t="n">
-        <v>89</v>
-      </c>
-      <c r="BW34" t="n">
-        <v>25</v>
-      </c>
-      <c r="BX34" t="n">
-        <v>90</v>
-      </c>
-      <c r="BY34" t="n">
-        <v>50</v>
-      </c>
-      <c r="BZ34" t="n">
-        <v>88</v>
-      </c>
-      <c r="CA34" t="inlineStr"/>
-      <c r="CB34" t="inlineStr"/>
-      <c r="CC34" t="n">
-        <v>20</v>
-      </c>
-      <c r="CD34" t="n">
-        <v>87</v>
-      </c>
+      <c r="CD34" t="inlineStr"/>
       <c r="CE34" t="inlineStr"/>
       <c r="CF34" t="inlineStr"/>
       <c r="CG34" t="inlineStr"/>
       <c r="CH34" t="inlineStr"/>
       <c r="CI34" t="inlineStr"/>
-      <c r="CJ34" t="inlineStr"/>
+      <c r="CJ34" t="n">
+        <v>30</v>
+      </c>
       <c r="CK34" t="n">
-        <v>30</v>
-      </c>
-      <c r="CL34" t="n">
         <v>92</v>
       </c>
+      <c r="CL34" t="inlineStr"/>
       <c r="CM34" t="inlineStr"/>
       <c r="CN34" t="inlineStr"/>
       <c r="CO34" t="inlineStr"/>
@@ -7112,10 +7075,14 @@
       <c r="CT34" t="inlineStr"/>
       <c r="CU34" t="inlineStr"/>
       <c r="CV34" t="inlineStr"/>
-      <c r="CW34" t="inlineStr"/>
+      <c r="CW34" t="inlineStr">
+        <is>
+          <t>+15 OVR 89 +25 Acceleration 90 +20 Shot Power 90 +10 Vision 87 +25 Composure 88 +25 Sprint Speed 93 +20 Long Shots 90 +10 Long Pass 87 +25 Dribbling 90 +20 Positioning 89 +20 Volleys 93 +15 Short Pass 88 +25 Ball Control 89 +30 Jumping 92 +20 Finishing 90 +10 Crossing 86 +15 Curve 89 +25 Reactions 90 +20 Heading Acc. 87 +20 Penalties 87 +15 Fk Accuracy 88 +25 Agility 88 +25 Balance 87 2 8 Level 1 Undav 87 ST PAC 86 SHO 89 PAS 81 DRI 87 DEF 40 PHY 84 CAM R 3 ★ 5 Undav 89 ST PAC 88 SHO 89 PAS 81 DRI 87 DEF 40 PHY 84 CAM R 3 ★ 5 UPGRADES +15 OVR 89 +25 Acceleration 90 +20 Shot Power 90 +10 Vision 87 +25 Composure 88 8</t>
+        </is>
+      </c>
       <c r="CX34" t="inlineStr">
         <is>
-          <t>+15 OVR 89 +25 Acceleration 90 +20 Shot Power 90 +10 Vision 87 +25 Composure 88 +25 Sprint Speed 93 +20 Long Shots 90 +10 Long Pass 87 +25 Dribbling 90 +20 Positioning 89 +20 Volleys 93 +15 Short Pass 88 +25 Ball Control 89 +30 Jumping 92 +20 Finishing 90 +10 Crossing 86 +15 Curve 89 +25 Reactions 90 +20 Heading Acc. 87 +20 Penalties 87 +15 Fk Accuracy 88 +25 Agility 88 +25 Balance 87 2 8 Level 1 Undav 87 ST PAC 86 SHO 89 PAS 81 DRI 87 DEF 40 PHY 84 CAM R 3 ★ 5 Undav 89 ST PAC 88 SHO 89 PAS 81 DRI 87 DEF 40 PHY 84 CAM R 3 ★ 5 UPGRADES +15 OVR 89 +25 Acceleration 90 +20 Shot Power 90 +10 Vision 87 +25 Composure 88 8</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 87 Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY34" t="inlineStr">
@@ -7125,15 +7092,10 @@
       </c>
       <c r="CZ34" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 87 Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Welsh Wonder Strike [Store]</t>
         </is>
       </c>
       <c r="DA34" t="inlineStr">
-        <is>
-          <t>Welsh Wonder Strike [Store]</t>
-        </is>
-      </c>
-      <c r="DB34" t="inlineStr">
         <is>
           <t>Welsh Wonder Strike [Store] Unlocked by purchasing the Captains' Armband EVO pack. Lukaku 85 CAM PAC 84 SHO 86 PAS 80 DRI 81 DEF 42 PHY 85 ST L 4 ★ 4 ST 80.4 Lukaku 89 CAM PAC 92 SHO 90 PAS 86 DRI 89 DEF 42 PHY 85 ST L 4 ★ 4 ST 90.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 87 Max PS 10 Max PS+ 2 UPGRADES +15 OVR 89 +25 Acceleration 90 +20 Shot Power 90 +10 Vision 87 +25 Composure 88 +25 Sprint Speed 93 +20 Long Shots 90 +10 Long Pass 87 +25 Dribbling 90 +20 Positioning 89 +20 Volleys 93 +15 Short Pass 88 +25 Ball Control 89 +30 Jumping 92 +20 Finishing 90 +10 Crossing 86 +15 Curve 89 +25 Reactions 90 +20 Heading Acc. 87 +20 Penalties 87 +15 Fk Accuracy 88 +25 Agility 88 +25 Balance 87 2 8 TRAINING TIME 31 minutes in 2 days in 2 days 18% 82%</t>
         </is>
@@ -7214,10 +7176,10 @@
       <c r="X35" t="n">
         <v>60</v>
       </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="n">
+      <c r="Y35" t="n">
         <v>91</v>
       </c>
+      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -7229,19 +7191,19 @@
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
+      <c r="AL35" t="n">
+        <v>60</v>
+      </c>
       <c r="AM35" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="AN35" t="n">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="AO35" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP35" t="n">
         <v>88</v>
       </c>
+      <c r="AP35" t="inlineStr"/>
       <c r="AQ35" t="inlineStr"/>
       <c r="AR35" t="inlineStr"/>
       <c r="AS35" t="inlineStr"/>
@@ -7253,133 +7215,137 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="inlineStr"/>
-      <c r="BB35" t="inlineStr"/>
+      <c r="BB35" t="n">
+        <v>30</v>
+      </c>
       <c r="BC35" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD35" t="n">
         <v>70</v>
       </c>
+      <c r="BD35" t="inlineStr"/>
       <c r="BE35" t="inlineStr"/>
       <c r="BF35" t="inlineStr"/>
       <c r="BG35" t="inlineStr"/>
-      <c r="BH35" t="inlineStr"/>
+      <c r="BH35" t="n">
+        <v>60</v>
+      </c>
       <c r="BI35" t="n">
+        <v>90</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>30</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>85</v>
+      </c>
+      <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
+      <c r="BN35" t="n">
+        <v>30</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>73</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>30</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>80</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>95</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>30</v>
+      </c>
+      <c r="BU35" t="n">
+        <v>75</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>75</v>
+      </c>
+      <c r="BX35" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>91</v>
+      </c>
+      <c r="BZ35" t="n">
+        <v>30</v>
+      </c>
+      <c r="CA35" t="n">
+        <v>93</v>
+      </c>
+      <c r="CB35" t="n">
         <v>60</v>
       </c>
-      <c r="BJ35" t="n">
+      <c r="CC35" t="n">
+        <v>92</v>
+      </c>
+      <c r="CD35" t="n">
+        <v>60</v>
+      </c>
+      <c r="CE35" t="n">
+        <v>95</v>
+      </c>
+      <c r="CF35" t="n">
+        <v>30</v>
+      </c>
+      <c r="CG35" t="n">
+        <v>92</v>
+      </c>
+      <c r="CH35" t="n">
+        <v>30</v>
+      </c>
+      <c r="CI35" t="n">
+        <v>92</v>
+      </c>
+      <c r="CJ35" t="n">
+        <v>30</v>
+      </c>
+      <c r="CK35" t="n">
         <v>90</v>
       </c>
-      <c r="BK35" t="n">
+      <c r="CL35" t="n">
         <v>30</v>
       </c>
-      <c r="BL35" t="n">
+      <c r="CM35" t="n">
+        <v>90</v>
+      </c>
+      <c r="CN35" t="n">
+        <v>30</v>
+      </c>
+      <c r="CO35" t="n">
+        <v>92</v>
+      </c>
+      <c r="CP35" t="n">
+        <v>30</v>
+      </c>
+      <c r="CQ35" t="n">
         <v>85</v>
       </c>
-      <c r="BM35" t="inlineStr"/>
-      <c r="BN35" t="inlineStr"/>
-      <c r="BO35" t="n">
-        <v>30</v>
-      </c>
-      <c r="BP35" t="n">
-        <v>73</v>
-      </c>
-      <c r="BQ35" t="n">
-        <v>30</v>
-      </c>
-      <c r="BR35" t="n">
-        <v>80</v>
-      </c>
-      <c r="BS35" t="n">
-        <v>30</v>
-      </c>
-      <c r="BT35" t="n">
-        <v>95</v>
-      </c>
-      <c r="BU35" t="n">
-        <v>30</v>
-      </c>
-      <c r="BV35" t="n">
-        <v>75</v>
-      </c>
-      <c r="BW35" t="n">
-        <v>30</v>
-      </c>
-      <c r="BX35" t="n">
-        <v>75</v>
-      </c>
-      <c r="BY35" t="n">
-        <v>30</v>
-      </c>
-      <c r="BZ35" t="n">
-        <v>91</v>
-      </c>
-      <c r="CA35" t="n">
-        <v>30</v>
-      </c>
-      <c r="CB35" t="n">
-        <v>93</v>
-      </c>
-      <c r="CC35" t="n">
-        <v>60</v>
-      </c>
-      <c r="CD35" t="n">
-        <v>92</v>
-      </c>
-      <c r="CE35" t="n">
-        <v>60</v>
-      </c>
-      <c r="CF35" t="n">
-        <v>95</v>
-      </c>
-      <c r="CG35" t="n">
-        <v>30</v>
-      </c>
-      <c r="CH35" t="n">
-        <v>92</v>
-      </c>
-      <c r="CI35" t="n">
-        <v>30</v>
-      </c>
-      <c r="CJ35" t="n">
-        <v>92</v>
-      </c>
-      <c r="CK35" t="n">
-        <v>30</v>
-      </c>
-      <c r="CL35" t="n">
-        <v>90</v>
-      </c>
-      <c r="CM35" t="n">
-        <v>30</v>
-      </c>
-      <c r="CN35" t="n">
-        <v>90</v>
-      </c>
-      <c r="CO35" t="n">
-        <v>30</v>
-      </c>
-      <c r="CP35" t="n">
-        <v>92</v>
-      </c>
-      <c r="CQ35" t="n">
-        <v>30</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>85</v>
-      </c>
+      <c r="CR35" t="inlineStr"/>
       <c r="CS35" t="inlineStr"/>
       <c r="CT35" t="inlineStr"/>
       <c r="CU35" t="inlineStr"/>
-      <c r="CV35" t="inlineStr"/>
+      <c r="CV35" t="inlineStr">
+        <is>
+          <t>CB Defender ++; CB Stopper ++; CB Wideback ++</t>
+        </is>
+      </c>
       <c r="CW35" t="inlineStr">
         <is>
-          <t>CB Defender ++; CB Stopper ++; CB Wideback ++</t>
+          <t>+30 OVR 91 +30 Acceleration 87 +30 Short Pass 90 +30 Heading Acc. 92 +30 Defensive Awareness 95 +30 Sprint Speed 88 +30 Vision 70 +30 Agility 73 +30 Balance 80 +30 Long Pass 85 +30 Ball Control 75 +30 Dribbling 75 +30 Reactions 95 +30 Composure 91 +30 Interceptions 93 +30 Standing Tackle 92 +30 Sliding Tackle 92 +30 Stamina 90 +30 Strength 92 +30 Jumping 90 +30 Aggression 85 CB Defender ++ CB Stopper ++ CB Wideback ++ 2 8 Level 1 Gonçalo Inácio 89 CB PAC 83 SHO 43 PAS 80 DRI 81 DEF 89 PHY 89 L 3 ★ 4 Gonçalo Inácio 91 CB PAC 84 SHO 43 PAS 80 DRI 81 DEF 91 PHY 89 L 3 ★ 4 UPGRADES +30 OVR 91 +30 Acceleration 87 +30 Short Pass 90 +30 Heading Acc. 92 +30 Defensive Awareness 95 2</t>
         </is>
       </c>
       <c r="CX35" t="inlineStr">
         <is>
-          <t>+30 OVR 91 +30 Acceleration 87 +30 Short Pass 90 +30 Heading Acc. 92 +30 Defensive Awareness 95 +30 Sprint Speed 88 +30 Vision 70 +30 Agility 73 +30 Balance 80 +30 Long Pass 85 +30 Ball Control 75 +30 Dribbling 75 +30 Reactions 95 +30 Composure 91 +30 Interceptions 93 +30 Standing Tackle 92 +30 Sliding Tackle 92 +30 Stamina 90 +30 Strength 92 +30 Jumping 90 +30 Aggression 85 CB Defender ++ CB Stopper ++ CB Wideback ++ 2 8 Level 1 Gonçalo Inácio 89 CB PAC 83 SHO 43 PAS 80 DRI 81 DEF 89 PHY 89 L 3 ★ 4 Gonçalo Inácio 91 CB PAC 84 SHO 43 PAS 80 DRI 81 DEF 91 PHY 89 L 3 ★ 4 UPGRADES +30 OVR 91 +30 Acceleration 87 +30 Short Pass 90 +30 Heading Acc. 92 +30 Defensive Awareness 95 2</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Position CB Excluded Position CM Max PS 10 Max PS+ 2 Pace Max. 90 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY35" t="inlineStr">
@@ -7389,15 +7355,10 @@
       </c>
       <c r="CZ35" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Position CB Excluded Position CM Max PS 10 Max PS+ 2 Pace Max. 90 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Il Capitano [Store]</t>
         </is>
       </c>
       <c r="DA35" t="inlineStr">
-        <is>
-          <t>Il Capitano [Store]</t>
-        </is>
-      </c>
-      <c r="DB35" t="inlineStr">
         <is>
           <t>Il Capitano [Store] Unlocked by purchasing the Captains' Armband EVO pack. Lawrence 70 CB PAC 60 SHO 26 PAS 49 DRI 46 DEF 70 PHY 73 R 2 ★ 2 CB 62.3 Lawrence 91 CB PAC 88 SHO 26 PAS 68 DRI 72 DEF 93 PHY 90 R 2 ★ 2 CB 92.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Position CB Excluded Position CM Max PS 10 Max PS+ 2 Pace Max. 90 UPGRADES +30 OVR 91 +30 Acceleration 87 +30 Short Pass 90 +30 Heading Acc. 92 +30 Defensive Awareness 95 +30 Sprint Speed 88 +30 Vision 70 +30 Agility 73 +30 Balance 80 +30 Long Pass 85 +30 Ball Control 75 +30 Dribbling 75 +30 Reactions 95 +30 Composure 91 +30 Interceptions 93 +30 Standing Tackle 92 +30 Sliding Tackle 92 +30 Stamina 90 +30 Strength 92 +30 Jumping 90 +30 Aggression 85 CB Defender ++ CB Stopper ++ CB Wideback ++ 2 8 in 2 days in 2 days 19% 81%</t>
         </is>
@@ -7536,10 +7497,14 @@
       <c r="CT36" t="inlineStr"/>
       <c r="CU36" t="inlineStr"/>
       <c r="CV36" t="inlineStr"/>
-      <c r="CW36" t="inlineStr"/>
+      <c r="CW36" t="inlineStr">
+        <is>
+          <t>2 Level 1 Hancko 89 CB PAC 87 SHO 72 PAS 81 DRI 85 DEF 90 PHY 89 LB LM L 5 ★ 5 Hancko 89 CB PAC 87 SHO 72 PAS 81 DRI 85 DEF 90 PHY 89 LB LM L 5 ★ 5 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX36" t="inlineStr">
         <is>
-          <t>2 Level 1 Hancko 89 CB PAC 87 SHO 72 PAS 81 DRI 85 DEF 90 PHY 89 LB LM L 5 ★ 5 Hancko 89 CB PAC 87 SHO 72 PAS 81 DRI 85 DEF 90 PHY 89 LB LM L 5 ★ 5 UPGRADES 2</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY36" t="inlineStr">
@@ -7549,15 +7514,10 @@
       </c>
       <c r="CZ36" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Intercept+ &amp; Quick Step+</t>
         </is>
       </c>
       <c r="DA36" t="inlineStr">
-        <is>
-          <t>Intercept+ &amp; Quick Step+</t>
-        </is>
-      </c>
-      <c r="DB36" t="inlineStr">
         <is>
           <t>Intercept+ &amp; Quick Step+ Unlocked by completing the Score in 30 task in the S7 Spirit of Africa League objective António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 86.6 António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 90.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 1 UPGRADES 2 in 28 days in 28 days 75% 25%</t>
         </is>
@@ -7618,10 +7578,10 @@
       <c r="X37" t="n">
         <v>10</v>
       </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="n">
+      <c r="Y37" t="n">
         <v>74</v>
       </c>
+      <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
@@ -7663,69 +7623,73 @@
       <c r="BM37" t="inlineStr"/>
       <c r="BN37" t="inlineStr"/>
       <c r="BO37" t="inlineStr"/>
-      <c r="BP37" t="inlineStr"/>
-      <c r="BQ37" t="n">
+      <c r="BP37" t="n">
         <v>2</v>
       </c>
-      <c r="BR37" t="inlineStr"/>
-      <c r="BS37" t="n">
+      <c r="BQ37" t="inlineStr"/>
+      <c r="BR37" t="n">
         <v>2</v>
       </c>
+      <c r="BS37" t="inlineStr"/>
       <c r="BT37" t="inlineStr"/>
       <c r="BU37" t="inlineStr"/>
       <c r="BV37" t="inlineStr"/>
       <c r="BW37" t="inlineStr"/>
-      <c r="BX37" t="inlineStr"/>
-      <c r="BY37" t="n">
+      <c r="BX37" t="n">
         <v>6</v>
       </c>
-      <c r="BZ37" t="inlineStr"/>
-      <c r="CA37" t="n">
+      <c r="BY37" t="inlineStr"/>
+      <c r="BZ37" t="n">
         <v>4</v>
       </c>
-      <c r="CB37" t="inlineStr"/>
-      <c r="CC37" t="n">
+      <c r="CA37" t="inlineStr"/>
+      <c r="CB37" t="n">
         <v>2</v>
       </c>
-      <c r="CD37" t="inlineStr"/>
-      <c r="CE37" t="n">
+      <c r="CC37" t="inlineStr"/>
+      <c r="CD37" t="n">
         <v>3</v>
       </c>
-      <c r="CF37" t="inlineStr"/>
-      <c r="CG37" t="n">
+      <c r="CE37" t="inlineStr"/>
+      <c r="CF37" t="n">
         <v>2</v>
       </c>
-      <c r="CH37" t="inlineStr"/>
-      <c r="CI37" t="n">
+      <c r="CG37" t="inlineStr"/>
+      <c r="CH37" t="n">
         <v>4</v>
       </c>
-      <c r="CJ37" t="inlineStr"/>
-      <c r="CK37" t="n">
+      <c r="CI37" t="inlineStr"/>
+      <c r="CJ37" t="n">
         <v>4</v>
       </c>
-      <c r="CL37" t="inlineStr"/>
-      <c r="CM37" t="n">
+      <c r="CK37" t="inlineStr"/>
+      <c r="CL37" t="n">
         <v>3</v>
       </c>
-      <c r="CN37" t="inlineStr"/>
-      <c r="CO37" t="n">
+      <c r="CM37" t="inlineStr"/>
+      <c r="CN37" t="n">
         <v>2</v>
       </c>
-      <c r="CP37" t="inlineStr"/>
+      <c r="CO37" t="inlineStr"/>
+      <c r="CP37" t="n">
+        <v>2</v>
+      </c>
       <c r="CQ37" t="n">
-        <v>2</v>
-      </c>
-      <c r="CR37" t="n">
         <v>3</v>
       </c>
+      <c r="CR37" t="inlineStr"/>
       <c r="CS37" t="inlineStr"/>
       <c r="CT37" t="inlineStr"/>
       <c r="CU37" t="inlineStr"/>
       <c r="CV37" t="inlineStr"/>
-      <c r="CW37" t="inlineStr"/>
+      <c r="CW37" t="inlineStr">
+        <is>
+          <t>+5 OVR 74 +3 Composure +2 Interceptions +2 Sliding Tackle +2 Jumping +2 Balance +2 Heading Acc. +2 Standing Tackle +3 Stamina +2 Reactions +3 Defensive Awareness +2 Strength +2 Aggression 3 Level 1 Fernando Torres 74 ST PAC 83 SHO 75 PAS 72 DRI 78 DEF 42 PHY 62 R 4 ★ 4 Fernando Torres 74 ST PAC 83 SHO 75 PAS 72 DRI 78 DEF 42 PHY 62 R 4 ★ 4 UPGRADES +5 OVR 74 +3 Composure +2 Interceptions +2 Sliding Tackle +2 Jumping</t>
+        </is>
+      </c>
       <c r="CX37" t="inlineStr">
         <is>
-          <t>+5 OVR 74 +3 Composure +2 Interceptions +2 Sliding Tackle +2 Jumping +2 Balance +2 Heading Acc. +2 Standing Tackle +3 Stamina +2 Reactions +3 Defensive Awareness +2 Strength +2 Aggression 3 Level 1 Fernando Torres 74 ST PAC 83 SHO 75 PAS 72 DRI 78 DEF 42 PHY 62 R 4 ★ 4 Fernando Torres 74 ST PAC 83 SHO 75 PAS 72 DRI 78 DEF 42 PHY 62 R 4 ★ 4 UPGRADES +5 OVR 74 +3 Composure +2 Interceptions +2 Sliding Tackle +2 Jumping</t>
+          <t>Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY37" t="inlineStr">
@@ -7735,15 +7699,10 @@
       </c>
       <c r="CZ37" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>WTSS Defender Boost</t>
         </is>
       </c>
       <c r="DA37" t="inlineStr">
-        <is>
-          <t>WTSS Defender Boost</t>
-        </is>
-      </c>
-      <c r="DB37" t="inlineStr">
         <is>
           <t>WTSS Defender Boost Unlocked by completing the S7 Spirit of Africa Tournament objective Moore 74 CB PAC 74 SHO 42 PAS 70 DRI 57 DEF 83 PHY 72 R 2 ★ 3 CB 68.4 Moore 74 CB PAC 74 SHO 42 PAS 70 DRI 57 DEF 85 PHY 74 R 2 ★ 3 CB 76.2 REQUIREMENTS Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 UPGRADES +5 OVR 74 +3 Composure +2 Interceptions +2 Sliding Tackle +2 Jumping +2 Balance +2 Heading Acc. +2 Standing Tackle +3 Stamina +2 Reactions +3 Defensive Awareness +2 Strength +2 Aggression 3 in 28 days in 28 days 74% 26%</t>
         </is>
@@ -7804,10 +7763,10 @@
       <c r="X38" t="n">
         <v>10</v>
       </c>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="n">
+      <c r="Y38" t="n">
         <v>74</v>
       </c>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
@@ -7819,38 +7778,38 @@
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="n">
+      <c r="AL38" t="n">
         <v>2</v>
       </c>
-      <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="n">
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="n">
         <v>2</v>
       </c>
-      <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="n">
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="n">
         <v>4</v>
       </c>
-      <c r="AR38" t="inlineStr"/>
-      <c r="AS38" t="n">
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="n">
         <v>3</v>
       </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AU38" t="n">
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="n">
         <v>2</v>
       </c>
-      <c r="AV38" t="inlineStr"/>
-      <c r="AW38" t="n">
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="n">
         <v>2</v>
       </c>
-      <c r="AX38" t="inlineStr"/>
-      <c r="AY38" t="n">
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="n">
         <v>4</v>
       </c>
-      <c r="AZ38" t="inlineStr"/>
-      <c r="BA38" t="n">
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="n">
         <v>4</v>
       </c>
+      <c r="BA38" t="inlineStr"/>
       <c r="BB38" t="inlineStr"/>
       <c r="BC38" t="inlineStr"/>
       <c r="BD38" t="inlineStr"/>
@@ -7865,20 +7824,20 @@
       <c r="BM38" t="inlineStr"/>
       <c r="BN38" t="inlineStr"/>
       <c r="BO38" t="inlineStr"/>
-      <c r="BP38" t="inlineStr"/>
-      <c r="BQ38" t="n">
+      <c r="BP38" t="n">
         <v>4</v>
       </c>
+      <c r="BQ38" t="inlineStr"/>
       <c r="BR38" t="inlineStr"/>
       <c r="BS38" t="inlineStr"/>
       <c r="BT38" t="inlineStr"/>
       <c r="BU38" t="inlineStr"/>
       <c r="BV38" t="inlineStr"/>
       <c r="BW38" t="inlineStr"/>
-      <c r="BX38" t="inlineStr"/>
-      <c r="BY38" t="n">
+      <c r="BX38" t="n">
         <v>3</v>
       </c>
+      <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="inlineStr"/>
       <c r="CA38" t="inlineStr"/>
       <c r="CB38" t="inlineStr"/>
@@ -7891,13 +7850,13 @@
       <c r="CI38" t="inlineStr"/>
       <c r="CJ38" t="inlineStr"/>
       <c r="CK38" t="inlineStr"/>
-      <c r="CL38" t="inlineStr"/>
+      <c r="CL38" t="n">
+        <v>3</v>
+      </c>
       <c r="CM38" t="n">
         <v>3</v>
       </c>
-      <c r="CN38" t="n">
-        <v>3</v>
-      </c>
+      <c r="CN38" t="inlineStr"/>
       <c r="CO38" t="inlineStr"/>
       <c r="CP38" t="inlineStr"/>
       <c r="CQ38" t="inlineStr"/>
@@ -7906,10 +7865,14 @@
       <c r="CT38" t="inlineStr"/>
       <c r="CU38" t="inlineStr"/>
       <c r="CV38" t="inlineStr"/>
-      <c r="CW38" t="inlineStr"/>
+      <c r="CW38" t="inlineStr">
+        <is>
+          <t>+5 OVR 74 +2 Positioning +2 Volleys +2 Penalties +2 Balance +2 Acceleration +3 Finishing +2 Long Shots +3 Composure +2 Sprint Speed +2 Shot Power +3 Stamina 3 Level 1 Matthäus 74 CM PAC 72 SHO 76 PAS 85 DRI 71 DEF 77 PHY 72 CB CDM R 3 ★ 4 Matthäus 74 CM PAC 72 SHO 76 PAS 85 DRI 71 DEF 77 PHY 72 CB CDM R 3 ★ 4 UPGRADES +5 OVR 74 +2 Positioning +2 Volleys +2 Penalties +2 Balance</t>
+        </is>
+      </c>
       <c r="CX38" t="inlineStr">
         <is>
-          <t>+5 OVR 74 +2 Positioning +2 Volleys +2 Penalties +2 Balance +2 Acceleration +3 Finishing +2 Long Shots +3 Composure +2 Sprint Speed +2 Shot Power +3 Stamina 3 Level 1 Matthäus 74 CM PAC 72 SHO 76 PAS 85 DRI 71 DEF 77 PHY 72 CB CDM R 3 ★ 4 Matthäus 74 CM PAC 72 SHO 76 PAS 85 DRI 71 DEF 77 PHY 72 CB CDM R 3 ★ 4 UPGRADES +5 OVR 74 +2 Positioning +2 Volleys +2 Penalties +2 Balance</t>
+          <t>Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY38" t="inlineStr">
@@ -7919,15 +7882,10 @@
       </c>
       <c r="CZ38" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>WTSS Attacker Boost</t>
         </is>
       </c>
       <c r="DA38" t="inlineStr">
-        <is>
-          <t>WTSS Attacker Boost</t>
-        </is>
-      </c>
-      <c r="DB38" t="inlineStr">
         <is>
           <t>WTSS Attacker Boost Unlocked by completing the S7 Spirit of Africa League objective Šuker 73 ST PAC 71 SHO 83 PAS 70 DRI 83 DEF 30 PHY 65 L 4 ★ 4 ST 72.7 Šuker 74 ST PAC 73 SHO 86 PAS 70 DRI 83 DEF 30 PHY 65 L 4 ★ 4 ST 79.2 REQUIREMENTS Rarity World Tour Silver Stars Overall Max. 74 Max PS+ 1 UPGRADES +5 OVR 74 +2 Positioning +2 Volleys +2 Penalties +2 Balance +2 Acceleration +3 Finishing +2 Long Shots +3 Composure +2 Sprint Speed +2 Shot Power +3 Stamina 3 in 28 days in 28 days 78% 22%</t>
         </is>
@@ -8000,74 +7958,74 @@
       <c r="X39" t="n">
         <v>4</v>
       </c>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="n">
+      <c r="Y39" t="n">
         <v>92</v>
       </c>
+      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
+      <c r="AD39" t="n">
+        <v>4</v>
+      </c>
       <c r="AE39" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF39" t="n">
         <v>93</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
+      <c r="AL39" t="n">
+        <v>5</v>
+      </c>
       <c r="AM39" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN39" t="n">
         <v>5</v>
       </c>
-      <c r="AN39" t="n">
+      <c r="AO39" t="n">
         <v>90</v>
       </c>
-      <c r="AO39" t="n">
+      <c r="AP39" t="n">
         <v>5</v>
       </c>
-      <c r="AP39" t="n">
+      <c r="AQ39" t="n">
         <v>90</v>
       </c>
-      <c r="AQ39" t="n">
+      <c r="AR39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT39" t="n">
         <v>5</v>
       </c>
-      <c r="AR39" t="n">
-        <v>90</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>90</v>
-      </c>
       <c r="AU39" t="n">
+        <v>91</v>
+      </c>
+      <c r="AV39" t="n">
         <v>5</v>
       </c>
-      <c r="AV39" t="n">
+      <c r="AW39" t="n">
         <v>91</v>
       </c>
-      <c r="AW39" t="n">
+      <c r="AX39" t="n">
         <v>5</v>
       </c>
-      <c r="AX39" t="n">
-        <v>91</v>
-      </c>
       <c r="AY39" t="n">
+        <v>88</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>5</v>
       </c>
-      <c r="AZ39" t="n">
+      <c r="BA39" t="n">
         <v>88</v>
       </c>
-      <c r="BA39" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>88</v>
-      </c>
+      <c r="BB39" t="inlineStr"/>
       <c r="BC39" t="inlineStr"/>
       <c r="BD39" t="inlineStr"/>
       <c r="BE39" t="inlineStr"/>
@@ -8079,43 +8037,43 @@
       <c r="BK39" t="inlineStr"/>
       <c r="BL39" t="inlineStr"/>
       <c r="BM39" t="inlineStr"/>
-      <c r="BN39" t="inlineStr"/>
+      <c r="BN39" t="n">
+        <v>10</v>
+      </c>
       <c r="BO39" t="n">
+        <v>92</v>
+      </c>
+      <c r="BP39" t="n">
         <v>10</v>
       </c>
-      <c r="BP39" t="n">
+      <c r="BQ39" t="n">
         <v>92</v>
       </c>
-      <c r="BQ39" t="n">
+      <c r="BR39" t="n">
+        <v>20</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>91</v>
+      </c>
+      <c r="BT39" t="n">
         <v>10</v>
       </c>
-      <c r="BR39" t="n">
+      <c r="BU39" t="n">
         <v>92</v>
       </c>
-      <c r="BS39" t="n">
-        <v>20</v>
-      </c>
-      <c r="BT39" t="n">
-        <v>91</v>
-      </c>
-      <c r="BU39" t="n">
+      <c r="BV39" t="n">
         <v>10</v>
       </c>
-      <c r="BV39" t="n">
-        <v>92</v>
-      </c>
       <c r="BW39" t="n">
+        <v>93</v>
+      </c>
+      <c r="BX39" t="n">
         <v>10</v>
       </c>
-      <c r="BX39" t="n">
-        <v>93</v>
-      </c>
       <c r="BY39" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ39" t="n">
         <v>90</v>
       </c>
+      <c r="BZ39" t="inlineStr"/>
       <c r="CA39" t="inlineStr"/>
       <c r="CB39" t="inlineStr"/>
       <c r="CC39" t="inlineStr"/>
@@ -8135,17 +8093,21 @@
       <c r="CQ39" t="inlineStr"/>
       <c r="CR39" t="inlineStr"/>
       <c r="CS39" t="inlineStr"/>
-      <c r="CT39" t="inlineStr"/>
+      <c r="CT39" t="n">
+        <v>4</v>
+      </c>
       <c r="CU39" t="n">
-        <v>4</v>
-      </c>
-      <c r="CV39" t="n">
         <v>5</v>
       </c>
-      <c r="CW39" t="inlineStr"/>
+      <c r="CV39" t="inlineStr"/>
+      <c r="CW39" t="inlineStr">
+        <is>
+          <t>+2 OVR 92 +2 PAS 93 +4 WF 5 +5 Finishing 90 +10 Reactions 91 +5 Acceleration 90 +5 Shot Power 91 +10 Balance 92 +10 Ball Control 92 +5 Sprint Speed 90 +5 Long Shots 91 +5 Penalties 88 +10 Dribbling 93 +5 Positioning 90 +5 Volleys 88 +10 Agility 92 +10 Composure 90 3 8 Level 1 Vieira 90 CM PAC 88 SHO 88 PAS 91 DRI 87 DEF 89 PHY 89 CDM R 4 ★ 4 CM 87.7 Vieira 92 CM PAC 88 SHO 89 PAS 93 DRI 87 DEF 89 PHY 89 CDM R 4 ★ 4 CM 87.7 UPGRADES +2 OVR 92 +2 PAS 93 +5 Finishing 90 +10 Reactions 91 3</t>
+        </is>
+      </c>
       <c r="CX39" t="inlineStr">
         <is>
-          <t>+2 OVR 92 +2 PAS 93 +4 WF 5 +5 Finishing 90 +10 Reactions 91 +5 Acceleration 90 +5 Shot Power 91 +10 Balance 92 +10 Ball Control 92 +5 Sprint Speed 90 +5 Long Shots 91 +5 Penalties 88 +10 Dribbling 93 +5 Positioning 90 +5 Volleys 88 +10 Agility 92 +10 Composure 90 3 8 Level 1 Vieira 90 CM PAC 88 SHO 88 PAS 91 DRI 87 DEF 89 PHY 89 CDM R 4 ★ 4 CM 87.7 Vieira 92 CM PAC 88 SHO 89 PAS 93 DRI 87 DEF 89 PHY 89 CDM R 4 ★ 4 CM 87.7 UPGRADES +2 OVR 92 +2 PAS 93 +5 Finishing 90 +10 Reactions 91 3</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CAM, CM, CDM Max PS 10 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY39" t="inlineStr">
@@ -8155,15 +8117,10 @@
       </c>
       <c r="CZ39" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CAM, CM, CDM Max PS 10 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>WTSS Journey 3 - Midfielder [SP 21]</t>
         </is>
       </c>
       <c r="DA39" t="inlineStr">
-        <is>
-          <t>WTSS Journey 3 - Midfielder [SP 21]</t>
-        </is>
-      </c>
-      <c r="DB39" t="inlineStr">
         <is>
           <t>WTSS Journey 3 - Midfielder [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CAM, CM, CDM Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +2 PAS 93 +4 WF 5 +5 Finishing 90 +10 Reactions 91 +5 Acceleration 90 +5 Shot Power 91 +10 Balance 92 +10 Ball Control 92 +5 Sprint Speed 90 +5 Long Shots 91 +5 Penalties 88 +10 Dribbling 93 +5 Positioning 90 +5 Volleys 88 +10 Agility 92 +10 Composure 90 3 8 Show less in 1 month in 1 month 84% 16%</t>
         </is>
@@ -8302,10 +8259,14 @@
       <c r="CT40" t="inlineStr"/>
       <c r="CU40" t="inlineStr"/>
       <c r="CV40" t="inlineStr"/>
-      <c r="CW40" t="inlineStr"/>
+      <c r="CW40" t="inlineStr">
+        <is>
+          <t>3 Level 1 Lamine Yamal 91 RW PAC 87 SHO 83 PAS 88 DRI 92 DEF 25 PHY 55 RM L 5 ★ 3 Lamine Yamal 91 RW PAC 87 SHO 83 PAS 88 DRI 92 DEF 25 PHY 55 RM L 5 ★ 3 UPGRADES 3</t>
+        </is>
+      </c>
       <c r="CX40" t="inlineStr">
         <is>
-          <t>3 Level 1 Lamine Yamal 91 RW PAC 87 SHO 83 PAS 88 DRI 92 DEF 25 PHY 55 RM L 5 ★ 3 Lamine Yamal 91 RW PAC 87 SHO 83 PAS 88 DRI 92 DEF 25 PHY 55 RM L 5 ★ 3 UPGRADES 3</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY40" t="inlineStr">
@@ -8315,15 +8276,10 @@
       </c>
       <c r="CZ40" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Bruiser+ [SP+ 28]</t>
         </is>
       </c>
       <c r="DA40" t="inlineStr">
-        <is>
-          <t>Bruiser+ [SP+ 28]</t>
-        </is>
-      </c>
-      <c r="DB40" t="inlineStr">
         <is>
           <t>Bruiser+ [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 CB 90.5 van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 CB 93.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 2 UPGRADES 3 in 1 month in 1 month 91% 9%</t>
         </is>
@@ -8462,10 +8418,14 @@
       <c r="CT41" t="inlineStr"/>
       <c r="CU41" t="inlineStr"/>
       <c r="CV41" t="inlineStr"/>
-      <c r="CW41" t="inlineStr"/>
+      <c r="CW41" t="inlineStr">
+        <is>
+          <t>3 Level 1 van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 UPGRADES 3</t>
+        </is>
+      </c>
       <c r="CX41" t="inlineStr">
         <is>
-          <t>3 Level 1 van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 UPGRADES 3</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY41" t="inlineStr">
@@ -8475,15 +8435,10 @@
       </c>
       <c r="CZ41" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Incisive Pass+ [SP 27]</t>
         </is>
       </c>
       <c r="DA41" t="inlineStr">
-        <is>
-          <t>Incisive Pass+ [SP 27]</t>
-        </is>
-      </c>
-      <c r="DB41" t="inlineStr">
         <is>
           <t>Incisive Pass+ [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Calafiori 90 LB PAC 87 SHO 80 PAS 85 DRI 89 DEF 90 PHY 91 CB L 3 ★ 4 LB 89.9 Calafiori 90 LB PAC 87 SHO 80 PAS 85 DRI 89 DEF 90 PHY 91 CB L 3 ★ 4 LB 91.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 UPGRADES 3 in 1 month in 1 month 85% 15%</t>
         </is>
@@ -8561,19 +8516,19 @@
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="inlineStr"/>
+      <c r="AL42" t="n">
+        <v>10</v>
+      </c>
       <c r="AM42" t="n">
+        <v>91</v>
+      </c>
+      <c r="AN42" t="n">
         <v>10</v>
       </c>
-      <c r="AN42" t="n">
-        <v>91</v>
-      </c>
       <c r="AO42" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP42" t="n">
         <v>92</v>
       </c>
+      <c r="AP42" t="inlineStr"/>
       <c r="AQ42" t="inlineStr"/>
       <c r="AR42" t="inlineStr"/>
       <c r="AS42" t="inlineStr"/>
@@ -8601,85 +8556,89 @@
       <c r="BO42" t="inlineStr"/>
       <c r="BP42" t="inlineStr"/>
       <c r="BQ42" t="inlineStr"/>
-      <c r="BR42" t="inlineStr"/>
+      <c r="BR42" t="n">
+        <v>5</v>
+      </c>
       <c r="BS42" t="n">
-        <v>5</v>
-      </c>
-      <c r="BT42" t="n">
         <v>93</v>
       </c>
+      <c r="BT42" t="inlineStr"/>
       <c r="BU42" t="inlineStr"/>
       <c r="BV42" t="inlineStr"/>
       <c r="BW42" t="inlineStr"/>
-      <c r="BX42" t="inlineStr"/>
+      <c r="BX42" t="n">
+        <v>5</v>
+      </c>
       <c r="BY42" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ42" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA42" t="n">
+        <v>93</v>
+      </c>
+      <c r="CB42" t="n">
+        <v>2</v>
+      </c>
+      <c r="CC42" t="n">
+        <v>94</v>
+      </c>
+      <c r="CD42" t="n">
+        <v>2</v>
+      </c>
+      <c r="CE42" t="n">
+        <v>93</v>
+      </c>
+      <c r="CF42" t="n">
         <v>5</v>
       </c>
-      <c r="BZ42" t="n">
+      <c r="CG42" t="n">
+        <v>91</v>
+      </c>
+      <c r="CH42" t="n">
+        <v>5</v>
+      </c>
+      <c r="CI42" t="n">
+        <v>92</v>
+      </c>
+      <c r="CJ42" t="n">
+        <v>2</v>
+      </c>
+      <c r="CK42" t="n">
         <v>93</v>
       </c>
-      <c r="CA42" t="n">
+      <c r="CL42" t="n">
         <v>2</v>
       </c>
-      <c r="CB42" t="n">
+      <c r="CM42" t="n">
+        <v>92</v>
+      </c>
+      <c r="CN42" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO42" t="n">
         <v>93</v>
       </c>
-      <c r="CC42" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD42" t="n">
-        <v>94</v>
-      </c>
-      <c r="CE42" t="n">
-        <v>2</v>
-      </c>
-      <c r="CF42" t="n">
-        <v>93</v>
-      </c>
-      <c r="CG42" t="n">
+      <c r="CP42" t="n">
         <v>5</v>
       </c>
-      <c r="CH42" t="n">
-        <v>91</v>
-      </c>
-      <c r="CI42" t="n">
-        <v>5</v>
-      </c>
-      <c r="CJ42" t="n">
+      <c r="CQ42" t="n">
         <v>92</v>
       </c>
-      <c r="CK42" t="n">
-        <v>2</v>
-      </c>
-      <c r="CL42" t="n">
-        <v>93</v>
-      </c>
-      <c r="CM42" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN42" t="n">
-        <v>92</v>
-      </c>
-      <c r="CO42" t="n">
-        <v>2</v>
-      </c>
-      <c r="CP42" t="n">
-        <v>93</v>
-      </c>
-      <c r="CQ42" t="n">
-        <v>5</v>
-      </c>
-      <c r="CR42" t="n">
-        <v>92</v>
-      </c>
+      <c r="CR42" t="inlineStr"/>
       <c r="CS42" t="inlineStr"/>
       <c r="CT42" t="inlineStr"/>
       <c r="CU42" t="inlineStr"/>
       <c r="CV42" t="inlineStr"/>
-      <c r="CW42" t="inlineStr"/>
+      <c r="CW42" t="inlineStr">
+        <is>
+          <t>+1 OVR +5 Acceleration 91 +5 Sprint Speed 92 +1 Interceptions 93 +1 Heading Acc. 94 +1 Defensive Awareness 93 +5 Reactions 93 +5 Composure 93 +5 Standing Tackle 91 +5 Sliding Tackle 92 +2 Jumping 93 +2 Stamina 92 +2 Strength 93 +5 Aggression 92 8 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 90 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 64 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES +1 OVR +5 Acceleration 91 +5 Sprint Speed 92 +1 Interceptions 93 +1 Heading Acc. 94 +1 Defensive Awareness 93</t>
+        </is>
+      </c>
       <c r="CX42" t="inlineStr">
         <is>
-          <t>+1 OVR +5 Acceleration 91 +5 Sprint Speed 92 +1 Interceptions 93 +1 Heading Acc. 94 +1 Defensive Awareness 93 +5 Reactions 93 +5 Composure 93 +5 Standing Tackle 91 +5 Sliding Tackle 92 +2 Jumping 93 +2 Stamina 92 +2 Strength 93 +5 Aggression 92 8 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 90 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 64 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES +1 OVR +5 Acceleration 91 +5 Sprint Speed 92 +1 Interceptions 93 +1 Heading Acc. 94 +1 Defensive Awareness 93</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY42" t="inlineStr">
@@ -8689,15 +8648,10 @@
       </c>
       <c r="CZ42" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Defender Round Out [SP 1] 10</t>
         </is>
       </c>
       <c r="DA42" t="inlineStr">
-        <is>
-          <t>Defender Round Out [SP 1] 10</t>
-        </is>
-      </c>
-      <c r="DB42" t="inlineStr">
         <is>
           <t>Defender Round Out [SP 1] 10 Unlocked by reaching level 1 in the Standard Season Pass. Timber 88 RB PAC 87 SHO 54 PAS 83 DRI 86 DEF 88 PHY 88 CB LB RM R 4 ★ 5 LB 88.6 Timber 89 RB PAC 92 SHO 54 PAS 83 DRI 87 DEF 89 PHY 91 CB LB RM R 4 ★ 5 LB 92.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +1 OVR +5 Acceleration 91 +5 Sprint Speed 92 +1 Interceptions 93 +1 Heading Acc. 94 +1 Defensive Awareness 93 +5 Reactions 93 +5 Composure 93 +5 Standing Tackle 91 +5 Sliding Tackle 92 +2 Jumping 93 +2 Stamina 92 +2 Strength 93 +5 Aggression 92 8 in 1 month in 1 month 90% 10%</t>
         </is>
@@ -8770,10 +8724,10 @@
       <c r="X43" t="n">
         <v>4</v>
       </c>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="n">
+      <c r="Y43" t="n">
         <v>91</v>
       </c>
+      <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr"/>
@@ -8785,123 +8739,123 @@
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="inlineStr"/>
+      <c r="AL43" t="n">
+        <v>6</v>
+      </c>
       <c r="AM43" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="AN43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>94</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ43" t="n">
         <v>93</v>
       </c>
-      <c r="AO43" t="n">
+      <c r="AR43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>94</v>
+      </c>
+      <c r="AT43" t="n">
         <v>3</v>
       </c>
-      <c r="AP43" t="n">
+      <c r="AU43" t="n">
+        <v>93</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>92</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY43" t="n">
         <v>94</v>
       </c>
-      <c r="AQ43" t="n">
+      <c r="AZ43" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>94</v>
+      </c>
+      <c r="BB43" t="n">
         <v>5</v>
       </c>
-      <c r="AR43" t="n">
+      <c r="BC43" t="n">
         <v>93</v>
       </c>
-      <c r="AS43" t="n">
+      <c r="BD43" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>94</v>
+      </c>
+      <c r="BF43" t="inlineStr"/>
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="n">
         <v>5</v>
       </c>
-      <c r="AT43" t="n">
+      <c r="BI43" t="n">
+        <v>95</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK43" t="n">
         <v>94</v>
       </c>
-      <c r="AU43" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV43" t="n">
+      <c r="BL43" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>92</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>94</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ43" t="n">
         <v>93</v>
       </c>
-      <c r="AW43" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX43" t="n">
+      <c r="BR43" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS43" t="n">
         <v>92</v>
       </c>
-      <c r="AY43" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ43" t="n">
+      <c r="BT43" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU43" t="n">
         <v>94</v>
       </c>
-      <c r="BA43" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>94</v>
-      </c>
-      <c r="BC43" t="n">
+      <c r="BV43" t="n">
         <v>5</v>
       </c>
-      <c r="BD43" t="n">
-        <v>93</v>
-      </c>
-      <c r="BE43" t="n">
+      <c r="BW43" t="n">
+        <v>95</v>
+      </c>
+      <c r="BX43" t="n">
         <v>2</v>
       </c>
-      <c r="BF43" t="n">
-        <v>94</v>
-      </c>
-      <c r="BG43" t="inlineStr"/>
-      <c r="BH43" t="inlineStr"/>
-      <c r="BI43" t="n">
-        <v>5</v>
-      </c>
-      <c r="BJ43" t="n">
+      <c r="BY43" t="n">
         <v>95</v>
       </c>
-      <c r="BK43" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL43" t="n">
-        <v>94</v>
-      </c>
-      <c r="BM43" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN43" t="n">
-        <v>92</v>
-      </c>
-      <c r="BO43" t="n">
-        <v>10</v>
-      </c>
-      <c r="BP43" t="n">
-        <v>94</v>
-      </c>
-      <c r="BQ43" t="n">
-        <v>10</v>
-      </c>
-      <c r="BR43" t="n">
-        <v>93</v>
-      </c>
-      <c r="BS43" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT43" t="n">
-        <v>92</v>
-      </c>
-      <c r="BU43" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV43" t="n">
-        <v>94</v>
-      </c>
-      <c r="BW43" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX43" t="n">
-        <v>95</v>
-      </c>
-      <c r="BY43" t="n">
-        <v>2</v>
-      </c>
-      <c r="BZ43" t="n">
-        <v>95</v>
-      </c>
+      <c r="BZ43" t="inlineStr"/>
       <c r="CA43" t="inlineStr"/>
       <c r="CB43" t="inlineStr"/>
       <c r="CC43" t="inlineStr"/>
@@ -8924,10 +8878,14 @@
       <c r="CT43" t="inlineStr"/>
       <c r="CU43" t="inlineStr"/>
       <c r="CV43" t="inlineStr"/>
-      <c r="CW43" t="inlineStr"/>
+      <c r="CW43" t="inlineStr">
+        <is>
+          <t>+2 OVR 91 +3 Acceleration 93 +5 Agility 94 +5 Balance 93 +3 Sprint Speed 94 +5 Long Pass 94 +2 Curve 92 +2 Composure 95 +5 Positioning 93 +5 Finishing 94 +3 Shot Power 93 +2 Reactions 92 +5 Ball Control 94 +3 Long Shots 92 +3 Volleys 94 +3 Penalties 94 +5 Short Pass 95 +5 Dribbling 95 +5 Vision 93 +2 Crossing 94 +2 Fk Accuracy 92 8 Level 1 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 Kerolin Nicoli 91 RM PAC 92 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 UPGRADES +2 OVR 91 +3 Acceleration 93 +5 Agility 94 +5 Balance 93 8</t>
+        </is>
+      </c>
       <c r="CX43" t="inlineStr">
         <is>
-          <t>+2 OVR 91 +3 Acceleration 93 +5 Agility 94 +5 Balance 93 +3 Sprint Speed 94 +5 Long Pass 94 +2 Curve 92 +2 Composure 95 +5 Positioning 93 +5 Finishing 94 +3 Shot Power 93 +2 Reactions 92 +5 Ball Control 94 +3 Long Shots 92 +3 Volleys 94 +3 Penalties 94 +5 Short Pass 95 +5 Dribbling 95 +5 Vision 93 +2 Crossing 94 +2 Fk Accuracy 92 8 Level 1 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 Kerolin Nicoli 91 RM PAC 92 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 UPGRADES +2 OVR 91 +3 Acceleration 93 +5 Agility 94 +5 Balance 93 8</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Excluded Position CB Max PS 10 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY43" t="inlineStr">
@@ -8937,15 +8895,10 @@
       </c>
       <c r="CZ43" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Excluded Position CB Max PS 10 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Attacker Round Out [SP+ 1] 20</t>
         </is>
       </c>
       <c r="DA43" t="inlineStr">
-        <is>
-          <t>Attacker Round Out [SP+ 1] 20</t>
-        </is>
-      </c>
-      <c r="DB43" t="inlineStr">
         <is>
           <t>Attacker Round Out [SP+ 1] 20 Unlocked by reaching level 1 in the Premium Season Pass. Mead 89 LW PAC 89 SHO 88 PAS 87 DRI 90 DEF 70 PHY 77 RM RW ST R 5 ★ 4 RW 86.9 Mead 91 LW PAC 92 SHO 91 PAS 91 DRI 93 DEF 70 PHY 77 RM RW ST R 5 ★ 4 RW 91.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Excluded Position CB Max PS 10 UPGRADES +2 OVR 91 +3 Acceleration 93 +5 Agility 94 +5 Balance 93 +3 Sprint Speed 94 +5 Long Pass 94 +2 Curve 92 +2 Composure 95 +5 Positioning 93 +5 Finishing 94 +3 Shot Power 93 +2 Reactions 92 +5 Ball Control 94 +3 Long Shots 92 +3 Volleys 94 +3 Penalties 94 +5 Short Pass 95 +5 Dribbling 95 +5 Vision 93 +2 Crossing 94 +2 Fk Accuracy 92 8 in 1 month in 1 month 93% 7%</t>
         </is>
@@ -9018,10 +8971,10 @@
       <c r="X44" t="n">
         <v>4</v>
       </c>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="n">
+      <c r="Y44" t="n">
         <v>90</v>
       </c>
+      <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr"/>
@@ -9033,55 +8986,55 @@
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="inlineStr"/>
+      <c r="AL44" t="n">
+        <v>20</v>
+      </c>
       <c r="AM44" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN44" t="n">
         <v>20</v>
       </c>
-      <c r="AN44" t="n">
+      <c r="AO44" t="n">
         <v>90</v>
       </c>
-      <c r="AO44" t="n">
+      <c r="AP44" t="n">
         <v>20</v>
       </c>
-      <c r="AP44" t="n">
+      <c r="AQ44" t="n">
         <v>90</v>
       </c>
-      <c r="AQ44" t="n">
+      <c r="AR44" t="n">
         <v>20</v>
       </c>
-      <c r="AR44" t="n">
+      <c r="AS44" t="n">
         <v>90</v>
       </c>
-      <c r="AS44" t="n">
-        <v>20</v>
-      </c>
       <c r="AT44" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>91</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW44" t="n">
         <v>90</v>
       </c>
-      <c r="AU44" t="n">
+      <c r="AX44" t="n">
         <v>10</v>
       </c>
-      <c r="AV44" t="n">
-        <v>91</v>
-      </c>
-      <c r="AW44" t="n">
+      <c r="AY44" t="n">
+        <v>89</v>
+      </c>
+      <c r="AZ44" t="n">
         <v>10</v>
       </c>
-      <c r="AX44" t="n">
+      <c r="BA44" t="n">
         <v>90</v>
       </c>
-      <c r="AY44" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>89</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>90</v>
-      </c>
+      <c r="BB44" t="inlineStr"/>
       <c r="BC44" t="inlineStr"/>
       <c r="BD44" t="inlineStr"/>
       <c r="BE44" t="inlineStr"/>
@@ -9091,49 +9044,49 @@
       <c r="BI44" t="inlineStr"/>
       <c r="BJ44" t="inlineStr"/>
       <c r="BK44" t="inlineStr"/>
-      <c r="BL44" t="inlineStr"/>
+      <c r="BL44" t="n">
+        <v>10</v>
+      </c>
       <c r="BM44" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="BN44" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="BO44" t="n">
+        <v>92</v>
+      </c>
+      <c r="BP44" t="n">
         <v>15</v>
       </c>
-      <c r="BP44" t="n">
-        <v>92</v>
-      </c>
       <c r="BQ44" t="n">
+        <v>89</v>
+      </c>
+      <c r="BR44" t="n">
         <v>15</v>
       </c>
-      <c r="BR44" t="n">
+      <c r="BS44" t="n">
         <v>89</v>
       </c>
-      <c r="BS44" t="n">
+      <c r="BT44" t="n">
         <v>15</v>
       </c>
-      <c r="BT44" t="n">
+      <c r="BU44" t="n">
+        <v>88</v>
+      </c>
+      <c r="BV44" t="n">
+        <v>15</v>
+      </c>
+      <c r="BW44" t="n">
         <v>89</v>
       </c>
-      <c r="BU44" t="n">
+      <c r="BX44" t="n">
         <v>15</v>
       </c>
-      <c r="BV44" t="n">
+      <c r="BY44" t="n">
         <v>88</v>
       </c>
-      <c r="BW44" t="n">
-        <v>15</v>
-      </c>
-      <c r="BX44" t="n">
-        <v>89</v>
-      </c>
-      <c r="BY44" t="n">
-        <v>15</v>
-      </c>
-      <c r="BZ44" t="n">
-        <v>88</v>
-      </c>
+      <c r="BZ44" t="inlineStr"/>
       <c r="CA44" t="inlineStr"/>
       <c r="CB44" t="inlineStr"/>
       <c r="CC44" t="inlineStr"/>
@@ -9153,17 +9106,21 @@
       <c r="CQ44" t="inlineStr"/>
       <c r="CR44" t="inlineStr"/>
       <c r="CS44" t="inlineStr"/>
-      <c r="CT44" t="inlineStr"/>
+      <c r="CT44" t="n">
+        <v>3</v>
+      </c>
       <c r="CU44" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV44" t="n">
         <v>4</v>
       </c>
-      <c r="CW44" t="inlineStr"/>
+      <c r="CV44" t="inlineStr"/>
+      <c r="CW44" t="inlineStr">
+        <is>
+          <t>+2 OVR 90 +3 WF 4 +10 Acceleration 90 +10 Sprint Speed 90 +10 Finishing 90 +10 Positioning 90 +10 Volleys 89 +10 Penalties 90 +10 Curve 90 +15 Agility 92 +15 Balance 89 +15 Reactions 89 +10 Shot Power 91 +10 Long Shots 90 +15 Ball Control 88 +15 Dribbling 89 +15 Composure 88 2 8 Level 1 Park Ji Sung 88 RW PAC 88 SHO 87 PAS 89 DRI 88 DEF 85 PHY 84 RM CM CAM R 4 ★ 4 CM 85.3 Park Ji Sung 90 RW PAC 90 SHO 89 PAS 89 DRI 88 DEF 85 PHY 84 RM CM CAM R 4 ★ 4 CM 85.3 UPGRADES +2 OVR 90 +10 Acceleration 90 +10 Sprint Speed 90 +10 Finishing 90 +10 Positioning 90 8</t>
+        </is>
+      </c>
       <c r="CX44" t="inlineStr">
         <is>
-          <t>+2 OVR 90 +3 WF 4 +10 Acceleration 90 +10 Sprint Speed 90 +10 Finishing 90 +10 Positioning 90 +10 Volleys 89 +10 Penalties 90 +10 Curve 90 +15 Agility 92 +15 Balance 89 +15 Reactions 89 +10 Shot Power 91 +10 Long Shots 90 +15 Ball Control 88 +15 Dribbling 89 +15 Composure 88 2 8 Level 1 Park Ji Sung 88 RW PAC 88 SHO 87 PAS 89 DRI 88 DEF 85 PHY 84 RM CM CAM R 4 ★ 4 CM 85.3 Park Ji Sung 90 RW PAC 90 SHO 89 PAS 89 DRI 88 DEF 85 PHY 84 RM CM CAM R 4 ★ 4 CM 85.3 UPGRADES +2 OVR 90 +10 Acceleration 90 +10 Sprint Speed 90 +10 Finishing 90 +10 Positioning 90 8</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position ST, RW, LW Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY44" t="inlineStr">
@@ -9173,15 +9130,10 @@
       </c>
       <c r="CZ44" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position ST, RW, LW Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>WTSS Journey 2 - Attacker [SP 8]</t>
         </is>
       </c>
       <c r="DA44" t="inlineStr">
-        <is>
-          <t>WTSS Journey 2 - Attacker [SP 8]</t>
-        </is>
-      </c>
-      <c r="DB44" t="inlineStr">
         <is>
           <t>WTSS Journey 2 - Attacker [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Garrincha 70 RW PAC 82 SHO 64 PAS 67 DRI 78 DEF 34 PHY 48 RM R 5 ★ 4 RM 70.4 Garrincha 90 RW PAC 90 SHO 90 PAS 87 DRI 89 DEF 34 PHY 67 RM R 5 ★ 4 RM 88.6 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position ST, RW, LW Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +3 WF 4 +10 Acceleration 90 +10 Sprint Speed 90 +10 Finishing 90 +10 Positioning 90 +10 Volleys 89 +10 Penalties 90 +10 Curve 90 +15 Agility 92 +15 Balance 89 +15 Reactions 89 +10 Shot Power 91 +10 Long Shots 90 +15 Ball Control 88 +15 Dribbling 89 +15 Composure 88 2 8 in 1 month in 1 month 68% 32%</t>
         </is>
@@ -9254,16 +9206,16 @@
       <c r="X45" t="n">
         <v>4</v>
       </c>
-      <c r="Y45" t="inlineStr"/>
+      <c r="Y45" t="n">
+        <v>90</v>
+      </c>
       <c r="Z45" t="n">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="AA45" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB45" t="n">
         <v>87</v>
       </c>
+      <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="inlineStr"/>
@@ -9301,65 +9253,65 @@
       <c r="BK45" t="inlineStr"/>
       <c r="BL45" t="inlineStr"/>
       <c r="BM45" t="inlineStr"/>
-      <c r="BN45" t="inlineStr"/>
+      <c r="BN45" t="n">
+        <v>10</v>
+      </c>
       <c r="BO45" t="n">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="BP45" t="n">
+        <v>5</v>
+      </c>
+      <c r="BQ45" t="n">
         <v>88</v>
       </c>
-      <c r="BQ45" t="n">
+      <c r="BR45" t="n">
         <v>5</v>
       </c>
-      <c r="BR45" t="n">
-        <v>88</v>
-      </c>
       <c r="BS45" t="n">
-        <v>5</v>
-      </c>
-      <c r="BT45" t="n">
         <v>90</v>
       </c>
+      <c r="BT45" t="inlineStr"/>
       <c r="BU45" t="inlineStr"/>
       <c r="BV45" t="inlineStr"/>
       <c r="BW45" t="inlineStr"/>
-      <c r="BX45" t="inlineStr"/>
+      <c r="BX45" t="n">
+        <v>5</v>
+      </c>
       <c r="BY45" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="BZ45" t="n">
+        <v>10</v>
+      </c>
+      <c r="CA45" t="n">
+        <v>93</v>
+      </c>
+      <c r="CB45" t="n">
+        <v>10</v>
+      </c>
+      <c r="CC45" t="n">
+        <v>94</v>
+      </c>
+      <c r="CD45" t="n">
+        <v>10</v>
+      </c>
+      <c r="CE45" t="n">
         <v>90</v>
       </c>
-      <c r="CA45" t="n">
+      <c r="CF45" t="n">
         <v>10</v>
       </c>
-      <c r="CB45" t="n">
-        <v>93</v>
-      </c>
-      <c r="CC45" t="n">
+      <c r="CG45" t="n">
+        <v>92</v>
+      </c>
+      <c r="CH45" t="n">
         <v>10</v>
       </c>
-      <c r="CD45" t="n">
-        <v>94</v>
-      </c>
-      <c r="CE45" t="n">
-        <v>10</v>
-      </c>
-      <c r="CF45" t="n">
-        <v>90</v>
-      </c>
-      <c r="CG45" t="n">
-        <v>10</v>
-      </c>
-      <c r="CH45" t="n">
+      <c r="CI45" t="n">
         <v>92</v>
       </c>
-      <c r="CI45" t="n">
-        <v>10</v>
-      </c>
-      <c r="CJ45" t="n">
-        <v>92</v>
-      </c>
+      <c r="CJ45" t="inlineStr"/>
       <c r="CK45" t="inlineStr"/>
       <c r="CL45" t="inlineStr"/>
       <c r="CM45" t="inlineStr"/>
@@ -9372,10 +9324,14 @@
       <c r="CT45" t="inlineStr"/>
       <c r="CU45" t="inlineStr"/>
       <c r="CV45" t="inlineStr"/>
-      <c r="CW45" t="inlineStr"/>
+      <c r="CW45" t="inlineStr">
+        <is>
+          <t>+2 OVR 90 +2 PAC 87 +5 Agility 88 +5 Balance 88 +5 Reactions 90 +5 Composure 90 +10 Standing Tackle 92 +10 Sliding Tackle 92 +10 Interceptions 93 +10 Heading Acc. 94 +10 Defensive Awareness 90 2 8 Level 1 Kohler 88 CB PAC 85 SHO 56 PAS 79 DRI 75 DEF 87 PHY 87 R 3 ★ 4 CB 85.4 Kohler 90 CB PAC 87 SHO 56 PAS 79 DRI 76 DEF 87 PHY 87 R 3 ★ 4 CB 85.4 UPGRADES +2 OVR 90 +2 PAC 87 +5 Agility 88 2 8</t>
+        </is>
+      </c>
       <c r="CX45" t="inlineStr">
         <is>
-          <t>+2 OVR 90 +2 PAC 87 +5 Agility 88 +5 Balance 88 +5 Reactions 90 +5 Composure 90 +10 Standing Tackle 92 +10 Sliding Tackle 92 +10 Interceptions 93 +10 Heading Acc. 94 +10 Defensive Awareness 90 2 8 Level 1 Kohler 88 CB PAC 85 SHO 56 PAS 79 DRI 75 DEF 87 PHY 87 R 3 ★ 4 CB 85.4 Kohler 90 CB PAC 87 SHO 56 PAS 79 DRI 76 DEF 87 PHY 87 R 3 ★ 4 CB 85.4 UPGRADES +2 OVR 90 +2 PAC 87 +5 Agility 88 2 8</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CB, LB, RB Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY45" t="inlineStr">
@@ -9385,15 +9341,10 @@
       </c>
       <c r="CZ45" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CB, LB, RB Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>WTSS Journey 2 - Defender [SP 8]</t>
         </is>
       </c>
       <c r="DA45" t="inlineStr">
-        <is>
-          <t>WTSS Journey 2 - Defender [SP 8]</t>
-        </is>
-      </c>
-      <c r="DB45" t="inlineStr">
         <is>
           <t>WTSS Journey 2 - Defender [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Koeman 71 CB PAC 70 SHO 72 PAS 71 DRI 68 DEF 82 PHY 73 CDM R 3 ★ 3 CB 64.0 Koeman 90 CB PAC 87 SHO 72 PAS 80 DRI 83 DEF 92 PHY 87 CDM R 4 ★ 4 CB 86.0 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CB, LB, RB Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +2 PAC 87 +5 Agility 88 +5 Balance 88 +5 Reactions 90 +5 Composure 90 +10 Standing Tackle 92 +10 Sliding Tackle 92 +10 Interceptions 93 +10 Heading Acc. 94 +10 Defensive Awareness 90 2 8 in 1 month in 1 month 73% 27%</t>
         </is>
@@ -9466,10 +9417,10 @@
       <c r="X46" t="n">
         <v>4</v>
       </c>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="n">
+      <c r="Y46" t="n">
         <v>92</v>
       </c>
+      <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
@@ -9481,31 +9432,31 @@
       <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
-      <c r="AL46" t="inlineStr"/>
+      <c r="AL46" t="n">
+        <v>10</v>
+      </c>
       <c r="AM46" t="n">
+        <v>92</v>
+      </c>
+      <c r="AN46" t="n">
         <v>10</v>
       </c>
-      <c r="AN46" t="n">
+      <c r="AO46" t="n">
         <v>92</v>
       </c>
-      <c r="AO46" t="n">
-        <v>10</v>
-      </c>
       <c r="AP46" t="n">
-        <v>92</v>
+        <v>5</v>
       </c>
       <c r="AQ46" t="n">
+        <v>93</v>
+      </c>
+      <c r="AR46" t="n">
         <v>5</v>
       </c>
-      <c r="AR46" t="n">
-        <v>93</v>
-      </c>
       <c r="AS46" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT46" t="n">
         <v>94</v>
       </c>
+      <c r="AT46" t="inlineStr"/>
       <c r="AU46" t="inlineStr"/>
       <c r="AV46" t="inlineStr"/>
       <c r="AW46" t="inlineStr"/>
@@ -9523,45 +9474,45 @@
       <c r="BI46" t="inlineStr"/>
       <c r="BJ46" t="inlineStr"/>
       <c r="BK46" t="inlineStr"/>
-      <c r="BL46" t="inlineStr"/>
+      <c r="BL46" t="n">
+        <v>5</v>
+      </c>
       <c r="BM46" t="n">
+        <v>93</v>
+      </c>
+      <c r="BN46" t="inlineStr"/>
+      <c r="BO46" t="inlineStr"/>
+      <c r="BP46" t="n">
         <v>5</v>
       </c>
-      <c r="BN46" t="n">
+      <c r="BQ46" t="n">
+        <v>94</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS46" t="n">
         <v>93</v>
       </c>
-      <c r="BO46" t="inlineStr"/>
-      <c r="BP46" t="inlineStr"/>
-      <c r="BQ46" t="n">
+      <c r="BT46" t="n">
         <v>5</v>
       </c>
-      <c r="BR46" t="n">
+      <c r="BU46" t="n">
         <v>94</v>
       </c>
-      <c r="BS46" t="n">
+      <c r="BV46" t="n">
         <v>5</v>
       </c>
-      <c r="BT46" t="n">
+      <c r="BW46" t="n">
+        <v>94</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BY46" t="n">
         <v>93</v>
       </c>
-      <c r="BU46" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV46" t="n">
-        <v>94</v>
-      </c>
-      <c r="BW46" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX46" t="n">
-        <v>94</v>
-      </c>
-      <c r="BY46" t="n">
-        <v>5</v>
-      </c>
-      <c r="BZ46" t="n">
-        <v>93</v>
-      </c>
+      <c r="BZ46" t="inlineStr"/>
       <c r="CA46" t="inlineStr"/>
       <c r="CB46" t="inlineStr"/>
       <c r="CC46" t="inlineStr"/>
@@ -9579,17 +9530,21 @@
       <c r="CO46" t="inlineStr"/>
       <c r="CP46" t="inlineStr"/>
       <c r="CQ46" t="inlineStr"/>
-      <c r="CR46" t="inlineStr"/>
-      <c r="CS46" t="n">
+      <c r="CR46" t="n">
         <v>4</v>
       </c>
+      <c r="CS46" t="inlineStr"/>
       <c r="CT46" t="inlineStr"/>
       <c r="CU46" t="inlineStr"/>
       <c r="CV46" t="inlineStr"/>
-      <c r="CW46" t="inlineStr"/>
+      <c r="CW46" t="inlineStr">
+        <is>
+          <t>+2 OVR 92 +4 SM +5 Acceleration 92 +5 Sprint Speed 92 +5 Positioning 93 +5 Finishing 94 +5 Curve 93 +5 Balance 94 +5 Reactions 93 +5 Ball Control 94 +5 Dribbling 94 +5 Composure 93 3 8 Level 1 Park Ji Sung 90 RW PAC 90 SHO 90 PAS 89 DRI 89 DEF 64 PHY 77 RM CM CAM R 4 ★ 4 RM 85.7 Park Ji Sung 92 RW PAC 92 SHO 90 PAS 89 DRI 89 DEF 64 PHY 77 RM CM CAM R 4 ★ 4 RM 85.7 UPGRADES +2 OVR 92 +5 Acceleration 92 +5 Sprint Speed 92 3 8</t>
+        </is>
+      </c>
       <c r="CX46" t="inlineStr">
         <is>
-          <t>+2 OVR 92 +4 SM +5 Acceleration 92 +5 Sprint Speed 92 +5 Positioning 93 +5 Finishing 94 +5 Curve 93 +5 Balance 94 +5 Reactions 93 +5 Ball Control 94 +5 Dribbling 94 +5 Composure 93 3 8 Level 1 Park Ji Sung 90 RW PAC 90 SHO 90 PAS 89 DRI 89 DEF 64 PHY 77 RM CM CAM R 4 ★ 4 RM 85.7 Park Ji Sung 92 RW PAC 92 SHO 90 PAS 89 DRI 89 DEF 64 PHY 77 RM CM CAM R 4 ★ 4 RM 85.7 UPGRADES +2 OVR 92 +5 Acceleration 92 +5 Sprint Speed 92 3 8</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position ST, RW, LW Max PS 10 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY46" t="inlineStr">
@@ -9599,15 +9554,10 @@
       </c>
       <c r="CZ46" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position ST, RW, LW Max PS 10 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>WTSS Journey 3 - Attacker [SP 21]</t>
         </is>
       </c>
       <c r="DA46" t="inlineStr">
-        <is>
-          <t>WTSS Journey 3 - Attacker [SP 21]</t>
-        </is>
-      </c>
-      <c r="DB46" t="inlineStr">
         <is>
           <t>WTSS Journey 3 - Attacker [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. Smolarek 73 ST PAC 80 SHO 84 PAS 67 DRI 77 DEF 28 PHY 68 LW L 3 ★ 3 LW 70.8 Smolarek 92 ST PAC 92 SHO 92 PAS 86 DRI 93 DEF 28 PHY 76 LW L 5 ★ 4 LW 92.4 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position ST, RW, LW Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +4 SM +5 Acceleration 92 +5 Sprint Speed 92 +5 Positioning 93 +5 Finishing 94 +5 Curve 93 +5 Balance 94 +5 Reactions 93 +5 Ball Control 94 +5 Dribbling 94 +5 Composure 93 3 8 in 1 month in 1 month 71% 29%</t>
         </is>
@@ -9680,16 +9630,16 @@
       <c r="X47" t="n">
         <v>4</v>
       </c>
-      <c r="Y47" t="inlineStr"/>
+      <c r="Y47" t="n">
+        <v>92</v>
+      </c>
       <c r="Z47" t="n">
-        <v>92</v>
+        <v>3</v>
       </c>
       <c r="AA47" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB47" t="n">
         <v>90</v>
       </c>
+      <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr"/>
@@ -9715,59 +9665,59 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr"/>
       <c r="BA47" t="inlineStr"/>
-      <c r="BB47" t="inlineStr"/>
+      <c r="BB47" t="n">
+        <v>5</v>
+      </c>
       <c r="BC47" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD47" t="n">
         <v>88</v>
       </c>
+      <c r="BD47" t="inlineStr"/>
       <c r="BE47" t="inlineStr"/>
       <c r="BF47" t="inlineStr"/>
       <c r="BG47" t="inlineStr"/>
-      <c r="BH47" t="inlineStr"/>
+      <c r="BH47" t="n">
+        <v>5</v>
+      </c>
       <c r="BI47" t="n">
+        <v>88</v>
+      </c>
+      <c r="BJ47" t="n">
         <v>5</v>
       </c>
-      <c r="BJ47" t="n">
+      <c r="BK47" t="n">
         <v>88</v>
       </c>
-      <c r="BK47" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL47" t="n">
-        <v>88</v>
-      </c>
+      <c r="BL47" t="inlineStr"/>
       <c r="BM47" t="inlineStr"/>
       <c r="BN47" t="inlineStr"/>
       <c r="BO47" t="inlineStr"/>
       <c r="BP47" t="inlineStr"/>
       <c r="BQ47" t="inlineStr"/>
-      <c r="BR47" t="inlineStr"/>
+      <c r="BR47" t="n">
+        <v>10</v>
+      </c>
       <c r="BS47" t="n">
+        <v>93</v>
+      </c>
+      <c r="BT47" t="n">
         <v>10</v>
       </c>
-      <c r="BT47" t="n">
+      <c r="BU47" t="n">
+        <v>88</v>
+      </c>
+      <c r="BV47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BW47" t="n">
+        <v>88</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BY47" t="n">
         <v>93</v>
       </c>
-      <c r="BU47" t="n">
-        <v>10</v>
-      </c>
-      <c r="BV47" t="n">
-        <v>88</v>
-      </c>
-      <c r="BW47" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX47" t="n">
-        <v>88</v>
-      </c>
-      <c r="BY47" t="n">
-        <v>5</v>
-      </c>
-      <c r="BZ47" t="n">
-        <v>93</v>
-      </c>
+      <c r="BZ47" t="inlineStr"/>
       <c r="CA47" t="inlineStr"/>
       <c r="CB47" t="inlineStr"/>
       <c r="CC47" t="inlineStr"/>
@@ -9777,45 +9727,49 @@
       <c r="CG47" t="inlineStr"/>
       <c r="CH47" t="inlineStr"/>
       <c r="CI47" t="inlineStr"/>
-      <c r="CJ47" t="inlineStr"/>
+      <c r="CJ47" t="n">
+        <v>10</v>
+      </c>
       <c r="CK47" t="n">
+        <v>90</v>
+      </c>
+      <c r="CL47" t="n">
         <v>10</v>
       </c>
-      <c r="CL47" t="n">
-        <v>90</v>
-      </c>
       <c r="CM47" t="n">
+        <v>95</v>
+      </c>
+      <c r="CN47" t="n">
         <v>10</v>
       </c>
-      <c r="CN47" t="n">
-        <v>95</v>
-      </c>
       <c r="CO47" t="n">
+        <v>93</v>
+      </c>
+      <c r="CP47" t="n">
         <v>10</v>
       </c>
-      <c r="CP47" t="n">
-        <v>93</v>
-      </c>
       <c r="CQ47" t="n">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="CR47" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="CS47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CT47" t="n">
         <v>4</v>
       </c>
-      <c r="CU47" t="n">
-        <v>4</v>
-      </c>
+      <c r="CU47" t="inlineStr"/>
       <c r="CV47" t="inlineStr"/>
-      <c r="CW47" t="inlineStr"/>
+      <c r="CW47" t="inlineStr">
+        <is>
+          <t>+2 OVR 92 +3 PAC 90 +3 SM 4 +4 WF +5 Reactions 93 +5 Ball Control 88 +5 Dribbling 88 +5 Composure 93 +5 Vision 88 +5 Short Pass 88 +5 Long Pass 88 +10 Aggression 88 +10 Jumping 90 +10 Stamina 95 +10 Strength 93 3 8 Level 1 Kohler 90 CB PAC 87 SHO 56 PAS 79 DRI 76 DEF 92 PHY 87 R 3 ★ 4 CB 88.3 Kohler 92 CB PAC 87 SHO 56 PAS 79 DRI 78 DEF 92 PHY 87 R 3 ★ 4 CB 88.3 UPGRADES +2 OVR 92 +5 Reactions 93 +5 Ball Control 88 3 8</t>
+        </is>
+      </c>
       <c r="CX47" t="inlineStr">
         <is>
-          <t>+2 OVR 92 +3 PAC 90 +3 SM 4 +4 WF +5 Reactions 93 +5 Ball Control 88 +5 Dribbling 88 +5 Composure 93 +5 Vision 88 +5 Short Pass 88 +5 Long Pass 88 +10 Aggression 88 +10 Jumping 90 +10 Stamina 95 +10 Strength 93 3 8 Level 1 Kohler 90 CB PAC 87 SHO 56 PAS 79 DRI 76 DEF 92 PHY 87 R 3 ★ 4 CB 88.3 Kohler 92 CB PAC 87 SHO 56 PAS 79 DRI 78 DEF 92 PHY 87 R 3 ★ 4 CB 88.3 UPGRADES +2 OVR 92 +5 Reactions 93 +5 Ball Control 88 3 8</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CB, LB, RB Max PS 10 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY47" t="inlineStr">
@@ -9825,15 +9779,10 @@
       </c>
       <c r="CZ47" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CB, LB, RB Max PS 10 Max PS+ 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>WTSS Journey 3 - Defender [SP 21]</t>
         </is>
       </c>
       <c r="DA47" t="inlineStr">
-        <is>
-          <t>WTSS Journey 3 - Defender [SP 21]</t>
-        </is>
-      </c>
-      <c r="DB47" t="inlineStr">
         <is>
           <t>WTSS Journey 3 - Defender [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. Thuram 74 RB PAC 75 SHO 52 PAS 67 DRI 65 DEF 84 PHY 74 CB R 3 ★ 3 RB 69.3 Thuram 92 RB PAC 90 SHO 70 PAS 82 DRI 85 DEF 92 PHY 93 CB R 4 ★ 5 RB 92.5 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CB, LB, RB Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +3 PAC 90 +3 SM 4 +4 WF +5 Reactions 93 +5 Ball Control 88 +5 Dribbling 88 +5 Composure 93 +5 Vision 88 +5 Short Pass 88 +5 Long Pass 88 +10 Aggression 88 +10 Jumping 90 +10 Stamina 95 +10 Strength 93 3 8 Show less in 1 month in 1 month 76% 24%</t>
         </is>
@@ -9906,18 +9855,18 @@
       <c r="X48" t="n">
         <v>4</v>
       </c>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="n">
+      <c r="Y48" t="n">
         <v>90</v>
       </c>
+      <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
+      <c r="AB48" t="n">
+        <v>4</v>
+      </c>
       <c r="AC48" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD48" t="n">
         <v>88</v>
       </c>
+      <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
@@ -9925,19 +9874,19 @@
       <c r="AI48" t="inlineStr"/>
       <c r="AJ48" t="inlineStr"/>
       <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="inlineStr"/>
+      <c r="AL48" t="n">
+        <v>5</v>
+      </c>
       <c r="AM48" t="n">
-        <v>5</v>
+        <v>88</v>
       </c>
       <c r="AN48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO48" t="n">
         <v>88</v>
       </c>
-      <c r="AO48" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>88</v>
-      </c>
+      <c r="AP48" t="inlineStr"/>
       <c r="AQ48" t="inlineStr"/>
       <c r="AR48" t="inlineStr"/>
       <c r="AS48" t="inlineStr"/>
@@ -9949,39 +9898,39 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr"/>
       <c r="BA48" t="inlineStr"/>
-      <c r="BB48" t="inlineStr"/>
+      <c r="BB48" t="n">
+        <v>15</v>
+      </c>
       <c r="BC48" t="n">
+        <v>91</v>
+      </c>
+      <c r="BD48" t="n">
         <v>15</v>
       </c>
-      <c r="BD48" t="n">
-        <v>91</v>
-      </c>
       <c r="BE48" t="n">
+        <v>89</v>
+      </c>
+      <c r="BF48" t="inlineStr"/>
+      <c r="BG48" t="inlineStr"/>
+      <c r="BH48" t="n">
+        <v>30</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>93</v>
+      </c>
+      <c r="BJ48" t="n">
         <v>15</v>
       </c>
-      <c r="BF48" t="n">
-        <v>89</v>
-      </c>
-      <c r="BG48" t="inlineStr"/>
-      <c r="BH48" t="inlineStr"/>
-      <c r="BI48" t="n">
-        <v>30</v>
-      </c>
-      <c r="BJ48" t="n">
-        <v>93</v>
-      </c>
       <c r="BK48" t="n">
+        <v>92</v>
+      </c>
+      <c r="BL48" t="n">
         <v>15</v>
       </c>
-      <c r="BL48" t="n">
-        <v>92</v>
-      </c>
       <c r="BM48" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN48" t="n">
         <v>90</v>
       </c>
+      <c r="BN48" t="inlineStr"/>
       <c r="BO48" t="inlineStr"/>
       <c r="BP48" t="inlineStr"/>
       <c r="BQ48" t="inlineStr"/>
@@ -9993,73 +9942,77 @@
       <c r="BW48" t="inlineStr"/>
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
-      <c r="BZ48" t="inlineStr"/>
+      <c r="BZ48" t="n">
+        <v>30</v>
+      </c>
       <c r="CA48" t="n">
+        <v>90</v>
+      </c>
+      <c r="CB48" t="n">
+        <v>15</v>
+      </c>
+      <c r="CC48" t="n">
+        <v>89</v>
+      </c>
+      <c r="CD48" t="n">
+        <v>15</v>
+      </c>
+      <c r="CE48" t="n">
+        <v>89</v>
+      </c>
+      <c r="CF48" t="n">
+        <v>15</v>
+      </c>
+      <c r="CG48" t="n">
+        <v>90</v>
+      </c>
+      <c r="CH48" t="n">
+        <v>15</v>
+      </c>
+      <c r="CI48" t="n">
+        <v>88</v>
+      </c>
+      <c r="CJ48" t="n">
+        <v>15</v>
+      </c>
+      <c r="CK48" t="n">
+        <v>89</v>
+      </c>
+      <c r="CL48" t="n">
         <v>30</v>
       </c>
-      <c r="CB48" t="n">
+      <c r="CM48" t="n">
         <v>90</v>
       </c>
-      <c r="CC48" t="n">
+      <c r="CN48" t="n">
         <v>15</v>
       </c>
-      <c r="CD48" t="n">
+      <c r="CO48" t="n">
         <v>89</v>
       </c>
-      <c r="CE48" t="n">
+      <c r="CP48" t="n">
         <v>15</v>
       </c>
-      <c r="CF48" t="n">
+      <c r="CQ48" t="n">
         <v>89</v>
       </c>
-      <c r="CG48" t="n">
-        <v>15</v>
-      </c>
-      <c r="CH48" t="n">
-        <v>90</v>
-      </c>
-      <c r="CI48" t="n">
-        <v>15</v>
-      </c>
-      <c r="CJ48" t="n">
-        <v>88</v>
-      </c>
-      <c r="CK48" t="n">
-        <v>15</v>
-      </c>
-      <c r="CL48" t="n">
-        <v>89</v>
-      </c>
-      <c r="CM48" t="n">
-        <v>30</v>
-      </c>
-      <c r="CN48" t="n">
-        <v>90</v>
-      </c>
-      <c r="CO48" t="n">
-        <v>15</v>
-      </c>
-      <c r="CP48" t="n">
-        <v>89</v>
-      </c>
-      <c r="CQ48" t="n">
-        <v>15</v>
-      </c>
       <c r="CR48" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="CS48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT48" t="n">
         <v>4</v>
       </c>
+      <c r="CT48" t="inlineStr"/>
       <c r="CU48" t="inlineStr"/>
       <c r="CV48" t="inlineStr"/>
-      <c r="CW48" t="inlineStr"/>
+      <c r="CW48" t="inlineStr">
+        <is>
+          <t>+2 OVR 90 +4 SHO 88 +1 SM 4 +5 Sprint Speed 88 +15 Short Pass 93 +15 Interceptions 90 +15 Stamina 90 +5 Acceleration 88 +15 Fk Accuracy 89 +15 Defensive Awareness 89 +15 Strength 89 +15 Vision 91 +15 Long Pass 92 +15 Heading Acc. 89 +15 Sliding Tackle 88 +15 Aggression 89 +15 Crossing 89 +15 Curve 90 +15 Standing Tackle 90 +15 Jumping 89 2 8 Level 1 Ronaldinho 88 CAM PAC 88 SHO 86 PAS 89 DRI 87 DEF 30 PHY 78 LW R 5 ★ 4 LW 83.8 Ronaldinho 90 CAM PAC 88 SHO 86 PAS 90 DRI 87 DEF 33 PHY 78 LW R 5 ★ 4 LW 83.8 UPGRADES +2 OVR 90 +5 Sprint Speed 88 +15 Short Pass 93 +15 Interceptions 90 +15 Stamina 90 2</t>
+        </is>
+      </c>
       <c r="CX48" t="inlineStr">
         <is>
-          <t>+2 OVR 90 +4 SHO 88 +1 SM 4 +5 Sprint Speed 88 +15 Short Pass 93 +15 Interceptions 90 +15 Stamina 90 +5 Acceleration 88 +15 Fk Accuracy 89 +15 Defensive Awareness 89 +15 Strength 89 +15 Vision 91 +15 Long Pass 92 +15 Heading Acc. 89 +15 Sliding Tackle 88 +15 Aggression 89 +15 Crossing 89 +15 Curve 90 +15 Standing Tackle 90 +15 Jumping 89 2 8 Level 1 Ronaldinho 88 CAM PAC 88 SHO 86 PAS 89 DRI 87 DEF 30 PHY 78 LW R 5 ★ 4 LW 83.8 Ronaldinho 90 CAM PAC 88 SHO 86 PAS 90 DRI 87 DEF 33 PHY 78 LW R 5 ★ 4 LW 83.8 UPGRADES +2 OVR 90 +5 Sprint Speed 88 +15 Short Pass 93 +15 Interceptions 90 +15 Stamina 90 2</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CAM, CDM, CM Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY48" t="inlineStr">
@@ -10069,15 +10022,10 @@
       </c>
       <c r="CZ48" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CAM, CDM, CM Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>WTSS Journey 2 - Midfielder [SP 8]</t>
         </is>
       </c>
       <c r="DA48" t="inlineStr">
-        <is>
-          <t>WTSS Journey 2 - Midfielder [SP 8]</t>
-        </is>
-      </c>
-      <c r="DB48" t="inlineStr">
         <is>
           <t>WTSS Journey 2 - Midfielder [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Beckenbauer 71 CDM PAC 70 SHO 52 PAS 76 DRI 64 DEF 80 PHY 70 CB CM R 3 ★ 4 CDM 69.4 Beckenbauer 90 CDM PAC 88 SHO 76 PAS 91 DRI 87 DEF 89 PHY 90 CB CM R 4 ★ 4 CM 89.6 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CAM, CDM, CM Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +4 SHO 88 +1 SM 4 +5 Sprint Speed 88 +15 Short Pass 93 +15 Interceptions 90 +15 Stamina 90 +5 Acceleration 88 +15 Fk Accuracy 89 +15 Defensive Awareness 89 +15 Strength 89 +15 Vision 91 +15 Long Pass 92 +15 Heading Acc. 89 +15 Sliding Tackle 88 +15 Aggression 89 +15 Crossing 89 +15 Curve 90 +15 Standing Tackle 90 +15 Jumping 89 2 8 Show less in 1 month in 1 month 77% 23%</t>
         </is>
@@ -10142,10 +10090,10 @@
       <c r="X49" t="n">
         <v>60</v>
       </c>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="n">
+      <c r="Y49" t="n">
         <v>88</v>
       </c>
+      <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr"/>
@@ -10157,123 +10105,123 @@
       <c r="AI49" t="inlineStr"/>
       <c r="AJ49" t="inlineStr"/>
       <c r="AK49" t="inlineStr"/>
-      <c r="AL49" t="inlineStr"/>
+      <c r="AL49" t="n">
+        <v>60</v>
+      </c>
       <c r="AM49" t="n">
+        <v>88</v>
+      </c>
+      <c r="AN49" t="n">
         <v>60</v>
       </c>
-      <c r="AN49" t="n">
+      <c r="AO49" t="n">
         <v>88</v>
       </c>
-      <c r="AO49" t="n">
+      <c r="AP49" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>84</v>
+      </c>
+      <c r="AR49" t="n">
         <v>60</v>
       </c>
-      <c r="AP49" t="n">
+      <c r="AS49" t="n">
+        <v>87</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>60</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>83</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>60</v>
+      </c>
+      <c r="AW49" t="n">
         <v>88</v>
       </c>
-      <c r="AQ49" t="n">
+      <c r="AX49" t="n">
         <v>30</v>
       </c>
-      <c r="AR49" t="n">
-        <v>84</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT49" t="n">
+      <c r="AY49" t="n">
         <v>87</v>
       </c>
-      <c r="AU49" t="n">
-        <v>60</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>83</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX49" t="n">
+      <c r="AZ49" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>80</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC49" t="n">
         <v>88</v>
       </c>
-      <c r="AY49" t="n">
-        <v>30</v>
-      </c>
-      <c r="AZ49" t="n">
+      <c r="BD49" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE49" t="n">
         <v>87</v>
       </c>
-      <c r="BA49" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>80</v>
-      </c>
-      <c r="BC49" t="n">
+      <c r="BF49" t="inlineStr"/>
+      <c r="BG49" t="inlineStr"/>
+      <c r="BH49" t="n">
         <v>20</v>
       </c>
-      <c r="BD49" t="n">
+      <c r="BI49" t="n">
+        <v>90</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK49" t="n">
         <v>88</v>
       </c>
-      <c r="BE49" t="n">
+      <c r="BL49" t="n">
         <v>20</v>
       </c>
-      <c r="BF49" t="n">
+      <c r="BM49" t="n">
+        <v>88</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>25</v>
+      </c>
+      <c r="BO49" t="n">
         <v>87</v>
       </c>
-      <c r="BG49" t="inlineStr"/>
-      <c r="BH49" t="inlineStr"/>
-      <c r="BI49" t="n">
-        <v>20</v>
-      </c>
-      <c r="BJ49" t="n">
-        <v>90</v>
-      </c>
-      <c r="BK49" t="n">
-        <v>20</v>
-      </c>
-      <c r="BL49" t="n">
+      <c r="BP49" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ49" t="n">
         <v>88</v>
       </c>
-      <c r="BM49" t="n">
-        <v>20</v>
-      </c>
-      <c r="BN49" t="n">
+      <c r="BR49" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS49" t="n">
+        <v>86</v>
+      </c>
+      <c r="BT49" t="n">
+        <v>25</v>
+      </c>
+      <c r="BU49" t="n">
         <v>88</v>
       </c>
-      <c r="BO49" t="n">
+      <c r="BV49" t="n">
         <v>25</v>
       </c>
-      <c r="BP49" t="n">
+      <c r="BW49" t="n">
         <v>87</v>
       </c>
-      <c r="BQ49" t="n">
+      <c r="BX49" t="n">
         <v>25</v>
       </c>
-      <c r="BR49" t="n">
+      <c r="BY49" t="n">
         <v>88</v>
       </c>
-      <c r="BS49" t="n">
-        <v>25</v>
-      </c>
-      <c r="BT49" t="n">
-        <v>86</v>
-      </c>
-      <c r="BU49" t="n">
-        <v>25</v>
-      </c>
-      <c r="BV49" t="n">
-        <v>88</v>
-      </c>
-      <c r="BW49" t="n">
-        <v>25</v>
-      </c>
-      <c r="BX49" t="n">
-        <v>87</v>
-      </c>
-      <c r="BY49" t="n">
-        <v>25</v>
-      </c>
-      <c r="BZ49" t="n">
-        <v>88</v>
-      </c>
+      <c r="BZ49" t="inlineStr"/>
       <c r="CA49" t="inlineStr"/>
       <c r="CB49" t="inlineStr"/>
       <c r="CC49" t="inlineStr"/>
@@ -10285,41 +10233,45 @@
       <c r="CI49" t="inlineStr"/>
       <c r="CJ49" t="inlineStr"/>
       <c r="CK49" t="inlineStr"/>
-      <c r="CL49" t="inlineStr"/>
+      <c r="CL49" t="n">
+        <v>20</v>
+      </c>
       <c r="CM49" t="n">
+        <v>90</v>
+      </c>
+      <c r="CN49" t="n">
         <v>20</v>
       </c>
-      <c r="CN49" t="n">
-        <v>90</v>
-      </c>
       <c r="CO49" t="n">
+        <v>75</v>
+      </c>
+      <c r="CP49" t="n">
         <v>20</v>
       </c>
-      <c r="CP49" t="n">
-        <v>75</v>
-      </c>
       <c r="CQ49" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="CR49" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="CS49" t="n">
+        <v>4</v>
+      </c>
+      <c r="CT49" t="n">
         <v>1</v>
       </c>
-      <c r="CT49" t="n">
+      <c r="CU49" t="n">
         <v>4</v>
       </c>
-      <c r="CU49" t="n">
-        <v>1</v>
-      </c>
-      <c r="CV49" t="n">
-        <v>4</v>
-      </c>
-      <c r="CW49" t="inlineStr"/>
+      <c r="CV49" t="inlineStr"/>
+      <c r="CW49" t="inlineStr">
+        <is>
+          <t>+30 OVR 88 +1 SM 4 +1 WF 4 +30 Acceleration 88 +30 Sprint Speed 88 +30 Finishing 87 +30 Shot Power 83 +30 Long Shots 88 +30 Positioning 84 +20 Vision 88 +20 Crossing 87 +20 Fk Accuracy 88 +20 Short Pass 90 +20 Long Pass 88 +30 Volleys 87 +30 Penalties 80 +25 Agility 87 +25 Balance 88 +20 Curve 88 +25 Reactions 86 +25 Ball Control 88 +20 Aggression 70 +25 Dribbling 87 +25 Composure 88 +20 Stamina 90 +20 Strength 75 8 Level 1 Maradona 74 CAM PAC 77 SHO 76 PAS 77 DRI 85 DEF 30 PHY 62 ST L 5 ★ 3 Maradona 88 CAM PAC 88 SHO 85 PAS 77 DRI 85 DEF 30 PHY 62 ST L 5 ★ 3 UPGRADES +30 OVR 88 +30 Acceleration 88 +30 Sprint Speed 88 +30 Finishing 87 +30 Shot Power 83 +30 Long Shots 88</t>
+        </is>
+      </c>
       <c r="CX49" t="inlineStr">
         <is>
-          <t>+30 OVR 88 +1 SM 4 +1 WF 4 +30 Acceleration 88 +30 Sprint Speed 88 +30 Finishing 87 +30 Shot Power 83 +30 Long Shots 88 +30 Positioning 84 +20 Vision 88 +20 Crossing 87 +20 Fk Accuracy 88 +20 Short Pass 90 +20 Long Pass 88 +30 Volleys 87 +30 Penalties 80 +25 Agility 87 +25 Balance 88 +20 Curve 88 +25 Reactions 86 +25 Ball Control 88 +20 Aggression 70 +25 Dribbling 87 +25 Composure 88 +20 Stamina 90 +20 Strength 75 8 Level 1 Maradona 74 CAM PAC 77 SHO 76 PAS 77 DRI 85 DEF 30 PHY 62 ST L 5 ★ 3 Maradona 88 CAM PAC 88 SHO 85 PAS 77 DRI 85 DEF 30 PHY 62 ST L 5 ★ 3 UPGRADES +30 OVR 88 +30 Acceleration 88 +30 Sprint Speed 88 +30 Finishing 87 +30 Shot Power 83 +30 Long Shots 88</t>
+          <t>Rarity World Tour Silver Stars Position ST, RW, LW Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY49" t="inlineStr">
@@ -10329,15 +10281,10 @@
       </c>
       <c r="CZ49" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Position ST, RW, LW Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>WTSS Journey 1 - Attacker [SP 3]</t>
         </is>
       </c>
       <c r="DA49" t="inlineStr">
-        <is>
-          <t>WTSS Journey 1 - Attacker [SP 3]</t>
-        </is>
-      </c>
-      <c r="DB49" t="inlineStr">
         <is>
           <t>WTSS Journey 1 - Attacker [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Garrincha 70 RW PAC 82 SHO 64 PAS 67 DRI 78 DEF 34 PHY 48 RM R 5 ★ 4 RM 70.4 Garrincha 88 RW PAC 88 SHO 86 PAS 87 DRI 87 DEF 34 PHY 67 RM R 5 ★ 4 RM 83.9 REQUIREMENTS Rarity World Tour Silver Stars Position ST, RW, LW Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +1 SM 4 +1 WF 4 +30 Acceleration 88 +30 Sprint Speed 88 +30 Finishing 87 +30 Shot Power 83 +30 Long Shots 88 +30 Positioning 84 +20 Vision 88 +20 Crossing 87 +20 Fk Accuracy 88 +20 Short Pass 90 +20 Long Pass 88 +30 Volleys 87 +30 Penalties 80 +25 Agility 87 +25 Balance 88 +20 Curve 88 +25 Reactions 86 +25 Ball Control 88 +20 Aggression 70 +25 Dribbling 87 +25 Composure 88 +20 Stamina 90 +20 Strength 75 8 in 1 month in 1 month 78% 22%</t>
         </is>
@@ -10402,10 +10349,10 @@
       <c r="X50" t="n">
         <v>60</v>
       </c>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="n">
+      <c r="Y50" t="n">
         <v>88</v>
       </c>
+      <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr"/>
@@ -10415,159 +10362,159 @@
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="inlineStr"/>
-      <c r="AJ50" t="inlineStr"/>
+      <c r="AJ50" t="n">
+        <v>20</v>
+      </c>
       <c r="AK50" t="n">
+        <v>84</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP50" t="n">
         <v>20</v>
       </c>
-      <c r="AL50" t="n">
+      <c r="AQ50" t="n">
+        <v>85</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>87</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>87</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>90</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>88</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>85</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>86</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF50" t="inlineStr"/>
+      <c r="BG50" t="inlineStr"/>
+      <c r="BH50" t="n">
+        <v>30</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>87</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>30</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>88</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>60</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>86</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>60</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>86</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>60</v>
+      </c>
+      <c r="BQ50" t="n">
         <v>84</v>
       </c>
-      <c r="AM50" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN50" t="n">
+      <c r="BR50" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS50" t="n">
+        <v>87</v>
+      </c>
+      <c r="BT50" t="n">
+        <v>30</v>
+      </c>
+      <c r="BU50" t="n">
         <v>85</v>
       </c>
-      <c r="AO50" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP50" t="n">
+      <c r="BV50" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW50" t="n">
+        <v>88</v>
+      </c>
+      <c r="BX50" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY50" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ50" t="n">
+        <v>30</v>
+      </c>
+      <c r="CA50" t="n">
         <v>85</v>
       </c>
-      <c r="AQ50" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR50" t="n">
+      <c r="CB50" t="n">
+        <v>30</v>
+      </c>
+      <c r="CC50" t="n">
+        <v>88</v>
+      </c>
+      <c r="CD50" t="n">
+        <v>30</v>
+      </c>
+      <c r="CE50" t="n">
         <v>85</v>
       </c>
-      <c r="AS50" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>87</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>20</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>87</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>90</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ50" t="n">
+      <c r="CF50" t="n">
+        <v>30</v>
+      </c>
+      <c r="CG50" t="n">
+        <v>86</v>
+      </c>
+      <c r="CH50" t="n">
+        <v>30</v>
+      </c>
+      <c r="CI50" t="n">
         <v>88</v>
       </c>
-      <c r="BA50" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>85</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>86</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>30</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>85</v>
-      </c>
-      <c r="BG50" t="inlineStr"/>
-      <c r="BH50" t="inlineStr"/>
-      <c r="BI50" t="n">
-        <v>30</v>
-      </c>
-      <c r="BJ50" t="n">
-        <v>87</v>
-      </c>
-      <c r="BK50" t="n">
-        <v>30</v>
-      </c>
-      <c r="BL50" t="n">
-        <v>88</v>
-      </c>
-      <c r="BM50" t="n">
-        <v>60</v>
-      </c>
-      <c r="BN50" t="n">
-        <v>86</v>
-      </c>
-      <c r="BO50" t="n">
-        <v>60</v>
-      </c>
-      <c r="BP50" t="n">
-        <v>86</v>
-      </c>
-      <c r="BQ50" t="n">
-        <v>60</v>
-      </c>
-      <c r="BR50" t="n">
-        <v>84</v>
-      </c>
-      <c r="BS50" t="n">
-        <v>30</v>
-      </c>
-      <c r="BT50" t="n">
-        <v>87</v>
-      </c>
-      <c r="BU50" t="n">
-        <v>30</v>
-      </c>
-      <c r="BV50" t="n">
-        <v>85</v>
-      </c>
-      <c r="BW50" t="n">
-        <v>30</v>
-      </c>
-      <c r="BX50" t="n">
-        <v>88</v>
-      </c>
-      <c r="BY50" t="n">
-        <v>30</v>
-      </c>
-      <c r="BZ50" t="n">
-        <v>88</v>
-      </c>
-      <c r="CA50" t="n">
-        <v>30</v>
-      </c>
-      <c r="CB50" t="n">
-        <v>85</v>
-      </c>
-      <c r="CC50" t="n">
-        <v>30</v>
-      </c>
-      <c r="CD50" t="n">
-        <v>88</v>
-      </c>
-      <c r="CE50" t="n">
-        <v>30</v>
-      </c>
-      <c r="CF50" t="n">
-        <v>85</v>
-      </c>
-      <c r="CG50" t="n">
-        <v>30</v>
-      </c>
-      <c r="CH50" t="n">
-        <v>86</v>
-      </c>
-      <c r="CI50" t="n">
-        <v>30</v>
-      </c>
-      <c r="CJ50" t="n">
-        <v>88</v>
-      </c>
+      <c r="CJ50" t="inlineStr"/>
       <c r="CK50" t="inlineStr"/>
       <c r="CL50" t="inlineStr"/>
       <c r="CM50" t="inlineStr"/>
@@ -10575,23 +10522,27 @@
       <c r="CO50" t="inlineStr"/>
       <c r="CP50" t="inlineStr"/>
       <c r="CQ50" t="inlineStr"/>
-      <c r="CR50" t="inlineStr"/>
+      <c r="CR50" t="n">
+        <v>1</v>
+      </c>
       <c r="CS50" t="n">
+        <v>4</v>
+      </c>
+      <c r="CT50" t="n">
         <v>1</v>
       </c>
-      <c r="CT50" t="n">
+      <c r="CU50" t="n">
         <v>4</v>
       </c>
-      <c r="CU50" t="n">
-        <v>1</v>
-      </c>
-      <c r="CV50" t="n">
-        <v>4</v>
-      </c>
-      <c r="CW50" t="inlineStr"/>
+      <c r="CV50" t="inlineStr"/>
+      <c r="CW50" t="inlineStr">
+        <is>
+          <t>+30 OVR 88 +20 PHY 84 +1 SM 4 +1 WF 4 +30 Acceleration 85 +30 Sprint Speed 85 +30 Curve 86 +30 Agility 86 +30 Balance 84 +20 Positioning 85 +20 Finishing 87 +20 Shot Power 87 +20 Long Shots 90 +20 Volleys 88 +20 Penalties 85 +30 Reactions 87 +30 Ball Control 85 +30 Vision 86 +30 Crossing 85 +30 Fk Accuracy 88 +30 Short Pass 87 +30 Long Pass 88 +30 Heading Acc. 88 +30 Dribbling 88 +30 Composure 88 +30 Interceptions 85 +30 Defensive Awareness 85 +30 Standing Tackle 86 +30 Sliding Tackle 88 8 Level 1 Cesc Fàbregas 74 CAM PAC 72 SHO 74 PAS 84 DRI 82 DEF 54 PHY 60 ST R 3 ★ 3 Cesc Fàbregas 88 CAM PAC 85 SHO 74 PAS 84 DRI 83 DEF 54 PHY 60 ST R 3 ★ 3 UPGRADES +30 OVR 88 +30 Acceleration 85 +30 Sprint Speed 85 +30 Curve 86 +30 Agility 86 +30 Balance 84 8</t>
+        </is>
+      </c>
       <c r="CX50" t="inlineStr">
         <is>
-          <t>+30 OVR 88 +20 PHY 84 +1 SM 4 +1 WF 4 +30 Acceleration 85 +30 Sprint Speed 85 +30 Curve 86 +30 Agility 86 +30 Balance 84 +20 Positioning 85 +20 Finishing 87 +20 Shot Power 87 +20 Long Shots 90 +20 Volleys 88 +20 Penalties 85 +30 Reactions 87 +30 Ball Control 85 +30 Vision 86 +30 Crossing 85 +30 Fk Accuracy 88 +30 Short Pass 87 +30 Long Pass 88 +30 Heading Acc. 88 +30 Dribbling 88 +30 Composure 88 +30 Interceptions 85 +30 Defensive Awareness 85 +30 Standing Tackle 86 +30 Sliding Tackle 88 8 Level 1 Cesc Fàbregas 74 CAM PAC 72 SHO 74 PAS 84 DRI 82 DEF 54 PHY 60 ST R 3 ★ 3 Cesc Fàbregas 88 CAM PAC 85 SHO 74 PAS 84 DRI 83 DEF 54 PHY 60 ST R 3 ★ 3 UPGRADES +30 OVR 88 +30 Acceleration 85 +30 Sprint Speed 85 +30 Curve 86 +30 Agility 86 +30 Balance 84 8</t>
+          <t>Rarity World Tour Silver Stars Position CAM, CM, CDM Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY50" t="inlineStr">
@@ -10601,15 +10552,10 @@
       </c>
       <c r="CZ50" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Position CAM, CM, CDM Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>WTSS Journey 1 - Midfielder [SP 3]</t>
         </is>
       </c>
       <c r="DA50" t="inlineStr">
-        <is>
-          <t>WTSS Journey 1 - Midfielder [SP 3]</t>
-        </is>
-      </c>
-      <c r="DB50" t="inlineStr">
         <is>
           <t>WTSS Journey 1 - Midfielder [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Beckenbauer 71 CDM PAC 70 SHO 52 PAS 76 DRI 64 DEF 80 PHY 70 CB CM R 3 ★ 4 CDM 69.4 Beckenbauer 88 CDM PAC 85 SHO 72 PAS 87 DRI 87 DEF 86 PHY 84 CB CM R 4 ★ 4 CM 84.3 REQUIREMENTS Rarity World Tour Silver Stars Position CAM, CM, CDM Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +20 PHY 84 +1 SM 4 +1 WF 4 +30 Acceleration 85 +30 Sprint Speed 85 +30 Curve 86 +30 Agility 86 +30 Balance 84 +20 Positioning 85 +20 Finishing 87 +20 Shot Power 87 +20 Long Shots 90 +20 Volleys 88 +20 Penalties 85 +30 Reactions 87 +30 Ball Control 85 +30 Vision 86 +30 Crossing 85 +30 Fk Accuracy 88 +30 Short Pass 87 +30 Long Pass 88 +30 Heading Acc. 88 +30 Dribbling 88 +30 Composure 88 +30 Interceptions 85 +30 Defensive Awareness 85 +30 Standing Tackle 86 +30 Sliding Tackle 88 8 Show less in 1 month in 1 month 80% 20%</t>
         </is>
@@ -10674,18 +10620,18 @@
       <c r="X51" t="n">
         <v>60</v>
       </c>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="n">
+      <c r="Y51" t="n">
         <v>88</v>
       </c>
+      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
+      <c r="AB51" t="n">
+        <v>20</v>
+      </c>
       <c r="AC51" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD51" t="n">
         <v>70</v>
       </c>
+      <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
@@ -10693,19 +10639,19 @@
       <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="inlineStr"/>
+      <c r="AL51" t="n">
+        <v>30</v>
+      </c>
       <c r="AM51" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN51" t="n">
         <v>30</v>
       </c>
-      <c r="AN51" t="n">
+      <c r="AO51" t="n">
         <v>85</v>
       </c>
-      <c r="AO51" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>85</v>
-      </c>
+      <c r="AP51" t="inlineStr"/>
       <c r="AQ51" t="inlineStr"/>
       <c r="AR51" t="inlineStr"/>
       <c r="AS51" t="inlineStr"/>
@@ -10717,145 +10663,149 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="inlineStr"/>
-      <c r="BB51" t="inlineStr"/>
+      <c r="BB51" t="n">
+        <v>30</v>
+      </c>
       <c r="BC51" t="n">
+        <v>75</v>
+      </c>
+      <c r="BD51" t="n">
         <v>30</v>
       </c>
-      <c r="BD51" t="n">
+      <c r="BE51" t="n">
         <v>75</v>
       </c>
-      <c r="BE51" t="n">
+      <c r="BF51" t="inlineStr"/>
+      <c r="BG51" t="inlineStr"/>
+      <c r="BH51" t="n">
         <v>30</v>
       </c>
-      <c r="BF51" t="n">
-        <v>75</v>
-      </c>
-      <c r="BG51" t="inlineStr"/>
-      <c r="BH51" t="inlineStr"/>
       <c r="BI51" t="n">
+        <v>85</v>
+      </c>
+      <c r="BJ51" t="n">
         <v>30</v>
       </c>
-      <c r="BJ51" t="n">
+      <c r="BK51" t="n">
+        <v>80</v>
+      </c>
+      <c r="BL51" t="n">
+        <v>60</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>80</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>30</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>80</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>80</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS51" t="n">
+        <v>88</v>
+      </c>
+      <c r="BT51" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU51" t="n">
         <v>85</v>
       </c>
-      <c r="BK51" t="n">
+      <c r="BV51" t="n">
+        <v>15</v>
+      </c>
+      <c r="BW51" t="n">
+        <v>85</v>
+      </c>
+      <c r="BX51" t="n">
         <v>30</v>
       </c>
-      <c r="BL51" t="n">
+      <c r="BY51" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ51" t="n">
+        <v>30</v>
+      </c>
+      <c r="CA51" t="n">
+        <v>88</v>
+      </c>
+      <c r="CB51" t="n">
+        <v>30</v>
+      </c>
+      <c r="CC51" t="n">
+        <v>87</v>
+      </c>
+      <c r="CD51" t="n">
+        <v>60</v>
+      </c>
+      <c r="CE51" t="n">
+        <v>87</v>
+      </c>
+      <c r="CF51" t="n">
+        <v>60</v>
+      </c>
+      <c r="CG51" t="n">
+        <v>88</v>
+      </c>
+      <c r="CH51" t="n">
+        <v>60</v>
+      </c>
+      <c r="CI51" t="n">
+        <v>86</v>
+      </c>
+      <c r="CJ51" t="n">
+        <v>30</v>
+      </c>
+      <c r="CK51" t="n">
         <v>80</v>
       </c>
-      <c r="BM51" t="n">
-        <v>60</v>
-      </c>
-      <c r="BN51" t="n">
-        <v>80</v>
-      </c>
-      <c r="BO51" t="n">
+      <c r="CL51" t="n">
         <v>30</v>
       </c>
-      <c r="BP51" t="n">
-        <v>80</v>
-      </c>
-      <c r="BQ51" t="n">
-        <v>15</v>
-      </c>
-      <c r="BR51" t="n">
-        <v>80</v>
-      </c>
-      <c r="BS51" t="n">
+      <c r="CM51" t="n">
+        <v>85</v>
+      </c>
+      <c r="CN51" t="n">
         <v>30</v>
       </c>
-      <c r="BT51" t="n">
-        <v>88</v>
-      </c>
-      <c r="BU51" t="n">
-        <v>15</v>
-      </c>
-      <c r="BV51" t="n">
-        <v>85</v>
-      </c>
-      <c r="BW51" t="n">
-        <v>15</v>
-      </c>
-      <c r="BX51" t="n">
-        <v>85</v>
-      </c>
-      <c r="BY51" t="n">
+      <c r="CO51" t="n">
+        <v>87</v>
+      </c>
+      <c r="CP51" t="n">
         <v>30</v>
       </c>
-      <c r="BZ51" t="n">
-        <v>88</v>
-      </c>
-      <c r="CA51" t="n">
-        <v>30</v>
-      </c>
-      <c r="CB51" t="n">
-        <v>88</v>
-      </c>
-      <c r="CC51" t="n">
-        <v>30</v>
-      </c>
-      <c r="CD51" t="n">
-        <v>87</v>
-      </c>
-      <c r="CE51" t="n">
-        <v>60</v>
-      </c>
-      <c r="CF51" t="n">
-        <v>87</v>
-      </c>
-      <c r="CG51" t="n">
-        <v>60</v>
-      </c>
-      <c r="CH51" t="n">
-        <v>88</v>
-      </c>
-      <c r="CI51" t="n">
-        <v>60</v>
-      </c>
-      <c r="CJ51" t="n">
-        <v>86</v>
-      </c>
-      <c r="CK51" t="n">
-        <v>30</v>
-      </c>
-      <c r="CL51" t="n">
-        <v>80</v>
-      </c>
-      <c r="CM51" t="n">
-        <v>30</v>
-      </c>
-      <c r="CN51" t="n">
-        <v>85</v>
-      </c>
-      <c r="CO51" t="n">
-        <v>30</v>
-      </c>
-      <c r="CP51" t="n">
-        <v>87</v>
-      </c>
       <c r="CQ51" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="CR51" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="CS51" t="n">
+        <v>4</v>
+      </c>
+      <c r="CT51" t="n">
         <v>1</v>
       </c>
-      <c r="CT51" t="n">
+      <c r="CU51" t="n">
         <v>4</v>
       </c>
-      <c r="CU51" t="n">
-        <v>1</v>
-      </c>
-      <c r="CV51" t="n">
-        <v>4</v>
-      </c>
-      <c r="CW51" t="inlineStr"/>
+      <c r="CV51" t="inlineStr"/>
+      <c r="CW51" t="inlineStr">
+        <is>
+          <t>+30 OVR 88 +20 SHO 70 +1 SM 4 +1 WF 4 +30 Curve 80 +15 Agility 80 +30 Defensive Awareness 87 +30 Standing Tackle 88 +30 Sliding Tackle 86 +30 Acceleration 85 +30 Sprint Speed 85 +30 Vision 75 +30 Crossing 75 +30 Fk Accuracy 65 +30 Short Pass 85 +30 Long Pass 80 +15 Balance 80 +30 Reactions 88 +15 Ball Control 85 +30 Jumping 80 +30 Stamina 85 +30 Strength 87 +15 Dribbling 85 +30 Composure 88 +30 Interceptions 88 +30 Heading Acc. 87 +30 Aggression 90 8 Level 1 Petit 74 CDM PAC 70 SHO 70 PAS 85 DRI 72 DEF 74 PHY 76 LB CM L 3 ★ 3 Petit 88 CDM PAC 70 SHO 70 PAS 86 DRI 73 DEF 83 PHY 76 LB CM L 3 ★ 3 UPGRADES +30 OVR 88 +30 Curve 80 +15 Agility 80 +30 Defensive Awareness 87 +30 Standing Tackle 88 +30 Sliding Tackle 86</t>
+        </is>
+      </c>
       <c r="CX51" t="inlineStr">
         <is>
-          <t>+30 OVR 88 +20 SHO 70 +1 SM 4 +1 WF 4 +30 Curve 80 +15 Agility 80 +30 Defensive Awareness 87 +30 Standing Tackle 88 +30 Sliding Tackle 86 +30 Acceleration 85 +30 Sprint Speed 85 +30 Vision 75 +30 Crossing 75 +30 Fk Accuracy 65 +30 Short Pass 85 +30 Long Pass 80 +15 Balance 80 +30 Reactions 88 +15 Ball Control 85 +30 Jumping 80 +30 Stamina 85 +30 Strength 87 +15 Dribbling 85 +30 Composure 88 +30 Interceptions 88 +30 Heading Acc. 87 +30 Aggression 90 8 Level 1 Petit 74 CDM PAC 70 SHO 70 PAS 85 DRI 72 DEF 74 PHY 76 LB CM L 3 ★ 3 Petit 88 CDM PAC 70 SHO 70 PAS 86 DRI 73 DEF 83 PHY 76 LB CM L 3 ★ 3 UPGRADES +30 OVR 88 +30 Curve 80 +15 Agility 80 +30 Defensive Awareness 87 +30 Standing Tackle 88 +30 Sliding Tackle 86</t>
+          <t>Rarity World Tour Silver Stars Position CB, LB, RB Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY51" t="inlineStr">
@@ -10865,15 +10815,10 @@
       </c>
       <c r="CZ51" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Position CB, LB, RB Max PS 10 Max PS+ 1 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>WTSS Journey 1 - Defender [SP 3]</t>
         </is>
       </c>
       <c r="DA51" t="inlineStr">
-        <is>
-          <t>WTSS Journey 1 - Defender [SP 3]</t>
-        </is>
-      </c>
-      <c r="DB51" t="inlineStr">
         <is>
           <t>WTSS Journey 1 - Defender [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Koeman 71 CB PAC 70 SHO 72 PAS 71 DRI 68 DEF 82 PHY 73 CDM R 3 ★ 3 CB 64.0 Koeman 88 CB PAC 85 SHO 72 PAS 80 DRI 82 DEF 87 PHY 87 CDM R 4 ★ 4 CB 80.4 REQUIREMENTS Rarity World Tour Silver Stars Position CB, LB, RB Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +20 SHO 70 +1 SM 4 +1 WF 4 +30 Curve 80 +15 Agility 80 +30 Defensive Awareness 87 +30 Standing Tackle 88 +30 Sliding Tackle 86 +30 Acceleration 85 +30 Sprint Speed 85 +30 Vision 75 +30 Crossing 75 +30 Fk Accuracy 65 +30 Short Pass 85 +30 Long Pass 80 +15 Balance 80 +30 Reactions 88 +15 Ball Control 85 +30 Jumping 80 +30 Stamina 85 +30 Strength 87 +15 Dribbling 85 +30 Composure 88 +30 Interceptions 88 +30 Heading Acc. 87 +30 Aggression 90 8 Show less in 1 month in 1 month 82% 18%</t>
         </is>
@@ -11004,10 +10949,14 @@
       <c r="CT52" t="inlineStr"/>
       <c r="CU52" t="inlineStr"/>
       <c r="CV52" t="inlineStr"/>
-      <c r="CW52" t="inlineStr"/>
+      <c r="CW52" t="inlineStr">
+        <is>
+          <t>No upgrades Level 1 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 UPGRADES No upgrades</t>
+        </is>
+      </c>
       <c r="CX52" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 UPGRADES No upgrades</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY52" t="inlineStr">
@@ -11017,15 +10966,10 @@
       </c>
       <c r="CZ52" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Season Ladder Excellence [SP 27]</t>
         </is>
       </c>
       <c r="DA52" t="inlineStr">
-        <is>
-          <t>Season Ladder Excellence [SP 27]</t>
-        </is>
-      </c>
-      <c r="DB52" t="inlineStr">
         <is>
           <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Jacobo Ramón 94 CB PAC 88 SHO 46 PAS 84 DRI 81 DEF 94 PHY 91 R 3 ★ 4 CB 93.8 Jacobo Ramón 94 CB PAC 88 SHO 46 PAS 84 DRI 81 DEF 94 PHY 91 R 3 ★ 4 CB 93.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 1 month in 1 month 30% 70%</t>
         </is>
@@ -11101,13 +11045,13 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="inlineStr"/>
+      <c r="AH53" t="n">
+        <v>2</v>
+      </c>
       <c r="AI53" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ53" t="n">
         <v>92</v>
       </c>
+      <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="inlineStr"/>
       <c r="AM53" t="inlineStr"/>
@@ -11172,10 +11116,14 @@
       <c r="CT53" t="inlineStr"/>
       <c r="CU53" t="inlineStr"/>
       <c r="CV53" t="inlineStr"/>
-      <c r="CW53" t="inlineStr"/>
+      <c r="CW53" t="inlineStr">
+        <is>
+          <t>+2 DEF 92 2 8 Level 1 Lamine Yamal 91 RW PAC 87 SHO 83 PAS 88 DRI 92 DEF 25 PHY 55 RM L 5 ★ 3 Lamine Yamal 91 RW PAC 87 SHO 83 PAS 88 DRI 92 DEF 25 PHY 55 RM L 5 ★ 3 UPGRADES 8</t>
+        </is>
+      </c>
       <c r="CX53" t="inlineStr">
         <is>
-          <t>+2 DEF 92 2 8 Level 1 Lamine Yamal 91 RW PAC 87 SHO 83 PAS 88 DRI 92 DEF 25 PHY 55 RM L 5 ★ 3 Lamine Yamal 91 RW PAC 87 SHO 83 PAS 88 DRI 92 DEF 25 PHY 55 RM L 5 ★ 3 UPGRADES 8</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY53" t="inlineStr">
@@ -11185,15 +11133,10 @@
       </c>
       <c r="CZ53" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
+          <t>Crunch Time</t>
         </is>
       </c>
       <c r="DA53" t="inlineStr">
-        <is>
-          <t>Crunch Time</t>
-        </is>
-      </c>
-      <c r="DB53" t="inlineStr">
         <is>
           <t>Crunch Time Unlocked by completing the Unbreakable objective van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 CB 90.5 van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 90 PHY 88 L 3 ★ 3 CB 93.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 UPGRADES +2 DEF 92 2 8 in 7 months in 7 months 92% 8%</t>
         </is>
@@ -11336,10 +11279,14 @@
       <c r="CT54" t="inlineStr"/>
       <c r="CU54" t="inlineStr"/>
       <c r="CV54" t="inlineStr"/>
-      <c r="CW54" t="inlineStr"/>
+      <c r="CW54" t="inlineStr">
+        <is>
+          <t>2 8 Level 1 Doué 91 RW PAC 91 SHO 87 PAS 86 DRI 95 DEF 61 PHY 83 RM CM LW R 5 ★ 4 Doué 91 RW PAC 91 SHO 87 PAS 86 DRI 95 DEF 61 PHY 83 RM CM LW R 5 ★ 4 UPGRADES 8</t>
+        </is>
+      </c>
       <c r="CX54" t="inlineStr">
         <is>
-          <t>2 8 Level 1 Doué 91 RW PAC 91 SHO 87 PAS 86 DRI 95 DEF 61 PHY 83 RM CM LW R 5 ★ 4 Doué 91 RW PAC 91 SHO 87 PAS 86 DRI 95 DEF 61 PHY 83 RM CM LW R 5 ★ 4 UPGRADES 8</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY54" t="inlineStr">
@@ -11349,15 +11296,10 @@
       </c>
       <c r="CZ54" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
+          <t>Passing Technician</t>
         </is>
       </c>
       <c r="DA54" t="inlineStr">
-        <is>
-          <t>Passing Technician</t>
-        </is>
-      </c>
-      <c r="DB54" t="inlineStr">
         <is>
           <t>Passing Technician Unlocked by completing the Passing Mastermind objective Martínez 88 GK DIV 87 HAN 86 KIC 86 REF 88 SPD 60 POS 90 R 1 ★ 4 GK 89.1 Martínez 88 GK DIV 87 HAN 86 KIC 86 REF 88 SPD 60 POS 90 R 1 ★ 4 GK 91.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 UPGRADES 2 8 in 7 months in 7 months 86% 14%</t>
         </is>
@@ -11419,43 +11361,43 @@
         <v>2</v>
       </c>
       <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
+      <c r="Z55" t="n">
+        <v>4</v>
+      </c>
       <c r="AA55" t="n">
+        <v>92</v>
+      </c>
+      <c r="AB55" t="n">
         <v>4</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AC55" t="n">
+        <v>91</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE55" t="n">
         <v>92</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AF55" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>93</v>
+      </c>
+      <c r="AH55" t="n">
         <v>4</v>
       </c>
-      <c r="AD55" t="n">
-        <v>91</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>92</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>93</v>
-      </c>
       <c r="AI55" t="n">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="AJ55" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="AK55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL55" t="n">
         <v>89</v>
       </c>
+      <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="inlineStr"/>
       <c r="AN55" t="inlineStr"/>
       <c r="AO55" t="inlineStr"/>
@@ -11518,10 +11460,14 @@
       <c r="CT55" t="inlineStr"/>
       <c r="CU55" t="inlineStr"/>
       <c r="CV55" t="inlineStr"/>
-      <c r="CW55" t="inlineStr"/>
+      <c r="CW55" t="inlineStr">
+        <is>
+          <t>+1 OVR +2 PAC 92 +2 SHO 91 +2 PAS 92 +3 DRI 93 +2 DEF 90 +1 PHY 89 Level 1 Doué 91 RW PAC 91 SHO 87 PAS 86 DRI 95 DEF 61 PHY 83 RM CM LW R 5 ★ 4 Doué 92 RW PAC 92 SHO 89 PAS 88 DRI 95 DEF 63 PHY 84 RM CM LW R 5 ★ 4 UPGRADES +1 OVR +2 PAC 92 +2 SHO 91 +2 PAS 92 +3 DRI 93 +2 DEF 90 +1 PHY 89</t>
+        </is>
+      </c>
       <c r="CX55" t="inlineStr">
         <is>
-          <t>+1 OVR +2 PAC 92 +2 SHO 91 +2 PAS 92 +3 DRI 93 +2 DEF 90 +1 PHY 89 Level 1 Doué 91 RW PAC 91 SHO 87 PAS 86 DRI 95 DEF 61 PHY 83 RM CM LW R 5 ★ 4 Doué 92 RW PAC 92 SHO 89 PAS 88 DRI 95 DEF 63 PHY 84 RM CM LW R 5 ★ 4 UPGRADES +1 OVR +2 PAC 92 +2 SHO 91 +2 PAS 92 +3 DRI 93 +2 DEF 90 +1 PHY 89</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY55" t="inlineStr">
@@ -11531,15 +11477,10 @@
       </c>
       <c r="CZ55" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
+          <t>All-Around Impact</t>
         </is>
       </c>
       <c r="DA55" t="inlineStr">
-        <is>
-          <t>All-Around Impact</t>
-        </is>
-      </c>
-      <c r="DB55" t="inlineStr">
         <is>
           <t>All-Around Impact Unlocked by completing the Formation Excellence objective Nesta 88 CB PAC 87 SHO 43 PAS 65 DRI 80 DEF 88 PHY 86 R 3 ★ 4 CB 90.9 Nesta 89 CB PAC 89 SHO 45 PAS 67 DRI 83 DEF 90 PHY 87 R 3 ★ 4 CB 92.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 UPGRADES +1 OVR +2 PAC 92 +2 SHO 91 +2 PAS 92 +3 DRI 93 +2 DEF 90 +1 PHY 89 in 7 months in 7 months 98% 2%</t>
         </is>
@@ -11678,10 +11619,14 @@
       <c r="CT56" t="inlineStr"/>
       <c r="CU56" t="inlineStr"/>
       <c r="CV56" t="inlineStr"/>
-      <c r="CW56" t="inlineStr"/>
+      <c r="CW56" t="inlineStr">
+        <is>
+          <t>2 Level 1 Dembélé 91 CAM PAC 92 SHO 89 PAS 90 DRI 94 DEF 53 PHY 70 RW ST L 5 ★ 5 Dembélé 91 CAM PAC 92 SHO 89 PAS 90 DRI 94 DEF 53 PHY 70 RW ST L 5 ★ 5 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX56" t="inlineStr">
         <is>
-          <t>2 Level 1 Dembélé 91 CAM PAC 92 SHO 89 PAS 90 DRI 94 DEF 53 PHY 70 RW ST L 5 ★ 5 Dembélé 91 CAM PAC 92 SHO 89 PAS 90 DRI 94 DEF 53 PHY 70 RW ST L 5 ★ 5 UPGRADES 2</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY56" t="inlineStr">
@@ -11691,15 +11636,10 @@
       </c>
       <c r="CZ56" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
+          <t>Quick Step+</t>
         </is>
       </c>
       <c r="DA56" t="inlineStr">
-        <is>
-          <t>Quick Step+</t>
-        </is>
-      </c>
-      <c r="DB56" t="inlineStr">
         <is>
           <t>Quick Step+ Unlocked by completing the Ancient Triangle task in the Formation Excellence objective Henrichs 88 RB PAC 90 SHO 75 PAS 85 DRI 86 DEF 88 PHY 84 LB RM R 3 ★ 5 LB 87.0 Henrichs 88 RB PAC 90 SHO 75 PAS 85 DRI 86 DEF 88 PHY 84 LB RM R 3 ★ 5 LB 89.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 UPGRADES 2 in 7 months in 7 months 94% 6%</t>
         </is>
@@ -11838,10 +11778,14 @@
       <c r="CT57" t="inlineStr"/>
       <c r="CU57" t="inlineStr"/>
       <c r="CV57" t="inlineStr"/>
-      <c r="CW57" t="inlineStr"/>
+      <c r="CW57" t="inlineStr">
+        <is>
+          <t>2 Level 1 Doku 91 LW PAC 97 SHO 86 PAS 84 DRI 93 DEF 45 PHY 82 LM RW R 5 ★ 5 Doku 91 LW PAC 97 SHO 86 PAS 84 DRI 93 DEF 45 PHY 82 LM RW R 5 ★ 5 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX57" t="inlineStr">
         <is>
-          <t>2 Level 1 Doku 91 LW PAC 97 SHO 86 PAS 84 DRI 93 DEF 45 PHY 82 LM RW R 5 ★ 5 Doku 91 LW PAC 97 SHO 86 PAS 84 DRI 93 DEF 45 PHY 82 LM RW R 5 ★ 5 UPGRADES 2</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY57" t="inlineStr">
@@ -11851,15 +11795,10 @@
       </c>
       <c r="CZ57" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
+          <t>Finesse Shot+</t>
         </is>
       </c>
       <c r="DA57" t="inlineStr">
-        <is>
-          <t>Finesse Shot+</t>
-        </is>
-      </c>
-      <c r="DB57" t="inlineStr">
         <is>
           <t>Finesse Shot+ Unlocked by completing the Magic Rectangle task in the Formation Excellence objective Kögel 89 LM PAC 93 SHO 88 PAS 86 DRI 89 DEF 61 PHY 76 LW L 5 ★ 4 LM 87.3 Kögel 89 LM PAC 93 SHO 88 PAS 86 DRI 89 DEF 61 PHY 76 LW L 5 ★ 4 LM 89.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 UPGRADES 2 in 7 months in 7 months 95% 5%</t>
         </is>
@@ -11998,10 +11937,14 @@
       <c r="CT58" t="inlineStr"/>
       <c r="CU58" t="inlineStr"/>
       <c r="CV58" t="inlineStr"/>
-      <c r="CW58" t="inlineStr"/>
+      <c r="CW58" t="inlineStr">
+        <is>
+          <t>2 Level 1 Dybala 91 CAM PAC 90 SHO 90 PAS 90 DRI 92 DEF 50 PHY 75 RW ST L 5 ★ 5 Dybala 91 CAM PAC 90 SHO 90 PAS 90 DRI 92 DEF 50 PHY 75 RW ST L 5 ★ 5 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX58" t="inlineStr">
         <is>
-          <t>2 Level 1 Dybala 91 CAM PAC 90 SHO 90 PAS 90 DRI 92 DEF 50 PHY 75 RW ST L 5 ★ 5 Dybala 91 CAM PAC 90 SHO 90 PAS 90 DRI 92 DEF 50 PHY 75 RW ST L 5 ★ 5 UPGRADES 2</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY58" t="inlineStr">
@@ -12011,15 +11954,10 @@
       </c>
       <c r="CZ58" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
+          <t>Technical+</t>
         </is>
       </c>
       <c r="DA58" t="inlineStr">
-        <is>
-          <t>Technical+</t>
-        </is>
-      </c>
-      <c r="DB58" t="inlineStr">
         <is>
           <t>Technical+ Unlocked by completing the The Trident task in the Formation Excellence objective Vini Jr. 90 ST PAC 95 SHO 88 PAS 81 DRI 92 DEF 30 PHY 75 LM LW R 5 ★ 4 LM 87.4 Vini Jr. 90 ST PAC 95 SHO 88 PAS 81 DRI 92 DEF 30 PHY 75 LM LW R 5 ★ 4 LM 88.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 UPGRADES 2 in 7 months in 7 months 82% 18%</t>
         </is>
@@ -12158,10 +12096,14 @@
       <c r="CT59" t="inlineStr"/>
       <c r="CU59" t="inlineStr"/>
       <c r="CV59" t="inlineStr"/>
-      <c r="CW59" t="inlineStr"/>
+      <c r="CW59" t="inlineStr">
+        <is>
+          <t>2 Level 1 Vitinha 91 CM PAC 85 SHO 82 PAS 88 DRI 92 DEF 80 PHY 73 CDM CAM R 5 ★ 4 Vitinha 91 CM PAC 85 SHO 82 PAS 88 DRI 92 DEF 80 PHY 73 CDM CAM R 5 ★ 4 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX59" t="inlineStr">
         <is>
-          <t>2 Level 1 Vitinha 91 CM PAC 85 SHO 82 PAS 88 DRI 92 DEF 80 PHY 73 CDM CAM R 5 ★ 4 Vitinha 91 CM PAC 85 SHO 82 PAS 88 DRI 92 DEF 80 PHY 73 CDM CAM R 5 ★ 4 UPGRADES 2</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY59" t="inlineStr">
@@ -12171,15 +12113,10 @@
       </c>
       <c r="CZ59" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
+          <t>Anticipate+</t>
         </is>
       </c>
       <c r="DA59" t="inlineStr">
-        <is>
-          <t>Anticipate+</t>
-        </is>
-      </c>
-      <c r="DB59" t="inlineStr">
         <is>
           <t>Anticipate+ Unlocked by completing the Three at the Back task in the Formation Excellence objective Mendy 87 LB PAC 91 SHO 70 PAS 80 DRI 81 DEF 84 PHY 90 LM L 4 ★ 5 LB 87.0 Mendy 87 LB PAC 91 SHO 70 PAS 80 DRI 81 DEF 84 PHY 90 LM L 4 ★ 5 LB 88.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 1 UPGRADES 2 in 7 months in 7 months 90% 10%</t>
         </is>
@@ -12318,10 +12255,14 @@
       <c r="CT60" t="inlineStr"/>
       <c r="CU60" t="inlineStr"/>
       <c r="CV60" t="inlineStr"/>
-      <c r="CW60" t="inlineStr"/>
+      <c r="CW60" t="inlineStr">
+        <is>
+          <t>8 Level 1 Rodman 88 ST PAC 91 SHO 88 PAS 81 DRI 86 DEF 70 PHY 86 RM RW R 4 ★ 5 Rodman 88 ST PAC 91 SHO 88 PAS 81 DRI 86 DEF 70 PHY 86 RM RW R 4 ★ 5 UPGRADES 8</t>
+        </is>
+      </c>
       <c r="CX60" t="inlineStr">
         <is>
-          <t>8 Level 1 Rodman 88 ST PAC 91 SHO 88 PAS 81 DRI 86 DEF 70 PHY 86 RM RW R 4 ★ 5 Rodman 88 ST PAC 91 SHO 88 PAS 81 DRI 86 DEF 70 PHY 86 RM RW R 4 ★ 5 UPGRADES 8</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 7 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY60" t="inlineStr">
@@ -12331,15 +12272,10 @@
       </c>
       <c r="CZ60" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 7 Details Submit by in 5 days Expiry in 5 days Coins Cost Free Points Cost Free</t>
+          <t>Finesse Shot</t>
         </is>
       </c>
       <c r="DA60" t="inlineStr">
-        <is>
-          <t>Finesse Shot</t>
-        </is>
-      </c>
-      <c r="DB60" t="inlineStr">
         <is>
           <t>Finesse Shot Unlocked by completing the 10 Finesse Shots task in the Lowe's Scoring Marathon objective Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 88.2 Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 89.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 7 UPGRADES 8 in 5 days in 5 days 28% 72%</t>
         </is>
@@ -12478,10 +12414,14 @@
       <c r="CT61" t="inlineStr"/>
       <c r="CU61" t="inlineStr"/>
       <c r="CV61" t="inlineStr"/>
-      <c r="CW61" t="inlineStr"/>
+      <c r="CW61" t="inlineStr">
+        <is>
+          <t>2 Level 1 Szoboszlai 90 CAM PAC 87 SHO 90 PAS 90 DRI 92 DEF 80 PHY 85 RB CM R 5 ★ 5 Szoboszlai 90 CAM PAC 87 SHO 90 PAS 90 DRI 92 DEF 80 PHY 85 RB CM R 5 ★ 5 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX61" t="inlineStr">
         <is>
-          <t>2 Level 1 Szoboszlai 90 CAM PAC 87 SHO 90 PAS 90 DRI 92 DEF 80 PHY 85 RB CM R 5 ★ 5 Szoboszlai 90 CAM PAC 87 SHO 90 PAS 90 DRI 92 DEF 80 PHY 85 RB CM R 5 ★ 5 UPGRADES 2</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY61" t="inlineStr">
@@ -12491,15 +12431,10 @@
       </c>
       <c r="CZ61" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
+          <t>Low Driven Shot+</t>
         </is>
       </c>
       <c r="DA61" t="inlineStr">
-        <is>
-          <t>Low Driven Shot+</t>
-        </is>
-      </c>
-      <c r="DB61" t="inlineStr">
         <is>
           <t>Low Driven Shot+ Unlocked by completing the Low Driven Shot+ Milestone objective Ginola 90 LM PAC 91 SHO 90 PAS 88 DRI 92 DEF 56 PHY 86 CAM ST R 5 ★ 5 ST 87.6 Ginola 90 LM PAC 91 SHO 90 PAS 88 DRI 92 DEF 56 PHY 86 CAM ST R 5 ★ 5 ST 89.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 UPGRADES 2 in 7 months in 7 months 88% 12%</t>
         </is>
@@ -12638,10 +12573,14 @@
       <c r="CT62" t="inlineStr"/>
       <c r="CU62" t="inlineStr"/>
       <c r="CV62" t="inlineStr"/>
-      <c r="CW62" t="inlineStr"/>
+      <c r="CW62" t="inlineStr">
+        <is>
+          <t>2 Level 1 Dumornay 90 ST PAC 96 SHO 90 PAS 85 DRI 90 DEF 66 PHY 80 CAM R 5 ★ 5 Dumornay 90 ST PAC 96 SHO 90 PAS 85 DRI 90 DEF 66 PHY 80 CAM R 5 ★ 5 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX62" t="inlineStr">
         <is>
-          <t>2 Level 1 Dumornay 90 ST PAC 96 SHO 90 PAS 85 DRI 90 DEF 66 PHY 80 CAM R 5 ★ 5 Dumornay 90 ST PAC 96 SHO 90 PAS 85 DRI 90 DEF 66 PHY 80 CAM R 5 ★ 5 UPGRADES 2</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY62" t="inlineStr">
@@ -12651,15 +12590,10 @@
       </c>
       <c r="CZ62" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 Details Submit by in 7 months Expiry in 7 months Coins Cost Free Points Cost Free</t>
+          <t>Intercept+</t>
         </is>
       </c>
       <c r="DA62" t="inlineStr">
-        <is>
-          <t>Intercept+</t>
-        </is>
-      </c>
-      <c r="DB62" t="inlineStr">
         <is>
           <t>Intercept+ Unlocked by completing the Intercept+ Milestone objective António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 86.6 António Silva 87 CB PAC 89 SHO 46 PAS 75 DRI 78 DEF 87 PHY 89 R 3 ★ 3 CB 90.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 UPGRADES 2 in 7 months in 7 months 96% 4%</t>
         </is>
@@ -12798,10 +12732,14 @@
       <c r="CT63" t="inlineStr"/>
       <c r="CU63" t="inlineStr"/>
       <c r="CV63" t="inlineStr"/>
-      <c r="CW63" t="inlineStr"/>
+      <c r="CW63" t="inlineStr">
+        <is>
+          <t>9 Level 1 Prinz 89 ST PAC 91 SHO 90 PAS 80 DRI 88 DEF 53 PHY 91 R 4 ★ 4 Prinz 89 ST PAC 91 SHO 90 PAS 80 DRI 88 DEF 53 PHY 91 R 4 ★ 4 UPGRADES 9</t>
+        </is>
+      </c>
       <c r="CX63" t="inlineStr">
         <is>
-          <t>9 Level 1 Prinz 89 ST PAC 91 SHO 90 PAS 80 DRI 88 DEF 53 PHY 91 R 4 ★ 4 Prinz 89 ST PAC 91 SHO 90 PAS 80 DRI 88 DEF 53 PHY 91 R 4 ★ 4 UPGRADES 9</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 8 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY63" t="inlineStr">
@@ -12811,15 +12749,10 @@
       </c>
       <c r="CZ63" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 8 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Architect of Play [SP+ 4] 2</t>
         </is>
       </c>
       <c r="DA63" t="inlineStr">
-        <is>
-          <t>Architect of Play [SP+ 4] 2</t>
-        </is>
-      </c>
-      <c r="DB63" t="inlineStr">
         <is>
           <t>Architect of Play [SP+ 4] 2 Unlocked by reaching level 4 in the Premium Season Pass. Sergi Cardona 88 LB PAC 90 SHO 75 PAS 84 DRI 86 DEF 88 PHY 88 LM L 4 ★ 4 LB 89.2 Sergi Cardona 88 LB PAC 90 SHO 75 PAS 84 DRI 86 DEF 88 PHY 88 LM L 4 ★ 4 LB 91.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 8 UPGRADES 9 in 5 months 4 days ago 91% 9%</t>
         </is>
@@ -12958,10 +12891,14 @@
       <c r="CT64" t="inlineStr"/>
       <c r="CU64" t="inlineStr"/>
       <c r="CV64" t="inlineStr"/>
-      <c r="CW64" t="inlineStr"/>
+      <c r="CW64" t="inlineStr">
+        <is>
+          <t>1 Level 1 UPGRADES 1</t>
+        </is>
+      </c>
       <c r="CX64" t="inlineStr">
         <is>
-          <t>1 Level 1 UPGRADES 1</t>
+          <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY64" t="inlineStr">
@@ -12971,15 +12908,10 @@
       </c>
       <c r="CZ64" t="inlineStr">
         <is>
-          <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Make Your Idol - Tiki Taka+ [SP 3]</t>
         </is>
       </c>
       <c r="DA64" t="inlineStr">
-        <is>
-          <t>Make Your Idol - Tiki Taka+ [SP 3]</t>
-        </is>
-      </c>
-      <c r="DB64" t="inlineStr">
         <is>
           <t>Make Your Idol - Tiki Taka+ [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 UPGRADES 1 in 5 months 4 days ago 69% 31%</t>
         </is>
@@ -13118,10 +13050,14 @@
       <c r="CT65" t="inlineStr"/>
       <c r="CU65" t="inlineStr"/>
       <c r="CV65" t="inlineStr"/>
-      <c r="CW65" t="inlineStr"/>
+      <c r="CW65" t="inlineStr">
+        <is>
+          <t>1 Level 1 UPGRADES 1</t>
+        </is>
+      </c>
       <c r="CX65" t="inlineStr">
         <is>
-          <t>1 Level 1 UPGRADES 1</t>
+          <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY65" t="inlineStr">
@@ -13131,15 +13067,10 @@
       </c>
       <c r="CZ65" t="inlineStr">
         <is>
-          <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Make Your Idol - Incisive Pass+ [SP 3]</t>
         </is>
       </c>
       <c r="DA65" t="inlineStr">
-        <is>
-          <t>Make Your Idol - Incisive Pass+ [SP 3]</t>
-        </is>
-      </c>
-      <c r="DB65" t="inlineStr">
         <is>
           <t>Make Your Idol - Incisive Pass+ [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 UPGRADES 1 in 5 months 4 days ago 68% 32%</t>
         </is>
@@ -13278,10 +13209,14 @@
       <c r="CT66" t="inlineStr"/>
       <c r="CU66" t="inlineStr"/>
       <c r="CV66" t="inlineStr"/>
-      <c r="CW66" t="inlineStr"/>
+      <c r="CW66" t="inlineStr">
+        <is>
+          <t>1 Level 1 UPGRADES 1</t>
+        </is>
+      </c>
       <c r="CX66" t="inlineStr">
         <is>
-          <t>1 Level 1 UPGRADES 1</t>
+          <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY66" t="inlineStr">
@@ -13291,15 +13226,10 @@
       </c>
       <c r="CZ66" t="inlineStr">
         <is>
-          <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Make Your Idol - Low Driven+ [SP 3]</t>
         </is>
       </c>
       <c r="DA66" t="inlineStr">
-        <is>
-          <t>Make Your Idol - Low Driven+ [SP 3]</t>
-        </is>
-      </c>
-      <c r="DB66" t="inlineStr">
         <is>
           <t>Make Your Idol - Low Driven+ [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 UPGRADES 1 in 5 months 4 days ago 26% 74%</t>
         </is>
@@ -13438,10 +13368,14 @@
       <c r="CT67" t="inlineStr"/>
       <c r="CU67" t="inlineStr"/>
       <c r="CV67" t="inlineStr"/>
-      <c r="CW67" t="inlineStr"/>
+      <c r="CW67" t="inlineStr">
+        <is>
+          <t>1 Level 1 UPGRADES 1</t>
+        </is>
+      </c>
       <c r="CX67" t="inlineStr">
         <is>
-          <t>1 Level 1 UPGRADES 1</t>
+          <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY67" t="inlineStr">
@@ -13451,15 +13385,10 @@
       </c>
       <c r="CZ67" t="inlineStr">
         <is>
-          <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Make Your Idol - Technical+ [SP 3]</t>
         </is>
       </c>
       <c r="DA67" t="inlineStr">
-        <is>
-          <t>Make Your Idol - Technical+ [SP 3]</t>
-        </is>
-      </c>
-      <c r="DB67" t="inlineStr">
         <is>
           <t>Make Your Idol - Technical+ [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 UPGRADES 1 in 5 months 4 days ago 29% 71%</t>
         </is>
@@ -13598,10 +13527,14 @@
       <c r="CT68" t="inlineStr"/>
       <c r="CU68" t="inlineStr"/>
       <c r="CV68" t="inlineStr"/>
-      <c r="CW68" t="inlineStr"/>
+      <c r="CW68" t="inlineStr">
+        <is>
+          <t>1 Level 1 UPGRADES 1</t>
+        </is>
+      </c>
       <c r="CX68" t="inlineStr">
         <is>
-          <t>1 Level 1 UPGRADES 1</t>
+          <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY68" t="inlineStr">
@@ -13611,15 +13544,10 @@
       </c>
       <c r="CZ68" t="inlineStr">
         <is>
-          <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Make Your Idol - Jockey+ [SP 3]</t>
         </is>
       </c>
       <c r="DA68" t="inlineStr">
-        <is>
-          <t>Make Your Idol - Jockey+ [SP 3]</t>
-        </is>
-      </c>
-      <c r="DB68" t="inlineStr">
         <is>
           <t>Make Your Idol - Jockey+ [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 UPGRADES 1 in 5 months 4 days ago 25% 75%</t>
         </is>
@@ -13758,10 +13686,14 @@
       <c r="CT69" t="inlineStr"/>
       <c r="CU69" t="inlineStr"/>
       <c r="CV69" t="inlineStr"/>
-      <c r="CW69" t="inlineStr"/>
+      <c r="CW69" t="inlineStr">
+        <is>
+          <t>1 Level 1 UPGRADES 1</t>
+        </is>
+      </c>
       <c r="CX69" t="inlineStr">
         <is>
-          <t>1 Level 1 UPGRADES 1</t>
+          <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY69" t="inlineStr">
@@ -13771,15 +13703,10 @@
       </c>
       <c r="CZ69" t="inlineStr">
         <is>
-          <t>Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Make Your Idol - Intercept+ [SP 3]</t>
         </is>
       </c>
       <c r="DA69" t="inlineStr">
-        <is>
-          <t>Make Your Idol - Intercept+ [SP 3]</t>
-        </is>
-      </c>
-      <c r="DB69" t="inlineStr">
         <is>
           <t>Make Your Idol - Intercept+ [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 87 Overall Max. 87 Max PS+ 0 UPGRADES 1 in 5 months 4 days ago 38% 62%</t>
         </is>
@@ -13918,10 +13845,14 @@
       <c r="CT70" t="inlineStr"/>
       <c r="CU70" t="inlineStr"/>
       <c r="CV70" t="inlineStr"/>
-      <c r="CW70" t="inlineStr"/>
+      <c r="CW70" t="inlineStr">
+        <is>
+          <t>2 Level 1 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX70" t="inlineStr">
         <is>
-          <t>2 Level 1 UPGRADES 2</t>
+          <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY70" t="inlineStr">
@@ -13931,15 +13862,10 @@
       </c>
       <c r="CZ70" t="inlineStr">
         <is>
-          <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Make Your Idol - Finesse Shot+ [SP 7]</t>
         </is>
       </c>
       <c r="DA70" t="inlineStr">
-        <is>
-          <t>Make Your Idol - Finesse Shot+ [SP 7]</t>
-        </is>
-      </c>
-      <c r="DB70" t="inlineStr">
         <is>
           <t>Make Your Idol - Finesse Shot+ [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 UPGRADES 2 in 5 months 4 days ago 44% 56%</t>
         </is>
@@ -14078,10 +14004,14 @@
       <c r="CT71" t="inlineStr"/>
       <c r="CU71" t="inlineStr"/>
       <c r="CV71" t="inlineStr"/>
-      <c r="CW71" t="inlineStr"/>
+      <c r="CW71" t="inlineStr">
+        <is>
+          <t>2 Level 1 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX71" t="inlineStr">
         <is>
-          <t>2 Level 1 UPGRADES 2</t>
+          <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY71" t="inlineStr">
@@ -14091,15 +14021,10 @@
       </c>
       <c r="CZ71" t="inlineStr">
         <is>
-          <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Make Your Idol - First Touch+ [SP 7]</t>
         </is>
       </c>
       <c r="DA71" t="inlineStr">
-        <is>
-          <t>Make Your Idol - First Touch+ [SP 7]</t>
-        </is>
-      </c>
-      <c r="DB71" t="inlineStr">
         <is>
           <t>Make Your Idol - First Touch+ [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 UPGRADES 2 in 5 months 4 days ago 28% 72%</t>
         </is>
@@ -14238,10 +14163,14 @@
       <c r="CT72" t="inlineStr"/>
       <c r="CU72" t="inlineStr"/>
       <c r="CV72" t="inlineStr"/>
-      <c r="CW72" t="inlineStr"/>
+      <c r="CW72" t="inlineStr">
+        <is>
+          <t>2 Level 1 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX72" t="inlineStr">
         <is>
-          <t>2 Level 1 UPGRADES 2</t>
+          <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY72" t="inlineStr">
@@ -14251,15 +14180,10 @@
       </c>
       <c r="CZ72" t="inlineStr">
         <is>
-          <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Make Your Idol - Pinged Pass+ [SP 7]</t>
         </is>
       </c>
       <c r="DA72" t="inlineStr">
-        <is>
-          <t>Make Your Idol - Pinged Pass+ [SP 7]</t>
-        </is>
-      </c>
-      <c r="DB72" t="inlineStr">
         <is>
           <t>Make Your Idol - Pinged Pass+ [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 UPGRADES 2 in 5 months 4 days ago 33% 67%</t>
         </is>
@@ -14398,10 +14322,14 @@
       <c r="CT73" t="inlineStr"/>
       <c r="CU73" t="inlineStr"/>
       <c r="CV73" t="inlineStr"/>
-      <c r="CW73" t="inlineStr"/>
+      <c r="CW73" t="inlineStr">
+        <is>
+          <t>2 Level 1 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX73" t="inlineStr">
         <is>
-          <t>2 Level 1 UPGRADES 2</t>
+          <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY73" t="inlineStr">
@@ -14411,15 +14339,10 @@
       </c>
       <c r="CZ73" t="inlineStr">
         <is>
-          <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Make Your Idol - Rapid+ [SP 7]</t>
         </is>
       </c>
       <c r="DA73" t="inlineStr">
-        <is>
-          <t>Make Your Idol - Rapid+ [SP 7]</t>
-        </is>
-      </c>
-      <c r="DB73" t="inlineStr">
         <is>
           <t>Make Your Idol - Rapid+ [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 UPGRADES 2 in 5 months 4 days ago 37% 63%</t>
         </is>
@@ -14558,10 +14481,14 @@
       <c r="CT74" t="inlineStr"/>
       <c r="CU74" t="inlineStr"/>
       <c r="CV74" t="inlineStr"/>
-      <c r="CW74" t="inlineStr"/>
+      <c r="CW74" t="inlineStr">
+        <is>
+          <t>2 Level 1 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX74" t="inlineStr">
         <is>
-          <t>2 Level 1 UPGRADES 2</t>
+          <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY74" t="inlineStr">
@@ -14571,15 +14498,10 @@
       </c>
       <c r="CZ74" t="inlineStr">
         <is>
-          <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Make Your Idol - Quick Step+ [SP 7]</t>
         </is>
       </c>
       <c r="DA74" t="inlineStr">
-        <is>
-          <t>Make Your Idol - Quick Step+ [SP 7]</t>
-        </is>
-      </c>
-      <c r="DB74" t="inlineStr">
         <is>
           <t>Make Your Idol - Quick Step+ [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 UPGRADES 2 in 5 months 4 days ago 37% 63%</t>
         </is>
@@ -14718,10 +14640,14 @@
       <c r="CT75" t="inlineStr"/>
       <c r="CU75" t="inlineStr"/>
       <c r="CV75" t="inlineStr"/>
-      <c r="CW75" t="inlineStr"/>
+      <c r="CW75" t="inlineStr">
+        <is>
+          <t>2 Level 1 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX75" t="inlineStr">
         <is>
-          <t>2 Level 1 UPGRADES 2</t>
+          <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY75" t="inlineStr">
@@ -14731,15 +14657,10 @@
       </c>
       <c r="CZ75" t="inlineStr">
         <is>
-          <t>Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Make Your Idol - Anticipate+ [SP 7]</t>
         </is>
       </c>
       <c r="DA75" t="inlineStr">
-        <is>
-          <t>Make Your Idol - Anticipate+ [SP 7]</t>
-        </is>
-      </c>
-      <c r="DB75" t="inlineStr">
         <is>
           <t>Make Your Idol - Anticipate+ [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. REQUIREMENTS Rarity Choose Your Idol Overall Min. 89 Overall Max. 89 Min PS+ 1 Max PS+ 2 UPGRADES 2 in 5 months 4 days ago 35% 65%</t>
         </is>
@@ -14878,10 +14799,14 @@
       <c r="CT76" t="inlineStr"/>
       <c r="CU76" t="inlineStr"/>
       <c r="CV76" t="inlineStr"/>
-      <c r="CW76" t="inlineStr"/>
+      <c r="CW76" t="inlineStr">
+        <is>
+          <t>9 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES 9</t>
+        </is>
+      </c>
       <c r="CX76" t="inlineStr">
         <is>
-          <t>9 Level 1 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 Bahoya 89 LM PAC 98 SHO 84 PAS 86 DRI 89 DEF 63 PHY 75 CAM ST LW R 5 ★ 5 UPGRADES 9</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 8 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY76" t="inlineStr">
@@ -14891,15 +14816,10 @@
       </c>
       <c r="CZ76" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 8 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Guardian of the Line [SP+ 10] 2</t>
         </is>
       </c>
       <c r="DA76" t="inlineStr">
-        <is>
-          <t>Guardian of the Line [SP+ 10] 2</t>
-        </is>
-      </c>
-      <c r="DB76" t="inlineStr">
         <is>
           <t>Guardian of the Line [SP+ 10] 2 Unlocked by reaching level 10 in the Premium Season Pass. Dorgu 89 LM PAC 94 SHO 82 PAS 86 DRI 89 DEF 86 PHY 88 LB LW L 3 ★ 4 LB 88.8 Dorgu 89 LM PAC 94 SHO 82 PAS 86 DRI 89 DEF 86 PHY 88 LB LW L 3 ★ 4 LB 90.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 8 UPGRADES 9 in 5 months 4 days ago 89% 11%</t>
         </is>
@@ -14969,23 +14889,23 @@
         <v>4</v>
       </c>
       <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
+      <c r="Z77" t="n">
+        <v>4</v>
+      </c>
       <c r="AA77" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB77" t="n">
         <v>91</v>
       </c>
+      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr"/>
-      <c r="AF77" t="inlineStr"/>
+      <c r="AF77" t="n">
+        <v>4</v>
+      </c>
       <c r="AG77" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH77" t="n">
         <v>91</v>
       </c>
+      <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="inlineStr"/>
       <c r="AJ77" t="inlineStr"/>
       <c r="AK77" t="inlineStr"/>
@@ -14993,59 +14913,59 @@
       <c r="AM77" t="inlineStr"/>
       <c r="AN77" t="inlineStr"/>
       <c r="AO77" t="inlineStr"/>
-      <c r="AP77" t="inlineStr"/>
+      <c r="AP77" t="n">
+        <v>16</v>
+      </c>
       <c r="AQ77" t="n">
+        <v>92</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>92</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>92</v>
+      </c>
+      <c r="AV77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr"/>
+      <c r="AX77" t="n">
         <v>16</v>
       </c>
-      <c r="AR77" t="n">
-        <v>92</v>
-      </c>
-      <c r="AS77" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT77" t="n">
-        <v>92</v>
-      </c>
-      <c r="AU77" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV77" t="n">
-        <v>92</v>
-      </c>
-      <c r="AW77" t="inlineStr"/>
-      <c r="AX77" t="inlineStr"/>
       <c r="AY77" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ77" t="n">
         <v>91</v>
       </c>
+      <c r="AZ77" t="inlineStr"/>
       <c r="BA77" t="inlineStr"/>
-      <c r="BB77" t="inlineStr"/>
+      <c r="BB77" t="n">
+        <v>4</v>
+      </c>
       <c r="BC77" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD77" t="n">
         <v>91</v>
       </c>
+      <c r="BD77" t="inlineStr"/>
       <c r="BE77" t="inlineStr"/>
       <c r="BF77" t="inlineStr"/>
       <c r="BG77" t="inlineStr"/>
-      <c r="BH77" t="inlineStr"/>
+      <c r="BH77" t="n">
+        <v>4</v>
+      </c>
       <c r="BI77" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ77" t="n">
         <v>92</v>
       </c>
+      <c r="BJ77" t="inlineStr"/>
       <c r="BK77" t="inlineStr"/>
-      <c r="BL77" t="inlineStr"/>
+      <c r="BL77" t="n">
+        <v>8</v>
+      </c>
       <c r="BM77" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN77" t="n">
         <v>92</v>
       </c>
+      <c r="BN77" t="inlineStr"/>
       <c r="BO77" t="inlineStr"/>
       <c r="BP77" t="inlineStr"/>
       <c r="BQ77" t="inlineStr"/>
@@ -15080,10 +15000,14 @@
       <c r="CT77" t="inlineStr"/>
       <c r="CU77" t="inlineStr"/>
       <c r="CV77" t="inlineStr"/>
-      <c r="CW77" t="inlineStr"/>
+      <c r="CW77" t="inlineStr">
+        <is>
+          <t>+2 OVR +4 PAC 91 +4 DRI 91 +8 Positioning 92 +8 Volleys 91 +4 Curve 92 +8 Shot Power 92 +4 Vision 91 +8 Finishing 92 +4 Short Pass 92 2 9 Level 1 Amaiur Sarriegi 89 ST PAC 94 SHO 88 PAS 86 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 Amaiur Sarriegi 91 ST PAC 94 SHO 89 PAS 86 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 UPGRADES +2 OVR +8 Positioning 92 +8 Volleys 91 +4 Curve 92 9</t>
+        </is>
+      </c>
       <c r="CX77" t="inlineStr">
         <is>
-          <t>+2 OVR +4 PAC 91 +4 DRI 91 +8 Positioning 92 +8 Volleys 91 +4 Curve 92 +8 Shot Power 92 +4 Vision 91 +8 Finishing 92 +4 Short Pass 92 2 9 Level 1 Amaiur Sarriegi 89 ST PAC 94 SHO 88 PAS 86 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 Amaiur Sarriegi 91 ST PAC 94 SHO 89 PAS 86 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 UPGRADES +2 OVR +8 Positioning 92 +8 Volleys 91 +4 Curve 92 9</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY77" t="inlineStr">
@@ -15093,15 +15017,10 @@
       </c>
       <c r="CZ77" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Up to Speed [SP+ 26]</t>
         </is>
       </c>
       <c r="DA77" t="inlineStr">
-        <is>
-          <t>Up to Speed [SP+ 26]</t>
-        </is>
-      </c>
-      <c r="DB77" t="inlineStr">
         <is>
           <t>Up to Speed [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Hall 89 LB PAC 88 SHO 82 PAS 88 DRI 89 DEF 89 PHY 86 L 4 ★ 4 LB 88.5 Hall 91 LB PAC 91 SHO 87 PAS 91 DRI 91 DEF 89 PHY 86 L 4 ★ 4 LB 91.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Max PS+ 2 UPGRADES +2 OVR +4 PAC 91 +4 DRI 91 +8 Positioning 92 +8 Volleys 91 +4 Curve 92 +8 Shot Power 92 +4 Vision 91 +8 Finishing 92 +4 Short Pass 92 2 9 in 5 months 4 days ago 85% 15%</t>
         </is>
@@ -15232,10 +15151,14 @@
       <c r="CT78" t="inlineStr"/>
       <c r="CU78" t="inlineStr"/>
       <c r="CV78" t="inlineStr"/>
-      <c r="CW78" t="inlineStr"/>
+      <c r="CW78" t="inlineStr">
+        <is>
+          <t>No upgrades Level 1 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 UPGRADES No upgrades</t>
+        </is>
+      </c>
       <c r="CX78" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 UPGRADES No upgrades</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY78" t="inlineStr">
@@ -15245,15 +15168,10 @@
       </c>
       <c r="CZ78" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Fantasy Captain ICON [SP 27]</t>
         </is>
       </c>
       <c r="DA78" t="inlineStr">
-        <is>
-          <t>Fantasy Captain ICON [SP 27]</t>
-        </is>
-      </c>
-      <c r="DB78" t="inlineStr">
         <is>
           <t>Fantasy Captain ICON [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Jacobo Ramón 94 CB PAC 88 SHO 46 PAS 84 DRI 81 DEF 94 PHY 91 R 3 ★ 4 CB 93.8 Jacobo Ramón 94 CB PAC 88 SHO 46 PAS 84 DRI 81 DEF 94 PHY 91 R 3 ★ 4 CB 93.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 5 months 4 days ago 96% 4%</t>
         </is>
@@ -15384,10 +15302,14 @@
       <c r="CT79" t="inlineStr"/>
       <c r="CU79" t="inlineStr"/>
       <c r="CV79" t="inlineStr"/>
-      <c r="CW79" t="inlineStr"/>
+      <c r="CW79" t="inlineStr">
+        <is>
+          <t>No upgrades Level 1 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 UPGRADES No upgrades</t>
+        </is>
+      </c>
       <c r="CX79" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 Shaw 97 ST PAC 95 SHO 97 PAS 84 DRI 91 DEF 40 PHY 92 R 4 ★ 5 UPGRADES No upgrades</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY79" t="inlineStr">
@@ -15397,15 +15319,10 @@
       </c>
       <c r="CZ79" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Season Ladder Excellence [SP 15]</t>
         </is>
       </c>
       <c r="DA79" t="inlineStr">
-        <is>
-          <t>Season Ladder Excellence [SP 15]</t>
-        </is>
-      </c>
-      <c r="DB79" t="inlineStr">
         <is>
           <t>Season Ladder Excellence [SP 15] Unlocked by reaching level 15 in the Standard Season Pass. Jacobo Ramón 94 CB PAC 88 SHO 46 PAS 84 DRI 81 DEF 94 PHY 91 R 3 ★ 4 CB 93.8 Jacobo Ramón 94 CB PAC 88 SHO 46 PAS 84 DRI 81 DEF 94 PHY 91 R 3 ★ 4 CB 93.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 5 months 4 days ago 39% 61%</t>
         </is>
@@ -15544,10 +15461,14 @@
       <c r="CT80" t="inlineStr"/>
       <c r="CU80" t="inlineStr"/>
       <c r="CV80" t="inlineStr"/>
-      <c r="CW80" t="inlineStr"/>
+      <c r="CW80" t="inlineStr">
+        <is>
+          <t>3 Level 1 Dumornay 90 ST PAC 96 SHO 90 PAS 85 DRI 90 DEF 66 PHY 80 CAM R 5 ★ 5 Dumornay 90 ST PAC 96 SHO 90 PAS 85 DRI 90 DEF 66 PHY 80 CAM R 5 ★ 5 UPGRADES 3</t>
+        </is>
+      </c>
       <c r="CX80" t="inlineStr">
         <is>
-          <t>3 Level 1 Dumornay 90 ST PAC 96 SHO 90 PAS 85 DRI 90 DEF 66 PHY 80 CAM R 5 ★ 5 Dumornay 90 ST PAC 96 SHO 90 PAS 85 DRI 90 DEF 66 PHY 80 CAM R 5 ★ 5 UPGRADES 3</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY80" t="inlineStr">
@@ -15557,15 +15478,10 @@
       </c>
       <c r="CZ80" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Pinged Pass+ [SP+ 28]</t>
         </is>
       </c>
       <c r="DA80" t="inlineStr">
-        <is>
-          <t>Pinged Pass+ [SP+ 28]</t>
-        </is>
-      </c>
-      <c r="DB80" t="inlineStr">
         <is>
           <t>Pinged Pass+ [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Messi 90 ST PAC 90 SHO 90 PAS 90 DRI 94 DEF 37 PHY 71 RM CAM RW L 4 ★ 5 CAM 90.3 Messi 90 ST PAC 90 SHO 90 PAS 90 DRI 94 DEF 37 PHY 71 RM CAM RW L 4 ★ 5 CAM 91.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 UPGRADES 3 in 5 months 4 days ago 95% 5%</t>
         </is>
@@ -15704,10 +15620,14 @@
       <c r="CT81" t="inlineStr"/>
       <c r="CU81" t="inlineStr"/>
       <c r="CV81" t="inlineStr"/>
-      <c r="CW81" t="inlineStr"/>
+      <c r="CW81" t="inlineStr">
+        <is>
+          <t>3 Level 1 Francisco Conceição 89 RM PAC 93 SHO 86 PAS 87 DRI 91 DEF 45 PHY 70 CAM RW L 4 ★ 3 Francisco Conceição 89 RM PAC 93 SHO 86 PAS 87 DRI 91 DEF 45 PHY 70 CAM RW L 4 ★ 3 UPGRADES 3</t>
+        </is>
+      </c>
       <c r="CX81" t="inlineStr">
         <is>
-          <t>3 Level 1 Francisco Conceição 89 RM PAC 93 SHO 86 PAS 87 DRI 91 DEF 45 PHY 70 CAM RW L 4 ★ 3 Francisco Conceição 89 RM PAC 93 SHO 86 PAS 87 DRI 91 DEF 45 PHY 70 CAM RW L 4 ★ 3 UPGRADES 3</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY81" t="inlineStr">
@@ -15717,15 +15637,10 @@
       </c>
       <c r="CZ81" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Relentless+ [SP+ 27]</t>
         </is>
       </c>
       <c r="DA81" t="inlineStr">
-        <is>
-          <t>Relentless+ [SP+ 27]</t>
-        </is>
-      </c>
-      <c r="DB81" t="inlineStr">
         <is>
           <t>Relentless+ [SP+ 27] Unlocked by reaching level 27 in the Premium Season Pass. Spinazzola 89 LB PAC 93 SHO 76 PAS 87 DRI 89 DEF 88 PHY 84 LM R 4 ★ 4 LB 89.7 Spinazzola 89 LB PAC 93 SHO 76 PAS 87 DRI 89 DEF 88 PHY 84 LM R 4 ★ 4 LB 90.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS+ 2 UPGRADES 3 in 5 months 4 days ago 14% 86%</t>
         </is>
@@ -15819,31 +15734,31 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="inlineStr"/>
-      <c r="BB82" t="inlineStr"/>
+      <c r="BB82" t="n">
+        <v>20</v>
+      </c>
       <c r="BC82" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD82" t="n">
         <v>92</v>
       </c>
+      <c r="BD82" t="inlineStr"/>
       <c r="BE82" t="inlineStr"/>
       <c r="BF82" t="inlineStr"/>
       <c r="BG82" t="inlineStr"/>
       <c r="BH82" t="inlineStr"/>
       <c r="BI82" t="inlineStr"/>
-      <c r="BJ82" t="inlineStr"/>
+      <c r="BJ82" t="n">
+        <v>20</v>
+      </c>
       <c r="BK82" t="n">
+        <v>92</v>
+      </c>
+      <c r="BL82" t="n">
         <v>20</v>
       </c>
-      <c r="BL82" t="n">
+      <c r="BM82" t="n">
         <v>92</v>
       </c>
-      <c r="BM82" t="n">
-        <v>20</v>
-      </c>
-      <c r="BN82" t="n">
-        <v>92</v>
-      </c>
+      <c r="BN82" t="inlineStr"/>
       <c r="BO82" t="inlineStr"/>
       <c r="BP82" t="inlineStr"/>
       <c r="BQ82" t="inlineStr"/>
@@ -15853,23 +15768,23 @@
       <c r="BU82" t="inlineStr"/>
       <c r="BV82" t="inlineStr"/>
       <c r="BW82" t="inlineStr"/>
-      <c r="BX82" t="inlineStr"/>
+      <c r="BX82" t="n">
+        <v>20</v>
+      </c>
       <c r="BY82" t="n">
-        <v>20</v>
-      </c>
-      <c r="BZ82" t="n">
         <v>91</v>
       </c>
+      <c r="BZ82" t="inlineStr"/>
       <c r="CA82" t="inlineStr"/>
       <c r="CB82" t="inlineStr"/>
       <c r="CC82" t="inlineStr"/>
-      <c r="CD82" t="inlineStr"/>
+      <c r="CD82" t="n">
+        <v>20</v>
+      </c>
       <c r="CE82" t="n">
-        <v>20</v>
-      </c>
-      <c r="CF82" t="n">
         <v>91</v>
       </c>
+      <c r="CF82" t="inlineStr"/>
       <c r="CG82" t="inlineStr"/>
       <c r="CH82" t="inlineStr"/>
       <c r="CI82" t="inlineStr"/>
@@ -15886,10 +15801,14 @@
       <c r="CT82" t="inlineStr"/>
       <c r="CU82" t="inlineStr"/>
       <c r="CV82" t="inlineStr"/>
-      <c r="CW82" t="inlineStr"/>
+      <c r="CW82" t="inlineStr">
+        <is>
+          <t>+1 OVR +10 Vision 92 +10 Long Pass 92 +10 Curve 92 +10 Composure 91 +10 Defensive Awareness 91 9 Level 1 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 Kerolin Nicoli 90 RM PAC 91 SHO 86 PAS 88 DRI 90 DEF 55 PHY 86 RW ST R 5 ★ 5 UPGRADES +1 OVR +10 Vision 92 +10 Long Pass 92 +10 Curve 92 +10 Composure 91 +10 Defensive Awareness 91 9</t>
+        </is>
+      </c>
       <c r="CX82" t="inlineStr">
         <is>
-          <t>+1 OVR +10 Vision 92 +10 Long Pass 92 +10 Curve 92 +10 Composure 91 +10 Defensive Awareness 91 9 Level 1 Kerolin Nicoli 89 RM PAC 91 SHO 86 PAS 85 DRI 90 DEF 52 PHY 86 RW ST R 5 ★ 5 Kerolin Nicoli 90 RM PAC 91 SHO 86 PAS 88 DRI 90 DEF 55 PHY 86 RW ST R 5 ★ 5 UPGRADES +1 OVR +10 Vision 92 +10 Long Pass 92 +10 Curve 92 +10 Composure 91 +10 Defensive Awareness 91 9</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY82" t="inlineStr">
@@ -15899,15 +15818,10 @@
       </c>
       <c r="CZ82" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Dish 'em Out [SP+ 1]</t>
         </is>
       </c>
       <c r="DA82" t="inlineStr">
-        <is>
-          <t>Dish 'em Out [SP+ 1]</t>
-        </is>
-      </c>
-      <c r="DB82" t="inlineStr">
         <is>
           <t>Dish 'em Out [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Hernández 88 LB PAC 92 SHO 81 PAS 82 DRI 87 DEF 83 PHY 86 LM L 4 ★ 3 LB 89.3 Hernández 89 LB PAC 92 SHO 81 PAS 86 DRI 87 DEF 86 PHY 86 LM L 4 ★ 3 LB 91.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +1 OVR +10 Vision 92 +10 Long Pass 92 +10 Curve 92 +10 Composure 91 +10 Defensive Awareness 91 9 in 5 months 4 days ago 92% 8%</t>
         </is>
@@ -15981,19 +15895,19 @@
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
-      <c r="AH83" t="inlineStr"/>
+      <c r="AH83" t="n">
+        <v>4</v>
+      </c>
       <c r="AI83" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ83" t="n">
         <v>4</v>
       </c>
-      <c r="AJ83" t="n">
-        <v>90</v>
-      </c>
       <c r="AK83" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL83" t="n">
         <v>91</v>
       </c>
+      <c r="AL83" t="inlineStr"/>
       <c r="AM83" t="inlineStr"/>
       <c r="AN83" t="inlineStr"/>
       <c r="AO83" t="inlineStr"/>
@@ -16009,55 +15923,55 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr"/>
       <c r="BA83" t="inlineStr"/>
-      <c r="BB83" t="inlineStr"/>
+      <c r="BB83" t="n">
+        <v>12</v>
+      </c>
       <c r="BC83" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD83" t="n">
         <v>92</v>
       </c>
+      <c r="BD83" t="inlineStr"/>
       <c r="BE83" t="inlineStr"/>
       <c r="BF83" t="inlineStr"/>
       <c r="BG83" t="inlineStr"/>
-      <c r="BH83" t="inlineStr"/>
+      <c r="BH83" t="n">
+        <v>12</v>
+      </c>
       <c r="BI83" t="n">
+        <v>92</v>
+      </c>
+      <c r="BJ83" t="inlineStr"/>
+      <c r="BK83" t="inlineStr"/>
+      <c r="BL83" t="n">
         <v>12</v>
       </c>
-      <c r="BJ83" t="n">
-        <v>92</v>
-      </c>
-      <c r="BK83" t="inlineStr"/>
-      <c r="BL83" t="inlineStr"/>
       <c r="BM83" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN83" t="n">
         <v>89</v>
       </c>
+      <c r="BN83" t="inlineStr"/>
       <c r="BO83" t="inlineStr"/>
       <c r="BP83" t="inlineStr"/>
       <c r="BQ83" t="inlineStr"/>
-      <c r="BR83" t="inlineStr"/>
+      <c r="BR83" t="n">
+        <v>12</v>
+      </c>
       <c r="BS83" t="n">
+        <v>90</v>
+      </c>
+      <c r="BT83" t="n">
         <v>12</v>
       </c>
-      <c r="BT83" t="n">
+      <c r="BU83" t="n">
         <v>90</v>
       </c>
-      <c r="BU83" t="n">
-        <v>12</v>
-      </c>
-      <c r="BV83" t="n">
+      <c r="BV83" t="inlineStr"/>
+      <c r="BW83" t="inlineStr"/>
+      <c r="BX83" t="n">
+        <v>6</v>
+      </c>
+      <c r="BY83" t="n">
         <v>90</v>
       </c>
-      <c r="BW83" t="inlineStr"/>
-      <c r="BX83" t="inlineStr"/>
-      <c r="BY83" t="n">
-        <v>6</v>
-      </c>
-      <c r="BZ83" t="n">
-        <v>90</v>
-      </c>
+      <c r="BZ83" t="inlineStr"/>
       <c r="CA83" t="inlineStr"/>
       <c r="CB83" t="inlineStr"/>
       <c r="CC83" t="inlineStr"/>
@@ -16080,10 +15994,14 @@
       <c r="CT83" t="inlineStr"/>
       <c r="CU83" t="inlineStr"/>
       <c r="CV83" t="inlineStr"/>
-      <c r="CW83" t="inlineStr"/>
+      <c r="CW83" t="inlineStr">
+        <is>
+          <t>+2 OVR +4 DEF 90 +4 PHY 91 +6 Vision 92 +6 Short Pass 92 +6 Curve 89 +6 Reactions 90 +6 Ball Control 90 +6 Composure 90 9 Level 1 Claudia Pina 88 LW PAC 85 SHO 89 PAS 87 DRI 90 DEF 48 PHY 74 LM ST R 5 ★ 5 Claudia Pina 90 LW PAC 85 SHO 89 PAS 89 DRI 90 DEF 48 PHY 74 LM ST R 5 ★ 5 UPGRADES +2 OVR +6 Vision 92 +6 Short Pass 92 +6 Curve 89 +6 Reactions 90 +6 Ball Control 90</t>
+        </is>
+      </c>
       <c r="CX83" t="inlineStr">
         <is>
-          <t>+2 OVR +4 DEF 90 +4 PHY 91 +6 Vision 92 +6 Short Pass 92 +6 Curve 89 +6 Reactions 90 +6 Ball Control 90 +6 Composure 90 9 Level 1 Claudia Pina 88 LW PAC 85 SHO 89 PAS 87 DRI 90 DEF 48 PHY 74 LM ST R 5 ★ 5 Claudia Pina 90 LW PAC 85 SHO 89 PAS 89 DRI 90 DEF 48 PHY 74 LM ST R 5 ★ 5 UPGRADES +2 OVR +6 Vision 92 +6 Short Pass 92 +6 Curve 89 +6 Reactions 90 +6 Ball Control 90</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY83" t="inlineStr">
@@ -16093,15 +16011,10 @@
       </c>
       <c r="CZ83" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Locked &amp; Loaded [SP 25]</t>
         </is>
       </c>
       <c r="DA83" t="inlineStr">
-        <is>
-          <t>Locked &amp; Loaded [SP 25]</t>
-        </is>
-      </c>
-      <c r="DB83" t="inlineStr">
         <is>
           <t>Locked &amp; Loaded [SP 25] Unlocked by reaching level 25 in the Standard Season Pass. O'Reilly 87 LB PAC 89 SHO 82 PAS 86 DRI 87 DEF 85 PHY 85 CM CAM L 3 ★ 3 LB 87.2 O'Reilly 89 LB PAC 89 SHO 82 PAS 88 DRI 88 DEF 89 PHY 89 CM CAM L 3 ★ 3 LB 90.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 Max PS 10 UPGRADES +2 OVR +4 DEF 90 +4 PHY 91 +6 Vision 92 +6 Short Pass 92 +6 Curve 89 +6 Reactions 90 +6 Ball Control 90 +6 Composure 90 9 in 5 months 4 days ago 91% 9%</t>
         </is>
@@ -16177,27 +16090,27 @@
       <c r="AM84" t="inlineStr"/>
       <c r="AN84" t="inlineStr"/>
       <c r="AO84" t="inlineStr"/>
-      <c r="AP84" t="inlineStr"/>
+      <c r="AP84" t="n">
+        <v>4</v>
+      </c>
       <c r="AQ84" t="n">
+        <v>90</v>
+      </c>
+      <c r="AR84" t="n">
         <v>4</v>
       </c>
-      <c r="AR84" t="n">
+      <c r="AS84" t="n">
         <v>90</v>
       </c>
-      <c r="AS84" t="n">
+      <c r="AT84" t="inlineStr"/>
+      <c r="AU84" t="inlineStr"/>
+      <c r="AV84" t="n">
         <v>4</v>
       </c>
-      <c r="AT84" t="n">
+      <c r="AW84" t="n">
         <v>90</v>
       </c>
-      <c r="AU84" t="inlineStr"/>
-      <c r="AV84" t="inlineStr"/>
-      <c r="AW84" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX84" t="n">
-        <v>90</v>
-      </c>
+      <c r="AX84" t="inlineStr"/>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr"/>
       <c r="BA84" t="inlineStr"/>
@@ -16248,10 +16161,14 @@
       <c r="CT84" t="inlineStr"/>
       <c r="CU84" t="inlineStr"/>
       <c r="CV84" t="inlineStr"/>
-      <c r="CW84" t="inlineStr"/>
+      <c r="CW84" t="inlineStr">
+        <is>
+          <t>+2 Positioning 90 +2 Finishing 90 +2 Long Shots 90 Level 1 Ona Batlle 88 RB PAC 88 SHO 60 PAS 84 DRI 83 DEF 83 PHY 78 LB RM R 3 ★ 4 Ona Batlle 88 RB PAC 88 SHO 62 PAS 84 DRI 83 DEF 83 PHY 78 LB RM R 3 ★ 4 UPGRADES +2 Positioning 90 +2 Finishing 90 +2 Long Shots 90</t>
+        </is>
+      </c>
       <c r="CX84" t="inlineStr">
         <is>
-          <t>+2 Positioning 90 +2 Finishing 90 +2 Long Shots 90 Level 1 Ona Batlle 88 RB PAC 88 SHO 60 PAS 84 DRI 83 DEF 83 PHY 78 LB RM R 3 ★ 4 Ona Batlle 88 RB PAC 88 SHO 62 PAS 84 DRI 83 DEF 83 PHY 78 LB RM R 3 ★ 4 UPGRADES +2 Positioning 90 +2 Finishing 90 +2 Long Shots 90</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY84" t="inlineStr">
@@ -16261,15 +16178,10 @@
       </c>
       <c r="CZ84" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 88 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Goal Machine [SP 8] 5</t>
         </is>
       </c>
       <c r="DA84" t="inlineStr">
-        <is>
-          <t>Goal Machine [SP 8] 5</t>
-        </is>
-      </c>
-      <c r="DB84" t="inlineStr">
         <is>
           <t>Goal Machine [SP 8] 5 Unlocked by reaching level 8 in the Standard Season Pass. Pedrinho 88 RM PAC 93 SHO 85 PAS 87 DRI 91 DEF 60 PHY 75 LM CAM RW L 5 ★ 4 LM 90.9 Pedrinho 88 RM PAC 93 SHO 87 PAS 87 DRI 91 DEF 60 PHY 75 LM CAM RW L 5 ★ 4 LM 91.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 88 UPGRADES +2 Positioning 90 +2 Finishing 90 +2 Long Shots 90 in 5 months 4 days ago 92% 8%</t>
         </is>
@@ -16335,23 +16247,23 @@
         <v>4</v>
       </c>
       <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="inlineStr"/>
+      <c r="Z85" t="n">
+        <v>14</v>
+      </c>
       <c r="AA85" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB85" t="n">
         <v>90</v>
       </c>
+      <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="inlineStr"/>
       <c r="AD85" t="inlineStr"/>
       <c r="AE85" t="inlineStr"/>
-      <c r="AF85" t="inlineStr"/>
+      <c r="AF85" t="n">
+        <v>14</v>
+      </c>
       <c r="AG85" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH85" t="n">
         <v>91</v>
       </c>
+      <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="inlineStr"/>
       <c r="AJ85" t="inlineStr"/>
       <c r="AK85" t="inlineStr"/>
@@ -16418,10 +16330,14 @@
       <c r="CT85" t="inlineStr"/>
       <c r="CU85" t="inlineStr"/>
       <c r="CV85" t="inlineStr"/>
-      <c r="CW85" t="inlineStr"/>
+      <c r="CW85" t="inlineStr">
+        <is>
+          <t>+2 OVR +7 PAC 90 +7 DRI 91 9 Level 1 Amaiur Sarriegi 89 ST PAC 94 SHO 88 PAS 86 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 Amaiur Sarriegi 91 ST PAC 94 SHO 88 PAS 86 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 UPGRADES +2 OVR +7 PAC 90 +7 DRI 91 9</t>
+        </is>
+      </c>
       <c r="CX85" t="inlineStr">
         <is>
-          <t>+2 OVR +7 PAC 90 +7 DRI 91 9 Level 1 Amaiur Sarriegi 89 ST PAC 94 SHO 88 PAS 86 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 Amaiur Sarriegi 91 ST PAC 94 SHO 88 PAS 86 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 UPGRADES +2 OVR +7 PAC 90 +7 DRI 91 9</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY85" t="inlineStr">
@@ -16431,15 +16347,10 @@
       </c>
       <c r="CZ85" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Roadrunner [SP+ 24]</t>
         </is>
       </c>
       <c r="DA85" t="inlineStr">
-        <is>
-          <t>Roadrunner [SP+ 24]</t>
-        </is>
-      </c>
-      <c r="DB85" t="inlineStr">
         <is>
           <t>Roadrunner [SP+ 24] Unlocked by reaching level 24 in the Premium Season Pass. Bardakcı 88 CB PAC 85 SHO 53 PAS 85 DRI 76 DEF 88 PHY 92 LB LM L 4 ★ 5 LB 88.3 Bardakcı 90 CB PAC 90 SHO 53 PAS 85 DRI 84 DEF 88 PHY 92 LB LM L 4 ★ 5 LB 91.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +2 OVR +7 PAC 90 +7 DRI 91 9 in 5 months 4 days ago 84% 16%</t>
         </is>
@@ -16509,21 +16420,21 @@
       <c r="AA86" t="inlineStr"/>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr"/>
-      <c r="AD86" t="inlineStr"/>
+      <c r="AD86" t="n">
+        <v>14</v>
+      </c>
       <c r="AE86" t="n">
+        <v>91</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr"/>
+      <c r="AH86" t="n">
         <v>14</v>
       </c>
-      <c r="AF86" t="n">
+      <c r="AI86" t="n">
         <v>91</v>
       </c>
-      <c r="AG86" t="inlineStr"/>
-      <c r="AH86" t="inlineStr"/>
-      <c r="AI86" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ86" t="n">
-        <v>91</v>
-      </c>
+      <c r="AJ86" t="inlineStr"/>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
       <c r="AM86" t="inlineStr"/>
@@ -16588,10 +16499,14 @@
       <c r="CT86" t="inlineStr"/>
       <c r="CU86" t="inlineStr"/>
       <c r="CV86" t="inlineStr"/>
-      <c r="CW86" t="inlineStr"/>
+      <c r="CW86" t="inlineStr">
+        <is>
+          <t>+2 OVR +7 PAS 91 +7 DEF 91 9 Level 1 James 89 ST PAC 91 SHO 86 PAS 82 DRI 91 DEF 44 PHY 86 CAM R 4 ★ 5 James 91 ST PAC 91 SHO 86 PAS 90 DRI 91 DEF 51 PHY 86 CAM R 4 ★ 5 UPGRADES +2 OVR +7 PAS 91 +7 DEF 91 9</t>
+        </is>
+      </c>
       <c r="CX86" t="inlineStr">
         <is>
-          <t>+2 OVR +7 PAS 91 +7 DEF 91 9 Level 1 James 89 ST PAC 91 SHO 86 PAS 82 DRI 91 DEF 44 PHY 86 CAM R 4 ★ 5 James 91 ST PAC 91 SHO 86 PAS 90 DRI 91 DEF 51 PHY 86 CAM R 4 ★ 5 UPGRADES +2 OVR +7 PAS 91 +7 DEF 91 9</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY86" t="inlineStr">
@@ -16601,15 +16516,10 @@
       </c>
       <c r="CZ86" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 5 months Expiry 4 days ago Coins Cost Free Points Cost Free</t>
+          <t>Sweep &amp; Supply [SP+ 18]</t>
         </is>
       </c>
       <c r="DA86" t="inlineStr">
-        <is>
-          <t>Sweep &amp; Supply [SP+ 18]</t>
-        </is>
-      </c>
-      <c r="DB86" t="inlineStr">
         <is>
           <t>Sweep &amp; Supply [SP+ 18] Unlocked by reaching level 18 in the Premium Season Pass. Timber 88 RB PAC 87 SHO 54 PAS 83 DRI 86 DEF 88 PHY 88 CB LB RM R 4 ★ 5 LB 88.6 Timber 90 RB PAC 87 SHO 54 PAS 90 DRI 86 DEF 91 PHY 88 CB LB RM R 4 ★ 5 LB 91.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +2 OVR +7 PAS 91 +7 DEF 91 9 in 5 months 4 days ago 86% 14%</t>
         </is>
@@ -16748,10 +16658,14 @@
       <c r="CT87" t="inlineStr"/>
       <c r="CU87" t="inlineStr"/>
       <c r="CV87" t="inlineStr"/>
-      <c r="CW87" t="inlineStr"/>
+      <c r="CW87" t="inlineStr">
+        <is>
+          <t>2 Level 1 Karchaoui 90 CM PAC 92 SHO 82 PAS 90 DRI 91 DEF 85 PHY 74 LB CAM LW L 5 ★ 4 Karchaoui 90 CM PAC 92 SHO 82 PAS 90 DRI 91 DEF 85 PHY 74 LB CAM LW L 5 ★ 4 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX87" t="inlineStr">
         <is>
-          <t>2 Level 1 Karchaoui 90 CM PAC 92 SHO 82 PAS 90 DRI 91 DEF 85 PHY 74 LB CAM LW L 5 ★ 4 Karchaoui 90 CM PAC 92 SHO 82 PAS 90 DRI 91 DEF 85 PHY 74 LB CAM LW L 5 ★ 4 UPGRADES 2</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 Details Submit by in 8 months Expiry in 8 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY87" t="inlineStr">
@@ -16761,15 +16675,10 @@
       </c>
       <c r="CZ87" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 Details Submit by in 8 months Expiry in 8 months Coins Cost Free Points Cost Free</t>
+          <t>Quick Step+</t>
         </is>
       </c>
       <c r="DA87" t="inlineStr">
-        <is>
-          <t>Quick Step+</t>
-        </is>
-      </c>
-      <c r="DB87" t="inlineStr">
         <is>
           <t>Quick Step+ Unlocked by completing the Quick Step+ Milestone objective Henrichs 88 RB PAC 90 SHO 75 PAS 85 DRI 86 DEF 88 PHY 84 LB RM R 3 ★ 5 LB 87.0 Henrichs 88 RB PAC 90 SHO 75 PAS 85 DRI 86 DEF 88 PHY 84 LB RM R 3 ★ 5 LB 89.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 UPGRADES 2 in 8 months in 8 months 94% 6%</t>
         </is>
@@ -16908,10 +16817,14 @@
       <c r="CT88" t="inlineStr"/>
       <c r="CU88" t="inlineStr"/>
       <c r="CV88" t="inlineStr"/>
-      <c r="CW88" t="inlineStr"/>
+      <c r="CW88" t="inlineStr">
+        <is>
+          <t>2 Level 1 Gravenberch 90 CDM PAC 84 SHO 83 PAS 87 DRI 90 DEF 88 PHY 88 CM R 4 ★ 4 Gravenberch 90 CDM PAC 84 SHO 83 PAS 87 DRI 90 DEF 88 PHY 88 CM R 4 ★ 4 UPGRADES 2</t>
+        </is>
+      </c>
       <c r="CX88" t="inlineStr">
         <is>
-          <t>2 Level 1 Gravenberch 90 CDM PAC 84 SHO 83 PAS 87 DRI 90 DEF 88 PHY 88 CM R 4 ★ 4 Gravenberch 90 CDM PAC 84 SHO 83 PAS 87 DRI 90 DEF 88 PHY 88 CM R 4 ★ 4 UPGRADES 2</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 Details Submit by in 3 years Expiry in 3 years Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY88" t="inlineStr">
@@ -16921,15 +16834,10 @@
       </c>
       <c r="CZ88" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 Details Submit by in 3 years Expiry in 3 years Coins Cost Free Points Cost Free</t>
+          <t>Finesse Shot+</t>
         </is>
       </c>
       <c r="DA88" t="inlineStr">
-        <is>
-          <t>Finesse Shot+</t>
-        </is>
-      </c>
-      <c r="DB88" t="inlineStr">
         <is>
           <t>Finesse Shot+ Unlocked by completing the Finesse Shot+ Milestone objective Pulisic 90 CAM PAC 92 SHO 88 PAS 87 DRI 93 DEF 52 PHY 75 RM RW R 4 ★ 5 RM 86.8 Pulisic 90 CAM PAC 92 SHO 88 PAS 87 DRI 93 DEF 52 PHY 75 RM RW R 4 ★ 5 RM 88.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 1 UPGRADES 2 in 3 years in 3 years 94% 6%</t>
         </is>
@@ -17015,69 +16923,69 @@
       <c r="AQ89" t="inlineStr"/>
       <c r="AR89" t="inlineStr"/>
       <c r="AS89" t="inlineStr"/>
-      <c r="AT89" t="inlineStr"/>
+      <c r="AT89" t="n">
+        <v>6</v>
+      </c>
       <c r="AU89" t="n">
+        <v>80</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX89" t="n">
         <v>6</v>
       </c>
-      <c r="AV89" t="n">
+      <c r="AY89" t="n">
+        <v>79</v>
+      </c>
+      <c r="AZ89" t="inlineStr"/>
+      <c r="BA89" t="inlineStr"/>
+      <c r="BB89" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC89" t="n">
         <v>80</v>
       </c>
-      <c r="AW89" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX89" t="n">
-        <v>80</v>
-      </c>
-      <c r="AY89" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ89" t="n">
-        <v>79</v>
-      </c>
-      <c r="BA89" t="inlineStr"/>
-      <c r="BB89" t="inlineStr"/>
-      <c r="BC89" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD89" t="n">
-        <v>80</v>
-      </c>
+      <c r="BD89" t="inlineStr"/>
       <c r="BE89" t="inlineStr"/>
       <c r="BF89" t="inlineStr"/>
       <c r="BG89" t="inlineStr"/>
-      <c r="BH89" t="inlineStr"/>
+      <c r="BH89" t="n">
+        <v>3</v>
+      </c>
       <c r="BI89" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="BJ89" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="BK89" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL89" t="n">
         <v>79</v>
       </c>
+      <c r="BL89" t="inlineStr"/>
       <c r="BM89" t="inlineStr"/>
       <c r="BN89" t="inlineStr"/>
       <c r="BO89" t="inlineStr"/>
       <c r="BP89" t="inlineStr"/>
       <c r="BQ89" t="inlineStr"/>
-      <c r="BR89" t="inlineStr"/>
+      <c r="BR89" t="n">
+        <v>4</v>
+      </c>
       <c r="BS89" t="n">
+        <v>81</v>
+      </c>
+      <c r="BT89" t="inlineStr"/>
+      <c r="BU89" t="inlineStr"/>
+      <c r="BV89" t="n">
         <v>4</v>
       </c>
-      <c r="BT89" t="n">
+      <c r="BW89" t="n">
         <v>81</v>
       </c>
-      <c r="BU89" t="inlineStr"/>
-      <c r="BV89" t="inlineStr"/>
-      <c r="BW89" t="n">
-        <v>4</v>
-      </c>
-      <c r="BX89" t="n">
-        <v>81</v>
-      </c>
+      <c r="BX89" t="inlineStr"/>
       <c r="BY89" t="inlineStr"/>
       <c r="BZ89" t="inlineStr"/>
       <c r="CA89" t="inlineStr"/>
@@ -17102,10 +17010,14 @@
       <c r="CT89" t="inlineStr"/>
       <c r="CU89" t="inlineStr"/>
       <c r="CV89" t="inlineStr"/>
-      <c r="CW89" t="inlineStr"/>
+      <c r="CW89" t="inlineStr">
+        <is>
+          <t>+1 OVR +3 Shot Power 80 +3 Vision 80 +4 Long Shots 80 +3 Volleys 79 +3 Short Pass 80 +4 Fk Accuracy 80 +4 Dribbling 81 +4 Reactions 81 +4 Long Pass 79 Level 1 Posch 82 RB PAC 82 SHO 60 PAS 74 DRI 73 DEF 83 PHY 80 RM R 2 ★ 3 Posch 83 RB PAC 82 SHO 62 PAS 75 DRI 73 DEF 83 PHY 80 RM R 2 ★ 3 UPGRADES +1 OVR +3 Shot Power 80 +3 Vision 80 +4 Long Shots 80 +3 Volleys 79</t>
+        </is>
+      </c>
       <c r="CX89" t="inlineStr">
         <is>
-          <t>+1 OVR +3 Shot Power 80 +3 Vision 80 +4 Long Shots 80 +3 Volleys 79 +3 Short Pass 80 +4 Fk Accuracy 80 +4 Dribbling 81 +4 Reactions 81 +4 Long Pass 79 Level 1 Posch 82 RB PAC 82 SHO 60 PAS 74 DRI 73 DEF 83 PHY 80 RM R 2 ★ 3 Posch 83 RB PAC 82 SHO 62 PAS 75 DRI 73 DEF 83 PHY 80 RM R 2 ★ 3 UPGRADES +1 OVR +3 Shot Power 80 +3 Vision 80 +4 Long Shots 80 +3 Volleys 79</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Pace Max. 84 Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY89" t="inlineStr">
@@ -17115,15 +17027,10 @@
       </c>
       <c r="CZ89" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Pace Max. 84 Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
+          <t>Intro to Rewards EVOs</t>
         </is>
       </c>
       <c r="DA89" t="inlineStr">
-        <is>
-          <t>Intro to Rewards EVOs</t>
-        </is>
-      </c>
-      <c r="DB89" t="inlineStr">
         <is>
           <t>Intro to Rewards EVOs Upgrade your qualified Player's attributes and Overall Rating with this Evolution. Tzolis 80 LM PAC 78 SHO 77 PAS 75 DRI 83 DEF 38 PHY 71 LW R 4 ★ 4 LM 75.9 Tzolis 81 LM PAC 78 SHO 78 PAS 77 DRI 83 DEF 38 PHY 71 LW R 4 ★ 4 LM 76.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Pace Max. 84 UPGRADES +1 OVR +3 Shot Power 80 +3 Vision 80 +4 Long Shots 80 +3 Volleys 79 +3 Short Pass 80 +4 Fk Accuracy 80 +4 Dribbling 81 +4 Reactions 81 +4 Long Pass 79 in 5 months in 5 months 84% 16%</t>
         </is>
@@ -17261,15 +17168,19 @@
       <c r="CS90" t="inlineStr"/>
       <c r="CT90" t="inlineStr"/>
       <c r="CU90" t="inlineStr"/>
-      <c r="CV90" t="inlineStr"/>
+      <c r="CV90" t="inlineStr">
+        <is>
+          <t>ST Advanced Forward +; ST Poacher +; ST Target Forward +</t>
+        </is>
+      </c>
       <c r="CW90" t="inlineStr">
         <is>
-          <t>ST Advanced Forward +; ST Poacher +; ST Target Forward +</t>
+          <t>ST Advanced Forward + ST Poacher + ST False 9 + ST Target Forward + Level 1 Tabaković 83 ST PAC 81 SHO 83 PAS 75 DRI 80 DEF 39 PHY 88 R 2 ★ 3 Tabaković 83 ST PAC 81 SHO 83 PAS 75 DRI 80 DEF 39 PHY 88 R 2 ★ 3 UPGRADES ST Advanced Forward + ST Poacher + ST False 9 + ST Target Forward +</t>
         </is>
       </c>
       <c r="CX90" t="inlineStr">
         <is>
-          <t>ST Advanced Forward + ST Poacher + ST False 9 + ST Target Forward + Level 1 Tabaković 83 ST PAC 81 SHO 83 PAS 75 DRI 80 DEF 39 PHY 88 R 2 ★ 3 Tabaković 83 ST PAC 81 SHO 83 PAS 75 DRI 80 DEF 39 PHY 88 R 2 ★ 3 UPGRADES ST Advanced Forward + ST Poacher + ST False 9 + ST Target Forward +</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 83 Position ST Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY90" t="inlineStr">
@@ -17279,15 +17190,10 @@
       </c>
       <c r="CZ90" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 83 Position ST Details Submit by in 5 months Expiry in 5 months Coins Cost Free Points Cost Free</t>
+          <t>Club Member Reward</t>
         </is>
       </c>
       <c r="DA90" t="inlineStr">
-        <is>
-          <t>Club Member Reward</t>
-        </is>
-      </c>
-      <c r="DB90" t="inlineStr">
         <is>
           <t>Club Member Reward Unlocked by being a Club Member on FC 26. Iñaki Williams 83 RM PAC 94 SHO 81 PAS 74 DRI 80 DEF 45 PHY 84 RW ST R 4 ★ 3 RM 79.3 Iñaki Williams 83 RM PAC 94 SHO 81 PAS 74 DRI 80 DEF 45 PHY 84 RW ST R 4 ★ 3 ST 79.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 83 Position ST UPGRADES ST Advanced Forward + ST Poacher + ST False 9 + ST Target Forward + in 5 months in 5 months 91% 9%</t>
         </is>
@@ -68230,7 +68136,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-11T06:51:56</t>
+          <t>2026-05-11T07:03:55</t>
         </is>
       </c>
     </row>

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -3145,12 +3145,12 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 10 hours Expiry in 7 days Coins Cost 100,000 Points Cost 500</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 9 hours Expiry in 7 days Coins Cost 100,000 Points Cost 500</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 10 hours Expiry in 7 days Coins Cost 100,000 Points Cost 500</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 9 hours Expiry in 7 days Coins Cost 100,000 Points Cost 500</t>
         </is>
       </c>
       <c r="CZ11" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>Cut In, Say Less 100,000 500 Elevate your favourite qualified player with enhanced pace, dribbling, shooting, and passing, allowing them to cut inside, get past defenders, and deliver in decisive moments! Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 92 RW PAC 92 SHO 90 PAS 92 DRI 93 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 93.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 in 10 hours in 7 days 64% 36%</t>
+          <t>Cut In, Say Less 100,000 500 Elevate your favourite qualified player with enhanced pace, dribbling, shooting, and passing, allowing them to cut inside, get past defenders, and deliver in decisive moments! Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 92 RW PAC 92 SHO 90 PAS 92 DRI 93 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 93.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 in 9 hours in 7 days 64% 36%</t>
         </is>
       </c>
     </row>
@@ -65932,7 +65932,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cut In, Say Less 100,000 500 Elevate your favourite qualified player with enhanced pace, dribbling, shooting, and passing, allowing them to cut inside, get past defenders, and deliver in decisive moments! Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 92 RW PAC 92 SHO 90 PAS 92 DRI 93 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 93.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 in 10 hours in 7 days 64% 36%</t>
+          <t>Cut In, Say Less 100,000 500 Elevate your favourite qualified player with enhanced pace, dribbling, shooting, and passing, allowing them to cut inside, get past defenders, and deliver in decisive moments! Debinha 89 RW PAC 87 SHO 82 PAS 87 DRI 92 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 86.5 Debinha 92 RW PAC 92 SHO 90 PAS 92 DRI 93 DEF 48 PHY 78 RM CM CAM R 5 ★ 5 RM 93.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +17 OVR 92 +4 SM 5 +17 Acceleration 93 +17 Sprint Speed 91 +17 Vision 93 +17 Crossing 90 +17 Fk Accuracy 89 +17 Short Pass 92 +17 Long Pass 91 +17 Agility 94 +17 Balance 92 +17 Reactions 91 +17 Ball Control 91 +17 Dribbling 92 +17 Composure 91 +17 Curve 94 +17 Finishing 92 +17 Shot Power 91 +17 Long Shots 90 +17 Volleys 86 3 7 in 9 hours in 7 days 64% 36%</t>
         </is>
       </c>
     </row>
@@ -68136,7 +68136,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-11T07:03:55</t>
+          <t>2026-05-11T07:42:38</t>
         </is>
       </c>
     </row>

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -60872,7 +60872,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-11T08:41:34</t>
+          <t>2026-05-11T08:58:43</t>
         </is>
       </c>
     </row>

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Max Pos. 5 Overall Max. 90 Position RB Excluded Position CB, ST Max PS 10 Max PS+ 3 Details Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Max Pos. 5 Overall Max. 90 Position RB Excluded Position CB, ST Max PS 10 Max PS+ 3 Details Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Max Pos. 5 Overall Max. 90 Position RB Excluded Position CB, ST Max PS 10 Max PS+ 3 Details Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Max Pos. 5 Overall Max. 90 Position RB Excluded Position CB, ST Max PS 10 Max PS+ 3 Details Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>No Payne No Gain NEW</t>
+          <t>No Payne No Gain</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>No Payne No Gain NEW The best right backs are unsung until they’re not. Evolve your player and bring the commitment that turned the world’s attention to Tim Payne. Kimmich 90 CDM PAC 82 SHO 75 PAS 90 DRI 86 DEF 85 PHY 83 RB CM R 3 ★ 4 RB 79.2 Kimmich 94 CDM PAC 93 SHO 75 PAS 95 DRI 86 DEF 95 PHY 83 RB RM CM R 3 ★ 4 CDM 87.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max Pos. 5 Overall Max. 90 Position RB Excluded Position CB, ST Max PS 10 Max PS+ 3 UPGRADES +15 OVR 94 RM +15 Acceleration 93 +15 Sprint Speed 93 +15 Crossing 95 +15 Fk Accuracy 95 +15 Short Pass 95 +15 Long Pass 95 +15 Curve 95 +15 Vision 95 +15 Interceptions 96 +15 Heading Acc. 96 +15 Defensive Awareness 96 +15 Standing Tackle 95 +15 Sliding Tackle 95 RB Fullback ++ RM Inside Forward ++ 3 8 in 10 days in 17 days 51% 49%</t>
+          <t>No Payne No Gain The best right backs are unsung until they’re not. Evolve your player and bring the commitment that turned the world’s attention to Tim Payne. Kimmich 90 CDM PAC 82 SHO 75 PAS 90 DRI 86 DEF 85 PHY 83 RB CM R 3 ★ 4 RB 79.2 Kimmich 94 CDM PAC 93 SHO 75 PAS 95 DRI 86 DEF 95 PHY 83 RB RM CM R 3 ★ 4 CDM 87.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max Pos. 5 Overall Max. 90 Position RB Excluded Position CB, ST Max PS 10 Max PS+ 3 UPGRADES +15 OVR 94 RM +15 Acceleration 93 +15 Sprint Speed 93 +15 Crossing 95 +15 Fk Accuracy 95 +15 Short Pass 95 +15 Long Pass 95 +15 Curve 95 +15 Vision 95 +15 Interceptions 96 +15 Heading Acc. 96 +15 Defensive Awareness 96 +15 Standing Tackle 95 +15 Sliding Tackle 95 RB Fullback ++ RM Inside Forward ++ 3 8 in 9 days in 16 days 52% 48%</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position ST Max PS 10 Max PS+ 3 Details Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position ST Max PS 10 Max PS+ 3 Details Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position ST Max PS 10 Max PS+ 3 Details Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position ST Max PS 10 Max PS+ 3 Details Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>Woodsy's Way Some strikers make every chance count no matter the stage. Evolve your striker and bring the clinical instinct that made Chris Wood a Premier League great. Dumornay 90 ST PAC 96 SHO 89 PAS 84 DRI 90 DEF 65 PHY 78 CAM R 4 ★ 4 ST 85.9 Dumornay 93 ST PAC 96 SHO 94 PAS 89 DRI 90 DEF 65 PHY 91 CAM R 4 ★ 5 ST 90.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position ST Max PS 10 Max PS+ 3 UPGRADES +15 OVR 93 +4 WF +15 Positioning 95 +15 Finishing 95 +15 Shot Power 94 +15 Long Shots 94 +15 Volleys 95 +15 Penalties 95 +15 Vision 93 +15 Short Pass 93 +15 Long Pass 93 +15 Jumping 96 +15 Stamina 95 +15 Strength 96 +15 Aggression 95 ST Advanced Forward ++ ST Target Forward ++ 3 8 in 9 days in 16 days 16% 84%</t>
+          <t>Woodsy's Way Some strikers make every chance count no matter the stage. Evolve your striker and bring the clinical instinct that made Chris Wood a Premier League great. Dumornay 90 ST PAC 96 SHO 89 PAS 84 DRI 90 DEF 65 PHY 78 CAM R 4 ★ 4 ST 85.9 Dumornay 93 ST PAC 96 SHO 94 PAS 89 DRI 90 DEF 65 PHY 91 CAM R 4 ★ 5 ST 90.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position ST Max PS 10 Max PS+ 3 UPGRADES +15 OVR 93 +4 WF +15 Positioning 95 +15 Finishing 95 +15 Shot Power 94 +15 Long Shots 94 +15 Volleys 95 +15 Penalties 95 +15 Vision 93 +15 Short Pass 93 +15 Long Pass 93 +15 Jumping 96 +15 Stamina 95 +15 Strength 96 +15 Aggression 95 ST Advanced Forward ++ ST Target Forward ++ 3 8 in 8 days in 15 days 16% 84%</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CM Max PS 10 Max PS+ 3 Details Submit by in 8 days Expiry in 15 days Coins Cost 100,000 Points Cost 500</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CM Max PS 10 Max PS+ 3 Details Submit by in 7 days Expiry in 14 days Coins Cost 100,000 Points Cost 500</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CM Max PS 10 Max PS+ 3 Details Submit by in 8 days Expiry in 15 days Coins Cost 100,000 Points Cost 500</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CM Max PS 10 Max PS+ 3 Details Submit by in 7 days Expiry in 14 days Coins Cost 100,000 Points Cost 500</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>Complete Connection 100,000 500 Connect your squad's defense and attack by bolstering your Central Midfielder's skills, allowing them to deliver more accurate passes and increase team possession. Matthäus 91 CM PAC 90 SHO 88 PAS 90 DRI 84 DEF 92 PHY 85 CB CDM R 5 ★ 5 CM 86.7 Matthäus 95 CM PAC 90 SHO 88 PAS 96 DRI 96 DEF 96 PHY 85 CB CDM R 5 ★ 5 CM 92.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CM Max PS 10 Max PS+ 3 UPGRADES +30 OVR 95 +4 WF +30 Vision 96 +30 Crossing 95 +30 Fk Accuracy 95 +30 Interceptions 96 +30 Heading Acc. 96 +30 Defensive Awareness 96 +30 Standing Tackle 96 +30 Sliding Tackle 97 +30 Short Pass 96 +30 Long Pass 96 +30 Curve 96 +30 Composure 94 +30 Agility 96 +30 Balance 96 +30 Reactions 95 +30 Ball Control 96 +30 Dribbling 96 3 8 in 8 days in 15 days 80% 20%</t>
+          <t>Complete Connection 100,000 500 Connect your squad's defense and attack by bolstering your Central Midfielder's skills, allowing them to deliver more accurate passes and increase team possession. Matthäus 91 CM PAC 90 SHO 88 PAS 90 DRI 84 DEF 92 PHY 85 CB CDM R 5 ★ 5 CM 86.7 Matthäus 95 CM PAC 90 SHO 88 PAS 96 DRI 96 DEF 96 PHY 85 CB CDM R 5 ★ 5 CM 92.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CM Max PS 10 Max PS+ 3 UPGRADES +30 OVR 95 +4 WF +30 Vision 96 +30 Crossing 95 +30 Fk Accuracy 95 +30 Interceptions 96 +30 Heading Acc. 96 +30 Defensive Awareness 96 +30 Standing Tackle 96 +30 Sliding Tackle 97 +30 Short Pass 96 +30 Long Pass 96 +30 Curve 96 +30 Composure 94 +30 Agility 96 +30 Balance 96 +30 Reactions 95 +30 Ball Control 96 +30 Dribbling 96 3 8 in 7 days in 14 days 80% 20%</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Details Submit by in 11 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Details Submit by in 11 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>Build your own FUT Birthday [Store] Unlocked by purchasing the Historical Birthday Cosmetic EVO Pack from the store (325,000 coins or 800 FC Points) João Cancelo 91 RB PAC 92 SHO 82 PAS 92 DRI 92 DEF 90 PHY 99 LB RM R 5 ★ 4 LB 91.8 João Cancelo 91 RB PAC 92 SHO 82 PAS 92 DRI 92 DEF 90 PHY 99 LB RM R 5 ★ 4 LB 91.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 UPGRADES No upgrades in 11 days in 11 days 81% 19%</t>
+          <t>Build your own FUT Birthday [Store] Unlocked by purchasing the Historical Birthday Cosmetic EVO Pack from the store (325,000 coins or 800 FC Points) João Cancelo 91 RB PAC 92 SHO 82 PAS 92 DRI 92 DEF 90 PHY 99 LB RM R 5 ★ 4 LB 91.8 João Cancelo 91 RB PAC 92 SHO 82 PAS 92 DRI 92 DEF 90 PHY 99 LB RM R 5 ★ 4 LB 91.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 UPGRADES No upgrades in 10 days in 10 days 80% 20%</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1976,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 Details Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 Details Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 Details Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 Details Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>Shadow Step 2 Evolve your player and bring the pace and defensive qualities that made the Shadow chemistry style a fan favourite. Katić 90 CB PAC 86 SHO 45 PAS 80 DRI 82 DEF 89 PHY 91 R 3 ★ 4 CB 88.6 Katić 91 CB PAC 92 SHO 45 PAS 80 DRI 82 DEF 95 PHY 91 R 3 ★ 4 CB 92.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 UPGRADES +1 OVR 91 +7 Acceleration 93 +7 Sprint Speed 93 +7 Interceptions 95 +7 Heading Acc. 94 +7 Defensive Awareness 95 +7 Standing Tackle 95 +7 Sliding Tackle 94 3 in 7 days in 14 days 63% 37%</t>
+          <t>Shadow Step 2 Evolve your player and bring the pace and defensive qualities that made the Shadow chemistry style a fan favourite. Katić 90 CB PAC 86 SHO 45 PAS 80 DRI 82 DEF 89 PHY 91 R 3 ★ 4 CB 88.6 Katić 91 CB PAC 92 SHO 45 PAS 80 DRI 82 DEF 95 PHY 91 R 3 ★ 4 CB 92.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 UPGRADES +1 OVR 91 +7 Acceleration 93 +7 Sprint Speed 93 +7 Interceptions 95 +7 Heading Acc. 94 +7 Defensive Awareness 95 +7 Standing Tackle 95 +7 Sliding Tackle 94 3 in 6 days in 13 days 64% 36%</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 21 days Token Cost 15</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 20 days Token Cost 15</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 21 days Token Cost 15</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 20 days Token Cost 15</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -2127,12 +2127,12 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 21 days Token Cost 15</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 20 days Token Cost 15</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 21 days Token Cost 15</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 20 days Token Cost 15</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>Path to Glory 15 Transform your favourite player into a Path to Glory player. This item rarity offers five nation links to chemistry! REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 4 months in 21 days 80% 20%</t>
+          <t>Path to Glory 15 Transform your favourite player into a Path to Glory player. This item rarity offers five nation links to chemistry! REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 3 months in 20 days 81% 19%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 Details Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 Details Submit by in 5 days Expiry in 12 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 Details Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 Details Submit by in 5 days Expiry in 12 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>Go on Son 2 The best finishers never give defenders an easy choice. Evolve your player and develop the two footed-threat that defined Son’s game. Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 85.6 Bobb 89 RW PAC 93 SHO 94 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 5 LW 90.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 UPGRADES +1 OVR 92 +4 WF +7 Positioning 94 +7 Finishing 95 +7 Shot Power 94 +7 Long Shots 94 +7 Volleys 93 +7 Penalties 93 3 8 in 6 days in 13 days 89% 11%</t>
+          <t>Go on Son 2 The best finishers never give defenders an easy choice. Evolve your player and develop the two footed-threat that defined Son’s game. Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 85.6 Bobb 89 RW PAC 93 SHO 94 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 5 LW 90.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 UPGRADES +1 OVR 92 +4 WF +7 Positioning 94 +7 Finishing 95 +7 Shot Power 94 +7 Long Shots 94 +7 Volleys 93 +7 Penalties 93 3 8 in 5 days in 12 days 89% 11%</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CB Max PS 10 Max PS+ 3 Details Submit by in 6 days Expiry in 13 days Coins Cost 75,000 Points Cost 350</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CB Max PS 10 Max PS+ 3 Details Submit by in 5 days Expiry in 12 days Coins Cost 75,000 Points Cost 350</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CB Max PS 10 Max PS+ 3 Details Submit by in 6 days Expiry in 13 days Coins Cost 75,000 Points Cost 350</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CB Max PS 10 Max PS+ 3 Details Submit by in 5 days Expiry in 12 days Coins Cost 75,000 Points Cost 350</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>Hold the Fort 75,000 350 Every great defence needs a cornerstone. Evolve your player and build the qualities that make every backline unshakeable. Carragher 89 CB PAC 85 SHO 55 PAS 80 DRI 85 DEF 90 PHY 90 RB LB R 3 ★ 4 CB 87.3 Carragher 94 CB PAC 90 SHO 55 PAS 86 DRI 85 DEF 95 PHY 95 RB LB R 3 ★ 4 CB 92.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CB Max PS 10 Max PS+ 3 UPGRADES +20 OVR 94 +20 Acceleration 90 +20 Sprint Speed 90 +20 Short Pass 92 +20 Long Pass 92 +20 Interceptions 95 +20 Heading Acc. 95 +20 Vision 92 +20 Defensive Awareness 95 +20 Standing Tackle 96 +20 Sliding Tackle 96 +20 Jumping 95 +20 Stamina 94 +20 Strength 95 +20 Aggression 95 CB Defender ++ CB Ball Playing Defender ++ 3 8 in 6 days in 13 days 82% 18%</t>
+          <t>Hold the Fort 75,000 350 Every great defence needs a cornerstone. Evolve your player and build the qualities that make every backline unshakeable. Carragher 89 CB PAC 85 SHO 55 PAS 80 DRI 85 DEF 90 PHY 90 RB LB R 3 ★ 4 CB 87.3 Carragher 94 CB PAC 90 SHO 55 PAS 86 DRI 85 DEF 95 PHY 95 RB LB R 3 ★ 4 CB 92.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CB Max PS 10 Max PS+ 3 UPGRADES +20 OVR 94 +20 Acceleration 90 +20 Sprint Speed 90 +20 Short Pass 92 +20 Long Pass 92 +20 Interceptions 95 +20 Heading Acc. 95 +20 Vision 92 +20 Defensive Awareness 95 +20 Standing Tackle 96 +20 Sliding Tackle 96 +20 Jumping 95 +20 Stamina 94 +20 Strength 95 +20 Aggression 95 CB Defender ++ CB Ball Playing Defender ++ 3 8 in 5 days in 12 days 82% 18%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 5 days Expiry in 12 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 5 days Expiry in 12 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>La Pulga From the streets of Rosario to the pinnacle of the game. Evolve your player and unlock the complete game that made Messi untouchable. Munetsi 84 CDM PAC 80 SHO 78 PAS 80 DRI 83 DEF 84 PHY 87 CM CAM RW R 3 ★ 4 CM 78.9 Munetsi 93 CDM PAC 95 SHO 89 PAS 90 DRI 94 DEF 84 PHY 87 CM CAM RW R 5 ★ 4 CM 91.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +20 OVR 93 +4 SM +20 Acceleration 95 +20 Sprint Speed 95 +20 Positioning 94 +20 Finishing 94 +20 Shot Power 94 +20 Volleys 94 +20 Crossing 94 +20 Short Pass 93 +20 Long Pass 93 +20 Curve 95 +20 Agility 96 +20 Balance 94 +20 Reactions 95 +20 Ball Control 95 +20 Vision 94 +20 Dribbling 95 +20 Composure 94 3 8 in 5 days in 12 days 91% 9%</t>
+          <t>La Pulga From the streets of Rosario to the pinnacle of the game. Evolve your player and unlock the complete game that made Messi untouchable. Munetsi 84 CDM PAC 80 SHO 78 PAS 80 DRI 83 DEF 84 PHY 87 CM CAM RW R 3 ★ 4 CM 78.9 Munetsi 93 CDM PAC 95 SHO 89 PAS 90 DRI 94 DEF 84 PHY 87 CM CAM RW R 5 ★ 4 CM 91.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +20 OVR 93 +4 SM +20 Acceleration 95 +20 Sprint Speed 95 +20 Positioning 94 +20 Finishing 94 +20 Shot Power 94 +20 Volleys 94 +20 Crossing 94 +20 Short Pass 93 +20 Long Pass 93 +20 Curve 95 +20 Agility 96 +20 Balance 94 +20 Reactions 95 +20 Ball Control 95 +20 Vision 94 +20 Dribbling 95 +20 Composure 94 3 8 in 4 days in 11 days 91% 9%</t>
         </is>
       </c>
     </row>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 2 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 2 Details Submit by in 4 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 2 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ11" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>Backbone Brilliance 3 Every great team is built on a solid backbone. Evolve your player and develop the qualities that hold your squad together Álvaro Carreras 90 LB PAC 92 SHO 76 PAS 87 DRI 90 DEF 87 PHY 90 LM L 4 ★ 4 LB 87.1 Álvaro Carreras 91 LB PAC 92 SHO 76 PAS 90 DRI 90 DEF 91 PHY 93 LM L 4 ★ 4 LB 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 2 UPGRADES +1 OVR +5 Vision 95 +5 Short Pass 95 +5 Long Pass 95 +5 Interceptions 95 +5 Defensive Awareness 94 +5 Standing Tackle 94 +5 Stamina 94 +5 Strength 95 +5 Aggression 94 in 4 days in 11 days 62% 38%</t>
+          <t>Backbone Brilliance 3 Every great team is built on a solid backbone. Evolve your player and develop the qualities that hold your squad together Álvaro Carreras 90 LB PAC 92 SHO 76 PAS 87 DRI 90 DEF 87 PHY 90 LM L 4 ★ 4 LB 87.1 Álvaro Carreras 91 LB PAC 92 SHO 76 PAS 90 DRI 90 DEF 91 PHY 93 LM L 4 ★ 4 LB 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 2 UPGRADES +1 OVR +5 Vision 95 +5 Short Pass 95 +5 Long Pass 95 +5 Interceptions 95 +5 Defensive Awareness 94 +5 Standing Tackle 94 +5 Stamina 94 +5 Strength 95 +5 Aggression 94 in 3 days in 10 days 62% 38%</t>
         </is>
       </c>
     </row>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 2 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY12" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 2 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ12" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="DA12" t="inlineStr">
         <is>
-          <t>Free Kick Mastery 2 The best free kick takers make it look inevitable. Evolve your player and master the art of the dead ball. Amaiur Sarriegi 89 ST PAC 94 SHO 88 PAS 86 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 ST 88.4 Amaiur Sarriegi 90 ST PAC 94 SHO 89 PAS 89 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 RM 88.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 2 UPGRADES +1 OVR +20 Shot Power 95 +20 Crossing 95 +20 Fk Accuracy +20 Curve 95 3 in 3 days in 10 days 12% 88%</t>
+          <t>Free Kick Mastery 2 The best free kick takers make it look inevitable. Evolve your player and master the art of the dead ball. Amaiur Sarriegi 89 ST PAC 94 SHO 88 PAS 86 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 ST 88.4 Amaiur Sarriegi 90 ST PAC 94 SHO 89 PAS 89 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 RM 88.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 2 UPGRADES +1 OVR +20 Shot Power 95 +20 Crossing 95 +20 Fk Accuracy +20 Curve 95 3 in 2 days in 9 days 12% 88%</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Details Submit by in 2 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Details Submit by in 2 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ13" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="DA13" t="inlineStr">
         <is>
-          <t>Final Preparations Fine-tune every detail before the biggest stage, and prepare for the path that lies ahead. Trincão 90 CAM PAC 91 SHO 91 PAS 89 DRI 94 DEF 49 PHY 85 RM RW ST L 4 ★ 3 RM 87.6 Trincão 92 CAM PAC 93 SHO 93 PAS 91 DRI 95 DEF 51 PHY 87 RM RW ST L 5 ★ 5 RM 90.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 UPGRADES +2 OVR +2 PAC 95 +2 SHO 95 +2 PAS 95 +2 DRI 95 +2 DEF 95 +2 PHY 95 +4 SM 5 +4 WF 5 TRAINING TIME 2 days in 3 days in 10 days 90% 10%</t>
+          <t>Final Preparations Fine-tune every detail before the biggest stage, and prepare for the path that lies ahead. Trincão 90 CAM PAC 91 SHO 91 PAS 89 DRI 94 DEF 49 PHY 85 RM RW ST L 4 ★ 3 RM 87.6 Trincão 92 CAM PAC 93 SHO 93 PAS 91 DRI 95 DEF 51 PHY 87 RM RW ST L 5 ★ 5 RM 90.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 UPGRADES +2 OVR +2 PAC 95 +2 SHO 95 +2 PAS 95 +2 DRI 95 +2 DEF 95 +2 PHY 95 +4 SM 5 +4 WF 5 TRAINING TIME 2 days in 2 days in 9 days 90% 10%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 9 days Coins Cost 50,000 Points Cost 250</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 Details Submit by in 21 hours Expiry in 8 days Coins Cost 50,000 Points Cost 250</t>
         </is>
       </c>
       <c r="CY14" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 9 days Coins Cost 50,000 Points Cost 250</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 Details Submit by in 21 hours Expiry in 8 days Coins Cost 50,000 Points Cost 250</t>
         </is>
       </c>
       <c r="CZ14" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="DA14" t="inlineStr">
         <is>
-          <t>Hawk Eye 50,000 250 Fast, powerful, and clinical. Evolve your player and unlock the attributes that made the Hawk chemistry style iconic. Kohler 91 CB PAC 84 SHO 54 PAS 85 DRI 80 DEF 93 PHY 92 R 3 ★ 4 CB 87.5 Kohler 93 CB PAC 93 SHO 73 PAS 85 DRI 80 DEF 93 PHY 95 R 3 ★ 4 CB 92.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 UPGRADES +20 OVR 93 +20 Acceleration 93 +20 Sprint Speed 93 +20 Positioning 95 +20 Finishing 95 +20 Shot Power 95 +20 Long Shots 95 +20 Volleys 96 +20 Jumping 95 +20 Stamina 95 +20 Strength 95 +20 Aggression 95 3 8 in 2 days in 9 days 75% 25%</t>
+          <t>Hawk Eye 50,000 250 Fast, powerful, and clinical. Evolve your player and unlock the attributes that made the Hawk chemistry style iconic. Kohler 91 CB PAC 84 SHO 54 PAS 85 DRI 80 DEF 93 PHY 92 R 3 ★ 4 CB 87.5 Kohler 93 CB PAC 93 SHO 73 PAS 85 DRI 80 DEF 93 PHY 95 R 3 ★ 4 CB 92.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 UPGRADES +20 OVR 93 +20 Acceleration 93 +20 Sprint Speed 93 +20 Positioning 95 +20 Finishing 95 +20 Shot Power 95 +20 Long Shots 95 +20 Volleys 96 +20 Jumping 95 +20 Stamina 95 +20 Strength 95 +20 Aggression 95 3 8 in 22 hours in 8 days 75% 25%</t>
         </is>
       </c>
     </row>
@@ -3618,12 +3618,12 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 24 days Token Cost 25</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 23 days Token Cost 25</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 24 days Token Cost 25</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 23 days Token Cost 25</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -3721,12 +3721,12 @@
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 24 days Token Cost 25</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 23 days Token Cost 25</t>
         </is>
       </c>
       <c r="CY15" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 24 days Token Cost 25</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 23 days Token Cost 25</t>
         </is>
       </c>
       <c r="CZ15" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="DA15" t="inlineStr">
         <is>
-          <t>FC Champions Excellence 25 4 Show off your FC Champions Excellence! Give your favourite player a luxurious new look to showcase their elite status at your club. REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 4 months in 24 days 28% 72%</t>
+          <t>FC Champions Excellence 25 4 Show off your FC Champions Excellence! Give your favourite player a luxurious new look to showcase their elite status at your club. REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 3 months in 23 days 28% 72%</t>
         </is>
       </c>
     </row>
@@ -3769,12 +3769,12 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 24 days Token Cost 25</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 23 days Token Cost 25</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 24 days Token Cost 25</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 23 days Token Cost 25</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -3872,12 +3872,12 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 24 days Token Cost 25</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 23 days Token Cost 25</t>
         </is>
       </c>
       <c r="CY16" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 24 days Token Cost 25</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 23 days Token Cost 25</t>
         </is>
       </c>
       <c r="CZ16" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="DA16" t="inlineStr">
         <is>
-          <t>FC Champions Excellence 25 4 Show off your FC Champions Excellence! Give your favourite player a luxurious new look to showcase their elite status at your club. REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 4 months in 24 days 29% 71%</t>
+          <t>FC Champions Excellence 25 4 Show off your FC Champions Excellence! Give your favourite player a luxurious new look to showcase their elite status at your club. REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 3 months in 23 days 29% 71%</t>
         </is>
       </c>
     </row>
@@ -5216,12 +5216,12 @@
       </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 85 Position CAM Max PS 10 Max PS+ 1 Pace Max. 85 Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 85 Position CAM Max PS 10 Max PS+ 1 Pace Max. 85 Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY24" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 85 Position CAM Max PS 10 Max PS+ 1 Pace Max. 85 Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 85 Position CAM Max PS 10 Max PS+ 1 Pace Max. 85 Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ24" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="DA24" t="inlineStr">
         <is>
-          <t>Star in Motion Celebrate Jamal Musiala’s rise to football’s elite. Step into the spotlight with enhanced creativity, flair, and precision that define the face of the game’s new generation. Dunn 82 CM PAC 85 SHO 76 PAS 80 DRI 82 DEF 75 PHY 79 LB RM CAM R 4 ★ 4 RM 74.9 Dunn 86 CM PAC 85 SHO 82 PAS 82 DRI 88 DEF 75 PHY 79 LB RM CAM R 5 ★ 4 CAM 80.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 85 Position CAM Max PS 10 Max PS+ 1 Pace Max. 85 UPGRADES +10 OVR 86 +25 PAC 80 +10 SHO 82 +10 DRI 88 +5 DEF 60 +10 PAS 82 +4 SM +15 Jumping 80 +20 Stamina 80 +15 Aggression 65 +15 Strength 70 CAM Shadow Striker ++ CAM Half Winger + 1 6 Show less in 4 months in 4 months 90% 10%</t>
+          <t>Star in Motion Celebrate Jamal Musiala’s rise to football’s elite. Step into the spotlight with enhanced creativity, flair, and precision that define the face of the game’s new generation. Dunn 82 CM PAC 85 SHO 76 PAS 80 DRI 82 DEF 75 PHY 79 LB RM CAM R 4 ★ 4 RM 74.9 Dunn 86 CM PAC 85 SHO 82 PAS 82 DRI 88 DEF 75 PHY 79 LB RM CAM R 5 ★ 4 CAM 80.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 85 Position CAM Max PS 10 Max PS+ 1 Pace Max. 85 UPGRADES +10 OVR 86 +25 PAC 80 +10 SHO 82 +10 DRI 88 +5 DEF 60 +10 PAS 82 +4 SM +15 Jumping 80 +20 Stamina 80 +15 Aggression 65 +15 Strength 70 CAM Shadow Striker ++ CAM Half Winger + 1 6 Show less in 3 months in 3 months 90% 10%</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>GK Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>GK Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -5379,12 +5379,12 @@
       </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Position GK Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Position GK Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY25" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Position GK Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Position GK Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ25" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="DA25" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs I Assign a GK to Training Camp Evolutions through the Companion App. When the training session concludes, collect their earned upgrades. Casteels 82 GK DIV 82 HAN 79 KIC 74 REF 85 SPD 45 POS 83 L 1 ★ 2 GK 76.7 Casteels 82 GK DIV 82 HAN 79 KIC 74 REF 85 SPD 45 POS 83 L 1 ★ 2 GK 76.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Position GK UPGRADES GK Sweeper Keeper + TRAINING TIME 1 day in 4 months in 4 months 69% 31%</t>
+          <t>Intro to Training Camp EVOs I Assign a GK to Training Camp Evolutions through the Companion App. When the training session concludes, collect their earned upgrades. Casteels 82 GK DIV 82 HAN 79 KIC 74 REF 85 SPD 45 POS 83 L 1 ★ 2 GK 76.7 Casteels 82 GK DIV 82 HAN 79 KIC 74 REF 85 SPD 45 POS 83 L 1 ★ 2 GK 76.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Position GK UPGRADES GK Sweeper Keeper + TRAINING TIME 1 day in 3 months in 3 months 69% 31%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="CX26" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Max PS 3 Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Max PS 3 Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY26" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Max PS 3 Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Max PS 3 Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ26" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="DA26" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs II Assign a Player to Training Camp Evolutions through the Companion App. When the training session concludes, collect their earned upgrades. Dunn 82 CM PAC 85 SHO 76 PAS 80 DRI 82 DEF 75 PHY 79 LB RM CAM R 4 ★ 4 RM 74.9 Dunn 82 CM PAC 85 SHO 76 PAS 80 DRI 82 DEF 75 PHY 79 LB RM CAM R 4 ★ 4 RM 76.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Max PS 3 UPGRADES 4 TRAINING TIME 1 day in 4 months in 4 months 75% 25%</t>
+          <t>Intro to Training Camp EVOs II Assign a Player to Training Camp Evolutions through the Companion App. When the training session concludes, collect their earned upgrades. Dunn 82 CM PAC 85 SHO 76 PAS 80 DRI 82 DEF 75 PHY 79 LB RM CAM R 4 ★ 4 RM 74.9 Dunn 82 CM PAC 85 SHO 76 PAS 80 DRI 82 DEF 75 PHY 79 LB RM CAM R 4 ★ 4 RM 76.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Max PS 3 UPGRADES 4 TRAINING TIME 1 day in 3 months in 3 months 75% 25%</t>
         </is>
       </c>
     </row>
@@ -5705,12 +5705,12 @@
       </c>
       <c r="CX27" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 81 Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 81 Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY27" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 81 Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 81 Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ27" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="DA27" t="inlineStr">
         <is>
-          <t>Intro to Evolutions 2 Welcome to FC 26! Kick things off by exploring Evolutions, where you can upgrade Players over time until they reach their stated maximum. Laurienté 80 LW PAC 91 SHO 77 PAS 74 DRI 83 DEF 36 PHY 57 LM R 4 ★ 3 LM 76.5 Laurienté 81 LW PAC 91 SHO 78 PAS 74 DRI 83 DEF 36 PHY 57 LM R 4 ★ 3 LM 76.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 81 UPGRADES +1 OVR 82 +1 PAC 83 +1 SHO 83 in 4 months in 4 months 79% 21%</t>
+          <t>Intro to Evolutions 2 Welcome to FC 26! Kick things off by exploring Evolutions, where you can upgrade Players over time until they reach their stated maximum. Laurienté 80 LW PAC 91 SHO 77 PAS 74 DRI 83 DEF 36 PHY 57 LM R 4 ★ 3 LM 76.5 Laurienté 81 LW PAC 91 SHO 78 PAS 74 DRI 83 DEF 36 PHY 57 LM R 4 ★ 3 LM 76.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 81 UPGRADES +1 OVR 82 +1 PAC 83 +1 SHO 83 in 3 months in 3 months 79% 21%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="CX28" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY28" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ28" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="DA28" t="inlineStr">
         <is>
-          <t>National Pride Unlocked by completing the Triple Crown task in the Festival of Football Gauntlet objective Lee Kang In 92 RW PAC 96 SHO 92 PAS 93 DRI 96 DEF 62 PHY 82 RM CM L 4 ★ 4 RM 91.2 Lee Kang In 92 RW PAC 96 SHO 92 PAS 93 DRI 96 DEF 62 PHY 82 RM CM L 4 ★ 4 RM 91.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 UPGRADES No upgrades in 10 days in 10 days 88% 13%</t>
+          <t>National Pride Unlocked by completing the Triple Crown task in the Festival of Football Gauntlet objective Lee Kang In 92 RW PAC 96 SHO 92 PAS 93 DRI 96 DEF 62 PHY 82 RM CM L 4 ★ 4 RM 91.2 Lee Kang In 92 RW PAC 96 SHO 92 PAS 93 DRI 96 DEF 62 PHY 82 RM CM L 4 ★ 4 RM 91.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 UPGRADES No upgrades in 9 days in 9 days 88% 12%</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="DA29" t="inlineStr">
         <is>
-          <t>Tiny Tim Unlocked by completing the Tiny Tim task in the Perfect Volley objective Nico Williams 89 LM PAC 95 SHO 80 PAS 85 DRI 89 DEF 40 PHY 75 RM ST LW R 5 ★ 4 RM 83.8 Nico Williams 93 LM PAC 95 SHO 93 PAS 88 DRI 92 DEF 43 PHY 94 RM ST LW R 5 ★ 5 RM 91.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max Pos. 4 Overall Max. 91 Position ST Max PS 10 Max PS+ 3 UPGRADES +25 OVR 93 LM RM +4 WF 5 +35 Finishing 95 +35 Volleys 96 +35 Reactions 95 +40 Aggression 97 +15 Acceleration 91 +30 Long Shots 93 +25 Agility 90 +40 Heading Acc. +30 Positioning 93 +30 Vision 91 +25 Balance 90 +40 Jumping 97 +15 Sprint Speed 93 +30 Short Pass 93 +25 Ball Control 92 +30 Strength 94 +35 Shot Power 96 +25 Dribbling 92 +35 Composure 95 +30 Stamina 92 3 8 in 3 months in 3 months 75% 25%</t>
+          <t>Tiny Tim Unlocked by completing the Tiny Tim task in the Perfect Volley objective Nico Williams 89 LM PAC 95 SHO 80 PAS 85 DRI 89 DEF 40 PHY 75 RM ST LW R 5 ★ 4 RM 83.8 Nico Williams 93 LM PAC 95 SHO 93 PAS 88 DRI 92 DEF 43 PHY 94 RM ST LW R 5 ★ 5 RM 91.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max Pos. 4 Overall Max. 91 Position ST Max PS 10 Max PS+ 3 UPGRADES +25 OVR 93 LM RM +4 WF 5 +35 Finishing 95 +35 Volleys 96 +35 Reactions 95 +40 Aggression 97 +15 Acceleration 91 +30 Long Shots 93 +25 Agility 90 +40 Heading Acc. +30 Positioning 93 +30 Vision 91 +25 Balance 90 +40 Jumping 97 +15 Sprint Speed 93 +30 Short Pass 93 +25 Ball Control 92 +30 Strength 94 +35 Shot Power 96 +25 Dribbling 92 +35 Composure 95 +30 Stamina 92 3 8 in 3 months in 3 months 76% 24%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="CX38" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY38" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ38" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="DA38" t="inlineStr">
         <is>
-          <t>Defense Wins Championships Unlocked by completing the South Korea vs. Czechia task in the Path to Glory! objective Arrey-Mbi 90 CB PAC 91 SHO 52 PAS 77 DRI 86 DEF 89 PHY 90 LB L 3 ★ 3 CB 89.5 Arrey-Mbi 90 CB PAC 91 SHO 52 PAS 77 DRI 86 DEF 95 PHY 90 LB L 3 ★ 3 CB 90.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 UPGRADES +6 Interceptions 95 +8 Defensive Awareness 94 +6 Sliding Tackle 94 +10 Heading Acc. +6 Standing Tackle 95 in 2 days in 2 days 90% 10%</t>
+          <t>Defense Wins Championships Unlocked by completing the South Korea vs. Czechia task in the Path to Glory! objective Arrey-Mbi 90 CB PAC 91 SHO 52 PAS 77 DRI 86 DEF 89 PHY 90 LB L 3 ★ 3 CB 89.5 Arrey-Mbi 90 CB PAC 91 SHO 52 PAS 77 DRI 86 DEF 95 PHY 90 LB L 3 ★ 3 CB 90.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 UPGRADES +6 Interceptions 95 +8 Defensive Awareness 94 +6 Sliding Tackle 94 +10 Heading Acc. +6 Standing Tackle 95 in 23 hours in 23 hours 90% 10%</t>
         </is>
       </c>
     </row>
@@ -8205,12 +8205,12 @@
       </c>
       <c r="CX39" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Position ST Excluded Position CB Max PS 10 Max PS+ 3 Details Submit by in 4 months Expiry in 4 months Token Cost 2,000</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Position ST Excluded Position CB Max PS 10 Max PS+ 3 Details Submit by in 3 months Expiry in 3 months Token Cost 2,000</t>
         </is>
       </c>
       <c r="CY39" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Position ST Excluded Position CB Max PS 10 Max PS+ 3 Details Submit by in 4 months Expiry in 4 months Token Cost 2,000</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Position ST Excluded Position CB Max PS 10 Max PS+ 3 Details Submit by in 3 months Expiry in 3 months Token Cost 2,000</t>
         </is>
       </c>
       <c r="CZ39" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="DA39" t="inlineStr">
         <is>
-          <t>The Main Event 2,000 Unlocked in the Token Store for 2000 tokens. Built for the spotlight. Enhance attacking presence and decisive ability to take center stage and define the biggest moments of the match. Doumbia 89 ST PAC 96 SHO 89 PAS 80 DRI 88 DEF 50 PHY 79 LM LW R 4 ★ 4 LM 86.8 Doumbia 97 ST PAC 97 SHO 97 PAS 86 DRI 94 DEF 50 PHY 89 LM LW R 5 ★ 5 ST 94.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 Position ST Excluded Position CB Max PS 10 Max PS+ 3 UPGRADES +50 OVR 97 +4 SM +4 WF +50 Acceleration 96 +50 Sprint Speed 96 +50 Stamina 93 +50 Strength 93 +45 Positioning 97 +45 Finishing 97 +45 Shot Power 96 +50 Ball Control 96 +50 Dribbling 93 +50 Composure 93 +45 Long Shots 96 +45 Volleys 97 +45 Penalties 97 +50 Vision 94 +50 Short Pass 94 +50 Long Pass 92 +50 Reactions 95 +50 Curve 95 +50 Agility 96 +50 Balance 93 4 8 in 4 months in 4 months 97% 3%</t>
+          <t>The Main Event 2,000 Unlocked in the Token Store for 2000 tokens. Built for the spotlight. Enhance attacking presence and decisive ability to take center stage and define the biggest moments of the match. Doumbia 89 ST PAC 96 SHO 89 PAS 80 DRI 88 DEF 50 PHY 79 LM LW R 4 ★ 4 LM 86.8 Doumbia 97 ST PAC 97 SHO 97 PAS 86 DRI 94 DEF 50 PHY 89 LM LW R 5 ★ 5 ST 94.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 Position ST Excluded Position CB Max PS 10 Max PS+ 3 UPGRADES +50 OVR 97 +4 SM +4 WF +50 Acceleration 96 +50 Sprint Speed 96 +50 Stamina 93 +50 Strength 93 +45 Positioning 97 +45 Finishing 97 +45 Shot Power 96 +50 Ball Control 96 +50 Dribbling 93 +50 Composure 93 +45 Long Shots 96 +45 Volleys 97 +45 Penalties 97 +50 Vision 94 +50 Short Pass 94 +50 Long Pass 92 +50 Reactions 95 +50 Curve 95 +50 Agility 96 +50 Balance 93 4 8 in 3 months in 3 months 97% 3%</t>
         </is>
       </c>
     </row>
@@ -8454,12 +8454,12 @@
       </c>
       <c r="CX40" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Details Submit by in 4 months Expiry in 4 months Token Cost 500</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Details Submit by in 3 months Expiry in 3 months Token Cost 500</t>
         </is>
       </c>
       <c r="CY40" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Details Submit by in 4 months Expiry in 4 months Token Cost 500</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Details Submit by in 3 months Expiry in 3 months Token Cost 500</t>
         </is>
       </c>
       <c r="CZ40" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="DA40" t="inlineStr">
         <is>
-          <t>Gold Standard 500 Unlocked in the Token Store for 500 tokens. The benchmark of excellence. Upgrade defensive quality and composure to deliver consistent, elite-level performances when it matters most. Nesta 88 CB PAC 87 SHO 43 PAS 65 DRI 80 DEF 88 PHY 86 R 3 ★ 4 CB 88.9 Nesta 94 CB PAC 93 SHO 61 PAS 81 DRI 90 DEF 95 PHY 94 R 3 ★ 5 CB 93.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 UPGRADES +50 OVR 94 +4 WF +50 Acceleration 92 +45 Heading Acc. 94 +45 Defensive Awareness 95 +45 Standing Tackle 95 +50 Sprint Speed 93 +50 Vision 94 +50 Short Pass 94 +45 Sliding Tackle 92 +40 Jumping 92 +40 Stamina 92 +50 Shot Power 92 +50 Long Shots 92 +40 Composure 92 +45 Interceptions 95 +45 Strength 96 +50 Aggression 92 +50 Long Pass 94 +40 Agility 91 +40 Balance 90 +40 Reactions 93 +40 Ball Control 89 +40 Dribbling 90 in 4 months in 4 months 92% 8%</t>
+          <t>Gold Standard 500 Unlocked in the Token Store for 500 tokens. The benchmark of excellence. Upgrade defensive quality and composure to deliver consistent, elite-level performances when it matters most. Nesta 88 CB PAC 87 SHO 43 PAS 65 DRI 80 DEF 88 PHY 86 R 3 ★ 4 CB 88.9 Nesta 94 CB PAC 93 SHO 61 PAS 81 DRI 90 DEF 95 PHY 94 R 3 ★ 5 CB 93.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 UPGRADES +50 OVR 94 +4 WF +50 Acceleration 92 +45 Heading Acc. 94 +45 Defensive Awareness 95 +45 Standing Tackle 95 +50 Sprint Speed 93 +50 Vision 94 +50 Short Pass 94 +45 Sliding Tackle 92 +40 Jumping 92 +40 Stamina 92 +50 Shot Power 92 +50 Long Shots 92 +40 Composure 92 +45 Interceptions 95 +45 Strength 96 +50 Aggression 92 +50 Long Pass 94 +40 Agility 91 +40 Balance 90 +40 Reactions 93 +40 Ball Control 89 +40 Dribbling 90 in 3 months in 3 months 92% 8%</t>
         </is>
       </c>
     </row>
@@ -8639,12 +8639,12 @@
       </c>
       <c r="CX41" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Details Submit by in 4 months Expiry in 2 days Token Cost 100</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Details Submit by in 3 months Expiry in 1 day Token Cost 100</t>
         </is>
       </c>
       <c r="CY41" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Details Submit by in 4 months Expiry in 2 days Token Cost 100</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Details Submit by in 3 months Expiry in 1 day Token Cost 100</t>
         </is>
       </c>
       <c r="CZ41" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="DA41" t="inlineStr">
         <is>
-          <t>One Step Ahead 100 Unlocked in the Token Store for 100 tokens. Sharp thinking meets sharper movement. Boost dribbling to glide past pressure and stay a move ahead of every defender. Calba 91 ST PAC 92 SHO 91 PAS 88 DRI 90 DEF 44 PHY 80 RM LM LW R 4 ★ 5 RM 89.5 Calba 91 ST PAC 92 SHO 91 PAS 88 DRI 96 DEF 44 PHY 80 RM LM LW R 5 ★ 5 RM 92.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 UPGRADES +4 SM +10 Agility 93 +10 Ball Control 94 +10 Composure +10 Balance 93 +10 Reactions 95 +10 Dribbling 8 in 4 months in 2 days 94% 6%</t>
+          <t>One Step Ahead 100 Unlocked in the Token Store for 100 tokens. Sharp thinking meets sharper movement. Boost dribbling to glide past pressure and stay a move ahead of every defender. Calba 91 ST PAC 92 SHO 91 PAS 88 DRI 90 DEF 44 PHY 80 RM LM LW R 4 ★ 5 RM 89.5 Calba 91 ST PAC 92 SHO 91 PAS 88 DRI 96 DEF 44 PHY 80 RM LM LW R 5 ★ 5 RM 92.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 UPGRADES +4 SM +10 Agility 93 +10 Ball Control 94 +10 Composure +10 Balance 93 +10 Reactions 95 +10 Dribbling 8 in 3 months in 1 day 94% 6%</t>
         </is>
       </c>
     </row>
@@ -8687,12 +8687,12 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 12 days Token Cost 15</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 11 days Token Cost 15</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 12 days Token Cost 15</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 11 days Token Cost 15</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -8790,12 +8790,12 @@
       </c>
       <c r="CX42" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 12 days Token Cost 15</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 11 days Token Cost 15</t>
         </is>
       </c>
       <c r="CY42" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 12 days Token Cost 15</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 11 days Token Cost 15</t>
         </is>
       </c>
       <c r="CZ42" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="DA42" t="inlineStr">
         <is>
-          <t>Path to Glory 15 Unlocked in the Token Store for 15 tokens. Transform your favourite player into a Path to Glory player. This item rarity offers five nation links to chemistry! REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 4 months in 12 days 24% 76%</t>
+          <t>Path to Glory 15 Unlocked in the Token Store for 15 tokens. Transform your favourite player into a Path to Glory player. This item rarity offers five nation links to chemistry! REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 3 months in 11 days 23% 77%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="CX43" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY43" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ43" t="inlineStr">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="DA43" t="inlineStr">
         <is>
-          <t>Five Star Phenom II Unlocked by completing the Season 8 Exhibition objective Ounahi 91 CM PAC 91 SHO 93 PAS 94 DRI 95 DEF 81 PHY 83 CAM R 4 ★ 4 CM 89.7 Ounahi 91 CM PAC 91 SHO 93 PAS 94 DRI 95 DEF 81 PHY 83 CAM R 5 ★ 5 CM 91.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 UPGRADES +4 SM 5 +4 WF 5 in 27 days in 27 days 87% 13%</t>
+          <t>Five Star Phenom II Unlocked by completing the Season 8 Exhibition objective Ounahi 91 CM PAC 91 SHO 93 PAS 94 DRI 95 DEF 81 PHY 83 CAM R 4 ★ 4 CM 89.7 Ounahi 91 CM PAC 91 SHO 93 PAS 94 DRI 95 DEF 81 PHY 83 CAM R 5 ★ 5 CM 91.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 UPGRADES +4 SM 5 +4 WF 5 in 26 days in 26 days 87% 13%</t>
         </is>
       </c>
     </row>
@@ -9212,12 +9212,12 @@
       </c>
       <c r="CX44" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Position ST Max PS 10 Max PS+ 3 Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Position ST Max PS 10 Max PS+ 3 Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY44" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Position ST Max PS 10 Max PS+ 3 Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Position ST Max PS 10 Max PS+ 3 Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ44" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="DA44" t="inlineStr">
         <is>
-          <t>The Iron 9 2 Unlocked by completing the Score in 30 task in the Season 8 Exhibition objective Matthäus 91 CM PAC 89 SHO 88 PAS 89 DRI 83 DEF 91 PHY 84 RB CB CDM RM CAM ST R 4 ★ 5 CM 83.6 Matthäus 93 CM PAC 91 SHO 95 PAS 93 DRI 91 DEF 91 PHY 90 RB CB CDM RM CAM ST R 4 ★ 5 CM 91.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Position ST Max PS 10 Max PS+ 3 UPGRADES +15 OVR 93 +15 Sprint Speed 90 +20 Positioning 95 +20 Fk Accuracy 93 +20 Short Pass 95 +10 Stamina 95 +15 Acceleration 90 +20 Long Pass 88 +20 Curve 95 +10 Composure 92 +20 Finishing 94 +20 Long Shots 93 +20 Volleys 93 +10 Agility 90 +10 Balance 90 +10 Reactions 94 +20 Shot Power 93 +20 Penalties 93 +20 Vision 92 +20 Crossing 89 +10 Ball Control 92 +10 Dribbling 92 +10 Strength 94 +10 Aggression 88 3 8 in 27 days in 27 days 93% 7%</t>
+          <t>The Iron 9 2 Unlocked by completing the Score in 30 task in the Season 8 Exhibition objective Matthäus 91 CM PAC 89 SHO 88 PAS 89 DRI 83 DEF 91 PHY 84 RB CB CDM RM CAM ST R 4 ★ 5 CM 83.6 Matthäus 93 CM PAC 91 SHO 95 PAS 93 DRI 91 DEF 91 PHY 90 RB CB CDM RM CAM ST R 4 ★ 5 CM 91.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Position ST Max PS 10 Max PS+ 3 UPGRADES +15 OVR 93 +15 Sprint Speed 90 +20 Positioning 95 +20 Fk Accuracy 93 +20 Short Pass 95 +10 Stamina 95 +15 Acceleration 90 +20 Long Pass 88 +20 Curve 95 +10 Composure 92 +20 Finishing 94 +20 Long Shots 93 +20 Volleys 93 +10 Agility 90 +10 Balance 90 +10 Reactions 94 +20 Shot Power 93 +20 Penalties 93 +20 Vision 92 +20 Crossing 89 +10 Ball Control 92 +10 Dribbling 92 +10 Strength 94 +10 Aggression 88 3 8 in 26 days in 26 days 93% 7%</t>
         </is>
       </c>
     </row>
@@ -9463,12 +9463,12 @@
       </c>
       <c r="CX45" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CM Max PS 10 Max PS+ 3 Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CM Max PS 10 Max PS+ 3 Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY45" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CM Max PS 10 Max PS+ 3 Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CM Max PS 10 Max PS+ 3 Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ45" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="DA45" t="inlineStr">
         <is>
-          <t>Trequartista 2 Unlocked by completing the Score in 25 task in the Season 8 Exhibition objective Cambiasso 89 CDM PAC 85 SHO 84 PAS 88 DRI 88 DEF 89 PHY 86 CM L 5 ★ 5 CM 87.3 Cambiasso 93 CDM PAC 92 SHO 94 PAS 91 DRI 94 DEF 89 PHY 86 CM L 5 ★ 5 CM 92.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CM Max PS 10 Max PS+ 3 UPGRADES +10 OVR 93 +4 WF 5 +10 Acceleration 92 +15 Agility 92 +15 Reactions 94 +15 Balance 92 +10 Sprint Speed 92 +15 Finishing 94 +15 Shot Power 95 +10 Short Pass 94 +10 Curve 95 +10 Long Pass 94 +15 Positioning 93 +10 Vision 93 +10 Crossing 90 +10 Fk Accuracy 95 +15 Composure 93 +15 Long Shots 95 +15 Volleys 93 +15 Penalties 93 +15 Ball Control 94 +15 Dribbling 95 3 8 in 27 days in 27 days 86% 14%</t>
+          <t>Trequartista 2 Unlocked by completing the Score in 25 task in the Season 8 Exhibition objective Cambiasso 89 CDM PAC 85 SHO 84 PAS 88 DRI 88 DEF 89 PHY 86 CM L 5 ★ 5 CM 87.3 Cambiasso 93 CDM PAC 92 SHO 94 PAS 91 DRI 94 DEF 89 PHY 86 CM L 5 ★ 5 CM 92.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CM Max PS 10 Max PS+ 3 UPGRADES +10 OVR 93 +4 WF 5 +10 Acceleration 92 +15 Agility 92 +15 Reactions 94 +15 Balance 92 +10 Sprint Speed 92 +15 Finishing 94 +15 Shot Power 95 +10 Short Pass 94 +10 Curve 95 +10 Long Pass 94 +15 Positioning 93 +10 Vision 93 +10 Crossing 90 +10 Fk Accuracy 95 +15 Composure 93 +15 Long Shots 95 +15 Volleys 93 +15 Penalties 93 +15 Ball Control 94 +15 Dribbling 95 3 8 in 26 days in 26 days 86% 14%</t>
         </is>
       </c>
     </row>
@@ -11299,12 +11299,12 @@
       </c>
       <c r="CX53" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Excluded Position CB, CM Max PS 10 Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Excluded Position CB, CM Max PS 10 Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY53" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Excluded Position CB, CM Max PS 10 Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Excluded Position CB, CM Max PS 10 Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ53" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="DA53" t="inlineStr">
         <is>
-          <t>Old School Winger [SP 1] 8 Unlocked by reaching level 1 in the Standard Season Pass. Cristiano Ronaldo 90 ST PAC 90 SHO 93 PAS 82 DRI 89 DEF 40 PHY 83 R 5 ★ 4 ST 87.2 Cristiano Ronaldo 92 ST PAC 94 SHO 93 PAS 85 DRI 94 DEF 40 PHY 83 R 5 ★ 4 ST 90.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Excluded Position CB, CM Max PS 10 UPGRADES +2 OVR 92 +5 Sprint Speed 95 +3 Vision 94 +3 Crossing 94 +6 Dribbling 95 +6 Composure 95 +5 Acceleration 94 +6 Balance 96 +6 Reactions 95 +6 Ball Control 96 +3 Fk Accuracy 95 +3 Short Pass 96 +3 Long Pass 95 +3 Curve 95 +6 Agility 94 8 in 4 months in 1 month 90% 10%</t>
+          <t>Old School Winger [SP 1] 8 Unlocked by reaching level 1 in the Standard Season Pass. Cristiano Ronaldo 90 ST PAC 90 SHO 93 PAS 82 DRI 89 DEF 40 PHY 83 R 5 ★ 4 ST 87.2 Cristiano Ronaldo 92 ST PAC 94 SHO 93 PAS 85 DRI 94 DEF 40 PHY 83 R 5 ★ 4 ST 90.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Excluded Position CB, CM Max PS 10 UPGRADES +2 OVR 92 +5 Sprint Speed 95 +3 Vision 94 +3 Crossing 94 +6 Dribbling 95 +6 Composure 95 +5 Acceleration 94 +6 Balance 96 +6 Reactions 95 +6 Ball Control 96 +3 Fk Accuracy 95 +3 Short Pass 96 +3 Long Pass 95 +3 Curve 95 +6 Agility 94 8 in 3 months in 1 month 90% 10%</t>
         </is>
       </c>
     </row>
@@ -11506,12 +11506,12 @@
       </c>
       <c r="CX54" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY54" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ54" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="DA54" t="inlineStr">
         <is>
-          <t>Try Again Tomorrow [SP 8] 3 Unlocked by reaching level 8 in the Standard Season Pass. Calafiori 90 LB PAC 87 SHO 80 PAS 85 DRI 89 DEF 90 PHY 91 CB L 3 ★ 4 LB 86.7 Calafiori 92 LB PAC 92 SHO 80 PAS 85 DRI 89 DEF 94 PHY 94 CB L 3 ★ 4 LB 91.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 UPGRADES +2 OVR 92 +6 Interceptions 94 +6 Heading Acc. 93 +3 Strength 93 +3 Aggression 94 +5 Acceleration 93 +5 Sprint Speed 94 +6 Defensive Awareness 94 +6 Standing Tackle 95 +6 Sliding Tackle 94 +3 Jumping 94 +3 Stamina 94 8 in 4 months in 1 month 94% 6%</t>
+          <t>Try Again Tomorrow [SP 8] 3 Unlocked by reaching level 8 in the Standard Season Pass. Calafiori 90 LB PAC 87 SHO 80 PAS 85 DRI 89 DEF 90 PHY 91 CB L 3 ★ 4 LB 86.7 Calafiori 92 LB PAC 92 SHO 80 PAS 85 DRI 89 DEF 94 PHY 94 CB L 3 ★ 4 LB 91.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 UPGRADES +2 OVR 92 +6 Interceptions 94 +6 Heading Acc. 93 +3 Strength 93 +3 Aggression 94 +5 Acceleration 93 +5 Sprint Speed 94 +6 Defensive Awareness 94 +6 Standing Tackle 95 +6 Sliding Tackle 94 +3 Jumping 94 +3 Stamina 94 8 in 3 months in 1 month 94% 6%</t>
         </is>
       </c>
     </row>
@@ -11673,12 +11673,12 @@
       </c>
       <c r="CX55" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Max PS 10 Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Max PS 10 Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY55" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Max PS 10 Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Max PS 10 Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ55" t="inlineStr">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="DA55" t="inlineStr">
         <is>
-          <t>Afterburner [SP+ 10] 5 Unlocked by reaching level 10 in the Premium Season Pass. Zézé 91 CB PAC 86 SHO 50 PAS 80 DRI 85 DEF 91 PHY 91 L 3 ★ 4 CB 89.9 Zézé 92 CB PAC 93 SHO 50 PAS 80 DRI 85 DEF 91 PHY 91 L 3 ★ 4 CB 92.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 Max PS 10 UPGRADES +1 OVR 93 +10 PAC 93 8 in 4 months in 1 month 63% 37%</t>
+          <t>Afterburner [SP+ 10] 5 Unlocked by reaching level 10 in the Premium Season Pass. Zézé 91 CB PAC 86 SHO 50 PAS 80 DRI 85 DEF 91 PHY 91 L 3 ★ 4 CB 89.9 Zézé 92 CB PAC 93 SHO 50 PAS 80 DRI 85 DEF 91 PHY 91 L 3 ★ 4 CB 92.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 Max PS 10 UPGRADES +1 OVR 93 +10 PAC 93 8 in 3 months in 1 month 64% 36%</t>
         </is>
       </c>
     </row>
@@ -11832,12 +11832,12 @@
       </c>
       <c r="CX56" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Max PS 10 Max PS+ 3 Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Max PS 10 Max PS+ 3 Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY56" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Max PS 10 Max PS+ 3 Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Max PS 10 Max PS+ 3 Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ56" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="DA56" t="inlineStr">
         <is>
-          <t>No Looking Back [SP+ 18] Unlocked by reaching level 18 in the Premium Season Pass. Marcos Llorente 95 RB PAC 96 SHO 90 PAS 93 DRI 91 DEF 91 PHY 94 RM CM R 5 ★ 5 CM 92.5 Marcos Llorente 95 RB PAC 96 SHO 90 PAS 93 DRI 91 DEF 91 PHY 94 RM CM R 5 ★ 5 CM 93.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max PS 10 Max PS+ 3 UPGRADES 3 8 in 4 months in 1 month 95% 5%</t>
+          <t>No Looking Back [SP+ 18] Unlocked by reaching level 18 in the Premium Season Pass. Marcos Llorente 95 RB PAC 96 SHO 90 PAS 93 DRI 91 DEF 91 PHY 94 RM CM R 5 ★ 5 CM 92.5 Marcos Llorente 95 RB PAC 96 SHO 90 PAS 93 DRI 91 DEF 91 PHY 94 RM CM R 5 ★ 5 CM 93.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max PS 10 Max PS+ 3 UPGRADES 3 8 in 3 months in 1 month 95% 5%</t>
         </is>
       </c>
     </row>
@@ -12083,12 +12083,12 @@
       </c>
       <c r="CX57" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Max PS 10 Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Max PS 10 Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY57" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Max PS 10 Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 92 Max PS 10 Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ57" t="inlineStr">
@@ -12098,7 +12098,7 @@
       </c>
       <c r="DA57" t="inlineStr">
         <is>
-          <t>Covering Ground [SP+ 1] 8 Unlocked by reaching level 1 in the Premium Season Pass. Sithole 90 CDM PAC 90 SHO 80 PAS 87 DRI 87 DEF 90 PHY 92 CM R 4 ★ 4 CM 89.4 Sithole 93 CDM PAC 92 SHO 80 PAS 92 DRI 89 DEF 93 PHY 94 CM R 4 ★ 4 CM 93.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 Max PS 10 UPGRADES +3 OVR 95 +2 Acceleration 93 +2 Sprint Speed 93 +6 Vision 96 +2 Strength 95 +2 Aggression 95 +6 Crossing 95 +6 Short Pass 97 +6 Long Pass 95 +3 Sliding Tackle 94 +2 Jumping 95 +2 Stamina 97 +6 Fk Accuracy 96 +3 Heading Acc. 95 +3 Defensive Awareness 95 +3 Standing Tackle 95 +6 Curve 96 +2 Agility 97 +2 Ball Control 95 +2 Dribbling 94 +3 Interceptions 97 +2 Balance 96 +2 Reactions 96 +2 Composure 96 8 in 4 months in 1 month 95% 5%</t>
+          <t>Covering Ground [SP+ 1] 8 Unlocked by reaching level 1 in the Premium Season Pass. Sithole 90 CDM PAC 90 SHO 80 PAS 87 DRI 87 DEF 90 PHY 92 CM R 4 ★ 4 CM 89.4 Sithole 93 CDM PAC 92 SHO 80 PAS 92 DRI 89 DEF 93 PHY 94 CM R 4 ★ 4 CM 93.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 Max PS 10 UPGRADES +3 OVR 95 +2 Acceleration 93 +2 Sprint Speed 93 +6 Vision 96 +2 Strength 95 +2 Aggression 95 +6 Crossing 95 +6 Short Pass 97 +6 Long Pass 95 +3 Sliding Tackle 94 +2 Jumping 95 +2 Stamina 97 +6 Fk Accuracy 96 +3 Heading Acc. 95 +3 Defensive Awareness 95 +3 Standing Tackle 95 +6 Curve 96 +2 Agility 97 +2 Ball Control 95 +2 Dribbling 94 +3 Interceptions 97 +2 Balance 96 +2 Reactions 96 +2 Composure 96 8 in 3 months in 1 month 95% 5%</t>
         </is>
       </c>
     </row>
@@ -12242,12 +12242,12 @@
       </c>
       <c r="CX58" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 94 Max PS+ 3 Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 94 Max PS+ 3 Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY58" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 94 Max PS+ 3 Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 94 Max PS+ 3 Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ58" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="DA58" t="inlineStr">
         <is>
-          <t>Finesse Shot+ [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Valverde 94 CM PAC 94 SHO 92 PAS 93 DRI 92 DEF 90 PHY 90 RB CDM RM RW R 5 ★ 5 CM 93.3 Valverde 94 CM PAC 94 SHO 92 PAS 93 DRI 92 DEF 90 PHY 90 RB CDM RM RW R 5 ★ 5 CM 94.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 94 Max PS+ 3 UPGRADES 4 in 4 months in 1 month 100% 0%</t>
+          <t>Finesse Shot+ [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Valverde 94 CM PAC 94 SHO 92 PAS 93 DRI 92 DEF 90 PHY 90 RB CDM RM RW R 5 ★ 5 CM 93.3 Valverde 94 CM PAC 94 SHO 92 PAS 93 DRI 92 DEF 90 PHY 90 RB CDM RM RW R 5 ★ 5 CM 94.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 94 Max PS+ 3 UPGRADES 4 in 3 months in 1 month 100% 0%</t>
         </is>
       </c>
     </row>
@@ -12431,12 +12431,12 @@
       </c>
       <c r="CX59" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY59" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ59" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="DA59" t="inlineStr">
         <is>
-          <t>Deadeye [SP 21] 3 Unlocked by reaching level 21 in the Standard Season Pass. Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 85.6 Bobb 89 RW PAC 93 SHO 92 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 LW 90.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 UPGRADES +1 OVR +5 Positioning 93 +5 Shot Power 96 +5 Volleys 93 +5 Penalties +5 Finishing 96 +5 Long Shots 95 3 8 in 4 months in 1 month 90% 10%</t>
+          <t>Deadeye [SP 21] 3 Unlocked by reaching level 21 in the Standard Season Pass. Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 85.6 Bobb 89 RW PAC 93 SHO 92 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 LW 90.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 UPGRADES +1 OVR +5 Positioning 93 +5 Shot Power 96 +5 Volleys 93 +5 Penalties +5 Finishing 96 +5 Long Shots 95 3 8 in 3 months in 1 month 90% 10%</t>
         </is>
       </c>
     </row>
@@ -12479,12 +12479,12 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
@@ -12582,12 +12582,12 @@
       </c>
       <c r="CX60" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY60" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ60" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="DA60" t="inlineStr">
         <is>
-          <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Doué 96 RW PAC 96 SHO 95 PAS 92 DRI 99 DEF 67 PHY 88 RM CM LW R 5 ★ 5 RM 93.5 Doué 96 RW PAC 96 SHO 95 PAS 92 DRI 99 DEF 67 PHY 88 RM CM LW R 5 ★ 5 RM 93.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 4 months in 1 month 57% 43%</t>
+          <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Doué 96 RW PAC 96 SHO 95 PAS 92 DRI 99 DEF 67 PHY 88 RM CM LW R 5 ★ 5 RM 93.5 Doué 96 RW PAC 96 SHO 95 PAS 92 DRI 99 DEF 67 PHY 88 RM CM LW R 5 ★ 5 RM 93.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 3 months in 1 month 57% 43%</t>
         </is>
       </c>
     </row>
@@ -12741,12 +12741,12 @@
       </c>
       <c r="CX61" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 93 Max PS+ 3 Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 93 Max PS+ 3 Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY61" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 93 Max PS+ 3 Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 93 Max PS+ 3 Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ61" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="DA61" t="inlineStr">
         <is>
-          <t>Intercept+ [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Álvarez 93 CDM PAC 90 SHO 80 PAS 87 DRI 91 DEF 95 PHY 93 CM R 4 ★ 4 CM 91.3 Álvarez 93 CDM PAC 90 SHO 80 PAS 87 DRI 91 DEF 93 PHY 93 CM R 4 ★ 4 CM 92.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 93 Max PS+ 3 UPGRADES 4 in 4 months in 1 month 98% 2%</t>
+          <t>Intercept+ [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Álvarez 93 CDM PAC 90 SHO 80 PAS 87 DRI 91 DEF 95 PHY 93 CM R 4 ★ 4 CM 91.3 Álvarez 93 CDM PAC 90 SHO 80 PAS 87 DRI 91 DEF 93 PHY 93 CM R 4 ★ 4 CM 92.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 93 Max PS+ 3 UPGRADES 4 in 3 months in 1 month 98% 2%</t>
         </is>
       </c>
     </row>
@@ -12976,12 +12976,12 @@
       </c>
       <c r="CX62" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CAM, CM, CDM Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CAM, CM, CDM Max PS 10 Max PS+ 2 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY62" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CAM, CM, CDM Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CAM, CM, CDM Max PS 10 Max PS+ 2 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ62" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="DA62" t="inlineStr">
         <is>
-          <t>WTSS Journey 3 - Midfielder [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. Beckenbauer 71 CDM PAC 70 SHO 52 PAS 76 DRI 64 DEF 80 PHY 70 CB CM R 3 ★ 4 CM 67.5 Beckenbauer 92 CDM PAC 90 SHO 81 PAS 93 DRI 92 DEF 89 PHY 90 CB CM R 4 ★ 5 CM 90.2 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CAM, CM, CDM Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +2 PAS 93 +4 WF 5 +5 Finishing 90 +10 Reactions 91 +5 Acceleration 90 +5 Shot Power 91 +10 Balance 92 +10 Ball Control 92 +5 Sprint Speed 90 +5 Long Shots 91 +5 Penalties 88 +10 Dribbling 93 +5 Positioning 90 +5 Volleys 88 +10 Agility 92 +10 Composure 90 3 8 Show less in 2 days in 2 days 84% 16%</t>
+          <t>WTSS Journey 3 - Midfielder [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. Beckenbauer 71 CDM PAC 70 SHO 52 PAS 76 DRI 64 DEF 80 PHY 70 CB CM R 3 ★ 4 CM 67.5 Beckenbauer 92 CDM PAC 90 SHO 81 PAS 93 DRI 92 DEF 89 PHY 90 CB CM R 4 ★ 5 CM 90.2 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CAM, CM, CDM Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +2 PAS 93 +4 WF 5 +5 Finishing 90 +10 Reactions 91 +5 Acceleration 90 +5 Shot Power 91 +10 Balance 92 +10 Ball Control 92 +5 Sprint Speed 90 +5 Long Shots 91 +5 Penalties 88 +10 Dribbling 93 +5 Positioning 90 +5 Volleys 88 +10 Agility 92 +10 Composure 90 3 8 Show less in 23 hours in 23 hours 84% 16%</t>
         </is>
       </c>
     </row>
@@ -13135,12 +13135,12 @@
       </c>
       <c r="CX63" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 2 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY63" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 2 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ63" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="DA63" t="inlineStr">
         <is>
-          <t>Bruiser+ [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 CB 88.7 van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 CB 91.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 2 UPGRADES 3 in 2 days in 2 days 91% 9%</t>
+          <t>Bruiser+ [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 CB 88.7 van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 CB 91.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 2 UPGRADES 3 in 23 hours in 23 hours 91% 9%</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="CX64" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY64" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ64" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="DA64" t="inlineStr">
         <is>
-          <t>Incisive Pass+ [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Frattesi 90 CM PAC 92 SHO 87 PAS 89 DRI 92 DEF 86 PHY 87 CAM R 4 ★ 4 CM 87.4 Frattesi 90 CM PAC 92 SHO 87 PAS 89 DRI 92 DEF 86 PHY 87 CAM R 4 ★ 4 CM 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 UPGRADES 3 in 2 days in 2 days 85% 15%</t>
+          <t>Incisive Pass+ [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Frattesi 90 CM PAC 92 SHO 87 PAS 89 DRI 92 DEF 86 PHY 87 CAM R 4 ★ 4 CM 87.4 Frattesi 90 CM PAC 92 SHO 87 PAS 89 DRI 92 DEF 86 PHY 87 CAM R 4 ★ 4 CM 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 UPGRADES 3 in 23 hours in 23 hours 85% 15%</t>
         </is>
       </c>
     </row>
@@ -13507,12 +13507,12 @@
       </c>
       <c r="CX65" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY65" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ65" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="DA65" t="inlineStr">
         <is>
-          <t>Defender Round Out [SP 1] 10 Unlocked by reaching level 1 in the Standard Season Pass. Timber 88 RB PAC 87 SHO 54 PAS 83 DRI 86 DEF 88 PHY 88 CB LB RM R 4 ★ 5 LB 85.6 Timber 89 RB PAC 92 SHO 54 PAS 83 DRI 87 DEF 89 PHY 91 CB LB RM R 4 ★ 5 LB 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +1 OVR +5 Acceleration 91 +5 Sprint Speed 92 +1 Interceptions 93 +1 Heading Acc. 94 +1 Defensive Awareness 93 +5 Reactions 93 +5 Composure 93 +5 Standing Tackle 91 +5 Sliding Tackle 92 +2 Jumping 93 +2 Stamina 92 +2 Strength 93 +5 Aggression 92 8 in 2 days in 2 days 91% 9%</t>
+          <t>Defender Round Out [SP 1] 10 Unlocked by reaching level 1 in the Standard Season Pass. Timber 88 RB PAC 87 SHO 54 PAS 83 DRI 86 DEF 88 PHY 88 CB LB RM R 4 ★ 5 LB 85.6 Timber 89 RB PAC 92 SHO 54 PAS 83 DRI 87 DEF 89 PHY 91 CB LB RM R 4 ★ 5 LB 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +1 OVR +5 Acceleration 91 +5 Sprint Speed 92 +1 Interceptions 93 +1 Heading Acc. 94 +1 Defensive Awareness 93 +5 Reactions 93 +5 Composure 93 +5 Standing Tackle 91 +5 Sliding Tackle 92 +2 Jumping 93 +2 Stamina 92 +2 Strength 93 +5 Aggression 92 8 in 23 hours in 23 hours 91% 9%</t>
         </is>
       </c>
     </row>
@@ -13754,12 +13754,12 @@
       </c>
       <c r="CX66" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Excluded Position CB Max PS 10 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Excluded Position CB Max PS 10 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY66" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Excluded Position CB Max PS 10 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 89 Excluded Position CB Max PS 10 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ66" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="DA66" t="inlineStr">
         <is>
-          <t>Attacker Round Out [SP+ 1] 20 Unlocked by reaching level 1 in the Premium Season Pass. Carlos Espí 88 ST PAC 91 SHO 86 PAS 80 DRI 88 DEF 58 PHY 94 R 4 ★ 4 ST 86.9 Carlos Espí 90 ST PAC 93 SHO 90 PAS 84 DRI 92 DEF 58 PHY 94 R 4 ★ 4 ST 89.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Excluded Position CB Max PS 10 UPGRADES +2 OVR 91 +3 Acceleration 93 +5 Agility 94 +5 Balance 93 +3 Sprint Speed 94 +5 Long Pass 94 +2 Curve 92 +2 Composure 95 +5 Positioning 93 +5 Finishing 94 +3 Shot Power 93 +2 Reactions 92 +5 Ball Control 94 +3 Long Shots 92 +3 Volleys 94 +3 Penalties 94 +5 Short Pass 95 +5 Dribbling 95 +5 Vision 93 +2 Crossing 94 +2 Fk Accuracy 92 8 in 2 days in 2 days 93% 7%</t>
+          <t>Attacker Round Out [SP+ 1] 20 Unlocked by reaching level 1 in the Premium Season Pass. Carlos Espí 88 ST PAC 91 SHO 86 PAS 80 DRI 88 DEF 58 PHY 94 R 4 ★ 4 ST 86.9 Carlos Espí 90 ST PAC 93 SHO 90 PAS 84 DRI 92 DEF 58 PHY 94 R 4 ★ 4 ST 89.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Excluded Position CB Max PS 10 UPGRADES +2 OVR 91 +3 Acceleration 93 +5 Agility 94 +5 Balance 93 +3 Sprint Speed 94 +5 Long Pass 94 +2 Curve 92 +2 Composure 95 +5 Positioning 93 +5 Finishing 94 +3 Shot Power 93 +2 Reactions 92 +5 Ball Control 94 +3 Long Shots 92 +3 Volleys 94 +3 Penalties 94 +5 Short Pass 95 +5 Dribbling 95 +5 Vision 93 +2 Crossing 94 +2 Fk Accuracy 92 8 in 23 hours in 23 hours 93% 7%</t>
         </is>
       </c>
     </row>
@@ -13989,12 +13989,12 @@
       </c>
       <c r="CX67" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position ST, RW, LW Max PS 10 Max PS+ 1 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position ST, RW, LW Max PS 10 Max PS+ 1 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY67" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position ST, RW, LW Max PS 10 Max PS+ 1 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position ST, RW, LW Max PS 10 Max PS+ 1 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ67" t="inlineStr">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="DA67" t="inlineStr">
         <is>
-          <t>WTSS Journey 2 - Attacker [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Garrincha 70 RW PAC 82 SHO 64 PAS 67 DRI 78 DEF 34 PHY 48 RM R 5 ★ 4 RM 68.5 Garrincha 90 RW PAC 90 SHO 90 PAS 87 DRI 89 DEF 34 PHY 67 RM R 5 ★ 4 RM 86.7 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position ST, RW, LW Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +3 WF 4 +10 Acceleration 90 +10 Sprint Speed 90 +10 Finishing 90 +10 Positioning 90 +10 Volleys 89 +10 Penalties 90 +10 Curve 90 +15 Agility 92 +15 Balance 89 +15 Reactions 89 +10 Shot Power 91 +10 Long Shots 90 +15 Ball Control 88 +15 Dribbling 89 +15 Composure 88 2 8 in 2 days in 2 days 68% 32%</t>
+          <t>WTSS Journey 2 - Attacker [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Garrincha 70 RW PAC 82 SHO 64 PAS 67 DRI 78 DEF 34 PHY 48 RM R 5 ★ 4 RM 68.5 Garrincha 90 RW PAC 90 SHO 90 PAS 87 DRI 89 DEF 34 PHY 67 RM R 5 ★ 4 RM 86.7 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position ST, RW, LW Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +3 WF 4 +10 Acceleration 90 +10 Sprint Speed 90 +10 Finishing 90 +10 Positioning 90 +10 Volleys 89 +10 Penalties 90 +10 Curve 90 +15 Agility 92 +15 Balance 89 +15 Reactions 89 +10 Shot Power 91 +10 Long Shots 90 +15 Ball Control 88 +15 Dribbling 89 +15 Composure 88 2 8 in 23 hours in 23 hours 69% 31%</t>
         </is>
       </c>
     </row>
@@ -14200,12 +14200,12 @@
       </c>
       <c r="CX68" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CB, LB, RB Max PS 10 Max PS+ 1 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CB, LB, RB Max PS 10 Max PS+ 1 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY68" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CB, LB, RB Max PS 10 Max PS+ 1 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CB, LB, RB Max PS 10 Max PS+ 1 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ68" t="inlineStr">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="DA68" t="inlineStr">
         <is>
-          <t>WTSS Journey 2 - Defender [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Koeman 71 CB PAC 70 SHO 72 PAS 71 DRI 68 DEF 82 PHY 73 CDM R 3 ★ 3 CB 62.0 Koeman 90 CB PAC 87 SHO 72 PAS 80 DRI 83 DEF 92 PHY 87 CDM R 4 ★ 4 CB 83.8 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CB, LB, RB Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +2 PAC 87 +5 Agility 88 +5 Balance 88 +5 Reactions 90 +5 Composure 90 +10 Standing Tackle 92 +10 Sliding Tackle 92 +10 Interceptions 93 +10 Heading Acc. 94 +10 Defensive Awareness 90 2 8 in 2 days in 2 days 74% 26%</t>
+          <t>WTSS Journey 2 - Defender [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Koeman 71 CB PAC 70 SHO 72 PAS 71 DRI 68 DEF 82 PHY 73 CDM R 3 ★ 3 CB 62.0 Koeman 90 CB PAC 87 SHO 72 PAS 80 DRI 83 DEF 92 PHY 87 CDM R 4 ★ 4 CB 83.8 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CB, LB, RB Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +2 PAC 87 +5 Agility 88 +5 Balance 88 +5 Reactions 90 +5 Composure 90 +10 Standing Tackle 92 +10 Sliding Tackle 92 +10 Interceptions 93 +10 Heading Acc. 94 +10 Defensive Awareness 90 2 8 in 23 hours in 23 hours 74% 26%</t>
         </is>
       </c>
     </row>
@@ -14413,12 +14413,12 @@
       </c>
       <c r="CX69" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position ST, RW, LW Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position ST, RW, LW Max PS 10 Max PS+ 2 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY69" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position ST, RW, LW Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position ST, RW, LW Max PS 10 Max PS+ 2 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ69" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="DA69" t="inlineStr">
         <is>
-          <t>WTSS Journey 3 - Attacker [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. Garrincha 70 RW PAC 82 SHO 64 PAS 67 DRI 78 DEF 34 PHY 48 RM R 5 ★ 4 RM 68.5 Garrincha 92 RW PAC 92 SHO 92 PAS 87 DRI 93 DEF 34 PHY 67 RM R 5 ★ 4 RM 89.9 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position ST, RW, LW Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +4 SM +5 Acceleration 92 +5 Sprint Speed 92 +5 Positioning 93 +5 Finishing 94 +5 Curve 93 +5 Balance 94 +5 Reactions 93 +5 Ball Control 94 +5 Dribbling 94 +5 Composure 93 3 8 in 2 days in 2 days 72% 28%</t>
+          <t>WTSS Journey 3 - Attacker [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. Garrincha 70 RW PAC 82 SHO 64 PAS 67 DRI 78 DEF 34 PHY 48 RM R 5 ★ 4 RM 68.5 Garrincha 92 RW PAC 92 SHO 92 PAS 87 DRI 93 DEF 34 PHY 67 RM R 5 ★ 4 RM 89.9 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position ST, RW, LW Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +4 SM +5 Acceleration 92 +5 Sprint Speed 92 +5 Positioning 93 +5 Finishing 94 +5 Curve 93 +5 Balance 94 +5 Reactions 93 +5 Ball Control 94 +5 Dribbling 94 +5 Composure 93 3 8 in 23 hours in 23 hours 73% 27%</t>
         </is>
       </c>
     </row>
@@ -14638,12 +14638,12 @@
       </c>
       <c r="CX70" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CB, LB, RB Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CB, LB, RB Max PS 10 Max PS+ 2 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY70" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CB, LB, RB Max PS 10 Max PS+ 2 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CB, LB, RB Max PS 10 Max PS+ 2 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ70" t="inlineStr">
@@ -14653,7 +14653,7 @@
       </c>
       <c r="DA70" t="inlineStr">
         <is>
-          <t>WTSS Journey 3 - Defender [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. Petit 74 CDM PAC 70 SHO 70 PAS 85 DRI 72 DEF 74 PHY 76 LB CM L 3 ★ 3 CM 65.3 Petit 92 CDM PAC 90 SHO 70 PAS 87 DRI 87 DEF 92 PHY 93 LB CM L 4 ★ 5 CM 89.0 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CB, LB, RB Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +3 PAC 90 +3 SM 4 +4 WF +5 Reactions 93 +5 Ball Control 88 +5 Dribbling 88 +5 Composure 93 +5 Vision 88 +5 Short Pass 88 +5 Long Pass 88 +10 Aggression 88 +10 Jumping 90 +10 Stamina 95 +10 Strength 93 3 8 Show less in 2 days in 2 days 75% 25%</t>
+          <t>WTSS Journey 3 - Defender [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. Petit 74 CDM PAC 70 SHO 70 PAS 85 DRI 72 DEF 74 PHY 76 LB CM L 3 ★ 3 CM 65.3 Petit 92 CDM PAC 90 SHO 70 PAS 87 DRI 87 DEF 92 PHY 93 LB CM L 4 ★ 5 CM 89.0 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CB, LB, RB Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +3 PAC 90 +3 SM 4 +4 WF +5 Reactions 93 +5 Ball Control 88 +5 Dribbling 88 +5 Composure 93 +5 Vision 88 +5 Short Pass 88 +5 Long Pass 88 +10 Aggression 88 +10 Jumping 90 +10 Stamina 95 +10 Strength 93 3 8 Show less in 23 hours in 23 hours 76% 24%</t>
         </is>
       </c>
     </row>
@@ -14881,12 +14881,12 @@
       </c>
       <c r="CX71" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CAM, CDM, CM Max PS 10 Max PS+ 1 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CAM, CDM, CM Max PS 10 Max PS+ 1 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY71" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CAM, CDM, CM Max PS 10 Max PS+ 1 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CAM, CDM, CM Max PS 10 Max PS+ 1 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ71" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="DA71" t="inlineStr">
         <is>
-          <t>WTSS Journey 2 - Midfielder [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Petit 74 CDM PAC 70 SHO 70 PAS 85 DRI 72 DEF 74 PHY 76 LB CM L 3 ★ 3 CM 65.3 Petit 90 CDM PAC 88 SHO 74 PAS 92 DRI 83 DEF 89 PHY 89 LB CM L 4 ★ 4 CM 84.9 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CAM, CDM, CM Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +4 SHO 88 +1 SM 4 +5 Sprint Speed 88 +15 Short Pass 93 +15 Interceptions 90 +15 Stamina 90 +5 Acceleration 88 +15 Fk Accuracy 89 +15 Defensive Awareness 89 +15 Strength 89 +15 Vision 91 +15 Long Pass 92 +15 Heading Acc. 89 +15 Sliding Tackle 88 +15 Aggression 89 +15 Crossing 89 +15 Curve 90 +15 Standing Tackle 90 +15 Jumping 89 2 8 Show less in 2 days in 2 days 78% 22%</t>
+          <t>WTSS Journey 2 - Midfielder [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Petit 74 CDM PAC 70 SHO 70 PAS 85 DRI 72 DEF 74 PHY 76 LB CM L 3 ★ 3 CM 65.3 Petit 90 CDM PAC 88 SHO 74 PAS 92 DRI 83 DEF 89 PHY 89 LB CM L 4 ★ 4 CM 84.9 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CAM, CDM, CM Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +4 SHO 88 +1 SM 4 +5 Sprint Speed 88 +15 Short Pass 93 +15 Interceptions 90 +15 Stamina 90 +5 Acceleration 88 +15 Fk Accuracy 89 +15 Defensive Awareness 89 +15 Strength 89 +15 Vision 91 +15 Long Pass 92 +15 Heading Acc. 89 +15 Sliding Tackle 88 +15 Aggression 89 +15 Crossing 89 +15 Curve 90 +15 Standing Tackle 90 +15 Jumping 89 2 8 Show less in 23 hours in 23 hours 78% 22%</t>
         </is>
       </c>
     </row>
@@ -15140,12 +15140,12 @@
       </c>
       <c r="CX72" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Position ST, RW, LW Max PS 10 Max PS+ 1 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Position ST, RW, LW Max PS 10 Max PS+ 1 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY72" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Position ST, RW, LW Max PS 10 Max PS+ 1 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Position ST, RW, LW Max PS 10 Max PS+ 1 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ72" t="inlineStr">
@@ -15155,7 +15155,7 @@
       </c>
       <c r="DA72" t="inlineStr">
         <is>
-          <t>WTSS Journey 1 - Attacker [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Garrincha 70 RW PAC 82 SHO 64 PAS 67 DRI 78 DEF 34 PHY 48 RM R 5 ★ 4 RM 68.5 Garrincha 88 RW PAC 88 SHO 86 PAS 87 DRI 87 DEF 34 PHY 67 RM R 5 ★ 4 RM 81.5 REQUIREMENTS Rarity World Tour Silver Stars Position ST, RW, LW Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +1 SM 4 +1 WF 4 +30 Acceleration 88 +30 Sprint Speed 88 +30 Finishing 87 +30 Shot Power 83 +30 Long Shots 88 +30 Positioning 84 +20 Vision 88 +20 Crossing 87 +20 Fk Accuracy 88 +20 Short Pass 90 +20 Long Pass 88 +30 Volleys 87 +30 Penalties 80 +25 Agility 87 +25 Balance 88 +20 Curve 88 +25 Reactions 86 +25 Ball Control 88 +20 Aggression 70 +25 Dribbling 87 +25 Composure 88 +20 Stamina 90 +20 Strength 75 8 in 2 days in 2 days 79% 21%</t>
+          <t>WTSS Journey 1 - Attacker [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Garrincha 70 RW PAC 82 SHO 64 PAS 67 DRI 78 DEF 34 PHY 48 RM R 5 ★ 4 RM 68.5 Garrincha 88 RW PAC 88 SHO 86 PAS 87 DRI 87 DEF 34 PHY 67 RM R 5 ★ 4 RM 81.5 REQUIREMENTS Rarity World Tour Silver Stars Position ST, RW, LW Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +1 SM 4 +1 WF 4 +30 Acceleration 88 +30 Sprint Speed 88 +30 Finishing 87 +30 Shot Power 83 +30 Long Shots 88 +30 Positioning 84 +20 Vision 88 +20 Crossing 87 +20 Fk Accuracy 88 +20 Short Pass 90 +20 Long Pass 88 +30 Volleys 87 +30 Penalties 80 +25 Agility 87 +25 Balance 88 +20 Curve 88 +25 Reactions 86 +25 Ball Control 88 +20 Aggression 70 +25 Dribbling 87 +25 Composure 88 +20 Stamina 90 +20 Strength 75 8 in 23 hours in 23 hours 79% 21%</t>
         </is>
       </c>
     </row>
@@ -15411,12 +15411,12 @@
       </c>
       <c r="CX73" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Position CAM, CM, CDM Max PS 10 Max PS+ 1 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Position CAM, CM, CDM Max PS 10 Max PS+ 1 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY73" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Position CAM, CM, CDM Max PS 10 Max PS+ 1 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Position CAM, CM, CDM Max PS 10 Max PS+ 1 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ73" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="DA73" t="inlineStr">
         <is>
-          <t>WTSS Journey 1 - Midfielder [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Beckenbauer 71 CDM PAC 70 SHO 52 PAS 76 DRI 64 DEF 80 PHY 70 CB CM R 3 ★ 4 CM 67.5 Beckenbauer 88 CDM PAC 85 SHO 72 PAS 87 DRI 87 DEF 86 PHY 84 CB CM R 4 ★ 4 CM 81.2 REQUIREMENTS Rarity World Tour Silver Stars Position CAM, CM, CDM Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +20 PHY 84 +1 SM 4 +1 WF 4 +30 Acceleration 85 +30 Sprint Speed 85 +30 Curve 86 +30 Agility 86 +30 Balance 84 +20 Positioning 85 +20 Finishing 87 +20 Shot Power 87 +20 Long Shots 90 +20 Volleys 88 +20 Penalties 85 +30 Reactions 87 +30 Ball Control 85 +30 Vision 86 +30 Crossing 85 +30 Fk Accuracy 88 +30 Short Pass 87 +30 Long Pass 88 +30 Heading Acc. 88 +30 Dribbling 88 +30 Composure 88 +30 Interceptions 85 +30 Defensive Awareness 85 +30 Standing Tackle 86 +30 Sliding Tackle 88 8 Show less in 2 days in 2 days 81% 19%</t>
+          <t>WTSS Journey 1 - Midfielder [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Beckenbauer 71 CDM PAC 70 SHO 52 PAS 76 DRI 64 DEF 80 PHY 70 CB CM R 3 ★ 4 CM 67.5 Beckenbauer 88 CDM PAC 85 SHO 72 PAS 87 DRI 87 DEF 86 PHY 84 CB CM R 4 ★ 4 CM 81.2 REQUIREMENTS Rarity World Tour Silver Stars Position CAM, CM, CDM Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +20 PHY 84 +1 SM 4 +1 WF 4 +30 Acceleration 85 +30 Sprint Speed 85 +30 Curve 86 +30 Agility 86 +30 Balance 84 +20 Positioning 85 +20 Finishing 87 +20 Shot Power 87 +20 Long Shots 90 +20 Volleys 88 +20 Penalties 85 +30 Reactions 87 +30 Ball Control 85 +30 Vision 86 +30 Crossing 85 +30 Fk Accuracy 88 +30 Short Pass 87 +30 Long Pass 88 +30 Heading Acc. 88 +30 Dribbling 88 +30 Composure 88 +30 Interceptions 85 +30 Defensive Awareness 85 +30 Standing Tackle 86 +30 Sliding Tackle 88 8 Show less in 23 hours in 23 hours 81% 19%</t>
         </is>
       </c>
     </row>
@@ -15674,12 +15674,12 @@
       </c>
       <c r="CX74" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Position CB, LB, RB Max PS 10 Max PS+ 1 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Position CB, LB, RB Max PS 10 Max PS+ 1 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY74" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Position CB, LB, RB Max PS 10 Max PS+ 1 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Position CB, LB, RB Max PS 10 Max PS+ 1 Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ74" t="inlineStr">
@@ -15689,7 +15689,7 @@
       </c>
       <c r="DA74" t="inlineStr">
         <is>
-          <t>WTSS Journey 1 - Defender [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Petit 74 CDM PAC 70 SHO 70 PAS 85 DRI 72 DEF 74 PHY 76 LB CM L 3 ★ 3 CM 65.3 Petit 88 CDM PAC 85 SHO 70 PAS 86 DRI 83 DEF 87 PHY 87 LB CM L 4 ★ 4 CM 80.9 REQUIREMENTS Rarity World Tour Silver Stars Position CB, LB, RB Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +20 SHO 70 +1 SM 4 +1 WF 4 +30 Curve 80 +15 Agility 80 +30 Defensive Awareness 87 +30 Standing Tackle 88 +30 Sliding Tackle 86 +30 Acceleration 85 +30 Sprint Speed 85 +30 Vision 75 +30 Crossing 75 +30 Fk Accuracy 65 +30 Short Pass 85 +30 Long Pass 80 +15 Balance 80 +30 Reactions 88 +15 Ball Control 85 +30 Jumping 80 +30 Stamina 85 +30 Strength 87 +15 Dribbling 85 +30 Composure 88 +30 Interceptions 88 +30 Heading Acc. 87 +30 Aggression 90 8 Show less in 2 days in 2 days 83% 17%</t>
+          <t>WTSS Journey 1 - Defender [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Petit 74 CDM PAC 70 SHO 70 PAS 85 DRI 72 DEF 74 PHY 76 LB CM L 3 ★ 3 CM 65.3 Petit 88 CDM PAC 85 SHO 70 PAS 86 DRI 83 DEF 87 PHY 87 LB CM L 4 ★ 4 CM 80.9 REQUIREMENTS Rarity World Tour Silver Stars Position CB, LB, RB Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +20 SHO 70 +1 SM 4 +1 WF 4 +30 Curve 80 +15 Agility 80 +30 Defensive Awareness 87 +30 Standing Tackle 88 +30 Sliding Tackle 86 +30 Acceleration 85 +30 Sprint Speed 85 +30 Vision 75 +30 Crossing 75 +30 Fk Accuracy 65 +30 Short Pass 85 +30 Long Pass 80 +15 Balance 80 +30 Reactions 88 +15 Ball Control 85 +30 Jumping 80 +30 Stamina 85 +30 Strength 87 +15 Dribbling 85 +30 Composure 88 +30 Interceptions 88 +30 Heading Acc. 87 +30 Aggression 90 8 Show less in 23 hours in 23 hours 83% 17%</t>
         </is>
       </c>
     </row>
@@ -15722,12 +15722,12 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>World Tour Silver Stars Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>World Tour Silver Stars Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
@@ -15825,12 +15825,12 @@
       </c>
       <c r="CX75" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY75" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ75" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="DA75" t="inlineStr">
         <is>
-          <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Doué 96 RW PAC 96 SHO 95 PAS 92 DRI 99 DEF 67 PHY 88 RM CM LW R 5 ★ 5 RM 93.5 Doué 96 RW PAC 96 SHO 95 PAS 92 DRI 99 DEF 67 PHY 88 RM CM LW R 5 ★ 5 RM 93.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 2 days in 2 days 30% 70%</t>
+          <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Doué 96 RW PAC 96 SHO 95 PAS 92 DRI 99 DEF 67 PHY 88 RM CM LW R 5 ★ 5 RM 93.5 Doué 96 RW PAC 96 SHO 95 PAS 92 DRI 99 DEF 67 PHY 88 RM CM LW R 5 ★ 5 RM 93.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 23 hours in 23 hours 30% 70%</t>
         </is>
       </c>
     </row>
@@ -17165,12 +17165,12 @@
       </c>
       <c r="CX83" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Pace Max. 84 Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Pace Max. 84 Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY83" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Pace Max. 84 Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 82 Pace Max. 84 Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ83" t="inlineStr">
@@ -17180,7 +17180,7 @@
       </c>
       <c r="DA83" t="inlineStr">
         <is>
-          <t>Intro to Rewards EVOs Upgrade your qualified Player's attributes and Overall Rating with this Evolution. Trenskow 74 RM PAC 80 SHO 74 PAS 76 DRI 79 DEF 60 PHY 63 CM RW L 4 ★ 3 RM 72.9 Trenskow 75 RM PAC 80 SHO 76 PAS 78 DRI 80 DEF 60 PHY 63 CM RW L 4 ★ 3 RM 73.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Pace Max. 84 UPGRADES +1 OVR +3 Shot Power 80 +3 Vision 80 +4 Long Shots 80 +3 Volleys 79 +3 Short Pass 80 +4 Fk Accuracy 80 +4 Dribbling 81 +4 Reactions 81 +4 Long Pass 79 in 4 months in 4 months 84% 16%</t>
+          <t>Intro to Rewards EVOs Upgrade your qualified Player's attributes and Overall Rating with this Evolution. Trenskow 74 RM PAC 80 SHO 74 PAS 76 DRI 79 DEF 60 PHY 63 CM RW L 4 ★ 3 RM 72.9 Trenskow 75 RM PAC 80 SHO 76 PAS 78 DRI 80 DEF 60 PHY 63 CM RW L 4 ★ 3 RM 73.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Pace Max. 84 UPGRADES +1 OVR +3 Shot Power 80 +3 Vision 80 +4 Long Shots 80 +3 Volleys 79 +3 Short Pass 80 +4 Fk Accuracy 80 +4 Dribbling 81 +4 Reactions 81 +4 Long Pass 79 in 3 months in 3 months 84% 16%</t>
         </is>
       </c>
     </row>
@@ -17215,7 +17215,7 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ST Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>ST Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="J84" t="inlineStr"/>
@@ -17328,12 +17328,12 @@
       </c>
       <c r="CX84" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 83 Position ST Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 83 Position ST Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY84" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Overall Max. 83 Position ST Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Overall Max. 83 Position ST Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ84" t="inlineStr">
@@ -17343,7 +17343,7 @@
       </c>
       <c r="DA84" t="inlineStr">
         <is>
-          <t>Club Member Reward Unlocked by being a Club Member on FC 26. Amaiur Sarriegi 81 ST PAC 88 SHO 78 PAS 75 DRI 84 DEF 47 PHY 81 RM RW LW R 4 ★ 4 RW 77.7 Amaiur Sarriegi 81 ST PAC 88 SHO 78 PAS 75 DRI 84 DEF 47 PHY 81 RM RW LW R 4 ★ 4 ST 78.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 83 Position ST UPGRADES ST Advanced Forward + ST Poacher + ST False 9 + ST Target Forward + in 4 months in 4 months 90% 10%</t>
+          <t>Club Member Reward Unlocked by being a Club Member on FC 26. Amaiur Sarriegi 81 ST PAC 88 SHO 78 PAS 75 DRI 84 DEF 47 PHY 81 RM RW LW R 4 ★ 4 RW 77.7 Amaiur Sarriegi 81 ST PAC 88 SHO 78 PAS 75 DRI 84 DEF 47 PHY 81 RM RW LW R 4 ★ 4 ST 78.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 83 Position ST UPGRADES ST Advanced Forward + ST Poacher + ST False 9 + ST Target Forward + in 3 months in 3 months 90% 10%</t>
         </is>
       </c>
     </row>
@@ -53194,12 +53194,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 21 days Token Cost 15</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 20 days Token Cost 15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 21 days Token Cost 15</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 20 days Token Cost 15</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -53241,12 +53241,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 21 days Token Cost 15</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 20 days Token Cost 15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 21 days Token Cost 15</t>
+          <t>Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 20 days Token Cost 15</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -54933,12 +54933,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 24 days Token Cost 25</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 23 days Token Cost 25</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 24 days Token Cost 25</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 23 days Token Cost 25</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -54980,12 +54980,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 24 days Token Cost 25</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 23 days Token Cost 25</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 24 days Token Cost 25</t>
+          <t>Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 23 days Token Cost 25</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -55027,12 +55027,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 24 days Token Cost 25</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 23 days Token Cost 25</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 24 days Token Cost 25</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 23 days Token Cost 25</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -55074,12 +55074,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 24 days Token Cost 25</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 23 days Token Cost 25</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 24 days Token Cost 25</t>
+          <t>Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 23 days Token Cost 25</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -56672,12 +56672,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>GK Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>GK Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Position GK Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>Position GK Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -60291,12 +60291,12 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 12 days Token Cost 15</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 11 days Token Cost 15</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 12 days Token Cost 15</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 11 days Token Cost 15</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -60338,12 +60338,12 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 12 days Token Cost 15</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 11 days Token Cost 15</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 12 days Token Cost 15</t>
+          <t>Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 11 days Token Cost 15</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -64427,12 +64427,12 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -64474,12 +64474,12 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>World Tour Silver Stars Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Details Submit by in 4 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Details Submit by in 3 months Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -67811,12 +67811,12 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>World Tour Silver Stars Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Rarity World Tour Silver Stars Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -67858,12 +67858,12 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>World Tour Silver Stars Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>World Tour Silver Stars Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Rarity World Tour Silver Stars Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity World Tour Silver Stars Details Submit by in 22 hours Expiry in 22 hours Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -69503,12 +69503,12 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>ST Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>ST Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Position ST Details Submit by in 4 months Expiry in 4 months Coins Cost Free Points Cost Free</t>
+          <t>Position ST Details Submit by in 3 months Expiry in 3 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -69685,12 +69685,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>No Payne No Gain NEW</t>
+          <t>No Payne No Gain</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>No Payne No Gain NEW The best right backs are unsung until they’re not. Evolve your player and bring the commitment that turned the world’s attention to Tim Payne. Kimmich 90 CDM PAC 82 SHO 75 PAS 90 DRI 86 DEF 85 PHY 83 RB CM R 3 ★ 4 RB 79.2 Kimmich 94 CDM PAC 93 SHO 75 PAS 95 DRI 86 DEF 95 PHY 83 RB RM CM R 3 ★ 4 CDM 87.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max Pos. 5 Overall Max. 90 Position RB Excluded Position CB, ST Max PS 10 Max PS+ 3 UPGRADES +15 OVR 94 RM +15 Acceleration 93 +15 Sprint Speed 93 +15 Crossing 95 +15 Fk Accuracy 95 +15 Short Pass 95 +15 Long Pass 95 +15 Curve 95 +15 Vision 95 +15 Interceptions 96 +15 Heading Acc. 96 +15 Defensive Awareness 96 +15 Standing Tackle 95 +15 Sliding Tackle 95 RB Fullback ++ RM Inside Forward ++ 3 8 in 10 days in 17 days 51% 49%</t>
+          <t>No Payne No Gain The best right backs are unsung until they’re not. Evolve your player and bring the commitment that turned the world’s attention to Tim Payne. Kimmich 90 CDM PAC 82 SHO 75 PAS 90 DRI 86 DEF 85 PHY 83 RB CM R 3 ★ 4 RB 79.2 Kimmich 94 CDM PAC 93 SHO 75 PAS 95 DRI 86 DEF 95 PHY 83 RB RM CM R 3 ★ 4 CDM 87.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max Pos. 5 Overall Max. 90 Position RB Excluded Position CB, ST Max PS 10 Max PS+ 3 UPGRADES +15 OVR 94 RM +15 Acceleration 93 +15 Sprint Speed 93 +15 Crossing 95 +15 Fk Accuracy 95 +15 Short Pass 95 +15 Long Pass 95 +15 Curve 95 +15 Vision 95 +15 Interceptions 96 +15 Heading Acc. 96 +15 Defensive Awareness 96 +15 Standing Tackle 95 +15 Sliding Tackle 95 RB Fullback ++ RM Inside Forward ++ 3 8 in 9 days in 16 days 52% 48%</t>
         </is>
       </c>
     </row>
@@ -69717,7 +69717,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Woodsy's Way Some strikers make every chance count no matter the stage. Evolve your striker and bring the clinical instinct that made Chris Wood a Premier League great. Dumornay 90 ST PAC 96 SHO 89 PAS 84 DRI 90 DEF 65 PHY 78 CAM R 4 ★ 4 ST 85.9 Dumornay 93 ST PAC 96 SHO 94 PAS 89 DRI 90 DEF 65 PHY 91 CAM R 4 ★ 5 ST 90.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position ST Max PS 10 Max PS+ 3 UPGRADES +15 OVR 93 +4 WF +15 Positioning 95 +15 Finishing 95 +15 Shot Power 94 +15 Long Shots 94 +15 Volleys 95 +15 Penalties 95 +15 Vision 93 +15 Short Pass 93 +15 Long Pass 93 +15 Jumping 96 +15 Stamina 95 +15 Strength 96 +15 Aggression 95 ST Advanced Forward ++ ST Target Forward ++ 3 8 in 9 days in 16 days 16% 84%</t>
+          <t>Woodsy's Way Some strikers make every chance count no matter the stage. Evolve your striker and bring the clinical instinct that made Chris Wood a Premier League great. Dumornay 90 ST PAC 96 SHO 89 PAS 84 DRI 90 DEF 65 PHY 78 CAM R 4 ★ 4 ST 85.9 Dumornay 93 ST PAC 96 SHO 94 PAS 89 DRI 90 DEF 65 PHY 91 CAM R 4 ★ 5 ST 90.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position ST Max PS 10 Max PS+ 3 UPGRADES +15 OVR 93 +4 WF +15 Positioning 95 +15 Finishing 95 +15 Shot Power 94 +15 Long Shots 94 +15 Volleys 95 +15 Penalties 95 +15 Vision 93 +15 Short Pass 93 +15 Long Pass 93 +15 Jumping 96 +15 Stamina 95 +15 Strength 96 +15 Aggression 95 ST Advanced Forward ++ ST Target Forward ++ 3 8 in 8 days in 15 days 16% 84%</t>
         </is>
       </c>
     </row>
@@ -69744,7 +69744,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Complete Connection 100,000 500 Connect your squad's defense and attack by bolstering your Central Midfielder's skills, allowing them to deliver more accurate passes and increase team possession. Matthäus 91 CM PAC 90 SHO 88 PAS 90 DRI 84 DEF 92 PHY 85 CB CDM R 5 ★ 5 CM 86.7 Matthäus 95 CM PAC 90 SHO 88 PAS 96 DRI 96 DEF 96 PHY 85 CB CDM R 5 ★ 5 CM 92.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CM Max PS 10 Max PS+ 3 UPGRADES +30 OVR 95 +4 WF +30 Vision 96 +30 Crossing 95 +30 Fk Accuracy 95 +30 Interceptions 96 +30 Heading Acc. 96 +30 Defensive Awareness 96 +30 Standing Tackle 96 +30 Sliding Tackle 97 +30 Short Pass 96 +30 Long Pass 96 +30 Curve 96 +30 Composure 94 +30 Agility 96 +30 Balance 96 +30 Reactions 95 +30 Ball Control 96 +30 Dribbling 96 3 8 in 8 days in 15 days 80% 20%</t>
+          <t>Complete Connection 100,000 500 Connect your squad's defense and attack by bolstering your Central Midfielder's skills, allowing them to deliver more accurate passes and increase team possession. Matthäus 91 CM PAC 90 SHO 88 PAS 90 DRI 84 DEF 92 PHY 85 CB CDM R 5 ★ 5 CM 86.7 Matthäus 95 CM PAC 90 SHO 88 PAS 96 DRI 96 DEF 96 PHY 85 CB CDM R 5 ★ 5 CM 92.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CM Max PS 10 Max PS+ 3 UPGRADES +30 OVR 95 +4 WF +30 Vision 96 +30 Crossing 95 +30 Fk Accuracy 95 +30 Interceptions 96 +30 Heading Acc. 96 +30 Defensive Awareness 96 +30 Standing Tackle 96 +30 Sliding Tackle 97 +30 Short Pass 96 +30 Long Pass 96 +30 Curve 96 +30 Composure 94 +30 Agility 96 +30 Balance 96 +30 Reactions 95 +30 Ball Control 96 +30 Dribbling 96 3 8 in 7 days in 14 days 80% 20%</t>
         </is>
       </c>
     </row>
@@ -69771,7 +69771,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Build your own FUT Birthday [Store] Unlocked by purchasing the Historical Birthday Cosmetic EVO Pack from the store (325,000 coins or 800 FC Points) João Cancelo 91 RB PAC 92 SHO 82 PAS 92 DRI 92 DEF 90 PHY 99 LB RM R 5 ★ 4 LB 91.8 João Cancelo 91 RB PAC 92 SHO 82 PAS 92 DRI 92 DEF 90 PHY 99 LB RM R 5 ★ 4 LB 91.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 UPGRADES No upgrades in 11 days in 11 days 81% 19%</t>
+          <t>Build your own FUT Birthday [Store] Unlocked by purchasing the Historical Birthday Cosmetic EVO Pack from the store (325,000 coins or 800 FC Points) João Cancelo 91 RB PAC 92 SHO 82 PAS 92 DRI 92 DEF 90 PHY 99 LB RM R 5 ★ 4 LB 91.8 João Cancelo 91 RB PAC 92 SHO 82 PAS 92 DRI 92 DEF 90 PHY 99 LB RM R 5 ★ 4 LB 91.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 UPGRADES No upgrades in 10 days in 10 days 80% 20%</t>
         </is>
       </c>
     </row>
@@ -69798,7 +69798,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shadow Step 2 Evolve your player and bring the pace and defensive qualities that made the Shadow chemistry style a fan favourite. Katić 90 CB PAC 86 SHO 45 PAS 80 DRI 82 DEF 89 PHY 91 R 3 ★ 4 CB 88.6 Katić 91 CB PAC 92 SHO 45 PAS 80 DRI 82 DEF 95 PHY 91 R 3 ★ 4 CB 92.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 UPGRADES +1 OVR 91 +7 Acceleration 93 +7 Sprint Speed 93 +7 Interceptions 95 +7 Heading Acc. 94 +7 Defensive Awareness 95 +7 Standing Tackle 95 +7 Sliding Tackle 94 3 in 7 days in 14 days 63% 37%</t>
+          <t>Shadow Step 2 Evolve your player and bring the pace and defensive qualities that made the Shadow chemistry style a fan favourite. Katić 90 CB PAC 86 SHO 45 PAS 80 DRI 82 DEF 89 PHY 91 R 3 ★ 4 CB 88.6 Katić 91 CB PAC 92 SHO 45 PAS 80 DRI 82 DEF 95 PHY 91 R 3 ★ 4 CB 92.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 UPGRADES +1 OVR 91 +7 Acceleration 93 +7 Sprint Speed 93 +7 Interceptions 95 +7 Heading Acc. 94 +7 Defensive Awareness 95 +7 Standing Tackle 95 +7 Sliding Tackle 94 3 in 6 days in 13 days 64% 36%</t>
         </is>
       </c>
     </row>
@@ -69825,7 +69825,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Path to Glory 15 Transform your favourite player into a Path to Glory player. This item rarity offers five nation links to chemistry! REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 4 months in 21 days 80% 20%</t>
+          <t>Path to Glory 15 Transform your favourite player into a Path to Glory player. This item rarity offers five nation links to chemistry! REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 3 months in 20 days 81% 19%</t>
         </is>
       </c>
     </row>
@@ -69852,7 +69852,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Go on Son 2 The best finishers never give defenders an easy choice. Evolve your player and develop the two footed-threat that defined Son’s game. Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 85.6 Bobb 89 RW PAC 93 SHO 94 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 5 LW 90.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 UPGRADES +1 OVR 92 +4 WF +7 Positioning 94 +7 Finishing 95 +7 Shot Power 94 +7 Long Shots 94 +7 Volleys 93 +7 Penalties 93 3 8 in 6 days in 13 days 89% 11%</t>
+          <t>Go on Son 2 The best finishers never give defenders an easy choice. Evolve your player and develop the two footed-threat that defined Son’s game. Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 85.6 Bobb 89 RW PAC 93 SHO 94 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 5 LW 90.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 UPGRADES +1 OVR 92 +4 WF +7 Positioning 94 +7 Finishing 95 +7 Shot Power 94 +7 Long Shots 94 +7 Volleys 93 +7 Penalties 93 3 8 in 5 days in 12 days 89% 11%</t>
         </is>
       </c>
     </row>
@@ -69879,7 +69879,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hold the Fort 75,000 350 Every great defence needs a cornerstone. Evolve your player and build the qualities that make every backline unshakeable. Carragher 89 CB PAC 85 SHO 55 PAS 80 DRI 85 DEF 90 PHY 90 RB LB R 3 ★ 4 CB 87.3 Carragher 94 CB PAC 90 SHO 55 PAS 86 DRI 85 DEF 95 PHY 95 RB LB R 3 ★ 4 CB 92.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CB Max PS 10 Max PS+ 3 UPGRADES +20 OVR 94 +20 Acceleration 90 +20 Sprint Speed 90 +20 Short Pass 92 +20 Long Pass 92 +20 Interceptions 95 +20 Heading Acc. 95 +20 Vision 92 +20 Defensive Awareness 95 +20 Standing Tackle 96 +20 Sliding Tackle 96 +20 Jumping 95 +20 Stamina 94 +20 Strength 95 +20 Aggression 95 CB Defender ++ CB Ball Playing Defender ++ 3 8 in 6 days in 13 days 82% 18%</t>
+          <t>Hold the Fort 75,000 350 Every great defence needs a cornerstone. Evolve your player and build the qualities that make every backline unshakeable. Carragher 89 CB PAC 85 SHO 55 PAS 80 DRI 85 DEF 90 PHY 90 RB LB R 3 ★ 4 CB 87.3 Carragher 94 CB PAC 90 SHO 55 PAS 86 DRI 85 DEF 95 PHY 95 RB LB R 3 ★ 4 CB 92.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CB Max PS 10 Max PS+ 3 UPGRADES +20 OVR 94 +20 Acceleration 90 +20 Sprint Speed 90 +20 Short Pass 92 +20 Long Pass 92 +20 Interceptions 95 +20 Heading Acc. 95 +20 Vision 92 +20 Defensive Awareness 95 +20 Standing Tackle 96 +20 Sliding Tackle 96 +20 Jumping 95 +20 Stamina 94 +20 Strength 95 +20 Aggression 95 CB Defender ++ CB Ball Playing Defender ++ 3 8 in 5 days in 12 days 82% 18%</t>
         </is>
       </c>
     </row>
@@ -69906,7 +69906,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>La Pulga From the streets of Rosario to the pinnacle of the game. Evolve your player and unlock the complete game that made Messi untouchable. Munetsi 84 CDM PAC 80 SHO 78 PAS 80 DRI 83 DEF 84 PHY 87 CM CAM RW R 3 ★ 4 CM 78.9 Munetsi 93 CDM PAC 95 SHO 89 PAS 90 DRI 94 DEF 84 PHY 87 CM CAM RW R 5 ★ 4 CM 91.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +20 OVR 93 +4 SM +20 Acceleration 95 +20 Sprint Speed 95 +20 Positioning 94 +20 Finishing 94 +20 Shot Power 94 +20 Volleys 94 +20 Crossing 94 +20 Short Pass 93 +20 Long Pass 93 +20 Curve 95 +20 Agility 96 +20 Balance 94 +20 Reactions 95 +20 Ball Control 95 +20 Vision 94 +20 Dribbling 95 +20 Composure 94 3 8 in 5 days in 12 days 91% 9%</t>
+          <t>La Pulga From the streets of Rosario to the pinnacle of the game. Evolve your player and unlock the complete game that made Messi untouchable. Munetsi 84 CDM PAC 80 SHO 78 PAS 80 DRI 83 DEF 84 PHY 87 CM CAM RW R 3 ★ 4 CM 78.9 Munetsi 93 CDM PAC 95 SHO 89 PAS 90 DRI 94 DEF 84 PHY 87 CM CAM RW R 5 ★ 4 CM 91.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Position RM, RW Max PS 10 Max PS+ 2 UPGRADES +20 OVR 93 +4 SM +20 Acceleration 95 +20 Sprint Speed 95 +20 Positioning 94 +20 Finishing 94 +20 Shot Power 94 +20 Volleys 94 +20 Crossing 94 +20 Short Pass 93 +20 Long Pass 93 +20 Curve 95 +20 Agility 96 +20 Balance 94 +20 Reactions 95 +20 Ball Control 95 +20 Vision 94 +20 Dribbling 95 +20 Composure 94 3 8 in 4 days in 11 days 91% 9%</t>
         </is>
       </c>
     </row>
@@ -69933,7 +69933,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Backbone Brilliance 3 Every great team is built on a solid backbone. Evolve your player and develop the qualities that hold your squad together Álvaro Carreras 90 LB PAC 92 SHO 76 PAS 87 DRI 90 DEF 87 PHY 90 LM L 4 ★ 4 LB 87.1 Álvaro Carreras 91 LB PAC 92 SHO 76 PAS 90 DRI 90 DEF 91 PHY 93 LM L 4 ★ 4 LB 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 2 UPGRADES +1 OVR +5 Vision 95 +5 Short Pass 95 +5 Long Pass 95 +5 Interceptions 95 +5 Defensive Awareness 94 +5 Standing Tackle 94 +5 Stamina 94 +5 Strength 95 +5 Aggression 94 in 4 days in 11 days 62% 38%</t>
+          <t>Backbone Brilliance 3 Every great team is built on a solid backbone. Evolve your player and develop the qualities that hold your squad together Álvaro Carreras 90 LB PAC 92 SHO 76 PAS 87 DRI 90 DEF 87 PHY 90 LM L 4 ★ 4 LB 87.1 Álvaro Carreras 91 LB PAC 92 SHO 76 PAS 90 DRI 90 DEF 91 PHY 93 LM L 4 ★ 4 LB 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 2 UPGRADES +1 OVR +5 Vision 95 +5 Short Pass 95 +5 Long Pass 95 +5 Interceptions 95 +5 Defensive Awareness 94 +5 Standing Tackle 94 +5 Stamina 94 +5 Strength 95 +5 Aggression 94 in 3 days in 10 days 62% 38%</t>
         </is>
       </c>
     </row>
@@ -69960,7 +69960,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Free Kick Mastery 2 The best free kick takers make it look inevitable. Evolve your player and master the art of the dead ball. Amaiur Sarriegi 89 ST PAC 94 SHO 88 PAS 86 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 ST 88.4 Amaiur Sarriegi 90 ST PAC 94 SHO 89 PAS 89 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 RM 88.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 2 UPGRADES +1 OVR +20 Shot Power 95 +20 Crossing 95 +20 Fk Accuracy +20 Curve 95 3 in 3 days in 10 days 12% 88%</t>
+          <t>Free Kick Mastery 2 The best free kick takers make it look inevitable. Evolve your player and master the art of the dead ball. Amaiur Sarriegi 89 ST PAC 94 SHO 88 PAS 86 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 ST 88.4 Amaiur Sarriegi 90 ST PAC 94 SHO 89 PAS 89 DRI 92 DEF 56 PHY 89 RM RW LW R 4 ★ 4 RM 88.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 2 UPGRADES +1 OVR +20 Shot Power 95 +20 Crossing 95 +20 Fk Accuracy +20 Curve 95 3 in 2 days in 9 days 12% 88%</t>
         </is>
       </c>
     </row>
@@ -69987,7 +69987,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Final Preparations Fine-tune every detail before the biggest stage, and prepare for the path that lies ahead. Trincão 90 CAM PAC 91 SHO 91 PAS 89 DRI 94 DEF 49 PHY 85 RM RW ST L 4 ★ 3 RM 87.6 Trincão 92 CAM PAC 93 SHO 93 PAS 91 DRI 95 DEF 51 PHY 87 RM RW ST L 5 ★ 5 RM 90.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 UPGRADES +2 OVR +2 PAC 95 +2 SHO 95 +2 PAS 95 +2 DRI 95 +2 DEF 95 +2 PHY 95 +4 SM 5 +4 WF 5 TRAINING TIME 2 days in 3 days in 10 days 90% 10%</t>
+          <t>Final Preparations Fine-tune every detail before the biggest stage, and prepare for the path that lies ahead. Trincão 90 CAM PAC 91 SHO 91 PAS 89 DRI 94 DEF 49 PHY 85 RM RW ST L 4 ★ 3 RM 87.6 Trincão 92 CAM PAC 93 SHO 93 PAS 91 DRI 95 DEF 51 PHY 87 RM RW ST L 5 ★ 5 RM 90.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 UPGRADES +2 OVR +2 PAC 95 +2 SHO 95 +2 PAS 95 +2 DRI 95 +2 DEF 95 +2 PHY 95 +4 SM 5 +4 WF 5 TRAINING TIME 2 days in 2 days in 9 days 90% 10%</t>
         </is>
       </c>
     </row>
@@ -70014,7 +70014,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hawk Eye 50,000 250 Fast, powerful, and clinical. Evolve your player and unlock the attributes that made the Hawk chemistry style iconic. Kohler 91 CB PAC 84 SHO 54 PAS 85 DRI 80 DEF 93 PHY 92 R 3 ★ 4 CB 87.5 Kohler 93 CB PAC 93 SHO 73 PAS 85 DRI 80 DEF 93 PHY 95 R 3 ★ 4 CB 92.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 UPGRADES +20 OVR 93 +20 Acceleration 93 +20 Sprint Speed 93 +20 Positioning 95 +20 Finishing 95 +20 Shot Power 95 +20 Long Shots 95 +20 Volleys 96 +20 Jumping 95 +20 Stamina 95 +20 Strength 95 +20 Aggression 95 3 8 in 2 days in 9 days 75% 25%</t>
+          <t>Hawk Eye 50,000 250 Fast, powerful, and clinical. Evolve your player and unlock the attributes that made the Hawk chemistry style iconic. Kohler 91 CB PAC 84 SHO 54 PAS 85 DRI 80 DEF 93 PHY 92 R 3 ★ 4 CB 87.5 Kohler 93 CB PAC 93 SHO 73 PAS 85 DRI 80 DEF 93 PHY 95 R 3 ★ 4 CB 92.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 Max PS+ 2 UPGRADES +20 OVR 93 +20 Acceleration 93 +20 Sprint Speed 93 +20 Positioning 95 +20 Finishing 95 +20 Shot Power 95 +20 Long Shots 95 +20 Volleys 96 +20 Jumping 95 +20 Stamina 95 +20 Strength 95 +20 Aggression 95 3 8 in 22 hours in 8 days 75% 25%</t>
         </is>
       </c>
     </row>
@@ -70041,7 +70041,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FC Champions Excellence 25 4 Show off your FC Champions Excellence! Give your favourite player a luxurious new look to showcase their elite status at your club. REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 4 months in 24 days 28% 72%</t>
+          <t>FC Champions Excellence 25 4 Show off your FC Champions Excellence! Give your favourite player a luxurious new look to showcase their elite status at your club. REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 3 months in 23 days 28% 72%</t>
         </is>
       </c>
     </row>
@@ -70068,7 +70068,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FC Champions Excellence 25 4 Show off your FC Champions Excellence! Give your favourite player a luxurious new look to showcase their elite status at your club. REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 4 months in 24 days 29% 71%</t>
+          <t>FC Champions Excellence 25 4 Show off your FC Champions Excellence! Give your favourite player a luxurious new look to showcase their elite status at your club. REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 3 months in 23 days 29% 71%</t>
         </is>
       </c>
     </row>
@@ -70284,7 +70284,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Star in Motion Celebrate Jamal Musiala’s rise to football’s elite. Step into the spotlight with enhanced creativity, flair, and precision that define the face of the game’s new generation. Dunn 82 CM PAC 85 SHO 76 PAS 80 DRI 82 DEF 75 PHY 79 LB RM CAM R 4 ★ 4 RM 74.9 Dunn 86 CM PAC 85 SHO 82 PAS 82 DRI 88 DEF 75 PHY 79 LB RM CAM R 5 ★ 4 CAM 80.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 85 Position CAM Max PS 10 Max PS+ 1 Pace Max. 85 UPGRADES +10 OVR 86 +25 PAC 80 +10 SHO 82 +10 DRI 88 +5 DEF 60 +10 PAS 82 +4 SM +15 Jumping 80 +20 Stamina 80 +15 Aggression 65 +15 Strength 70 CAM Shadow Striker ++ CAM Half Winger + 1 6 Show less in 4 months in 4 months 90% 10%</t>
+          <t>Star in Motion Celebrate Jamal Musiala’s rise to football’s elite. Step into the spotlight with enhanced creativity, flair, and precision that define the face of the game’s new generation. Dunn 82 CM PAC 85 SHO 76 PAS 80 DRI 82 DEF 75 PHY 79 LB RM CAM R 4 ★ 4 RM 74.9 Dunn 86 CM PAC 85 SHO 82 PAS 82 DRI 88 DEF 75 PHY 79 LB RM CAM R 5 ★ 4 CAM 80.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 85 Position CAM Max PS 10 Max PS+ 1 Pace Max. 85 UPGRADES +10 OVR 86 +25 PAC 80 +10 SHO 82 +10 DRI 88 +5 DEF 60 +10 PAS 82 +4 SM +15 Jumping 80 +20 Stamina 80 +15 Aggression 65 +15 Strength 70 CAM Shadow Striker ++ CAM Half Winger + 1 6 Show less in 3 months in 3 months 90% 10%</t>
         </is>
       </c>
     </row>
@@ -70311,7 +70311,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs I Assign a GK to Training Camp Evolutions through the Companion App. When the training session concludes, collect their earned upgrades. Casteels 82 GK DIV 82 HAN 79 KIC 74 REF 85 SPD 45 POS 83 L 1 ★ 2 GK 76.7 Casteels 82 GK DIV 82 HAN 79 KIC 74 REF 85 SPD 45 POS 83 L 1 ★ 2 GK 76.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Position GK UPGRADES GK Sweeper Keeper + TRAINING TIME 1 day in 4 months in 4 months 69% 31%</t>
+          <t>Intro to Training Camp EVOs I Assign a GK to Training Camp Evolutions through the Companion App. When the training session concludes, collect their earned upgrades. Casteels 82 GK DIV 82 HAN 79 KIC 74 REF 85 SPD 45 POS 83 L 1 ★ 2 GK 76.7 Casteels 82 GK DIV 82 HAN 79 KIC 74 REF 85 SPD 45 POS 83 L 1 ★ 2 GK 76.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Position GK UPGRADES GK Sweeper Keeper + TRAINING TIME 1 day in 3 months in 3 months 69% 31%</t>
         </is>
       </c>
     </row>
@@ -70338,7 +70338,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs II Assign a Player to Training Camp Evolutions through the Companion App. When the training session concludes, collect their earned upgrades. Dunn 82 CM PAC 85 SHO 76 PAS 80 DRI 82 DEF 75 PHY 79 LB RM CAM R 4 ★ 4 RM 74.9 Dunn 82 CM PAC 85 SHO 76 PAS 80 DRI 82 DEF 75 PHY 79 LB RM CAM R 4 ★ 4 RM 76.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Max PS 3 UPGRADES 4 TRAINING TIME 1 day in 4 months in 4 months 75% 25%</t>
+          <t>Intro to Training Camp EVOs II Assign a Player to Training Camp Evolutions through the Companion App. When the training session concludes, collect their earned upgrades. Dunn 82 CM PAC 85 SHO 76 PAS 80 DRI 82 DEF 75 PHY 79 LB RM CAM R 4 ★ 4 RM 74.9 Dunn 82 CM PAC 85 SHO 76 PAS 80 DRI 82 DEF 75 PHY 79 LB RM CAM R 4 ★ 4 RM 76.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Max PS 3 UPGRADES 4 TRAINING TIME 1 day in 3 months in 3 months 75% 25%</t>
         </is>
       </c>
     </row>
@@ -70365,7 +70365,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Intro to Evolutions 2 Welcome to FC 26! Kick things off by exploring Evolutions, where you can upgrade Players over time until they reach their stated maximum. Laurienté 80 LW PAC 91 SHO 77 PAS 74 DRI 83 DEF 36 PHY 57 LM R 4 ★ 3 LM 76.5 Laurienté 81 LW PAC 91 SHO 78 PAS 74 DRI 83 DEF 36 PHY 57 LM R 4 ★ 3 LM 76.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 81 UPGRADES +1 OVR 82 +1 PAC 83 +1 SHO 83 in 4 months in 4 months 79% 21%</t>
+          <t>Intro to Evolutions 2 Welcome to FC 26! Kick things off by exploring Evolutions, where you can upgrade Players over time until they reach their stated maximum. Laurienté 80 LW PAC 91 SHO 77 PAS 74 DRI 83 DEF 36 PHY 57 LM R 4 ★ 3 LM 76.5 Laurienté 81 LW PAC 91 SHO 78 PAS 74 DRI 83 DEF 36 PHY 57 LM R 4 ★ 3 LM 76.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 81 UPGRADES +1 OVR 82 +1 PAC 83 +1 SHO 83 in 3 months in 3 months 79% 21%</t>
         </is>
       </c>
     </row>
@@ -70392,7 +70392,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>National Pride Unlocked by completing the Triple Crown task in the Festival of Football Gauntlet objective Lee Kang In 92 RW PAC 96 SHO 92 PAS 93 DRI 96 DEF 62 PHY 82 RM CM L 4 ★ 4 RM 91.2 Lee Kang In 92 RW PAC 96 SHO 92 PAS 93 DRI 96 DEF 62 PHY 82 RM CM L 4 ★ 4 RM 91.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 UPGRADES No upgrades in 10 days in 10 days 88% 13%</t>
+          <t>National Pride Unlocked by completing the Triple Crown task in the Festival of Football Gauntlet objective Lee Kang In 92 RW PAC 96 SHO 92 PAS 93 DRI 96 DEF 62 PHY 82 RM CM L 4 ★ 4 RM 91.2 Lee Kang In 92 RW PAC 96 SHO 92 PAS 93 DRI 96 DEF 62 PHY 82 RM CM L 4 ★ 4 RM 91.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 UPGRADES No upgrades in 9 days in 9 days 88% 12%</t>
         </is>
       </c>
     </row>
@@ -70419,7 +70419,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tiny Tim Unlocked by completing the Tiny Tim task in the Perfect Volley objective Nico Williams 89 LM PAC 95 SHO 80 PAS 85 DRI 89 DEF 40 PHY 75 RM ST LW R 5 ★ 4 RM 83.8 Nico Williams 93 LM PAC 95 SHO 93 PAS 88 DRI 92 DEF 43 PHY 94 RM ST LW R 5 ★ 5 RM 91.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max Pos. 4 Overall Max. 91 Position ST Max PS 10 Max PS+ 3 UPGRADES +25 OVR 93 LM RM +4 WF 5 +35 Finishing 95 +35 Volleys 96 +35 Reactions 95 +40 Aggression 97 +15 Acceleration 91 +30 Long Shots 93 +25 Agility 90 +40 Heading Acc. +30 Positioning 93 +30 Vision 91 +25 Balance 90 +40 Jumping 97 +15 Sprint Speed 93 +30 Short Pass 93 +25 Ball Control 92 +30 Strength 94 +35 Shot Power 96 +25 Dribbling 92 +35 Composure 95 +30 Stamina 92 3 8 in 3 months in 3 months 75% 25%</t>
+          <t>Tiny Tim Unlocked by completing the Tiny Tim task in the Perfect Volley objective Nico Williams 89 LM PAC 95 SHO 80 PAS 85 DRI 89 DEF 40 PHY 75 RM ST LW R 5 ★ 4 RM 83.8 Nico Williams 93 LM PAC 95 SHO 93 PAS 88 DRI 92 DEF 43 PHY 94 RM ST LW R 5 ★ 5 RM 91.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max Pos. 4 Overall Max. 91 Position ST Max PS 10 Max PS+ 3 UPGRADES +25 OVR 93 LM RM +4 WF 5 +35 Finishing 95 +35 Volleys 96 +35 Reactions 95 +40 Aggression 97 +15 Acceleration 91 +30 Long Shots 93 +25 Agility 90 +40 Heading Acc. +30 Positioning 93 +30 Vision 91 +25 Balance 90 +40 Jumping 97 +15 Sprint Speed 93 +30 Short Pass 93 +25 Ball Control 92 +30 Strength 94 +35 Shot Power 96 +25 Dribbling 92 +35 Composure 95 +30 Stamina 92 3 8 in 3 months in 3 months 76% 24%</t>
         </is>
       </c>
     </row>
@@ -70662,7 +70662,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Defense Wins Championships Unlocked by completing the South Korea vs. Czechia task in the Path to Glory! objective Arrey-Mbi 90 CB PAC 91 SHO 52 PAS 77 DRI 86 DEF 89 PHY 90 LB L 3 ★ 3 CB 89.5 Arrey-Mbi 90 CB PAC 91 SHO 52 PAS 77 DRI 86 DEF 95 PHY 90 LB L 3 ★ 3 CB 90.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 UPGRADES +6 Interceptions 95 +8 Defensive Awareness 94 +6 Sliding Tackle 94 +10 Heading Acc. +6 Standing Tackle 95 in 2 days in 2 days 90% 10%</t>
+          <t>Defense Wins Championships Unlocked by completing the South Korea vs. Czechia task in the Path to Glory! objective Arrey-Mbi 90 CB PAC 91 SHO 52 PAS 77 DRI 86 DEF 89 PHY 90 LB L 3 ★ 3 CB 89.5 Arrey-Mbi 90 CB PAC 91 SHO 52 PAS 77 DRI 86 DEF 95 PHY 90 LB L 3 ★ 3 CB 90.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 UPGRADES +6 Interceptions 95 +8 Defensive Awareness 94 +6 Sliding Tackle 94 +10 Heading Acc. +6 Standing Tackle 95 in 23 hours in 23 hours 90% 10%</t>
         </is>
       </c>
     </row>
@@ -70689,7 +70689,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>The Main Event 2,000 Unlocked in the Token Store for 2000 tokens. Built for the spotlight. Enhance attacking presence and decisive ability to take center stage and define the biggest moments of the match. Doumbia 89 ST PAC 96 SHO 89 PAS 80 DRI 88 DEF 50 PHY 79 LM LW R 4 ★ 4 LM 86.8 Doumbia 97 ST PAC 97 SHO 97 PAS 86 DRI 94 DEF 50 PHY 89 LM LW R 5 ★ 5 ST 94.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 Position ST Excluded Position CB Max PS 10 Max PS+ 3 UPGRADES +50 OVR 97 +4 SM +4 WF +50 Acceleration 96 +50 Sprint Speed 96 +50 Stamina 93 +50 Strength 93 +45 Positioning 97 +45 Finishing 97 +45 Shot Power 96 +50 Ball Control 96 +50 Dribbling 93 +50 Composure 93 +45 Long Shots 96 +45 Volleys 97 +45 Penalties 97 +50 Vision 94 +50 Short Pass 94 +50 Long Pass 92 +50 Reactions 95 +50 Curve 95 +50 Agility 96 +50 Balance 93 4 8 in 4 months in 4 months 97% 3%</t>
+          <t>The Main Event 2,000 Unlocked in the Token Store for 2000 tokens. Built for the spotlight. Enhance attacking presence and decisive ability to take center stage and define the biggest moments of the match. Doumbia 89 ST PAC 96 SHO 89 PAS 80 DRI 88 DEF 50 PHY 79 LM LW R 4 ★ 4 LM 86.8 Doumbia 97 ST PAC 97 SHO 97 PAS 86 DRI 94 DEF 50 PHY 89 LM LW R 5 ★ 5 ST 94.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 Position ST Excluded Position CB Max PS 10 Max PS+ 3 UPGRADES +50 OVR 97 +4 SM +4 WF +50 Acceleration 96 +50 Sprint Speed 96 +50 Stamina 93 +50 Strength 93 +45 Positioning 97 +45 Finishing 97 +45 Shot Power 96 +50 Ball Control 96 +50 Dribbling 93 +50 Composure 93 +45 Long Shots 96 +45 Volleys 97 +45 Penalties 97 +50 Vision 94 +50 Short Pass 94 +50 Long Pass 92 +50 Reactions 95 +50 Curve 95 +50 Agility 96 +50 Balance 93 4 8 in 3 months in 3 months 97% 3%</t>
         </is>
       </c>
     </row>
@@ -70716,7 +70716,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gold Standard 500 Unlocked in the Token Store for 500 tokens. The benchmark of excellence. Upgrade defensive quality and composure to deliver consistent, elite-level performances when it matters most. Nesta 88 CB PAC 87 SHO 43 PAS 65 DRI 80 DEF 88 PHY 86 R 3 ★ 4 CB 88.9 Nesta 94 CB PAC 93 SHO 61 PAS 81 DRI 90 DEF 95 PHY 94 R 3 ★ 5 CB 93.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 UPGRADES +50 OVR 94 +4 WF +50 Acceleration 92 +45 Heading Acc. 94 +45 Defensive Awareness 95 +45 Standing Tackle 95 +50 Sprint Speed 93 +50 Vision 94 +50 Short Pass 94 +45 Sliding Tackle 92 +40 Jumping 92 +40 Stamina 92 +50 Shot Power 92 +50 Long Shots 92 +40 Composure 92 +45 Interceptions 95 +45 Strength 96 +50 Aggression 92 +50 Long Pass 94 +40 Agility 91 +40 Balance 90 +40 Reactions 93 +40 Ball Control 89 +40 Dribbling 90 in 4 months in 4 months 92% 8%</t>
+          <t>Gold Standard 500 Unlocked in the Token Store for 500 tokens. The benchmark of excellence. Upgrade defensive quality and composure to deliver consistent, elite-level performances when it matters most. Nesta 88 CB PAC 87 SHO 43 PAS 65 DRI 80 DEF 88 PHY 86 R 3 ★ 4 CB 88.9 Nesta 94 CB PAC 93 SHO 61 PAS 81 DRI 90 DEF 95 PHY 94 R 3 ★ 5 CB 93.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 UPGRADES +50 OVR 94 +4 WF +50 Acceleration 92 +45 Heading Acc. 94 +45 Defensive Awareness 95 +45 Standing Tackle 95 +50 Sprint Speed 93 +50 Vision 94 +50 Short Pass 94 +45 Sliding Tackle 92 +40 Jumping 92 +40 Stamina 92 +50 Shot Power 92 +50 Long Shots 92 +40 Composure 92 +45 Interceptions 95 +45 Strength 96 +50 Aggression 92 +50 Long Pass 94 +40 Agility 91 +40 Balance 90 +40 Reactions 93 +40 Ball Control 89 +40 Dribbling 90 in 3 months in 3 months 92% 8%</t>
         </is>
       </c>
     </row>
@@ -70743,7 +70743,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>One Step Ahead 100 Unlocked in the Token Store for 100 tokens. Sharp thinking meets sharper movement. Boost dribbling to glide past pressure and stay a move ahead of every defender. Calba 91 ST PAC 92 SHO 91 PAS 88 DRI 90 DEF 44 PHY 80 RM LM LW R 4 ★ 5 RM 89.5 Calba 91 ST PAC 92 SHO 91 PAS 88 DRI 96 DEF 44 PHY 80 RM LM LW R 5 ★ 5 RM 92.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 UPGRADES +4 SM +10 Agility 93 +10 Ball Control 94 +10 Composure +10 Balance 93 +10 Reactions 95 +10 Dribbling 8 in 4 months in 2 days 94% 6%</t>
+          <t>One Step Ahead 100 Unlocked in the Token Store for 100 tokens. Sharp thinking meets sharper movement. Boost dribbling to glide past pressure and stay a move ahead of every defender. Calba 91 ST PAC 92 SHO 91 PAS 88 DRI 90 DEF 44 PHY 80 RM LM LW R 4 ★ 5 RM 89.5 Calba 91 ST PAC 92 SHO 91 PAS 88 DRI 96 DEF 44 PHY 80 RM LM LW R 5 ★ 5 RM 92.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS 10 UPGRADES +4 SM +10 Agility 93 +10 Ball Control 94 +10 Composure +10 Balance 93 +10 Reactions 95 +10 Dribbling 8 in 3 months in 1 day 94% 6%</t>
         </is>
       </c>
     </row>
@@ -70770,7 +70770,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Path to Glory 15 Unlocked in the Token Store for 15 tokens. Transform your favourite player into a Path to Glory player. This item rarity offers five nation links to chemistry! REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 4 months in 12 days 24% 76%</t>
+          <t>Path to Glory 15 Unlocked in the Token Store for 15 tokens. Transform your favourite player into a Path to Glory player. This item rarity offers five nation links to chemistry! REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 3 months in 11 days 23% 77%</t>
         </is>
       </c>
     </row>
@@ -70797,7 +70797,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Five Star Phenom II Unlocked by completing the Season 8 Exhibition objective Ounahi 91 CM PAC 91 SHO 93 PAS 94 DRI 95 DEF 81 PHY 83 CAM R 4 ★ 4 CM 89.7 Ounahi 91 CM PAC 91 SHO 93 PAS 94 DRI 95 DEF 81 PHY 83 CAM R 5 ★ 5 CM 91.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 UPGRADES +4 SM 5 +4 WF 5 in 27 days in 27 days 87% 13%</t>
+          <t>Five Star Phenom II Unlocked by completing the Season 8 Exhibition objective Ounahi 91 CM PAC 91 SHO 93 PAS 94 DRI 95 DEF 81 PHY 83 CAM R 4 ★ 4 CM 89.7 Ounahi 91 CM PAC 91 SHO 93 PAS 94 DRI 95 DEF 81 PHY 83 CAM R 5 ★ 5 CM 91.0 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 UPGRADES +4 SM 5 +4 WF 5 in 26 days in 26 days 87% 13%</t>
         </is>
       </c>
     </row>
@@ -70824,7 +70824,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Iron 9 2 Unlocked by completing the Score in 30 task in the Season 8 Exhibition objective Matthäus 91 CM PAC 89 SHO 88 PAS 89 DRI 83 DEF 91 PHY 84 RB CB CDM RM CAM ST R 4 ★ 5 CM 83.6 Matthäus 93 CM PAC 91 SHO 95 PAS 93 DRI 91 DEF 91 PHY 90 RB CB CDM RM CAM ST R 4 ★ 5 CM 91.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Position ST Max PS 10 Max PS+ 3 UPGRADES +15 OVR 93 +15 Sprint Speed 90 +20 Positioning 95 +20 Fk Accuracy 93 +20 Short Pass 95 +10 Stamina 95 +15 Acceleration 90 +20 Long Pass 88 +20 Curve 95 +10 Composure 92 +20 Finishing 94 +20 Long Shots 93 +20 Volleys 93 +10 Agility 90 +10 Balance 90 +10 Reactions 94 +20 Shot Power 93 +20 Penalties 93 +20 Vision 92 +20 Crossing 89 +10 Ball Control 92 +10 Dribbling 92 +10 Strength 94 +10 Aggression 88 3 8 in 27 days in 27 days 93% 7%</t>
+          <t>The Iron 9 2 Unlocked by completing the Score in 30 task in the Season 8 Exhibition objective Matthäus 91 CM PAC 89 SHO 88 PAS 89 DRI 83 DEF 91 PHY 84 RB CB CDM RM CAM ST R 4 ★ 5 CM 83.6 Matthäus 93 CM PAC 91 SHO 95 PAS 93 DRI 91 DEF 91 PHY 90 RB CB CDM RM CAM ST R 4 ★ 5 CM 91.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Position ST Max PS 10 Max PS+ 3 UPGRADES +15 OVR 93 +15 Sprint Speed 90 +20 Positioning 95 +20 Fk Accuracy 93 +20 Short Pass 95 +10 Stamina 95 +15 Acceleration 90 +20 Long Pass 88 +20 Curve 95 +10 Composure 92 +20 Finishing 94 +20 Long Shots 93 +20 Volleys 93 +10 Agility 90 +10 Balance 90 +10 Reactions 94 +20 Shot Power 93 +20 Penalties 93 +20 Vision 92 +20 Crossing 89 +10 Ball Control 92 +10 Dribbling 92 +10 Strength 94 +10 Aggression 88 3 8 in 26 days in 26 days 93% 7%</t>
         </is>
       </c>
     </row>
@@ -70851,7 +70851,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trequartista 2 Unlocked by completing the Score in 25 task in the Season 8 Exhibition objective Cambiasso 89 CDM PAC 85 SHO 84 PAS 88 DRI 88 DEF 89 PHY 86 CM L 5 ★ 5 CM 87.3 Cambiasso 93 CDM PAC 92 SHO 94 PAS 91 DRI 94 DEF 89 PHY 86 CM L 5 ★ 5 CM 92.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CM Max PS 10 Max PS+ 3 UPGRADES +10 OVR 93 +4 WF 5 +10 Acceleration 92 +15 Agility 92 +15 Reactions 94 +15 Balance 92 +10 Sprint Speed 92 +15 Finishing 94 +15 Shot Power 95 +10 Short Pass 94 +10 Curve 95 +10 Long Pass 94 +15 Positioning 93 +10 Vision 93 +10 Crossing 90 +10 Fk Accuracy 95 +15 Composure 93 +15 Long Shots 95 +15 Volleys 93 +15 Penalties 93 +15 Ball Control 94 +15 Dribbling 95 3 8 in 27 days in 27 days 86% 14%</t>
+          <t>Trequartista 2 Unlocked by completing the Score in 25 task in the Season 8 Exhibition objective Cambiasso 89 CDM PAC 85 SHO 84 PAS 88 DRI 88 DEF 89 PHY 86 CM L 5 ★ 5 CM 87.3 Cambiasso 93 CDM PAC 92 SHO 94 PAS 91 DRI 94 DEF 89 PHY 86 CM L 5 ★ 5 CM 92.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Position CM Max PS 10 Max PS+ 3 UPGRADES +10 OVR 93 +4 WF 5 +10 Acceleration 92 +15 Agility 92 +15 Reactions 94 +15 Balance 92 +10 Sprint Speed 92 +15 Finishing 94 +15 Shot Power 95 +10 Short Pass 94 +10 Curve 95 +10 Long Pass 94 +15 Positioning 93 +10 Vision 93 +10 Crossing 90 +10 Fk Accuracy 95 +15 Composure 93 +15 Long Shots 95 +15 Volleys 93 +15 Penalties 93 +15 Ball Control 94 +15 Dribbling 95 3 8 in 26 days in 26 days 86% 14%</t>
         </is>
       </c>
     </row>
@@ -71067,7 +71067,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Old School Winger [SP 1] 8 Unlocked by reaching level 1 in the Standard Season Pass. Cristiano Ronaldo 90 ST PAC 90 SHO 93 PAS 82 DRI 89 DEF 40 PHY 83 R 5 ★ 4 ST 87.2 Cristiano Ronaldo 92 ST PAC 94 SHO 93 PAS 85 DRI 94 DEF 40 PHY 83 R 5 ★ 4 ST 90.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Excluded Position CB, CM Max PS 10 UPGRADES +2 OVR 92 +5 Sprint Speed 95 +3 Vision 94 +3 Crossing 94 +6 Dribbling 95 +6 Composure 95 +5 Acceleration 94 +6 Balance 96 +6 Reactions 95 +6 Ball Control 96 +3 Fk Accuracy 95 +3 Short Pass 96 +3 Long Pass 95 +3 Curve 95 +6 Agility 94 8 in 4 months in 1 month 90% 10%</t>
+          <t>Old School Winger [SP 1] 8 Unlocked by reaching level 1 in the Standard Season Pass. Cristiano Ronaldo 90 ST PAC 90 SHO 93 PAS 82 DRI 89 DEF 40 PHY 83 R 5 ★ 4 ST 87.2 Cristiano Ronaldo 92 ST PAC 94 SHO 93 PAS 85 DRI 94 DEF 40 PHY 83 R 5 ★ 4 ST 90.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Excluded Position CB, CM Max PS 10 UPGRADES +2 OVR 92 +5 Sprint Speed 95 +3 Vision 94 +3 Crossing 94 +6 Dribbling 95 +6 Composure 95 +5 Acceleration 94 +6 Balance 96 +6 Reactions 95 +6 Ball Control 96 +3 Fk Accuracy 95 +3 Short Pass 96 +3 Long Pass 95 +3 Curve 95 +6 Agility 94 8 in 3 months in 1 month 90% 10%</t>
         </is>
       </c>
     </row>
@@ -71094,7 +71094,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Try Again Tomorrow [SP 8] 3 Unlocked by reaching level 8 in the Standard Season Pass. Calafiori 90 LB PAC 87 SHO 80 PAS 85 DRI 89 DEF 90 PHY 91 CB L 3 ★ 4 LB 86.7 Calafiori 92 LB PAC 92 SHO 80 PAS 85 DRI 89 DEF 94 PHY 94 CB L 3 ★ 4 LB 91.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 UPGRADES +2 OVR 92 +6 Interceptions 94 +6 Heading Acc. 93 +3 Strength 93 +3 Aggression 94 +5 Acceleration 93 +5 Sprint Speed 94 +6 Defensive Awareness 94 +6 Standing Tackle 95 +6 Sliding Tackle 94 +3 Jumping 94 +3 Stamina 94 8 in 4 months in 1 month 94% 6%</t>
+          <t>Try Again Tomorrow [SP 8] 3 Unlocked by reaching level 8 in the Standard Season Pass. Calafiori 90 LB PAC 87 SHO 80 PAS 85 DRI 89 DEF 90 PHY 91 CB L 3 ★ 4 LB 86.7 Calafiori 92 LB PAC 92 SHO 80 PAS 85 DRI 89 DEF 94 PHY 94 CB L 3 ★ 4 LB 91.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 UPGRADES +2 OVR 92 +6 Interceptions 94 +6 Heading Acc. 93 +3 Strength 93 +3 Aggression 94 +5 Acceleration 93 +5 Sprint Speed 94 +6 Defensive Awareness 94 +6 Standing Tackle 95 +6 Sliding Tackle 94 +3 Jumping 94 +3 Stamina 94 8 in 3 months in 1 month 94% 6%</t>
         </is>
       </c>
     </row>
@@ -71121,7 +71121,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Afterburner [SP+ 10] 5 Unlocked by reaching level 10 in the Premium Season Pass. Zézé 91 CB PAC 86 SHO 50 PAS 80 DRI 85 DEF 91 PHY 91 L 3 ★ 4 CB 89.9 Zézé 92 CB PAC 93 SHO 50 PAS 80 DRI 85 DEF 91 PHY 91 L 3 ★ 4 CB 92.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 Max PS 10 UPGRADES +1 OVR 93 +10 PAC 93 8 in 4 months in 1 month 63% 37%</t>
+          <t>Afterburner [SP+ 10] 5 Unlocked by reaching level 10 in the Premium Season Pass. Zézé 91 CB PAC 86 SHO 50 PAS 80 DRI 85 DEF 91 PHY 91 L 3 ★ 4 CB 89.9 Zézé 92 CB PAC 93 SHO 50 PAS 80 DRI 85 DEF 91 PHY 91 L 3 ★ 4 CB 92.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 Max PS 10 UPGRADES +1 OVR 93 +10 PAC 93 8 in 3 months in 1 month 64% 36%</t>
         </is>
       </c>
     </row>
@@ -71148,7 +71148,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>No Looking Back [SP+ 18] Unlocked by reaching level 18 in the Premium Season Pass. Marcos Llorente 95 RB PAC 96 SHO 90 PAS 93 DRI 91 DEF 91 PHY 94 RM CM R 5 ★ 5 CM 92.5 Marcos Llorente 95 RB PAC 96 SHO 90 PAS 93 DRI 91 DEF 91 PHY 94 RM CM R 5 ★ 5 CM 93.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max PS 10 Max PS+ 3 UPGRADES 3 8 in 4 months in 1 month 95% 5%</t>
+          <t>No Looking Back [SP+ 18] Unlocked by reaching level 18 in the Premium Season Pass. Marcos Llorente 95 RB PAC 96 SHO 90 PAS 93 DRI 91 DEF 91 PHY 94 RM CM R 5 ★ 5 CM 92.5 Marcos Llorente 95 RB PAC 96 SHO 90 PAS 93 DRI 91 DEF 91 PHY 94 RM CM R 5 ★ 5 CM 93.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Max PS 10 Max PS+ 3 UPGRADES 3 8 in 3 months in 1 month 95% 5%</t>
         </is>
       </c>
     </row>
@@ -71175,7 +71175,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Covering Ground [SP+ 1] 8 Unlocked by reaching level 1 in the Premium Season Pass. Sithole 90 CDM PAC 90 SHO 80 PAS 87 DRI 87 DEF 90 PHY 92 CM R 4 ★ 4 CM 89.4 Sithole 93 CDM PAC 92 SHO 80 PAS 92 DRI 89 DEF 93 PHY 94 CM R 4 ★ 4 CM 93.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 Max PS 10 UPGRADES +3 OVR 95 +2 Acceleration 93 +2 Sprint Speed 93 +6 Vision 96 +2 Strength 95 +2 Aggression 95 +6 Crossing 95 +6 Short Pass 97 +6 Long Pass 95 +3 Sliding Tackle 94 +2 Jumping 95 +2 Stamina 97 +6 Fk Accuracy 96 +3 Heading Acc. 95 +3 Defensive Awareness 95 +3 Standing Tackle 95 +6 Curve 96 +2 Agility 97 +2 Ball Control 95 +2 Dribbling 94 +3 Interceptions 97 +2 Balance 96 +2 Reactions 96 +2 Composure 96 8 in 4 months in 1 month 95% 5%</t>
+          <t>Covering Ground [SP+ 1] 8 Unlocked by reaching level 1 in the Premium Season Pass. Sithole 90 CDM PAC 90 SHO 80 PAS 87 DRI 87 DEF 90 PHY 92 CM R 4 ★ 4 CM 89.4 Sithole 93 CDM PAC 92 SHO 80 PAS 92 DRI 89 DEF 93 PHY 94 CM R 4 ★ 4 CM 93.1 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 92 Max PS 10 UPGRADES +3 OVR 95 +2 Acceleration 93 +2 Sprint Speed 93 +6 Vision 96 +2 Strength 95 +2 Aggression 95 +6 Crossing 95 +6 Short Pass 97 +6 Long Pass 95 +3 Sliding Tackle 94 +2 Jumping 95 +2 Stamina 97 +6 Fk Accuracy 96 +3 Heading Acc. 95 +3 Defensive Awareness 95 +3 Standing Tackle 95 +6 Curve 96 +2 Agility 97 +2 Ball Control 95 +2 Dribbling 94 +3 Interceptions 97 +2 Balance 96 +2 Reactions 96 +2 Composure 96 8 in 3 months in 1 month 95% 5%</t>
         </is>
       </c>
     </row>
@@ -71202,7 +71202,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Finesse Shot+ [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Valverde 94 CM PAC 94 SHO 92 PAS 93 DRI 92 DEF 90 PHY 90 RB CDM RM RW R 5 ★ 5 CM 93.3 Valverde 94 CM PAC 94 SHO 92 PAS 93 DRI 92 DEF 90 PHY 90 RB CDM RM RW R 5 ★ 5 CM 94.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 94 Max PS+ 3 UPGRADES 4 in 4 months in 1 month 100% 0%</t>
+          <t>Finesse Shot+ [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Valverde 94 CM PAC 94 SHO 92 PAS 93 DRI 92 DEF 90 PHY 90 RB CDM RM RW R 5 ★ 5 CM 93.3 Valverde 94 CM PAC 94 SHO 92 PAS 93 DRI 92 DEF 90 PHY 90 RB CDM RM RW R 5 ★ 5 CM 94.8 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 94 Max PS+ 3 UPGRADES 4 in 3 months in 1 month 100% 0%</t>
         </is>
       </c>
     </row>
@@ -71229,7 +71229,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deadeye [SP 21] 3 Unlocked by reaching level 21 in the Standard Season Pass. Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 85.6 Bobb 89 RW PAC 93 SHO 92 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 LW 90.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 UPGRADES +1 OVR +5 Positioning 93 +5 Shot Power 96 +5 Volleys 93 +5 Penalties +5 Finishing 96 +5 Long Shots 95 3 8 in 4 months in 1 month 90% 10%</t>
+          <t>Deadeye [SP 21] 3 Unlocked by reaching level 21 in the Standard Season Pass. Bobb 88 RW PAC 93 SHO 87 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 RM 85.6 Bobb 89 RW PAC 93 SHO 92 PAS 88 DRI 93 DEF 48 PHY 69 RM LW L 5 ★ 4 LW 90.2 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS 10 Max PS+ 3 UPGRADES +1 OVR +5 Positioning 93 +5 Shot Power 96 +5 Volleys 93 +5 Penalties +5 Finishing 96 +5 Long Shots 95 3 8 in 3 months in 1 month 90% 10%</t>
         </is>
       </c>
     </row>
@@ -71256,7 +71256,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Doué 96 RW PAC 96 SHO 95 PAS 92 DRI 99 DEF 67 PHY 88 RM CM LW R 5 ★ 5 RM 93.5 Doué 96 RW PAC 96 SHO 95 PAS 92 DRI 99 DEF 67 PHY 88 RM CM LW R 5 ★ 5 RM 93.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 4 months in 1 month 57% 43%</t>
+          <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Doué 96 RW PAC 96 SHO 95 PAS 92 DRI 99 DEF 67 PHY 88 RM CM LW R 5 ★ 5 RM 93.5 Doué 96 RW PAC 96 SHO 95 PAS 92 DRI 99 DEF 67 PHY 88 RM CM LW R 5 ★ 5 RM 93.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 3 months in 1 month 57% 43%</t>
         </is>
       </c>
     </row>
@@ -71283,7 +71283,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Intercept+ [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Álvarez 93 CDM PAC 90 SHO 80 PAS 87 DRI 91 DEF 95 PHY 93 CM R 4 ★ 4 CM 91.3 Álvarez 93 CDM PAC 90 SHO 80 PAS 87 DRI 91 DEF 93 PHY 93 CM R 4 ★ 4 CM 92.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 93 Max PS+ 3 UPGRADES 4 in 4 months in 1 month 98% 2%</t>
+          <t>Intercept+ [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Álvarez 93 CDM PAC 90 SHO 80 PAS 87 DRI 91 DEF 95 PHY 93 CM R 4 ★ 4 CM 91.3 Álvarez 93 CDM PAC 90 SHO 80 PAS 87 DRI 91 DEF 93 PHY 93 CM R 4 ★ 4 CM 92.9 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 93 Max PS+ 3 UPGRADES 4 in 3 months in 1 month 98% 2%</t>
         </is>
       </c>
     </row>
@@ -71310,7 +71310,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>WTSS Journey 3 - Midfielder [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. Beckenbauer 71 CDM PAC 70 SHO 52 PAS 76 DRI 64 DEF 80 PHY 70 CB CM R 3 ★ 4 CM 67.5 Beckenbauer 92 CDM PAC 90 SHO 81 PAS 93 DRI 92 DEF 89 PHY 90 CB CM R 4 ★ 5 CM 90.2 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CAM, CM, CDM Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +2 PAS 93 +4 WF 5 +5 Finishing 90 +10 Reactions 91 +5 Acceleration 90 +5 Shot Power 91 +10 Balance 92 +10 Ball Control 92 +5 Sprint Speed 90 +5 Long Shots 91 +5 Penalties 88 +10 Dribbling 93 +5 Positioning 90 +5 Volleys 88 +10 Agility 92 +10 Composure 90 3 8 Show less in 2 days in 2 days 84% 16%</t>
+          <t>WTSS Journey 3 - Midfielder [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. Beckenbauer 71 CDM PAC 70 SHO 52 PAS 76 DRI 64 DEF 80 PHY 70 CB CM R 3 ★ 4 CM 67.5 Beckenbauer 92 CDM PAC 90 SHO 81 PAS 93 DRI 92 DEF 89 PHY 90 CB CM R 4 ★ 5 CM 90.2 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CAM, CM, CDM Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +2 PAS 93 +4 WF 5 +5 Finishing 90 +10 Reactions 91 +5 Acceleration 90 +5 Shot Power 91 +10 Balance 92 +10 Ball Control 92 +5 Sprint Speed 90 +5 Long Shots 91 +5 Penalties 88 +10 Dribbling 93 +5 Positioning 90 +5 Volleys 88 +10 Agility 92 +10 Composure 90 3 8 Show less in 23 hours in 23 hours 84% 16%</t>
         </is>
       </c>
     </row>
@@ -71337,7 +71337,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bruiser+ [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 CB 88.7 van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 CB 91.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 2 UPGRADES 3 in 2 days in 2 days 91% 9%</t>
+          <t>Bruiser+ [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 CB 88.7 van de Ven 90 CB PAC 94 SHO 52 PAS 71 DRI 81 DEF 88 PHY 88 L 3 ★ 3 CB 91.4 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 91 Max PS+ 2 UPGRADES 3 in 23 hours in 23 hours 91% 9%</t>
         </is>
       </c>
     </row>
@@ -71364,7 +71364,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Incisive Pass+ [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Frattesi 90 CM PAC 92 SHO 87 PAS 89 DRI 92 DEF 86 PHY 87 CAM R 4 ★ 4 CM 87.4 Frattesi 90 CM PAC 92 SHO 87 PAS 89 DRI 92 DEF 86 PHY 87 CAM R 4 ★ 4 CM 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 UPGRADES 3 in 2 days in 2 days 85% 15%</t>
+          <t>Incisive Pass+ [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Frattesi 90 CM PAC 92 SHO 87 PAS 89 DRI 92 DEF 86 PHY 87 CAM R 4 ★ 4 CM 87.4 Frattesi 90 CM PAC 92 SHO 87 PAS 89 DRI 92 DEF 86 PHY 87 CAM R 4 ★ 4 CM 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 90 Max PS+ 2 UPGRADES 3 in 23 hours in 23 hours 85% 15%</t>
         </is>
       </c>
     </row>
@@ -71391,7 +71391,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Defender Round Out [SP 1] 10 Unlocked by reaching level 1 in the Standard Season Pass. Timber 88 RB PAC 87 SHO 54 PAS 83 DRI 86 DEF 88 PHY 88 CB LB RM R 4 ★ 5 LB 85.6 Timber 89 RB PAC 92 SHO 54 PAS 83 DRI 87 DEF 89 PHY 91 CB LB RM R 4 ★ 5 LB 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +1 OVR +5 Acceleration 91 +5 Sprint Speed 92 +1 Interceptions 93 +1 Heading Acc. 94 +1 Defensive Awareness 93 +5 Reactions 93 +5 Composure 93 +5 Standing Tackle 91 +5 Sliding Tackle 92 +2 Jumping 93 +2 Stamina 92 +2 Strength 93 +5 Aggression 92 8 in 2 days in 2 days 91% 9%</t>
+          <t>Defender Round Out [SP 1] 10 Unlocked by reaching level 1 in the Standard Season Pass. Timber 88 RB PAC 87 SHO 54 PAS 83 DRI 86 DEF 88 PHY 88 CB LB RM R 4 ★ 5 LB 85.6 Timber 89 RB PAC 92 SHO 54 PAS 83 DRI 87 DEF 89 PHY 91 CB LB RM R 4 ★ 5 LB 89.3 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Max PS 10 UPGRADES +1 OVR +5 Acceleration 91 +5 Sprint Speed 92 +1 Interceptions 93 +1 Heading Acc. 94 +1 Defensive Awareness 93 +5 Reactions 93 +5 Composure 93 +5 Standing Tackle 91 +5 Sliding Tackle 92 +2 Jumping 93 +2 Stamina 92 +2 Strength 93 +5 Aggression 92 8 in 23 hours in 23 hours 91% 9%</t>
         </is>
       </c>
     </row>
@@ -71418,7 +71418,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Attacker Round Out [SP+ 1] 20 Unlocked by reaching level 1 in the Premium Season Pass. Carlos Espí 88 ST PAC 91 SHO 86 PAS 80 DRI 88 DEF 58 PHY 94 R 4 ★ 4 ST 86.9 Carlos Espí 90 ST PAC 93 SHO 90 PAS 84 DRI 92 DEF 58 PHY 94 R 4 ★ 4 ST 89.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Excluded Position CB Max PS 10 UPGRADES +2 OVR 91 +3 Acceleration 93 +5 Agility 94 +5 Balance 93 +3 Sprint Speed 94 +5 Long Pass 94 +2 Curve 92 +2 Composure 95 +5 Positioning 93 +5 Finishing 94 +3 Shot Power 93 +2 Reactions 92 +5 Ball Control 94 +3 Long Shots 92 +3 Volleys 94 +3 Penalties 94 +5 Short Pass 95 +5 Dribbling 95 +5 Vision 93 +2 Crossing 94 +2 Fk Accuracy 92 8 in 2 days in 2 days 93% 7%</t>
+          <t>Attacker Round Out [SP+ 1] 20 Unlocked by reaching level 1 in the Premium Season Pass. Carlos Espí 88 ST PAC 91 SHO 86 PAS 80 DRI 88 DEF 58 PHY 94 R 4 ★ 4 ST 86.9 Carlos Espí 90 ST PAC 93 SHO 90 PAS 84 DRI 92 DEF 58 PHY 94 R 4 ★ 4 ST 89.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 89 Excluded Position CB Max PS 10 UPGRADES +2 OVR 91 +3 Acceleration 93 +5 Agility 94 +5 Balance 93 +3 Sprint Speed 94 +5 Long Pass 94 +2 Curve 92 +2 Composure 95 +5 Positioning 93 +5 Finishing 94 +3 Shot Power 93 +2 Reactions 92 +5 Ball Control 94 +3 Long Shots 92 +3 Volleys 94 +3 Penalties 94 +5 Short Pass 95 +5 Dribbling 95 +5 Vision 93 +2 Crossing 94 +2 Fk Accuracy 92 8 in 23 hours in 23 hours 93% 7%</t>
         </is>
       </c>
     </row>
@@ -71445,7 +71445,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>WTSS Journey 2 - Attacker [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Garrincha 70 RW PAC 82 SHO 64 PAS 67 DRI 78 DEF 34 PHY 48 RM R 5 ★ 4 RM 68.5 Garrincha 90 RW PAC 90 SHO 90 PAS 87 DRI 89 DEF 34 PHY 67 RM R 5 ★ 4 RM 86.7 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position ST, RW, LW Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +3 WF 4 +10 Acceleration 90 +10 Sprint Speed 90 +10 Finishing 90 +10 Positioning 90 +10 Volleys 89 +10 Penalties 90 +10 Curve 90 +15 Agility 92 +15 Balance 89 +15 Reactions 89 +10 Shot Power 91 +10 Long Shots 90 +15 Ball Control 88 +15 Dribbling 89 +15 Composure 88 2 8 in 2 days in 2 days 68% 32%</t>
+          <t>WTSS Journey 2 - Attacker [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Garrincha 70 RW PAC 82 SHO 64 PAS 67 DRI 78 DEF 34 PHY 48 RM R 5 ★ 4 RM 68.5 Garrincha 90 RW PAC 90 SHO 90 PAS 87 DRI 89 DEF 34 PHY 67 RM R 5 ★ 4 RM 86.7 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position ST, RW, LW Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +3 WF 4 +10 Acceleration 90 +10 Sprint Speed 90 +10 Finishing 90 +10 Positioning 90 +10 Volleys 89 +10 Penalties 90 +10 Curve 90 +15 Agility 92 +15 Balance 89 +15 Reactions 89 +10 Shot Power 91 +10 Long Shots 90 +15 Ball Control 88 +15 Dribbling 89 +15 Composure 88 2 8 in 23 hours in 23 hours 69% 31%</t>
         </is>
       </c>
     </row>
@@ -71472,7 +71472,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>WTSS Journey 2 - Defender [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Koeman 71 CB PAC 70 SHO 72 PAS 71 DRI 68 DEF 82 PHY 73 CDM R 3 ★ 3 CB 62.0 Koeman 90 CB PAC 87 SHO 72 PAS 80 DRI 83 DEF 92 PHY 87 CDM R 4 ★ 4 CB 83.8 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CB, LB, RB Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +2 PAC 87 +5 Agility 88 +5 Balance 88 +5 Reactions 90 +5 Composure 90 +10 Standing Tackle 92 +10 Sliding Tackle 92 +10 Interceptions 93 +10 Heading Acc. 94 +10 Defensive Awareness 90 2 8 in 2 days in 2 days 74% 26%</t>
+          <t>WTSS Journey 2 - Defender [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Koeman 71 CB PAC 70 SHO 72 PAS 71 DRI 68 DEF 82 PHY 73 CDM R 3 ★ 3 CB 62.0 Koeman 90 CB PAC 87 SHO 72 PAS 80 DRI 83 DEF 92 PHY 87 CDM R 4 ★ 4 CB 83.8 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CB, LB, RB Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +2 PAC 87 +5 Agility 88 +5 Balance 88 +5 Reactions 90 +5 Composure 90 +10 Standing Tackle 92 +10 Sliding Tackle 92 +10 Interceptions 93 +10 Heading Acc. 94 +10 Defensive Awareness 90 2 8 in 23 hours in 23 hours 74% 26%</t>
         </is>
       </c>
     </row>
@@ -71499,7 +71499,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>WTSS Journey 3 - Attacker [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. Garrincha 70 RW PAC 82 SHO 64 PAS 67 DRI 78 DEF 34 PHY 48 RM R 5 ★ 4 RM 68.5 Garrincha 92 RW PAC 92 SHO 92 PAS 87 DRI 93 DEF 34 PHY 67 RM R 5 ★ 4 RM 89.9 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position ST, RW, LW Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +4 SM +5 Acceleration 92 +5 Sprint Speed 92 +5 Positioning 93 +5 Finishing 94 +5 Curve 93 +5 Balance 94 +5 Reactions 93 +5 Ball Control 94 +5 Dribbling 94 +5 Composure 93 3 8 in 2 days in 2 days 72% 28%</t>
+          <t>WTSS Journey 3 - Attacker [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. Garrincha 70 RW PAC 82 SHO 64 PAS 67 DRI 78 DEF 34 PHY 48 RM R 5 ★ 4 RM 68.5 Garrincha 92 RW PAC 92 SHO 92 PAS 87 DRI 93 DEF 34 PHY 67 RM R 5 ★ 4 RM 89.9 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position ST, RW, LW Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +4 SM +5 Acceleration 92 +5 Sprint Speed 92 +5 Positioning 93 +5 Finishing 94 +5 Curve 93 +5 Balance 94 +5 Reactions 93 +5 Ball Control 94 +5 Dribbling 94 +5 Composure 93 3 8 in 23 hours in 23 hours 73% 27%</t>
         </is>
       </c>
     </row>
@@ -71526,7 +71526,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>WTSS Journey 3 - Defender [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. Petit 74 CDM PAC 70 SHO 70 PAS 85 DRI 72 DEF 74 PHY 76 LB CM L 3 ★ 3 CM 65.3 Petit 92 CDM PAC 90 SHO 70 PAS 87 DRI 87 DEF 92 PHY 93 LB CM L 4 ★ 5 CM 89.0 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CB, LB, RB Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +3 PAC 90 +3 SM 4 +4 WF +5 Reactions 93 +5 Ball Control 88 +5 Dribbling 88 +5 Composure 93 +5 Vision 88 +5 Short Pass 88 +5 Long Pass 88 +10 Aggression 88 +10 Jumping 90 +10 Stamina 95 +10 Strength 93 3 8 Show less in 2 days in 2 days 75% 25%</t>
+          <t>WTSS Journey 3 - Defender [SP 21] Unlocked by reaching level 21 in the Standard Season Pass. Petit 74 CDM PAC 70 SHO 70 PAS 85 DRI 72 DEF 74 PHY 76 LB CM L 3 ★ 3 CM 65.3 Petit 92 CDM PAC 90 SHO 70 PAS 87 DRI 87 DEF 92 PHY 93 LB CM L 4 ★ 5 CM 89.0 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 90 Overall Max. 90 Position CB, LB, RB Max PS 10 Max PS+ 2 UPGRADES +2 OVR 92 +3 PAC 90 +3 SM 4 +4 WF +5 Reactions 93 +5 Ball Control 88 +5 Dribbling 88 +5 Composure 93 +5 Vision 88 +5 Short Pass 88 +5 Long Pass 88 +10 Aggression 88 +10 Jumping 90 +10 Stamina 95 +10 Strength 93 3 8 Show less in 23 hours in 23 hours 76% 24%</t>
         </is>
       </c>
     </row>
@@ -71553,7 +71553,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>WTSS Journey 2 - Midfielder [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Petit 74 CDM PAC 70 SHO 70 PAS 85 DRI 72 DEF 74 PHY 76 LB CM L 3 ★ 3 CM 65.3 Petit 90 CDM PAC 88 SHO 74 PAS 92 DRI 83 DEF 89 PHY 89 LB CM L 4 ★ 4 CM 84.9 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CAM, CDM, CM Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +4 SHO 88 +1 SM 4 +5 Sprint Speed 88 +15 Short Pass 93 +15 Interceptions 90 +15 Stamina 90 +5 Acceleration 88 +15 Fk Accuracy 89 +15 Defensive Awareness 89 +15 Strength 89 +15 Vision 91 +15 Long Pass 92 +15 Heading Acc. 89 +15 Sliding Tackle 88 +15 Aggression 89 +15 Crossing 89 +15 Curve 90 +15 Standing Tackle 90 +15 Jumping 89 2 8 Show less in 2 days in 2 days 78% 22%</t>
+          <t>WTSS Journey 2 - Midfielder [SP 8] Unlocked by reaching level 8 in the Standard Season Pass. Petit 74 CDM PAC 70 SHO 70 PAS 85 DRI 72 DEF 74 PHY 76 LB CM L 3 ★ 3 CM 65.3 Petit 90 CDM PAC 88 SHO 74 PAS 92 DRI 83 DEF 89 PHY 89 LB CM L 4 ★ 4 CM 84.9 REQUIREMENTS Rarity World Tour Silver Stars Overall Min. 88 Overall Max. 88 Position CAM, CDM, CM Max PS 10 Max PS+ 1 UPGRADES +2 OVR 90 +4 SHO 88 +1 SM 4 +5 Sprint Speed 88 +15 Short Pass 93 +15 Interceptions 90 +15 Stamina 90 +5 Acceleration 88 +15 Fk Accuracy 89 +15 Defensive Awareness 89 +15 Strength 89 +15 Vision 91 +15 Long Pass 92 +15 Heading Acc. 89 +15 Sliding Tackle 88 +15 Aggression 89 +15 Crossing 89 +15 Curve 90 +15 Standing Tackle 90 +15 Jumping 89 2 8 Show less in 23 hours in 23 hours 78% 22%</t>
         </is>
       </c>
     </row>
@@ -71580,7 +71580,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>WTSS Journey 1 - Attacker [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Garrincha 70 RW PAC 82 SHO 64 PAS 67 DRI 78 DEF 34 PHY 48 RM R 5 ★ 4 RM 68.5 Garrincha 88 RW PAC 88 SHO 86 PAS 87 DRI 87 DEF 34 PHY 67 RM R 5 ★ 4 RM 81.5 REQUIREMENTS Rarity World Tour Silver Stars Position ST, RW, LW Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +1 SM 4 +1 WF 4 +30 Acceleration 88 +30 Sprint Speed 88 +30 Finishing 87 +30 Shot Power 83 +30 Long Shots 88 +30 Positioning 84 +20 Vision 88 +20 Crossing 87 +20 Fk Accuracy 88 +20 Short Pass 90 +20 Long Pass 88 +30 Volleys 87 +30 Penalties 80 +25 Agility 87 +25 Balance 88 +20 Curve 88 +25 Reactions 86 +25 Ball Control 88 +20 Aggression 70 +25 Dribbling 87 +25 Composure 88 +20 Stamina 90 +20 Strength 75 8 in 2 days in 2 days 79% 21%</t>
+          <t>WTSS Journey 1 - Attacker [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Garrincha 70 RW PAC 82 SHO 64 PAS 67 DRI 78 DEF 34 PHY 48 RM R 5 ★ 4 RM 68.5 Garrincha 88 RW PAC 88 SHO 86 PAS 87 DRI 87 DEF 34 PHY 67 RM R 5 ★ 4 RM 81.5 REQUIREMENTS Rarity World Tour Silver Stars Position ST, RW, LW Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +1 SM 4 +1 WF 4 +30 Acceleration 88 +30 Sprint Speed 88 +30 Finishing 87 +30 Shot Power 83 +30 Long Shots 88 +30 Positioning 84 +20 Vision 88 +20 Crossing 87 +20 Fk Accuracy 88 +20 Short Pass 90 +20 Long Pass 88 +30 Volleys 87 +30 Penalties 80 +25 Agility 87 +25 Balance 88 +20 Curve 88 +25 Reactions 86 +25 Ball Control 88 +20 Aggression 70 +25 Dribbling 87 +25 Composure 88 +20 Stamina 90 +20 Strength 75 8 in 23 hours in 23 hours 79% 21%</t>
         </is>
       </c>
     </row>
@@ -71607,7 +71607,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>WTSS Journey 1 - Midfielder [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Beckenbauer 71 CDM PAC 70 SHO 52 PAS 76 DRI 64 DEF 80 PHY 70 CB CM R 3 ★ 4 CM 67.5 Beckenbauer 88 CDM PAC 85 SHO 72 PAS 87 DRI 87 DEF 86 PHY 84 CB CM R 4 ★ 4 CM 81.2 REQUIREMENTS Rarity World Tour Silver Stars Position CAM, CM, CDM Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +20 PHY 84 +1 SM 4 +1 WF 4 +30 Acceleration 85 +30 Sprint Speed 85 +30 Curve 86 +30 Agility 86 +30 Balance 84 +20 Positioning 85 +20 Finishing 87 +20 Shot Power 87 +20 Long Shots 90 +20 Volleys 88 +20 Penalties 85 +30 Reactions 87 +30 Ball Control 85 +30 Vision 86 +30 Crossing 85 +30 Fk Accuracy 88 +30 Short Pass 87 +30 Long Pass 88 +30 Heading Acc. 88 +30 Dribbling 88 +30 Composure 88 +30 Interceptions 85 +30 Defensive Awareness 85 +30 Standing Tackle 86 +30 Sliding Tackle 88 8 Show less in 2 days in 2 days 81% 19%</t>
+          <t>WTSS Journey 1 - Midfielder [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Beckenbauer 71 CDM PAC 70 SHO 52 PAS 76 DRI 64 DEF 80 PHY 70 CB CM R 3 ★ 4 CM 67.5 Beckenbauer 88 CDM PAC 85 SHO 72 PAS 87 DRI 87 DEF 86 PHY 84 CB CM R 4 ★ 4 CM 81.2 REQUIREMENTS Rarity World Tour Silver Stars Position CAM, CM, CDM Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +20 PHY 84 +1 SM 4 +1 WF 4 +30 Acceleration 85 +30 Sprint Speed 85 +30 Curve 86 +30 Agility 86 +30 Balance 84 +20 Positioning 85 +20 Finishing 87 +20 Shot Power 87 +20 Long Shots 90 +20 Volleys 88 +20 Penalties 85 +30 Reactions 87 +30 Ball Control 85 +30 Vision 86 +30 Crossing 85 +30 Fk Accuracy 88 +30 Short Pass 87 +30 Long Pass 88 +30 Heading Acc. 88 +30 Dribbling 88 +30 Composure 88 +30 Interceptions 85 +30 Defensive Awareness 85 +30 Standing Tackle 86 +30 Sliding Tackle 88 8 Show less in 23 hours in 23 hours 81% 19%</t>
         </is>
       </c>
     </row>
@@ -71634,7 +71634,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>WTSS Journey 1 - Defender [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Petit 74 CDM PAC 70 SHO 70 PAS 85 DRI 72 DEF 74 PHY 76 LB CM L 3 ★ 3 CM 65.3 Petit 88 CDM PAC 85 SHO 70 PAS 86 DRI 83 DEF 87 PHY 87 LB CM L 4 ★ 4 CM 80.9 REQUIREMENTS Rarity World Tour Silver Stars Position CB, LB, RB Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +20 SHO 70 +1 SM 4 +1 WF 4 +30 Curve 80 +15 Agility 80 +30 Defensive Awareness 87 +30 Standing Tackle 88 +30 Sliding Tackle 86 +30 Acceleration 85 +30 Sprint Speed 85 +30 Vision 75 +30 Crossing 75 +30 Fk Accuracy 65 +30 Short Pass 85 +30 Long Pass 80 +15 Balance 80 +30 Reactions 88 +15 Ball Control 85 +30 Jumping 80 +30 Stamina 85 +30 Strength 87 +15 Dribbling 85 +30 Composure 88 +30 Interceptions 88 +30 Heading Acc. 87 +30 Aggression 90 8 Show less in 2 days in 2 days 83% 17%</t>
+          <t>WTSS Journey 1 - Defender [SP 3] Unlocked by reaching level 3 in the Standard Season Pass. Petit 74 CDM PAC 70 SHO 70 PAS 85 DRI 72 DEF 74 PHY 76 LB CM L 3 ★ 3 CM 65.3 Petit 88 CDM PAC 85 SHO 70 PAS 86 DRI 83 DEF 87 PHY 87 LB CM L 4 ★ 4 CM 80.9 REQUIREMENTS Rarity World Tour Silver Stars Position CB, LB, RB Max PS 10 Max PS+ 1 UPGRADES +30 OVR 88 +20 SHO 70 +1 SM 4 +1 WF 4 +30 Curve 80 +15 Agility 80 +30 Defensive Awareness 87 +30 Standing Tackle 88 +30 Sliding Tackle 86 +30 Acceleration 85 +30 Sprint Speed 85 +30 Vision 75 +30 Crossing 75 +30 Fk Accuracy 65 +30 Short Pass 85 +30 Long Pass 80 +15 Balance 80 +30 Reactions 88 +15 Ball Control 85 +30 Jumping 80 +30 Stamina 85 +30 Strength 87 +15 Dribbling 85 +30 Composure 88 +30 Interceptions 88 +30 Heading Acc. 87 +30 Aggression 90 8 Show less in 23 hours in 23 hours 83% 17%</t>
         </is>
       </c>
     </row>
@@ -71661,7 +71661,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Doué 96 RW PAC 96 SHO 95 PAS 92 DRI 99 DEF 67 PHY 88 RM CM LW R 5 ★ 5 RM 93.5 Doué 96 RW PAC 96 SHO 95 PAS 92 DRI 99 DEF 67 PHY 88 RM CM LW R 5 ★ 5 RM 93.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 2 days in 2 days 30% 70%</t>
+          <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Doué 96 RW PAC 96 SHO 95 PAS 92 DRI 99 DEF 67 PHY 88 RM CM LW R 5 ★ 5 RM 93.5 Doué 96 RW PAC 96 SHO 95 PAS 92 DRI 99 DEF 67 PHY 88 RM CM LW R 5 ★ 5 RM 93.5 REQUIREMENTS Excluded Rarity World Tour Silver Stars UPGRADES No upgrades in 23 hours in 23 hours 30% 70%</t>
         </is>
       </c>
     </row>
@@ -71877,7 +71877,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Intro to Rewards EVOs Upgrade your qualified Player's attributes and Overall Rating with this Evolution. Trenskow 74 RM PAC 80 SHO 74 PAS 76 DRI 79 DEF 60 PHY 63 CM RW L 4 ★ 3 RM 72.9 Trenskow 75 RM PAC 80 SHO 76 PAS 78 DRI 80 DEF 60 PHY 63 CM RW L 4 ★ 3 RM 73.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Pace Max. 84 UPGRADES +1 OVR +3 Shot Power 80 +3 Vision 80 +4 Long Shots 80 +3 Volleys 79 +3 Short Pass 80 +4 Fk Accuracy 80 +4 Dribbling 81 +4 Reactions 81 +4 Long Pass 79 in 4 months in 4 months 84% 16%</t>
+          <t>Intro to Rewards EVOs Upgrade your qualified Player's attributes and Overall Rating with this Evolution. Trenskow 74 RM PAC 80 SHO 74 PAS 76 DRI 79 DEF 60 PHY 63 CM RW L 4 ★ 3 RM 72.9 Trenskow 75 RM PAC 80 SHO 76 PAS 78 DRI 80 DEF 60 PHY 63 CM RW L 4 ★ 3 RM 73.6 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 82 Pace Max. 84 UPGRADES +1 OVR +3 Shot Power 80 +3 Vision 80 +4 Long Shots 80 +3 Volleys 79 +3 Short Pass 80 +4 Fk Accuracy 80 +4 Dribbling 81 +4 Reactions 81 +4 Long Pass 79 in 3 months in 3 months 84% 16%</t>
         </is>
       </c>
     </row>
@@ -71904,7 +71904,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Club Member Reward Unlocked by being a Club Member on FC 26. Amaiur Sarriegi 81 ST PAC 88 SHO 78 PAS 75 DRI 84 DEF 47 PHY 81 RM RW LW R 4 ★ 4 RW 77.7 Amaiur Sarriegi 81 ST PAC 88 SHO 78 PAS 75 DRI 84 DEF 47 PHY 81 RM RW LW R 4 ★ 4 ST 78.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 83 Position ST UPGRADES ST Advanced Forward + ST Poacher + ST False 9 + ST Target Forward + in 4 months in 4 months 90% 10%</t>
+          <t>Club Member Reward Unlocked by being a Club Member on FC 26. Amaiur Sarriegi 81 ST PAC 88 SHO 78 PAS 75 DRI 84 DEF 47 PHY 81 RM RW LW R 4 ★ 4 RW 77.7 Amaiur Sarriegi 81 ST PAC 88 SHO 78 PAS 75 DRI 84 DEF 47 PHY 81 RM RW LW R 4 ★ 4 ST 78.7 REQUIREMENTS Excluded Rarity World Tour Silver Stars Overall Max. 83 Position ST UPGRADES ST Advanced Forward + ST Poacher + ST False 9 + ST Target Forward + in 3 months in 3 months 90% 10%</t>
         </is>
       </c>
     </row>
@@ -71975,7 +71975,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-16T20:21:44</t>
+          <t>2026-06-17T19:32:59</t>
         </is>
       </c>
     </row>
